--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB285B30-C3CC-400E-9031-FBC135ED69C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89438499-D406-4A88-A889-A198DA4468EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="792">
   <si>
     <t>3-ديوان</t>
   </si>
@@ -2961,7 +2961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E5C9A6-5EC3-4592-9122-0E1001CE6231}">
-  <dimension ref="A1:E696"/>
+  <dimension ref="A1:E699"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.8984375" style="2" bestFit="1" customWidth="1"/>
@@ -3194,7 +3194,7 @@
         <v>537</v>
       </c>
       <c r="D15" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         <v>524</v>
       </c>
       <c r="D20" s="13">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
@@ -3942,7 +3942,7 @@
         <v>44</v>
       </c>
       <c r="D59" s="13">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
@@ -3953,13 +3953,13 @@
         <v>632</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>45</v>
       </c>
       <c r="D60" s="13">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3970,13 +3970,13 @@
         <v>632</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>45</v>
       </c>
       <c r="D61" s="13">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -4106,13 +4106,13 @@
         <v>634</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D69" s="13">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E69" s="1">
         <v>0</v>
@@ -4123,13 +4123,13 @@
         <v>634</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D70" s="13">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
@@ -4174,13 +4174,13 @@
         <v>634</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D73" s="13">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
@@ -4191,13 +4191,13 @@
         <v>634</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D74" s="13">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
@@ -4265,7 +4265,7 @@
         <v>776</v>
       </c>
       <c r="D78" s="13">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E78" s="1">
         <v>0</v>
@@ -4378,13 +4378,13 @@
         <v>638</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D85" s="13">
-        <v>2725</v>
+        <v>150</v>
       </c>
       <c r="E85" s="1">
         <v>0</v>
@@ -4412,13 +4412,13 @@
         <v>638</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C87" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D87" s="13">
-        <v>150</v>
+        <v>2725</v>
       </c>
       <c r="E87" s="1">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>638</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>58</v>
@@ -4480,7 +4480,7 @@
         <v>638</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>58</v>
@@ -4673,7 +4673,7 @@
         <v>64</v>
       </c>
       <c r="D102" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102" s="1">
         <v>0</v>
@@ -5177,13 +5177,13 @@
         <v>650</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D132" s="13">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -5194,13 +5194,13 @@
         <v>650</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D133" s="13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -5245,13 +5245,13 @@
         <v>650</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>85</v>
       </c>
       <c r="D136" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
@@ -5262,13 +5262,13 @@
         <v>650</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>85</v>
       </c>
       <c r="D137" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
@@ -5279,13 +5279,13 @@
         <v>650</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>86</v>
       </c>
       <c r="D138" s="13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
@@ -5296,13 +5296,13 @@
         <v>650</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>86</v>
       </c>
       <c r="D139" s="13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
@@ -5659,7 +5659,7 @@
         <v>470</v>
       </c>
       <c r="D160" s="13">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E160" s="1">
         <v>0</v>
@@ -5942,13 +5942,13 @@
         <v>621</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>464</v>
       </c>
       <c r="D177" s="13">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E177" s="1">
         <v>0</v>
@@ -5959,13 +5959,13 @@
         <v>621</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>464</v>
       </c>
       <c r="D178" s="13">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E178" s="1">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>478</v>
       </c>
       <c r="D190" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E190" s="1">
         <v>0</v>
@@ -6186,7 +6186,7 @@
         <v>778</v>
       </c>
       <c r="D191" s="13">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E191" s="1">
         <v>0</v>
@@ -7081,13 +7081,13 @@
         <v>673</v>
       </c>
       <c r="B244" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C244" s="10" t="s">
         <v>154</v>
       </c>
       <c r="D244" s="13">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="E244" s="1">
         <v>0</v>
@@ -7098,13 +7098,13 @@
         <v>673</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C245" s="10" t="s">
         <v>154</v>
       </c>
       <c r="D245" s="13">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="E245" s="1">
         <v>0</v>
@@ -7183,13 +7183,13 @@
         <v>673</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C250" s="10" t="s">
         <v>157</v>
       </c>
       <c r="D250" s="13">
-        <v>520</v>
+        <v>600</v>
       </c>
       <c r="E250" s="1">
         <v>0</v>
@@ -7200,13 +7200,13 @@
         <v>673</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C251" s="10" t="s">
         <v>157</v>
       </c>
       <c r="D251" s="13">
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="E251" s="1">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>177</v>
       </c>
       <c r="D277" s="13">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E277" s="1">
         <v>0</v>
@@ -8033,13 +8033,13 @@
         <v>681</v>
       </c>
       <c r="B300" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C300" s="10" t="s">
         <v>567</v>
       </c>
       <c r="D300" s="13">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E300" s="1">
         <v>0</v>
@@ -8053,10 +8053,10 @@
         <v>9</v>
       </c>
       <c r="C301" s="10" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D301" s="13">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E301" s="1">
         <v>0</v>
@@ -8067,13 +8067,13 @@
         <v>681</v>
       </c>
       <c r="B302" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>191</v>
+        <v>560</v>
       </c>
       <c r="D302" s="13">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E302" s="1">
         <v>0</v>
@@ -8084,10 +8084,10 @@
         <v>681</v>
       </c>
       <c r="B303" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C303" s="10" t="s">
-        <v>192</v>
+        <v>560</v>
       </c>
       <c r="D303" s="13">
         <v>10</v>
@@ -8101,13 +8101,13 @@
         <v>681</v>
       </c>
       <c r="B304" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C304" s="10" t="s">
-        <v>568</v>
+        <v>191</v>
       </c>
       <c r="D304" s="13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E304" s="1">
         <v>0</v>
@@ -8115,16 +8115,16 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="10" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B305" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C305" s="10" t="s">
-        <v>740</v>
+        <v>192</v>
       </c>
       <c r="D305" s="13">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="E305" s="1">
         <v>0</v>
@@ -8132,16 +8132,16 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="10" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B306" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C306" s="10" t="s">
-        <v>480</v>
+        <v>568</v>
       </c>
       <c r="D306" s="13">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E306" s="1">
         <v>0</v>
@@ -8149,16 +8149,16 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="10" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B307" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C307" s="10" t="s">
-        <v>193</v>
+        <v>568</v>
       </c>
       <c r="D307" s="13">
-        <v>475</v>
+        <v>15</v>
       </c>
       <c r="E307" s="1">
         <v>0</v>
@@ -8166,16 +8166,16 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="10" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B308" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C308" s="10" t="s">
-        <v>193</v>
+        <v>740</v>
       </c>
       <c r="D308" s="13">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="E308" s="1">
         <v>0</v>
@@ -8183,16 +8183,16 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="10" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B309" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C309" s="10" t="s">
-        <v>395</v>
+        <v>480</v>
       </c>
       <c r="D309" s="13">
-        <v>235</v>
+        <v>39</v>
       </c>
       <c r="E309" s="1">
         <v>0</v>
@@ -8206,10 +8206,10 @@
         <v>40</v>
       </c>
       <c r="C310" s="10" t="s">
-        <v>399</v>
+        <v>193</v>
       </c>
       <c r="D310" s="13">
-        <v>1960</v>
+        <v>475</v>
       </c>
       <c r="E310" s="1">
         <v>0</v>
@@ -8217,16 +8217,16 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="10" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B311" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C311" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D311" s="13">
-        <v>125</v>
+        <v>650</v>
       </c>
       <c r="E311" s="1">
         <v>0</v>
@@ -8234,16 +8234,16 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="10" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="B312" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C312" s="10" t="s">
-        <v>194</v>
+        <v>395</v>
       </c>
       <c r="D312" s="13">
-        <v>880</v>
+        <v>235</v>
       </c>
       <c r="E312" s="1">
         <v>0</v>
@@ -8251,16 +8251,16 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="10" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B313" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C313" s="10" t="s">
-        <v>194</v>
+        <v>399</v>
       </c>
       <c r="D313" s="13">
-        <v>175</v>
+        <v>1960</v>
       </c>
       <c r="E313" s="1">
         <v>0</v>
@@ -8268,16 +8268,16 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="10" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C314" s="10" t="s">
-        <v>518</v>
+        <v>194</v>
       </c>
       <c r="D314" s="13">
-        <v>990</v>
+        <v>175</v>
       </c>
       <c r="E314" s="1">
         <v>0</v>
@@ -8288,13 +8288,13 @@
         <v>680</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C315" s="10" t="s">
-        <v>420</v>
+        <v>194</v>
       </c>
       <c r="D315" s="13">
-        <v>525</v>
+        <v>125</v>
       </c>
       <c r="E315" s="1">
         <v>0</v>
@@ -8302,16 +8302,16 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="10" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C316" s="10" t="s">
-        <v>481</v>
+        <v>194</v>
       </c>
       <c r="D316" s="13">
-        <v>98</v>
+        <v>880</v>
       </c>
       <c r="E316" s="1">
         <v>0</v>
@@ -8325,10 +8325,10 @@
         <v>9</v>
       </c>
       <c r="C317" s="10" t="s">
-        <v>195</v>
+        <v>518</v>
       </c>
       <c r="D317" s="13">
-        <v>320</v>
+        <v>990</v>
       </c>
       <c r="E317" s="1">
         <v>0</v>
@@ -8342,10 +8342,10 @@
         <v>40</v>
       </c>
       <c r="C318" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D318" s="13">
-        <v>350</v>
+        <v>525</v>
       </c>
       <c r="E318" s="1">
         <v>0</v>
@@ -8359,10 +8359,10 @@
         <v>0</v>
       </c>
       <c r="C319" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D319" s="13">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="E319" s="1">
         <v>0</v>
@@ -8373,13 +8373,13 @@
         <v>683</v>
       </c>
       <c r="B320" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C320" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D320" s="13">
-        <v>10</v>
+        <v>320</v>
       </c>
       <c r="E320" s="1">
         <v>0</v>
@@ -8387,16 +8387,16 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="10" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B321" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C321" s="10" t="s">
-        <v>197</v>
+        <v>421</v>
       </c>
       <c r="D321" s="13">
-        <v>4</v>
+        <v>350</v>
       </c>
       <c r="E321" s="1">
         <v>0</v>
@@ -8404,16 +8404,16 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B322" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C322" s="10" t="s">
-        <v>197</v>
+        <v>482</v>
       </c>
       <c r="D322" s="13">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="E322" s="1">
         <v>0</v>
@@ -8421,16 +8421,16 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="10" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B323" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C323" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D323" s="13">
-        <v>1150</v>
+        <v>10</v>
       </c>
       <c r="E323" s="1">
         <v>0</v>
@@ -8438,16 +8438,16 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="10" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B324" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C324" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D324" s="13">
-        <v>290</v>
+        <v>4</v>
       </c>
       <c r="E324" s="1">
         <v>0</v>
@@ -8455,16 +8455,16 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="10" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C325" s="10" t="s">
-        <v>515</v>
+        <v>197</v>
       </c>
       <c r="D325" s="13">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="E325" s="1">
         <v>0</v>
@@ -8472,16 +8472,16 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B326" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C326" s="10" t="s">
-        <v>516</v>
+        <v>198</v>
       </c>
       <c r="D326" s="13">
-        <v>5</v>
+        <v>1150</v>
       </c>
       <c r="E326" s="1">
         <v>0</v>
@@ -8489,16 +8489,16 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B327" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C327" s="10" t="s">
-        <v>517</v>
+        <v>199</v>
       </c>
       <c r="D327" s="13">
-        <v>8</v>
+        <v>290</v>
       </c>
       <c r="E327" s="1">
         <v>0</v>
@@ -8506,16 +8506,16 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="10" t="s">
-        <v>769</v>
+        <v>686</v>
       </c>
       <c r="B328" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C328" s="10" t="s">
-        <v>770</v>
+        <v>515</v>
       </c>
       <c r="D328" s="13">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E328" s="1">
         <v>0</v>
@@ -8523,16 +8523,16 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B329" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C329" s="10" t="s">
-        <v>561</v>
+        <v>516</v>
       </c>
       <c r="D329" s="13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E329" s="1">
         <v>0</v>
@@ -8540,16 +8540,16 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B330" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C330" s="10" t="s">
-        <v>559</v>
+        <v>517</v>
       </c>
       <c r="D330" s="13">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E330" s="1">
         <v>0</v>
@@ -8557,16 +8557,16 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="10" t="s">
-        <v>687</v>
+        <v>769</v>
       </c>
       <c r="B331" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C331" s="10" t="s">
-        <v>562</v>
+        <v>770</v>
       </c>
       <c r="D331" s="13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E331" s="1">
         <v>0</v>
@@ -8574,16 +8574,16 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B332" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C332" s="10" t="s">
-        <v>200</v>
+        <v>561</v>
       </c>
       <c r="D332" s="13">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="E332" s="1">
         <v>0</v>
@@ -8591,16 +8591,16 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B333" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C333" s="10" t="s">
-        <v>201</v>
+        <v>559</v>
       </c>
       <c r="D333" s="13">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="E333" s="1">
         <v>0</v>
@@ -8608,16 +8608,16 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B334" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C334" s="10" t="s">
-        <v>413</v>
+        <v>562</v>
       </c>
       <c r="D334" s="13">
-        <v>450</v>
+        <v>10</v>
       </c>
       <c r="E334" s="1">
         <v>0</v>
@@ -8631,10 +8631,10 @@
         <v>40</v>
       </c>
       <c r="C335" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D335" s="13">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E335" s="1">
         <v>0</v>
@@ -8645,13 +8645,13 @@
         <v>688</v>
       </c>
       <c r="B336" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C336" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D336" s="13">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="E336" s="1">
         <v>0</v>
@@ -8665,10 +8665,10 @@
         <v>40</v>
       </c>
       <c r="C337" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D337" s="13">
-        <v>168</v>
+        <v>450</v>
       </c>
       <c r="E337" s="1">
         <v>0</v>
@@ -8682,10 +8682,10 @@
         <v>40</v>
       </c>
       <c r="C338" s="10" t="s">
-        <v>415</v>
+        <v>202</v>
       </c>
       <c r="D338" s="13">
-        <v>33</v>
+        <v>300</v>
       </c>
       <c r="E338" s="1">
         <v>0</v>
@@ -8696,13 +8696,13 @@
         <v>688</v>
       </c>
       <c r="B339" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C339" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D339" s="13">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="E339" s="1">
         <v>0</v>
@@ -8710,16 +8710,16 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B340" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C340" s="10" t="s">
-        <v>204</v>
+        <v>414</v>
       </c>
       <c r="D340" s="13">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="E340" s="1">
         <v>0</v>
@@ -8727,16 +8727,16 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B341" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C341" s="10" t="s">
-        <v>204</v>
+        <v>415</v>
       </c>
       <c r="D341" s="13">
-        <v>160</v>
+        <v>33</v>
       </c>
       <c r="E341" s="1">
         <v>0</v>
@@ -8744,16 +8744,16 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B342" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C342" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D342" s="13">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E342" s="1">
         <v>0</v>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="C343" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D343" s="13">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E343" s="1">
         <v>0</v>
@@ -8781,13 +8781,13 @@
         <v>689</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C344" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D344" s="13">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E344" s="1">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>689</v>
       </c>
       <c r="B345" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C345" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D345" s="13">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E345" s="1">
         <v>0</v>
@@ -8812,16 +8812,16 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="10" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C346" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D346" s="13">
-        <v>196</v>
+        <v>100</v>
       </c>
       <c r="E346" s="1">
         <v>0</v>
@@ -8829,16 +8829,16 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" s="10" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B347" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C347" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="D347" s="13">
         <v>40</v>
-      </c>
-      <c r="C347" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="D347" s="13">
-        <v>200</v>
       </c>
       <c r="E347" s="1">
         <v>0</v>
@@ -8846,16 +8846,16 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="10" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B348" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C348" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D348" s="13">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E348" s="1">
         <v>0</v>
@@ -8863,16 +8863,16 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B349" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C349" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D349" s="13">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E349" s="1">
         <v>0</v>
@@ -8886,10 +8886,10 @@
         <v>40</v>
       </c>
       <c r="C350" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D350" s="13">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E350" s="1">
         <v>0</v>
@@ -8897,16 +8897,16 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="10" t="s">
-        <v>780</v>
+        <v>691</v>
       </c>
       <c r="B351" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C351" s="10" t="s">
-        <v>781</v>
+        <v>208</v>
       </c>
       <c r="D351" s="13">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E351" s="1">
         <v>0</v>
@@ -8917,13 +8917,13 @@
         <v>691</v>
       </c>
       <c r="B352" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C352" s="10" t="s">
-        <v>411</v>
+        <v>208</v>
       </c>
       <c r="D352" s="13">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="E352" s="1">
         <v>0</v>
@@ -8937,10 +8937,10 @@
         <v>40</v>
       </c>
       <c r="C353" s="10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D353" s="13">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E353" s="1">
         <v>0</v>
@@ -8948,16 +8948,16 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="10" t="s">
-        <v>691</v>
+        <v>780</v>
       </c>
       <c r="B354" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C354" s="10" t="s">
-        <v>209</v>
+        <v>781</v>
       </c>
       <c r="D354" s="13">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E354" s="1">
         <v>0</v>
@@ -8965,16 +8965,16 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>609</v>
+        <v>691</v>
       </c>
       <c r="B355" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C355" s="10" t="s">
-        <v>210</v>
+        <v>411</v>
       </c>
       <c r="D355" s="13">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="E355" s="1">
         <v>0</v>
@@ -8982,16 +8982,16 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="10" t="s">
-        <v>627</v>
+        <v>691</v>
       </c>
       <c r="B356" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C356" s="10" t="s">
-        <v>211</v>
+        <v>412</v>
       </c>
       <c r="D356" s="13">
-        <v>188</v>
+        <v>60</v>
       </c>
       <c r="E356" s="1">
         <v>0</v>
@@ -8999,16 +8999,16 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" s="10" t="s">
-        <v>627</v>
+        <v>691</v>
       </c>
       <c r="B357" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C357" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D357" s="13">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="E357" s="1">
         <v>0</v>
@@ -9016,16 +9016,16 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="10" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="B358" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C358" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D358" s="13">
-        <v>288</v>
+        <v>4</v>
       </c>
       <c r="E358" s="1">
         <v>0</v>
@@ -9033,16 +9033,16 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="10" t="s">
-        <v>678</v>
+        <v>627</v>
       </c>
       <c r="B359" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C359" s="10" t="s">
-        <v>526</v>
+        <v>211</v>
       </c>
       <c r="D359" s="13">
-        <v>1</v>
+        <v>188</v>
       </c>
       <c r="E359" s="1">
         <v>0</v>
@@ -9050,16 +9050,16 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" s="10" t="s">
-        <v>653</v>
+        <v>627</v>
       </c>
       <c r="B360" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C360" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D360" s="13">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="E360" s="1">
         <v>0</v>
@@ -9067,16 +9067,16 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="10" t="s">
-        <v>653</v>
+        <v>627</v>
       </c>
       <c r="B361" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C361" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D361" s="13">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="E361" s="1">
         <v>0</v>
@@ -9084,16 +9084,16 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="10" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="B362" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C362" s="10" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="D362" s="13">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E362" s="1">
         <v>0</v>
@@ -9101,16 +9101,16 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="10" t="s">
-        <v>693</v>
+        <v>653</v>
       </c>
       <c r="B363" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C363" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D363" s="13">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E363" s="1">
         <v>0</v>
@@ -9118,13 +9118,13 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="10" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="B364" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C364" s="10" t="s">
-        <v>398</v>
+        <v>214</v>
       </c>
       <c r="D364" s="13">
         <v>1</v>
@@ -9135,16 +9135,16 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="10" t="s">
-        <v>625</v>
+        <v>692</v>
       </c>
       <c r="B365" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C365" s="10" t="s">
-        <v>757</v>
+        <v>539</v>
       </c>
       <c r="D365" s="13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E365" s="1">
         <v>0</v>
@@ -9152,16 +9152,16 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="10" t="s">
-        <v>625</v>
+        <v>693</v>
       </c>
       <c r="B366" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C366" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D366" s="13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E366" s="1">
         <v>0</v>
@@ -9169,16 +9169,16 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="10" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="B367" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C367" s="10" t="s">
-        <v>782</v>
+        <v>398</v>
       </c>
       <c r="D367" s="13">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E367" s="1">
         <v>0</v>
@@ -9189,13 +9189,13 @@
         <v>625</v>
       </c>
       <c r="B368" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C368" s="10" t="s">
-        <v>217</v>
+        <v>757</v>
       </c>
       <c r="D368" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E368" s="1">
         <v>0</v>
@@ -9209,10 +9209,10 @@
         <v>0</v>
       </c>
       <c r="C369" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D369" s="13">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E369" s="1">
         <v>0</v>
@@ -9223,13 +9223,13 @@
         <v>625</v>
       </c>
       <c r="B370" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C370" s="10" t="s">
-        <v>219</v>
+        <v>782</v>
       </c>
       <c r="D370" s="13">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E370" s="1">
         <v>0</v>
@@ -9240,13 +9240,13 @@
         <v>625</v>
       </c>
       <c r="B371" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C371" s="10" t="s">
-        <v>551</v>
+        <v>217</v>
       </c>
       <c r="D371" s="13">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="E371" s="1">
         <v>0</v>
@@ -9260,10 +9260,10 @@
         <v>0</v>
       </c>
       <c r="C372" s="10" t="s">
-        <v>473</v>
+        <v>218</v>
       </c>
       <c r="D372" s="13">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E372" s="1">
         <v>0</v>
@@ -9277,10 +9277,10 @@
         <v>0</v>
       </c>
       <c r="C373" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D373" s="13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E373" s="1">
         <v>0</v>
@@ -9291,13 +9291,13 @@
         <v>625</v>
       </c>
       <c r="B374" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C374" s="10" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="D374" s="13">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E374" s="1">
         <v>0</v>
@@ -9305,13 +9305,13 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B375" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C375" s="10" t="s">
-        <v>529</v>
+        <v>473</v>
       </c>
       <c r="D375" s="13">
         <v>1</v>
@@ -9328,7 +9328,7 @@
         <v>0</v>
       </c>
       <c r="C376" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D376" s="13">
         <v>1</v>
@@ -9345,7 +9345,7 @@
         <v>0</v>
       </c>
       <c r="C377" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D377" s="13">
         <v>1</v>
@@ -9356,16 +9356,16 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="10" t="s">
-        <v>694</v>
+        <v>626</v>
       </c>
       <c r="B378" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C378" s="10" t="s">
-        <v>425</v>
+        <v>529</v>
       </c>
       <c r="D378" s="13">
-        <v>1800</v>
+        <v>1</v>
       </c>
       <c r="E378" s="1">
         <v>0</v>
@@ -9373,16 +9373,16 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="10" t="s">
-        <v>694</v>
+        <v>625</v>
       </c>
       <c r="B379" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C379" s="10" t="s">
-        <v>426</v>
+        <v>222</v>
       </c>
       <c r="D379" s="13">
-        <v>2700</v>
+        <v>1</v>
       </c>
       <c r="E379" s="1">
         <v>0</v>
@@ -9390,16 +9390,16 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="10" t="s">
-        <v>694</v>
+        <v>625</v>
       </c>
       <c r="B380" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C380" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D380" s="13">
-        <v>900</v>
+        <v>1</v>
       </c>
       <c r="E380" s="1">
         <v>0</v>
@@ -9413,10 +9413,10 @@
         <v>40</v>
       </c>
       <c r="C381" s="10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D381" s="13">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="E381" s="1">
         <v>0</v>
@@ -9430,10 +9430,10 @@
         <v>40</v>
       </c>
       <c r="C382" s="10" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D382" s="13">
-        <v>1200</v>
+        <v>2700</v>
       </c>
       <c r="E382" s="1">
         <v>0</v>
@@ -9441,16 +9441,16 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B383" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C383" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D383" s="13">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="E383" s="1">
         <v>0</v>
@@ -9458,16 +9458,16 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="10" t="s">
-        <v>611</v>
+        <v>694</v>
       </c>
       <c r="B384" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C384" s="10" t="s">
-        <v>226</v>
+        <v>427</v>
       </c>
       <c r="D384" s="13">
-        <v>2</v>
+        <v>900</v>
       </c>
       <c r="E384" s="1">
         <v>0</v>
@@ -9475,16 +9475,16 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="10" t="s">
-        <v>610</v>
+        <v>694</v>
       </c>
       <c r="B385" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C385" s="10" t="s">
-        <v>227</v>
+        <v>428</v>
       </c>
       <c r="D385" s="13">
-        <v>36</v>
+        <v>1200</v>
       </c>
       <c r="E385" s="1">
         <v>0</v>
@@ -9492,16 +9492,16 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B386" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C386" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D386" s="13">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="E386" s="1">
         <v>0</v>
@@ -9509,16 +9509,16 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="10" t="s">
-        <v>697</v>
+        <v>611</v>
       </c>
       <c r="B387" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C387" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D387" s="13">
-        <v>480</v>
+        <v>2</v>
       </c>
       <c r="E387" s="1">
         <v>0</v>
@@ -9526,16 +9526,16 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="10" t="s">
-        <v>696</v>
+        <v>610</v>
       </c>
       <c r="B388" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C388" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D388" s="13">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="E388" s="1">
         <v>0</v>
@@ -9543,16 +9543,16 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="10" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B389" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C389" s="10" t="s">
-        <v>483</v>
+        <v>228</v>
       </c>
       <c r="D389" s="13">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="E389" s="1">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>40</v>
       </c>
       <c r="C390" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D390" s="13">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="E390" s="1">
         <v>0</v>
@@ -9577,16 +9577,16 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B391" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C391" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D391" s="13">
-        <v>3000</v>
+        <v>120</v>
       </c>
       <c r="E391" s="1">
         <v>0</v>
@@ -9594,16 +9594,16 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="10" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B392" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C392" s="10" t="s">
-        <v>231</v>
+        <v>483</v>
       </c>
       <c r="D392" s="13">
-        <v>400</v>
+        <v>19</v>
       </c>
       <c r="E392" s="1">
         <v>0</v>
@@ -9614,13 +9614,13 @@
         <v>697</v>
       </c>
       <c r="B393" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C393" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D393" s="13">
-        <v>120</v>
+        <v>3000</v>
       </c>
       <c r="E393" s="1">
         <v>0</v>
@@ -9634,10 +9634,10 @@
         <v>0</v>
       </c>
       <c r="C394" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D394" s="13">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E394" s="1">
         <v>0</v>
@@ -9651,10 +9651,10 @@
         <v>40</v>
       </c>
       <c r="C395" s="10" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D395" s="13">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="E395" s="1">
         <v>0</v>
@@ -9668,7 +9668,7 @@
         <v>40</v>
       </c>
       <c r="C396" s="10" t="s">
-        <v>408</v>
+        <v>232</v>
       </c>
       <c r="D396" s="13">
         <v>120</v>
@@ -9679,16 +9679,16 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="10" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B397" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C397" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D397" s="13">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="E397" s="1">
         <v>0</v>
@@ -9696,16 +9696,16 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="10" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B398" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C398" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D398" s="13">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E398" s="1">
         <v>0</v>
@@ -9713,16 +9713,16 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="10" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B399" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C399" s="10" t="s">
-        <v>237</v>
+        <v>408</v>
       </c>
       <c r="D399" s="13">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="E399" s="1">
         <v>0</v>
@@ -9730,16 +9730,16 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B400" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C400" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D400" s="13">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="E400" s="1">
         <v>0</v>
@@ -9747,16 +9747,16 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B401" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C401" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D401" s="13">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="E401" s="1">
         <v>0</v>
@@ -9764,16 +9764,16 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B402" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C402" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D402" s="13">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="E402" s="1">
         <v>0</v>
@@ -9781,16 +9781,16 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B403" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C403" s="10" t="s">
-        <v>503</v>
+        <v>238</v>
       </c>
       <c r="D403" s="13">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="E403" s="1">
         <v>0</v>
@@ -9798,16 +9798,16 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B404" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C404" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D404" s="13">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E404" s="1">
         <v>0</v>
@@ -9815,16 +9815,16 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B405" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C405" s="10" t="s">
-        <v>504</v>
+        <v>240</v>
       </c>
       <c r="D405" s="13">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E405" s="1">
         <v>0</v>
@@ -9832,16 +9832,16 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B406" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C406" s="10" t="s">
-        <v>242</v>
+        <v>503</v>
       </c>
       <c r="D406" s="13">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c r="E406" s="1">
         <v>0</v>
@@ -9849,16 +9849,16 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B407" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C407" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D407" s="13">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E407" s="1">
         <v>0</v>
@@ -9866,16 +9866,16 @@
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B408" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C408" s="10" t="s">
-        <v>243</v>
+        <v>504</v>
       </c>
       <c r="D408" s="13">
-        <v>316</v>
+        <v>29</v>
       </c>
       <c r="E408" s="1">
         <v>0</v>
@@ -9889,10 +9889,10 @@
         <v>9</v>
       </c>
       <c r="C409" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D409" s="13">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="E409" s="1">
         <v>0</v>
@@ -9903,13 +9903,13 @@
         <v>702</v>
       </c>
       <c r="B410" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C410" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D410" s="13">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E410" s="1">
         <v>0</v>
@@ -9923,10 +9923,10 @@
         <v>9</v>
       </c>
       <c r="C411" s="10" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D411" s="13">
-        <v>1200</v>
+        <v>316</v>
       </c>
       <c r="E411" s="1">
         <v>0</v>
@@ -9937,13 +9937,13 @@
         <v>702</v>
       </c>
       <c r="B412" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C412" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D412" s="13">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E412" s="1">
         <v>0</v>
@@ -9951,16 +9951,16 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="10" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B413" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C413" s="10" t="s">
-        <v>435</v>
+        <v>245</v>
       </c>
       <c r="D413" s="13">
-        <v>400</v>
+        <v>6</v>
       </c>
       <c r="E413" s="1">
         <v>0</v>
@@ -9968,16 +9968,16 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B414" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C414" s="10" t="s">
-        <v>484</v>
+        <v>246</v>
       </c>
       <c r="D414" s="13">
-        <v>75</v>
+        <v>1200</v>
       </c>
       <c r="E414" s="1">
         <v>0</v>
@@ -9985,16 +9985,16 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="10" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B415" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>400</v>
+        <v>246</v>
       </c>
       <c r="D415" s="13">
-        <v>1200</v>
+        <v>129</v>
       </c>
       <c r="E415" s="1">
         <v>0</v>
@@ -10008,10 +10008,10 @@
         <v>40</v>
       </c>
       <c r="C416" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D416" s="13">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="E416" s="1">
         <v>0</v>
@@ -10025,10 +10025,10 @@
         <v>0</v>
       </c>
       <c r="C417" s="10" t="s">
-        <v>783</v>
+        <v>484</v>
       </c>
       <c r="D417" s="13">
-        <v>450</v>
+        <v>75</v>
       </c>
       <c r="E417" s="1">
         <v>0</v>
@@ -10042,10 +10042,10 @@
         <v>40</v>
       </c>
       <c r="C418" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D418" s="13">
-        <v>27900</v>
+        <v>1200</v>
       </c>
       <c r="E418" s="1">
         <v>0</v>
@@ -10053,16 +10053,16 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="10" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B419" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C419" s="10" t="s">
-        <v>485</v>
+        <v>436</v>
       </c>
       <c r="D419" s="13">
-        <v>15</v>
+        <v>1200</v>
       </c>
       <c r="E419" s="1">
         <v>0</v>
@@ -10070,16 +10070,16 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B420" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C420" s="10" t="s">
-        <v>247</v>
+        <v>783</v>
       </c>
       <c r="D420" s="13">
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="E420" s="1">
         <v>0</v>
@@ -10090,13 +10090,13 @@
         <v>705</v>
       </c>
       <c r="B421" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C421" s="10" t="s">
-        <v>247</v>
+        <v>401</v>
       </c>
       <c r="D421" s="13">
-        <v>300</v>
+        <v>27900</v>
       </c>
       <c r="E421" s="1">
         <v>0</v>
@@ -10104,16 +10104,16 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B422" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C422" s="10" t="s">
-        <v>247</v>
+        <v>485</v>
       </c>
       <c r="D422" s="13">
-        <v>2025</v>
+        <v>15</v>
       </c>
       <c r="E422" s="1">
         <v>0</v>
@@ -10121,16 +10121,16 @@
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" s="10" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B423" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C423" s="10" t="s">
-        <v>486</v>
+        <v>247</v>
       </c>
       <c r="D423" s="13">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="E423" s="1">
         <v>0</v>
@@ -10141,13 +10141,13 @@
         <v>705</v>
       </c>
       <c r="B424" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C424" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D424" s="13">
-        <v>360</v>
+        <v>2025</v>
       </c>
       <c r="E424" s="1">
         <v>0</v>
@@ -10158,13 +10158,13 @@
         <v>705</v>
       </c>
       <c r="B425" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C425" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D425" s="13">
-        <v>450</v>
+        <v>375</v>
       </c>
       <c r="E425" s="1">
         <v>0</v>
@@ -10172,16 +10172,16 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B426" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C426" s="10" t="s">
-        <v>402</v>
+        <v>486</v>
       </c>
       <c r="D426" s="13">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E426" s="1">
         <v>0</v>
@@ -10195,10 +10195,10 @@
         <v>40</v>
       </c>
       <c r="C427" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D427" s="13">
-        <v>90</v>
+        <v>360</v>
       </c>
       <c r="E427" s="1">
         <v>0</v>
@@ -10206,16 +10206,16 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="10" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="B428" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C428" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D428" s="13">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="E428" s="1">
         <v>0</v>
@@ -10223,16 +10223,16 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="10" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B429" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C429" s="10" t="s">
-        <v>251</v>
+        <v>402</v>
       </c>
       <c r="D429" s="13">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="E429" s="1">
         <v>0</v>
@@ -10240,16 +10240,16 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" s="10" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B430" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C430" s="10" t="s">
-        <v>505</v>
+        <v>249</v>
       </c>
       <c r="D430" s="13">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="E430" s="1">
         <v>0</v>
@@ -10257,16 +10257,16 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" s="10" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="B431" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C431" s="10" t="s">
-        <v>396</v>
+        <v>250</v>
       </c>
       <c r="D431" s="13">
-        <v>91</v>
+        <v>600</v>
       </c>
       <c r="E431" s="1">
         <v>0</v>
@@ -10274,16 +10274,16 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" s="10" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B432" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C432" s="10" t="s">
-        <v>543</v>
+        <v>251</v>
       </c>
       <c r="D432" s="13">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="E432" s="1">
         <v>0</v>
@@ -10297,10 +10297,10 @@
         <v>0</v>
       </c>
       <c r="C433" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D433" s="13">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E433" s="1">
         <v>0</v>
@@ -10308,16 +10308,16 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="10" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B434" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C434" s="10" t="s">
-        <v>252</v>
+        <v>396</v>
       </c>
       <c r="D434" s="13">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E434" s="1">
         <v>0</v>
@@ -10325,16 +10325,16 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="10" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B435" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C435" s="10" t="s">
-        <v>253</v>
+        <v>543</v>
       </c>
       <c r="D435" s="13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E435" s="1">
         <v>0</v>
@@ -10342,16 +10342,16 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="10" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B436" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C436" s="10" t="s">
-        <v>254</v>
+        <v>506</v>
       </c>
       <c r="D436" s="13">
-        <v>530</v>
+        <v>6</v>
       </c>
       <c r="E436" s="1">
         <v>0</v>
@@ -10359,16 +10359,16 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B437" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C437" s="10" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D437" s="13">
-        <v>400</v>
+        <v>95</v>
       </c>
       <c r="E437" s="1">
         <v>0</v>
@@ -10376,16 +10376,16 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="10" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B438" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C438" s="10" t="s">
-        <v>487</v>
+        <v>253</v>
       </c>
       <c r="D438" s="13">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E438" s="1">
         <v>0</v>
@@ -10393,16 +10393,16 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="10" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B439" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C439" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D439" s="13">
-        <v>1200</v>
+        <v>530</v>
       </c>
       <c r="E439" s="1">
         <v>0</v>
@@ -10410,16 +10410,16 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="10" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B440" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C440" s="10" t="s">
-        <v>784</v>
+        <v>255</v>
       </c>
       <c r="D440" s="13">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E440" s="1">
         <v>0</v>
@@ -10433,10 +10433,10 @@
         <v>0</v>
       </c>
       <c r="C441" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D441" s="13">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="E441" s="1">
         <v>0</v>
@@ -10450,10 +10450,10 @@
         <v>40</v>
       </c>
       <c r="C442" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D442" s="13">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="E442" s="1">
         <v>0</v>
@@ -10461,16 +10461,16 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B443" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C443" s="10" t="s">
-        <v>257</v>
+        <v>784</v>
       </c>
       <c r="D443" s="13">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="E443" s="1">
         <v>0</v>
@@ -10484,10 +10484,10 @@
         <v>0</v>
       </c>
       <c r="C444" s="10" t="s">
-        <v>785</v>
+        <v>488</v>
       </c>
       <c r="D444" s="13">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="E444" s="1">
         <v>0</v>
@@ -10498,13 +10498,13 @@
         <v>711</v>
       </c>
       <c r="B445" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C445" s="10" t="s">
-        <v>403</v>
+        <v>257</v>
       </c>
       <c r="D445" s="13">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="E445" s="1">
         <v>0</v>
@@ -10518,10 +10518,10 @@
         <v>40</v>
       </c>
       <c r="C446" s="10" t="s">
-        <v>404</v>
+        <v>257</v>
       </c>
       <c r="D446" s="13">
-        <v>96</v>
+        <v>300</v>
       </c>
       <c r="E446" s="1">
         <v>0</v>
@@ -10529,16 +10529,16 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B447" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C447" s="10" t="s">
-        <v>405</v>
+        <v>785</v>
       </c>
       <c r="D447" s="13">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="E447" s="1">
         <v>0</v>
@@ -10546,16 +10546,16 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" s="10" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="B448" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C448" s="10" t="s">
-        <v>258</v>
+        <v>403</v>
       </c>
       <c r="D448" s="13">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="E448" s="1">
         <v>0</v>
@@ -10563,16 +10563,16 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B449" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C449" s="10" t="s">
-        <v>259</v>
+        <v>404</v>
       </c>
       <c r="D449" s="13">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="E449" s="1">
         <v>0</v>
@@ -10580,16 +10580,16 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B450" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C450" s="10" t="s">
-        <v>260</v>
+        <v>405</v>
       </c>
       <c r="D450" s="13">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E450" s="1">
         <v>0</v>
@@ -10597,16 +10597,16 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="10" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="B451" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C451" s="10" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D451" s="13">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="E451" s="1">
         <v>0</v>
@@ -10620,10 +10620,10 @@
         <v>0</v>
       </c>
       <c r="C452" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D452" s="13">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E452" s="1">
         <v>0</v>
@@ -10637,7 +10637,7 @@
         <v>0</v>
       </c>
       <c r="C453" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D453" s="13">
         <v>1</v>
@@ -10654,10 +10654,10 @@
         <v>0</v>
       </c>
       <c r="C454" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D454" s="13">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E454" s="1">
         <v>0</v>
@@ -10671,10 +10671,10 @@
         <v>0</v>
       </c>
       <c r="C455" s="10" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D455" s="13">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E455" s="1">
         <v>0</v>
@@ -10682,16 +10682,16 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="10" t="s">
-        <v>652</v>
+        <v>712</v>
       </c>
       <c r="B456" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C456" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D456" s="13">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E456" s="1">
         <v>0</v>
@@ -10699,16 +10699,16 @@
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="10" t="s">
-        <v>652</v>
+        <v>712</v>
       </c>
       <c r="B457" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C457" s="10" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D457" s="13">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E457" s="1">
         <v>0</v>
@@ -10716,16 +10716,16 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="10" t="s">
-        <v>652</v>
+        <v>712</v>
       </c>
       <c r="B458" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C458" s="10" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D458" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E458" s="1">
         <v>0</v>
@@ -10733,16 +10733,16 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="10" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="B459" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C459" s="10" t="s">
-        <v>760</v>
+        <v>266</v>
       </c>
       <c r="D459" s="13">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E459" s="1">
         <v>0</v>
@@ -10750,16 +10750,16 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="10" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="B460" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C460" s="10" t="s">
-        <v>519</v>
+        <v>267</v>
       </c>
       <c r="D460" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E460" s="1">
         <v>0</v>
@@ -10767,16 +10767,16 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="10" t="s">
-        <v>713</v>
+        <v>652</v>
       </c>
       <c r="B461" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C461" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D461" s="13">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E461" s="1">
         <v>0</v>
@@ -10784,16 +10784,16 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="10" t="s">
-        <v>714</v>
+        <v>643</v>
       </c>
       <c r="B462" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C462" s="10" t="s">
-        <v>270</v>
+        <v>760</v>
       </c>
       <c r="D462" s="13">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="E462" s="1">
         <v>0</v>
@@ -10801,16 +10801,16 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="10" t="s">
-        <v>714</v>
+        <v>643</v>
       </c>
       <c r="B463" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C463" s="10" t="s">
-        <v>271</v>
+        <v>519</v>
       </c>
       <c r="D463" s="13">
-        <v>830</v>
+        <v>10</v>
       </c>
       <c r="E463" s="1">
         <v>0</v>
@@ -10818,16 +10818,16 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B464" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C464" s="10" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D464" s="13">
-        <v>850</v>
+        <v>18</v>
       </c>
       <c r="E464" s="1">
         <v>0</v>
@@ -10838,13 +10838,13 @@
         <v>714</v>
       </c>
       <c r="B465" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C465" s="10" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D465" s="13">
-        <v>1350</v>
+        <v>47</v>
       </c>
       <c r="E465" s="1">
         <v>0</v>
@@ -10858,10 +10858,10 @@
         <v>40</v>
       </c>
       <c r="C466" s="10" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D466" s="13">
-        <v>450</v>
+        <v>830</v>
       </c>
       <c r="E466" s="1">
         <v>0</v>
@@ -10869,16 +10869,16 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="10" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B467" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C467" s="10" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D467" s="13">
-        <v>779</v>
+        <v>850</v>
       </c>
       <c r="E467" s="1">
         <v>0</v>
@@ -10886,16 +10886,16 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="10" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B468" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C468" s="10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D468" s="13">
-        <v>570</v>
+        <v>1350</v>
       </c>
       <c r="E468" s="1">
         <v>0</v>
@@ -10903,16 +10903,16 @@
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="10" t="s">
-        <v>612</v>
+        <v>714</v>
       </c>
       <c r="B469" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C469" s="10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D469" s="13">
-        <v>273</v>
+        <v>450</v>
       </c>
       <c r="E469" s="1">
         <v>0</v>
@@ -10920,16 +10920,16 @@
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="10" t="s">
-        <v>628</v>
+        <v>713</v>
       </c>
       <c r="B470" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C470" s="10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D470" s="13">
-        <v>3</v>
+        <v>570</v>
       </c>
       <c r="E470" s="1">
         <v>0</v>
@@ -10937,16 +10937,16 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="10" t="s">
-        <v>628</v>
+        <v>713</v>
       </c>
       <c r="B471" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C471" s="10" t="s">
-        <v>554</v>
+        <v>275</v>
       </c>
       <c r="D471" s="13">
-        <v>40</v>
+        <v>779</v>
       </c>
       <c r="E471" s="1">
         <v>0</v>
@@ -10954,16 +10954,16 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="10" t="s">
-        <v>666</v>
+        <v>612</v>
       </c>
       <c r="B472" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C472" s="10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D472" s="13">
-        <v>11</v>
+        <v>273</v>
       </c>
       <c r="E472" s="1">
         <v>0</v>
@@ -10971,16 +10971,16 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>666</v>
+        <v>628</v>
       </c>
       <c r="B473" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C473" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D473" s="13">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E473" s="1">
         <v>0</v>
@@ -10988,16 +10988,16 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>666</v>
+        <v>628</v>
       </c>
       <c r="B474" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C474" s="10" t="s">
-        <v>280</v>
+        <v>554</v>
       </c>
       <c r="D474" s="13">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E474" s="1">
         <v>0</v>
@@ -11011,10 +11011,10 @@
         <v>0</v>
       </c>
       <c r="C475" s="10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D475" s="13">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E475" s="1">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="C476" s="10" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D476" s="13">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E476" s="1">
         <v>0</v>
@@ -11042,13 +11042,13 @@
         <v>666</v>
       </c>
       <c r="B477" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C477" s="10" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D477" s="13">
-        <v>840</v>
+        <v>2</v>
       </c>
       <c r="E477" s="1">
         <v>0</v>
@@ -11059,13 +11059,13 @@
         <v>666</v>
       </c>
       <c r="B478" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C478" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D478" s="13">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E478" s="1">
         <v>0</v>
@@ -11076,13 +11076,13 @@
         <v>666</v>
       </c>
       <c r="B479" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C479" s="10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D479" s="13">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E479" s="1">
         <v>0</v>
@@ -11096,10 +11096,10 @@
         <v>40</v>
       </c>
       <c r="C480" s="10" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D480" s="13">
-        <v>70</v>
+        <v>840</v>
       </c>
       <c r="E480" s="1">
         <v>0</v>
@@ -11113,10 +11113,10 @@
         <v>40</v>
       </c>
       <c r="C481" s="10" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D481" s="13">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E481" s="1">
         <v>0</v>
@@ -11130,10 +11130,10 @@
         <v>40</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D482" s="13">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E482" s="1">
         <v>0</v>
@@ -11147,10 +11147,10 @@
         <v>40</v>
       </c>
       <c r="C483" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D483" s="13">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="E483" s="1">
         <v>0</v>
@@ -11164,10 +11164,10 @@
         <v>40</v>
       </c>
       <c r="C484" s="10" t="s">
-        <v>452</v>
+        <v>287</v>
       </c>
       <c r="D484" s="13">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E484" s="1">
         <v>0</v>
@@ -11175,16 +11175,16 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="10" t="s">
-        <v>609</v>
+        <v>666</v>
       </c>
       <c r="B485" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C485" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D485" s="13">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="E485" s="1">
         <v>0</v>
@@ -11192,16 +11192,16 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="10" t="s">
-        <v>713</v>
+        <v>666</v>
       </c>
       <c r="B486" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C486" s="10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D486" s="13">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E486" s="1">
         <v>0</v>
@@ -11209,16 +11209,16 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" s="10" t="s">
-        <v>611</v>
+        <v>666</v>
       </c>
       <c r="B487" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D487" s="13">
-        <v>16400</v>
+        <v>15</v>
       </c>
       <c r="E487" s="1">
         <v>0</v>
@@ -11226,16 +11226,16 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" s="10" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="B488" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C488" s="10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D488" s="13">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="E488" s="1">
         <v>0</v>
@@ -11243,16 +11243,16 @@
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
-        <v>625</v>
+        <v>713</v>
       </c>
       <c r="B489" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C489" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D489" s="13">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E489" s="1">
         <v>0</v>
@@ -11260,16 +11260,16 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="B490" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C490" s="10" t="s">
-        <v>564</v>
+        <v>444</v>
       </c>
       <c r="D490" s="13">
-        <v>17</v>
+        <v>16400</v>
       </c>
       <c r="E490" s="1">
         <v>0</v>
@@ -11280,13 +11280,13 @@
         <v>625</v>
       </c>
       <c r="B491" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C491" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D491" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E491" s="1">
         <v>0</v>
@@ -11300,10 +11300,10 @@
         <v>0</v>
       </c>
       <c r="C492" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D492" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E492" s="1">
         <v>0</v>
@@ -11314,13 +11314,13 @@
         <v>625</v>
       </c>
       <c r="B493" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C493" s="10" t="s">
-        <v>295</v>
+        <v>564</v>
       </c>
       <c r="D493" s="13">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E493" s="1">
         <v>0</v>
@@ -11334,10 +11334,10 @@
         <v>0</v>
       </c>
       <c r="C494" s="10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D494" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E494" s="1">
         <v>0</v>
@@ -11351,10 +11351,10 @@
         <v>0</v>
       </c>
       <c r="C495" s="10" t="s">
-        <v>514</v>
+        <v>294</v>
       </c>
       <c r="D495" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E495" s="1">
         <v>0</v>
@@ -11368,10 +11368,10 @@
         <v>0</v>
       </c>
       <c r="C496" s="10" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D496" s="13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E496" s="1">
         <v>0</v>
@@ -11385,10 +11385,10 @@
         <v>0</v>
       </c>
       <c r="C497" s="10" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D497" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E497" s="1">
         <v>0</v>
@@ -11402,10 +11402,10 @@
         <v>0</v>
       </c>
       <c r="C498" s="10" t="s">
-        <v>299</v>
+        <v>514</v>
       </c>
       <c r="D498" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E498" s="1">
         <v>0</v>
@@ -11419,7 +11419,7 @@
         <v>0</v>
       </c>
       <c r="C499" s="10" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D499" s="13">
         <v>1</v>
@@ -11436,10 +11436,10 @@
         <v>0</v>
       </c>
       <c r="C500" s="10" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D500" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E500" s="1">
         <v>0</v>
@@ -11453,7 +11453,7 @@
         <v>0</v>
       </c>
       <c r="C501" s="10" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D501" s="13">
         <v>1</v>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="C502" s="10" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D502" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E502" s="1">
         <v>0</v>
@@ -11481,16 +11481,16 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B503" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C503" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D503" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E503" s="1">
         <v>0</v>
@@ -11504,10 +11504,10 @@
         <v>0</v>
       </c>
       <c r="C504" s="10" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D504" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E504" s="1">
         <v>0</v>
@@ -11521,10 +11521,10 @@
         <v>0</v>
       </c>
       <c r="C505" s="10" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D505" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E505" s="1">
         <v>0</v>
@@ -11538,7 +11538,7 @@
         <v>0</v>
       </c>
       <c r="C506" s="10" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D506" s="13">
         <v>1</v>
@@ -11549,16 +11549,16 @@
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B507" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C507" s="10" t="s">
-        <v>466</v>
+        <v>305</v>
       </c>
       <c r="D507" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E507" s="1">
         <v>0</v>
@@ -11566,13 +11566,13 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="B508" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C508" s="10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D508" s="13">
         <v>1</v>
@@ -11583,13 +11583,13 @@
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>671</v>
+        <v>626</v>
       </c>
       <c r="B509" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C509" s="10" t="s">
-        <v>523</v>
+        <v>307</v>
       </c>
       <c r="D509" s="13">
         <v>1</v>
@@ -11600,13 +11600,13 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>671</v>
+        <v>626</v>
       </c>
       <c r="B510" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C510" s="10" t="s">
-        <v>309</v>
+        <v>466</v>
       </c>
       <c r="D510" s="13">
         <v>1</v>
@@ -11623,10 +11623,10 @@
         <v>0</v>
       </c>
       <c r="C511" s="10" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D511" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E511" s="1">
         <v>0</v>
@@ -11634,13 +11634,13 @@
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" s="10" t="s">
-        <v>615</v>
+        <v>671</v>
       </c>
       <c r="B512" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C512" s="10" t="s">
-        <v>772</v>
+        <v>523</v>
       </c>
       <c r="D512" s="13">
         <v>1</v>
@@ -11651,16 +11651,16 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>615</v>
+        <v>671</v>
       </c>
       <c r="B513" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C513" s="10" t="s">
-        <v>773</v>
+        <v>309</v>
       </c>
       <c r="D513" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E513" s="1">
         <v>0</v>
@@ -11668,16 +11668,16 @@
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="B514" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C514" s="10" t="s">
-        <v>738</v>
+        <v>310</v>
       </c>
       <c r="D514" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E514" s="1">
         <v>0</v>
@@ -11691,10 +11691,10 @@
         <v>570</v>
       </c>
       <c r="C515" s="10" t="s">
-        <v>571</v>
+        <v>772</v>
       </c>
       <c r="D515" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E515" s="1">
         <v>0</v>
@@ -11708,10 +11708,10 @@
         <v>570</v>
       </c>
       <c r="C516" s="10" t="s">
-        <v>572</v>
+        <v>773</v>
       </c>
       <c r="D516" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E516" s="1">
         <v>0</v>
@@ -11719,16 +11719,16 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
-        <v>717</v>
+        <v>615</v>
       </c>
       <c r="B517" s="10" t="s">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="C517" s="10" t="s">
-        <v>759</v>
+        <v>738</v>
       </c>
       <c r="D517" s="13">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E517" s="1">
         <v>0</v>
@@ -11742,10 +11742,10 @@
         <v>570</v>
       </c>
       <c r="C518" s="10" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D518" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E518" s="1">
         <v>0</v>
@@ -11759,10 +11759,10 @@
         <v>570</v>
       </c>
       <c r="C519" s="10" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D519" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E519" s="1">
         <v>0</v>
@@ -11770,16 +11770,16 @@
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
-        <v>615</v>
+        <v>717</v>
       </c>
       <c r="B520" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C520" s="10" t="s">
-        <v>742</v>
+        <v>759</v>
       </c>
       <c r="D520" s="13">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E520" s="1">
         <v>0</v>
@@ -11793,10 +11793,10 @@
         <v>570</v>
       </c>
       <c r="C521" s="10" t="s">
-        <v>761</v>
+        <v>573</v>
       </c>
       <c r="D521" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E521" s="1">
         <v>0</v>
@@ -11804,16 +11804,16 @@
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
-        <v>715</v>
+        <v>615</v>
       </c>
       <c r="B522" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C522" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D522" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E522" s="1">
         <v>0</v>
@@ -11827,10 +11827,10 @@
         <v>570</v>
       </c>
       <c r="C523" s="10" t="s">
-        <v>774</v>
+        <v>742</v>
       </c>
       <c r="D523" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E523" s="1">
         <v>0</v>
@@ -11844,7 +11844,7 @@
         <v>570</v>
       </c>
       <c r="C524" s="10" t="s">
-        <v>576</v>
+        <v>761</v>
       </c>
       <c r="D524" s="13">
         <v>2</v>
@@ -11855,13 +11855,13 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" s="10" t="s">
-        <v>615</v>
+        <v>715</v>
       </c>
       <c r="B525" s="10" t="s">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="C525" s="10" t="s">
-        <v>532</v>
+        <v>575</v>
       </c>
       <c r="D525" s="13">
         <v>1</v>
@@ -11875,13 +11875,13 @@
         <v>615</v>
       </c>
       <c r="B526" s="10" t="s">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="C526" s="10" t="s">
-        <v>311</v>
+        <v>774</v>
       </c>
       <c r="D526" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E526" s="1">
         <v>0</v>
@@ -11889,16 +11889,16 @@
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" s="10" t="s">
-        <v>716</v>
+        <v>615</v>
       </c>
       <c r="B527" s="10" t="s">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="C527" s="10" t="s">
-        <v>533</v>
+        <v>576</v>
       </c>
       <c r="D527" s="13">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E527" s="1">
         <v>0</v>
@@ -11906,16 +11906,16 @@
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" s="10" t="s">
-        <v>716</v>
+        <v>615</v>
       </c>
       <c r="B528" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C528" s="10" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D528" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E528" s="1">
         <v>0</v>
@@ -11923,13 +11923,13 @@
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" s="10" t="s">
-        <v>717</v>
+        <v>615</v>
       </c>
       <c r="B529" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C529" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D529" s="13">
         <v>1</v>
@@ -11940,16 +11940,16 @@
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" s="10" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B530" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C530" s="10" t="s">
-        <v>313</v>
+        <v>533</v>
       </c>
       <c r="D530" s="13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E530" s="1">
         <v>0</v>
@@ -11957,16 +11957,16 @@
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" s="10" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B531" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C531" s="10" t="s">
-        <v>314</v>
+        <v>534</v>
       </c>
       <c r="D531" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E531" s="1">
         <v>0</v>
@@ -11980,7 +11980,7 @@
         <v>0</v>
       </c>
       <c r="C532" s="10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D532" s="13">
         <v>1</v>
@@ -11997,10 +11997,10 @@
         <v>0</v>
       </c>
       <c r="C533" s="10" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D533" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E533" s="1">
         <v>0</v>
@@ -12014,7 +12014,7 @@
         <v>0</v>
       </c>
       <c r="C534" s="10" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D534" s="13">
         <v>1</v>
@@ -12031,10 +12031,10 @@
         <v>0</v>
       </c>
       <c r="C535" s="10" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D535" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E535" s="1">
         <v>0</v>
@@ -12042,16 +12042,16 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="10" t="s">
-        <v>615</v>
+        <v>717</v>
       </c>
       <c r="B536" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C536" s="10" t="s">
-        <v>577</v>
+        <v>316</v>
       </c>
       <c r="D536" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E536" s="1">
         <v>0</v>
@@ -12059,16 +12059,16 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" s="10" t="s">
-        <v>615</v>
+        <v>717</v>
       </c>
       <c r="B537" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C537" s="10" t="s">
-        <v>764</v>
+        <v>317</v>
       </c>
       <c r="D537" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E537" s="1">
         <v>0</v>
@@ -12076,13 +12076,13 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="10" t="s">
-        <v>615</v>
+        <v>717</v>
       </c>
       <c r="B538" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C538" s="10" t="s">
-        <v>578</v>
+        <v>318</v>
       </c>
       <c r="D538" s="13">
         <v>2</v>
@@ -12099,10 +12099,10 @@
         <v>570</v>
       </c>
       <c r="C539" s="10" t="s">
-        <v>758</v>
+        <v>577</v>
       </c>
       <c r="D539" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E539" s="1">
         <v>0</v>
@@ -12116,10 +12116,10 @@
         <v>570</v>
       </c>
       <c r="C540" s="10" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="D540" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E540" s="1">
         <v>0</v>
@@ -12127,16 +12127,16 @@
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" s="10" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B541" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C541" s="10" t="s">
-        <v>762</v>
+        <v>578</v>
       </c>
       <c r="D541" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E541" s="1">
         <v>0</v>
@@ -12144,16 +12144,16 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" s="10" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B542" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C542" s="10" t="s">
-        <v>579</v>
+        <v>758</v>
       </c>
       <c r="D542" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E542" s="1">
         <v>0</v>
@@ -12161,16 +12161,16 @@
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" s="10" t="s">
-        <v>715</v>
+        <v>615</v>
       </c>
       <c r="B543" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C543" s="10" t="s">
-        <v>580</v>
+        <v>771</v>
       </c>
       <c r="D543" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E543" s="1">
         <v>0</v>
@@ -12178,13 +12178,13 @@
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" s="10" t="s">
-        <v>715</v>
+        <v>617</v>
       </c>
       <c r="B544" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C544" s="10" t="s">
-        <v>581</v>
+        <v>762</v>
       </c>
       <c r="D544" s="13">
         <v>1</v>
@@ -12201,7 +12201,7 @@
         <v>570</v>
       </c>
       <c r="C545" s="10" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D545" s="13">
         <v>1</v>
@@ -12212,13 +12212,13 @@
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" s="10" t="s">
-        <v>617</v>
+        <v>715</v>
       </c>
       <c r="B546" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C546" s="10" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D546" s="13">
         <v>1</v>
@@ -12229,13 +12229,13 @@
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" s="10" t="s">
-        <v>617</v>
+        <v>715</v>
       </c>
       <c r="B547" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C547" s="10" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="D547" s="13">
         <v>1</v>
@@ -12252,10 +12252,10 @@
         <v>570</v>
       </c>
       <c r="C548" s="10" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D548" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E548" s="1">
         <v>0</v>
@@ -12269,7 +12269,7 @@
         <v>570</v>
       </c>
       <c r="C549" s="10" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D549" s="13">
         <v>1</v>
@@ -12280,16 +12280,16 @@
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" s="10" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B550" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C550" s="10" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D550" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E550" s="1">
         <v>0</v>
@@ -12297,16 +12297,16 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" s="10" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B551" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C551" s="10" t="s">
-        <v>604</v>
+        <v>585</v>
       </c>
       <c r="D551" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E551" s="1">
         <v>0</v>
@@ -12314,16 +12314,16 @@
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552" s="10" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B552" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C552" s="10" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D552" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E552" s="1">
         <v>0</v>
@@ -12337,10 +12337,10 @@
         <v>570</v>
       </c>
       <c r="C553" s="10" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D553" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E553" s="1">
         <v>0</v>
@@ -12354,10 +12354,10 @@
         <v>570</v>
       </c>
       <c r="C554" s="10" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="D554" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E554" s="1">
         <v>0</v>
@@ -12365,16 +12365,16 @@
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" s="10" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B555" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C555" s="10" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D555" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E555" s="1">
         <v>0</v>
@@ -12382,13 +12382,13 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" s="10" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B556" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C556" s="10" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="D556" s="13">
         <v>1</v>
@@ -12405,7 +12405,7 @@
         <v>570</v>
       </c>
       <c r="C557" s="10" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="D557" s="13">
         <v>2</v>
@@ -12416,13 +12416,13 @@
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" s="10" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B558" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C558" s="10" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="D558" s="13">
         <v>1</v>
@@ -12433,13 +12433,13 @@
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" s="10" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B559" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C559" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D559" s="13">
         <v>1</v>
@@ -12456,10 +12456,10 @@
         <v>570</v>
       </c>
       <c r="C560" s="10" t="s">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="D560" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E560" s="1">
         <v>0</v>
@@ -12473,10 +12473,10 @@
         <v>570</v>
       </c>
       <c r="C561" s="10" t="s">
-        <v>594</v>
+        <v>607</v>
       </c>
       <c r="D561" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E561" s="1">
         <v>0</v>
@@ -12490,7 +12490,7 @@
         <v>570</v>
       </c>
       <c r="C562" s="10" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D562" s="13">
         <v>1</v>
@@ -12507,10 +12507,10 @@
         <v>570</v>
       </c>
       <c r="C563" s="10" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D563" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E563" s="1">
         <v>0</v>
@@ -12524,10 +12524,10 @@
         <v>570</v>
       </c>
       <c r="C564" s="10" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D564" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E564" s="1">
         <v>0</v>
@@ -12541,10 +12541,10 @@
         <v>570</v>
       </c>
       <c r="C565" s="10" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D565" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E565" s="1">
         <v>0</v>
@@ -12558,7 +12558,7 @@
         <v>570</v>
       </c>
       <c r="C566" s="10" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D566" s="13">
         <v>2</v>
@@ -12569,16 +12569,16 @@
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" s="10" t="s">
-        <v>671</v>
+        <v>615</v>
       </c>
       <c r="B567" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C567" s="10" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D567" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E567" s="1">
         <v>0</v>
@@ -12586,16 +12586,16 @@
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" s="10" t="s">
-        <v>717</v>
+        <v>615</v>
       </c>
       <c r="B568" s="10" t="s">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="C568" s="10" t="s">
-        <v>319</v>
+        <v>598</v>
       </c>
       <c r="D568" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E568" s="1">
         <v>0</v>
@@ -12606,13 +12606,13 @@
         <v>615</v>
       </c>
       <c r="B569" s="10" t="s">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="C569" s="10" t="s">
-        <v>320</v>
+        <v>599</v>
       </c>
       <c r="D569" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E569" s="1">
         <v>0</v>
@@ -12620,16 +12620,16 @@
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" s="10" t="s">
-        <v>615</v>
+        <v>671</v>
       </c>
       <c r="B570" s="10" t="s">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="C570" s="10" t="s">
-        <v>535</v>
+        <v>600</v>
       </c>
       <c r="D570" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E570" s="1">
         <v>0</v>
@@ -12637,16 +12637,16 @@
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" s="10" t="s">
-        <v>615</v>
+        <v>717</v>
       </c>
       <c r="B571" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C571" s="10" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D571" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E571" s="1">
         <v>0</v>
@@ -12657,13 +12657,13 @@
         <v>615</v>
       </c>
       <c r="B572" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C572" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D572" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E572" s="1">
         <v>0</v>
@@ -12671,16 +12671,16 @@
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" s="10" t="s">
-        <v>671</v>
+        <v>615</v>
       </c>
       <c r="B573" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C573" s="10" t="s">
-        <v>322</v>
+        <v>535</v>
       </c>
       <c r="D573" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E573" s="1">
         <v>0</v>
@@ -12688,16 +12688,16 @@
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" s="10" t="s">
-        <v>671</v>
+        <v>615</v>
       </c>
       <c r="B574" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C574" s="10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D574" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E574" s="1">
         <v>0</v>
@@ -12705,16 +12705,16 @@
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" s="10" t="s">
-        <v>671</v>
+        <v>615</v>
       </c>
       <c r="B575" s="10" t="s">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="C575" s="10" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D575" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E575" s="1">
         <v>0</v>
@@ -12722,16 +12722,16 @@
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" s="10" t="s">
-        <v>617</v>
+        <v>671</v>
       </c>
       <c r="B576" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C576" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D576" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E576" s="1">
         <v>0</v>
@@ -12739,13 +12739,13 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" s="10" t="s">
-        <v>617</v>
+        <v>671</v>
       </c>
       <c r="B577" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C577" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D577" s="13">
         <v>1</v>
@@ -12756,16 +12756,16 @@
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578" s="10" t="s">
-        <v>615</v>
+        <v>671</v>
       </c>
       <c r="B578" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C578" s="10" t="s">
-        <v>743</v>
+        <v>324</v>
       </c>
       <c r="D578" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E578" s="1">
         <v>0</v>
@@ -12773,13 +12773,13 @@
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" s="10" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B579" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C579" s="10" t="s">
-        <v>744</v>
+        <v>325</v>
       </c>
       <c r="D579" s="13">
         <v>1</v>
@@ -12790,16 +12790,16 @@
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" s="10" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B580" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C580" s="10" t="s">
-        <v>745</v>
+        <v>326</v>
       </c>
       <c r="D580" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E580" s="1">
         <v>0</v>
@@ -12813,10 +12813,10 @@
         <v>570</v>
       </c>
       <c r="C581" s="10" t="s">
-        <v>601</v>
+        <v>743</v>
       </c>
       <c r="D581" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E581" s="1">
         <v>0</v>
@@ -12830,7 +12830,7 @@
         <v>570</v>
       </c>
       <c r="C582" s="10" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D582" s="13">
         <v>1</v>
@@ -12847,10 +12847,10 @@
         <v>570</v>
       </c>
       <c r="C583" s="10" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D583" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E583" s="1">
         <v>0</v>
@@ -12864,10 +12864,10 @@
         <v>570</v>
       </c>
       <c r="C584" s="10" t="s">
-        <v>748</v>
+        <v>601</v>
       </c>
       <c r="D584" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E584" s="1">
         <v>0</v>
@@ -12881,10 +12881,10 @@
         <v>570</v>
       </c>
       <c r="C585" s="10" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D585" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E585" s="1">
         <v>0</v>
@@ -12898,10 +12898,10 @@
         <v>570</v>
       </c>
       <c r="C586" s="10" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D586" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E586" s="1">
         <v>0</v>
@@ -12915,7 +12915,7 @@
         <v>570</v>
       </c>
       <c r="C587" s="10" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="D587" s="13">
         <v>4</v>
@@ -12932,7 +12932,7 @@
         <v>570</v>
       </c>
       <c r="C588" s="10" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D588" s="13">
         <v>2</v>
@@ -12949,10 +12949,10 @@
         <v>570</v>
       </c>
       <c r="C589" s="10" t="s">
-        <v>602</v>
+        <v>750</v>
       </c>
       <c r="D589" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E589" s="1">
         <v>0</v>
@@ -12966,10 +12966,10 @@
         <v>570</v>
       </c>
       <c r="C590" s="10" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="D590" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E590" s="1">
         <v>0</v>
@@ -12977,16 +12977,16 @@
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>671</v>
+        <v>615</v>
       </c>
       <c r="B591" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C591" s="10" t="s">
-        <v>603</v>
+        <v>752</v>
       </c>
       <c r="D591" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E591" s="1">
         <v>0</v>
@@ -12994,13 +12994,13 @@
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A592" s="10" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B592" s="10" t="s">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="C592" s="10" t="s">
-        <v>327</v>
+        <v>602</v>
       </c>
       <c r="D592" s="13">
         <v>2</v>
@@ -13011,13 +13011,13 @@
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A593" s="10" t="s">
-        <v>671</v>
+        <v>615</v>
       </c>
       <c r="B593" s="10" t="s">
         <v>570</v>
       </c>
       <c r="C593" s="10" t="s">
-        <v>608</v>
+        <v>739</v>
       </c>
       <c r="D593" s="13">
         <v>1</v>
@@ -13028,16 +13028,16 @@
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A594" s="10" t="s">
-        <v>694</v>
+        <v>671</v>
       </c>
       <c r="B594" s="10" t="s">
-        <v>40</v>
+        <v>570</v>
       </c>
       <c r="C594" s="10" t="s">
-        <v>429</v>
+        <v>603</v>
       </c>
       <c r="D594" s="13">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E594" s="1">
         <v>0</v>
@@ -13045,16 +13045,16 @@
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A595" s="10" t="s">
-        <v>694</v>
+        <v>617</v>
       </c>
       <c r="B595" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C595" s="10" t="s">
-        <v>430</v>
+        <v>327</v>
       </c>
       <c r="D595" s="13">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E595" s="1">
         <v>0</v>
@@ -13062,16 +13062,16 @@
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A596" s="10" t="s">
-        <v>694</v>
+        <v>671</v>
       </c>
       <c r="B596" s="10" t="s">
-        <v>40</v>
+        <v>570</v>
       </c>
       <c r="C596" s="10" t="s">
-        <v>431</v>
+        <v>608</v>
       </c>
       <c r="D596" s="13">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E596" s="1">
         <v>0</v>
@@ -13079,16 +13079,16 @@
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A597" s="10" t="s">
-        <v>609</v>
+        <v>694</v>
       </c>
       <c r="B597" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C597" s="10" t="s">
-        <v>328</v>
+        <v>429</v>
       </c>
       <c r="D597" s="13">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E597" s="1">
         <v>0</v>
@@ -13096,16 +13096,16 @@
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A598" s="10" t="s">
-        <v>718</v>
+        <v>694</v>
       </c>
       <c r="B598" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C598" s="10" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
       <c r="D598" s="13">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E598" s="1">
         <v>0</v>
@@ -13113,16 +13113,16 @@
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A599" s="10" t="s">
-        <v>718</v>
+        <v>694</v>
       </c>
       <c r="B599" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C599" s="10" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="D599" s="13">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E599" s="1">
         <v>0</v>
@@ -13130,16 +13130,16 @@
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A600" s="10" t="s">
-        <v>718</v>
+        <v>609</v>
       </c>
       <c r="B600" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C600" s="10" t="s">
-        <v>459</v>
+        <v>328</v>
       </c>
       <c r="D600" s="13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E600" s="1">
         <v>0</v>
@@ -13153,10 +13153,10 @@
         <v>9</v>
       </c>
       <c r="C601" s="10" t="s">
-        <v>566</v>
+        <v>457</v>
       </c>
       <c r="D601" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E601" s="1">
         <v>0</v>
@@ -13170,10 +13170,10 @@
         <v>9</v>
       </c>
       <c r="C602" s="10" t="s">
-        <v>565</v>
+        <v>458</v>
       </c>
       <c r="D602" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E602" s="1">
         <v>0</v>
@@ -13187,10 +13187,10 @@
         <v>9</v>
       </c>
       <c r="C603" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D603" s="13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E603" s="1">
         <v>0</v>
@@ -13204,7 +13204,7 @@
         <v>9</v>
       </c>
       <c r="C604" s="10" t="s">
-        <v>461</v>
+        <v>566</v>
       </c>
       <c r="D604" s="13">
         <v>4</v>
@@ -13215,16 +13215,16 @@
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A605" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B605" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C605" s="10" t="s">
-        <v>329</v>
+        <v>565</v>
       </c>
       <c r="D605" s="13">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E605" s="1">
         <v>0</v>
@@ -13232,16 +13232,16 @@
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A606" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B606" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C606" s="10" t="s">
-        <v>330</v>
+        <v>460</v>
       </c>
       <c r="D606" s="13">
-        <v>800</v>
+        <v>2</v>
       </c>
       <c r="E606" s="1">
         <v>0</v>
@@ -13249,16 +13249,16 @@
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A607" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B607" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C607" s="10" t="s">
-        <v>331</v>
+        <v>461</v>
       </c>
       <c r="D607" s="13">
-        <v>1600</v>
+        <v>4</v>
       </c>
       <c r="E607" s="1">
         <v>0</v>
@@ -13269,13 +13269,13 @@
         <v>719</v>
       </c>
       <c r="B608" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C608" s="10" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D608" s="13">
-        <v>1000</v>
+        <v>37</v>
       </c>
       <c r="E608" s="1">
         <v>0</v>
@@ -13286,13 +13286,13 @@
         <v>719</v>
       </c>
       <c r="B609" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C609" s="10" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D609" s="13">
-        <v>1070</v>
+        <v>800</v>
       </c>
       <c r="E609" s="1">
         <v>0</v>
@@ -13306,7 +13306,7 @@
         <v>40</v>
       </c>
       <c r="C610" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D610" s="13">
         <v>1600</v>
@@ -13323,10 +13323,10 @@
         <v>40</v>
       </c>
       <c r="C611" s="10" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D611" s="13">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E611" s="1">
         <v>0</v>
@@ -13337,13 +13337,13 @@
         <v>719</v>
       </c>
       <c r="B612" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C612" s="10" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D612" s="13">
-        <v>2000</v>
+        <v>1070</v>
       </c>
       <c r="E612" s="1">
         <v>0</v>
@@ -13357,10 +13357,10 @@
         <v>40</v>
       </c>
       <c r="C613" s="10" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D613" s="13">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="E613" s="1">
         <v>0</v>
@@ -13368,16 +13368,16 @@
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A614" s="10" t="s">
-        <v>625</v>
+        <v>719</v>
       </c>
       <c r="B614" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C614" s="10" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D614" s="13">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="E614" s="1">
         <v>0</v>
@@ -13385,16 +13385,16 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" s="10" t="s">
-        <v>625</v>
+        <v>719</v>
       </c>
       <c r="B615" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C615" s="10" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D615" s="13">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="E615" s="1">
         <v>0</v>
@@ -13402,16 +13402,16 @@
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A616" s="10" t="s">
-        <v>626</v>
+        <v>719</v>
       </c>
       <c r="B616" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C616" s="10" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D616" s="13">
-        <v>1</v>
+        <v>1800</v>
       </c>
       <c r="E616" s="1">
         <v>0</v>
@@ -13419,13 +13419,13 @@
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B617" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C617" s="10" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D617" s="13">
         <v>1</v>
@@ -13436,16 +13436,16 @@
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A618" s="10" t="s">
-        <v>720</v>
+        <v>625</v>
       </c>
       <c r="B618" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C618" s="10" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D618" s="13">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E618" s="1">
         <v>0</v>
@@ -13453,16 +13453,16 @@
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A619" s="10" t="s">
-        <v>721</v>
+        <v>626</v>
       </c>
       <c r="B619" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C619" s="10" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D619" s="13">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E619" s="1">
         <v>0</v>
@@ -13470,16 +13470,16 @@
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A620" s="10" t="s">
-        <v>721</v>
+        <v>626</v>
       </c>
       <c r="B620" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C620" s="10" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D620" s="13">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="E620" s="1">
         <v>0</v>
@@ -13487,16 +13487,16 @@
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A621" s="10" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B621" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C621" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="D621" s="13">
         <v>40</v>
-      </c>
-      <c r="C621" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="D621" s="13">
-        <v>300</v>
       </c>
       <c r="E621" s="1">
         <v>0</v>
@@ -13504,16 +13504,16 @@
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A622" s="10" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B622" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C622" s="10" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D622" s="13">
-        <v>300</v>
+        <v>46</v>
       </c>
       <c r="E622" s="1">
         <v>0</v>
@@ -13521,16 +13521,16 @@
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A623" s="10" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B623" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C623" s="10" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D623" s="13">
-        <v>300</v>
+        <v>121</v>
       </c>
       <c r="E623" s="1">
         <v>0</v>
@@ -13541,13 +13541,13 @@
         <v>722</v>
       </c>
       <c r="B624" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C624" s="10" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D624" s="13">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E624" s="1">
         <v>0</v>
@@ -13555,16 +13555,16 @@
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A625" s="10" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B625" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C625" s="10" t="s">
-        <v>489</v>
+        <v>345</v>
       </c>
       <c r="D625" s="13">
-        <v>73</v>
+        <v>300</v>
       </c>
       <c r="E625" s="1">
         <v>0</v>
@@ -13575,13 +13575,13 @@
         <v>723</v>
       </c>
       <c r="B626" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C626" s="10" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D626" s="13">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E626" s="1">
         <v>0</v>
@@ -13589,16 +13589,16 @@
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A627" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B627" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C627" s="10" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D627" s="13">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E627" s="1">
         <v>0</v>
@@ -13606,16 +13606,16 @@
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A628" s="10" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B628" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C628" s="10" t="s">
-        <v>349</v>
+        <v>489</v>
       </c>
       <c r="D628" s="13">
-        <v>280</v>
+        <v>73</v>
       </c>
       <c r="E628" s="1">
         <v>0</v>
@@ -13626,13 +13626,13 @@
         <v>723</v>
       </c>
       <c r="B629" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C629" s="10" t="s">
-        <v>424</v>
+        <v>348</v>
       </c>
       <c r="D629" s="13">
-        <v>42</v>
+        <v>250</v>
       </c>
       <c r="E629" s="1">
         <v>0</v>
@@ -13643,13 +13643,13 @@
         <v>723</v>
       </c>
       <c r="B630" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C630" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D630" s="13">
-        <v>24</v>
+        <v>280</v>
       </c>
       <c r="E630" s="1">
         <v>0</v>
@@ -13657,16 +13657,16 @@
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A631" s="10" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B631" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C631" s="10" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D631" s="13">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E631" s="1">
         <v>0</v>
@@ -13674,16 +13674,16 @@
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632" s="10" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B632" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C632" s="10" t="s">
-        <v>352</v>
+        <v>424</v>
       </c>
       <c r="D632" s="13">
-        <v>1250</v>
+        <v>42</v>
       </c>
       <c r="E632" s="1">
         <v>0</v>
@@ -13691,16 +13691,16 @@
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A633" s="10" t="s">
-        <v>786</v>
+        <v>723</v>
       </c>
       <c r="B633" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C633" s="10" t="s">
-        <v>787</v>
+        <v>350</v>
       </c>
       <c r="D633" s="13">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="E633" s="1">
         <v>0</v>
@@ -13708,16 +13708,16 @@
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A634" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B634" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C634" s="10" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D634" s="13">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="E634" s="1">
         <v>0</v>
@@ -13725,16 +13725,16 @@
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A635" s="10" t="s">
-        <v>786</v>
+        <v>726</v>
       </c>
       <c r="B635" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C635" s="10" t="s">
-        <v>788</v>
+        <v>352</v>
       </c>
       <c r="D635" s="13">
-        <v>50</v>
+        <v>1250</v>
       </c>
       <c r="E635" s="1">
         <v>0</v>
@@ -13742,16 +13742,16 @@
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636" s="10" t="s">
-        <v>726</v>
+        <v>786</v>
       </c>
       <c r="B636" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C636" s="10" t="s">
-        <v>354</v>
+        <v>787</v>
       </c>
       <c r="D636" s="13">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E636" s="1">
         <v>0</v>
@@ -13762,13 +13762,13 @@
         <v>726</v>
       </c>
       <c r="B637" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C637" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D637" s="13">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E637" s="1">
         <v>0</v>
@@ -13782,10 +13782,10 @@
         <v>0</v>
       </c>
       <c r="C638" s="10" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D638" s="13">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E638" s="1">
         <v>0</v>
@@ -13799,10 +13799,10 @@
         <v>40</v>
       </c>
       <c r="C639" s="1" t="s">
-        <v>422</v>
+        <v>354</v>
       </c>
       <c r="D639" s="14">
-        <v>48</v>
+        <v>600</v>
       </c>
       <c r="E639" s="1">
         <v>0</v>
@@ -13813,13 +13813,13 @@
         <v>726</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>423</v>
+        <v>354</v>
       </c>
       <c r="D640" s="14">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="E640" s="1">
         <v>0</v>
@@ -13827,16 +13827,16 @@
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>726</v>
+        <v>786</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C641" s="1" t="s">
-        <v>355</v>
+        <v>789</v>
       </c>
       <c r="D641" s="14">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="E641" s="1">
         <v>0</v>
@@ -13844,16 +13844,16 @@
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>439</v>
+        <v>40</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="D642" s="14">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E642" s="1">
         <v>0</v>
@@ -13861,16 +13861,16 @@
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>356</v>
+        <v>423</v>
       </c>
       <c r="D643" s="14">
-        <v>1300</v>
+        <v>63</v>
       </c>
       <c r="E643" s="1">
         <v>0</v>
@@ -13878,16 +13878,16 @@
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C644" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D644" s="14">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="E644" s="1">
         <v>0</v>
@@ -13898,13 +13898,13 @@
         <v>727</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="C645" s="1" t="s">
-        <v>358</v>
+        <v>450</v>
       </c>
       <c r="D645" s="14">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E645" s="1">
         <v>0</v>
@@ -13912,16 +13912,16 @@
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B646" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C646" s="1" t="s">
-        <v>507</v>
+        <v>356</v>
       </c>
       <c r="D646" s="14">
-        <v>14</v>
+        <v>1300</v>
       </c>
       <c r="E646" s="1">
         <v>0</v>
@@ -13929,16 +13929,16 @@
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B647" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C647" s="1" t="s">
-        <v>508</v>
+        <v>357</v>
       </c>
       <c r="D647" s="14">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E647" s="1">
         <v>0</v>
@@ -13946,16 +13946,16 @@
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B648" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>509</v>
+        <v>358</v>
       </c>
       <c r="D648" s="14">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E648" s="1">
         <v>0</v>
@@ -13963,16 +13963,16 @@
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C649" s="1" t="s">
-        <v>359</v>
+        <v>507</v>
       </c>
       <c r="D649" s="14">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="E649" s="1">
         <v>0</v>
@@ -13980,16 +13980,16 @@
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B650" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C650" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D650" s="14">
         <v>9</v>
-      </c>
-      <c r="C650" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="D650" s="14">
-        <v>123</v>
       </c>
       <c r="E650" s="1">
         <v>0</v>
@@ -13997,16 +13997,16 @@
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>361</v>
+        <v>509</v>
       </c>
       <c r="D651" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E651" s="1">
         <v>0</v>
@@ -14020,10 +14020,10 @@
         <v>9</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D652" s="14">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c r="E652" s="1">
         <v>0</v>
@@ -14031,16 +14031,16 @@
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C653" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D653" s="14">
-        <v>600</v>
+        <v>123</v>
       </c>
       <c r="E653" s="1">
         <v>0</v>
@@ -14048,16 +14048,16 @@
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C654" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D654" s="14">
-        <v>825</v>
+        <v>8</v>
       </c>
       <c r="E654" s="1">
         <v>0</v>
@@ -14065,16 +14065,16 @@
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C655" s="1" t="s">
-        <v>790</v>
+        <v>362</v>
       </c>
       <c r="D655" s="14">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E655" s="1">
         <v>0</v>
@@ -14082,13 +14082,13 @@
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C656" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D656" s="14">
         <v>600</v>
@@ -14099,16 +14099,16 @@
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C657" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D657" s="14">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="E657" s="1">
         <v>0</v>
@@ -14122,10 +14122,10 @@
         <v>0</v>
       </c>
       <c r="C658" s="1" t="s">
-        <v>490</v>
+        <v>790</v>
       </c>
       <c r="D658" s="14">
-        <v>7</v>
+        <v>500</v>
       </c>
       <c r="E658" s="1">
         <v>0</v>
@@ -14133,16 +14133,16 @@
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B659" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C659" s="1" t="s">
-        <v>491</v>
+        <v>365</v>
       </c>
       <c r="D659" s="14">
-        <v>65</v>
+        <v>800</v>
       </c>
       <c r="E659" s="1">
         <v>0</v>
@@ -14153,13 +14153,13 @@
         <v>731</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C660" s="1" t="s">
-        <v>406</v>
+        <v>365</v>
       </c>
       <c r="D660" s="14">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="E660" s="1">
         <v>0</v>
@@ -14167,16 +14167,16 @@
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C661" s="1" t="s">
-        <v>366</v>
+        <v>490</v>
       </c>
       <c r="D661" s="14">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="E661" s="1">
         <v>0</v>
@@ -14184,16 +14184,16 @@
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B662" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>367</v>
+        <v>491</v>
       </c>
       <c r="D662" s="14">
-        <v>1501</v>
+        <v>65</v>
       </c>
       <c r="E662" s="1">
         <v>0</v>
@@ -14201,16 +14201,16 @@
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C663" s="1" t="s">
-        <v>368</v>
+        <v>406</v>
       </c>
       <c r="D663" s="14">
-        <v>1508</v>
+        <v>80</v>
       </c>
       <c r="E663" s="1">
         <v>0</v>
@@ -14218,16 +14218,16 @@
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D664" s="14">
-        <v>600</v>
+        <v>72</v>
       </c>
       <c r="E664" s="1">
         <v>0</v>
@@ -14235,16 +14235,16 @@
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B665" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C665" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D665" s="14">
-        <v>400</v>
+        <v>1501</v>
       </c>
       <c r="E665" s="1">
         <v>0</v>
@@ -14252,16 +14252,16 @@
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B666" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C666" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D666" s="14">
-        <v>300</v>
+        <v>1508</v>
       </c>
       <c r="E666" s="1">
         <v>0</v>
@@ -14275,10 +14275,10 @@
         <v>0</v>
       </c>
       <c r="C667" s="1" t="s">
-        <v>552</v>
+        <v>369</v>
       </c>
       <c r="D667" s="14">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="E667" s="1">
         <v>0</v>
@@ -14292,10 +14292,10 @@
         <v>0</v>
       </c>
       <c r="C668" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D668" s="14">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E668" s="1">
         <v>0</v>
@@ -14309,10 +14309,10 @@
         <v>0</v>
       </c>
       <c r="C669" s="1" t="s">
-        <v>438</v>
+        <v>371</v>
       </c>
       <c r="D669" s="14">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E669" s="1">
         <v>0</v>
@@ -14326,10 +14326,10 @@
         <v>0</v>
       </c>
       <c r="C670" s="1" t="s">
-        <v>373</v>
+        <v>552</v>
       </c>
       <c r="D670" s="14">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E670" s="1">
         <v>0</v>
@@ -14337,16 +14337,16 @@
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>720</v>
+        <v>734</v>
       </c>
       <c r="B671" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C671" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D671" s="14">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="E671" s="1">
         <v>0</v>
@@ -14354,16 +14354,16 @@
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>720</v>
+        <v>734</v>
       </c>
       <c r="B672" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C672" s="1" t="s">
-        <v>375</v>
+        <v>438</v>
       </c>
       <c r="D672" s="14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E672" s="1">
         <v>0</v>
@@ -14371,16 +14371,16 @@
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B673" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C673" s="1" t="s">
-        <v>510</v>
+        <v>373</v>
       </c>
       <c r="D673" s="14">
-        <v>13</v>
+        <v>500</v>
       </c>
       <c r="E673" s="1">
         <v>0</v>
@@ -14388,16 +14388,16 @@
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="B674" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C674" s="1" t="s">
-        <v>511</v>
+        <v>374</v>
       </c>
       <c r="D674" s="14">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="E674" s="1">
         <v>0</v>
@@ -14405,16 +14405,16 @@
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="B675" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C675" s="1" t="s">
-        <v>512</v>
+        <v>375</v>
       </c>
       <c r="D675" s="14">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="E675" s="1">
         <v>0</v>
@@ -14422,16 +14422,16 @@
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>721</v>
+        <v>735</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C676" s="1" t="s">
-        <v>376</v>
+        <v>510</v>
       </c>
       <c r="D676" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E676" s="1">
         <v>0</v>
@@ -14439,16 +14439,16 @@
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>721</v>
+        <v>735</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C677" s="1" t="s">
-        <v>377</v>
+        <v>511</v>
       </c>
       <c r="D677" s="14">
-        <v>225</v>
+        <v>24</v>
       </c>
       <c r="E677" s="1">
         <v>0</v>
@@ -14456,16 +14456,16 @@
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>721</v>
+        <v>735</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C678" s="1" t="s">
-        <v>378</v>
+        <v>512</v>
       </c>
       <c r="D678" s="14">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="E678" s="1">
         <v>0</v>
@@ -14473,16 +14473,16 @@
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C679" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D679" s="14">
-        <v>1200</v>
+        <v>15</v>
       </c>
       <c r="E679" s="1">
         <v>0</v>
@@ -14490,16 +14490,16 @@
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C680" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D680" s="14">
-        <v>1200</v>
+        <v>225</v>
       </c>
       <c r="E680" s="1">
         <v>0</v>
@@ -14507,16 +14507,16 @@
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C681" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D681" s="14">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="E681" s="1">
         <v>0</v>
@@ -14527,13 +14527,13 @@
         <v>736</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C682" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D682" s="14">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="E682" s="1">
         <v>0</v>
@@ -14547,10 +14547,10 @@
         <v>40</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D683" s="14">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="E683" s="1">
         <v>0</v>
@@ -14558,16 +14558,16 @@
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B684" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C684" s="1" t="s">
-        <v>791</v>
+        <v>381</v>
       </c>
       <c r="D684" s="14">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="E684" s="1">
         <v>0</v>
@@ -14578,13 +14578,13 @@
         <v>736</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C685" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D685" s="14">
-        <v>950</v>
+        <v>300</v>
       </c>
       <c r="E685" s="1">
         <v>0</v>
@@ -14598,10 +14598,10 @@
         <v>40</v>
       </c>
       <c r="C686" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D686" s="14">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E686" s="1">
         <v>0</v>
@@ -14609,16 +14609,16 @@
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B687" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C687" s="1" t="s">
-        <v>384</v>
+        <v>791</v>
       </c>
       <c r="D687" s="14">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E687" s="1">
         <v>0</v>
@@ -14632,10 +14632,10 @@
         <v>0</v>
       </c>
       <c r="C688" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D688" s="14">
-        <v>225</v>
+        <v>950</v>
       </c>
       <c r="E688" s="1">
         <v>0</v>
@@ -14643,16 +14643,16 @@
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C689" s="1" t="s">
-        <v>492</v>
+        <v>383</v>
       </c>
       <c r="D689" s="14">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="E689" s="1">
         <v>0</v>
@@ -14666,10 +14666,10 @@
         <v>0</v>
       </c>
       <c r="C690" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D690" s="14">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="E690" s="1">
         <v>0</v>
@@ -14680,13 +14680,13 @@
         <v>736</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C691" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D691" s="14">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="E691" s="1">
         <v>0</v>
@@ -14694,16 +14694,16 @@
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B692" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C692" s="1" t="s">
-        <v>387</v>
+        <v>492</v>
       </c>
       <c r="D692" s="14">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="E692" s="1">
         <v>0</v>
@@ -14714,13 +14714,13 @@
         <v>736</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C693" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D693" s="14">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="E693" s="1">
         <v>0</v>
@@ -14731,13 +14731,13 @@
         <v>736</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C694" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D694" s="14">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E694" s="1">
         <v>0</v>
@@ -14751,10 +14751,10 @@
         <v>0</v>
       </c>
       <c r="C695" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D695" s="14">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="E695" s="1">
         <v>0</v>
@@ -14768,12 +14768,63 @@
         <v>40</v>
       </c>
       <c r="C696" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D696" s="14">
+        <v>100</v>
+      </c>
+      <c r="E696" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A697" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C697" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D697" s="14">
+        <v>60</v>
+      </c>
+      <c r="E697" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A698" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C698" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D696" s="14">
+      <c r="D698" s="14">
         <v>64</v>
       </c>
-      <c r="E696" s="1">
+      <c r="E698" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A699" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C699" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D699" s="14">
+        <v>30</v>
+      </c>
+      <c r="E699" s="1">
         <v>0</v>
       </c>
     </row>

--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89438499-D406-4A88-A889-A198DA4468EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE3D8DA-92F9-4D7E-A8B8-79AD84A0AD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="792">
   <si>
     <t>3-ديوان</t>
   </si>
@@ -1603,9 +1603,6 @@
     <t>شاسيه صندوق تعليق غروهي مع رجلين 39452000 GROHE</t>
   </si>
   <si>
-    <t>مغسلة ابيض مع نص عامود صبة وحدة 402 AGA Ceramic</t>
-  </si>
-  <si>
     <t>قسطل حديد 1 1/4</t>
   </si>
   <si>
@@ -2435,6 +2432,9 @@
   </si>
   <si>
     <t>وصل مخالف تلحيم 25*40 ملم اخضر ايطالي ITALY RIETTI</t>
+  </si>
+  <si>
+    <t>قطع وصل ذكر تلحيم 25*3/4 ملم اخضر ايطالي ITALY RIETTI</t>
   </si>
 </sst>
 </file>
@@ -2961,7 +2961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E5C9A6-5EC3-4592-9122-0E1001CE6231}">
-  <dimension ref="A1:E699"/>
+  <dimension ref="A1:E698"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.8984375" style="2" bestFit="1" customWidth="1"/>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>0</v>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>0</v>
@@ -3032,7 +3032,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>0</v>
@@ -3049,7 +3049,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>0</v>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>0</v>
@@ -3083,7 +3083,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>9</v>
@@ -3100,7 +3100,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>0</v>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>0</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>0</v>
@@ -3143,7 +3143,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="13">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>0</v>
@@ -3168,7 +3168,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>9</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D15" s="13">
         <v>5</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>0</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>0</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>0</v>
@@ -3270,13 +3270,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D20" s="13">
         <v>360</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>0</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>0</v>
@@ -3321,13 +3321,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D23" s="13">
         <v>8</v>
@@ -3338,13 +3338,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D24" s="13">
         <v>2</v>
@@ -3355,7 +3355,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>0</v>
@@ -3372,7 +3372,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>0</v>
@@ -3389,13 +3389,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D27" s="13">
         <v>2</v>
@@ -3406,7 +3406,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>0</v>
@@ -3423,13 +3423,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D29" s="13">
         <v>7</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>0</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>0</v>
@@ -3508,7 +3508,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>0</v>
@@ -3525,7 +3525,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>0</v>
@@ -3576,7 +3576,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>0</v>
@@ -3593,7 +3593,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>0</v>
@@ -3610,7 +3610,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>0</v>
@@ -3627,7 +3627,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>0</v>
@@ -3644,7 +3644,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>0</v>
@@ -3661,7 +3661,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>0</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>0</v>
@@ -3695,7 +3695,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>0</v>
@@ -3712,13 +3712,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D46" s="13">
         <v>790</v>
@@ -3729,7 +3729,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>0</v>
@@ -3746,7 +3746,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>0</v>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>0</v>
@@ -3780,7 +3780,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>0</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>40</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>40</v>
@@ -3831,7 +3831,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>40</v>
@@ -3848,7 +3848,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>0</v>
@@ -3865,13 +3865,13 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D55" s="13">
         <v>240</v>
@@ -3882,7 +3882,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>0</v>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>0</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B61" s="10" t="s">
         <v>9</v>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>9</v>
@@ -4001,7 +4001,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>9</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>0</v>
@@ -4035,7 +4035,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>9</v>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>0</v>
@@ -4069,7 +4069,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>0</v>
@@ -4103,7 +4103,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>0</v>
@@ -4120,7 +4120,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>9</v>
@@ -4137,7 +4137,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B71" s="10" t="s">
         <v>9</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>0</v>
@@ -4171,16 +4171,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D73" s="13">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
@@ -4188,16 +4188,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D74" s="13">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
@@ -4205,7 +4205,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>0</v>
@@ -4222,7 +4222,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>0</v>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B77" s="10" t="s">
         <v>40</v>
@@ -4256,13 +4256,13 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C78" s="10" t="s">
         <v>775</v>
-      </c>
-      <c r="B78" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>776</v>
       </c>
       <c r="D78" s="13">
         <v>80</v>
@@ -4273,7 +4273,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>0</v>
@@ -4290,7 +4290,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B80" s="10" t="s">
         <v>40</v>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B81" s="10" t="s">
         <v>40</v>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>0</v>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B83" s="10" t="s">
         <v>40</v>
@@ -4358,16 +4358,16 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D84" s="13">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="E84" s="1">
         <v>0</v>
@@ -4375,7 +4375,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>40</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>9</v>
@@ -4409,7 +4409,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>0</v>
@@ -4426,7 +4426,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>0</v>
@@ -4435,7 +4435,7 @@
         <v>475</v>
       </c>
       <c r="D88" s="13">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E88" s="1">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B89" s="10" t="s">
         <v>9</v>
@@ -4460,7 +4460,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B90" s="10" t="s">
         <v>0</v>
@@ -4477,7 +4477,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>40</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>0</v>
@@ -4511,7 +4511,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B93" s="10" t="s">
         <v>40</v>
@@ -4528,7 +4528,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B94" s="10" t="s">
         <v>0</v>
@@ -4545,7 +4545,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B95" s="10" t="s">
         <v>40</v>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B96" s="10" t="s">
         <v>40</v>
@@ -4579,7 +4579,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B97" s="10" t="s">
         <v>0</v>
@@ -4596,7 +4596,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>9</v>
@@ -4613,7 +4613,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B99" s="10" t="s">
         <v>9</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B100" s="10" t="s">
         <v>0</v>
@@ -4647,13 +4647,13 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D101" s="13">
         <v>4</v>
@@ -4664,7 +4664,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>0</v>
@@ -4681,13 +4681,13 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B103" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D103" s="13">
         <v>4</v>
@@ -4698,7 +4698,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B104" s="10" t="s">
         <v>0</v>
@@ -4715,13 +4715,13 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B105" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D105" s="13">
         <v>8</v>
@@ -4732,13 +4732,13 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D106" s="13">
         <v>4</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>9</v>
@@ -4766,7 +4766,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>0</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B109" s="10" t="s">
         <v>0</v>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>0</v>
@@ -4817,7 +4817,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B111" s="10" t="s">
         <v>0</v>
@@ -4834,7 +4834,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B112" s="10" t="s">
         <v>0</v>
@@ -4851,7 +4851,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B113" s="10" t="s">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B114" s="10" t="s">
         <v>0</v>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B115" s="10" t="s">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>40</v>
@@ -4919,7 +4919,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B117" s="10" t="s">
         <v>0</v>
@@ -4936,7 +4936,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B118" s="10" t="s">
         <v>0</v>
@@ -4953,7 +4953,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B119" s="10" t="s">
         <v>0</v>
@@ -4970,7 +4970,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B120" s="10" t="s">
         <v>0</v>
@@ -4987,13 +4987,13 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B121" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D121" s="13">
         <v>1</v>
@@ -5004,13 +5004,13 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D122" s="13">
         <v>2</v>
@@ -5021,7 +5021,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B123" s="10" t="s">
         <v>40</v>
@@ -5038,7 +5038,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B124" s="10" t="s">
         <v>40</v>
@@ -5055,7 +5055,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B125" s="10" t="s">
         <v>40</v>
@@ -5072,7 +5072,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B126" s="10" t="s">
         <v>40</v>
@@ -5089,7 +5089,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B127" s="10" t="s">
         <v>40</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B128" s="10" t="s">
         <v>0</v>
@@ -5123,7 +5123,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B129" s="10" t="s">
         <v>40</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B130" s="10" t="s">
         <v>40</v>
@@ -5157,7 +5157,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B131" s="10" t="s">
         <v>0</v>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B132" s="10" t="s">
         <v>0</v>
@@ -5191,7 +5191,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B133" s="10" t="s">
         <v>40</v>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B134" s="10" t="s">
         <v>0</v>
@@ -5225,7 +5225,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B135" s="10" t="s">
         <v>40</v>
@@ -5242,7 +5242,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B136" s="10" t="s">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B137" s="10" t="s">
         <v>40</v>
@@ -5276,7 +5276,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B138" s="10" t="s">
         <v>40</v>
@@ -5293,7 +5293,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B139" s="10" t="s">
         <v>0</v>
@@ -5310,7 +5310,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B140" s="10" t="s">
         <v>40</v>
@@ -5327,7 +5327,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B141" s="10" t="s">
         <v>40</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B142" s="10" t="s">
         <v>0</v>
@@ -5361,7 +5361,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B143" s="10" t="s">
         <v>40</v>
@@ -5378,7 +5378,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B144" s="10" t="s">
         <v>40</v>
@@ -5395,7 +5395,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B145" s="10" t="s">
         <v>40</v>
@@ -5412,7 +5412,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B146" s="10" t="s">
         <v>40</v>
@@ -5429,7 +5429,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B147" s="10" t="s">
         <v>40</v>
@@ -5446,7 +5446,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B148" s="10" t="s">
         <v>40</v>
@@ -5463,7 +5463,7 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B149" s="10" t="s">
         <v>40</v>
@@ -5480,7 +5480,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B150" s="10" t="s">
         <v>40</v>
@@ -5497,7 +5497,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B151" s="10" t="s">
         <v>0</v>
@@ -5514,7 +5514,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B152" s="10" t="s">
         <v>40</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B153" s="10" t="s">
         <v>0</v>
@@ -5548,7 +5548,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B154" s="10" t="s">
         <v>40</v>
@@ -5565,7 +5565,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B155" s="10" t="s">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B156" s="10" t="s">
         <v>0</v>
@@ -5599,7 +5599,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B157" s="10" t="s">
         <v>0</v>
@@ -5616,7 +5616,7 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B158" s="10" t="s">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B159" s="10" t="s">
         <v>40</v>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B160" s="10" t="s">
         <v>0</v>
@@ -5667,7 +5667,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B161" s="10" t="s">
         <v>0</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B162" s="10" t="s">
         <v>0</v>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B163" s="10" t="s">
         <v>0</v>
@@ -5718,7 +5718,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B164" s="10" t="s">
         <v>40</v>
@@ -5735,7 +5735,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B165" s="10" t="s">
         <v>0</v>
@@ -5752,7 +5752,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B166" s="10" t="s">
         <v>0</v>
@@ -5769,7 +5769,7 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B167" s="10" t="s">
         <v>0</v>
@@ -5786,7 +5786,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B168" s="10" t="s">
         <v>0</v>
@@ -5803,7 +5803,7 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B169" s="10" t="s">
         <v>40</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B170" s="10" t="s">
         <v>0</v>
@@ -5837,7 +5837,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B171" s="10" t="s">
         <v>0</v>
@@ -5854,7 +5854,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B172" s="10" t="s">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B173" s="10" t="s">
         <v>0</v>
@@ -5888,7 +5888,7 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B174" s="10" t="s">
         <v>0</v>
@@ -5905,7 +5905,7 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B175" s="10" t="s">
         <v>0</v>
@@ -5922,7 +5922,7 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B176" s="10" t="s">
         <v>0</v>
@@ -5939,16 +5939,16 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>464</v>
       </c>
       <c r="D177" s="13">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E177" s="1">
         <v>0</v>
@@ -5956,16 +5956,16 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>464</v>
       </c>
       <c r="D178" s="13">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E178" s="1">
         <v>0</v>
@@ -5973,7 +5973,7 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B179" s="10" t="s">
         <v>0</v>
@@ -5990,7 +5990,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B180" s="10" t="s">
         <v>0</v>
@@ -6007,13 +6007,13 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B181" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D181" s="13">
         <v>1</v>
@@ -6024,7 +6024,7 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B182" s="10" t="s">
         <v>40</v>
@@ -6041,7 +6041,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B183" s="10" t="s">
         <v>0</v>
@@ -6058,16 +6058,16 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C184" s="10" t="s">
         <v>119</v>
       </c>
       <c r="D184" s="13">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E184" s="1">
         <v>0</v>
@@ -6075,16 +6075,16 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C185" s="10" t="s">
         <v>119</v>
       </c>
       <c r="D185" s="13">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E185" s="1">
         <v>0</v>
@@ -6092,7 +6092,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B186" s="10" t="s">
         <v>40</v>
@@ -6109,7 +6109,7 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B187" s="10" t="s">
         <v>40</v>
@@ -6126,7 +6126,7 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B188" s="10" t="s">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B189" s="10" t="s">
         <v>40</v>
@@ -6160,7 +6160,7 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B190" s="10" t="s">
         <v>0</v>
@@ -6177,13 +6177,13 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B191" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D191" s="13">
         <v>14</v>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B192" s="10" t="s">
         <v>9</v>
@@ -6211,13 +6211,13 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B193" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D193" s="13">
         <v>600</v>
@@ -6228,13 +6228,13 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B194" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D194" s="13">
         <v>240</v>
@@ -6245,13 +6245,13 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B195" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D195" s="13">
         <v>1200</v>
@@ -6262,7 +6262,7 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B196" s="10" t="s">
         <v>0</v>
@@ -6279,13 +6279,13 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B197" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D197" s="13">
         <v>600</v>
@@ -6296,13 +6296,13 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B198" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D198" s="13">
         <v>3040</v>
@@ -6313,7 +6313,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B199" s="10" t="s">
         <v>0</v>
@@ -6330,13 +6330,13 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B200" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D200" s="13">
         <v>1200</v>
@@ -6347,7 +6347,7 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="10" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B201" s="10" t="s">
         <v>40</v>
@@ -6364,7 +6364,7 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="10" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B202" s="10" t="s">
         <v>0</v>
@@ -6381,7 +6381,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="10" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B203" s="10" t="s">
         <v>40</v>
@@ -6398,7 +6398,7 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="10" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B204" s="10" t="s">
         <v>40</v>
@@ -6415,7 +6415,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="10" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B205" s="10" t="s">
         <v>40</v>
@@ -6432,7 +6432,7 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="10" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B206" s="10" t="s">
         <v>40</v>
@@ -6449,7 +6449,7 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B207" s="10" t="s">
         <v>0</v>
@@ -6466,7 +6466,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B208" s="10" t="s">
         <v>0</v>
@@ -6483,7 +6483,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B209" s="10" t="s">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B210" s="10" t="s">
         <v>0</v>
@@ -6517,7 +6517,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B211" s="10" t="s">
         <v>0</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B212" s="10" t="s">
         <v>0</v>
@@ -6551,7 +6551,7 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B213" s="10" t="s">
         <v>0</v>
@@ -6568,7 +6568,7 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="10" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B214" s="10" t="s">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="10" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B215" s="10" t="s">
         <v>0</v>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="10" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B216" s="10" t="s">
         <v>0</v>
@@ -6619,13 +6619,13 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B217" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C217" s="10" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D217" s="13">
         <v>21</v>
@@ -6636,7 +6636,7 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B218" s="10" t="s">
         <v>0</v>
@@ -6653,7 +6653,7 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="10" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B219" s="10" t="s">
         <v>0</v>
@@ -6670,7 +6670,7 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="10" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B220" s="10" t="s">
         <v>0</v>
@@ -6687,7 +6687,7 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="10" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B221" s="10" t="s">
         <v>0</v>
@@ -6704,7 +6704,7 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="10" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B222" s="10" t="s">
         <v>0</v>
@@ -6721,7 +6721,7 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="10" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B223" s="10" t="s">
         <v>0</v>
@@ -6738,7 +6738,7 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="10" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B224" s="10" t="s">
         <v>0</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="10" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B225" s="10" t="s">
         <v>0</v>
@@ -6772,13 +6772,13 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B226" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C226" s="10" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D226" s="13">
         <v>7</v>
@@ -6789,13 +6789,13 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B227" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C227" s="10" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D227" s="13">
         <v>19</v>
@@ -6806,7 +6806,7 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B228" s="10" t="s">
         <v>0</v>
@@ -6823,7 +6823,7 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B229" s="10" t="s">
         <v>0</v>
@@ -6840,13 +6840,13 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B230" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C230" s="10" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D230" s="13">
         <v>1</v>
@@ -6857,7 +6857,7 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B231" s="10" t="s">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B232" s="10" t="s">
         <v>0</v>
@@ -6891,7 +6891,7 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B233" s="10" t="s">
         <v>0</v>
@@ -6908,7 +6908,7 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="10" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B234" s="10" t="s">
         <v>0</v>
@@ -6925,7 +6925,7 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B235" s="10" t="s">
         <v>40</v>
@@ -6942,7 +6942,7 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B236" s="10" t="s">
         <v>40</v>
@@ -6959,7 +6959,7 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B237" s="10" t="s">
         <v>0</v>
@@ -6976,7 +6976,7 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="10" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B238" s="10" t="s">
         <v>0</v>
@@ -6993,7 +6993,7 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="10" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B239" s="10" t="s">
         <v>0</v>
@@ -7010,7 +7010,7 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B240" s="10" t="s">
         <v>0</v>
@@ -7027,13 +7027,13 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B241" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D241" s="13">
         <v>16</v>
@@ -7044,7 +7044,7 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B242" s="10" t="s">
         <v>9</v>
@@ -7061,7 +7061,7 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="10" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B243" s="10" t="s">
         <v>40</v>
@@ -7078,7 +7078,7 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B244" s="10" t="s">
         <v>40</v>
@@ -7095,7 +7095,7 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B245" s="10" t="s">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="10" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B246" s="10" t="s">
         <v>40</v>
@@ -7129,13 +7129,13 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B247" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C247" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D247" s="13">
         <v>60</v>
@@ -7146,7 +7146,7 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="10" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B248" s="10" t="s">
         <v>0</v>
@@ -7163,7 +7163,7 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="10" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B249" s="10" t="s">
         <v>40</v>
@@ -7180,7 +7180,7 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B250" s="10" t="s">
         <v>40</v>
@@ -7197,7 +7197,7 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B251" s="10" t="s">
         <v>0</v>
@@ -7214,7 +7214,7 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="10" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B252" s="10" t="s">
         <v>0</v>
@@ -7231,7 +7231,7 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B253" s="10" t="s">
         <v>40</v>
@@ -7248,7 +7248,7 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="10" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B254" s="10" t="s">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B255" s="10" t="s">
         <v>9</v>
@@ -7282,16 +7282,16 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C256" s="10" t="s">
         <v>161</v>
       </c>
       <c r="D256" s="13">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E256" s="1">
         <v>0</v>
@@ -7299,16 +7299,16 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C257" s="10" t="s">
         <v>161</v>
       </c>
       <c r="D257" s="13">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E257" s="1">
         <v>0</v>
@@ -7316,7 +7316,7 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B258" s="10" t="s">
         <v>0</v>
@@ -7333,7 +7333,7 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B259" s="10" t="s">
         <v>0</v>
@@ -7350,7 +7350,7 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B260" s="10" t="s">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B261" s="10" t="s">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B262" s="10" t="s">
         <v>0</v>
@@ -7401,7 +7401,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B263" s="10" t="s">
         <v>0</v>
@@ -7418,7 +7418,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B264" s="10" t="s">
         <v>0</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="10" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B265" s="10" t="s">
         <v>0</v>
@@ -7452,7 +7452,7 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="10" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B266" s="10" t="s">
         <v>0</v>
@@ -7469,13 +7469,13 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="10" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B267" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D267" s="13">
         <v>28</v>
@@ -7486,7 +7486,7 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B268" s="10" t="s">
         <v>0</v>
@@ -7503,7 +7503,7 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B269" s="10" t="s">
         <v>0</v>
@@ -7520,13 +7520,13 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B270" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C270" s="10" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D270" s="13">
         <v>12</v>
@@ -7537,7 +7537,7 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B271" s="10" t="s">
         <v>9</v>
@@ -7554,7 +7554,7 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B272" s="10" t="s">
         <v>9</v>
@@ -7571,7 +7571,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B273" s="10" t="s">
         <v>0</v>
@@ -7588,13 +7588,13 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B274" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C274" s="10" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D274" s="13">
         <v>40</v>
@@ -7605,13 +7605,13 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B275" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C275" s="10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D275" s="13">
         <v>60</v>
@@ -7622,7 +7622,7 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B276" s="10" t="s">
         <v>0</v>
@@ -7639,7 +7639,7 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B277" s="10" t="s">
         <v>0</v>
@@ -7656,13 +7656,13 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B278" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C278" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D278" s="13">
         <v>40</v>
@@ -7673,7 +7673,7 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B279" s="10" t="s">
         <v>0</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B280" s="10" t="s">
         <v>0</v>
@@ -7707,7 +7707,7 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B281" s="10" t="s">
         <v>0</v>
@@ -7724,7 +7724,7 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B282" s="10" t="s">
         <v>0</v>
@@ -7741,13 +7741,13 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B283" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C283" s="10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D283" s="13">
         <v>4</v>
@@ -7758,7 +7758,7 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B284" s="10" t="s">
         <v>0</v>
@@ -7775,13 +7775,13 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="10" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B285" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C285" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D285" s="13">
         <v>1</v>
@@ -7792,7 +7792,7 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="10" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B286" s="10" t="s">
         <v>0</v>
@@ -7809,7 +7809,7 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="10" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B287" s="10" t="s">
         <v>0</v>
@@ -7826,13 +7826,13 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="10" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B288" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C288" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D288" s="13">
         <v>12</v>
@@ -7843,13 +7843,13 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="10" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B289" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D289" s="13">
         <v>4</v>
@@ -7860,13 +7860,13 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B290" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C290" s="10" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D290" s="13">
         <v>1</v>
@@ -7877,7 +7877,7 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B291" s="10" t="s">
         <v>0</v>
@@ -7894,7 +7894,7 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B292" s="10" t="s">
         <v>0</v>
@@ -7911,7 +7911,7 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B293" s="10" t="s">
         <v>0</v>
@@ -7928,13 +7928,13 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B294" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C294" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D294" s="13">
         <v>1</v>
@@ -7945,7 +7945,7 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B295" s="10" t="s">
         <v>40</v>
@@ -7962,16 +7962,16 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B296" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D296" s="13">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E296" s="1">
         <v>0</v>
@@ -7979,13 +7979,13 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B297" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C297" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D297" s="13">
         <v>89</v>
@@ -7996,7 +7996,7 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B298" s="10" t="s">
         <v>40</v>
@@ -8013,7 +8013,7 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B299" s="10" t="s">
         <v>40</v>
@@ -8030,13 +8030,13 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B300" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C300" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D300" s="13">
         <v>15</v>
@@ -8047,13 +8047,13 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B301" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C301" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D301" s="13">
         <v>7</v>
@@ -8064,16 +8064,16 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B302" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D302" s="13">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E302" s="1">
         <v>0</v>
@@ -8081,16 +8081,16 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B303" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C303" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D303" s="13">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E303" s="1">
         <v>0</v>
@@ -8098,7 +8098,7 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B304" s="10" t="s">
         <v>40</v>
@@ -8115,7 +8115,7 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B305" s="10" t="s">
         <v>40</v>
@@ -8132,13 +8132,13 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B306" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C306" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D306" s="13">
         <v>14</v>
@@ -8149,13 +8149,13 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B307" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C307" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D307" s="13">
         <v>15</v>
@@ -8166,13 +8166,13 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="10" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B308" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C308" s="10" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D308" s="13">
         <v>300</v>
@@ -8183,7 +8183,7 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="10" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B309" s="10" t="s">
         <v>0</v>
@@ -8200,16 +8200,16 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C310" s="10" t="s">
         <v>193</v>
       </c>
       <c r="D310" s="13">
-        <v>475</v>
+        <v>650</v>
       </c>
       <c r="E310" s="1">
         <v>0</v>
@@ -8217,16 +8217,16 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B311" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C311" s="10" t="s">
         <v>193</v>
       </c>
       <c r="D311" s="13">
-        <v>650</v>
+        <v>475</v>
       </c>
       <c r="E311" s="1">
         <v>0</v>
@@ -8234,7 +8234,7 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="10" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B312" s="10" t="s">
         <v>40</v>
@@ -8251,7 +8251,7 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B313" s="10" t="s">
         <v>40</v>
@@ -8268,16 +8268,16 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C314" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D314" s="13">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="E314" s="1">
         <v>0</v>
@@ -8285,16 +8285,16 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C315" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D315" s="13">
-        <v>125</v>
+        <v>880</v>
       </c>
       <c r="E315" s="1">
         <v>0</v>
@@ -8302,16 +8302,16 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C316" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D316" s="13">
-        <v>880</v>
+        <v>175</v>
       </c>
       <c r="E316" s="1">
         <v>0</v>
@@ -8319,13 +8319,13 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B317" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C317" s="10" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D317" s="13">
         <v>990</v>
@@ -8336,7 +8336,7 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B318" s="10" t="s">
         <v>40</v>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="10" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B319" s="10" t="s">
         <v>0</v>
@@ -8370,7 +8370,7 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B320" s="10" t="s">
         <v>9</v>
@@ -8387,7 +8387,7 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B321" s="10" t="s">
         <v>40</v>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="10" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B322" s="10" t="s">
         <v>0</v>
@@ -8421,7 +8421,7 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B323" s="10" t="s">
         <v>40</v>
@@ -8438,16 +8438,16 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B324" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C324" s="10" t="s">
         <v>197</v>
       </c>
       <c r="D324" s="13">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="E324" s="1">
         <v>0</v>
@@ -8455,16 +8455,16 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C325" s="10" t="s">
         <v>197</v>
       </c>
       <c r="D325" s="13">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E325" s="1">
         <v>0</v>
@@ -8472,7 +8472,7 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="10" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B326" s="10" t="s">
         <v>40</v>
@@ -8489,7 +8489,7 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="10" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B327" s="10" t="s">
         <v>40</v>
@@ -8506,13 +8506,13 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B328" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C328" s="10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D328" s="13">
         <v>17</v>
@@ -8523,13 +8523,13 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B329" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C329" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D329" s="13">
         <v>5</v>
@@ -8540,13 +8540,13 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B330" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C330" s="10" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D330" s="13">
         <v>8</v>
@@ -8557,13 +8557,13 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B331" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C331" s="10" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D331" s="13">
         <v>1</v>
@@ -8574,13 +8574,13 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B332" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C332" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D332" s="13">
         <v>10</v>
@@ -8591,13 +8591,13 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B333" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C333" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D333" s="13">
         <v>25</v>
@@ -8608,13 +8608,13 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B334" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C334" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D334" s="13">
         <v>10</v>
@@ -8625,7 +8625,7 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B335" s="10" t="s">
         <v>40</v>
@@ -8642,7 +8642,7 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B336" s="10" t="s">
         <v>40</v>
@@ -8659,7 +8659,7 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B337" s="10" t="s">
         <v>40</v>
@@ -8676,16 +8676,16 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B338" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C338" s="10" t="s">
         <v>202</v>
       </c>
       <c r="D338" s="13">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="E338" s="1">
         <v>0</v>
@@ -8693,16 +8693,16 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B339" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C339" s="10" t="s">
         <v>202</v>
       </c>
       <c r="D339" s="13">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="E339" s="1">
         <v>0</v>
@@ -8710,7 +8710,7 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B340" s="10" t="s">
         <v>40</v>
@@ -8727,7 +8727,7 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B341" s="10" t="s">
         <v>40</v>
@@ -8744,7 +8744,7 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B342" s="10" t="s">
         <v>40</v>
@@ -8761,16 +8761,16 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C343" s="10" t="s">
         <v>204</v>
       </c>
       <c r="D343" s="13">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E343" s="1">
         <v>0</v>
@@ -8778,16 +8778,16 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C344" s="10" t="s">
         <v>204</v>
       </c>
       <c r="D344" s="13">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="E344" s="1">
         <v>0</v>
@@ -8795,7 +8795,7 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B345" s="10" t="s">
         <v>0</v>
@@ -8812,7 +8812,7 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B346" s="10" t="s">
         <v>40</v>
@@ -8829,16 +8829,16 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" s="10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B347" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C347" s="10" t="s">
         <v>206</v>
       </c>
       <c r="D347" s="13">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E347" s="1">
         <v>0</v>
@@ -8846,16 +8846,16 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B348" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C348" s="10" t="s">
         <v>206</v>
       </c>
       <c r="D348" s="13">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E348" s="1">
         <v>0</v>
@@ -8863,7 +8863,7 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="10" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B349" s="10" t="s">
         <v>0</v>
@@ -8880,7 +8880,7 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B350" s="10" t="s">
         <v>40</v>
@@ -8897,7 +8897,7 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B351" s="10" t="s">
         <v>40</v>
@@ -8914,16 +8914,16 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="10" t="s">
-        <v>691</v>
+        <v>779</v>
       </c>
       <c r="B352" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C352" s="10" t="s">
-        <v>208</v>
+        <v>791</v>
       </c>
       <c r="D352" s="13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E352" s="1">
         <v>0</v>
@@ -8931,7 +8931,7 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B353" s="10" t="s">
         <v>40</v>
@@ -8948,13 +8948,13 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="B354" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C354" s="10" t="s">
         <v>780</v>
-      </c>
-      <c r="B354" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C354" s="10" t="s">
-        <v>781</v>
       </c>
       <c r="D354" s="13">
         <v>50</v>
@@ -8965,7 +8965,7 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B355" s="10" t="s">
         <v>40</v>
@@ -8982,7 +8982,7 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B356" s="10" t="s">
         <v>40</v>
@@ -8999,7 +8999,7 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B357" s="10" t="s">
         <v>40</v>
@@ -9016,7 +9016,7 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B358" s="10" t="s">
         <v>0</v>
@@ -9033,7 +9033,7 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B359" s="10" t="s">
         <v>0</v>
@@ -9050,7 +9050,7 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B360" s="10" t="s">
         <v>0</v>
@@ -9067,7 +9067,7 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B361" s="10" t="s">
         <v>0</v>
@@ -9084,13 +9084,13 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="10" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B362" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C362" s="10" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D362" s="13">
         <v>1</v>
@@ -9101,10 +9101,10 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B363" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C363" s="10" t="s">
         <v>214</v>
@@ -9118,10 +9118,10 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B364" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C364" s="10" t="s">
         <v>214</v>
@@ -9135,13 +9135,13 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="10" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B365" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C365" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D365" s="13">
         <v>12</v>
@@ -9152,7 +9152,7 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="10" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B366" s="10" t="s">
         <v>0</v>
@@ -9169,7 +9169,7 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B367" s="10" t="s">
         <v>0</v>
@@ -9186,13 +9186,13 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B368" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C368" s="10" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D368" s="13">
         <v>7</v>
@@ -9203,7 +9203,7 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B369" s="10" t="s">
         <v>0</v>
@@ -9220,13 +9220,13 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B370" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C370" s="10" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D370" s="13">
         <v>19</v>
@@ -9237,7 +9237,7 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B371" s="10" t="s">
         <v>0</v>
@@ -9254,7 +9254,7 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B372" s="10" t="s">
         <v>0</v>
@@ -9263,7 +9263,7 @@
         <v>218</v>
       </c>
       <c r="D372" s="13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E372" s="1">
         <v>0</v>
@@ -9271,7 +9271,7 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B373" s="10" t="s">
         <v>0</v>
@@ -9288,13 +9288,13 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B374" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C374" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D374" s="13">
         <v>41</v>
@@ -9305,7 +9305,7 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B375" s="10" t="s">
         <v>0</v>
@@ -9322,7 +9322,7 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B376" s="10" t="s">
         <v>0</v>
@@ -9339,7 +9339,7 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B377" s="10" t="s">
         <v>0</v>
@@ -9356,13 +9356,13 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B378" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C378" s="10" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D378" s="13">
         <v>1</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B379" s="10" t="s">
         <v>0</v>
@@ -9390,7 +9390,7 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B380" s="10" t="s">
         <v>0</v>
@@ -9407,7 +9407,7 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B381" s="10" t="s">
         <v>40</v>
@@ -9424,7 +9424,7 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B382" s="10" t="s">
         <v>40</v>
@@ -9441,7 +9441,7 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B383" s="10" t="s">
         <v>40</v>
@@ -9458,7 +9458,7 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B384" s="10" t="s">
         <v>40</v>
@@ -9475,7 +9475,7 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B385" s="10" t="s">
         <v>40</v>
@@ -9492,7 +9492,7 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B386" s="10" t="s">
         <v>0</v>
@@ -9509,7 +9509,7 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B387" s="10" t="s">
         <v>0</v>
@@ -9526,7 +9526,7 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B388" s="10" t="s">
         <v>0</v>
@@ -9543,7 +9543,7 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B389" s="10" t="s">
         <v>0</v>
@@ -9560,7 +9560,7 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B390" s="10" t="s">
         <v>40</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B391" s="10" t="s">
         <v>0</v>
@@ -9594,7 +9594,7 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="10" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B392" s="10" t="s">
         <v>0</v>
@@ -9611,16 +9611,16 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B393" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C393" s="10" t="s">
         <v>231</v>
       </c>
       <c r="D393" s="13">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="E393" s="1">
         <v>0</v>
@@ -9628,16 +9628,16 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B394" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C394" s="10" t="s">
         <v>231</v>
       </c>
       <c r="D394" s="13">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="E394" s="1">
         <v>0</v>
@@ -9645,16 +9645,16 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B395" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C395" s="10" t="s">
         <v>231</v>
       </c>
       <c r="D395" s="13">
-        <v>360</v>
+        <v>3000</v>
       </c>
       <c r="E395" s="1">
         <v>0</v>
@@ -9662,7 +9662,7 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B396" s="10" t="s">
         <v>40</v>
@@ -9679,7 +9679,7 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B397" s="10" t="s">
         <v>0</v>
@@ -9696,7 +9696,7 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B398" s="10" t="s">
         <v>40</v>
@@ -9713,7 +9713,7 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B399" s="10" t="s">
         <v>40</v>
@@ -9730,7 +9730,7 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="10" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B400" s="10" t="s">
         <v>0</v>
@@ -9747,7 +9747,7 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="10" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B401" s="10" t="s">
         <v>0</v>
@@ -9764,7 +9764,7 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="10" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B402" s="10" t="s">
         <v>0</v>
@@ -9781,7 +9781,7 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B403" s="10" t="s">
         <v>0</v>
@@ -9798,7 +9798,7 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B404" s="10" t="s">
         <v>0</v>
@@ -9815,7 +9815,7 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B405" s="10" t="s">
         <v>0</v>
@@ -9832,7 +9832,7 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B406" s="10" t="s">
         <v>0</v>
@@ -9849,7 +9849,7 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" s="10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B407" s="10" t="s">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" s="10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B408" s="10" t="s">
         <v>0</v>
@@ -9883,7 +9883,7 @@
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B409" s="10" t="s">
         <v>9</v>
@@ -9900,7 +9900,7 @@
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B410" s="10" t="s">
         <v>0</v>
@@ -9917,7 +9917,7 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B411" s="10" t="s">
         <v>9</v>
@@ -9934,7 +9934,7 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B412" s="10" t="s">
         <v>9</v>
@@ -9951,7 +9951,7 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B413" s="10" t="s">
         <v>9</v>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B414" s="10" t="s">
         <v>9</v>
@@ -9985,7 +9985,7 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B415" s="10" t="s">
         <v>0</v>
@@ -10002,7 +10002,7 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="10" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B416" s="10" t="s">
         <v>40</v>
@@ -10019,7 +10019,7 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" s="10" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B417" s="10" t="s">
         <v>0</v>
@@ -10036,7 +10036,7 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B418" s="10" t="s">
         <v>40</v>
@@ -10053,7 +10053,7 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="10" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B419" s="10" t="s">
         <v>40</v>
@@ -10070,13 +10070,13 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="10" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B420" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C420" s="10" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D420" s="13">
         <v>450</v>
@@ -10087,7 +10087,7 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B421" s="10" t="s">
         <v>40</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" s="10" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B422" s="10" t="s">
         <v>0</v>
@@ -10121,16 +10121,16 @@
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B423" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C423" s="10" t="s">
         <v>247</v>
       </c>
       <c r="D423" s="13">
-        <v>300</v>
+        <v>2025</v>
       </c>
       <c r="E423" s="1">
         <v>0</v>
@@ -10138,16 +10138,16 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B424" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C424" s="10" t="s">
         <v>247</v>
       </c>
       <c r="D424" s="13">
-        <v>2025</v>
+        <v>375</v>
       </c>
       <c r="E424" s="1">
         <v>0</v>
@@ -10155,16 +10155,16 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B425" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C425" s="10" t="s">
         <v>247</v>
       </c>
       <c r="D425" s="13">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="E425" s="1">
         <v>0</v>
@@ -10172,7 +10172,7 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="10" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B426" s="10" t="s">
         <v>0</v>
@@ -10189,7 +10189,7 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B427" s="10" t="s">
         <v>40</v>
@@ -10206,7 +10206,7 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B428" s="10" t="s">
         <v>0</v>
@@ -10223,7 +10223,7 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B429" s="10" t="s">
         <v>40</v>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B430" s="10" t="s">
         <v>40</v>
@@ -10257,7 +10257,7 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B431" s="10" t="s">
         <v>0</v>
@@ -10274,7 +10274,7 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" s="10" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B432" s="10" t="s">
         <v>0</v>
@@ -10291,7 +10291,7 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="10" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B433" s="10" t="s">
         <v>0</v>
@@ -10308,7 +10308,7 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="10" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B434" s="10" t="s">
         <v>0</v>
@@ -10325,13 +10325,13 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="10" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B435" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C435" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D435" s="13">
         <v>1</v>
@@ -10342,7 +10342,7 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="10" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B436" s="10" t="s">
         <v>0</v>
@@ -10359,7 +10359,7 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="10" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B437" s="10" t="s">
         <v>9</v>
@@ -10376,7 +10376,7 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="10" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B438" s="10" t="s">
         <v>9</v>
@@ -10393,7 +10393,7 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="10" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B439" s="10" t="s">
         <v>9</v>
@@ -10410,7 +10410,7 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B440" s="10" t="s">
         <v>0</v>
@@ -10427,7 +10427,7 @@
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" s="10" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B441" s="10" t="s">
         <v>0</v>
@@ -10444,7 +10444,7 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B442" s="10" t="s">
         <v>40</v>
@@ -10461,13 +10461,13 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="10" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B443" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C443" s="10" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D443" s="13">
         <v>150</v>
@@ -10478,7 +10478,7 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="10" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B444" s="10" t="s">
         <v>0</v>
@@ -10495,16 +10495,16 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B445" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C445" s="10" t="s">
         <v>257</v>
       </c>
       <c r="D445" s="13">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E445" s="1">
         <v>0</v>
@@ -10512,16 +10512,16 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B446" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C446" s="10" t="s">
         <v>257</v>
       </c>
       <c r="D446" s="13">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E446" s="1">
         <v>0</v>
@@ -10529,13 +10529,13 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" s="10" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B447" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C447" s="10" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D447" s="13">
         <v>60</v>
@@ -10546,7 +10546,7 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B448" s="10" t="s">
         <v>40</v>
@@ -10563,7 +10563,7 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B449" s="10" t="s">
         <v>40</v>
@@ -10580,7 +10580,7 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B450" s="10" t="s">
         <v>40</v>
@@ -10597,7 +10597,7 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B451" s="10" t="s">
         <v>9</v>
@@ -10614,7 +10614,7 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B452" s="10" t="s">
         <v>0</v>
@@ -10631,7 +10631,7 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B453" s="10" t="s">
         <v>0</v>
@@ -10648,7 +10648,7 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B454" s="10" t="s">
         <v>0</v>
@@ -10665,7 +10665,7 @@
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B455" s="10" t="s">
         <v>0</v>
@@ -10682,7 +10682,7 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B456" s="10" t="s">
         <v>0</v>
@@ -10699,7 +10699,7 @@
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B457" s="10" t="s">
         <v>0</v>
@@ -10716,7 +10716,7 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B458" s="10" t="s">
         <v>0</v>
@@ -10733,7 +10733,7 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B459" s="10" t="s">
         <v>0</v>
@@ -10750,7 +10750,7 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B460" s="10" t="s">
         <v>0</v>
@@ -10767,7 +10767,7 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B461" s="10" t="s">
         <v>0</v>
@@ -10784,13 +10784,13 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B462" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C462" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D462" s="13">
         <v>4</v>
@@ -10801,13 +10801,13 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B463" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C463" s="10" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D463" s="13">
         <v>10</v>
@@ -10818,7 +10818,7 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="10" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B464" s="10" t="s">
         <v>0</v>
@@ -10835,7 +10835,7 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B465" s="10" t="s">
         <v>0</v>
@@ -10852,7 +10852,7 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B466" s="10" t="s">
         <v>40</v>
@@ -10869,7 +10869,7 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B467" s="10" t="s">
         <v>40</v>
@@ -10886,7 +10886,7 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B468" s="10" t="s">
         <v>40</v>
@@ -10903,7 +10903,7 @@
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B469" s="10" t="s">
         <v>40</v>
@@ -10920,7 +10920,7 @@
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="10" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B470" s="10" t="s">
         <v>40</v>
@@ -10937,7 +10937,7 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="10" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B471" s="10" t="s">
         <v>0</v>
@@ -10954,7 +10954,7 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B472" s="10" t="s">
         <v>0</v>
@@ -10971,7 +10971,7 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B473" s="10" t="s">
         <v>0</v>
@@ -10988,13 +10988,13 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B474" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C474" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D474" s="13">
         <v>40</v>
@@ -11005,7 +11005,7 @@
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B475" s="10" t="s">
         <v>0</v>
@@ -11022,7 +11022,7 @@
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B476" s="10" t="s">
         <v>0</v>
@@ -11039,7 +11039,7 @@
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B477" s="10" t="s">
         <v>0</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B478" s="10" t="s">
         <v>0</v>
@@ -11073,7 +11073,7 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B479" s="10" t="s">
         <v>0</v>
@@ -11090,7 +11090,7 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B480" s="10" t="s">
         <v>40</v>
@@ -11107,7 +11107,7 @@
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B481" s="10" t="s">
         <v>40</v>
@@ -11124,7 +11124,7 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B482" s="10" t="s">
         <v>40</v>
@@ -11141,7 +11141,7 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B483" s="10" t="s">
         <v>40</v>
@@ -11158,7 +11158,7 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B484" s="10" t="s">
         <v>40</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B485" s="10" t="s">
         <v>40</v>
@@ -11192,7 +11192,7 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B486" s="10" t="s">
         <v>40</v>
@@ -11209,7 +11209,7 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B487" s="10" t="s">
         <v>40</v>
@@ -11226,7 +11226,7 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B488" s="10" t="s">
         <v>0</v>
@@ -11243,7 +11243,7 @@
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B489" s="10" t="s">
         <v>0</v>
@@ -11260,7 +11260,7 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B490" s="10" t="s">
         <v>40</v>
@@ -11277,10 +11277,10 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B491" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C491" s="10" t="s">
         <v>292</v>
@@ -11294,10 +11294,10 @@
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B492" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C492" s="10" t="s">
         <v>292</v>
@@ -11311,13 +11311,13 @@
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B493" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C493" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D493" s="13">
         <v>17</v>
@@ -11328,7 +11328,7 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B494" s="10" t="s">
         <v>0</v>
@@ -11345,7 +11345,7 @@
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B495" s="10" t="s">
         <v>0</v>
@@ -11362,7 +11362,7 @@
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B496" s="10" t="s">
         <v>0</v>
@@ -11379,7 +11379,7 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B497" s="10" t="s">
         <v>0</v>
@@ -11396,16 +11396,16 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B498" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C498" s="10" t="s">
-        <v>514</v>
+        <v>297</v>
       </c>
       <c r="D498" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E498" s="1">
         <v>0</v>
@@ -11413,13 +11413,13 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B499" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C499" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D499" s="13">
         <v>1</v>
@@ -11430,13 +11430,13 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B500" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C500" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D500" s="13">
         <v>1</v>
@@ -11447,13 +11447,13 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B501" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C501" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D501" s="13">
         <v>1</v>
@@ -11464,16 +11464,16 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B502" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C502" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D502" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E502" s="1">
         <v>0</v>
@@ -11481,16 +11481,16 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B503" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C503" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D503" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E503" s="1">
         <v>0</v>
@@ -11498,16 +11498,16 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B504" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C504" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D504" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E504" s="1">
         <v>0</v>
@@ -11521,10 +11521,10 @@
         <v>0</v>
       </c>
       <c r="C505" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D505" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E505" s="1">
         <v>0</v>
@@ -11532,16 +11532,16 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B506" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C506" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D506" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E506" s="1">
         <v>0</v>
@@ -11549,16 +11549,16 @@
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B507" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C507" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D507" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E507" s="1">
         <v>0</v>
@@ -11572,7 +11572,7 @@
         <v>0</v>
       </c>
       <c r="C508" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D508" s="13">
         <v>1</v>
@@ -11583,13 +11583,13 @@
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B509" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C509" s="10" t="s">
-        <v>307</v>
+        <v>466</v>
       </c>
       <c r="D509" s="13">
         <v>1</v>
@@ -11600,13 +11600,13 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="B510" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C510" s="10" t="s">
-        <v>466</v>
+        <v>308</v>
       </c>
       <c r="D510" s="13">
         <v>1</v>
@@ -11617,13 +11617,13 @@
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" s="10" t="s">
-        <v>609</v>
+        <v>670</v>
       </c>
       <c r="B511" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C511" s="10" t="s">
-        <v>308</v>
+        <v>522</v>
       </c>
       <c r="D511" s="13">
         <v>1</v>
@@ -11634,13 +11634,13 @@
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B512" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C512" s="10" t="s">
-        <v>523</v>
+        <v>309</v>
       </c>
       <c r="D512" s="13">
         <v>1</v>
@@ -11651,16 +11651,16 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>671</v>
+        <v>608</v>
       </c>
       <c r="B513" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C513" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D513" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E513" s="1">
         <v>0</v>
@@ -11668,16 +11668,16 @@
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="B514" s="10" t="s">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="C514" s="10" t="s">
-        <v>310</v>
+        <v>771</v>
       </c>
       <c r="D514" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E514" s="1">
         <v>0</v>
@@ -11685,16 +11685,16 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B515" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C515" s="10" t="s">
         <v>772</v>
       </c>
       <c r="D515" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E515" s="1">
         <v>0</v>
@@ -11702,16 +11702,16 @@
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B516" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C516" s="10" t="s">
-        <v>773</v>
+        <v>737</v>
       </c>
       <c r="D516" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E516" s="1">
         <v>0</v>
@@ -11719,16 +11719,16 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B517" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="C517" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="C517" s="10" t="s">
-        <v>738</v>
-      </c>
       <c r="D517" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E517" s="1">
         <v>0</v>
@@ -11736,16 +11736,16 @@
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B518" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C518" s="10" t="s">
         <v>571</v>
       </c>
       <c r="D518" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E518" s="1">
         <v>0</v>
@@ -11753,16 +11753,16 @@
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519" s="10" t="s">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="B519" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C519" s="10" t="s">
-        <v>572</v>
+        <v>758</v>
       </c>
       <c r="D519" s="13">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E519" s="1">
         <v>0</v>
@@ -11770,16 +11770,16 @@
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
-        <v>717</v>
+        <v>614</v>
       </c>
       <c r="B520" s="10" t="s">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="C520" s="10" t="s">
-        <v>759</v>
+        <v>572</v>
       </c>
       <c r="D520" s="13">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E520" s="1">
         <v>0</v>
@@ -11787,16 +11787,16 @@
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B521" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C521" s="10" t="s">
         <v>573</v>
       </c>
       <c r="D521" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E521" s="1">
         <v>0</v>
@@ -11804,16 +11804,16 @@
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B522" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C522" s="10" t="s">
-        <v>574</v>
+        <v>741</v>
       </c>
       <c r="D522" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E522" s="1">
         <v>0</v>
@@ -11821,16 +11821,16 @@
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B523" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C523" s="10" t="s">
-        <v>742</v>
+        <v>760</v>
       </c>
       <c r="D523" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E523" s="1">
         <v>0</v>
@@ -11838,16 +11838,16 @@
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524" s="10" t="s">
-        <v>615</v>
+        <v>714</v>
       </c>
       <c r="B524" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C524" s="10" t="s">
-        <v>761</v>
+        <v>574</v>
       </c>
       <c r="D524" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E524" s="1">
         <v>0</v>
@@ -11855,16 +11855,16 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" s="10" t="s">
-        <v>715</v>
+        <v>614</v>
       </c>
       <c r="B525" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C525" s="10" t="s">
-        <v>575</v>
+        <v>773</v>
       </c>
       <c r="D525" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E525" s="1">
         <v>0</v>
@@ -11872,13 +11872,13 @@
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B526" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C526" s="10" t="s">
-        <v>774</v>
+        <v>575</v>
       </c>
       <c r="D526" s="13">
         <v>2</v>
@@ -11889,16 +11889,16 @@
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B527" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C527" s="10" t="s">
-        <v>576</v>
+        <v>531</v>
       </c>
       <c r="D527" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E527" s="1">
         <v>0</v>
@@ -11906,13 +11906,13 @@
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B528" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C528" s="10" t="s">
-        <v>532</v>
+        <v>311</v>
       </c>
       <c r="D528" s="13">
         <v>1</v>
@@ -11923,16 +11923,16 @@
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" s="10" t="s">
-        <v>615</v>
+        <v>715</v>
       </c>
       <c r="B529" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C529" s="10" t="s">
-        <v>311</v>
+        <v>532</v>
       </c>
       <c r="D529" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E529" s="1">
         <v>0</v>
@@ -11940,7 +11940,7 @@
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" s="10" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B530" s="10" t="s">
         <v>0</v>
@@ -11949,7 +11949,7 @@
         <v>533</v>
       </c>
       <c r="D530" s="13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E530" s="1">
         <v>0</v>
@@ -11963,10 +11963,10 @@
         <v>0</v>
       </c>
       <c r="C531" s="10" t="s">
-        <v>534</v>
+        <v>312</v>
       </c>
       <c r="D531" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E531" s="1">
         <v>0</v>
@@ -11974,16 +11974,16 @@
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B532" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C532" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D532" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E532" s="1">
         <v>0</v>
@@ -11991,16 +11991,16 @@
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" s="10" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B533" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C533" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D533" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E533" s="1">
         <v>0</v>
@@ -12008,13 +12008,13 @@
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" s="10" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B534" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C534" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D534" s="13">
         <v>1</v>
@@ -12025,13 +12025,13 @@
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" s="10" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B535" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C535" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D535" s="13">
         <v>1</v>
@@ -12042,13 +12042,13 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="10" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B536" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C536" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D536" s="13">
         <v>1</v>
@@ -12059,16 +12059,16 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" s="10" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B537" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C537" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D537" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E537" s="1">
         <v>0</v>
@@ -12076,13 +12076,13 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="10" t="s">
-        <v>717</v>
+        <v>614</v>
       </c>
       <c r="B538" s="10" t="s">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="C538" s="10" t="s">
-        <v>318</v>
+        <v>576</v>
       </c>
       <c r="D538" s="13">
         <v>2</v>
@@ -12093,16 +12093,16 @@
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B539" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C539" s="10" t="s">
-        <v>577</v>
+        <v>763</v>
       </c>
       <c r="D539" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E539" s="1">
         <v>0</v>
@@ -12110,16 +12110,16 @@
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B540" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C540" s="10" t="s">
-        <v>764</v>
+        <v>577</v>
       </c>
       <c r="D540" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E540" s="1">
         <v>0</v>
@@ -12127,16 +12127,16 @@
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B541" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C541" s="10" t="s">
-        <v>578</v>
+        <v>757</v>
       </c>
       <c r="D541" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E541" s="1">
         <v>0</v>
@@ -12144,16 +12144,16 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B542" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C542" s="10" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="D542" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E542" s="1">
         <v>0</v>
@@ -12161,16 +12161,16 @@
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" s="10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B543" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C543" s="10" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="D543" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E543" s="1">
         <v>0</v>
@@ -12178,13 +12178,13 @@
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B544" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C544" s="10" t="s">
-        <v>762</v>
+        <v>578</v>
       </c>
       <c r="D544" s="13">
         <v>1</v>
@@ -12195,10 +12195,10 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="10" t="s">
-        <v>617</v>
+        <v>714</v>
       </c>
       <c r="B545" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C545" s="10" t="s">
         <v>579</v>
@@ -12212,10 +12212,10 @@
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" s="10" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B546" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C546" s="10" t="s">
         <v>580</v>
@@ -12229,10 +12229,10 @@
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" s="10" t="s">
-        <v>715</v>
+        <v>616</v>
       </c>
       <c r="B547" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C547" s="10" t="s">
         <v>581</v>
@@ -12246,10 +12246,10 @@
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B548" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C548" s="10" t="s">
         <v>582</v>
@@ -12263,10 +12263,10 @@
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B549" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C549" s="10" t="s">
         <v>583</v>
@@ -12280,16 +12280,16 @@
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B550" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C550" s="10" t="s">
         <v>584</v>
       </c>
       <c r="D550" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E550" s="1">
         <v>0</v>
@@ -12297,16 +12297,16 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B551" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C551" s="10" t="s">
         <v>585</v>
       </c>
       <c r="D551" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E551" s="1">
         <v>0</v>
@@ -12314,16 +12314,16 @@
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552" s="10" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B552" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C552" s="10" t="s">
         <v>586</v>
       </c>
       <c r="D552" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E552" s="1">
         <v>0</v>
@@ -12331,13 +12331,13 @@
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B553" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C553" s="10" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="D553" s="13">
         <v>3</v>
@@ -12348,13 +12348,13 @@
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B554" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C554" s="10" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="D554" s="13">
         <v>3</v>
@@ -12365,16 +12365,16 @@
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B555" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C555" s="10" t="s">
-        <v>588</v>
+        <v>604</v>
       </c>
       <c r="D555" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E555" s="1">
         <v>0</v>
@@ -12382,16 +12382,16 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B556" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C556" s="10" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="D556" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E556" s="1">
         <v>0</v>
@@ -12399,16 +12399,16 @@
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" s="10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B557" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C557" s="10" t="s">
         <v>589</v>
       </c>
       <c r="D557" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E557" s="1">
         <v>0</v>
@@ -12416,10 +12416,10 @@
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B558" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C558" s="10" t="s">
         <v>590</v>
@@ -12433,16 +12433,16 @@
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" s="10" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B559" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C559" s="10" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="D559" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E559" s="1">
         <v>0</v>
@@ -12450,16 +12450,16 @@
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B560" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C560" s="10" t="s">
         <v>606</v>
       </c>
       <c r="D560" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E560" s="1">
         <v>0</v>
@@ -12467,13 +12467,13 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B561" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C561" s="10" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="D561" s="13">
         <v>1</v>
@@ -12484,16 +12484,16 @@
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B562" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C562" s="10" t="s">
         <v>592</v>
       </c>
       <c r="D562" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E562" s="1">
         <v>0</v>
@@ -12501,16 +12501,16 @@
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B563" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C563" s="10" t="s">
         <v>593</v>
       </c>
       <c r="D563" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E563" s="1">
         <v>0</v>
@@ -12518,16 +12518,16 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B564" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C564" s="10" t="s">
         <v>594</v>
       </c>
       <c r="D564" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E564" s="1">
         <v>0</v>
@@ -12535,16 +12535,16 @@
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B565" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C565" s="10" t="s">
         <v>595</v>
       </c>
       <c r="D565" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E565" s="1">
         <v>0</v>
@@ -12552,16 +12552,16 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B566" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C566" s="10" t="s">
         <v>596</v>
       </c>
       <c r="D566" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E566" s="1">
         <v>0</v>
@@ -12569,16 +12569,16 @@
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B567" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C567" s="10" t="s">
         <v>597</v>
       </c>
       <c r="D567" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E567" s="1">
         <v>0</v>
@@ -12586,16 +12586,16 @@
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B568" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C568" s="10" t="s">
         <v>598</v>
       </c>
       <c r="D568" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E568" s="1">
         <v>0</v>
@@ -12603,16 +12603,16 @@
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" s="10" t="s">
-        <v>615</v>
+        <v>670</v>
       </c>
       <c r="B569" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C569" s="10" t="s">
         <v>599</v>
       </c>
       <c r="D569" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E569" s="1">
         <v>0</v>
@@ -12620,16 +12620,16 @@
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" s="10" t="s">
-        <v>671</v>
+        <v>716</v>
       </c>
       <c r="B570" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C570" s="10" t="s">
-        <v>600</v>
+        <v>319</v>
       </c>
       <c r="D570" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E570" s="1">
         <v>0</v>
@@ -12637,13 +12637,13 @@
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" s="10" t="s">
-        <v>717</v>
+        <v>614</v>
       </c>
       <c r="B571" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C571" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D571" s="13">
         <v>1</v>
@@ -12654,13 +12654,13 @@
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B572" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C572" s="10" t="s">
-        <v>320</v>
+        <v>534</v>
       </c>
       <c r="D572" s="13">
         <v>1</v>
@@ -12671,16 +12671,16 @@
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B573" s="10" t="s">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="C573" s="10" t="s">
-        <v>535</v>
+        <v>321</v>
       </c>
       <c r="D573" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E573" s="1">
         <v>0</v>
@@ -12688,7 +12688,7 @@
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B574" s="10" t="s">
         <v>0</v>
@@ -12705,13 +12705,13 @@
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" s="10" t="s">
-        <v>615</v>
+        <v>670</v>
       </c>
       <c r="B575" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C575" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D575" s="13">
         <v>2</v>
@@ -12722,16 +12722,16 @@
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B576" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C576" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D576" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E576" s="1">
         <v>0</v>
@@ -12739,13 +12739,13 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B577" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C577" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D577" s="13">
         <v>1</v>
@@ -12756,13 +12756,13 @@
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578" s="10" t="s">
-        <v>671</v>
+        <v>616</v>
       </c>
       <c r="B578" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C578" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D578" s="13">
         <v>1</v>
@@ -12773,13 +12773,13 @@
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B579" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C579" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D579" s="13">
         <v>1</v>
@@ -12790,16 +12790,16 @@
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" s="10" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B580" s="10" t="s">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="C580" s="10" t="s">
-        <v>326</v>
+        <v>742</v>
       </c>
       <c r="D580" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E580" s="1">
         <v>0</v>
@@ -12807,16 +12807,16 @@
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B581" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C581" s="10" t="s">
         <v>743</v>
       </c>
       <c r="D581" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E581" s="1">
         <v>0</v>
@@ -12824,16 +12824,16 @@
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B582" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C582" s="10" t="s">
         <v>744</v>
       </c>
       <c r="D582" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E582" s="1">
         <v>0</v>
@@ -12841,16 +12841,16 @@
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A583" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B583" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C583" s="10" t="s">
-        <v>745</v>
+        <v>600</v>
       </c>
       <c r="D583" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E583" s="1">
         <v>0</v>
@@ -12858,13 +12858,13 @@
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B584" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C584" s="10" t="s">
-        <v>601</v>
+        <v>745</v>
       </c>
       <c r="D584" s="13">
         <v>1</v>
@@ -12875,10 +12875,10 @@
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B585" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C585" s="10" t="s">
         <v>746</v>
@@ -12892,16 +12892,16 @@
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A586" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B586" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C586" s="10" t="s">
         <v>747</v>
       </c>
       <c r="D586" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E586" s="1">
         <v>0</v>
@@ -12909,16 +12909,16 @@
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B587" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C587" s="10" t="s">
         <v>748</v>
       </c>
       <c r="D587" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E587" s="1">
         <v>0</v>
@@ -12926,16 +12926,16 @@
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B588" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C588" s="10" t="s">
         <v>749</v>
       </c>
       <c r="D588" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E588" s="1">
         <v>0</v>
@@ -12943,10 +12943,10 @@
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B589" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C589" s="10" t="s">
         <v>750</v>
@@ -12960,16 +12960,16 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B590" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C590" s="10" t="s">
         <v>751</v>
       </c>
       <c r="D590" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E590" s="1">
         <v>0</v>
@@ -12977,13 +12977,13 @@
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B591" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C591" s="10" t="s">
-        <v>752</v>
+        <v>601</v>
       </c>
       <c r="D591" s="13">
         <v>2</v>
@@ -12994,16 +12994,16 @@
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A592" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B592" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C592" s="10" t="s">
-        <v>602</v>
+        <v>738</v>
       </c>
       <c r="D592" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E592" s="1">
         <v>0</v>
@@ -13011,13 +13011,13 @@
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A593" s="10" t="s">
-        <v>615</v>
+        <v>670</v>
       </c>
       <c r="B593" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C593" s="10" t="s">
-        <v>739</v>
+        <v>602</v>
       </c>
       <c r="D593" s="13">
         <v>1</v>
@@ -13028,16 +13028,16 @@
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A594" s="10" t="s">
-        <v>671</v>
+        <v>616</v>
       </c>
       <c r="B594" s="10" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="C594" s="10" t="s">
-        <v>603</v>
+        <v>327</v>
       </c>
       <c r="D594" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E594" s="1">
         <v>0</v>
@@ -13045,16 +13045,16 @@
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A595" s="10" t="s">
-        <v>617</v>
+        <v>670</v>
       </c>
       <c r="B595" s="10" t="s">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="C595" s="10" t="s">
-        <v>327</v>
+        <v>607</v>
       </c>
       <c r="D595" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E595" s="1">
         <v>0</v>
@@ -13062,16 +13062,16 @@
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A596" s="10" t="s">
-        <v>671</v>
+        <v>693</v>
       </c>
       <c r="B596" s="10" t="s">
-        <v>570</v>
+        <v>40</v>
       </c>
       <c r="C596" s="10" t="s">
-        <v>608</v>
+        <v>429</v>
       </c>
       <c r="D596" s="13">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E596" s="1">
         <v>0</v>
@@ -13079,13 +13079,13 @@
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A597" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B597" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C597" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D597" s="13">
         <v>50</v>
@@ -13096,16 +13096,16 @@
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A598" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B598" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C598" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D598" s="13">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E598" s="1">
         <v>0</v>
@@ -13113,16 +13113,16 @@
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A599" s="10" t="s">
-        <v>694</v>
+        <v>608</v>
       </c>
       <c r="B599" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C599" s="10" t="s">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="D599" s="13">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E599" s="1">
         <v>0</v>
@@ -13130,13 +13130,13 @@
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A600" s="10" t="s">
-        <v>609</v>
+        <v>717</v>
       </c>
       <c r="B600" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C600" s="10" t="s">
-        <v>328</v>
+        <v>457</v>
       </c>
       <c r="D600" s="13">
         <v>1</v>
@@ -13147,16 +13147,16 @@
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A601" s="10" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B601" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C601" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D601" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E601" s="1">
         <v>0</v>
@@ -13164,16 +13164,16 @@
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A602" s="10" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B602" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C602" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D602" s="13">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E602" s="1">
         <v>0</v>
@@ -13181,16 +13181,16 @@
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A603" s="10" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B603" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C603" s="10" t="s">
-        <v>459</v>
+        <v>565</v>
       </c>
       <c r="D603" s="13">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E603" s="1">
         <v>0</v>
@@ -13198,16 +13198,16 @@
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A604" s="10" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B604" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C604" s="10" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D604" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E604" s="1">
         <v>0</v>
@@ -13215,16 +13215,16 @@
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A605" s="10" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B605" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C605" s="10" t="s">
-        <v>565</v>
+        <v>460</v>
       </c>
       <c r="D605" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E605" s="1">
         <v>0</v>
@@ -13232,16 +13232,16 @@
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A606" s="10" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B606" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C606" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D606" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E606" s="1">
         <v>0</v>
@@ -13252,13 +13252,13 @@
         <v>718</v>
       </c>
       <c r="B607" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C607" s="10" t="s">
-        <v>461</v>
+        <v>329</v>
       </c>
       <c r="D607" s="13">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="E607" s="1">
         <v>0</v>
@@ -13266,16 +13266,16 @@
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A608" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B608" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C608" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D608" s="13">
-        <v>37</v>
+        <v>800</v>
       </c>
       <c r="E608" s="1">
         <v>0</v>
@@ -13283,16 +13283,16 @@
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A609" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B609" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C609" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D609" s="13">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="E609" s="1">
         <v>0</v>
@@ -13300,16 +13300,16 @@
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A610" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B610" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C610" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D610" s="13">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="E610" s="1">
         <v>0</v>
@@ -13317,16 +13317,16 @@
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A611" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B611" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C611" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D611" s="13">
-        <v>1000</v>
+        <v>1070</v>
       </c>
       <c r="E611" s="1">
         <v>0</v>
@@ -13334,16 +13334,16 @@
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A612" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B612" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C612" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D612" s="13">
-        <v>1070</v>
+        <v>1600</v>
       </c>
       <c r="E612" s="1">
         <v>0</v>
@@ -13351,16 +13351,16 @@
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A613" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B613" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C613" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D613" s="13">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="E613" s="1">
         <v>0</v>
@@ -13368,16 +13368,16 @@
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A614" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B614" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C614" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D614" s="13">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="E614" s="1">
         <v>0</v>
@@ -13385,16 +13385,16 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B615" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C615" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D615" s="13">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="E615" s="1">
         <v>0</v>
@@ -13402,16 +13402,16 @@
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A616" s="10" t="s">
-        <v>719</v>
+        <v>624</v>
       </c>
       <c r="B616" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C616" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D616" s="13">
-        <v>1800</v>
+        <v>1</v>
       </c>
       <c r="E616" s="1">
         <v>0</v>
@@ -13419,16 +13419,16 @@
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B617" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C617" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D617" s="13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E617" s="1">
         <v>0</v>
@@ -13442,10 +13442,10 @@
         <v>0</v>
       </c>
       <c r="C618" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D618" s="13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E618" s="1">
         <v>0</v>
@@ -13453,13 +13453,13 @@
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A619" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B619" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C619" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D619" s="13">
         <v>1</v>
@@ -13470,16 +13470,16 @@
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A620" s="10" t="s">
-        <v>626</v>
+        <v>719</v>
       </c>
       <c r="B620" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C620" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D620" s="13">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E620" s="1">
         <v>0</v>
@@ -13493,10 +13493,10 @@
         <v>0</v>
       </c>
       <c r="C621" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D621" s="13">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E621" s="1">
         <v>0</v>
@@ -13504,16 +13504,16 @@
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A622" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B622" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C622" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D622" s="13">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="E622" s="1">
         <v>0</v>
@@ -13527,10 +13527,10 @@
         <v>0</v>
       </c>
       <c r="C623" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D623" s="13">
-        <v>121</v>
+        <v>300</v>
       </c>
       <c r="E623" s="1">
         <v>0</v>
@@ -13538,10 +13538,10 @@
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A624" s="10" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B624" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C624" s="10" t="s">
         <v>345</v>
@@ -13561,7 +13561,7 @@
         <v>40</v>
       </c>
       <c r="C625" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D625" s="13">
         <v>300</v>
@@ -13572,16 +13572,16 @@
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A626" s="10" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B626" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C626" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D626" s="13">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E626" s="1">
         <v>0</v>
@@ -13589,16 +13589,16 @@
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A627" s="10" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B627" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C627" s="10" t="s">
-        <v>347</v>
+        <v>489</v>
       </c>
       <c r="D627" s="13">
-        <v>310</v>
+        <v>73</v>
       </c>
       <c r="E627" s="1">
         <v>0</v>
@@ -13606,16 +13606,16 @@
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A628" s="10" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B628" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C628" s="10" t="s">
-        <v>489</v>
+        <v>348</v>
       </c>
       <c r="D628" s="13">
-        <v>73</v>
+        <v>250</v>
       </c>
       <c r="E628" s="1">
         <v>0</v>
@@ -13623,16 +13623,16 @@
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A629" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B629" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C629" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D629" s="13">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="E629" s="1">
         <v>0</v>
@@ -13640,16 +13640,16 @@
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A630" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B630" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C630" s="10" t="s">
         <v>349</v>
       </c>
       <c r="D630" s="13">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="E630" s="1">
         <v>0</v>
@@ -13657,16 +13657,16 @@
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A631" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B631" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C631" s="10" t="s">
-        <v>349</v>
+        <v>424</v>
       </c>
       <c r="D631" s="13">
-        <v>300</v>
+        <v>42</v>
       </c>
       <c r="E631" s="1">
         <v>0</v>
@@ -13674,16 +13674,16 @@
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B632" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C632" s="10" t="s">
-        <v>424</v>
+        <v>350</v>
       </c>
       <c r="D632" s="13">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E632" s="1">
         <v>0</v>
@@ -13691,16 +13691,16 @@
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A633" s="10" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B633" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C633" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D633" s="13">
-        <v>24</v>
+        <v>250</v>
       </c>
       <c r="E633" s="1">
         <v>0</v>
@@ -13711,13 +13711,13 @@
         <v>725</v>
       </c>
       <c r="B634" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C634" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D634" s="13">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="E634" s="1">
         <v>0</v>
@@ -13725,16 +13725,16 @@
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A635" s="10" t="s">
-        <v>726</v>
+        <v>785</v>
       </c>
       <c r="B635" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C635" s="10" t="s">
-        <v>352</v>
+        <v>786</v>
       </c>
       <c r="D635" s="13">
-        <v>1250</v>
+        <v>100</v>
       </c>
       <c r="E635" s="1">
         <v>0</v>
@@ -13742,16 +13742,16 @@
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636" s="10" t="s">
-        <v>786</v>
+        <v>725</v>
       </c>
       <c r="B636" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C636" s="10" t="s">
-        <v>787</v>
+        <v>353</v>
       </c>
       <c r="D636" s="13">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E636" s="1">
         <v>0</v>
@@ -13759,16 +13759,16 @@
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A637" s="10" t="s">
-        <v>726</v>
+        <v>785</v>
       </c>
       <c r="B637" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C637" s="10" t="s">
-        <v>353</v>
+        <v>787</v>
       </c>
       <c r="D637" s="13">
-        <v>160</v>
+        <v>35</v>
       </c>
       <c r="E637" s="1">
         <v>0</v>
@@ -13776,16 +13776,16 @@
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A638" s="10" t="s">
-        <v>786</v>
+        <v>725</v>
       </c>
       <c r="B638" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C638" s="10" t="s">
-        <v>788</v>
+        <v>354</v>
       </c>
       <c r="D638" s="13">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="E638" s="1">
         <v>0</v>
@@ -13793,16 +13793,16 @@
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B639" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C639" s="1" t="s">
         <v>354</v>
       </c>
       <c r="D639" s="14">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E639" s="1">
         <v>0</v>
@@ -13810,16 +13810,16 @@
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>726</v>
+        <v>785</v>
       </c>
       <c r="B640" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>354</v>
+        <v>788</v>
       </c>
       <c r="D640" s="14">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E640" s="1">
         <v>0</v>
@@ -13827,16 +13827,16 @@
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>786</v>
+        <v>725</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C641" s="1" t="s">
-        <v>789</v>
+        <v>422</v>
       </c>
       <c r="D641" s="14">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E641" s="1">
         <v>0</v>
@@ -13844,16 +13844,16 @@
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B642" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D642" s="14">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E642" s="1">
         <v>0</v>
@@ -13861,16 +13861,16 @@
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B643" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>423</v>
+        <v>355</v>
       </c>
       <c r="D643" s="14">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E643" s="1">
         <v>0</v>
@@ -13881,13 +13881,13 @@
         <v>726</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>40</v>
+        <v>439</v>
       </c>
       <c r="C644" s="1" t="s">
-        <v>355</v>
+        <v>450</v>
       </c>
       <c r="D644" s="14">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="E644" s="1">
         <v>0</v>
@@ -13895,16 +13895,16 @@
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="C645" s="1" t="s">
-        <v>450</v>
+        <v>356</v>
       </c>
       <c r="D645" s="14">
-        <v>2</v>
+        <v>1300</v>
       </c>
       <c r="E645" s="1">
         <v>0</v>
@@ -13912,16 +13912,16 @@
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B646" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C646" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D646" s="14">
-        <v>1300</v>
+        <v>29</v>
       </c>
       <c r="E646" s="1">
         <v>0</v>
@@ -13929,16 +13929,16 @@
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B647" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C647" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D647" s="14">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E647" s="1">
         <v>0</v>
@@ -13952,10 +13952,10 @@
         <v>0</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>358</v>
+        <v>507</v>
       </c>
       <c r="D648" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E648" s="1">
         <v>0</v>
@@ -13963,16 +13963,16 @@
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B649" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C649" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D649" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E649" s="1">
         <v>0</v>
@@ -13980,16 +13980,16 @@
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B650" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C650" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D650" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E650" s="1">
         <v>0</v>
@@ -14000,13 +14000,13 @@
         <v>728</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>509</v>
+        <v>359</v>
       </c>
       <c r="D651" s="14">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="E651" s="1">
         <v>0</v>
@@ -14014,16 +14014,16 @@
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B652" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D652" s="14">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="E652" s="1">
         <v>0</v>
@@ -14031,16 +14031,16 @@
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B653" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C653" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D653" s="14">
-        <v>123</v>
+        <v>8</v>
       </c>
       <c r="E653" s="1">
         <v>0</v>
@@ -14048,16 +14048,16 @@
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B654" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C654" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D654" s="14">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="E654" s="1">
         <v>0</v>
@@ -14068,13 +14068,13 @@
         <v>729</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C655" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D655" s="14">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E655" s="1">
         <v>0</v>
@@ -14082,16 +14082,16 @@
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B656" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C656" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D656" s="14">
-        <v>600</v>
+        <v>825</v>
       </c>
       <c r="E656" s="1">
         <v>0</v>
@@ -14099,16 +14099,16 @@
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C657" s="1" t="s">
-        <v>364</v>
+        <v>789</v>
       </c>
       <c r="D657" s="14">
-        <v>825</v>
+        <v>500</v>
       </c>
       <c r="E657" s="1">
         <v>0</v>
@@ -14116,16 +14116,16 @@
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B658" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C658" s="1" t="s">
-        <v>790</v>
+        <v>365</v>
       </c>
       <c r="D658" s="14">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E658" s="1">
         <v>0</v>
@@ -14133,16 +14133,16 @@
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C659" s="1" t="s">
         <v>365</v>
       </c>
       <c r="D659" s="14">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E659" s="1">
         <v>0</v>
@@ -14153,13 +14153,13 @@
         <v>731</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C660" s="1" t="s">
-        <v>365</v>
+        <v>490</v>
       </c>
       <c r="D660" s="14">
-        <v>600</v>
+        <v>7</v>
       </c>
       <c r="E660" s="1">
         <v>0</v>
@@ -14167,16 +14167,16 @@
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B661" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C661" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D661" s="14">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="E661" s="1">
         <v>0</v>
@@ -14184,16 +14184,16 @@
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>491</v>
+        <v>406</v>
       </c>
       <c r="D662" s="14">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E662" s="1">
         <v>0</v>
@@ -14201,16 +14201,16 @@
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B663" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C663" s="1" t="s">
-        <v>406</v>
+        <v>366</v>
       </c>
       <c r="D663" s="14">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E663" s="1">
         <v>0</v>
@@ -14218,16 +14218,16 @@
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D664" s="14">
-        <v>72</v>
+        <v>1501</v>
       </c>
       <c r="E664" s="1">
         <v>0</v>
@@ -14235,16 +14235,16 @@
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B665" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C665" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D665" s="14">
-        <v>1501</v>
+        <v>1508</v>
       </c>
       <c r="E665" s="1">
         <v>0</v>
@@ -14258,10 +14258,10 @@
         <v>0</v>
       </c>
       <c r="C666" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D666" s="14">
-        <v>1508</v>
+        <v>600</v>
       </c>
       <c r="E666" s="1">
         <v>0</v>
@@ -14269,16 +14269,16 @@
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B667" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C667" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D667" s="14">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E667" s="1">
         <v>0</v>
@@ -14286,16 +14286,16 @@
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B668" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C668" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D668" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E668" s="1">
         <v>0</v>
@@ -14303,16 +14303,16 @@
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B669" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C669" s="1" t="s">
-        <v>371</v>
+        <v>551</v>
       </c>
       <c r="D669" s="14">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="E669" s="1">
         <v>0</v>
@@ -14320,16 +14320,16 @@
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B670" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C670" s="1" t="s">
-        <v>552</v>
+        <v>372</v>
       </c>
       <c r="D670" s="14">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E670" s="1">
         <v>0</v>
@@ -14337,13 +14337,13 @@
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B671" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C671" s="1" t="s">
-        <v>372</v>
+        <v>438</v>
       </c>
       <c r="D671" s="14">
         <v>100</v>
@@ -14354,16 +14354,16 @@
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B672" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C672" s="1" t="s">
-        <v>438</v>
+        <v>373</v>
       </c>
       <c r="D672" s="14">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E672" s="1">
         <v>0</v>
@@ -14371,16 +14371,16 @@
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="B673" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C673" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D673" s="14">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="E673" s="1">
         <v>0</v>
@@ -14388,16 +14388,16 @@
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B674" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C674" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D674" s="14">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="E674" s="1">
         <v>0</v>
@@ -14405,16 +14405,16 @@
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>720</v>
+        <v>734</v>
       </c>
       <c r="B675" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C675" s="1" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="D675" s="14">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="E675" s="1">
         <v>0</v>
@@ -14422,16 +14422,16 @@
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B676" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C676" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D676" s="14">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E676" s="1">
         <v>0</v>
@@ -14439,16 +14439,16 @@
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B677" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C677" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D677" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E677" s="1">
         <v>0</v>
@@ -14456,16 +14456,16 @@
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C678" s="1" t="s">
-        <v>512</v>
+        <v>376</v>
       </c>
       <c r="D678" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E678" s="1">
         <v>0</v>
@@ -14473,16 +14473,16 @@
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B679" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C679" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D679" s="14">
-        <v>15</v>
+        <v>225</v>
       </c>
       <c r="E679" s="1">
         <v>0</v>
@@ -14490,16 +14490,16 @@
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B680" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C680" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D680" s="14">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="E680" s="1">
         <v>0</v>
@@ -14507,16 +14507,16 @@
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
-        <v>721</v>
+        <v>735</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C681" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D681" s="14">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="E681" s="1">
         <v>0</v>
@@ -14524,13 +14524,13 @@
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C682" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D682" s="14">
         <v>1200</v>
@@ -14541,16 +14541,16 @@
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D683" s="14">
-        <v>1200</v>
+        <v>225</v>
       </c>
       <c r="E683" s="1">
         <v>0</v>
@@ -14558,16 +14558,16 @@
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C684" s="1" t="s">
         <v>381</v>
       </c>
       <c r="D684" s="14">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="E684" s="1">
         <v>0</v>
@@ -14575,16 +14575,16 @@
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B685" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C685" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D685" s="14">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E685" s="1">
         <v>0</v>
@@ -14595,13 +14595,13 @@
         <v>736</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C686" s="1" t="s">
-        <v>382</v>
+        <v>790</v>
       </c>
       <c r="D686" s="14">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="E686" s="1">
         <v>0</v>
@@ -14609,16 +14609,16 @@
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C687" s="1" t="s">
-        <v>791</v>
+        <v>383</v>
       </c>
       <c r="D687" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E687" s="1">
         <v>0</v>
@@ -14626,7 +14626,7 @@
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B688" s="1" t="s">
         <v>0</v>
@@ -14643,16 +14643,16 @@
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C689" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D689" s="14">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E689" s="1">
         <v>0</v>
@@ -14660,16 +14660,16 @@
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B690" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C690" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D690" s="14">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="E690" s="1">
         <v>0</v>
@@ -14683,10 +14683,10 @@
         <v>0</v>
       </c>
       <c r="C691" s="1" t="s">
-        <v>385</v>
+        <v>492</v>
       </c>
       <c r="D691" s="14">
-        <v>225</v>
+        <v>10</v>
       </c>
       <c r="E691" s="1">
         <v>0</v>
@@ -14694,16 +14694,16 @@
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B692" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C692" s="1" t="s">
-        <v>492</v>
+        <v>386</v>
       </c>
       <c r="D692" s="14">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="E692" s="1">
         <v>0</v>
@@ -14711,7 +14711,7 @@
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B693" s="1" t="s">
         <v>40</v>
@@ -14728,16 +14728,16 @@
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B694" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C694" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D694" s="14">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E694" s="1">
         <v>0</v>
@@ -14745,16 +14745,16 @@
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C695" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D695" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E695" s="1">
         <v>0</v>
@@ -14762,16 +14762,16 @@
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C696" s="1" t="s">
         <v>388</v>
       </c>
       <c r="D696" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E696" s="1">
         <v>0</v>
@@ -14779,16 +14779,16 @@
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B697" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C697" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D697" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E697" s="1">
         <v>0</v>
@@ -14796,7 +14796,7 @@
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B698" s="1" t="s">
         <v>40</v>
@@ -14808,23 +14808,6 @@
         <v>64</v>
       </c>
       <c r="E698" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A699" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="B699" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C699" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="D699" s="14">
-        <v>30</v>
-      </c>
-      <c r="E699" s="1">
         <v>0</v>
       </c>
     </row>
@@ -14891,11 +14874,11 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str" cm="1">
-        <f t="array" ref="A6:C8">_xlfn._xlws.SORT(_xlfn._xlws.FILTER('جرد المواد'!B5:D9610,
-ISNUMBER(SEARCH(IF(B1="","*",B1),'جرد المواد'!C5:C9610))*
-ISNUMBER(SEARCH(IF(B2="","*",B2),'جرد المواد'!C5:C9610))*
-ISNUMBER(SEARCH(IF(B3="","*",B3),'جرد المواد'!C5:C9610))*
-ISNUMBER(SEARCH(IF(B4="","*",B4),'جرد المواد'!B5:B9610)),
+        <f t="array" ref="A6:C8">_xlfn._xlws.SORT(_xlfn._xlws.FILTER('جرد المواد'!B5:D9609,
+ISNUMBER(SEARCH(IF(B1="","*",B1),'جرد المواد'!C5:C9609))*
+ISNUMBER(SEARCH(IF(B2="","*",B2),'جرد المواد'!C5:C9609))*
+ISNUMBER(SEARCH(IF(B3="","*",B3),'جرد المواد'!C5:C9609))*
+ISNUMBER(SEARCH(IF(B4="","*",B4),'جرد المواد'!B5:B9609)),
 "لا توجد نتائج"),
 2,1)</f>
         <v>3-ديوان</v>
@@ -14928,7 +14911,7 @@
         <v>بار دوش شاور بانل دوبل كروم اسود تركي بريفا PRIVA</v>
       </c>
       <c r="C8" s="4">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D8" s="4"/>
     </row>

--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE3D8DA-92F9-4D7E-A8B8-79AD84A0AD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6918A1F9-5977-4EDF-A173-32BDE171432F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -3177,7 +3177,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="13">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -4044,7 +4044,7 @@
         <v>48</v>
       </c>
       <c r="D65" s="13">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
@@ -4174,13 +4174,13 @@
         <v>633</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D73" s="13">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
@@ -4191,13 +4191,13 @@
         <v>633</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D74" s="13">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
@@ -4310,13 +4310,13 @@
         <v>637</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D81" s="13">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="E81" s="1">
         <v>0</v>
@@ -4327,13 +4327,13 @@
         <v>637</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D82" s="13">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="E82" s="1">
         <v>0</v>
@@ -4395,13 +4395,13 @@
         <v>637</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C86" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D86" s="13">
-        <v>1350</v>
+        <v>2725</v>
       </c>
       <c r="E86" s="1">
         <v>0</v>
@@ -4412,13 +4412,13 @@
         <v>637</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C87" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D87" s="13">
-        <v>2725</v>
+        <v>1350</v>
       </c>
       <c r="E87" s="1">
         <v>0</v>
@@ -4446,13 +4446,13 @@
         <v>637</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>58</v>
       </c>
       <c r="D89" s="13">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="E89" s="1">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>637</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>58</v>
@@ -4480,13 +4480,13 @@
         <v>637</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>58</v>
       </c>
       <c r="D91" s="13">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
@@ -5177,13 +5177,13 @@
         <v>649</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D132" s="13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -5194,13 +5194,13 @@
         <v>649</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D133" s="13">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -5279,13 +5279,13 @@
         <v>649</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>86</v>
       </c>
       <c r="D138" s="13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
@@ -5296,13 +5296,13 @@
         <v>649</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>86</v>
       </c>
       <c r="D139" s="13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
@@ -5483,13 +5483,13 @@
         <v>649</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>96</v>
       </c>
       <c r="D150" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E150" s="1">
         <v>0</v>
@@ -5500,13 +5500,13 @@
         <v>649</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C151" s="10" t="s">
         <v>96</v>
       </c>
       <c r="D151" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E151" s="1">
         <v>0</v>
@@ -6061,13 +6061,13 @@
         <v>656</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C184" s="10" t="s">
         <v>119</v>
       </c>
       <c r="D184" s="13">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E184" s="1">
         <v>0</v>
@@ -6078,13 +6078,13 @@
         <v>656</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C185" s="10" t="s">
         <v>119</v>
       </c>
       <c r="D185" s="13">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E185" s="1">
         <v>0</v>
@@ -6129,13 +6129,13 @@
         <v>656</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C188" s="10" t="s">
         <v>122</v>
       </c>
       <c r="D188" s="13">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
@@ -6146,13 +6146,13 @@
         <v>656</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C189" s="10" t="s">
         <v>122</v>
       </c>
       <c r="D189" s="13">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
@@ -6781,7 +6781,7 @@
         <v>755</v>
       </c>
       <c r="D226" s="13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E226" s="1">
         <v>0</v>
@@ -6798,7 +6798,7 @@
         <v>778</v>
       </c>
       <c r="D227" s="13">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E227" s="1">
         <v>0</v>
@@ -7081,13 +7081,13 @@
         <v>672</v>
       </c>
       <c r="B244" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C244" s="10" t="s">
         <v>154</v>
       </c>
       <c r="D244" s="13">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="E244" s="1">
         <v>0</v>
@@ -7098,13 +7098,13 @@
         <v>672</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C245" s="10" t="s">
         <v>154</v>
       </c>
       <c r="D245" s="13">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="E245" s="1">
         <v>0</v>
@@ -7308,7 +7308,7 @@
         <v>161</v>
       </c>
       <c r="D257" s="13">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E257" s="1">
         <v>0</v>
@@ -7835,7 +7835,7 @@
         <v>568</v>
       </c>
       <c r="D288" s="13">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E288" s="1">
         <v>0</v>
@@ -7852,7 +7852,7 @@
         <v>562</v>
       </c>
       <c r="D289" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E289" s="1">
         <v>0</v>
@@ -8271,13 +8271,13 @@
         <v>679</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C314" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D314" s="13">
-        <v>125</v>
+        <v>880</v>
       </c>
       <c r="E314" s="1">
         <v>0</v>
@@ -8288,13 +8288,13 @@
         <v>679</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C315" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D315" s="13">
-        <v>880</v>
+        <v>125</v>
       </c>
       <c r="E315" s="1">
         <v>0</v>
@@ -8764,13 +8764,13 @@
         <v>688</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C343" s="10" t="s">
         <v>204</v>
       </c>
       <c r="D343" s="13">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="E343" s="1">
         <v>0</v>
@@ -8781,13 +8781,13 @@
         <v>688</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C344" s="10" t="s">
         <v>204</v>
       </c>
       <c r="D344" s="13">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E344" s="1">
         <v>0</v>
@@ -8798,7 +8798,7 @@
         <v>688</v>
       </c>
       <c r="B345" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C345" s="10" t="s">
         <v>205</v>
@@ -8815,7 +8815,7 @@
         <v>688</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C346" s="10" t="s">
         <v>205</v>
@@ -9104,7 +9104,7 @@
         <v>652</v>
       </c>
       <c r="B363" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C363" s="10" t="s">
         <v>214</v>
@@ -9121,7 +9121,7 @@
         <v>652</v>
       </c>
       <c r="B364" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C364" s="10" t="s">
         <v>214</v>
@@ -9195,7 +9195,7 @@
         <v>756</v>
       </c>
       <c r="D368" s="13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E368" s="1">
         <v>0</v>
@@ -9229,7 +9229,7 @@
         <v>781</v>
       </c>
       <c r="D370" s="13">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E370" s="1">
         <v>0</v>
@@ -10124,13 +10124,13 @@
         <v>704</v>
       </c>
       <c r="B423" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C423" s="10" t="s">
         <v>247</v>
       </c>
       <c r="D423" s="13">
-        <v>2025</v>
+        <v>300</v>
       </c>
       <c r="E423" s="1">
         <v>0</v>
@@ -10141,13 +10141,13 @@
         <v>704</v>
       </c>
       <c r="B424" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C424" s="10" t="s">
         <v>247</v>
       </c>
       <c r="D424" s="13">
-        <v>375</v>
+        <v>2025</v>
       </c>
       <c r="E424" s="1">
         <v>0</v>
@@ -10158,13 +10158,13 @@
         <v>704</v>
       </c>
       <c r="B425" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C425" s="10" t="s">
         <v>247</v>
       </c>
       <c r="D425" s="13">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="E425" s="1">
         <v>0</v>
@@ -10923,13 +10923,13 @@
         <v>712</v>
       </c>
       <c r="B470" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C470" s="10" t="s">
         <v>275</v>
       </c>
       <c r="D470" s="13">
-        <v>570</v>
+        <v>779</v>
       </c>
       <c r="E470" s="1">
         <v>0</v>
@@ -10940,13 +10940,13 @@
         <v>712</v>
       </c>
       <c r="B471" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C471" s="10" t="s">
         <v>275</v>
       </c>
       <c r="D471" s="13">
-        <v>779</v>
+        <v>570</v>
       </c>
       <c r="E471" s="1">
         <v>0</v>
@@ -11280,7 +11280,7 @@
         <v>624</v>
       </c>
       <c r="B491" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C491" s="10" t="s">
         <v>292</v>
@@ -11297,7 +11297,7 @@
         <v>624</v>
       </c>
       <c r="B492" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C492" s="10" t="s">
         <v>292</v>
@@ -11320,7 +11320,7 @@
         <v>563</v>
       </c>
       <c r="D493" s="13">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E493" s="1">
         <v>0</v>
@@ -11813,7 +11813,7 @@
         <v>741</v>
       </c>
       <c r="D522" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E522" s="1">
         <v>0</v>
@@ -13524,7 +13524,7 @@
         <v>721</v>
       </c>
       <c r="B623" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C623" s="10" t="s">
         <v>345</v>
@@ -13541,7 +13541,7 @@
         <v>721</v>
       </c>
       <c r="B624" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C624" s="10" t="s">
         <v>345</v>
@@ -13779,13 +13779,13 @@
         <v>725</v>
       </c>
       <c r="B638" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C638" s="10" t="s">
         <v>354</v>
       </c>
       <c r="D638" s="13">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E638" s="1">
         <v>0</v>
@@ -13796,13 +13796,13 @@
         <v>725</v>
       </c>
       <c r="B639" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C639" s="1" t="s">
         <v>354</v>
       </c>
       <c r="D639" s="14">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="E639" s="1">
         <v>0</v>
@@ -14119,13 +14119,13 @@
         <v>730</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C658" s="1" t="s">
         <v>365</v>
       </c>
       <c r="D658" s="14">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E658" s="1">
         <v>0</v>
@@ -14136,13 +14136,13 @@
         <v>730</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C659" s="1" t="s">
         <v>365</v>
       </c>
       <c r="D659" s="14">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E659" s="1">
         <v>0</v>
@@ -14612,13 +14612,13 @@
         <v>735</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C687" s="1" t="s">
         <v>383</v>
       </c>
       <c r="D687" s="14">
-        <v>200</v>
+        <v>950</v>
       </c>
       <c r="E687" s="1">
         <v>0</v>
@@ -14629,13 +14629,13 @@
         <v>735</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C688" s="1" t="s">
         <v>383</v>
       </c>
       <c r="D688" s="14">
-        <v>950</v>
+        <v>200</v>
       </c>
       <c r="E688" s="1">
         <v>0</v>
@@ -14748,13 +14748,13 @@
         <v>735</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C695" s="1" t="s">
         <v>388</v>
       </c>
       <c r="D695" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E695" s="1">
         <v>0</v>
@@ -14765,13 +14765,13 @@
         <v>735</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C696" s="1" t="s">
         <v>388</v>
       </c>
       <c r="D696" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E696" s="1">
         <v>0</v>

--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D7B35E-A5C5-4348-AE62-15C436F9B646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24DDAEAC-DA4F-49EF-80D6-25272EB4062D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -3145,7 +3145,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="13">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -3955,13 +3955,13 @@
         <v>611</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>45</v>
       </c>
       <c r="D61" s="13">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3972,13 +3972,13 @@
         <v>611</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>45</v>
       </c>
       <c r="D62" s="13">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -4108,13 +4108,13 @@
         <v>613</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D70" s="13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
@@ -4125,13 +4125,13 @@
         <v>613</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D71" s="13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
@@ -4176,13 +4176,13 @@
         <v>613</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D74" s="13">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
@@ -4193,13 +4193,13 @@
         <v>613</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D75" s="13">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
@@ -4312,13 +4312,13 @@
         <v>617</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D82" s="13">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="E82" s="1">
         <v>0</v>
@@ -4329,13 +4329,13 @@
         <v>617</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D83" s="13">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="E83" s="1">
         <v>0</v>
@@ -4380,13 +4380,13 @@
         <v>617</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C86" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D86" s="13">
-        <v>2725</v>
+        <v>1350</v>
       </c>
       <c r="E86" s="1">
         <v>0</v>
@@ -4397,13 +4397,13 @@
         <v>617</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C87" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D87" s="13">
-        <v>1350</v>
+        <v>150</v>
       </c>
       <c r="E87" s="1">
         <v>0</v>
@@ -4414,13 +4414,13 @@
         <v>617</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D88" s="13">
-        <v>150</v>
+        <v>2725</v>
       </c>
       <c r="E88" s="1">
         <v>0</v>
@@ -4641,7 +4641,7 @@
         <v>64</v>
       </c>
       <c r="D101" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="1">
         <v>0</v>
@@ -5128,13 +5128,13 @@
         <v>629</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D130" s="13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
@@ -5145,13 +5145,13 @@
         <v>629</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D131" s="13">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -5162,13 +5162,13 @@
         <v>629</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D132" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -5179,13 +5179,13 @@
         <v>629</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D133" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -5230,13 +5230,13 @@
         <v>629</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>85</v>
       </c>
       <c r="D136" s="13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
@@ -5247,13 +5247,13 @@
         <v>629</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>85</v>
       </c>
       <c r="D137" s="13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
@@ -5434,13 +5434,13 @@
         <v>629</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C148" s="10" t="s">
         <v>95</v>
       </c>
       <c r="D148" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E148" s="1">
         <v>0</v>
@@ -5451,13 +5451,13 @@
         <v>629</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>95</v>
       </c>
       <c r="D149" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E149" s="1">
         <v>0</v>
@@ -5944,13 +5944,13 @@
         <v>636</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>116</v>
       </c>
       <c r="D178" s="13">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E178" s="1">
         <v>0</v>
@@ -5961,13 +5961,13 @@
         <v>636</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C179" s="10" t="s">
         <v>116</v>
       </c>
       <c r="D179" s="13">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E179" s="1">
         <v>0</v>
@@ -6046,13 +6046,13 @@
         <v>636</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C184" s="10" t="s">
         <v>120</v>
       </c>
       <c r="D184" s="13">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="E184" s="1">
         <v>0</v>
@@ -6063,13 +6063,13 @@
         <v>636</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C185" s="10" t="s">
         <v>120</v>
       </c>
       <c r="D185" s="13">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="E185" s="1">
         <v>0</v>
@@ -8120,13 +8120,13 @@
         <v>662</v>
       </c>
       <c r="B306" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C306" s="10" t="s">
         <v>190</v>
       </c>
       <c r="D306" s="13">
-        <v>650</v>
+        <v>475</v>
       </c>
       <c r="E306" s="1">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>662</v>
       </c>
       <c r="B307" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C307" s="10" t="s">
         <v>190</v>
       </c>
       <c r="D307" s="13">
-        <v>475</v>
+        <v>650</v>
       </c>
       <c r="E307" s="1">
         <v>0</v>
@@ -8188,13 +8188,13 @@
         <v>659</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C310" s="10" t="s">
         <v>191</v>
       </c>
       <c r="D310" s="13">
-        <v>175</v>
+        <v>880</v>
       </c>
       <c r="E310" s="1">
         <v>0</v>
@@ -8205,13 +8205,13 @@
         <v>659</v>
       </c>
       <c r="B311" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C311" s="10" t="s">
         <v>191</v>
       </c>
       <c r="D311" s="13">
-        <v>880</v>
+        <v>175</v>
       </c>
       <c r="E311" s="1">
         <v>0</v>
@@ -8596,13 +8596,13 @@
         <v>667</v>
       </c>
       <c r="B334" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C334" s="10" t="s">
         <v>199</v>
       </c>
       <c r="D334" s="13">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="E334" s="1">
         <v>0</v>
@@ -8613,13 +8613,13 @@
         <v>667</v>
       </c>
       <c r="B335" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C335" s="10" t="s">
         <v>199</v>
       </c>
       <c r="D335" s="13">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="E335" s="1">
         <v>0</v>
@@ -8715,7 +8715,7 @@
         <v>668</v>
       </c>
       <c r="B341" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C341" s="10" t="s">
         <v>202</v>
@@ -8732,7 +8732,7 @@
         <v>668</v>
       </c>
       <c r="B342" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C342" s="10" t="s">
         <v>202</v>
@@ -8749,13 +8749,13 @@
         <v>668</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C343" s="10" t="s">
         <v>203</v>
       </c>
       <c r="D343" s="13">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E343" s="1">
         <v>0</v>
@@ -8766,13 +8766,13 @@
         <v>668</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C344" s="10" t="s">
         <v>203</v>
       </c>
       <c r="D344" s="13">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E344" s="1">
         <v>0</v>
@@ -9021,7 +9021,7 @@
         <v>632</v>
       </c>
       <c r="B359" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C359" s="10" t="s">
         <v>211</v>
@@ -9038,7 +9038,7 @@
         <v>632</v>
       </c>
       <c r="B360" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C360" s="10" t="s">
         <v>211</v>
@@ -9820,13 +9820,13 @@
         <v>681</v>
       </c>
       <c r="B406" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C406" s="10" t="s">
         <v>240</v>
       </c>
       <c r="D406" s="13">
-        <v>14</v>
+        <v>316</v>
       </c>
       <c r="E406" s="1">
         <v>0</v>
@@ -9837,13 +9837,13 @@
         <v>681</v>
       </c>
       <c r="B407" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C407" s="10" t="s">
         <v>240</v>
       </c>
       <c r="D407" s="13">
-        <v>316</v>
+        <v>14</v>
       </c>
       <c r="E407" s="1">
         <v>0</v>
@@ -9888,13 +9888,13 @@
         <v>681</v>
       </c>
       <c r="B410" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C410" s="10" t="s">
         <v>243</v>
       </c>
       <c r="D410" s="13">
-        <v>129</v>
+        <v>1200</v>
       </c>
       <c r="E410" s="1">
         <v>0</v>
@@ -9905,13 +9905,13 @@
         <v>681</v>
       </c>
       <c r="B411" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C411" s="10" t="s">
         <v>243</v>
       </c>
       <c r="D411" s="13">
-        <v>1200</v>
+        <v>129</v>
       </c>
       <c r="E411" s="1">
         <v>0</v>
@@ -10041,13 +10041,13 @@
         <v>684</v>
       </c>
       <c r="B419" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C419" s="10" t="s">
         <v>244</v>
       </c>
       <c r="D419" s="13">
-        <v>125</v>
+        <v>2025</v>
       </c>
       <c r="E419" s="1">
         <v>0</v>
@@ -10058,13 +10058,13 @@
         <v>684</v>
       </c>
       <c r="B420" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C420" s="10" t="s">
         <v>244</v>
       </c>
       <c r="D420" s="13">
-        <v>2025</v>
+        <v>125</v>
       </c>
       <c r="E420" s="1">
         <v>0</v>
@@ -10109,13 +10109,13 @@
         <v>684</v>
       </c>
       <c r="B423" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C423" s="10" t="s">
         <v>245</v>
       </c>
       <c r="D423" s="13">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="E423" s="1">
         <v>0</v>
@@ -10126,13 +10126,13 @@
         <v>684</v>
       </c>
       <c r="B424" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C424" s="10" t="s">
         <v>245</v>
       </c>
       <c r="D424" s="13">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E424" s="1">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         <v>690</v>
       </c>
       <c r="B441" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C441" s="10" t="s">
         <v>254</v>
       </c>
       <c r="D441" s="13">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E441" s="1">
         <v>0</v>
@@ -10432,13 +10432,13 @@
         <v>690</v>
       </c>
       <c r="B442" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C442" s="10" t="s">
         <v>254</v>
       </c>
       <c r="D442" s="13">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E442" s="1">
         <v>0</v>
@@ -10840,13 +10840,13 @@
         <v>692</v>
       </c>
       <c r="B466" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C466" s="10" t="s">
         <v>272</v>
       </c>
       <c r="D466" s="13">
-        <v>779</v>
+        <v>330</v>
       </c>
       <c r="E466" s="1">
         <v>0</v>
@@ -10857,13 +10857,13 @@
         <v>692</v>
       </c>
       <c r="B467" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C467" s="10" t="s">
         <v>272</v>
       </c>
       <c r="D467" s="13">
-        <v>330</v>
+        <v>779</v>
       </c>
       <c r="E467" s="1">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>604</v>
       </c>
       <c r="B486" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C486" s="10" t="s">
         <v>288</v>
@@ -11197,7 +11197,7 @@
         <v>604</v>
       </c>
       <c r="B487" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C487" s="10" t="s">
         <v>288</v>
@@ -11968,7 +11968,7 @@
         <v>743</v>
       </c>
       <c r="D532" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E532" s="1">
         <v>0</v>
@@ -12002,7 +12002,7 @@
         <v>737</v>
       </c>
       <c r="D534" s="13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E534" s="1">
         <v>0</v>
@@ -13611,13 +13611,13 @@
         <v>705</v>
       </c>
       <c r="B629" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C629" s="10" t="s">
         <v>343</v>
       </c>
       <c r="D629" s="13">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E629" s="1">
         <v>0</v>
@@ -13628,13 +13628,13 @@
         <v>705</v>
       </c>
       <c r="B630" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C630" s="10" t="s">
         <v>343</v>
       </c>
       <c r="D630" s="13">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="E630" s="1">
         <v>0</v>
@@ -14376,13 +14376,13 @@
         <v>715</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C674" s="1" t="s">
         <v>370</v>
       </c>
       <c r="D674" s="14">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="E674" s="1">
         <v>0</v>
@@ -14393,13 +14393,13 @@
         <v>715</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C675" s="1" t="s">
         <v>370</v>
       </c>
       <c r="D675" s="14">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="E675" s="1">
         <v>0</v>
@@ -14444,13 +14444,13 @@
         <v>715</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C678" s="1" t="s">
         <v>372</v>
       </c>
       <c r="D678" s="14">
-        <v>200</v>
+        <v>950</v>
       </c>
       <c r="E678" s="1">
         <v>0</v>
@@ -14461,13 +14461,13 @@
         <v>715</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C679" s="1" t="s">
         <v>372</v>
       </c>
       <c r="D679" s="14">
-        <v>950</v>
+        <v>200</v>
       </c>
       <c r="E679" s="1">
         <v>0</v>
@@ -14529,13 +14529,13 @@
         <v>715</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C683" s="1" t="s">
         <v>375</v>
       </c>
       <c r="D683" s="14">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="E683" s="1">
         <v>0</v>
@@ -14546,13 +14546,13 @@
         <v>715</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C684" s="1" t="s">
         <v>375</v>
       </c>
       <c r="D684" s="14">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="E684" s="1">
         <v>0</v>
@@ -14614,13 +14614,13 @@
         <v>715</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C688" s="1" t="s">
         <v>378</v>
       </c>
       <c r="D688" s="14">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E688" s="1">
         <v>0</v>
@@ -14631,13 +14631,13 @@
         <v>715</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C689" s="1" t="s">
         <v>378</v>
       </c>
       <c r="D689" s="14">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="E689" s="1">
         <v>0</v>

--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21922522-BB43-4684-8A6F-1BFEA917DA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D104174-F173-4D84-BD92-224CCBEBE668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="789">
   <si>
     <t>3-ديوان</t>
   </si>
@@ -2423,6 +2423,9 @@
   </si>
   <si>
     <t>وصل مخالف تلحيم 25*32 ملم اخضر ايطالي ITALY RIETTI</t>
+  </si>
+  <si>
+    <t>قسطل تلحيم 32 ملم اخضر لبناني</t>
   </si>
 </sst>
 </file>
@@ -2949,7 +2952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E5C9A6-5EC3-4592-9122-0E1001CE6231}">
-  <dimension ref="A1:E686"/>
+  <dimension ref="A1:E687"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.8984375" style="2" bestFit="1" customWidth="1"/>
@@ -3992,13 +3995,13 @@
         <v>605</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D63" s="13">
-        <v>31</v>
+        <v>200</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -4009,13 +4012,13 @@
         <v>605</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D64" s="13">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
@@ -4094,13 +4097,13 @@
         <v>607</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D69" s="13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E69" s="1">
         <v>0</v>
@@ -4111,13 +4114,13 @@
         <v>607</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D70" s="13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
@@ -4298,13 +4301,13 @@
         <v>611</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D81" s="13">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="E81" s="1">
         <v>0</v>
@@ -4315,13 +4318,13 @@
         <v>611</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D82" s="13">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="E82" s="1">
         <v>0</v>
@@ -4417,13 +4420,13 @@
         <v>611</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>58</v>
       </c>
       <c r="D88" s="13">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="E88" s="1">
         <v>0</v>
@@ -4434,13 +4437,13 @@
         <v>611</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>58</v>
       </c>
       <c r="D89" s="13">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="E89" s="1">
         <v>0</v>
@@ -5097,13 +5100,13 @@
         <v>623</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>81</v>
       </c>
       <c r="D128" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E128" s="1">
         <v>0</v>
@@ -5114,13 +5117,13 @@
         <v>623</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>81</v>
       </c>
       <c r="D129" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E129" s="1">
         <v>0</v>
@@ -5131,13 +5134,13 @@
         <v>623</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D130" s="13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
@@ -5148,13 +5151,13 @@
         <v>623</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D131" s="13">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -5199,13 +5202,13 @@
         <v>623</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>84</v>
       </c>
       <c r="D134" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -5216,13 +5219,13 @@
         <v>623</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>84</v>
       </c>
       <c r="D135" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
@@ -5233,13 +5236,13 @@
         <v>623</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>85</v>
       </c>
       <c r="D136" s="13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
@@ -5250,13 +5253,13 @@
         <v>623</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>85</v>
       </c>
       <c r="D137" s="13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
@@ -5284,13 +5287,13 @@
         <v>623</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>87</v>
       </c>
       <c r="D139" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
@@ -5301,13 +5304,13 @@
         <v>623</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C140" s="10" t="s">
         <v>87</v>
       </c>
       <c r="D140" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
@@ -5437,13 +5440,13 @@
         <v>623</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C148" s="10" t="s">
         <v>95</v>
       </c>
       <c r="D148" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E148" s="1">
         <v>0</v>
@@ -5454,13 +5457,13 @@
         <v>623</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>95</v>
       </c>
       <c r="D149" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E149" s="1">
         <v>0</v>
@@ -5930,13 +5933,13 @@
         <v>630</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>116</v>
       </c>
       <c r="D177" s="13">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E177" s="1">
         <v>0</v>
@@ -5947,13 +5950,13 @@
         <v>630</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>116</v>
       </c>
       <c r="D178" s="13">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E178" s="1">
         <v>0</v>
@@ -6032,13 +6035,13 @@
         <v>630</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C183" s="10" t="s">
         <v>120</v>
       </c>
       <c r="D183" s="13">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="E183" s="1">
         <v>0</v>
@@ -6049,13 +6052,13 @@
         <v>630</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C184" s="10" t="s">
         <v>120</v>
       </c>
       <c r="D184" s="13">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="E184" s="1">
         <v>0</v>
@@ -7018,13 +7021,13 @@
         <v>646</v>
       </c>
       <c r="B241" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C241" s="10" t="s">
         <v>152</v>
       </c>
       <c r="D241" s="13">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="E241" s="1">
         <v>0</v>
@@ -7035,13 +7038,13 @@
         <v>646</v>
       </c>
       <c r="B242" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C242" s="10" t="s">
         <v>152</v>
       </c>
       <c r="D242" s="13">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="E242" s="1">
         <v>0</v>
@@ -8106,13 +8109,13 @@
         <v>656</v>
       </c>
       <c r="B305" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C305" s="10" t="s">
         <v>189</v>
       </c>
       <c r="D305" s="13">
-        <v>650</v>
+        <v>400</v>
       </c>
       <c r="E305" s="1">
         <v>0</v>
@@ -8123,13 +8126,13 @@
         <v>656</v>
       </c>
       <c r="B306" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C306" s="10" t="s">
         <v>189</v>
       </c>
       <c r="D306" s="13">
-        <v>400</v>
+        <v>650</v>
       </c>
       <c r="E306" s="1">
         <v>0</v>
@@ -8191,13 +8194,13 @@
         <v>653</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C310" s="10" t="s">
         <v>190</v>
       </c>
       <c r="D310" s="13">
-        <v>880</v>
+        <v>175</v>
       </c>
       <c r="E310" s="1">
         <v>0</v>
@@ -8208,13 +8211,13 @@
         <v>653</v>
       </c>
       <c r="B311" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C311" s="10" t="s">
         <v>190</v>
       </c>
       <c r="D311" s="13">
-        <v>175</v>
+        <v>880</v>
       </c>
       <c r="E311" s="1">
         <v>0</v>
@@ -8265,7 +8268,7 @@
         <v>497</v>
       </c>
       <c r="D314" s="13">
-        <v>1440</v>
+        <v>990</v>
       </c>
       <c r="E314" s="1">
         <v>0</v>
@@ -8273,13 +8276,13 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="10" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C315" s="10" t="s">
-        <v>404</v>
+        <v>788</v>
       </c>
       <c r="D315" s="13">
         <v>450</v>
@@ -8290,16 +8293,16 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C316" s="10" t="s">
-        <v>462</v>
+        <v>404</v>
       </c>
       <c r="D316" s="13">
-        <v>98</v>
+        <v>450</v>
       </c>
       <c r="E316" s="1">
         <v>0</v>
@@ -8307,16 +8310,16 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B317" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C317" s="10" t="s">
-        <v>191</v>
+        <v>462</v>
       </c>
       <c r="D317" s="13">
-        <v>310</v>
+        <v>98</v>
       </c>
       <c r="E317" s="1">
         <v>0</v>
@@ -8324,16 +8327,16 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="10" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B318" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C318" s="10" t="s">
-        <v>405</v>
+        <v>191</v>
       </c>
       <c r="D318" s="13">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="E318" s="1">
         <v>0</v>
@@ -8341,16 +8344,16 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B319" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C319" s="10" t="s">
-        <v>463</v>
+        <v>405</v>
       </c>
       <c r="D319" s="13">
-        <v>9</v>
+        <v>350</v>
       </c>
       <c r="E319" s="1">
         <v>0</v>
@@ -8358,16 +8361,16 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B320" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C320" s="10" t="s">
-        <v>192</v>
+        <v>463</v>
       </c>
       <c r="D320" s="13">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="E320" s="1">
         <v>0</v>
@@ -8378,13 +8381,13 @@
         <v>656</v>
       </c>
       <c r="B321" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C321" s="10" t="s">
         <v>192</v>
       </c>
       <c r="D321" s="13">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="E321" s="1">
         <v>0</v>
@@ -8392,16 +8395,16 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="10" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B322" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C322" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D322" s="13">
-        <v>1150</v>
+        <v>4</v>
       </c>
       <c r="E322" s="1">
         <v>0</v>
@@ -8415,10 +8418,10 @@
         <v>40</v>
       </c>
       <c r="C323" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D323" s="13">
-        <v>260</v>
+        <v>1150</v>
       </c>
       <c r="E323" s="1">
         <v>0</v>
@@ -8426,16 +8429,16 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B324" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C324" s="10" t="s">
-        <v>494</v>
+        <v>194</v>
       </c>
       <c r="D324" s="13">
-        <v>17</v>
+        <v>260</v>
       </c>
       <c r="E324" s="1">
         <v>0</v>
@@ -8449,10 +8452,10 @@
         <v>9</v>
       </c>
       <c r="C325" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D325" s="13">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E325" s="1">
         <v>0</v>
@@ -8466,10 +8469,10 @@
         <v>9</v>
       </c>
       <c r="C326" s="10" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D326" s="13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E326" s="1">
         <v>0</v>
@@ -8477,16 +8480,16 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="10" t="s">
-        <v>741</v>
+        <v>659</v>
       </c>
       <c r="B327" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C327" s="10" t="s">
-        <v>742</v>
+        <v>496</v>
       </c>
       <c r="D327" s="13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E327" s="1">
         <v>0</v>
@@ -8494,16 +8497,16 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="10" t="s">
-        <v>660</v>
+        <v>741</v>
       </c>
       <c r="B328" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C328" s="10" t="s">
-        <v>537</v>
+        <v>742</v>
       </c>
       <c r="D328" s="13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E328" s="1">
         <v>0</v>
@@ -8517,10 +8520,10 @@
         <v>9</v>
       </c>
       <c r="C329" s="10" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D329" s="13">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E329" s="1">
         <v>0</v>
@@ -8534,10 +8537,10 @@
         <v>9</v>
       </c>
       <c r="C330" s="10" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D330" s="13">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E330" s="1">
         <v>0</v>
@@ -8545,16 +8548,16 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="10" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B331" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C331" s="10" t="s">
-        <v>195</v>
+        <v>538</v>
       </c>
       <c r="D331" s="13">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="E331" s="1">
         <v>0</v>
@@ -8568,10 +8571,10 @@
         <v>40</v>
       </c>
       <c r="C332" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D332" s="13">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E332" s="1">
         <v>0</v>
@@ -8585,10 +8588,10 @@
         <v>40</v>
       </c>
       <c r="C333" s="10" t="s">
-        <v>397</v>
+        <v>196</v>
       </c>
       <c r="D333" s="13">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="E333" s="1">
         <v>0</v>
@@ -8599,13 +8602,13 @@
         <v>661</v>
       </c>
       <c r="B334" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C334" s="10" t="s">
-        <v>197</v>
+        <v>397</v>
       </c>
       <c r="D334" s="13">
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="E334" s="1">
         <v>0</v>
@@ -8616,13 +8619,13 @@
         <v>661</v>
       </c>
       <c r="B335" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C335" s="10" t="s">
         <v>197</v>
       </c>
       <c r="D335" s="13">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="E335" s="1">
         <v>0</v>
@@ -8636,10 +8639,10 @@
         <v>40</v>
       </c>
       <c r="C336" s="10" t="s">
-        <v>398</v>
+        <v>197</v>
       </c>
       <c r="D336" s="13">
-        <v>168</v>
+        <v>300</v>
       </c>
       <c r="E336" s="1">
         <v>0</v>
@@ -8653,10 +8656,10 @@
         <v>40</v>
       </c>
       <c r="C337" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D337" s="13">
-        <v>33</v>
+        <v>168</v>
       </c>
       <c r="E337" s="1">
         <v>0</v>
@@ -8670,10 +8673,10 @@
         <v>40</v>
       </c>
       <c r="C338" s="10" t="s">
-        <v>198</v>
+        <v>399</v>
       </c>
       <c r="D338" s="13">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E338" s="1">
         <v>0</v>
@@ -8681,16 +8684,16 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="10" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B339" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C339" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D339" s="13">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="E339" s="1">
         <v>0</v>
@@ -8701,13 +8704,13 @@
         <v>662</v>
       </c>
       <c r="B340" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C340" s="10" t="s">
         <v>199</v>
       </c>
       <c r="D340" s="13">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E340" s="1">
         <v>0</v>
@@ -8718,13 +8721,13 @@
         <v>662</v>
       </c>
       <c r="B341" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C341" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D341" s="13">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E341" s="1">
         <v>0</v>
@@ -8752,13 +8755,13 @@
         <v>662</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C343" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D343" s="13">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E343" s="1">
         <v>0</v>
@@ -8783,16 +8786,16 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="10" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B345" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C345" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D345" s="13">
-        <v>196</v>
+        <v>40</v>
       </c>
       <c r="E345" s="1">
         <v>0</v>
@@ -8800,16 +8803,16 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="10" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C346" s="10" t="s">
-        <v>393</v>
+        <v>202</v>
       </c>
       <c r="D346" s="13">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E346" s="1">
         <v>0</v>
@@ -8823,7 +8826,7 @@
         <v>40</v>
       </c>
       <c r="C347" s="10" t="s">
-        <v>203</v>
+        <v>393</v>
       </c>
       <c r="D347" s="13">
         <v>200</v>
@@ -8834,16 +8837,16 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="10" t="s">
-        <v>751</v>
+        <v>664</v>
       </c>
       <c r="B348" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C348" s="10" t="s">
-        <v>763</v>
+        <v>203</v>
       </c>
       <c r="D348" s="13">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="E348" s="1">
         <v>0</v>
@@ -8851,16 +8854,16 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="10" t="s">
-        <v>664</v>
+        <v>751</v>
       </c>
       <c r="B349" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C349" s="10" t="s">
-        <v>394</v>
+        <v>763</v>
       </c>
       <c r="D349" s="13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E349" s="1">
         <v>0</v>
@@ -8868,16 +8871,16 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="10" t="s">
-        <v>751</v>
+        <v>664</v>
       </c>
       <c r="B350" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C350" s="10" t="s">
-        <v>752</v>
+        <v>394</v>
       </c>
       <c r="D350" s="13">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E350" s="1">
         <v>0</v>
@@ -8885,16 +8888,16 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="10" t="s">
-        <v>664</v>
+        <v>751</v>
       </c>
       <c r="B351" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C351" s="10" t="s">
-        <v>395</v>
+        <v>752</v>
       </c>
       <c r="D351" s="13">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="E351" s="1">
         <v>0</v>
@@ -8908,10 +8911,10 @@
         <v>40</v>
       </c>
       <c r="C352" s="10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D352" s="13">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="E352" s="1">
         <v>0</v>
@@ -8925,10 +8928,10 @@
         <v>40</v>
       </c>
       <c r="C353" s="10" t="s">
-        <v>204</v>
+        <v>396</v>
       </c>
       <c r="D353" s="13">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E353" s="1">
         <v>0</v>
@@ -8936,16 +8939,16 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="10" t="s">
-        <v>582</v>
+        <v>664</v>
       </c>
       <c r="B354" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C354" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D354" s="13">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E354" s="1">
         <v>0</v>
@@ -8953,16 +8956,16 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="B355" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C355" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D355" s="13">
-        <v>188</v>
+        <v>4</v>
       </c>
       <c r="E355" s="1">
         <v>0</v>
@@ -8976,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="C356" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D356" s="13">
-        <v>400</v>
+        <v>188</v>
       </c>
       <c r="E356" s="1">
         <v>0</v>
@@ -8993,10 +8996,10 @@
         <v>0</v>
       </c>
       <c r="C357" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D357" s="13">
-        <v>288</v>
+        <v>400</v>
       </c>
       <c r="E357" s="1">
         <v>0</v>
@@ -9004,16 +9007,16 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="10" t="s">
-        <v>651</v>
+        <v>600</v>
       </c>
       <c r="B358" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C358" s="10" t="s">
-        <v>505</v>
+        <v>208</v>
       </c>
       <c r="D358" s="13">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="E358" s="1">
         <v>0</v>
@@ -9021,13 +9024,13 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="10" t="s">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="B359" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C359" s="10" t="s">
-        <v>209</v>
+        <v>505</v>
       </c>
       <c r="D359" s="13">
         <v>1</v>
@@ -9055,16 +9058,16 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="10" t="s">
-        <v>665</v>
+        <v>626</v>
       </c>
       <c r="B361" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C361" s="10" t="s">
-        <v>516</v>
+        <v>209</v>
       </c>
       <c r="D361" s="13">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E361" s="1">
         <v>0</v>
@@ -9072,13 +9075,13 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B362" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C362" s="10" t="s">
-        <v>210</v>
+        <v>516</v>
       </c>
       <c r="D362" s="13">
         <v>12</v>
@@ -9089,16 +9092,16 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="10" t="s">
-        <v>582</v>
+        <v>666</v>
       </c>
       <c r="B363" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C363" s="10" t="s">
-        <v>384</v>
+        <v>210</v>
       </c>
       <c r="D363" s="13">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E363" s="1">
         <v>0</v>
@@ -9106,16 +9109,16 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="10" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="B364" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C364" s="10" t="s">
-        <v>729</v>
+        <v>384</v>
       </c>
       <c r="D364" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E364" s="1">
         <v>0</v>
@@ -9126,13 +9129,13 @@
         <v>598</v>
       </c>
       <c r="B365" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C365" s="10" t="s">
-        <v>211</v>
+        <v>729</v>
       </c>
       <c r="D365" s="13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E365" s="1">
         <v>0</v>
@@ -9143,13 +9146,13 @@
         <v>598</v>
       </c>
       <c r="B366" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C366" s="10" t="s">
-        <v>753</v>
+        <v>211</v>
       </c>
       <c r="D366" s="13">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E366" s="1">
         <v>0</v>
@@ -9160,13 +9163,13 @@
         <v>598</v>
       </c>
       <c r="B367" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C367" s="10" t="s">
-        <v>212</v>
+        <v>753</v>
       </c>
       <c r="D367" s="13">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E367" s="1">
         <v>0</v>
@@ -9174,16 +9177,16 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B368" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C368" s="10" t="s">
-        <v>772</v>
+        <v>212</v>
       </c>
       <c r="D368" s="13">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E368" s="1">
         <v>0</v>
@@ -9191,16 +9194,16 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B369" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C369" s="10" t="s">
-        <v>213</v>
+        <v>772</v>
       </c>
       <c r="D369" s="13">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E369" s="1">
         <v>0</v>
@@ -9214,7 +9217,7 @@
         <v>0</v>
       </c>
       <c r="C370" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D370" s="13">
         <v>10</v>
@@ -9228,13 +9231,13 @@
         <v>598</v>
       </c>
       <c r="B371" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C371" s="10" t="s">
-        <v>527</v>
+        <v>214</v>
       </c>
       <c r="D371" s="13">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="E371" s="1">
         <v>0</v>
@@ -9245,13 +9248,13 @@
         <v>598</v>
       </c>
       <c r="B372" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C372" s="10" t="s">
-        <v>454</v>
+        <v>527</v>
       </c>
       <c r="D372" s="13">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E372" s="1">
         <v>0</v>
@@ -9265,7 +9268,7 @@
         <v>0</v>
       </c>
       <c r="C373" s="10" t="s">
-        <v>215</v>
+        <v>454</v>
       </c>
       <c r="D373" s="13">
         <v>1</v>
@@ -9282,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="C374" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D374" s="13">
         <v>1</v>
@@ -9293,13 +9296,13 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B375" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C375" s="10" t="s">
-        <v>508</v>
+        <v>216</v>
       </c>
       <c r="D375" s="13">
         <v>1</v>
@@ -9310,13 +9313,13 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B376" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C376" s="10" t="s">
-        <v>217</v>
+        <v>508</v>
       </c>
       <c r="D376" s="13">
         <v>1</v>
@@ -9333,7 +9336,7 @@
         <v>0</v>
       </c>
       <c r="C377" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D377" s="13">
         <v>1</v>
@@ -9344,16 +9347,16 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="10" t="s">
-        <v>667</v>
+        <v>598</v>
       </c>
       <c r="B378" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C378" s="10" t="s">
-        <v>409</v>
+        <v>218</v>
       </c>
       <c r="D378" s="13">
-        <v>1800</v>
+        <v>1</v>
       </c>
       <c r="E378" s="1">
         <v>0</v>
@@ -9367,10 +9370,10 @@
         <v>40</v>
       </c>
       <c r="C379" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D379" s="13">
-        <v>2700</v>
+        <v>1800</v>
       </c>
       <c r="E379" s="1">
         <v>0</v>
@@ -9384,10 +9387,10 @@
         <v>40</v>
       </c>
       <c r="C380" s="10" t="s">
-        <v>219</v>
+        <v>410</v>
       </c>
       <c r="D380" s="13">
-        <v>900</v>
+        <v>2700</v>
       </c>
       <c r="E380" s="1">
         <v>0</v>
@@ -9401,7 +9404,7 @@
         <v>40</v>
       </c>
       <c r="C381" s="10" t="s">
-        <v>411</v>
+        <v>219</v>
       </c>
       <c r="D381" s="13">
         <v>900</v>
@@ -9418,10 +9421,10 @@
         <v>40</v>
       </c>
       <c r="C382" s="10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D382" s="13">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="E382" s="1">
         <v>0</v>
@@ -9429,16 +9432,16 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B383" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C383" s="10" t="s">
-        <v>220</v>
+        <v>412</v>
       </c>
       <c r="D383" s="13">
-        <v>40</v>
+        <v>1200</v>
       </c>
       <c r="E383" s="1">
         <v>0</v>
@@ -9446,16 +9449,16 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="10" t="s">
-        <v>584</v>
+        <v>668</v>
       </c>
       <c r="B384" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C384" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D384" s="13">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E384" s="1">
         <v>0</v>
@@ -9463,16 +9466,16 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="10" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B385" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C385" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D385" s="13">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="E385" s="1">
         <v>0</v>
@@ -9480,16 +9483,16 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="10" t="s">
-        <v>669</v>
+        <v>583</v>
       </c>
       <c r="B386" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C386" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D386" s="13">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="E386" s="1">
         <v>0</v>
@@ -9497,16 +9500,16 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="10" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B387" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C387" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D387" s="13">
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="E387" s="1">
         <v>0</v>
@@ -9514,16 +9517,16 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="10" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B388" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C388" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D388" s="13">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="E388" s="1">
         <v>0</v>
@@ -9531,16 +9534,16 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="10" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B389" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C389" s="10" t="s">
-        <v>464</v>
+        <v>225</v>
       </c>
       <c r="D389" s="13">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="E389" s="1">
         <v>0</v>
@@ -9548,16 +9551,16 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="10" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B390" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C390" s="10" t="s">
-        <v>226</v>
+        <v>464</v>
       </c>
       <c r="D390" s="13">
-        <v>2550</v>
+        <v>189</v>
       </c>
       <c r="E390" s="1">
         <v>0</v>
@@ -9568,13 +9571,13 @@
         <v>670</v>
       </c>
       <c r="B391" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C391" s="10" t="s">
         <v>226</v>
       </c>
       <c r="D391" s="13">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="E391" s="1">
         <v>0</v>
@@ -9585,13 +9588,13 @@
         <v>670</v>
       </c>
       <c r="B392" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C392" s="10" t="s">
         <v>226</v>
       </c>
       <c r="D392" s="13">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="E392" s="1">
         <v>0</v>
@@ -9602,13 +9605,13 @@
         <v>670</v>
       </c>
       <c r="B393" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C393" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D393" s="13">
-        <v>120</v>
+        <v>2550</v>
       </c>
       <c r="E393" s="1">
         <v>0</v>
@@ -9619,13 +9622,13 @@
         <v>670</v>
       </c>
       <c r="B394" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C394" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D394" s="13">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E394" s="1">
         <v>0</v>
@@ -9636,13 +9639,13 @@
         <v>670</v>
       </c>
       <c r="B395" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C395" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D395" s="13">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E395" s="1">
         <v>0</v>
@@ -9650,16 +9653,16 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="10" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B396" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C396" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D396" s="13">
-        <v>56</v>
+        <v>300</v>
       </c>
       <c r="E396" s="1">
         <v>0</v>
@@ -9673,10 +9676,10 @@
         <v>0</v>
       </c>
       <c r="C397" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D397" s="13">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="E397" s="1">
         <v>0</v>
@@ -9690,10 +9693,10 @@
         <v>0</v>
       </c>
       <c r="C398" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D398" s="13">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E398" s="1">
         <v>0</v>
@@ -9701,16 +9704,16 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B399" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C399" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D399" s="13">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="E399" s="1">
         <v>0</v>
@@ -9724,10 +9727,10 @@
         <v>0</v>
       </c>
       <c r="C400" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D400" s="13">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="E400" s="1">
         <v>0</v>
@@ -9741,10 +9744,10 @@
         <v>0</v>
       </c>
       <c r="C401" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D401" s="13">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="E401" s="1">
         <v>0</v>
@@ -9752,16 +9755,16 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="10" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B402" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C402" s="10" t="s">
-        <v>483</v>
+        <v>235</v>
       </c>
       <c r="D402" s="13">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E402" s="1">
         <v>0</v>
@@ -9775,10 +9778,10 @@
         <v>0</v>
       </c>
       <c r="C403" s="10" t="s">
-        <v>236</v>
+        <v>483</v>
       </c>
       <c r="D403" s="13">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E403" s="1">
         <v>0</v>
@@ -9792,10 +9795,10 @@
         <v>0</v>
       </c>
       <c r="C404" s="10" t="s">
-        <v>484</v>
+        <v>236</v>
       </c>
       <c r="D404" s="13">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="E404" s="1">
         <v>0</v>
@@ -9803,16 +9806,16 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="10" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B405" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C405" s="10" t="s">
-        <v>237</v>
+        <v>484</v>
       </c>
       <c r="D405" s="13">
-        <v>270</v>
+        <v>29</v>
       </c>
       <c r="E405" s="1">
         <v>0</v>
@@ -9823,13 +9826,13 @@
         <v>675</v>
       </c>
       <c r="B406" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C406" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D406" s="13">
-        <v>14</v>
+        <v>270</v>
       </c>
       <c r="E406" s="1">
         <v>0</v>
@@ -9857,13 +9860,13 @@
         <v>675</v>
       </c>
       <c r="B408" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C408" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D408" s="13">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="E408" s="1">
         <v>0</v>
@@ -9877,10 +9880,10 @@
         <v>9</v>
       </c>
       <c r="C409" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D409" s="13">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="E409" s="1">
         <v>0</v>
@@ -9894,10 +9897,10 @@
         <v>9</v>
       </c>
       <c r="C410" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D410" s="13">
-        <v>1200</v>
+        <v>6</v>
       </c>
       <c r="E410" s="1">
         <v>0</v>
@@ -9908,13 +9911,13 @@
         <v>675</v>
       </c>
       <c r="B411" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C411" s="10" t="s">
         <v>241</v>
       </c>
       <c r="D411" s="13">
-        <v>129</v>
+        <v>1200</v>
       </c>
       <c r="E411" s="1">
         <v>0</v>
@@ -9922,16 +9925,16 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="10" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B412" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C412" s="10" t="s">
-        <v>417</v>
+        <v>241</v>
       </c>
       <c r="D412" s="13">
-        <v>400</v>
+        <v>129</v>
       </c>
       <c r="E412" s="1">
         <v>0</v>
@@ -9939,16 +9942,16 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B413" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C413" s="10" t="s">
-        <v>465</v>
+        <v>417</v>
       </c>
       <c r="D413" s="13">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="E413" s="1">
         <v>0</v>
@@ -9956,16 +9959,16 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B414" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C414" s="10" t="s">
-        <v>386</v>
+        <v>465</v>
       </c>
       <c r="D414" s="13">
-        <v>1200</v>
+        <v>75</v>
       </c>
       <c r="E414" s="1">
         <v>0</v>
@@ -9973,13 +9976,13 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="10" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B415" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>418</v>
+        <v>386</v>
       </c>
       <c r="D415" s="13">
         <v>1200</v>
@@ -9990,16 +9993,16 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B416" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C416" s="10" t="s">
-        <v>754</v>
+        <v>418</v>
       </c>
       <c r="D416" s="13">
-        <v>290</v>
+        <v>1200</v>
       </c>
       <c r="E416" s="1">
         <v>0</v>
@@ -10007,16 +10010,16 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" s="10" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B417" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C417" s="10" t="s">
-        <v>387</v>
+        <v>754</v>
       </c>
       <c r="D417" s="13">
-        <v>26900</v>
+        <v>290</v>
       </c>
       <c r="E417" s="1">
         <v>0</v>
@@ -10024,16 +10027,16 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="10" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B418" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C418" s="10" t="s">
-        <v>466</v>
+        <v>387</v>
       </c>
       <c r="D418" s="13">
-        <v>80</v>
+        <v>26900</v>
       </c>
       <c r="E418" s="1">
         <v>0</v>
@@ -10041,16 +10044,16 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="10" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B419" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C419" s="10" t="s">
-        <v>242</v>
+        <v>466</v>
       </c>
       <c r="D419" s="13">
-        <v>2025</v>
+        <v>80</v>
       </c>
       <c r="E419" s="1">
         <v>0</v>
@@ -10061,13 +10064,13 @@
         <v>678</v>
       </c>
       <c r="B420" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C420" s="10" t="s">
         <v>242</v>
       </c>
       <c r="D420" s="13">
-        <v>300</v>
+        <v>2025</v>
       </c>
       <c r="E420" s="1">
         <v>0</v>
@@ -10075,16 +10078,16 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="10" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B421" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C421" s="10" t="s">
-        <v>467</v>
+        <v>242</v>
       </c>
       <c r="D421" s="13">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="E421" s="1">
         <v>0</v>
@@ -10092,16 +10095,16 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" s="10" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B422" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C422" s="10" t="s">
-        <v>243</v>
+        <v>467</v>
       </c>
       <c r="D422" s="13">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="E422" s="1">
         <v>0</v>
@@ -10112,13 +10115,13 @@
         <v>678</v>
       </c>
       <c r="B423" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C423" s="10" t="s">
         <v>243</v>
       </c>
       <c r="D423" s="13">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E423" s="1">
         <v>0</v>
@@ -10129,13 +10132,13 @@
         <v>678</v>
       </c>
       <c r="B424" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C424" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D424" s="13">
-        <v>90</v>
+        <v>360</v>
       </c>
       <c r="E424" s="1">
         <v>0</v>
@@ -10143,16 +10146,16 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="10" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="B425" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C425" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D425" s="13">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="E425" s="1">
         <v>0</v>
@@ -10160,16 +10163,16 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="10" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B426" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C426" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D426" s="13">
-        <v>97</v>
+        <v>600</v>
       </c>
       <c r="E426" s="1">
         <v>0</v>
@@ -10177,16 +10180,16 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B427" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C427" s="10" t="s">
-        <v>485</v>
+        <v>246</v>
       </c>
       <c r="D427" s="13">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="E427" s="1">
         <v>0</v>
@@ -10200,10 +10203,10 @@
         <v>0</v>
       </c>
       <c r="C428" s="10" t="s">
-        <v>382</v>
+        <v>485</v>
       </c>
       <c r="D428" s="13">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="E428" s="1">
         <v>0</v>
@@ -10217,10 +10220,10 @@
         <v>0</v>
       </c>
       <c r="C429" s="10" t="s">
-        <v>519</v>
+        <v>382</v>
       </c>
       <c r="D429" s="13">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="E429" s="1">
         <v>0</v>
@@ -10234,10 +10237,10 @@
         <v>0</v>
       </c>
       <c r="C430" s="10" t="s">
-        <v>486</v>
+        <v>519</v>
       </c>
       <c r="D430" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E430" s="1">
         <v>0</v>
@@ -10245,16 +10248,16 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B431" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C431" s="10" t="s">
-        <v>247</v>
+        <v>486</v>
       </c>
       <c r="D431" s="13">
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="E431" s="1">
         <v>0</v>
@@ -10268,10 +10271,10 @@
         <v>9</v>
       </c>
       <c r="C432" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D432" s="13">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E432" s="1">
         <v>0</v>
@@ -10285,10 +10288,10 @@
         <v>9</v>
       </c>
       <c r="C433" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D433" s="13">
-        <v>530</v>
+        <v>8</v>
       </c>
       <c r="E433" s="1">
         <v>0</v>
@@ -10296,16 +10299,16 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="10" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B434" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C434" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D434" s="13">
-        <v>400</v>
+        <v>530</v>
       </c>
       <c r="E434" s="1">
         <v>0</v>
@@ -10313,16 +10316,16 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B435" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C435" s="10" t="s">
-        <v>468</v>
+        <v>250</v>
       </c>
       <c r="D435" s="13">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="E435" s="1">
         <v>0</v>
@@ -10330,16 +10333,16 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="10" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B436" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C436" s="10" t="s">
-        <v>251</v>
+        <v>468</v>
       </c>
       <c r="D436" s="13">
-        <v>1200</v>
+        <v>50</v>
       </c>
       <c r="E436" s="1">
         <v>0</v>
@@ -10347,16 +10350,16 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="10" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B437" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C437" s="10" t="s">
-        <v>755</v>
+        <v>251</v>
       </c>
       <c r="D437" s="13">
-        <v>140</v>
+        <v>1200</v>
       </c>
       <c r="E437" s="1">
         <v>0</v>
@@ -10370,10 +10373,10 @@
         <v>0</v>
       </c>
       <c r="C438" s="10" t="s">
-        <v>469</v>
+        <v>755</v>
       </c>
       <c r="D438" s="13">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="E438" s="1">
         <v>0</v>
@@ -10381,16 +10384,16 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="10" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B439" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C439" s="10" t="s">
-        <v>252</v>
+        <v>469</v>
       </c>
       <c r="D439" s="13">
-        <v>400</v>
+        <v>31</v>
       </c>
       <c r="E439" s="1">
         <v>0</v>
@@ -10401,13 +10404,13 @@
         <v>684</v>
       </c>
       <c r="B440" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C440" s="10" t="s">
         <v>252</v>
       </c>
       <c r="D440" s="13">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E440" s="1">
         <v>0</v>
@@ -10415,16 +10418,16 @@
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" s="10" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B441" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C441" s="10" t="s">
-        <v>756</v>
+        <v>252</v>
       </c>
       <c r="D441" s="13">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="E441" s="1">
         <v>0</v>
@@ -10432,16 +10435,16 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="10" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B442" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C442" s="10" t="s">
-        <v>388</v>
+        <v>756</v>
       </c>
       <c r="D442" s="13">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E442" s="1">
         <v>0</v>
@@ -10455,10 +10458,10 @@
         <v>40</v>
       </c>
       <c r="C443" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D443" s="13">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E443" s="1">
         <v>0</v>
@@ -10472,10 +10475,10 @@
         <v>40</v>
       </c>
       <c r="C444" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D444" s="13">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="E444" s="1">
         <v>0</v>
@@ -10483,16 +10486,16 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="10" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="B445" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C445" s="10" t="s">
-        <v>253</v>
+        <v>390</v>
       </c>
       <c r="D445" s="13">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E445" s="1">
         <v>0</v>
@@ -10500,16 +10503,16 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="10" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="B446" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C446" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D446" s="13">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="E446" s="1">
         <v>0</v>
@@ -10523,10 +10526,10 @@
         <v>0</v>
       </c>
       <c r="C447" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D447" s="13">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E447" s="1">
         <v>0</v>
@@ -10540,10 +10543,10 @@
         <v>0</v>
       </c>
       <c r="C448" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D448" s="13">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E448" s="1">
         <v>0</v>
@@ -10557,10 +10560,10 @@
         <v>0</v>
       </c>
       <c r="C449" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D449" s="13">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E449" s="1">
         <v>0</v>
@@ -10574,10 +10577,10 @@
         <v>0</v>
       </c>
       <c r="C450" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D450" s="13">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E450" s="1">
         <v>0</v>
@@ -10591,10 +10594,10 @@
         <v>0</v>
       </c>
       <c r="C451" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D451" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E451" s="1">
         <v>0</v>
@@ -10608,10 +10611,10 @@
         <v>0</v>
       </c>
       <c r="C452" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D452" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E452" s="1">
         <v>0</v>
@@ -10619,16 +10622,16 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="10" t="s">
-        <v>625</v>
+        <v>685</v>
       </c>
       <c r="B453" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C453" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D453" s="13">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E453" s="1">
         <v>0</v>
@@ -10642,10 +10645,10 @@
         <v>0</v>
       </c>
       <c r="C454" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D454" s="13">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E454" s="1">
         <v>0</v>
@@ -10659,10 +10662,10 @@
         <v>0</v>
       </c>
       <c r="C455" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D455" s="13">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E455" s="1">
         <v>0</v>
@@ -10670,16 +10673,16 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="10" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="B456" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C456" s="10" t="s">
-        <v>732</v>
+        <v>263</v>
       </c>
       <c r="D456" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E456" s="1">
         <v>0</v>
@@ -10693,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="C457" s="10" t="s">
-        <v>498</v>
+        <v>732</v>
       </c>
       <c r="D457" s="13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E457" s="1">
         <v>0</v>
@@ -10704,16 +10707,16 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="10" t="s">
-        <v>686</v>
+        <v>616</v>
       </c>
       <c r="B458" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C458" s="10" t="s">
-        <v>264</v>
+        <v>498</v>
       </c>
       <c r="D458" s="13">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E458" s="1">
         <v>0</v>
@@ -10721,16 +10724,16 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B459" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C459" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D459" s="13">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E459" s="1">
         <v>0</v>
@@ -10741,13 +10744,13 @@
         <v>687</v>
       </c>
       <c r="B460" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C460" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D460" s="13">
-        <v>830</v>
+        <v>47</v>
       </c>
       <c r="E460" s="1">
         <v>0</v>
@@ -10761,10 +10764,10 @@
         <v>40</v>
       </c>
       <c r="C461" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D461" s="13">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="E461" s="1">
         <v>0</v>
@@ -10778,10 +10781,10 @@
         <v>40</v>
       </c>
       <c r="C462" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D462" s="13">
-        <v>1300</v>
+        <v>850</v>
       </c>
       <c r="E462" s="1">
         <v>0</v>
@@ -10795,10 +10798,10 @@
         <v>40</v>
       </c>
       <c r="C463" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D463" s="13">
-        <v>450</v>
+        <v>1300</v>
       </c>
       <c r="E463" s="1">
         <v>0</v>
@@ -10806,16 +10809,16 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="10" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B464" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C464" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D464" s="13">
-        <v>779</v>
+        <v>450</v>
       </c>
       <c r="E464" s="1">
         <v>0</v>
@@ -10840,16 +10843,16 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="10" t="s">
-        <v>585</v>
+        <v>686</v>
       </c>
       <c r="B466" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C466" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D466" s="13">
-        <v>273</v>
+        <v>779</v>
       </c>
       <c r="E466" s="1">
         <v>0</v>
@@ -10857,16 +10860,16 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="10" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="B467" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C467" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D467" s="13">
-        <v>3</v>
+        <v>273</v>
       </c>
       <c r="E467" s="1">
         <v>0</v>
@@ -10880,10 +10883,10 @@
         <v>0</v>
       </c>
       <c r="C468" s="10" t="s">
-        <v>530</v>
+        <v>272</v>
       </c>
       <c r="D468" s="13">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E468" s="1">
         <v>0</v>
@@ -10891,16 +10894,16 @@
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="10" t="s">
-        <v>639</v>
+        <v>601</v>
       </c>
       <c r="B469" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C469" s="10" t="s">
-        <v>273</v>
+        <v>530</v>
       </c>
       <c r="D469" s="13">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E469" s="1">
         <v>0</v>
@@ -10914,10 +10917,10 @@
         <v>0</v>
       </c>
       <c r="C470" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D470" s="13">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E470" s="1">
         <v>0</v>
@@ -10931,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="C471" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D471" s="13">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E471" s="1">
         <v>0</v>
@@ -10948,10 +10951,10 @@
         <v>0</v>
       </c>
       <c r="C472" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D472" s="13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E472" s="1">
         <v>0</v>
@@ -10965,10 +10968,10 @@
         <v>0</v>
       </c>
       <c r="C473" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D473" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E473" s="1">
         <v>0</v>
@@ -10979,13 +10982,13 @@
         <v>639</v>
       </c>
       <c r="B474" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C474" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D474" s="13">
-        <v>840</v>
+        <v>1</v>
       </c>
       <c r="E474" s="1">
         <v>0</v>
@@ -10999,10 +11002,10 @@
         <v>40</v>
       </c>
       <c r="C475" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D475" s="13">
-        <v>15</v>
+        <v>840</v>
       </c>
       <c r="E475" s="1">
         <v>0</v>
@@ -11016,10 +11019,10 @@
         <v>40</v>
       </c>
       <c r="C476" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D476" s="13">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E476" s="1">
         <v>0</v>
@@ -11033,10 +11036,10 @@
         <v>40</v>
       </c>
       <c r="C477" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D477" s="13">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="E477" s="1">
         <v>0</v>
@@ -11050,10 +11053,10 @@
         <v>40</v>
       </c>
       <c r="C478" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D478" s="13">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E478" s="1">
         <v>0</v>
@@ -11067,10 +11070,10 @@
         <v>40</v>
       </c>
       <c r="C479" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D479" s="13">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E479" s="1">
         <v>0</v>
@@ -11084,10 +11087,10 @@
         <v>40</v>
       </c>
       <c r="C480" s="10" t="s">
-        <v>433</v>
+        <v>283</v>
       </c>
       <c r="D480" s="13">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E480" s="1">
         <v>0</v>
@@ -11095,16 +11098,16 @@
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="10" t="s">
-        <v>582</v>
+        <v>639</v>
       </c>
       <c r="B481" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C481" s="10" t="s">
-        <v>284</v>
+        <v>433</v>
       </c>
       <c r="D481" s="13">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="E481" s="1">
         <v>0</v>
@@ -11112,16 +11115,16 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="10" t="s">
-        <v>686</v>
+        <v>582</v>
       </c>
       <c r="B482" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D482" s="13">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="E482" s="1">
         <v>0</v>
@@ -11129,16 +11132,16 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="10" t="s">
-        <v>584</v>
+        <v>686</v>
       </c>
       <c r="B483" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C483" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="D483" s="13">
         <v>40</v>
-      </c>
-      <c r="C483" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="D483" s="13">
-        <v>16400</v>
       </c>
       <c r="E483" s="1">
         <v>0</v>
@@ -11146,16 +11149,16 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="10" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="B484" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C484" s="10" t="s">
-        <v>286</v>
+        <v>425</v>
       </c>
       <c r="D484" s="13">
-        <v>2</v>
+        <v>16400</v>
       </c>
       <c r="E484" s="1">
         <v>0</v>
@@ -11166,7 +11169,7 @@
         <v>598</v>
       </c>
       <c r="B485" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C485" s="10" t="s">
         <v>286</v>
@@ -11186,10 +11189,10 @@
         <v>9</v>
       </c>
       <c r="C486" s="10" t="s">
-        <v>540</v>
+        <v>286</v>
       </c>
       <c r="D486" s="13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E486" s="1">
         <v>0</v>
@@ -11200,13 +11203,13 @@
         <v>598</v>
       </c>
       <c r="B487" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>287</v>
+        <v>540</v>
       </c>
       <c r="D487" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E487" s="1">
         <v>0</v>
@@ -11220,10 +11223,10 @@
         <v>0</v>
       </c>
       <c r="C488" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D488" s="13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E488" s="1">
         <v>0</v>
@@ -11237,10 +11240,10 @@
         <v>0</v>
       </c>
       <c r="C489" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D489" s="13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E489" s="1">
         <v>0</v>
@@ -11254,10 +11257,10 @@
         <v>0</v>
       </c>
       <c r="C490" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D490" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E490" s="1">
         <v>0</v>
@@ -11271,7 +11274,7 @@
         <v>0</v>
       </c>
       <c r="C491" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D491" s="13">
         <v>1</v>
@@ -11288,7 +11291,7 @@
         <v>0</v>
       </c>
       <c r="C492" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D492" s="13">
         <v>1</v>
@@ -11305,7 +11308,7 @@
         <v>0</v>
       </c>
       <c r="C493" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D493" s="13">
         <v>1</v>
@@ -11322,10 +11325,10 @@
         <v>0</v>
       </c>
       <c r="C494" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D494" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E494" s="1">
         <v>0</v>
@@ -11339,10 +11342,10 @@
         <v>0</v>
       </c>
       <c r="C495" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D495" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E495" s="1">
         <v>0</v>
@@ -11356,10 +11359,10 @@
         <v>0</v>
       </c>
       <c r="C496" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D496" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E496" s="1">
         <v>0</v>
@@ -11367,16 +11370,16 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B497" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C497" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D497" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E497" s="1">
         <v>0</v>
@@ -11384,16 +11387,16 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B498" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C498" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D498" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E498" s="1">
         <v>0</v>
@@ -11407,10 +11410,10 @@
         <v>0</v>
       </c>
       <c r="C499" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D499" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E499" s="1">
         <v>0</v>
@@ -11418,13 +11421,13 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B500" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C500" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D500" s="13">
         <v>1</v>
@@ -11441,7 +11444,7 @@
         <v>0</v>
       </c>
       <c r="C501" s="10" t="s">
-        <v>447</v>
+        <v>300</v>
       </c>
       <c r="D501" s="13">
         <v>1</v>
@@ -11452,13 +11455,13 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
       <c r="B502" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C502" s="10" t="s">
-        <v>301</v>
+        <v>447</v>
       </c>
       <c r="D502" s="13">
         <v>1</v>
@@ -11469,13 +11472,13 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>644</v>
+        <v>582</v>
       </c>
       <c r="B503" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C503" s="10" t="s">
-        <v>502</v>
+        <v>301</v>
       </c>
       <c r="D503" s="13">
         <v>1</v>
@@ -11492,7 +11495,7 @@
         <v>0</v>
       </c>
       <c r="C504" s="10" t="s">
-        <v>302</v>
+        <v>502</v>
       </c>
       <c r="D504" s="13">
         <v>1</v>
@@ -11503,16 +11506,16 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>582</v>
+        <v>644</v>
       </c>
       <c r="B505" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C505" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D505" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E505" s="1">
         <v>0</v>
@@ -11520,16 +11523,16 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="B506" s="10" t="s">
-        <v>545</v>
+        <v>0</v>
       </c>
       <c r="C506" s="10" t="s">
-        <v>744</v>
+        <v>303</v>
       </c>
       <c r="D506" s="13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E506" s="1">
         <v>0</v>
@@ -11543,10 +11546,10 @@
         <v>545</v>
       </c>
       <c r="C507" s="10" t="s">
-        <v>711</v>
+        <v>744</v>
       </c>
       <c r="D507" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E507" s="1">
         <v>0</v>
@@ -11560,10 +11563,10 @@
         <v>545</v>
       </c>
       <c r="C508" s="10" t="s">
-        <v>546</v>
+        <v>711</v>
       </c>
       <c r="D508" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E508" s="1">
         <v>0</v>
@@ -11577,10 +11580,10 @@
         <v>545</v>
       </c>
       <c r="C509" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D509" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E509" s="1">
         <v>0</v>
@@ -11588,16 +11591,16 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>690</v>
+        <v>588</v>
       </c>
       <c r="B510" s="10" t="s">
-        <v>0</v>
+        <v>545</v>
       </c>
       <c r="C510" s="10" t="s">
-        <v>731</v>
+        <v>547</v>
       </c>
       <c r="D510" s="13">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E510" s="1">
         <v>0</v>
@@ -11605,16 +11608,16 @@
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" s="10" t="s">
-        <v>588</v>
+        <v>690</v>
       </c>
       <c r="B511" s="10" t="s">
-        <v>545</v>
+        <v>0</v>
       </c>
       <c r="C511" s="10" t="s">
-        <v>548</v>
+        <v>731</v>
       </c>
       <c r="D511" s="13">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E511" s="1">
         <v>0</v>
@@ -11628,10 +11631,10 @@
         <v>545</v>
       </c>
       <c r="C512" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D512" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E512" s="1">
         <v>0</v>
@@ -11645,7 +11648,7 @@
         <v>545</v>
       </c>
       <c r="C513" s="10" t="s">
-        <v>715</v>
+        <v>549</v>
       </c>
       <c r="D513" s="13">
         <v>3</v>
@@ -11662,10 +11665,10 @@
         <v>545</v>
       </c>
       <c r="C514" s="10" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="D514" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E514" s="1">
         <v>0</v>
@@ -11673,16 +11676,16 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>688</v>
+        <v>588</v>
       </c>
       <c r="B515" s="10" t="s">
         <v>545</v>
       </c>
       <c r="C515" s="10" t="s">
-        <v>550</v>
+        <v>733</v>
       </c>
       <c r="D515" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E515" s="1">
         <v>0</v>
@@ -11690,16 +11693,16 @@
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>588</v>
+        <v>688</v>
       </c>
       <c r="B516" s="10" t="s">
         <v>545</v>
       </c>
       <c r="C516" s="10" t="s">
-        <v>745</v>
+        <v>550</v>
       </c>
       <c r="D516" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E516" s="1">
         <v>0</v>
@@ -11713,10 +11716,10 @@
         <v>545</v>
       </c>
       <c r="C517" s="10" t="s">
-        <v>551</v>
+        <v>745</v>
       </c>
       <c r="D517" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E517" s="1">
         <v>0</v>
@@ -11727,10 +11730,10 @@
         <v>588</v>
       </c>
       <c r="B518" s="10" t="s">
-        <v>0</v>
+        <v>545</v>
       </c>
       <c r="C518" s="10" t="s">
-        <v>510</v>
+        <v>551</v>
       </c>
       <c r="D518" s="13">
         <v>1</v>
@@ -11747,7 +11750,7 @@
         <v>0</v>
       </c>
       <c r="C519" s="10" t="s">
-        <v>304</v>
+        <v>510</v>
       </c>
       <c r="D519" s="13">
         <v>1</v>
@@ -11758,16 +11761,16 @@
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
-        <v>689</v>
+        <v>588</v>
       </c>
       <c r="B520" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C520" s="10" t="s">
-        <v>511</v>
+        <v>304</v>
       </c>
       <c r="D520" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E520" s="1">
         <v>0</v>
@@ -11775,16 +11778,16 @@
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521" s="10" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B521" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C521" s="10" t="s">
-        <v>305</v>
+        <v>511</v>
       </c>
       <c r="D521" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E521" s="1">
         <v>0</v>
@@ -11798,10 +11801,10 @@
         <v>0</v>
       </c>
       <c r="C522" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D522" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E522" s="1">
         <v>0</v>
@@ -11815,10 +11818,10 @@
         <v>0</v>
       </c>
       <c r="C523" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D523" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E523" s="1">
         <v>0</v>
@@ -11832,7 +11835,7 @@
         <v>0</v>
       </c>
       <c r="C524" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D524" s="13">
         <v>1</v>
@@ -11849,7 +11852,7 @@
         <v>0</v>
       </c>
       <c r="C525" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D525" s="13">
         <v>1</v>
@@ -11866,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="C526" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D526" s="13">
         <v>1</v>
@@ -11883,10 +11886,10 @@
         <v>0</v>
       </c>
       <c r="C527" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D527" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E527" s="1">
         <v>0</v>
@@ -11894,13 +11897,13 @@
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" s="10" t="s">
-        <v>588</v>
+        <v>690</v>
       </c>
       <c r="B528" s="10" t="s">
-        <v>545</v>
+        <v>0</v>
       </c>
       <c r="C528" s="10" t="s">
-        <v>552</v>
+        <v>311</v>
       </c>
       <c r="D528" s="13">
         <v>2</v>
@@ -11917,10 +11920,10 @@
         <v>545</v>
       </c>
       <c r="C529" s="10" t="s">
-        <v>736</v>
+        <v>552</v>
       </c>
       <c r="D529" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E529" s="1">
         <v>0</v>
@@ -11934,10 +11937,10 @@
         <v>545</v>
       </c>
       <c r="C530" s="10" t="s">
-        <v>553</v>
+        <v>736</v>
       </c>
       <c r="D530" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E530" s="1">
         <v>0</v>
@@ -11951,10 +11954,10 @@
         <v>545</v>
       </c>
       <c r="C531" s="10" t="s">
-        <v>730</v>
+        <v>553</v>
       </c>
       <c r="D531" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E531" s="1">
         <v>0</v>
@@ -11968,10 +11971,10 @@
         <v>545</v>
       </c>
       <c r="C532" s="10" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="D532" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E532" s="1">
         <v>0</v>
@@ -11979,16 +11982,16 @@
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" s="10" t="s">
-        <v>782</v>
+        <v>588</v>
       </c>
       <c r="B533" s="10" t="s">
-        <v>0</v>
+        <v>545</v>
       </c>
       <c r="C533" s="10" t="s">
-        <v>783</v>
+        <v>743</v>
       </c>
       <c r="D533" s="13">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E533" s="1">
         <v>0</v>
@@ -11996,16 +11999,16 @@
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" s="10" t="s">
-        <v>590</v>
+        <v>782</v>
       </c>
       <c r="B534" s="10" t="s">
-        <v>545</v>
+        <v>0</v>
       </c>
       <c r="C534" s="10" t="s">
-        <v>734</v>
+        <v>783</v>
       </c>
       <c r="D534" s="13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E534" s="1">
         <v>0</v>
@@ -12019,7 +12022,7 @@
         <v>545</v>
       </c>
       <c r="C535" s="10" t="s">
-        <v>554</v>
+        <v>734</v>
       </c>
       <c r="D535" s="13">
         <v>1</v>
@@ -12030,13 +12033,13 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="10" t="s">
-        <v>644</v>
+        <v>590</v>
       </c>
       <c r="B536" s="10" t="s">
         <v>545</v>
       </c>
       <c r="C536" s="10" t="s">
-        <v>774</v>
+        <v>554</v>
       </c>
       <c r="D536" s="13">
         <v>1</v>
@@ -12053,10 +12056,10 @@
         <v>545</v>
       </c>
       <c r="C537" s="10" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D537" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E537" s="1">
         <v>0</v>
@@ -12064,16 +12067,16 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="10" t="s">
-        <v>688</v>
+        <v>644</v>
       </c>
       <c r="B538" s="10" t="s">
         <v>545</v>
       </c>
       <c r="C538" s="10" t="s">
-        <v>555</v>
+        <v>775</v>
       </c>
       <c r="D538" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E538" s="1">
         <v>0</v>
@@ -12087,7 +12090,7 @@
         <v>545</v>
       </c>
       <c r="C539" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D539" s="13">
         <v>1</v>
@@ -12098,13 +12101,13 @@
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" s="10" t="s">
-        <v>590</v>
+        <v>688</v>
       </c>
       <c r="B540" s="10" t="s">
         <v>545</v>
       </c>
       <c r="C540" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D540" s="13">
         <v>1</v>
@@ -12121,7 +12124,7 @@
         <v>545</v>
       </c>
       <c r="C541" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D541" s="13">
         <v>1</v>
@@ -12138,7 +12141,7 @@
         <v>545</v>
       </c>
       <c r="C542" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D542" s="13">
         <v>1</v>
@@ -12155,10 +12158,10 @@
         <v>545</v>
       </c>
       <c r="C543" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D543" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E543" s="1">
         <v>0</v>
@@ -12172,10 +12175,10 @@
         <v>545</v>
       </c>
       <c r="C544" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D544" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E544" s="1">
         <v>0</v>
@@ -12183,16 +12186,16 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="10" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B545" s="10" t="s">
         <v>545</v>
       </c>
       <c r="C545" s="10" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="D545" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E545" s="1">
         <v>0</v>
@@ -12206,10 +12209,10 @@
         <v>545</v>
       </c>
       <c r="C546" s="10" t="s">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="D546" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E546" s="1">
         <v>0</v>
@@ -12223,10 +12226,10 @@
         <v>545</v>
       </c>
       <c r="C547" s="10" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="D547" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E547" s="1">
         <v>0</v>
@@ -12240,10 +12243,10 @@
         <v>545</v>
       </c>
       <c r="C548" s="10" t="s">
-        <v>563</v>
+        <v>578</v>
       </c>
       <c r="D548" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E548" s="1">
         <v>0</v>
@@ -12251,16 +12254,16 @@
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" s="10" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B549" s="10" t="s">
         <v>545</v>
       </c>
       <c r="C549" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D549" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E549" s="1">
         <v>0</v>
@@ -12274,7 +12277,7 @@
         <v>545</v>
       </c>
       <c r="C550" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D550" s="13">
         <v>1</v>
@@ -12285,13 +12288,13 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" s="10" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B551" s="10" t="s">
         <v>545</v>
       </c>
       <c r="C551" s="10" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="D551" s="13">
         <v>1</v>
@@ -12308,7 +12311,7 @@
         <v>545</v>
       </c>
       <c r="C552" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D552" s="13">
         <v>1</v>
@@ -12325,7 +12328,7 @@
         <v>545</v>
       </c>
       <c r="C553" s="10" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="D553" s="13">
         <v>1</v>
@@ -12342,10 +12345,10 @@
         <v>545</v>
       </c>
       <c r="C554" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D554" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E554" s="1">
         <v>0</v>
@@ -12359,10 +12362,10 @@
         <v>545</v>
       </c>
       <c r="C555" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D555" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E555" s="1">
         <v>0</v>
@@ -12376,7 +12379,7 @@
         <v>545</v>
       </c>
       <c r="C556" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D556" s="13">
         <v>2</v>
@@ -12393,10 +12396,10 @@
         <v>545</v>
       </c>
       <c r="C557" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D557" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E557" s="1">
         <v>0</v>
@@ -12410,10 +12413,10 @@
         <v>545</v>
       </c>
       <c r="C558" s="10" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D558" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E558" s="1">
         <v>0</v>
@@ -12427,10 +12430,10 @@
         <v>545</v>
       </c>
       <c r="C559" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D559" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E559" s="1">
         <v>0</v>
@@ -12438,16 +12441,16 @@
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" s="10" t="s">
-        <v>644</v>
+        <v>588</v>
       </c>
       <c r="B560" s="10" t="s">
         <v>545</v>
       </c>
       <c r="C560" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D560" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E560" s="1">
         <v>0</v>
@@ -12455,16 +12458,16 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" s="10" t="s">
-        <v>690</v>
+        <v>644</v>
       </c>
       <c r="B561" s="10" t="s">
-        <v>0</v>
+        <v>545</v>
       </c>
       <c r="C561" s="10" t="s">
-        <v>312</v>
+        <v>573</v>
       </c>
       <c r="D561" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E561" s="1">
         <v>0</v>
@@ -12472,13 +12475,13 @@
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" s="10" t="s">
-        <v>588</v>
+        <v>690</v>
       </c>
       <c r="B562" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C562" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D562" s="13">
         <v>1</v>
@@ -12495,7 +12498,7 @@
         <v>0</v>
       </c>
       <c r="C563" s="10" t="s">
-        <v>512</v>
+        <v>313</v>
       </c>
       <c r="D563" s="13">
         <v>1</v>
@@ -12509,13 +12512,13 @@
         <v>588</v>
       </c>
       <c r="B564" s="10" t="s">
-        <v>545</v>
+        <v>0</v>
       </c>
       <c r="C564" s="10" t="s">
-        <v>314</v>
+        <v>512</v>
       </c>
       <c r="D564" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E564" s="1">
         <v>0</v>
@@ -12526,7 +12529,7 @@
         <v>588</v>
       </c>
       <c r="B565" s="10" t="s">
-        <v>0</v>
+        <v>545</v>
       </c>
       <c r="C565" s="10" t="s">
         <v>314</v>
@@ -12540,13 +12543,13 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" s="10" t="s">
-        <v>644</v>
+        <v>588</v>
       </c>
       <c r="B566" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C566" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D566" s="13">
         <v>2</v>
@@ -12563,10 +12566,10 @@
         <v>0</v>
       </c>
       <c r="C567" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D567" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E567" s="1">
         <v>0</v>
@@ -12580,7 +12583,7 @@
         <v>0</v>
       </c>
       <c r="C568" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D568" s="13">
         <v>1</v>
@@ -12591,13 +12594,13 @@
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" s="10" t="s">
-        <v>590</v>
+        <v>644</v>
       </c>
       <c r="B569" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C569" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D569" s="13">
         <v>1</v>
@@ -12614,7 +12617,7 @@
         <v>0</v>
       </c>
       <c r="C570" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D570" s="13">
         <v>1</v>
@@ -12625,16 +12628,16 @@
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" s="10" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B571" s="10" t="s">
-        <v>545</v>
+        <v>0</v>
       </c>
       <c r="C571" s="10" t="s">
-        <v>716</v>
+        <v>319</v>
       </c>
       <c r="D571" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E571" s="1">
         <v>0</v>
@@ -12648,10 +12651,10 @@
         <v>545</v>
       </c>
       <c r="C572" s="10" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D572" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E572" s="1">
         <v>0</v>
@@ -12665,10 +12668,10 @@
         <v>545</v>
       </c>
       <c r="C573" s="10" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D573" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E573" s="1">
         <v>0</v>
@@ -12682,10 +12685,10 @@
         <v>545</v>
       </c>
       <c r="C574" s="10" t="s">
-        <v>574</v>
+        <v>718</v>
       </c>
       <c r="D574" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E574" s="1">
         <v>0</v>
@@ -12699,7 +12702,7 @@
         <v>545</v>
       </c>
       <c r="C575" s="10" t="s">
-        <v>719</v>
+        <v>574</v>
       </c>
       <c r="D575" s="13">
         <v>1</v>
@@ -12716,10 +12719,10 @@
         <v>545</v>
       </c>
       <c r="C576" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D576" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E576" s="1">
         <v>0</v>
@@ -12733,10 +12736,10 @@
         <v>545</v>
       </c>
       <c r="C577" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D577" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E577" s="1">
         <v>0</v>
@@ -12750,7 +12753,7 @@
         <v>545</v>
       </c>
       <c r="C578" s="10" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D578" s="13">
         <v>2</v>
@@ -12767,10 +12770,10 @@
         <v>545</v>
       </c>
       <c r="C579" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D579" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E579" s="1">
         <v>0</v>
@@ -12784,7 +12787,7 @@
         <v>545</v>
       </c>
       <c r="C580" s="10" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D580" s="13">
         <v>4</v>
@@ -12801,10 +12804,10 @@
         <v>545</v>
       </c>
       <c r="C581" s="10" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D581" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E581" s="1">
         <v>0</v>
@@ -12818,7 +12821,7 @@
         <v>545</v>
       </c>
       <c r="C582" s="10" t="s">
-        <v>575</v>
+        <v>725</v>
       </c>
       <c r="D582" s="13">
         <v>2</v>
@@ -12835,10 +12838,10 @@
         <v>545</v>
       </c>
       <c r="C583" s="10" t="s">
-        <v>712</v>
+        <v>575</v>
       </c>
       <c r="D583" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E583" s="1">
         <v>0</v>
@@ -12846,13 +12849,13 @@
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" s="10" t="s">
-        <v>644</v>
+        <v>588</v>
       </c>
       <c r="B584" s="10" t="s">
         <v>545</v>
       </c>
       <c r="C584" s="10" t="s">
-        <v>576</v>
+        <v>712</v>
       </c>
       <c r="D584" s="13">
         <v>1</v>
@@ -12863,16 +12866,16 @@
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585" s="10" t="s">
-        <v>590</v>
+        <v>644</v>
       </c>
       <c r="B585" s="10" t="s">
-        <v>0</v>
+        <v>545</v>
       </c>
       <c r="C585" s="10" t="s">
-        <v>320</v>
+        <v>576</v>
       </c>
       <c r="D585" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E585" s="1">
         <v>0</v>
@@ -12880,16 +12883,16 @@
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A586" s="10" t="s">
-        <v>644</v>
+        <v>590</v>
       </c>
       <c r="B586" s="10" t="s">
-        <v>545</v>
+        <v>0</v>
       </c>
       <c r="C586" s="10" t="s">
-        <v>581</v>
+        <v>320</v>
       </c>
       <c r="D586" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E586" s="1">
         <v>0</v>
@@ -12897,16 +12900,16 @@
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587" s="10" t="s">
-        <v>667</v>
+        <v>644</v>
       </c>
       <c r="B587" s="10" t="s">
-        <v>40</v>
+        <v>545</v>
       </c>
       <c r="C587" s="10" t="s">
-        <v>413</v>
+        <v>581</v>
       </c>
       <c r="D587" s="13">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E587" s="1">
         <v>0</v>
@@ -12920,10 +12923,10 @@
         <v>40</v>
       </c>
       <c r="C588" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D588" s="13">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E588" s="1">
         <v>0</v>
@@ -12931,16 +12934,16 @@
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" s="10" t="s">
-        <v>582</v>
+        <v>667</v>
       </c>
       <c r="B589" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C589" s="10" t="s">
-        <v>321</v>
+        <v>414</v>
       </c>
       <c r="D589" s="13">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E589" s="1">
         <v>0</v>
@@ -12948,13 +12951,13 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" s="10" t="s">
-        <v>691</v>
+        <v>582</v>
       </c>
       <c r="B590" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C590" s="10" t="s">
-        <v>438</v>
+        <v>321</v>
       </c>
       <c r="D590" s="13">
         <v>1</v>
@@ -12971,10 +12974,10 @@
         <v>9</v>
       </c>
       <c r="C591" s="10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D591" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E591" s="1">
         <v>0</v>
@@ -12988,10 +12991,10 @@
         <v>9</v>
       </c>
       <c r="C592" s="10" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D592" s="13">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E592" s="1">
         <v>0</v>
@@ -13005,10 +13008,10 @@
         <v>9</v>
       </c>
       <c r="C593" s="10" t="s">
-        <v>542</v>
+        <v>440</v>
       </c>
       <c r="D593" s="13">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E593" s="1">
         <v>0</v>
@@ -13022,10 +13025,10 @@
         <v>9</v>
       </c>
       <c r="C594" s="10" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D594" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E594" s="1">
         <v>0</v>
@@ -13039,10 +13042,10 @@
         <v>9</v>
       </c>
       <c r="C595" s="10" t="s">
-        <v>441</v>
+        <v>541</v>
       </c>
       <c r="D595" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E595" s="1">
         <v>0</v>
@@ -13056,10 +13059,10 @@
         <v>9</v>
       </c>
       <c r="C596" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D596" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E596" s="1">
         <v>0</v>
@@ -13067,16 +13070,16 @@
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A597" s="10" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B597" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C597" s="10" t="s">
-        <v>322</v>
+        <v>442</v>
       </c>
       <c r="D597" s="13">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="E597" s="1">
         <v>0</v>
@@ -13087,13 +13090,13 @@
         <v>692</v>
       </c>
       <c r="B598" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C598" s="10" t="s">
-        <v>766</v>
+        <v>322</v>
       </c>
       <c r="D598" s="13">
-        <v>800</v>
+        <v>37</v>
       </c>
       <c r="E598" s="1">
         <v>0</v>
@@ -13107,10 +13110,10 @@
         <v>40</v>
       </c>
       <c r="C599" s="10" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D599" s="13">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="E599" s="1">
         <v>0</v>
@@ -13124,10 +13127,10 @@
         <v>40</v>
       </c>
       <c r="C600" s="10" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D600" s="13">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="E600" s="1">
         <v>0</v>
@@ -13141,10 +13144,10 @@
         <v>40</v>
       </c>
       <c r="C601" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D601" s="13">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="E601" s="1">
         <v>0</v>
@@ -13158,10 +13161,10 @@
         <v>40</v>
       </c>
       <c r="C602" s="10" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D602" s="13">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="E602" s="1">
         <v>0</v>
@@ -13172,13 +13175,13 @@
         <v>692</v>
       </c>
       <c r="B603" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C603" s="10" t="s">
-        <v>323</v>
+        <v>770</v>
       </c>
       <c r="D603" s="13">
-        <v>1070</v>
+        <v>800</v>
       </c>
       <c r="E603" s="1">
         <v>0</v>
@@ -13186,16 +13189,16 @@
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A604" s="10" t="s">
-        <v>598</v>
+        <v>692</v>
       </c>
       <c r="B604" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C604" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D604" s="13">
-        <v>1</v>
+        <v>1070</v>
       </c>
       <c r="E604" s="1">
         <v>0</v>
@@ -13209,10 +13212,10 @@
         <v>0</v>
       </c>
       <c r="C605" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D605" s="13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E605" s="1">
         <v>0</v>
@@ -13220,16 +13223,16 @@
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A606" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B606" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C606" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D606" s="13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E606" s="1">
         <v>0</v>
@@ -13243,7 +13246,7 @@
         <v>0</v>
       </c>
       <c r="C607" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D607" s="13">
         <v>1</v>
@@ -13254,16 +13257,16 @@
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A608" s="10" t="s">
-        <v>693</v>
+        <v>599</v>
       </c>
       <c r="B608" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C608" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D608" s="13">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E608" s="1">
         <v>0</v>
@@ -13271,16 +13274,16 @@
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A609" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B609" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C609" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D609" s="13">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E609" s="1">
         <v>0</v>
@@ -13294,10 +13297,10 @@
         <v>0</v>
       </c>
       <c r="C610" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D610" s="13">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="E610" s="1">
         <v>0</v>
@@ -13305,16 +13308,16 @@
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A611" s="10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B611" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C611" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D611" s="13">
-        <v>300</v>
+        <v>121</v>
       </c>
       <c r="E611" s="1">
         <v>0</v>
@@ -13325,7 +13328,7 @@
         <v>695</v>
       </c>
       <c r="B612" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C612" s="10" t="s">
         <v>331</v>
@@ -13339,13 +13342,13 @@
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A613" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B613" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C613" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D613" s="13">
         <v>300</v>
@@ -13356,16 +13359,16 @@
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A614" s="10" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B614" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C614" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D614" s="13">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E614" s="1">
         <v>0</v>
@@ -13373,16 +13376,16 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" s="10" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B615" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C615" s="10" t="s">
-        <v>470</v>
+        <v>333</v>
       </c>
       <c r="D615" s="13">
-        <v>43</v>
+        <v>310</v>
       </c>
       <c r="E615" s="1">
         <v>0</v>
@@ -13390,16 +13393,16 @@
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A616" s="10" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B616" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C616" s="10" t="s">
-        <v>334</v>
+        <v>470</v>
       </c>
       <c r="D616" s="13">
-        <v>250</v>
+        <v>43</v>
       </c>
       <c r="E616" s="1">
         <v>0</v>
@@ -13410,13 +13413,13 @@
         <v>696</v>
       </c>
       <c r="B617" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C617" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D617" s="13">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E617" s="1">
         <v>0</v>
@@ -13447,10 +13450,10 @@
         <v>40</v>
       </c>
       <c r="C619" s="10" t="s">
-        <v>408</v>
+        <v>335</v>
       </c>
       <c r="D619" s="13">
-        <v>42</v>
+        <v>300</v>
       </c>
       <c r="E619" s="1">
         <v>0</v>
@@ -13464,10 +13467,10 @@
         <v>40</v>
       </c>
       <c r="C620" s="10" t="s">
-        <v>336</v>
+        <v>408</v>
       </c>
       <c r="D620" s="13">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E620" s="1">
         <v>0</v>
@@ -13475,16 +13478,16 @@
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A621" s="10" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B621" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C621" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D621" s="13">
-        <v>250</v>
+        <v>24</v>
       </c>
       <c r="E621" s="1">
         <v>0</v>
@@ -13492,16 +13495,16 @@
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A622" s="10" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B622" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C622" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D622" s="13">
-        <v>1250</v>
+        <v>250</v>
       </c>
       <c r="E622" s="1">
         <v>0</v>
@@ -13509,16 +13512,16 @@
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A623" s="10" t="s">
-        <v>757</v>
+        <v>699</v>
       </c>
       <c r="B623" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C623" s="10" t="s">
-        <v>758</v>
+        <v>338</v>
       </c>
       <c r="D623" s="13">
-        <v>100</v>
+        <v>1250</v>
       </c>
       <c r="E623" s="1">
         <v>0</v>
@@ -13526,16 +13529,16 @@
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A624" s="10" t="s">
-        <v>699</v>
+        <v>757</v>
       </c>
       <c r="B624" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C624" s="10" t="s">
-        <v>339</v>
+        <v>758</v>
       </c>
       <c r="D624" s="13">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="E624" s="1">
         <v>0</v>
@@ -13543,16 +13546,16 @@
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A625" s="10" t="s">
-        <v>757</v>
+        <v>699</v>
       </c>
       <c r="B625" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C625" s="10" t="s">
-        <v>759</v>
+        <v>339</v>
       </c>
       <c r="D625" s="13">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="E625" s="1">
         <v>0</v>
@@ -13560,16 +13563,16 @@
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A626" s="10" t="s">
-        <v>699</v>
+        <v>757</v>
       </c>
       <c r="B626" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C626" s="10" t="s">
-        <v>340</v>
+        <v>759</v>
       </c>
       <c r="D626" s="13">
-        <v>600</v>
+        <v>35</v>
       </c>
       <c r="E626" s="1">
         <v>0</v>
@@ -13594,16 +13597,16 @@
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A628" s="10" t="s">
-        <v>757</v>
+        <v>699</v>
       </c>
       <c r="B628" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C628" s="10" t="s">
-        <v>760</v>
+        <v>340</v>
       </c>
       <c r="D628" s="13">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="E628" s="1">
         <v>0</v>
@@ -13611,16 +13614,16 @@
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A629" s="10" t="s">
-        <v>699</v>
+        <v>757</v>
       </c>
       <c r="B629" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C629" s="10" t="s">
-        <v>406</v>
+        <v>760</v>
       </c>
       <c r="D629" s="13">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E629" s="1">
         <v>0</v>
@@ -13634,10 +13637,10 @@
         <v>40</v>
       </c>
       <c r="C630" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D630" s="13">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E630" s="1">
         <v>0</v>
@@ -13651,10 +13654,10 @@
         <v>40</v>
       </c>
       <c r="C631" s="10" t="s">
-        <v>341</v>
+        <v>407</v>
       </c>
       <c r="D631" s="13">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E631" s="1">
         <v>0</v>
@@ -13662,16 +13665,16 @@
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632" s="10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B632" s="10" t="s">
-        <v>420</v>
+        <v>40</v>
       </c>
       <c r="C632" s="10" t="s">
-        <v>431</v>
+        <v>341</v>
       </c>
       <c r="D632" s="13">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="E632" s="1">
         <v>0</v>
@@ -13682,13 +13685,13 @@
         <v>700</v>
       </c>
       <c r="B633" s="10" t="s">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="C633" s="10" t="s">
-        <v>342</v>
+        <v>431</v>
       </c>
       <c r="D633" s="13">
-        <v>1300</v>
+        <v>2</v>
       </c>
       <c r="E633" s="1">
         <v>0</v>
@@ -13702,10 +13705,10 @@
         <v>0</v>
       </c>
       <c r="C634" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D634" s="13">
-        <v>29</v>
+        <v>1300</v>
       </c>
       <c r="E634" s="1">
         <v>0</v>
@@ -13719,10 +13722,10 @@
         <v>0</v>
       </c>
       <c r="C635" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D635" s="13">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E635" s="1">
         <v>0</v>
@@ -13730,16 +13733,16 @@
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636" s="10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B636" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C636" s="10" t="s">
-        <v>487</v>
+        <v>344</v>
       </c>
       <c r="D636" s="13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E636" s="1">
         <v>0</v>
@@ -13753,10 +13756,10 @@
         <v>0</v>
       </c>
       <c r="C637" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D637" s="13">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E637" s="1">
         <v>0</v>
@@ -13770,10 +13773,10 @@
         <v>0</v>
       </c>
       <c r="C638" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D638" s="13">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E638" s="1">
         <v>0</v>
@@ -13781,16 +13784,16 @@
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B639" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C639" s="1" t="s">
-        <v>345</v>
+        <v>489</v>
       </c>
       <c r="D639" s="14">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="E639" s="1">
         <v>0</v>
@@ -13804,10 +13807,10 @@
         <v>9</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D640" s="14">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="E640" s="1">
         <v>0</v>
@@ -13821,10 +13824,10 @@
         <v>9</v>
       </c>
       <c r="C641" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D641" s="14">
-        <v>8</v>
+        <v>123</v>
       </c>
       <c r="E641" s="1">
         <v>0</v>
@@ -13838,10 +13841,10 @@
         <v>9</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D642" s="14">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="E642" s="1">
         <v>0</v>
@@ -13849,16 +13852,16 @@
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D643" s="14">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="E643" s="1">
         <v>0</v>
@@ -13872,10 +13875,10 @@
         <v>40</v>
       </c>
       <c r="C644" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D644" s="14">
-        <v>825</v>
+        <v>600</v>
       </c>
       <c r="E644" s="1">
         <v>0</v>
@@ -13883,16 +13886,16 @@
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C645" s="1" t="s">
-        <v>761</v>
+        <v>350</v>
       </c>
       <c r="D645" s="14">
-        <v>465</v>
+        <v>825</v>
       </c>
       <c r="E645" s="1">
         <v>0</v>
@@ -13900,16 +13903,16 @@
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C646" s="1" t="s">
-        <v>351</v>
+        <v>761</v>
       </c>
       <c r="D646" s="14">
-        <v>600</v>
+        <v>465</v>
       </c>
       <c r="E646" s="1">
         <v>0</v>
@@ -13934,16 +13937,16 @@
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B648" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>471</v>
+        <v>351</v>
       </c>
       <c r="D648" s="14">
-        <v>65</v>
+        <v>600</v>
       </c>
       <c r="E648" s="1">
         <v>0</v>
@@ -13951,16 +13954,16 @@
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C649" s="1" t="s">
-        <v>391</v>
+        <v>471</v>
       </c>
       <c r="D649" s="14">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E649" s="1">
         <v>0</v>
@@ -13974,10 +13977,10 @@
         <v>40</v>
       </c>
       <c r="C650" s="1" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
       <c r="D650" s="14">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E650" s="1">
         <v>0</v>
@@ -13985,16 +13988,16 @@
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D651" s="14">
-        <v>1501</v>
+        <v>72</v>
       </c>
       <c r="E651" s="1">
         <v>0</v>
@@ -14008,10 +14011,10 @@
         <v>0</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D652" s="14">
-        <v>1508</v>
+        <v>1501</v>
       </c>
       <c r="E652" s="1">
         <v>0</v>
@@ -14019,16 +14022,16 @@
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B653" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C653" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D653" s="14">
-        <v>600</v>
+        <v>1508</v>
       </c>
       <c r="E653" s="1">
         <v>0</v>
@@ -14042,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="C654" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D654" s="14">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E654" s="1">
         <v>0</v>
@@ -14059,10 +14062,10 @@
         <v>0</v>
       </c>
       <c r="C655" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D655" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E655" s="1">
         <v>0</v>
@@ -14076,10 +14079,10 @@
         <v>0</v>
       </c>
       <c r="C656" s="1" t="s">
-        <v>528</v>
+        <v>357</v>
       </c>
       <c r="D656" s="14">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="E656" s="1">
         <v>0</v>
@@ -14093,10 +14096,10 @@
         <v>0</v>
       </c>
       <c r="C657" s="1" t="s">
-        <v>358</v>
+        <v>528</v>
       </c>
       <c r="D657" s="14">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E657" s="1">
         <v>0</v>
@@ -14110,7 +14113,7 @@
         <v>0</v>
       </c>
       <c r="C658" s="1" t="s">
-        <v>419</v>
+        <v>358</v>
       </c>
       <c r="D658" s="14">
         <v>100</v>
@@ -14127,10 +14130,10 @@
         <v>0</v>
       </c>
       <c r="C659" s="1" t="s">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="D659" s="14">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E659" s="1">
         <v>0</v>
@@ -14138,16 +14141,16 @@
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>693</v>
+        <v>707</v>
       </c>
       <c r="B660" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C660" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D660" s="14">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="E660" s="1">
         <v>0</v>
@@ -14161,10 +14164,10 @@
         <v>0</v>
       </c>
       <c r="C661" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D661" s="14">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="E661" s="1">
         <v>0</v>
@@ -14172,16 +14175,16 @@
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>708</v>
+        <v>693</v>
       </c>
       <c r="B662" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>490</v>
+        <v>361</v>
       </c>
       <c r="D662" s="14">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="E662" s="1">
         <v>0</v>
@@ -14195,10 +14198,10 @@
         <v>0</v>
       </c>
       <c r="C663" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D663" s="14">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E663" s="1">
         <v>0</v>
@@ -14212,10 +14215,10 @@
         <v>0</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D664" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E664" s="1">
         <v>0</v>
@@ -14223,16 +14226,16 @@
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C665" s="1" t="s">
-        <v>362</v>
+        <v>492</v>
       </c>
       <c r="D665" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E665" s="1">
         <v>0</v>
@@ -14246,10 +14249,10 @@
         <v>9</v>
       </c>
       <c r="C666" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D666" s="14">
-        <v>225</v>
+        <v>15</v>
       </c>
       <c r="E666" s="1">
         <v>0</v>
@@ -14263,10 +14266,10 @@
         <v>9</v>
       </c>
       <c r="C667" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D667" s="14">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="E667" s="1">
         <v>0</v>
@@ -14274,16 +14277,16 @@
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>709</v>
+        <v>694</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C668" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D668" s="14">
-        <v>1200</v>
+        <v>150</v>
       </c>
       <c r="E668" s="1">
         <v>0</v>
@@ -14294,10 +14297,10 @@
         <v>709</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C669" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D669" s="14">
         <v>1200</v>
@@ -14314,10 +14317,10 @@
         <v>40</v>
       </c>
       <c r="C670" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D670" s="14">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="E670" s="1">
         <v>0</v>
@@ -14348,10 +14351,10 @@
         <v>40</v>
       </c>
       <c r="C672" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D672" s="14">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E672" s="1">
         <v>0</v>
@@ -14359,16 +14362,16 @@
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C673" s="1" t="s">
-        <v>787</v>
+        <v>368</v>
       </c>
       <c r="D673" s="14">
-        <v>235</v>
+        <v>500</v>
       </c>
       <c r="E673" s="1">
         <v>0</v>
@@ -14382,10 +14385,10 @@
         <v>0</v>
       </c>
       <c r="C674" s="1" t="s">
-        <v>762</v>
+        <v>787</v>
       </c>
       <c r="D674" s="14">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="E674" s="1">
         <v>0</v>
@@ -14393,16 +14396,16 @@
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B675" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C675" s="1" t="s">
-        <v>369</v>
+        <v>762</v>
       </c>
       <c r="D675" s="14">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="E675" s="1">
         <v>0</v>
@@ -14433,10 +14436,10 @@
         <v>0</v>
       </c>
       <c r="C677" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D677" s="14">
-        <v>175</v>
+        <v>950</v>
       </c>
       <c r="E677" s="1">
         <v>0</v>
@@ -14450,10 +14453,10 @@
         <v>0</v>
       </c>
       <c r="C678" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D678" s="14">
-        <v>225</v>
+        <v>175</v>
       </c>
       <c r="E678" s="1">
         <v>0</v>
@@ -14461,16 +14464,16 @@
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B679" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C679" s="1" t="s">
-        <v>472</v>
+        <v>371</v>
       </c>
       <c r="D679" s="14">
-        <v>10</v>
+        <v>225</v>
       </c>
       <c r="E679" s="1">
         <v>0</v>
@@ -14478,16 +14481,16 @@
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B680" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C680" s="1" t="s">
-        <v>372</v>
+        <v>472</v>
       </c>
       <c r="D680" s="14">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="E680" s="1">
         <v>0</v>
@@ -14498,13 +14501,13 @@
         <v>709</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C681" s="1" t="s">
         <v>372</v>
       </c>
       <c r="D681" s="14">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="E681" s="1">
         <v>0</v>
@@ -14515,13 +14518,13 @@
         <v>709</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C682" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D682" s="14">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="E682" s="1">
         <v>0</v>
@@ -14532,13 +14535,13 @@
         <v>709</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D683" s="14">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E683" s="1">
         <v>0</v>
@@ -14569,10 +14572,10 @@
         <v>40</v>
       </c>
       <c r="C685" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D685" s="14">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="E685" s="1">
         <v>0</v>
@@ -14592,6 +14595,23 @@
         <v>30</v>
       </c>
       <c r="E686" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A687" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C687" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D687" s="14">
+        <v>64</v>
+      </c>
+      <c r="E687" s="1">
         <v>0</v>
       </c>
     </row>

--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4ACC912-6E6C-471F-B040-E3228C29AD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A922A2-B7F7-4E59-8CB4-A2E17BDF3BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="782">
   <si>
     <t>3-ديوان</t>
   </si>
@@ -1697,9 +1697,6 @@
   </si>
   <si>
     <t>موتير 1/2 حصان توربين ليو LEO ACM37</t>
-  </si>
-  <si>
-    <t>موتير 3 حصان 3 فاز بينتاكس PENTAX CBT310</t>
   </si>
   <si>
     <t>موتير 3/4 حصان كاتم ليو LEO 4ACM60</t>
@@ -2934,7 +2931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E5C9A6-5EC3-4592-9122-0E1001CE6231}">
-  <dimension ref="A1:E681"/>
+  <dimension ref="A1:E680"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.8984375" style="2" bestFit="1" customWidth="1"/>
@@ -2971,7 +2968,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>0</v>
@@ -2988,7 +2985,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>0</v>
@@ -3005,7 +3002,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>0</v>
@@ -3022,7 +3019,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>0</v>
@@ -3039,7 +3036,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>0</v>
@@ -3056,16 +3053,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>429</v>
       </c>
       <c r="D9" s="13">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -3073,16 +3070,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>429</v>
       </c>
       <c r="D10" s="13">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -3090,7 +3087,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>0</v>
@@ -3107,7 +3104,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>0</v>
@@ -3124,7 +3121,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>0</v>
@@ -3141,7 +3138,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>0</v>
@@ -3158,7 +3155,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>9</v>
@@ -3175,13 +3172,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D16" s="13">
         <v>10</v>
@@ -3192,7 +3189,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>0</v>
@@ -3209,13 +3206,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D18" s="13">
         <v>1</v>
@@ -3226,7 +3223,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>0</v>
@@ -3243,7 +3240,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>0</v>
@@ -3260,7 +3257,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>0</v>
@@ -3277,7 +3274,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>0</v>
@@ -3294,7 +3291,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>0</v>
@@ -3311,7 +3308,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>0</v>
@@ -3328,7 +3325,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>0</v>
@@ -3345,13 +3342,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D26" s="13">
         <v>8</v>
@@ -3362,7 +3359,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>0</v>
@@ -3379,7 +3376,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>0</v>
@@ -3396,7 +3393,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>0</v>
@@ -3413,7 +3410,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>0</v>
@@ -3430,7 +3427,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>0</v>
@@ -3447,7 +3444,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>0</v>
@@ -3464,7 +3461,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>0</v>
@@ -3481,7 +3478,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>0</v>
@@ -3498,7 +3495,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>0</v>
@@ -3515,7 +3512,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>0</v>
@@ -3532,7 +3529,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>0</v>
@@ -3549,7 +3546,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>0</v>
@@ -3566,7 +3563,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>0</v>
@@ -3583,7 +3580,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>0</v>
@@ -3600,7 +3597,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>0</v>
@@ -3617,7 +3614,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>0</v>
@@ -3634,7 +3631,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>0</v>
@@ -3651,7 +3648,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>0</v>
@@ -3668,7 +3665,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>0</v>
@@ -3685,7 +3682,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>0</v>
@@ -3702,7 +3699,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>0</v>
@@ -3719,7 +3716,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>0</v>
@@ -3736,7 +3733,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>0</v>
@@ -3753,7 +3750,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>0</v>
@@ -3770,7 +3767,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>0</v>
@@ -3787,7 +3784,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>40</v>
@@ -3804,7 +3801,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>40</v>
@@ -3821,7 +3818,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>40</v>
@@ -3838,7 +3835,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>0</v>
@@ -3855,7 +3852,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>0</v>
@@ -3872,7 +3869,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>0</v>
@@ -3889,7 +3886,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>0</v>
@@ -3906,7 +3903,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>0</v>
@@ -3923,7 +3920,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>0</v>
@@ -3940,16 +3937,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>45</v>
       </c>
       <c r="D61" s="13">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3957,16 +3954,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>45</v>
       </c>
       <c r="D62" s="13">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3974,7 +3971,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>9</v>
@@ -3991,7 +3988,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>0</v>
@@ -4008,7 +4005,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>9</v>
@@ -4025,7 +4022,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>9</v>
@@ -4042,7 +4039,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>0</v>
@@ -4059,7 +4056,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>0</v>
@@ -4076,7 +4073,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>0</v>
@@ -4093,7 +4090,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>0</v>
@@ -4110,7 +4107,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B71" s="10" t="s">
         <v>9</v>
@@ -4127,7 +4124,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>9</v>
@@ -4144,7 +4141,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B73" s="10" t="s">
         <v>0</v>
@@ -4161,7 +4158,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>9</v>
@@ -4178,7 +4175,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>0</v>
@@ -4195,7 +4192,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>0</v>
@@ -4212,7 +4209,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B77" s="10" t="s">
         <v>0</v>
@@ -4229,7 +4226,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>40</v>
@@ -4246,13 +4243,13 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C79" s="10" t="s">
         <v>740</v>
-      </c>
-      <c r="B79" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>741</v>
       </c>
       <c r="D79" s="13">
         <v>70</v>
@@ -4263,7 +4260,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B80" s="10" t="s">
         <v>0</v>
@@ -4280,7 +4277,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B81" s="10" t="s">
         <v>40</v>
@@ -4297,16 +4294,16 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D82" s="13">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="E82" s="1">
         <v>0</v>
@@ -4314,16 +4311,16 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D83" s="13">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="E83" s="1">
         <v>0</v>
@@ -4331,7 +4328,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>40</v>
@@ -4348,13 +4345,13 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D85" s="13">
         <v>170</v>
@@ -4365,7 +4362,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>0</v>
@@ -4382,7 +4379,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>9</v>
@@ -4399,7 +4396,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>0</v>
@@ -4416,7 +4413,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B89" s="10" t="s">
         <v>0</v>
@@ -4433,7 +4430,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B90" s="10" t="s">
         <v>9</v>
@@ -4450,7 +4447,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>0</v>
@@ -4467,7 +4464,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>0</v>
@@ -4484,7 +4481,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B93" s="10" t="s">
         <v>40</v>
@@ -4501,7 +4498,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B94" s="10" t="s">
         <v>40</v>
@@ -4518,7 +4515,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B95" s="10" t="s">
         <v>0</v>
@@ -4535,7 +4532,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B96" s="10" t="s">
         <v>9</v>
@@ -4552,7 +4549,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B97" s="10" t="s">
         <v>9</v>
@@ -4569,7 +4566,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>0</v>
@@ -4586,13 +4583,13 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B99" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D99" s="13">
         <v>4</v>
@@ -4603,7 +4600,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B100" s="10" t="s">
         <v>0</v>
@@ -4620,7 +4617,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>0</v>
@@ -4637,13 +4634,13 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D102" s="13">
         <v>5</v>
@@ -4654,7 +4651,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B103" s="10" t="s">
         <v>0</v>
@@ -4671,7 +4668,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B104" s="10" t="s">
         <v>9</v>
@@ -4688,7 +4685,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B105" s="10" t="s">
         <v>0</v>
@@ -4705,7 +4702,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>0</v>
@@ -4722,7 +4719,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>0</v>
@@ -4739,7 +4736,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>0</v>
@@ -4756,7 +4753,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B109" s="10" t="s">
         <v>0</v>
@@ -4773,7 +4770,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>0</v>
@@ -4790,7 +4787,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B111" s="10" t="s">
         <v>0</v>
@@ -4807,7 +4804,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B112" s="10" t="s">
         <v>0</v>
@@ -4824,7 +4821,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B113" s="10" t="s">
         <v>40</v>
@@ -4841,7 +4838,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B114" s="10" t="s">
         <v>0</v>
@@ -4858,7 +4855,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B115" s="10" t="s">
         <v>0</v>
@@ -4875,7 +4872,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>0</v>
@@ -4892,7 +4889,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B117" s="10" t="s">
         <v>0</v>
@@ -4909,7 +4906,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B118" s="10" t="s">
         <v>0</v>
@@ -4926,7 +4923,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B119" s="10" t="s">
         <v>0</v>
@@ -4943,13 +4940,13 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B120" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D120" s="13">
         <v>3</v>
@@ -4960,13 +4957,13 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B121" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D121" s="13">
         <v>3</v>
@@ -4977,7 +4974,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>40</v>
@@ -4994,7 +4991,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B123" s="10" t="s">
         <v>40</v>
@@ -5011,7 +5008,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B124" s="10" t="s">
         <v>40</v>
@@ -5028,7 +5025,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B125" s="10" t="s">
         <v>40</v>
@@ -5045,7 +5042,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B126" s="10" t="s">
         <v>40</v>
@@ -5062,7 +5059,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B127" s="10" t="s">
         <v>0</v>
@@ -5079,7 +5076,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B128" s="10" t="s">
         <v>40</v>
@@ -5096,16 +5093,16 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>81</v>
       </c>
       <c r="D129" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E129" s="1">
         <v>0</v>
@@ -5113,16 +5110,16 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>81</v>
       </c>
       <c r="D130" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
@@ -5130,16 +5127,16 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D131" s="13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -5147,16 +5144,16 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D132" s="13">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -5164,7 +5161,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B133" s="10" t="s">
         <v>0</v>
@@ -5181,7 +5178,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B134" s="10" t="s">
         <v>40</v>
@@ -5198,7 +5195,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B135" s="10" t="s">
         <v>0</v>
@@ -5215,7 +5212,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B136" s="10" t="s">
         <v>40</v>
@@ -5232,7 +5229,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B137" s="10" t="s">
         <v>0</v>
@@ -5249,7 +5246,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B138" s="10" t="s">
         <v>40</v>
@@ -5266,7 +5263,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B139" s="10" t="s">
         <v>40</v>
@@ -5283,7 +5280,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B140" s="10" t="s">
         <v>40</v>
@@ -5300,7 +5297,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B141" s="10" t="s">
         <v>0</v>
@@ -5317,7 +5314,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B142" s="10" t="s">
         <v>40</v>
@@ -5334,7 +5331,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B143" s="10" t="s">
         <v>40</v>
@@ -5351,7 +5348,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B144" s="10" t="s">
         <v>40</v>
@@ -5368,7 +5365,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B145" s="10" t="s">
         <v>40</v>
@@ -5385,7 +5382,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B146" s="10" t="s">
         <v>40</v>
@@ -5402,7 +5399,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B147" s="10" t="s">
         <v>40</v>
@@ -5419,7 +5416,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B148" s="10" t="s">
         <v>40</v>
@@ -5436,16 +5433,16 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>95</v>
       </c>
       <c r="D149" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E149" s="1">
         <v>0</v>
@@ -5453,16 +5450,16 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>95</v>
       </c>
       <c r="D150" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E150" s="1">
         <v>0</v>
@@ -5470,7 +5467,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B151" s="10" t="s">
         <v>40</v>
@@ -5487,7 +5484,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B152" s="10" t="s">
         <v>40</v>
@@ -5504,7 +5501,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B153" s="10" t="s">
         <v>0</v>
@@ -5521,7 +5518,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B154" s="10" t="s">
         <v>0</v>
@@ -5538,7 +5535,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B155" s="10" t="s">
         <v>0</v>
@@ -5555,7 +5552,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B156" s="10" t="s">
         <v>40</v>
@@ -5572,7 +5569,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B157" s="10" t="s">
         <v>0</v>
@@ -5589,7 +5586,7 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B158" s="10" t="s">
         <v>0</v>
@@ -5606,7 +5603,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B159" s="10" t="s">
         <v>0</v>
@@ -5623,7 +5620,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B160" s="10" t="s">
         <v>0</v>
@@ -5640,7 +5637,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B161" s="10" t="s">
         <v>40</v>
@@ -5657,7 +5654,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B162" s="10" t="s">
         <v>0</v>
@@ -5674,7 +5671,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B163" s="10" t="s">
         <v>0</v>
@@ -5691,7 +5688,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B164" s="10" t="s">
         <v>0</v>
@@ -5708,7 +5705,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B165" s="10" t="s">
         <v>0</v>
@@ -5725,7 +5722,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B166" s="10" t="s">
         <v>40</v>
@@ -5742,7 +5739,7 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B167" s="10" t="s">
         <v>0</v>
@@ -5759,7 +5756,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B168" s="10" t="s">
         <v>0</v>
@@ -5776,7 +5773,7 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B169" s="10" t="s">
         <v>0</v>
@@ -5793,7 +5790,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B170" s="10" t="s">
         <v>0</v>
@@ -5810,7 +5807,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B171" s="10" t="s">
         <v>0</v>
@@ -5827,7 +5824,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B172" s="10" t="s">
         <v>0</v>
@@ -5844,7 +5841,7 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B173" s="10" t="s">
         <v>0</v>
@@ -5861,7 +5858,7 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B174" s="10" t="s">
         <v>0</v>
@@ -5878,7 +5875,7 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B175" s="10" t="s">
         <v>0</v>
@@ -5895,7 +5892,7 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B176" s="10" t="s">
         <v>0</v>
@@ -5912,16 +5909,16 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>116</v>
       </c>
       <c r="D177" s="13">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E177" s="1">
         <v>0</v>
@@ -5929,16 +5926,16 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>116</v>
       </c>
       <c r="D178" s="13">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E178" s="1">
         <v>0</v>
@@ -5946,7 +5943,7 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B179" s="10" t="s">
         <v>0</v>
@@ -5963,7 +5960,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B180" s="10" t="s">
         <v>40</v>
@@ -5980,7 +5977,7 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B181" s="10" t="s">
         <v>40</v>
@@ -5997,7 +5994,7 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B182" s="10" t="s">
         <v>40</v>
@@ -6014,16 +6011,16 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C183" s="10" t="s">
         <v>120</v>
       </c>
       <c r="D183" s="13">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="E183" s="1">
         <v>0</v>
@@ -6031,16 +6028,16 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C184" s="10" t="s">
         <v>120</v>
       </c>
       <c r="D184" s="13">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="E184" s="1">
         <v>0</v>
@@ -6048,7 +6045,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B185" s="10" t="s">
         <v>0</v>
@@ -6065,13 +6062,13 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B186" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D186" s="13">
         <v>14</v>
@@ -6082,7 +6079,7 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B187" s="10" t="s">
         <v>9</v>
@@ -6099,13 +6096,13 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B188" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D188" s="13">
         <v>600</v>
@@ -6116,7 +6113,7 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B189" s="10" t="s">
         <v>0</v>
@@ -6133,13 +6130,13 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B190" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D190" s="13">
         <v>1000</v>
@@ -6150,7 +6147,7 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B191" s="10" t="s">
         <v>0</v>
@@ -6167,7 +6164,7 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B192" s="10" t="s">
         <v>0</v>
@@ -6184,13 +6181,13 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B193" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D193" s="13">
         <v>3040</v>
@@ -6201,7 +6198,7 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B194" s="10" t="s">
         <v>0</v>
@@ -6218,13 +6215,13 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B195" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D195" s="13">
         <v>1200</v>
@@ -6235,7 +6232,7 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B196" s="10" t="s">
         <v>40</v>
@@ -6252,7 +6249,7 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B197" s="10" t="s">
         <v>0</v>
@@ -6269,7 +6266,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B198" s="10" t="s">
         <v>40</v>
@@ -6286,7 +6283,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B199" s="10" t="s">
         <v>40</v>
@@ -6303,7 +6300,7 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B200" s="10" t="s">
         <v>40</v>
@@ -6320,7 +6317,7 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B201" s="10" t="s">
         <v>40</v>
@@ -6337,7 +6334,7 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B202" s="10" t="s">
         <v>0</v>
@@ -6354,7 +6351,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B203" s="10" t="s">
         <v>0</v>
@@ -6371,7 +6368,7 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B204" s="10" t="s">
         <v>0</v>
@@ -6388,7 +6385,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B205" s="10" t="s">
         <v>0</v>
@@ -6405,7 +6402,7 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B206" s="10" t="s">
         <v>0</v>
@@ -6422,7 +6419,7 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B207" s="10" t="s">
         <v>0</v>
@@ -6439,7 +6436,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B208" s="10" t="s">
         <v>0</v>
@@ -6456,7 +6453,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B209" s="10" t="s">
         <v>0</v>
@@ -6473,7 +6470,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B210" s="10" t="s">
         <v>0</v>
@@ -6490,7 +6487,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B211" s="10" t="s">
         <v>0</v>
@@ -6507,13 +6504,13 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B212" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C212" s="10" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D212" s="13">
         <v>11</v>
@@ -6524,7 +6521,7 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B213" s="10" t="s">
         <v>0</v>
@@ -6541,7 +6538,7 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B214" s="10" t="s">
         <v>0</v>
@@ -6558,7 +6555,7 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B215" s="10" t="s">
         <v>0</v>
@@ -6575,7 +6572,7 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B216" s="10" t="s">
         <v>0</v>
@@ -6592,7 +6589,7 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B217" s="10" t="s">
         <v>0</v>
@@ -6609,7 +6606,7 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B218" s="10" t="s">
         <v>0</v>
@@ -6626,7 +6623,7 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B219" s="10" t="s">
         <v>0</v>
@@ -6643,7 +6640,7 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B220" s="10" t="s">
         <v>0</v>
@@ -6660,13 +6657,13 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B221" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D221" s="13">
         <v>24</v>
@@ -6677,7 +6674,7 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B222" s="10" t="s">
         <v>0</v>
@@ -6694,7 +6691,7 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B223" s="10" t="s">
         <v>0</v>
@@ -6711,13 +6708,13 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B224" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D224" s="13">
         <v>25</v>
@@ -6728,7 +6725,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B225" s="10" t="s">
         <v>0</v>
@@ -6745,7 +6742,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B226" s="10" t="s">
         <v>0</v>
@@ -6762,7 +6759,7 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B227" s="10" t="s">
         <v>0</v>
@@ -6779,7 +6776,7 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B228" s="10" t="s">
         <v>0</v>
@@ -6796,7 +6793,7 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B229" s="10" t="s">
         <v>0</v>
@@ -6813,7 +6810,7 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B230" s="10" t="s">
         <v>40</v>
@@ -6830,7 +6827,7 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B231" s="10" t="s">
         <v>40</v>
@@ -6847,7 +6844,7 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B232" s="10" t="s">
         <v>0</v>
@@ -6864,7 +6861,7 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B233" s="10" t="s">
         <v>0</v>
@@ -6881,7 +6878,7 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B234" s="10" t="s">
         <v>0</v>
@@ -6898,7 +6895,7 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B235" s="10" t="s">
         <v>0</v>
@@ -6915,7 +6912,7 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B236" s="10" t="s">
         <v>9</v>
@@ -6932,13 +6929,13 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B237" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C237" s="10" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D237" s="13">
         <v>2000</v>
@@ -6949,13 +6946,13 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B238" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C238" s="10" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D238" s="13">
         <v>1800</v>
@@ -6966,7 +6963,7 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B239" s="10" t="s">
         <v>40</v>
@@ -6983,7 +6980,7 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B240" s="10" t="s">
         <v>40</v>
@@ -7000,7 +6997,7 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B241" s="10" t="s">
         <v>0</v>
@@ -7017,7 +7014,7 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B242" s="10" t="s">
         <v>40</v>
@@ -7034,13 +7031,13 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B243" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D243" s="13">
         <v>40</v>
@@ -7051,7 +7048,7 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B244" s="10" t="s">
         <v>0</v>
@@ -7068,7 +7065,7 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B245" s="10" t="s">
         <v>40</v>
@@ -7085,7 +7082,7 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B246" s="10" t="s">
         <v>40</v>
@@ -7102,7 +7099,7 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B247" s="10" t="s">
         <v>0</v>
@@ -7119,7 +7116,7 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B248" s="10" t="s">
         <v>0</v>
@@ -7136,7 +7133,7 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B249" s="10" t="s">
         <v>40</v>
@@ -7153,7 +7150,7 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B250" s="10" t="s">
         <v>0</v>
@@ -7170,7 +7167,7 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B251" s="10" t="s">
         <v>9</v>
@@ -7187,16 +7184,16 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C252" s="10" t="s">
         <v>158</v>
       </c>
       <c r="D252" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E252" s="1">
         <v>0</v>
@@ -7204,16 +7201,16 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C253" s="10" t="s">
         <v>158</v>
       </c>
       <c r="D253" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E253" s="1">
         <v>0</v>
@@ -7221,7 +7218,7 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B254" s="10" t="s">
         <v>0</v>
@@ -7238,7 +7235,7 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B255" s="10" t="s">
         <v>0</v>
@@ -7255,7 +7252,7 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B256" s="10" t="s">
         <v>0</v>
@@ -7272,7 +7269,7 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B257" s="10" t="s">
         <v>0</v>
@@ -7289,7 +7286,7 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B258" s="10" t="s">
         <v>0</v>
@@ -7306,7 +7303,7 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B259" s="10" t="s">
         <v>0</v>
@@ -7323,7 +7320,7 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B260" s="10" t="s">
         <v>0</v>
@@ -7340,7 +7337,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B261" s="10" t="s">
         <v>0</v>
@@ -7357,7 +7354,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B262" s="10" t="s">
         <v>0</v>
@@ -7374,7 +7371,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B263" s="10" t="s">
         <v>0</v>
@@ -7391,7 +7388,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B264" s="10" t="s">
         <v>0</v>
@@ -7408,7 +7405,7 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B265" s="10" t="s">
         <v>0</v>
@@ -7425,7 +7422,7 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B266" s="10" t="s">
         <v>9</v>
@@ -7442,7 +7439,7 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B267" s="10" t="s">
         <v>9</v>
@@ -7459,7 +7456,7 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B268" s="10" t="s">
         <v>9</v>
@@ -7476,13 +7473,13 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B269" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C269" s="10" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D269" s="13">
         <v>100</v>
@@ -7493,7 +7490,7 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B270" s="10" t="s">
         <v>0</v>
@@ -7510,7 +7507,7 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B271" s="10" t="s">
         <v>0</v>
@@ -7527,7 +7524,7 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B272" s="10" t="s">
         <v>0</v>
@@ -7544,7 +7541,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B273" s="10" t="s">
         <v>0</v>
@@ -7561,7 +7558,7 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B274" s="10" t="s">
         <v>0</v>
@@ -7578,7 +7575,7 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B275" s="10" t="s">
         <v>0</v>
@@ -7595,7 +7592,7 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B276" s="10" t="s">
         <v>0</v>
@@ -7612,7 +7609,7 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B277" s="10" t="s">
         <v>0</v>
@@ -7629,7 +7626,7 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B278" s="10" t="s">
         <v>0</v>
@@ -7646,7 +7643,7 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B279" s="10" t="s">
         <v>0</v>
@@ -7663,7 +7660,7 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B280" s="10" t="s">
         <v>0</v>
@@ -7680,7 +7677,7 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B281" s="10" t="s">
         <v>0</v>
@@ -7697,7 +7694,7 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B282" s="10" t="s">
         <v>0</v>
@@ -7714,7 +7711,7 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B283" s="10" t="s">
         <v>0</v>
@@ -7731,13 +7728,13 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B284" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C284" s="10" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D284" s="13">
         <v>9</v>
@@ -7748,7 +7745,7 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B285" s="10" t="s">
         <v>0</v>
@@ -7765,13 +7762,13 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B286" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C286" s="10" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D286" s="13">
         <v>5</v>
@@ -7782,7 +7779,7 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B287" s="10" t="s">
         <v>0</v>
@@ -7799,7 +7796,7 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B288" s="10" t="s">
         <v>0</v>
@@ -7816,7 +7813,7 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B289" s="10" t="s">
         <v>0</v>
@@ -7833,7 +7830,7 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B290" s="10" t="s">
         <v>0</v>
@@ -7850,7 +7847,7 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B291" s="10" t="s">
         <v>0</v>
@@ -7867,7 +7864,7 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B292" s="10" t="s">
         <v>40</v>
@@ -7884,7 +7881,7 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B293" s="10" t="s">
         <v>0</v>
@@ -7901,7 +7898,7 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B294" s="10" t="s">
         <v>0</v>
@@ -7918,7 +7915,7 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B295" s="10" t="s">
         <v>40</v>
@@ -7935,7 +7932,7 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B296" s="10" t="s">
         <v>40</v>
@@ -7952,7 +7949,7 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B297" s="10" t="s">
         <v>9</v>
@@ -7969,7 +7966,7 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B298" s="10" t="s">
         <v>9</v>
@@ -7986,7 +7983,7 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B299" s="10" t="s">
         <v>40</v>
@@ -8003,7 +8000,7 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B300" s="10" t="s">
         <v>40</v>
@@ -8020,7 +8017,7 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B301" s="10" t="s">
         <v>9</v>
@@ -8037,13 +8034,13 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B302" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D302" s="13">
         <v>250</v>
@@ -8054,7 +8051,7 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B303" s="10" t="s">
         <v>0</v>
@@ -8071,7 +8068,7 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B304" s="10" t="s">
         <v>40</v>
@@ -8088,7 +8085,7 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B305" s="10" t="s">
         <v>9</v>
@@ -8105,7 +8102,7 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B306" s="10" t="s">
         <v>40</v>
@@ -8122,13 +8119,13 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B307" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C307" s="10" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D307" s="13">
         <v>75</v>
@@ -8139,7 +8136,7 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B308" s="10" t="s">
         <v>40</v>
@@ -8156,16 +8153,16 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B309" s="10" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C309" s="10" t="s">
         <v>190</v>
       </c>
       <c r="D309" s="13">
-        <v>800</v>
+        <v>125</v>
       </c>
       <c r="E309" s="1">
         <v>0</v>
@@ -8173,16 +8170,16 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C310" s="10" t="s">
         <v>190</v>
       </c>
       <c r="D310" s="13">
-        <v>175</v>
+        <v>800</v>
       </c>
       <c r="E310" s="1">
         <v>0</v>
@@ -8190,16 +8187,16 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B311" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C311" s="10" t="s">
         <v>190</v>
       </c>
       <c r="D311" s="13">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="E311" s="1">
         <v>0</v>
@@ -8207,13 +8204,13 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B312" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C312" s="10" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D312" s="13">
         <v>20</v>
@@ -8224,7 +8221,7 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B313" s="10" t="s">
         <v>9</v>
@@ -8241,13 +8238,13 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B314" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C314" s="10" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D314" s="13">
         <v>450</v>
@@ -8258,7 +8255,7 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B315" s="10" t="s">
         <v>40</v>
@@ -8275,7 +8272,7 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B316" s="10" t="s">
         <v>0</v>
@@ -8292,7 +8289,7 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B317" s="10" t="s">
         <v>9</v>
@@ -8309,7 +8306,7 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B318" s="10" t="s">
         <v>40</v>
@@ -8326,7 +8323,7 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B319" s="10" t="s">
         <v>0</v>
@@ -8343,7 +8340,7 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B320" s="10" t="s">
         <v>40</v>
@@ -8360,7 +8357,7 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B321" s="10" t="s">
         <v>0</v>
@@ -8377,7 +8374,7 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B322" s="10" t="s">
         <v>40</v>
@@ -8394,7 +8391,7 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B323" s="10" t="s">
         <v>40</v>
@@ -8411,7 +8408,7 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B324" s="10" t="s">
         <v>9</v>
@@ -8428,7 +8425,7 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B325" s="10" t="s">
         <v>9</v>
@@ -8445,7 +8442,7 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B326" s="10" t="s">
         <v>9</v>
@@ -8462,13 +8459,13 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="10" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B327" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C327" s="10" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D327" s="13">
         <v>1</v>
@@ -8479,7 +8476,7 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B328" s="10" t="s">
         <v>9</v>
@@ -8496,7 +8493,7 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B329" s="10" t="s">
         <v>9</v>
@@ -8513,7 +8510,7 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B330" s="10" t="s">
         <v>9</v>
@@ -8530,7 +8527,7 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B331" s="10" t="s">
         <v>40</v>
@@ -8547,7 +8544,7 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B332" s="10" t="s">
         <v>40</v>
@@ -8564,7 +8561,7 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B333" s="10" t="s">
         <v>40</v>
@@ -8581,7 +8578,7 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B334" s="10" t="s">
         <v>0</v>
@@ -8598,7 +8595,7 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B335" s="10" t="s">
         <v>40</v>
@@ -8615,7 +8612,7 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B336" s="10" t="s">
         <v>40</v>
@@ -8632,7 +8629,7 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B337" s="10" t="s">
         <v>40</v>
@@ -8649,7 +8646,7 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B338" s="10" t="s">
         <v>40</v>
@@ -8666,16 +8663,16 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B339" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C339" s="10" t="s">
         <v>199</v>
       </c>
       <c r="D339" s="13">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E339" s="1">
         <v>0</v>
@@ -8683,16 +8680,16 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B340" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C340" s="10" t="s">
         <v>199</v>
       </c>
       <c r="D340" s="13">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="E340" s="1">
         <v>0</v>
@@ -8700,7 +8697,7 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B341" s="10" t="s">
         <v>0</v>
@@ -8717,7 +8714,7 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B342" s="10" t="s">
         <v>40</v>
@@ -8734,7 +8731,7 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B343" s="10" t="s">
         <v>0</v>
@@ -8751,7 +8748,7 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B344" s="10" t="s">
         <v>40</v>
@@ -8768,7 +8765,7 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B345" s="10" t="s">
         <v>0</v>
@@ -8785,7 +8782,7 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B346" s="10" t="s">
         <v>40</v>
@@ -8802,7 +8799,7 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B347" s="10" t="s">
         <v>40</v>
@@ -8819,13 +8816,13 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B348" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C348" s="10" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D348" s="13">
         <v>90</v>
@@ -8836,7 +8833,7 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B349" s="10" t="s">
         <v>40</v>
@@ -8853,13 +8850,13 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="B350" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C350" s="10" t="s">
         <v>745</v>
-      </c>
-      <c r="B350" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C350" s="10" t="s">
-        <v>746</v>
       </c>
       <c r="D350" s="13">
         <v>50</v>
@@ -8870,7 +8867,7 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B351" s="10" t="s">
         <v>40</v>
@@ -8887,7 +8884,7 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B352" s="10" t="s">
         <v>40</v>
@@ -8904,7 +8901,7 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B353" s="10" t="s">
         <v>40</v>
@@ -8921,7 +8918,7 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B354" s="10" t="s">
         <v>0</v>
@@ -8938,7 +8935,7 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B355" s="10" t="s">
         <v>0</v>
@@ -8955,7 +8952,7 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B356" s="10" t="s">
         <v>0</v>
@@ -8972,7 +8969,7 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B357" s="10" t="s">
         <v>0</v>
@@ -8989,7 +8986,7 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B358" s="10" t="s">
         <v>0</v>
@@ -9006,7 +9003,7 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B359" s="10" t="s">
         <v>9</v>
@@ -9023,7 +9020,7 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B360" s="10" t="s">
         <v>0</v>
@@ -9040,7 +9037,7 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="10" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B361" s="10" t="s">
         <v>0</v>
@@ -9057,7 +9054,7 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="10" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B362" s="10" t="s">
         <v>0</v>
@@ -9074,7 +9071,7 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B363" s="10" t="s">
         <v>0</v>
@@ -9091,7 +9088,7 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B364" s="10" t="s">
         <v>0</v>
@@ -9108,13 +9105,13 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B365" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C365" s="10" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D365" s="13">
         <v>24</v>
@@ -9125,7 +9122,7 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B366" s="10" t="s">
         <v>0</v>
@@ -9142,13 +9139,13 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B367" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C367" s="10" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D367" s="13">
         <v>25</v>
@@ -9159,7 +9156,7 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B368" s="10" t="s">
         <v>0</v>
@@ -9176,7 +9173,7 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B369" s="10" t="s">
         <v>0</v>
@@ -9193,7 +9190,7 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B370" s="10" t="s">
         <v>9</v>
@@ -9210,7 +9207,7 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B371" s="10" t="s">
         <v>0</v>
@@ -9227,7 +9224,7 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B372" s="10" t="s">
         <v>0</v>
@@ -9244,7 +9241,7 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B373" s="10" t="s">
         <v>0</v>
@@ -9261,7 +9258,7 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B374" s="10" t="s">
         <v>0</v>
@@ -9278,7 +9275,7 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B375" s="10" t="s">
         <v>0</v>
@@ -9295,7 +9292,7 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B376" s="10" t="s">
         <v>0</v>
@@ -9312,7 +9309,7 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="10" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B377" s="10" t="s">
         <v>40</v>
@@ -9329,7 +9326,7 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="10" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B378" s="10" t="s">
         <v>40</v>
@@ -9346,7 +9343,7 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="10" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B379" s="10" t="s">
         <v>40</v>
@@ -9363,7 +9360,7 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="10" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B380" s="10" t="s">
         <v>40</v>
@@ -9380,7 +9377,7 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="10" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B381" s="10" t="s">
         <v>40</v>
@@ -9397,7 +9394,7 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="10" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B382" s="10" t="s">
         <v>0</v>
@@ -9414,7 +9411,7 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B383" s="10" t="s">
         <v>0</v>
@@ -9431,7 +9428,7 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B384" s="10" t="s">
         <v>0</v>
@@ -9448,7 +9445,7 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="10" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B385" s="10" t="s">
         <v>0</v>
@@ -9465,7 +9462,7 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B386" s="10" t="s">
         <v>40</v>
@@ -9482,7 +9479,7 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="10" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B387" s="10" t="s">
         <v>0</v>
@@ -9499,7 +9496,7 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="10" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B388" s="10" t="s">
         <v>0</v>
@@ -9516,16 +9513,16 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B389" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C389" s="10" t="s">
         <v>226</v>
       </c>
       <c r="D389" s="13">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="E389" s="1">
         <v>0</v>
@@ -9533,7 +9530,7 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B390" s="10" t="s">
         <v>9</v>
@@ -9550,16 +9547,16 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B391" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C391" s="10" t="s">
         <v>226</v>
       </c>
       <c r="D391" s="13">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="E391" s="1">
         <v>0</v>
@@ -9567,7 +9564,7 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B392" s="10" t="s">
         <v>40</v>
@@ -9584,7 +9581,7 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B393" s="10" t="s">
         <v>0</v>
@@ -9601,7 +9598,7 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B394" s="10" t="s">
         <v>40</v>
@@ -9618,7 +9615,7 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B395" s="10" t="s">
         <v>0</v>
@@ -9635,7 +9632,7 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B396" s="10" t="s">
         <v>0</v>
@@ -9652,7 +9649,7 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B397" s="10" t="s">
         <v>0</v>
@@ -9669,7 +9666,7 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="10" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B398" s="10" t="s">
         <v>0</v>
@@ -9686,7 +9683,7 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="10" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B399" s="10" t="s">
         <v>0</v>
@@ -9703,7 +9700,7 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="10" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B400" s="10" t="s">
         <v>0</v>
@@ -9720,7 +9717,7 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="10" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B401" s="10" t="s">
         <v>0</v>
@@ -9737,7 +9734,7 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="10" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B402" s="10" t="s">
         <v>0</v>
@@ -9754,7 +9751,7 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="10" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B403" s="10" t="s">
         <v>0</v>
@@ -9771,7 +9768,7 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B404" s="10" t="s">
         <v>9</v>
@@ -9788,7 +9785,7 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B405" s="10" t="s">
         <v>0</v>
@@ -9805,7 +9802,7 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B406" s="10" t="s">
         <v>9</v>
@@ -9822,7 +9819,7 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B407" s="10" t="s">
         <v>9</v>
@@ -9839,7 +9836,7 @@
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B408" s="10" t="s">
         <v>9</v>
@@ -9856,7 +9853,7 @@
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B409" s="10" t="s">
         <v>0</v>
@@ -9873,7 +9870,7 @@
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B410" s="10" t="s">
         <v>9</v>
@@ -9890,7 +9887,7 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="10" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B411" s="10" t="s">
         <v>40</v>
@@ -9907,7 +9904,7 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B412" s="10" t="s">
         <v>0</v>
@@ -9924,7 +9921,7 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="10" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B413" s="10" t="s">
         <v>40</v>
@@ -9941,7 +9938,7 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B414" s="10" t="s">
         <v>40</v>
@@ -9958,13 +9955,13 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B415" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D415" s="13">
         <v>290</v>
@@ -9975,7 +9972,7 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="10" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B416" s="10" t="s">
         <v>40</v>
@@ -9992,7 +9989,7 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B417" s="10" t="s">
         <v>0</v>
@@ -10009,7 +10006,7 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="10" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B418" s="10" t="s">
         <v>0</v>
@@ -10026,7 +10023,7 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="10" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B419" s="10" t="s">
         <v>9</v>
@@ -10043,7 +10040,7 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B420" s="10" t="s">
         <v>0</v>
@@ -10060,16 +10057,16 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="10" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B421" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C421" s="10" t="s">
         <v>243</v>
       </c>
       <c r="D421" s="13">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E421" s="1">
         <v>0</v>
@@ -10077,16 +10074,16 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" s="10" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B422" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C422" s="10" t="s">
         <v>243</v>
       </c>
       <c r="D422" s="13">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="E422" s="1">
         <v>0</v>
@@ -10094,7 +10091,7 @@
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" s="10" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B423" s="10" t="s">
         <v>40</v>
@@ -10111,7 +10108,7 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B424" s="10" t="s">
         <v>0</v>
@@ -10128,7 +10125,7 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="10" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B425" s="10" t="s">
         <v>0</v>
@@ -10145,7 +10142,7 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="10" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B426" s="10" t="s">
         <v>0</v>
@@ -10162,7 +10159,7 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="10" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B427" s="10" t="s">
         <v>0</v>
@@ -10179,7 +10176,7 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="10" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B428" s="10" t="s">
         <v>0</v>
@@ -10196,7 +10193,7 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="10" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B429" s="10" t="s">
         <v>0</v>
@@ -10213,7 +10210,7 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B430" s="10" t="s">
         <v>9</v>
@@ -10230,7 +10227,7 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B431" s="10" t="s">
         <v>9</v>
@@ -10247,7 +10244,7 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B432" s="10" t="s">
         <v>9</v>
@@ -10264,7 +10261,7 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="10" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B433" s="10" t="s">
         <v>0</v>
@@ -10281,7 +10278,7 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B434" s="10" t="s">
         <v>0</v>
@@ -10298,7 +10295,7 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B435" s="10" t="s">
         <v>40</v>
@@ -10315,13 +10312,13 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B436" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C436" s="10" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D436" s="13">
         <v>140</v>
@@ -10332,7 +10329,7 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B437" s="10" t="s">
         <v>0</v>
@@ -10349,16 +10346,16 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B438" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C438" s="10" t="s">
         <v>252</v>
       </c>
       <c r="D438" s="13">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E438" s="1">
         <v>0</v>
@@ -10366,16 +10363,16 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B439" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C439" s="10" t="s">
         <v>252</v>
       </c>
       <c r="D439" s="13">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E439" s="1">
         <v>0</v>
@@ -10383,13 +10380,13 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B440" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C440" s="10" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D440" s="13">
         <v>60</v>
@@ -10400,7 +10397,7 @@
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B441" s="10" t="s">
         <v>40</v>
@@ -10417,7 +10414,7 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B442" s="10" t="s">
         <v>40</v>
@@ -10434,7 +10431,7 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B443" s="10" t="s">
         <v>40</v>
@@ -10451,7 +10448,7 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B444" s="10" t="s">
         <v>9</v>
@@ -10468,7 +10465,7 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B445" s="10" t="s">
         <v>0</v>
@@ -10485,7 +10482,7 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B446" s="10" t="s">
         <v>0</v>
@@ -10502,7 +10499,7 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B447" s="10" t="s">
         <v>0</v>
@@ -10519,7 +10516,7 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B448" s="10" t="s">
         <v>0</v>
@@ -10536,7 +10533,7 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B449" s="10" t="s">
         <v>0</v>
@@ -10553,7 +10550,7 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B450" s="10" t="s">
         <v>0</v>
@@ -10570,7 +10567,7 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B451" s="10" t="s">
         <v>0</v>
@@ -10587,7 +10584,7 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B452" s="10" t="s">
         <v>0</v>
@@ -10604,7 +10601,7 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B453" s="10" t="s">
         <v>0</v>
@@ -10621,7 +10618,7 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B454" s="10" t="s">
         <v>0</v>
@@ -10638,13 +10635,13 @@
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B455" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C455" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D455" s="13">
         <v>4</v>
@@ -10655,7 +10652,7 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B456" s="10" t="s">
         <v>0</v>
@@ -10672,7 +10669,7 @@
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="10" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B457" s="10" t="s">
         <v>0</v>
@@ -10689,7 +10686,7 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B458" s="10" t="s">
         <v>0</v>
@@ -10706,7 +10703,7 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B459" s="10" t="s">
         <v>40</v>
@@ -10723,7 +10720,7 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B460" s="10" t="s">
         <v>40</v>
@@ -10740,7 +10737,7 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B461" s="10" t="s">
         <v>40</v>
@@ -10757,7 +10754,7 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B462" s="10" t="s">
         <v>40</v>
@@ -10774,7 +10771,7 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="10" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B463" s="10" t="s">
         <v>40</v>
@@ -10791,7 +10788,7 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="10" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B464" s="10" t="s">
         <v>0</v>
@@ -10808,7 +10805,7 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B465" s="10" t="s">
         <v>0</v>
@@ -10825,7 +10822,7 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B466" s="10" t="s">
         <v>0</v>
@@ -10842,7 +10839,7 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B467" s="10" t="s">
         <v>0</v>
@@ -10859,7 +10856,7 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B468" s="10" t="s">
         <v>0</v>
@@ -10876,7 +10873,7 @@
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B469" s="10" t="s">
         <v>0</v>
@@ -10893,7 +10890,7 @@
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B470" s="10" t="s">
         <v>40</v>
@@ -10910,7 +10907,7 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B471" s="10" t="s">
         <v>40</v>
@@ -10927,7 +10924,7 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B472" s="10" t="s">
         <v>40</v>
@@ -10944,7 +10941,7 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B473" s="10" t="s">
         <v>40</v>
@@ -10961,7 +10958,7 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B474" s="10" t="s">
         <v>40</v>
@@ -10978,7 +10975,7 @@
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B475" s="10" t="s">
         <v>40</v>
@@ -10995,7 +10992,7 @@
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B476" s="10" t="s">
         <v>40</v>
@@ -11012,7 +11009,7 @@
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B477" s="10" t="s">
         <v>0</v>
@@ -11029,7 +11026,7 @@
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" s="10" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B478" s="10" t="s">
         <v>0</v>
@@ -11046,7 +11043,7 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B479" s="10" t="s">
         <v>40</v>
@@ -11063,7 +11060,7 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B480" s="10" t="s">
         <v>0</v>
@@ -11080,7 +11077,7 @@
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B481" s="10" t="s">
         <v>9</v>
@@ -11097,7 +11094,7 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B482" s="10" t="s">
         <v>0</v>
@@ -11114,7 +11111,7 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B483" s="10" t="s">
         <v>0</v>
@@ -11131,7 +11128,7 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B484" s="10" t="s">
         <v>0</v>
@@ -11148,7 +11145,7 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B485" s="10" t="s">
         <v>0</v>
@@ -11165,7 +11162,7 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B486" s="10" t="s">
         <v>0</v>
@@ -11182,7 +11179,7 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B487" s="10" t="s">
         <v>0</v>
@@ -11199,7 +11196,7 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B488" s="10" t="s">
         <v>0</v>
@@ -11216,7 +11213,7 @@
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B489" s="10" t="s">
         <v>0</v>
@@ -11233,7 +11230,7 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B490" s="10" t="s">
         <v>0</v>
@@ -11250,7 +11247,7 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B491" s="10" t="s">
         <v>0</v>
@@ -11267,7 +11264,7 @@
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B492" s="10" t="s">
         <v>0</v>
@@ -11284,7 +11281,7 @@
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B493" s="10" t="s">
         <v>0</v>
@@ -11301,7 +11298,7 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B494" s="10" t="s">
         <v>0</v>
@@ -11318,7 +11315,7 @@
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B495" s="10" t="s">
         <v>0</v>
@@ -11335,7 +11332,7 @@
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B496" s="10" t="s">
         <v>0</v>
@@ -11352,7 +11349,7 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B497" s="10" t="s">
         <v>0</v>
@@ -11369,7 +11366,7 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B498" s="10" t="s">
         <v>0</v>
@@ -11386,7 +11383,7 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B499" s="10" t="s">
         <v>0</v>
@@ -11403,7 +11400,7 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B500" s="10" t="s">
         <v>0</v>
@@ -11420,13 +11417,13 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B501" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C501" s="10" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D501" s="13">
         <v>3</v>
@@ -11437,13 +11434,13 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B502" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C502" s="10" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D502" s="13">
         <v>1</v>
@@ -11454,7 +11451,7 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B503" s="10" t="s">
         <v>541</v>
@@ -11471,7 +11468,7 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B504" s="10" t="s">
         <v>541</v>
@@ -11488,13 +11485,13 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B505" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C505" s="10" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D505" s="13">
         <v>27</v>
@@ -11505,7 +11502,7 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B506" s="10" t="s">
         <v>541</v>
@@ -11522,7 +11519,7 @@
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B507" s="10" t="s">
         <v>541</v>
@@ -11539,13 +11536,13 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B508" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C508" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D508" s="13">
         <v>3</v>
@@ -11556,13 +11553,13 @@
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B509" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C509" s="10" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D509" s="13">
         <v>2</v>
@@ -11573,16 +11570,16 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>684</v>
+        <v>583</v>
       </c>
       <c r="B510" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C510" s="10" t="s">
-        <v>546</v>
+        <v>738</v>
       </c>
       <c r="D510" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E510" s="1">
         <v>0</v>
@@ -11590,16 +11587,16 @@
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B511" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C511" s="10" t="s">
-        <v>739</v>
+        <v>546</v>
       </c>
       <c r="D511" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E511" s="1">
         <v>0</v>
@@ -11607,13 +11604,13 @@
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B512" s="10" t="s">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="C512" s="10" t="s">
-        <v>547</v>
+        <v>506</v>
       </c>
       <c r="D512" s="13">
         <v>1</v>
@@ -11624,13 +11621,13 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B513" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C513" s="10" t="s">
-        <v>506</v>
+        <v>301</v>
       </c>
       <c r="D513" s="13">
         <v>1</v>
@@ -11641,16 +11638,16 @@
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>584</v>
+        <v>684</v>
       </c>
       <c r="B514" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C514" s="10" t="s">
-        <v>301</v>
+        <v>507</v>
       </c>
       <c r="D514" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E514" s="1">
         <v>0</v>
@@ -11664,10 +11661,10 @@
         <v>0</v>
       </c>
       <c r="C515" s="10" t="s">
-        <v>507</v>
+        <v>302</v>
       </c>
       <c r="D515" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E515" s="1">
         <v>0</v>
@@ -11675,16 +11672,16 @@
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B516" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C516" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D516" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E516" s="1">
         <v>0</v>
@@ -11692,16 +11689,16 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B517" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C517" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D517" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E517" s="1">
         <v>0</v>
@@ -11709,13 +11706,13 @@
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B518" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C518" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D518" s="13">
         <v>1</v>
@@ -11726,13 +11723,13 @@
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B519" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C519" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D519" s="13">
         <v>1</v>
@@ -11743,13 +11740,13 @@
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B520" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C520" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D520" s="13">
         <v>1</v>
@@ -11760,16 +11757,16 @@
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B521" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C521" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D521" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E521" s="1">
         <v>0</v>
@@ -11777,13 +11774,13 @@
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
-        <v>686</v>
+        <v>583</v>
       </c>
       <c r="B522" s="10" t="s">
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="C522" s="10" t="s">
-        <v>308</v>
+        <v>547</v>
       </c>
       <c r="D522" s="13">
         <v>2</v>
@@ -11794,16 +11791,16 @@
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B523" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C523" s="10" t="s">
-        <v>548</v>
+        <v>729</v>
       </c>
       <c r="D523" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E523" s="1">
         <v>0</v>
@@ -11811,16 +11808,16 @@
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B524" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C524" s="10" t="s">
-        <v>730</v>
+        <v>548</v>
       </c>
       <c r="D524" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E524" s="1">
         <v>0</v>
@@ -11828,16 +11825,16 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B525" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C525" s="10" t="s">
-        <v>549</v>
+        <v>723</v>
       </c>
       <c r="D525" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E525" s="1">
         <v>0</v>
@@ -11845,16 +11842,16 @@
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B526" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C526" s="10" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="D526" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E526" s="1">
         <v>0</v>
@@ -11862,16 +11859,16 @@
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" s="10" t="s">
-        <v>584</v>
+        <v>775</v>
       </c>
       <c r="B527" s="10" t="s">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="C527" s="10" t="s">
-        <v>737</v>
+        <v>776</v>
       </c>
       <c r="D527" s="13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E527" s="1">
         <v>0</v>
@@ -11879,16 +11876,16 @@
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" s="10" t="s">
-        <v>776</v>
+        <v>585</v>
       </c>
       <c r="B528" s="10" t="s">
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="C528" s="10" t="s">
-        <v>777</v>
+        <v>727</v>
       </c>
       <c r="D528" s="13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E528" s="1">
         <v>0</v>
@@ -11896,13 +11893,13 @@
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B529" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C529" s="10" t="s">
-        <v>728</v>
+        <v>549</v>
       </c>
       <c r="D529" s="13">
         <v>1</v>
@@ -11913,13 +11910,13 @@
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" s="10" t="s">
-        <v>586</v>
+        <v>639</v>
       </c>
       <c r="B530" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C530" s="10" t="s">
-        <v>550</v>
+        <v>767</v>
       </c>
       <c r="D530" s="13">
         <v>1</v>
@@ -11930,7 +11927,7 @@
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B531" s="10" t="s">
         <v>541</v>
@@ -11939,7 +11936,7 @@
         <v>768</v>
       </c>
       <c r="D531" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E531" s="1">
         <v>0</v>
@@ -11947,16 +11944,16 @@
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
-        <v>640</v>
+        <v>683</v>
       </c>
       <c r="B532" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C532" s="10" t="s">
-        <v>769</v>
+        <v>550</v>
       </c>
       <c r="D532" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E532" s="1">
         <v>0</v>
@@ -11964,7 +11961,7 @@
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" s="10" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B533" s="10" t="s">
         <v>541</v>
@@ -11981,7 +11978,7 @@
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" s="10" t="s">
-        <v>684</v>
+        <v>585</v>
       </c>
       <c r="B534" s="10" t="s">
         <v>541</v>
@@ -11998,7 +11995,7 @@
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B535" s="10" t="s">
         <v>541</v>
@@ -12015,7 +12012,7 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B536" s="10" t="s">
         <v>541</v>
@@ -12032,7 +12029,7 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B537" s="10" t="s">
         <v>541</v>
@@ -12041,7 +12038,7 @@
         <v>555</v>
       </c>
       <c r="D537" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E537" s="1">
         <v>0</v>
@@ -12049,7 +12046,7 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B538" s="10" t="s">
         <v>541</v>
@@ -12058,7 +12055,7 @@
         <v>556</v>
       </c>
       <c r="D538" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E538" s="1">
         <v>0</v>
@@ -12066,16 +12063,16 @@
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" s="10" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B539" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C539" s="10" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="D539" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E539" s="1">
         <v>0</v>
@@ -12083,13 +12080,13 @@
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B540" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C540" s="10" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="D540" s="13">
         <v>2</v>
@@ -12100,16 +12097,16 @@
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B541" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C541" s="10" t="s">
-        <v>558</v>
+        <v>573</v>
       </c>
       <c r="D541" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E541" s="1">
         <v>0</v>
@@ -12117,16 +12114,16 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B542" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C542" s="10" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="D542" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E542" s="1">
         <v>0</v>
@@ -12134,7 +12131,7 @@
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" s="10" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B543" s="10" t="s">
         <v>541</v>
@@ -12143,7 +12140,7 @@
         <v>559</v>
       </c>
       <c r="D543" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E543" s="1">
         <v>0</v>
@@ -12151,7 +12148,7 @@
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B544" s="10" t="s">
         <v>541</v>
@@ -12168,13 +12165,13 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="10" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B545" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C545" s="10" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="D545" s="13">
         <v>1</v>
@@ -12185,7 +12182,7 @@
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B546" s="10" t="s">
         <v>541</v>
@@ -12202,13 +12199,13 @@
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B547" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C547" s="10" t="s">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="D547" s="13">
         <v>1</v>
@@ -12219,7 +12216,7 @@
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B548" s="10" t="s">
         <v>541</v>
@@ -12228,7 +12225,7 @@
         <v>562</v>
       </c>
       <c r="D548" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E548" s="1">
         <v>0</v>
@@ -12236,7 +12233,7 @@
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B549" s="10" t="s">
         <v>541</v>
@@ -12245,7 +12242,7 @@
         <v>563</v>
       </c>
       <c r="D549" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E549" s="1">
         <v>0</v>
@@ -12253,7 +12250,7 @@
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B550" s="10" t="s">
         <v>541</v>
@@ -12270,7 +12267,7 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B551" s="10" t="s">
         <v>541</v>
@@ -12279,7 +12276,7 @@
         <v>565</v>
       </c>
       <c r="D551" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E551" s="1">
         <v>0</v>
@@ -12287,7 +12284,7 @@
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B552" s="10" t="s">
         <v>541</v>
@@ -12296,7 +12293,7 @@
         <v>566</v>
       </c>
       <c r="D552" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E552" s="1">
         <v>0</v>
@@ -12304,7 +12301,7 @@
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B553" s="10" t="s">
         <v>541</v>
@@ -12313,7 +12310,7 @@
         <v>567</v>
       </c>
       <c r="D553" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E553" s="1">
         <v>0</v>
@@ -12321,7 +12318,7 @@
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" s="10" t="s">
-        <v>584</v>
+        <v>639</v>
       </c>
       <c r="B554" s="10" t="s">
         <v>541</v>
@@ -12330,7 +12327,7 @@
         <v>568</v>
       </c>
       <c r="D554" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E554" s="1">
         <v>0</v>
@@ -12338,16 +12335,16 @@
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" s="10" t="s">
-        <v>640</v>
+        <v>685</v>
       </c>
       <c r="B555" s="10" t="s">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="C555" s="10" t="s">
-        <v>569</v>
+        <v>309</v>
       </c>
       <c r="D555" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E555" s="1">
         <v>0</v>
@@ -12355,13 +12352,13 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" s="10" t="s">
-        <v>686</v>
+        <v>583</v>
       </c>
       <c r="B556" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C556" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D556" s="13">
         <v>1</v>
@@ -12372,13 +12369,13 @@
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B557" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C557" s="10" t="s">
-        <v>310</v>
+        <v>508</v>
       </c>
       <c r="D557" s="13">
         <v>1</v>
@@ -12389,16 +12386,16 @@
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B558" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C558" s="10" t="s">
-        <v>508</v>
+        <v>311</v>
       </c>
       <c r="D558" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E558" s="1">
         <v>0</v>
@@ -12406,7 +12403,7 @@
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B559" s="10" t="s">
         <v>541</v>
@@ -12423,13 +12420,13 @@
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" s="10" t="s">
-        <v>584</v>
+        <v>639</v>
       </c>
       <c r="B560" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C560" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D560" s="13">
         <v>2</v>
@@ -12440,16 +12437,16 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B561" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C561" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D561" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E561" s="1">
         <v>0</v>
@@ -12457,13 +12454,13 @@
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B562" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C562" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D562" s="13">
         <v>1</v>
@@ -12474,13 +12471,13 @@
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" s="10" t="s">
-        <v>640</v>
+        <v>585</v>
       </c>
       <c r="B563" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C563" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D563" s="13">
         <v>1</v>
@@ -12491,13 +12488,13 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B564" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C564" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D564" s="13">
         <v>1</v>
@@ -12508,16 +12505,16 @@
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" s="10" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B565" s="10" t="s">
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="C565" s="10" t="s">
-        <v>316</v>
+        <v>711</v>
       </c>
       <c r="D565" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E565" s="1">
         <v>0</v>
@@ -12525,7 +12522,7 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B566" s="10" t="s">
         <v>541</v>
@@ -12534,7 +12531,7 @@
         <v>712</v>
       </c>
       <c r="D566" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E566" s="1">
         <v>0</v>
@@ -12542,7 +12539,7 @@
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B567" s="10" t="s">
         <v>541</v>
@@ -12551,7 +12548,7 @@
         <v>713</v>
       </c>
       <c r="D567" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E567" s="1">
         <v>0</v>
@@ -12559,16 +12556,16 @@
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B568" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C568" s="10" t="s">
-        <v>714</v>
+        <v>569</v>
       </c>
       <c r="D568" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E568" s="1">
         <v>0</v>
@@ -12576,13 +12573,13 @@
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B569" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C569" s="10" t="s">
-        <v>570</v>
+        <v>714</v>
       </c>
       <c r="D569" s="13">
         <v>1</v>
@@ -12593,7 +12590,7 @@
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B570" s="10" t="s">
         <v>541</v>
@@ -12602,7 +12599,7 @@
         <v>715</v>
       </c>
       <c r="D570" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E570" s="1">
         <v>0</v>
@@ -12610,7 +12607,7 @@
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B571" s="10" t="s">
         <v>541</v>
@@ -12619,7 +12616,7 @@
         <v>716</v>
       </c>
       <c r="D571" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E571" s="1">
         <v>0</v>
@@ -12627,7 +12624,7 @@
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B572" s="10" t="s">
         <v>541</v>
@@ -12644,7 +12641,7 @@
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B573" s="10" t="s">
         <v>541</v>
@@ -12653,7 +12650,7 @@
         <v>718</v>
       </c>
       <c r="D573" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E573" s="1">
         <v>0</v>
@@ -12661,7 +12658,7 @@
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B574" s="10" t="s">
         <v>541</v>
@@ -12678,7 +12675,7 @@
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B575" s="10" t="s">
         <v>541</v>
@@ -12687,7 +12684,7 @@
         <v>720</v>
       </c>
       <c r="D575" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E575" s="1">
         <v>0</v>
@@ -12695,13 +12692,13 @@
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B576" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C576" s="10" t="s">
-        <v>721</v>
+        <v>570</v>
       </c>
       <c r="D576" s="13">
         <v>2</v>
@@ -12712,16 +12709,16 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B577" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C577" s="10" t="s">
-        <v>571</v>
+        <v>707</v>
       </c>
       <c r="D577" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E577" s="1">
         <v>0</v>
@@ -12729,13 +12726,13 @@
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578" s="10" t="s">
-        <v>584</v>
+        <v>639</v>
       </c>
       <c r="B578" s="10" t="s">
         <v>541</v>
       </c>
       <c r="C578" s="10" t="s">
-        <v>708</v>
+        <v>571</v>
       </c>
       <c r="D578" s="13">
         <v>1</v>
@@ -12746,16 +12743,16 @@
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" s="10" t="s">
-        <v>640</v>
+        <v>585</v>
       </c>
       <c r="B579" s="10" t="s">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="C579" s="10" t="s">
-        <v>572</v>
+        <v>317</v>
       </c>
       <c r="D579" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E579" s="1">
         <v>0</v>
@@ -12763,16 +12760,16 @@
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" s="10" t="s">
-        <v>586</v>
+        <v>639</v>
       </c>
       <c r="B580" s="10" t="s">
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="C580" s="10" t="s">
-        <v>317</v>
+        <v>576</v>
       </c>
       <c r="D580" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E580" s="1">
         <v>0</v>
@@ -12780,16 +12777,16 @@
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581" s="10" t="s">
-        <v>640</v>
+        <v>662</v>
       </c>
       <c r="B581" s="10" t="s">
-        <v>541</v>
+        <v>40</v>
       </c>
       <c r="C581" s="10" t="s">
-        <v>577</v>
+        <v>410</v>
       </c>
       <c r="D581" s="13">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E581" s="1">
         <v>0</v>
@@ -12797,16 +12794,16 @@
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" s="10" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B582" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C582" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D582" s="13">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E582" s="1">
         <v>0</v>
@@ -12814,16 +12811,16 @@
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A583" s="10" t="s">
-        <v>663</v>
+        <v>577</v>
       </c>
       <c r="B583" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C583" s="10" t="s">
-        <v>411</v>
+        <v>318</v>
       </c>
       <c r="D583" s="13">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E583" s="1">
         <v>0</v>
@@ -12831,13 +12828,13 @@
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" s="10" t="s">
-        <v>578</v>
+        <v>686</v>
       </c>
       <c r="B584" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C584" s="10" t="s">
-        <v>318</v>
+        <v>435</v>
       </c>
       <c r="D584" s="13">
         <v>1</v>
@@ -12848,16 +12845,16 @@
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B585" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C585" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D585" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E585" s="1">
         <v>0</v>
@@ -12865,16 +12862,16 @@
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A586" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B586" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C586" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D586" s="13">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E586" s="1">
         <v>0</v>
@@ -12882,16 +12879,16 @@
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B587" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C587" s="10" t="s">
-        <v>437</v>
+        <v>538</v>
       </c>
       <c r="D587" s="13">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E587" s="1">
         <v>0</v>
@@ -12899,16 +12896,16 @@
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B588" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C588" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D588" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E588" s="1">
         <v>0</v>
@@ -12916,16 +12913,16 @@
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B589" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C589" s="10" t="s">
-        <v>537</v>
+        <v>438</v>
       </c>
       <c r="D589" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E589" s="1">
         <v>0</v>
@@ -12933,16 +12930,16 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B590" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C590" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D590" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E590" s="1">
         <v>0</v>
@@ -12953,13 +12950,13 @@
         <v>687</v>
       </c>
       <c r="B591" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C591" s="10" t="s">
-        <v>439</v>
+        <v>319</v>
       </c>
       <c r="D591" s="13">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="E591" s="1">
         <v>0</v>
@@ -12967,16 +12964,16 @@
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A592" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B592" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C592" s="10" t="s">
-        <v>319</v>
+        <v>759</v>
       </c>
       <c r="D592" s="13">
-        <v>37</v>
+        <v>800</v>
       </c>
       <c r="E592" s="1">
         <v>0</v>
@@ -12984,7 +12981,7 @@
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A593" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B593" s="10" t="s">
         <v>40</v>
@@ -12993,7 +12990,7 @@
         <v>760</v>
       </c>
       <c r="D593" s="13">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="E593" s="1">
         <v>0</v>
@@ -13001,7 +12998,7 @@
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A594" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B594" s="10" t="s">
         <v>40</v>
@@ -13010,7 +13007,7 @@
         <v>761</v>
       </c>
       <c r="D594" s="13">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="E594" s="1">
         <v>0</v>
@@ -13018,7 +13015,7 @@
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A595" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B595" s="10" t="s">
         <v>40</v>
@@ -13027,7 +13024,7 @@
         <v>762</v>
       </c>
       <c r="D595" s="13">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="E595" s="1">
         <v>0</v>
@@ -13035,7 +13032,7 @@
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A596" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B596" s="10" t="s">
         <v>40</v>
@@ -13044,7 +13041,7 @@
         <v>763</v>
       </c>
       <c r="D596" s="13">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="E596" s="1">
         <v>0</v>
@@ -13052,16 +13049,16 @@
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A597" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B597" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C597" s="10" t="s">
-        <v>764</v>
+        <v>320</v>
       </c>
       <c r="D597" s="13">
-        <v>800</v>
+        <v>1070</v>
       </c>
       <c r="E597" s="1">
         <v>0</v>
@@ -13069,16 +13066,16 @@
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A598" s="10" t="s">
-        <v>688</v>
+        <v>593</v>
       </c>
       <c r="B598" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C598" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D598" s="13">
-        <v>1070</v>
+        <v>1</v>
       </c>
       <c r="E598" s="1">
         <v>0</v>
@@ -13086,16 +13083,16 @@
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A599" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B599" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C599" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D599" s="13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E599" s="1">
         <v>0</v>
@@ -13109,10 +13106,10 @@
         <v>0</v>
       </c>
       <c r="C600" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D600" s="13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E600" s="1">
         <v>0</v>
@@ -13120,13 +13117,13 @@
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A601" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B601" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C601" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D601" s="13">
         <v>1</v>
@@ -13137,16 +13134,16 @@
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A602" s="10" t="s">
-        <v>595</v>
+        <v>688</v>
       </c>
       <c r="B602" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C602" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D602" s="13">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E602" s="1">
         <v>0</v>
@@ -13160,10 +13157,10 @@
         <v>0</v>
       </c>
       <c r="C603" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D603" s="13">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E603" s="1">
         <v>0</v>
@@ -13171,16 +13168,16 @@
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A604" s="10" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B604" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C604" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D604" s="13">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="E604" s="1">
         <v>0</v>
@@ -13191,13 +13188,13 @@
         <v>690</v>
       </c>
       <c r="B605" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C605" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D605" s="13">
-        <v>121</v>
+        <v>300</v>
       </c>
       <c r="E605" s="1">
         <v>0</v>
@@ -13205,7 +13202,7 @@
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A606" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B606" s="10" t="s">
         <v>0</v>
@@ -13228,7 +13225,7 @@
         <v>40</v>
       </c>
       <c r="C607" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D607" s="13">
         <v>300</v>
@@ -13239,16 +13236,16 @@
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A608" s="10" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B608" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C608" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D608" s="13">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E608" s="1">
         <v>0</v>
@@ -13256,16 +13253,16 @@
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A609" s="10" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B609" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C609" s="10" t="s">
-        <v>330</v>
+        <v>466</v>
       </c>
       <c r="D609" s="13">
-        <v>310</v>
+        <v>43</v>
       </c>
       <c r="E609" s="1">
         <v>0</v>
@@ -13273,16 +13270,16 @@
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A610" s="10" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B610" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C610" s="10" t="s">
-        <v>466</v>
+        <v>331</v>
       </c>
       <c r="D610" s="13">
-        <v>43</v>
+        <v>250</v>
       </c>
       <c r="E610" s="1">
         <v>0</v>
@@ -13290,16 +13287,16 @@
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A611" s="10" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B611" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C611" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D611" s="13">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="E611" s="1">
         <v>0</v>
@@ -13307,7 +13304,7 @@
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A612" s="10" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B612" s="10" t="s">
         <v>40</v>
@@ -13324,16 +13321,16 @@
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A613" s="10" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B613" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C613" s="10" t="s">
-        <v>332</v>
+        <v>405</v>
       </c>
       <c r="D613" s="13">
-        <v>280</v>
+        <v>42</v>
       </c>
       <c r="E613" s="1">
         <v>0</v>
@@ -13341,16 +13338,16 @@
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A614" s="10" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B614" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C614" s="10" t="s">
-        <v>405</v>
+        <v>333</v>
       </c>
       <c r="D614" s="13">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E614" s="1">
         <v>0</v>
@@ -13358,16 +13355,16 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" s="10" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B615" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C615" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D615" s="13">
-        <v>24</v>
+        <v>250</v>
       </c>
       <c r="E615" s="1">
         <v>0</v>
@@ -13378,13 +13375,13 @@
         <v>694</v>
       </c>
       <c r="B616" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C616" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D616" s="13">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="E616" s="1">
         <v>0</v>
@@ -13392,16 +13389,16 @@
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" s="10" t="s">
-        <v>695</v>
+        <v>750</v>
       </c>
       <c r="B617" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C617" s="10" t="s">
-        <v>335</v>
+        <v>751</v>
       </c>
       <c r="D617" s="13">
-        <v>1250</v>
+        <v>100</v>
       </c>
       <c r="E617" s="1">
         <v>0</v>
@@ -13409,16 +13406,16 @@
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A618" s="10" t="s">
-        <v>751</v>
+        <v>694</v>
       </c>
       <c r="B618" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C618" s="10" t="s">
-        <v>752</v>
+        <v>336</v>
       </c>
       <c r="D618" s="13">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E618" s="1">
         <v>0</v>
@@ -13426,16 +13423,16 @@
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A619" s="10" t="s">
-        <v>695</v>
+        <v>750</v>
       </c>
       <c r="B619" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C619" s="10" t="s">
-        <v>336</v>
+        <v>752</v>
       </c>
       <c r="D619" s="13">
-        <v>160</v>
+        <v>35</v>
       </c>
       <c r="E619" s="1">
         <v>0</v>
@@ -13443,16 +13440,16 @@
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A620" s="10" t="s">
-        <v>751</v>
+        <v>694</v>
       </c>
       <c r="B620" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C620" s="10" t="s">
-        <v>753</v>
+        <v>337</v>
       </c>
       <c r="D620" s="13">
-        <v>35</v>
+        <v>600</v>
       </c>
       <c r="E620" s="1">
         <v>0</v>
@@ -13460,7 +13457,7 @@
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A621" s="10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B621" s="10" t="s">
         <v>0</v>
@@ -13477,16 +13474,16 @@
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A622" s="10" t="s">
-        <v>695</v>
+        <v>750</v>
       </c>
       <c r="B622" s="10" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C622" s="10" t="s">
-        <v>337</v>
+        <v>753</v>
       </c>
       <c r="D622" s="13">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="E622" s="1">
         <v>0</v>
@@ -13494,16 +13491,16 @@
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A623" s="10" t="s">
-        <v>751</v>
+        <v>694</v>
       </c>
       <c r="B623" s="10" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C623" s="10" t="s">
-        <v>754</v>
+        <v>403</v>
       </c>
       <c r="D623" s="13">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E623" s="1">
         <v>0</v>
@@ -13511,16 +13508,16 @@
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A624" s="10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B624" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C624" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D624" s="13">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E624" s="1">
         <v>0</v>
@@ -13528,16 +13525,16 @@
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A625" s="10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B625" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C625" s="10" t="s">
-        <v>404</v>
+        <v>338</v>
       </c>
       <c r="D625" s="13">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E625" s="1">
         <v>0</v>
@@ -13548,13 +13545,13 @@
         <v>695</v>
       </c>
       <c r="B626" s="10" t="s">
-        <v>40</v>
+        <v>417</v>
       </c>
       <c r="C626" s="10" t="s">
-        <v>338</v>
+        <v>428</v>
       </c>
       <c r="D626" s="13">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="E626" s="1">
         <v>0</v>
@@ -13562,16 +13559,16 @@
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A627" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B627" s="10" t="s">
-        <v>417</v>
+        <v>0</v>
       </c>
       <c r="C627" s="10" t="s">
-        <v>428</v>
+        <v>339</v>
       </c>
       <c r="D627" s="13">
-        <v>2</v>
+        <v>1300</v>
       </c>
       <c r="E627" s="1">
         <v>0</v>
@@ -13579,16 +13576,16 @@
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A628" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B628" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C628" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D628" s="13">
-        <v>1300</v>
+        <v>29</v>
       </c>
       <c r="E628" s="1">
         <v>0</v>
@@ -13596,16 +13593,16 @@
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A629" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B629" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C629" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D629" s="13">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E629" s="1">
         <v>0</v>
@@ -13619,10 +13616,10 @@
         <v>0</v>
       </c>
       <c r="C630" s="10" t="s">
-        <v>341</v>
+        <v>483</v>
       </c>
       <c r="D630" s="13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E630" s="1">
         <v>0</v>
@@ -13630,16 +13627,16 @@
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A631" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B631" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C631" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D631" s="13">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E631" s="1">
         <v>0</v>
@@ -13647,16 +13644,16 @@
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B632" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C632" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D632" s="13">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E632" s="1">
         <v>0</v>
@@ -13667,13 +13664,13 @@
         <v>697</v>
       </c>
       <c r="B633" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C633" s="10" t="s">
-        <v>485</v>
+        <v>342</v>
       </c>
       <c r="D633" s="13">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="E633" s="1">
         <v>0</v>
@@ -13681,16 +13678,16 @@
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A634" s="10" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B634" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C634" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D634" s="13">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="E634" s="1">
         <v>0</v>
@@ -13698,16 +13695,16 @@
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A635" s="10" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B635" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C635" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D635" s="13">
-        <v>123</v>
+        <v>8</v>
       </c>
       <c r="E635" s="1">
         <v>0</v>
@@ -13715,16 +13712,16 @@
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636" s="10" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B636" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C636" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D636" s="13">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="E636" s="1">
         <v>0</v>
@@ -13735,13 +13732,13 @@
         <v>698</v>
       </c>
       <c r="B637" s="10" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C637" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D637" s="13">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E637" s="1">
         <v>0</v>
@@ -13749,16 +13746,16 @@
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A638" s="10" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B638" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C638" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D638" s="13">
-        <v>600</v>
+        <v>825</v>
       </c>
       <c r="E638" s="1">
         <v>0</v>
@@ -13766,16 +13763,16 @@
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B639" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C639" s="1" t="s">
-        <v>347</v>
+        <v>754</v>
       </c>
       <c r="D639" s="14">
-        <v>825</v>
+        <v>465</v>
       </c>
       <c r="E639" s="1">
         <v>0</v>
@@ -13783,16 +13780,16 @@
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B640" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>755</v>
+        <v>348</v>
       </c>
       <c r="D640" s="14">
-        <v>465</v>
+        <v>400</v>
       </c>
       <c r="E640" s="1">
         <v>0</v>
@@ -13800,7 +13797,7 @@
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B641" s="1" t="s">
         <v>9</v>
@@ -13823,10 +13820,10 @@
         <v>0</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>348</v>
+        <v>467</v>
       </c>
       <c r="D642" s="14">
-        <v>400</v>
+        <v>65</v>
       </c>
       <c r="E642" s="1">
         <v>0</v>
@@ -13834,16 +13831,16 @@
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>467</v>
+        <v>388</v>
       </c>
       <c r="D643" s="14">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E643" s="1">
         <v>0</v>
@@ -13851,16 +13848,16 @@
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B644" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C644" s="1" t="s">
-        <v>388</v>
+        <v>349</v>
       </c>
       <c r="D644" s="14">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E644" s="1">
         <v>0</v>
@@ -13868,16 +13865,16 @@
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C645" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D645" s="14">
-        <v>72</v>
+        <v>1001</v>
       </c>
       <c r="E645" s="1">
         <v>0</v>
@@ -13885,16 +13882,16 @@
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B646" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C646" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D646" s="14">
-        <v>1001</v>
+        <v>1508</v>
       </c>
       <c r="E646" s="1">
         <v>0</v>
@@ -13908,10 +13905,10 @@
         <v>0</v>
       </c>
       <c r="C647" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D647" s="14">
-        <v>1508</v>
+        <v>600</v>
       </c>
       <c r="E647" s="1">
         <v>0</v>
@@ -13919,16 +13916,16 @@
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B648" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D648" s="14">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E648" s="1">
         <v>0</v>
@@ -13936,16 +13933,16 @@
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B649" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C649" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D649" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E649" s="1">
         <v>0</v>
@@ -13953,16 +13950,16 @@
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B650" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C650" s="1" t="s">
-        <v>354</v>
+        <v>524</v>
       </c>
       <c r="D650" s="14">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="E650" s="1">
         <v>0</v>
@@ -13970,16 +13967,16 @@
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B651" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>524</v>
+        <v>355</v>
       </c>
       <c r="D651" s="14">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E651" s="1">
         <v>0</v>
@@ -13987,13 +13984,13 @@
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B652" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>355</v>
+        <v>416</v>
       </c>
       <c r="D652" s="14">
         <v>100</v>
@@ -14004,16 +14001,16 @@
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B653" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C653" s="1" t="s">
-        <v>416</v>
+        <v>356</v>
       </c>
       <c r="D653" s="14">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E653" s="1">
         <v>0</v>
@@ -14021,16 +14018,16 @@
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>703</v>
+        <v>688</v>
       </c>
       <c r="B654" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C654" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D654" s="14">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="E654" s="1">
         <v>0</v>
@@ -14038,16 +14035,16 @@
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B655" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C655" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D655" s="14">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="E655" s="1">
         <v>0</v>
@@ -14055,16 +14052,16 @@
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>689</v>
+        <v>703</v>
       </c>
       <c r="B656" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C656" s="1" t="s">
-        <v>358</v>
+        <v>486</v>
       </c>
       <c r="D656" s="14">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="E656" s="1">
         <v>0</v>
@@ -14072,16 +14069,16 @@
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B657" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C657" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D657" s="14">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E657" s="1">
         <v>0</v>
@@ -14089,16 +14086,16 @@
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B658" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C658" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D658" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E658" s="1">
         <v>0</v>
@@ -14106,16 +14103,16 @@
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>704</v>
+        <v>689</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C659" s="1" t="s">
-        <v>488</v>
+        <v>359</v>
       </c>
       <c r="D659" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E659" s="1">
         <v>0</v>
@@ -14123,16 +14120,16 @@
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B660" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C660" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D660" s="14">
-        <v>15</v>
+        <v>225</v>
       </c>
       <c r="E660" s="1">
         <v>0</v>
@@ -14140,16 +14137,16 @@
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B661" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C661" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D661" s="14">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="E661" s="1">
         <v>0</v>
@@ -14157,16 +14154,16 @@
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>690</v>
+        <v>704</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D662" s="14">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="E662" s="1">
         <v>0</v>
@@ -14174,13 +14171,13 @@
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C663" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D663" s="14">
         <v>1200</v>
@@ -14191,16 +14188,16 @@
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D664" s="14">
-        <v>1200</v>
+        <v>225</v>
       </c>
       <c r="E664" s="1">
         <v>0</v>
@@ -14208,7 +14205,7 @@
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B665" s="1" t="s">
         <v>40</v>
@@ -14225,16 +14222,16 @@
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C666" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D666" s="14">
-        <v>225</v>
+        <v>500</v>
       </c>
       <c r="E666" s="1">
         <v>0</v>
@@ -14245,13 +14242,13 @@
         <v>705</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C667" s="1" t="s">
-        <v>365</v>
+        <v>780</v>
       </c>
       <c r="D667" s="14">
-        <v>500</v>
+        <v>235</v>
       </c>
       <c r="E667" s="1">
         <v>0</v>
@@ -14259,16 +14256,16 @@
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B668" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C668" s="1" t="s">
-        <v>781</v>
+        <v>755</v>
       </c>
       <c r="D668" s="14">
-        <v>235</v>
+        <v>150</v>
       </c>
       <c r="E668" s="1">
         <v>0</v>
@@ -14276,16 +14273,16 @@
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C669" s="1" t="s">
-        <v>756</v>
+        <v>366</v>
       </c>
       <c r="D669" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E669" s="1">
         <v>0</v>
@@ -14293,7 +14290,7 @@
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B670" s="1" t="s">
         <v>0</v>
@@ -14310,16 +14307,16 @@
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C671" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D671" s="14">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E671" s="1">
         <v>0</v>
@@ -14327,16 +14324,16 @@
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B672" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C672" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D672" s="14">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="E672" s="1">
         <v>0</v>
@@ -14350,10 +14347,10 @@
         <v>0</v>
       </c>
       <c r="C673" s="1" t="s">
-        <v>368</v>
+        <v>468</v>
       </c>
       <c r="D673" s="14">
-        <v>225</v>
+        <v>10</v>
       </c>
       <c r="E673" s="1">
         <v>0</v>
@@ -14361,16 +14358,16 @@
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B674" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C674" s="1" t="s">
-        <v>468</v>
+        <v>369</v>
       </c>
       <c r="D674" s="14">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="E674" s="1">
         <v>0</v>
@@ -14378,7 +14375,7 @@
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B675" s="1" t="s">
         <v>40</v>
@@ -14395,16 +14392,16 @@
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B676" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C676" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D676" s="14">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E676" s="1">
         <v>0</v>
@@ -14412,16 +14409,16 @@
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C677" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D677" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E677" s="1">
         <v>0</v>
@@ -14429,7 +14426,7 @@
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B678" s="1" t="s">
         <v>0</v>
@@ -14446,16 +14443,16 @@
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C679" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D679" s="14">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E679" s="1">
         <v>0</v>
@@ -14463,7 +14460,7 @@
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B680" s="1" t="s">
         <v>40</v>
@@ -14475,23 +14472,6 @@
         <v>64</v>
       </c>
       <c r="E680" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="681" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A681" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="B681" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C681" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="D681" s="14">
-        <v>30</v>
-      </c>
-      <c r="E681" s="1">
         <v>0</v>
       </c>
     </row>
@@ -14558,11 +14538,11 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str" cm="1">
-        <f t="array" ref="A6:C9">_xlfn._xlws.SORT(_xlfn._xlws.FILTER('جرد المواد'!B5:D9588,
-ISNUMBER(SEARCH(IF(B1="","*",B1),'جرد المواد'!C5:C9588))*
-ISNUMBER(SEARCH(IF(B2="","*",B2),'جرد المواد'!C5:C9588))*
-ISNUMBER(SEARCH(IF(B3="","*",B3),'جرد المواد'!C5:C9588))*
-ISNUMBER(SEARCH(IF(B4="","*",B4),'جرد المواد'!B5:B9588)),
+        <f t="array" ref="A6:C9">_xlfn._xlws.SORT(_xlfn._xlws.FILTER('جرد المواد'!B5:D9587,
+ISNUMBER(SEARCH(IF(B1="","*",B1),'جرد المواد'!C5:C9587))*
+ISNUMBER(SEARCH(IF(B2="","*",B2),'جرد المواد'!C5:C9587))*
+ISNUMBER(SEARCH(IF(B3="","*",B3),'جرد المواد'!C5:C9587))*
+ISNUMBER(SEARCH(IF(B4="","*",B4),'جرد المواد'!B5:B9587)),
 "لا توجد نتائج"),
 2,1)</f>
         <v>3-ديوان</v>

--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A29CCA-3E02-4987-9B79-044FA892944D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3CEF74-271B-4C29-A674-7352797031B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -3050,13 +3050,13 @@
         <v>571</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>424</v>
       </c>
       <c r="D9" s="13">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -3067,13 +3067,13 @@
         <v>571</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>424</v>
       </c>
       <c r="D10" s="13">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -4019,13 +4019,13 @@
         <v>591</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>46</v>
       </c>
       <c r="D66" s="13">
-        <v>31</v>
+        <v>200</v>
       </c>
       <c r="E66" s="1">
         <v>0</v>
@@ -4036,13 +4036,13 @@
         <v>591</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>46</v>
       </c>
       <c r="D67" s="13">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E67" s="1">
         <v>0</v>
@@ -4121,13 +4121,13 @@
         <v>593</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>48</v>
       </c>
       <c r="D72" s="13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
@@ -4138,13 +4138,13 @@
         <v>593</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>48</v>
       </c>
       <c r="D73" s="13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
@@ -4189,13 +4189,13 @@
         <v>593</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>51</v>
       </c>
       <c r="D76" s="13">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>593</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>51</v>
       </c>
       <c r="D77" s="13">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E77" s="1">
         <v>0</v>
@@ -4325,13 +4325,13 @@
         <v>597</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D84" s="13">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="E84" s="1">
         <v>0</v>
@@ -4342,13 +4342,13 @@
         <v>597</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D85" s="13">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="E85" s="1">
         <v>0</v>
@@ -4444,13 +4444,13 @@
         <v>597</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D91" s="13">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
@@ -4461,13 +4461,13 @@
         <v>597</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D92" s="13">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
@@ -5124,13 +5124,13 @@
         <v>609</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D131" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -5141,13 +5141,13 @@
         <v>609</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D132" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -5226,13 +5226,13 @@
         <v>609</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D137" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
@@ -5243,13 +5243,13 @@
         <v>609</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D138" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
@@ -5311,7 +5311,7 @@
         <v>609</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C142" s="10" t="s">
         <v>86</v>
@@ -5328,7 +5328,7 @@
         <v>609</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C143" s="10" t="s">
         <v>86</v>
@@ -5606,7 +5606,7 @@
         <v>441</v>
       </c>
       <c r="D159" s="13">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E159" s="1">
         <v>0</v>
@@ -5623,7 +5623,7 @@
         <v>442</v>
       </c>
       <c r="D160" s="13">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E160" s="1">
         <v>0</v>
@@ -5923,13 +5923,13 @@
         <v>616</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D178" s="13">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E178" s="1">
         <v>0</v>
@@ -5940,13 +5940,13 @@
         <v>616</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C179" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D179" s="13">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E179" s="1">
         <v>0</v>
@@ -5957,13 +5957,13 @@
         <v>616</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C180" s="10" t="s">
         <v>115</v>
       </c>
       <c r="D180" s="13">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E180" s="1">
         <v>0</v>
@@ -5974,13 +5974,13 @@
         <v>616</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C181" s="10" t="s">
         <v>115</v>
       </c>
       <c r="D181" s="13">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E181" s="1">
         <v>0</v>
@@ -6025,13 +6025,13 @@
         <v>616</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C184" s="10" t="s">
         <v>118</v>
       </c>
       <c r="D184" s="13">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="E184" s="1">
         <v>0</v>
@@ -6042,13 +6042,13 @@
         <v>616</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C185" s="10" t="s">
         <v>118</v>
       </c>
       <c r="D185" s="13">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="E185" s="1">
         <v>0</v>
@@ -7221,7 +7221,7 @@
         <v>155</v>
       </c>
       <c r="D254" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E254" s="1">
         <v>0</v>
@@ -7952,7 +7952,7 @@
         <v>530</v>
       </c>
       <c r="D297" s="13">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E297" s="1">
         <v>0</v>
@@ -7969,7 +7969,7 @@
         <v>523</v>
       </c>
       <c r="D298" s="13">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E298" s="1">
         <v>0</v>
@@ -8037,7 +8037,7 @@
         <v>531</v>
       </c>
       <c r="D302" s="13">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E302" s="1">
         <v>0</v>
@@ -8082,13 +8082,13 @@
         <v>642</v>
       </c>
       <c r="B305" s="10" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C305" s="10" t="s">
         <v>186</v>
       </c>
       <c r="D305" s="13">
-        <v>650</v>
+        <v>400</v>
       </c>
       <c r="E305" s="1">
         <v>0</v>
@@ -8099,13 +8099,13 @@
         <v>642</v>
       </c>
       <c r="B306" s="10" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C306" s="10" t="s">
         <v>186</v>
       </c>
       <c r="D306" s="13">
-        <v>400</v>
+        <v>650</v>
       </c>
       <c r="E306" s="1">
         <v>0</v>
@@ -8167,13 +8167,13 @@
         <v>639</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C310" s="10" t="s">
         <v>187</v>
       </c>
       <c r="D310" s="13">
-        <v>800</v>
+        <v>175</v>
       </c>
       <c r="E310" s="1">
         <v>0</v>
@@ -8201,13 +8201,13 @@
         <v>639</v>
       </c>
       <c r="B312" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C312" s="10" t="s">
         <v>187</v>
       </c>
       <c r="D312" s="13">
-        <v>175</v>
+        <v>800</v>
       </c>
       <c r="E312" s="1">
         <v>0</v>
@@ -8677,13 +8677,13 @@
         <v>648</v>
       </c>
       <c r="B340" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C340" s="10" t="s">
         <v>196</v>
       </c>
       <c r="D340" s="13">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="E340" s="1">
         <v>0</v>
@@ -8694,13 +8694,13 @@
         <v>648</v>
       </c>
       <c r="B341" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C341" s="10" t="s">
         <v>196</v>
       </c>
       <c r="D341" s="13">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E341" s="1">
         <v>0</v>
@@ -8745,13 +8745,13 @@
         <v>648</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C344" s="10" t="s">
         <v>198</v>
       </c>
       <c r="D344" s="13">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E344" s="1">
         <v>0</v>
@@ -8762,13 +8762,13 @@
         <v>648</v>
       </c>
       <c r="B345" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C345" s="10" t="s">
         <v>198</v>
       </c>
       <c r="D345" s="13">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E345" s="1">
         <v>0</v>
@@ -9000,7 +9000,7 @@
         <v>612</v>
       </c>
       <c r="B359" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C359" s="10" t="s">
         <v>206</v>
@@ -9017,7 +9017,7 @@
         <v>612</v>
       </c>
       <c r="B360" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C360" s="10" t="s">
         <v>206</v>
@@ -9193,7 +9193,7 @@
         <v>514</v>
       </c>
       <c r="D370" s="13">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E370" s="1">
         <v>0</v>
@@ -9527,13 +9527,13 @@
         <v>655</v>
       </c>
       <c r="B390" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C390" s="10" t="s">
         <v>223</v>
       </c>
       <c r="D390" s="13">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="E390" s="1">
         <v>0</v>
@@ -9544,13 +9544,13 @@
         <v>655</v>
       </c>
       <c r="B391" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C391" s="10" t="s">
         <v>223</v>
       </c>
       <c r="D391" s="13">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="E391" s="1">
         <v>0</v>
@@ -9782,13 +9782,13 @@
         <v>660</v>
       </c>
       <c r="B405" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C405" s="10" t="s">
         <v>235</v>
       </c>
       <c r="D405" s="13">
-        <v>14</v>
+        <v>316</v>
       </c>
       <c r="E405" s="1">
         <v>0</v>
@@ -9799,13 +9799,13 @@
         <v>660</v>
       </c>
       <c r="B406" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C406" s="10" t="s">
         <v>235</v>
       </c>
       <c r="D406" s="13">
-        <v>316</v>
+        <v>14</v>
       </c>
       <c r="E406" s="1">
         <v>0</v>
@@ -10343,13 +10343,13 @@
         <v>669</v>
       </c>
       <c r="B438" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C438" s="10" t="s">
         <v>249</v>
       </c>
       <c r="D438" s="13">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E438" s="1">
         <v>0</v>
@@ -10360,13 +10360,13 @@
         <v>669</v>
       </c>
       <c r="B439" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C439" s="10" t="s">
         <v>249</v>
       </c>
       <c r="D439" s="13">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E439" s="1">
         <v>0</v>
@@ -12366,7 +12366,7 @@
         <v>574</v>
       </c>
       <c r="B557" s="10" t="s">
-        <v>0</v>
+        <v>532</v>
       </c>
       <c r="C557" s="10" t="s">
         <v>307</v>
@@ -12383,7 +12383,7 @@
         <v>574</v>
       </c>
       <c r="B558" s="10" t="s">
-        <v>532</v>
+        <v>0</v>
       </c>
       <c r="C558" s="10" t="s">
         <v>307</v>
@@ -13267,13 +13267,13 @@
         <v>681</v>
       </c>
       <c r="B610" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C610" s="10" t="s">
         <v>328</v>
       </c>
       <c r="D610" s="13">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="E610" s="1">
         <v>0</v>
@@ -13284,13 +13284,13 @@
         <v>681</v>
       </c>
       <c r="B611" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C611" s="10" t="s">
         <v>328</v>
       </c>
       <c r="D611" s="13">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="E611" s="1">
         <v>0</v>
@@ -13420,13 +13420,13 @@
         <v>684</v>
       </c>
       <c r="B619" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C619" s="10" t="s">
         <v>333</v>
       </c>
       <c r="D619" s="13">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="E619" s="1">
         <v>0</v>
@@ -13437,13 +13437,13 @@
         <v>684</v>
       </c>
       <c r="B620" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C620" s="10" t="s">
         <v>333</v>
       </c>
       <c r="D620" s="13">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E620" s="1">
         <v>0</v>
@@ -14168,13 +14168,13 @@
         <v>694</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C663" s="1" t="s">
         <v>360</v>
       </c>
       <c r="D663" s="14">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="E663" s="1">
         <v>0</v>
@@ -14185,13 +14185,13 @@
         <v>694</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C664" s="1" t="s">
         <v>360</v>
       </c>
       <c r="D664" s="14">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="E664" s="1">
         <v>0</v>
@@ -14253,13 +14253,13 @@
         <v>694</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C668" s="1" t="s">
         <v>362</v>
       </c>
       <c r="D668" s="14">
-        <v>950</v>
+        <v>200</v>
       </c>
       <c r="E668" s="1">
         <v>0</v>
@@ -14270,13 +14270,13 @@
         <v>694</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C669" s="1" t="s">
         <v>362</v>
       </c>
       <c r="D669" s="14">
-        <v>200</v>
+        <v>950</v>
       </c>
       <c r="E669" s="1">
         <v>0</v>
@@ -14338,13 +14338,13 @@
         <v>694</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C673" s="1" t="s">
         <v>365</v>
       </c>
       <c r="D673" s="14">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="E673" s="1">
         <v>0</v>
@@ -14355,13 +14355,13 @@
         <v>694</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C674" s="1" t="s">
         <v>365</v>
       </c>
       <c r="D674" s="14">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="E674" s="1">
         <v>0</v>
@@ -14423,13 +14423,13 @@
         <v>694</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C678" s="1" t="s">
         <v>368</v>
       </c>
       <c r="D678" s="14">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="E678" s="1">
         <v>0</v>
@@ -14440,13 +14440,13 @@
         <v>694</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C679" s="1" t="s">
         <v>368</v>
       </c>
       <c r="D679" s="14">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E679" s="1">
         <v>0</v>

--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B35D666-A956-461A-B992-6728F16301B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9272AD59-27E4-4659-9F4D-01220A5B1A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -2131,9 +2131,6 @@
     <t>جرن مغسلة ابيض 1170A-60</t>
   </si>
   <si>
-    <t>موتير 2 حصان دوبل توربين ليو LEO 2ACM150</t>
-  </si>
-  <si>
     <t>موتير ليو LEO 2XCM160/160</t>
   </si>
   <si>
@@ -2443,18 +2440,12 @@
     <t>نربيج دوش بلاستيك 150 سم اسباني</t>
   </si>
   <si>
-    <t>نربيج دوش كروم 150 سم اسباني</t>
-  </si>
-  <si>
     <t>نربيج شطافة ابيض 120 سم اسباني</t>
   </si>
   <si>
     <t>نربيج شطافة بلاستيك 120 سم اسباني</t>
   </si>
   <si>
-    <t>نربيج شطافة كروم 120 سم اسباني</t>
-  </si>
-  <si>
     <t>نربيج فليكسيبل بولاد 40 سم اسباني</t>
   </si>
   <si>
@@ -2465,6 +2456,15 @@
   </si>
   <si>
     <t>نربيج فليكسيبل بولاد 80 سم اسباني</t>
+  </si>
+  <si>
+    <t>كرسي بدعسة ابيض هندي</t>
+  </si>
+  <si>
+    <t>نربيج دوش كروم 150 سم بريفا</t>
+  </si>
+  <si>
+    <t>نربيج شطافة كروم 120 سم بريفا</t>
   </si>
 </sst>
 </file>
@@ -3085,7 +3085,7 @@
         <v>39</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D7" s="13">
         <v>600</v>
@@ -3133,13 +3133,13 @@
         <v>561</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>417</v>
       </c>
       <c r="D10" s="13">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -3150,13 +3150,13 @@
         <v>561</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>417</v>
       </c>
       <c r="D11" s="13">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D17" s="13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D19" s="13">
         <v>1</v>
@@ -3394,7 +3394,7 @@
         <v>15</v>
       </c>
       <c r="D25" s="13">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D27" s="13">
         <v>8</v>
@@ -3442,7 +3442,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D28" s="13">
         <v>5</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D29" s="13">
         <v>3</v>
@@ -3510,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D32" s="13">
         <v>5</v>
@@ -3955,7 +3955,7 @@
         <v>488</v>
       </c>
       <c r="D58" s="13">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
@@ -4187,13 +4187,13 @@
         <v>583</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D72" s="13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
@@ -4204,13 +4204,13 @@
         <v>583</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D73" s="13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
@@ -4255,13 +4255,13 @@
         <v>583</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D76" s="13">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
@@ -4272,13 +4272,13 @@
         <v>583</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D77" s="13">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E77" s="1">
         <v>0</v>
@@ -4312,7 +4312,7 @@
         <v>462</v>
       </c>
       <c r="D79" s="13">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E79" s="1">
         <v>0</v>
@@ -4337,13 +4337,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C81" s="10" t="s">
         <v>719</v>
-      </c>
-      <c r="B81" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>720</v>
       </c>
       <c r="D81" s="13">
         <v>70</v>
@@ -4391,13 +4391,13 @@
         <v>587</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D84" s="13">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="E84" s="1">
         <v>0</v>
@@ -4408,13 +4408,13 @@
         <v>587</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D85" s="13">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="E85" s="1">
         <v>0</v>
@@ -4445,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D87" s="13">
         <v>170</v>
@@ -4459,13 +4459,13 @@
         <v>587</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D88" s="13">
-        <v>2725</v>
+        <v>1350</v>
       </c>
       <c r="E88" s="1">
         <v>0</v>
@@ -4476,13 +4476,13 @@
         <v>587</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D89" s="13">
-        <v>1350</v>
+        <v>2725</v>
       </c>
       <c r="E89" s="1">
         <v>0</v>
@@ -4510,13 +4510,13 @@
         <v>587</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D91" s="13">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
@@ -4527,13 +4527,13 @@
         <v>587</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D92" s="13">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
@@ -4683,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D101" s="13">
         <v>4</v>
@@ -4802,7 +4802,7 @@
         <v>39</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D108" s="13">
         <v>600</v>
@@ -5040,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D122" s="13">
         <v>1</v>
@@ -5057,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D123" s="13">
         <v>2</v>
@@ -5190,13 +5190,13 @@
         <v>599</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D131" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -5207,13 +5207,13 @@
         <v>599</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D132" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -5224,13 +5224,13 @@
         <v>599</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>79</v>
       </c>
       <c r="D133" s="13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -5241,13 +5241,13 @@
         <v>599</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>79</v>
       </c>
       <c r="D134" s="13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -5292,13 +5292,13 @@
         <v>599</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>81</v>
       </c>
       <c r="D137" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
@@ -5309,13 +5309,13 @@
         <v>599</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>81</v>
       </c>
       <c r="D138" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
@@ -5326,13 +5326,13 @@
         <v>599</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D139" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
@@ -5343,13 +5343,13 @@
         <v>599</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C140" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D140" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
@@ -5377,7 +5377,7 @@
         <v>599</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C142" s="10" t="s">
         <v>84</v>
@@ -5394,7 +5394,7 @@
         <v>599</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C143" s="10" t="s">
         <v>84</v>
@@ -5706,7 +5706,7 @@
         <v>98</v>
       </c>
       <c r="D161" s="13">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E161" s="1">
         <v>0</v>
@@ -5955,13 +5955,13 @@
         <v>606</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C176" s="10" t="s">
         <v>110</v>
       </c>
       <c r="D176" s="13">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E176" s="1">
         <v>0</v>
@@ -5972,13 +5972,13 @@
         <v>606</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>110</v>
       </c>
       <c r="D177" s="13">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E177" s="1">
         <v>0</v>
@@ -5989,13 +5989,13 @@
         <v>606</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>111</v>
       </c>
       <c r="D178" s="13">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E178" s="1">
         <v>0</v>
@@ -6006,13 +6006,13 @@
         <v>606</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C179" s="10" t="s">
         <v>111</v>
       </c>
       <c r="D179" s="13">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E179" s="1">
         <v>0</v>
@@ -6057,13 +6057,13 @@
         <v>606</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C182" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D182" s="13">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="E182" s="1">
         <v>0</v>
@@ -6074,13 +6074,13 @@
         <v>606</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C183" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D183" s="13">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="E183" s="1">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="C185" s="10" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D185" s="13">
         <v>14</v>
@@ -6142,13 +6142,13 @@
         <v>593</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C187" s="10" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D187" s="13">
-        <v>600</v>
+        <v>1920</v>
       </c>
       <c r="E187" s="1">
         <v>0</v>
@@ -6159,13 +6159,13 @@
         <v>593</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D188" s="13">
-        <v>1920</v>
+        <v>600</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
@@ -6176,13 +6176,13 @@
         <v>593</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C189" s="10" t="s">
         <v>504</v>
       </c>
       <c r="D189" s="13">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
@@ -6193,13 +6193,13 @@
         <v>593</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C190" s="10" t="s">
         <v>504</v>
       </c>
       <c r="D190" s="13">
-        <v>1600</v>
+        <v>240</v>
       </c>
       <c r="E190" s="1">
         <v>0</v>
@@ -6213,10 +6213,10 @@
         <v>9</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D191" s="13">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E191" s="1">
         <v>0</v>
@@ -6244,13 +6244,13 @@
         <v>593</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C193" s="10" t="s">
         <v>505</v>
       </c>
       <c r="D193" s="13">
-        <v>600</v>
+        <v>4400</v>
       </c>
       <c r="E193" s="1">
         <v>0</v>
@@ -6261,13 +6261,13 @@
         <v>593</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C194" s="10" t="s">
         <v>505</v>
       </c>
       <c r="D194" s="13">
-        <v>4400</v>
+        <v>600</v>
       </c>
       <c r="E194" s="1">
         <v>0</v>
@@ -6281,10 +6281,10 @@
         <v>9</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D195" s="13">
-        <v>3040</v>
+        <v>2880</v>
       </c>
       <c r="E195" s="1">
         <v>0</v>
@@ -6315,7 +6315,7 @@
         <v>39</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D197" s="13">
         <v>2040</v>
@@ -6332,10 +6332,10 @@
         <v>9</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D198" s="13">
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="E198" s="1">
         <v>0</v>
@@ -6420,7 +6420,7 @@
         <v>387</v>
       </c>
       <c r="D203" s="13">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E203" s="1">
         <v>0</v>
@@ -6621,10 +6621,10 @@
         <v>0</v>
       </c>
       <c r="C215" s="10" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D215" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E215" s="1">
         <v>0</v>
@@ -6774,7 +6774,7 @@
         <v>39</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D224" s="13">
         <v>100</v>
@@ -6791,7 +6791,7 @@
         <v>9</v>
       </c>
       <c r="C225" s="10" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D225" s="13">
         <v>4</v>
@@ -6808,7 +6808,7 @@
         <v>9</v>
       </c>
       <c r="C226" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D226" s="13">
         <v>11</v>
@@ -6859,7 +6859,7 @@
         <v>9</v>
       </c>
       <c r="C229" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D229" s="13">
         <v>15</v>
@@ -7046,7 +7046,7 @@
         <v>0</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D240" s="13">
         <v>10</v>
@@ -7063,7 +7063,7 @@
         <v>0</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D241" s="13">
         <v>10</v>
@@ -7080,7 +7080,7 @@
         <v>0</v>
       </c>
       <c r="C242" s="10" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D242" s="13">
         <v>15</v>
@@ -7131,7 +7131,7 @@
         <v>39</v>
       </c>
       <c r="C245" s="10" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D245" s="13">
         <v>800</v>
@@ -7148,7 +7148,7 @@
         <v>39</v>
       </c>
       <c r="C246" s="10" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D246" s="13">
         <v>2000</v>
@@ -7165,7 +7165,7 @@
         <v>39</v>
       </c>
       <c r="C247" s="10" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D247" s="13">
         <v>1800</v>
@@ -7250,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="C252" s="10" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D252" s="13">
         <v>40</v>
@@ -7298,13 +7298,13 @@
         <v>622</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C255" s="10" t="s">
         <v>148</v>
       </c>
       <c r="D255" s="13">
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="E255" s="1">
         <v>0</v>
@@ -7315,13 +7315,13 @@
         <v>622</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C256" s="10" t="s">
         <v>148</v>
       </c>
       <c r="D256" s="13">
-        <v>520</v>
+        <v>600</v>
       </c>
       <c r="E256" s="1">
         <v>0</v>
@@ -7386,7 +7386,7 @@
         <v>0</v>
       </c>
       <c r="C260" s="10" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D260" s="13">
         <v>49</v>
@@ -7658,7 +7658,7 @@
         <v>9</v>
       </c>
       <c r="C276" s="10" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D276" s="13">
         <v>100</v>
@@ -7896,7 +7896,7 @@
         <v>0</v>
       </c>
       <c r="C290" s="10" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D290" s="13">
         <v>4</v>
@@ -7930,7 +7930,7 @@
         <v>0</v>
       </c>
       <c r="C292" s="10" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D292" s="13">
         <v>5</v>
@@ -8270,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="C312" s="10" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D312" s="13">
         <v>75</v>
@@ -8301,13 +8301,13 @@
         <v>629</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C314" s="10" t="s">
         <v>181</v>
       </c>
       <c r="D314" s="13">
-        <v>800</v>
+        <v>102</v>
       </c>
       <c r="E314" s="1">
         <v>0</v>
@@ -8318,13 +8318,13 @@
         <v>629</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C315" s="10" t="s">
         <v>181</v>
       </c>
       <c r="D315" s="13">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="E315" s="1">
         <v>0</v>
@@ -8335,13 +8335,13 @@
         <v>629</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C316" s="10" t="s">
         <v>181</v>
       </c>
       <c r="D316" s="13">
-        <v>125</v>
+        <v>800</v>
       </c>
       <c r="E316" s="1">
         <v>0</v>
@@ -8355,7 +8355,7 @@
         <v>0</v>
       </c>
       <c r="C317" s="10" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D317" s="13">
         <v>20</v>
@@ -8389,7 +8389,7 @@
         <v>9</v>
       </c>
       <c r="C319" s="10" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D319" s="13">
         <v>450</v>
@@ -8488,13 +8488,13 @@
         <v>632</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C325" s="10" t="s">
         <v>183</v>
       </c>
       <c r="D325" s="13">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="E325" s="1">
         <v>0</v>
@@ -8505,13 +8505,13 @@
         <v>632</v>
       </c>
       <c r="B326" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C326" s="10" t="s">
         <v>183</v>
       </c>
       <c r="D326" s="13">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="E326" s="1">
         <v>0</v>
@@ -8587,13 +8587,13 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B331" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C331" s="10" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D331" s="13">
         <v>1</v>
@@ -8709,13 +8709,13 @@
         <v>637</v>
       </c>
       <c r="B338" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C338" s="10" t="s">
         <v>188</v>
       </c>
       <c r="D338" s="13">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="E338" s="1">
         <v>0</v>
@@ -8726,13 +8726,13 @@
         <v>637</v>
       </c>
       <c r="B339" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C339" s="10" t="s">
         <v>188</v>
       </c>
       <c r="D339" s="13">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="E339" s="1">
         <v>0</v>
@@ -8794,13 +8794,13 @@
         <v>638</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C343" s="10" t="s">
         <v>190</v>
       </c>
       <c r="D343" s="13">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="E343" s="1">
         <v>0</v>
@@ -8811,13 +8811,13 @@
         <v>638</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C344" s="10" t="s">
         <v>190</v>
       </c>
       <c r="D344" s="13">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E344" s="1">
         <v>0</v>
@@ -8828,7 +8828,7 @@
         <v>638</v>
       </c>
       <c r="B345" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C345" s="10" t="s">
         <v>191</v>
@@ -8845,7 +8845,7 @@
         <v>638</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C346" s="10" t="s">
         <v>191</v>
@@ -8944,13 +8944,13 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="10" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B352" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C352" s="10" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D352" s="13">
         <v>90</v>
@@ -8961,13 +8961,13 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="B353" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C353" s="10" t="s">
         <v>724</v>
-      </c>
-      <c r="B353" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C353" s="10" t="s">
-        <v>725</v>
       </c>
       <c r="D353" s="13">
         <v>50</v>
@@ -9188,7 +9188,7 @@
         <v>9</v>
       </c>
       <c r="C366" s="10" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D366" s="13">
         <v>4</v>
@@ -9222,7 +9222,7 @@
         <v>9</v>
       </c>
       <c r="C368" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D368" s="13">
         <v>11</v>
@@ -9256,7 +9256,7 @@
         <v>9</v>
       </c>
       <c r="C370" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D370" s="13">
         <v>19</v>
@@ -9273,10 +9273,10 @@
         <v>0</v>
       </c>
       <c r="C371" s="10" t="s">
-        <v>204</v>
+        <v>799</v>
       </c>
       <c r="D371" s="13">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E371" s="1">
         <v>0</v>
@@ -9290,7 +9290,7 @@
         <v>0</v>
       </c>
       <c r="C372" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D372" s="13">
         <v>10</v>
@@ -9304,13 +9304,13 @@
         <v>574</v>
       </c>
       <c r="B373" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C373" s="10" t="s">
-        <v>506</v>
+        <v>205</v>
       </c>
       <c r="D373" s="13">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E373" s="1">
         <v>0</v>
@@ -9321,13 +9321,13 @@
         <v>574</v>
       </c>
       <c r="B374" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C374" s="10" t="s">
-        <v>437</v>
+        <v>506</v>
       </c>
       <c r="D374" s="13">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="E374" s="1">
         <v>0</v>
@@ -9341,7 +9341,7 @@
         <v>0</v>
       </c>
       <c r="C375" s="10" t="s">
-        <v>206</v>
+        <v>437</v>
       </c>
       <c r="D375" s="13">
         <v>1</v>
@@ -9358,7 +9358,7 @@
         <v>0</v>
       </c>
       <c r="C376" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D376" s="13">
         <v>1</v>
@@ -9369,13 +9369,13 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B377" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C377" s="10" t="s">
-        <v>490</v>
+        <v>207</v>
       </c>
       <c r="D377" s="13">
         <v>1</v>
@@ -9386,13 +9386,13 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="10" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B378" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C378" s="10" t="s">
-        <v>208</v>
+        <v>490</v>
       </c>
       <c r="D378" s="13">
         <v>1</v>
@@ -9409,7 +9409,7 @@
         <v>0</v>
       </c>
       <c r="C379" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D379" s="13">
         <v>1</v>
@@ -9420,16 +9420,16 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="10" t="s">
-        <v>642</v>
+        <v>574</v>
       </c>
       <c r="B380" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C380" s="10" t="s">
-        <v>394</v>
+        <v>209</v>
       </c>
       <c r="D380" s="13">
-        <v>1800</v>
+        <v>1</v>
       </c>
       <c r="E380" s="1">
         <v>0</v>
@@ -9443,10 +9443,10 @@
         <v>39</v>
       </c>
       <c r="C381" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D381" s="13">
-        <v>2700</v>
+        <v>1800</v>
       </c>
       <c r="E381" s="1">
         <v>0</v>
@@ -9460,10 +9460,10 @@
         <v>39</v>
       </c>
       <c r="C382" s="10" t="s">
-        <v>210</v>
+        <v>395</v>
       </c>
       <c r="D382" s="13">
-        <v>900</v>
+        <v>2700</v>
       </c>
       <c r="E382" s="1">
         <v>0</v>
@@ -9477,7 +9477,7 @@
         <v>39</v>
       </c>
       <c r="C383" s="10" t="s">
-        <v>396</v>
+        <v>210</v>
       </c>
       <c r="D383" s="13">
         <v>900</v>
@@ -9494,10 +9494,10 @@
         <v>39</v>
       </c>
       <c r="C384" s="10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D384" s="13">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="E384" s="1">
         <v>0</v>
@@ -9505,16 +9505,16 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B385" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C385" s="10" t="s">
-        <v>211</v>
+        <v>397</v>
       </c>
       <c r="D385" s="13">
-        <v>40</v>
+        <v>1200</v>
       </c>
       <c r="E385" s="1">
         <v>0</v>
@@ -9522,16 +9522,16 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="10" t="s">
-        <v>560</v>
+        <v>643</v>
       </c>
       <c r="B386" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C386" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D386" s="13">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E386" s="1">
         <v>0</v>
@@ -9539,16 +9539,16 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="10" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B387" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C387" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D387" s="13">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="E387" s="1">
         <v>0</v>
@@ -9556,16 +9556,16 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="10" t="s">
-        <v>644</v>
+        <v>559</v>
       </c>
       <c r="B388" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C388" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D388" s="13">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="E388" s="1">
         <v>0</v>
@@ -9573,16 +9573,16 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B389" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C389" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D389" s="13">
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="E389" s="1">
         <v>0</v>
@@ -9590,16 +9590,16 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="10" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B390" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C390" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D390" s="13">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="E390" s="1">
         <v>0</v>
@@ -9607,16 +9607,16 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="10" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B391" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C391" s="10" t="s">
-        <v>447</v>
+        <v>216</v>
       </c>
       <c r="D391" s="13">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="E391" s="1">
         <v>0</v>
@@ -9624,16 +9624,16 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="10" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B392" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C392" s="10" t="s">
-        <v>217</v>
+        <v>447</v>
       </c>
       <c r="D392" s="13">
-        <v>2550</v>
+        <v>159</v>
       </c>
       <c r="E392" s="1">
         <v>0</v>
@@ -9644,13 +9644,13 @@
         <v>645</v>
       </c>
       <c r="B393" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C393" s="10" t="s">
         <v>217</v>
       </c>
       <c r="D393" s="13">
-        <v>200</v>
+        <v>2550</v>
       </c>
       <c r="E393" s="1">
         <v>0</v>
@@ -9661,13 +9661,13 @@
         <v>645</v>
       </c>
       <c r="B394" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C394" s="10" t="s">
         <v>217</v>
       </c>
       <c r="D394" s="13">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="E394" s="1">
         <v>0</v>
@@ -9681,10 +9681,10 @@
         <v>39</v>
       </c>
       <c r="C395" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D395" s="13">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="E395" s="1">
         <v>0</v>
@@ -9695,13 +9695,13 @@
         <v>645</v>
       </c>
       <c r="B396" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C396" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D396" s="13">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E396" s="1">
         <v>0</v>
@@ -9712,13 +9712,13 @@
         <v>645</v>
       </c>
       <c r="B397" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C397" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D397" s="13">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E397" s="1">
         <v>0</v>
@@ -9726,16 +9726,16 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="10" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B398" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C398" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D398" s="13">
-        <v>56</v>
+        <v>300</v>
       </c>
       <c r="E398" s="1">
         <v>0</v>
@@ -9749,10 +9749,10 @@
         <v>0</v>
       </c>
       <c r="C399" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D399" s="13">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="E399" s="1">
         <v>0</v>
@@ -9766,10 +9766,10 @@
         <v>0</v>
       </c>
       <c r="C400" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D400" s="13">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E400" s="1">
         <v>0</v>
@@ -9777,16 +9777,16 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B401" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C401" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D401" s="13">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="E401" s="1">
         <v>0</v>
@@ -9800,10 +9800,10 @@
         <v>0</v>
       </c>
       <c r="C402" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D402" s="13">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="E402" s="1">
         <v>0</v>
@@ -9817,10 +9817,10 @@
         <v>0</v>
       </c>
       <c r="C403" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D403" s="13">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="E403" s="1">
         <v>0</v>
@@ -9828,16 +9828,16 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B404" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C404" s="10" t="s">
-        <v>466</v>
+        <v>226</v>
       </c>
       <c r="D404" s="13">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E404" s="1">
         <v>0</v>
@@ -9851,10 +9851,10 @@
         <v>0</v>
       </c>
       <c r="C405" s="10" t="s">
-        <v>227</v>
+        <v>466</v>
       </c>
       <c r="D405" s="13">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E405" s="1">
         <v>0</v>
@@ -9868,10 +9868,10 @@
         <v>0</v>
       </c>
       <c r="C406" s="10" t="s">
-        <v>467</v>
+        <v>227</v>
       </c>
       <c r="D406" s="13">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="E406" s="1">
         <v>0</v>
@@ -9879,16 +9879,16 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B407" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C407" s="10" t="s">
-        <v>228</v>
+        <v>467</v>
       </c>
       <c r="D407" s="13">
-        <v>210</v>
+        <v>29</v>
       </c>
       <c r="E407" s="1">
         <v>0</v>
@@ -9902,10 +9902,10 @@
         <v>9</v>
       </c>
       <c r="C408" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D408" s="13">
-        <v>316</v>
+        <v>210</v>
       </c>
       <c r="E408" s="1">
         <v>0</v>
@@ -9936,10 +9936,10 @@
         <v>9</v>
       </c>
       <c r="C410" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D410" s="13">
-        <v>110</v>
+        <v>316</v>
       </c>
       <c r="E410" s="1">
         <v>0</v>
@@ -9953,10 +9953,10 @@
         <v>9</v>
       </c>
       <c r="C411" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D411" s="13">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="E411" s="1">
         <v>0</v>
@@ -9967,13 +9967,13 @@
         <v>650</v>
       </c>
       <c r="B412" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C412" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D412" s="13">
-        <v>129</v>
+        <v>6</v>
       </c>
       <c r="E412" s="1">
         <v>0</v>
@@ -9998,16 +9998,16 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B414" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C414" s="10" t="s">
-        <v>402</v>
+        <v>232</v>
       </c>
       <c r="D414" s="13">
-        <v>400</v>
+        <v>129</v>
       </c>
       <c r="E414" s="1">
         <v>0</v>
@@ -10015,16 +10015,16 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B415" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>448</v>
+        <v>402</v>
       </c>
       <c r="D415" s="13">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="E415" s="1">
         <v>0</v>
@@ -10032,16 +10032,16 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B416" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C416" s="10" t="s">
-        <v>372</v>
+        <v>448</v>
       </c>
       <c r="D416" s="13">
-        <v>1200</v>
+        <v>75</v>
       </c>
       <c r="E416" s="1">
         <v>0</v>
@@ -10049,13 +10049,13 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" s="10" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B417" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C417" s="10" t="s">
-        <v>403</v>
+        <v>372</v>
       </c>
       <c r="D417" s="13">
         <v>1200</v>
@@ -10066,16 +10066,16 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B418" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C418" s="10" t="s">
-        <v>727</v>
+        <v>403</v>
       </c>
       <c r="D418" s="13">
-        <v>290</v>
+        <v>1200</v>
       </c>
       <c r="E418" s="1">
         <v>0</v>
@@ -10083,16 +10083,16 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B419" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C419" s="10" t="s">
-        <v>373</v>
+        <v>726</v>
       </c>
       <c r="D419" s="13">
-        <v>26500</v>
+        <v>290</v>
       </c>
       <c r="E419" s="1">
         <v>0</v>
@@ -10100,16 +10100,16 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="10" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B420" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C420" s="10" t="s">
-        <v>449</v>
+        <v>373</v>
       </c>
       <c r="D420" s="13">
-        <v>80</v>
+        <v>26500</v>
       </c>
       <c r="E420" s="1">
         <v>0</v>
@@ -10117,16 +10117,16 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B421" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C421" s="10" t="s">
-        <v>233</v>
+        <v>449</v>
       </c>
       <c r="D421" s="13">
-        <v>1775</v>
+        <v>80</v>
       </c>
       <c r="E421" s="1">
         <v>0</v>
@@ -10151,16 +10151,16 @@
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" s="10" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B423" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C423" s="10" t="s">
-        <v>450</v>
+        <v>233</v>
       </c>
       <c r="D423" s="13">
-        <v>70</v>
+        <v>1775</v>
       </c>
       <c r="E423" s="1">
         <v>0</v>
@@ -10168,16 +10168,16 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B424" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C424" s="10" t="s">
-        <v>234</v>
+        <v>450</v>
       </c>
       <c r="D424" s="13">
-        <v>360</v>
+        <v>70</v>
       </c>
       <c r="E424" s="1">
         <v>0</v>
@@ -10188,13 +10188,13 @@
         <v>653</v>
       </c>
       <c r="B425" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C425" s="10" t="s">
         <v>234</v>
       </c>
       <c r="D425" s="13">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="E425" s="1">
         <v>0</v>
@@ -10208,10 +10208,10 @@
         <v>39</v>
       </c>
       <c r="C426" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D426" s="13">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E426" s="1">
         <v>0</v>
@@ -10219,16 +10219,16 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="10" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B427" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C427" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D427" s="13">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="E427" s="1">
         <v>0</v>
@@ -10236,16 +10236,16 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="10" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B428" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C428" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D428" s="13">
-        <v>97</v>
+        <v>600</v>
       </c>
       <c r="E428" s="1">
         <v>0</v>
@@ -10253,16 +10253,16 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B429" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C429" s="10" t="s">
-        <v>468</v>
+        <v>237</v>
       </c>
       <c r="D429" s="13">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="E429" s="1">
         <v>0</v>
@@ -10276,10 +10276,10 @@
         <v>0</v>
       </c>
       <c r="C430" s="10" t="s">
-        <v>368</v>
+        <v>468</v>
       </c>
       <c r="D430" s="13">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E430" s="1">
         <v>0</v>
@@ -10293,10 +10293,10 @@
         <v>0</v>
       </c>
       <c r="C431" s="10" t="s">
-        <v>498</v>
+        <v>368</v>
       </c>
       <c r="D431" s="13">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E431" s="1">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="C432" s="10" t="s">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="D432" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E432" s="1">
         <v>0</v>
@@ -10321,16 +10321,16 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B433" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C433" s="10" t="s">
-        <v>238</v>
+        <v>469</v>
       </c>
       <c r="D433" s="13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E433" s="1">
         <v>0</v>
@@ -10344,10 +10344,10 @@
         <v>9</v>
       </c>
       <c r="C434" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D434" s="13">
-        <v>530</v>
+        <v>8</v>
       </c>
       <c r="E434" s="1">
         <v>0</v>
@@ -10355,16 +10355,16 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B435" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C435" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D435" s="13">
-        <v>400</v>
+        <v>530</v>
       </c>
       <c r="E435" s="1">
         <v>0</v>
@@ -10372,16 +10372,16 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B436" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C436" s="10" t="s">
-        <v>451</v>
+        <v>240</v>
       </c>
       <c r="D436" s="13">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="E436" s="1">
         <v>0</v>
@@ -10389,16 +10389,16 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B437" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C437" s="10" t="s">
-        <v>241</v>
+        <v>451</v>
       </c>
       <c r="D437" s="13">
-        <v>1200</v>
+        <v>50</v>
       </c>
       <c r="E437" s="1">
         <v>0</v>
@@ -10406,16 +10406,16 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="10" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B438" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C438" s="10" t="s">
-        <v>728</v>
+        <v>241</v>
       </c>
       <c r="D438" s="13">
-        <v>140</v>
+        <v>1200</v>
       </c>
       <c r="E438" s="1">
         <v>0</v>
@@ -10429,10 +10429,10 @@
         <v>0</v>
       </c>
       <c r="C439" s="10" t="s">
-        <v>452</v>
+        <v>727</v>
       </c>
       <c r="D439" s="13">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="E439" s="1">
         <v>0</v>
@@ -10440,16 +10440,16 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B440" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C440" s="10" t="s">
-        <v>242</v>
+        <v>452</v>
       </c>
       <c r="D440" s="13">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="E440" s="1">
         <v>0</v>
@@ -10460,13 +10460,13 @@
         <v>659</v>
       </c>
       <c r="B441" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C441" s="10" t="s">
         <v>242</v>
       </c>
       <c r="D441" s="13">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E441" s="1">
         <v>0</v>
@@ -10474,16 +10474,16 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="10" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B442" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C442" s="10" t="s">
-        <v>729</v>
+        <v>242</v>
       </c>
       <c r="D442" s="13">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E442" s="1">
         <v>0</v>
@@ -10491,16 +10491,16 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B443" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C443" s="10" t="s">
-        <v>374</v>
+        <v>728</v>
       </c>
       <c r="D443" s="13">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E443" s="1">
         <v>0</v>
@@ -10514,10 +10514,10 @@
         <v>39</v>
       </c>
       <c r="C444" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D444" s="13">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="E444" s="1">
         <v>0</v>
@@ -10531,10 +10531,10 @@
         <v>39</v>
       </c>
       <c r="C445" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D445" s="13">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="E445" s="1">
         <v>0</v>
@@ -10542,16 +10542,16 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="10" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="B446" s="10" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C446" s="10" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="D446" s="13">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E446" s="1">
         <v>0</v>
@@ -10559,16 +10559,16 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" s="10" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="B447" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C447" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D447" s="13">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="E447" s="1">
         <v>0</v>
@@ -10582,10 +10582,10 @@
         <v>0</v>
       </c>
       <c r="C448" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D448" s="13">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E448" s="1">
         <v>0</v>
@@ -10599,10 +10599,10 @@
         <v>0</v>
       </c>
       <c r="C449" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D449" s="13">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E449" s="1">
         <v>0</v>
@@ -10616,10 +10616,10 @@
         <v>0</v>
       </c>
       <c r="C450" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D450" s="13">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E450" s="1">
         <v>0</v>
@@ -10633,10 +10633,10 @@
         <v>0</v>
       </c>
       <c r="C451" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D451" s="13">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E451" s="1">
         <v>0</v>
@@ -10650,10 +10650,10 @@
         <v>0</v>
       </c>
       <c r="C452" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D452" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E452" s="1">
         <v>0</v>
@@ -10667,10 +10667,10 @@
         <v>0</v>
       </c>
       <c r="C453" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D453" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E453" s="1">
         <v>0</v>
@@ -10678,16 +10678,16 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="10" t="s">
-        <v>601</v>
+        <v>660</v>
       </c>
       <c r="B454" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C454" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D454" s="13">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E454" s="1">
         <v>0</v>
@@ -10701,10 +10701,10 @@
         <v>0</v>
       </c>
       <c r="C455" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D455" s="13">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E455" s="1">
         <v>0</v>
@@ -10718,10 +10718,10 @@
         <v>0</v>
       </c>
       <c r="C456" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D456" s="13">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E456" s="1">
         <v>0</v>
@@ -10735,10 +10735,10 @@
         <v>0</v>
       </c>
       <c r="C457" s="10" t="s">
-        <v>774</v>
+        <v>253</v>
       </c>
       <c r="D457" s="13">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E457" s="1">
         <v>0</v>
@@ -10752,7 +10752,7 @@
         <v>0</v>
       </c>
       <c r="C458" s="10" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D458" s="13">
         <v>16</v>
@@ -10769,7 +10769,7 @@
         <v>0</v>
       </c>
       <c r="C459" s="10" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D459" s="13">
         <v>16</v>
@@ -10780,16 +10780,16 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="10" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="B460" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C460" s="10" t="s">
-        <v>705</v>
+        <v>775</v>
       </c>
       <c r="D460" s="13">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E460" s="1">
         <v>0</v>
@@ -10803,10 +10803,10 @@
         <v>0</v>
       </c>
       <c r="C461" s="10" t="s">
-        <v>480</v>
+        <v>704</v>
       </c>
       <c r="D461" s="13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E461" s="1">
         <v>0</v>
@@ -10814,16 +10814,16 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="10" t="s">
-        <v>661</v>
+        <v>592</v>
       </c>
       <c r="B462" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C462" s="10" t="s">
-        <v>254</v>
+        <v>480</v>
       </c>
       <c r="D462" s="13">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E462" s="1">
         <v>0</v>
@@ -10831,16 +10831,16 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="10" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B463" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C463" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D463" s="13">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E463" s="1">
         <v>0</v>
@@ -10851,13 +10851,13 @@
         <v>662</v>
       </c>
       <c r="B464" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C464" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D464" s="13">
-        <v>830</v>
+        <v>47</v>
       </c>
       <c r="E464" s="1">
         <v>0</v>
@@ -10871,10 +10871,10 @@
         <v>39</v>
       </c>
       <c r="C465" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D465" s="13">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="E465" s="1">
         <v>0</v>
@@ -10888,10 +10888,10 @@
         <v>39</v>
       </c>
       <c r="C466" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D466" s="13">
-        <v>1250</v>
+        <v>850</v>
       </c>
       <c r="E466" s="1">
         <v>0</v>
@@ -10905,10 +10905,10 @@
         <v>39</v>
       </c>
       <c r="C467" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D467" s="13">
-        <v>400</v>
+        <v>1250</v>
       </c>
       <c r="E467" s="1">
         <v>0</v>
@@ -10916,16 +10916,16 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="10" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B468" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C468" s="10" t="s">
-        <v>786</v>
+        <v>259</v>
       </c>
       <c r="D468" s="13">
-        <v>3560</v>
+        <v>400</v>
       </c>
       <c r="E468" s="1">
         <v>0</v>
@@ -10939,10 +10939,10 @@
         <v>39</v>
       </c>
       <c r="C469" s="10" t="s">
-        <v>260</v>
+        <v>785</v>
       </c>
       <c r="D469" s="13">
-        <v>280</v>
+        <v>3760</v>
       </c>
       <c r="E469" s="1">
         <v>0</v>
@@ -10953,13 +10953,13 @@
         <v>661</v>
       </c>
       <c r="B470" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C470" s="10" t="s">
         <v>260</v>
       </c>
       <c r="D470" s="13">
-        <v>779</v>
+        <v>280</v>
       </c>
       <c r="E470" s="1">
         <v>0</v>
@@ -10967,16 +10967,16 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="10" t="s">
-        <v>561</v>
+        <v>661</v>
       </c>
       <c r="B471" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C471" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D471" s="13">
-        <v>273</v>
+        <v>779</v>
       </c>
       <c r="E471" s="1">
         <v>0</v>
@@ -10984,16 +10984,16 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="10" t="s">
-        <v>661</v>
+        <v>561</v>
       </c>
       <c r="B472" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C472" s="10" t="s">
-        <v>787</v>
+        <v>261</v>
       </c>
       <c r="D472" s="13">
-        <v>1872</v>
+        <v>273</v>
       </c>
       <c r="E472" s="1">
         <v>0</v>
@@ -11001,16 +11001,16 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>577</v>
+        <v>661</v>
       </c>
       <c r="B473" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C473" s="10" t="s">
-        <v>262</v>
+        <v>786</v>
       </c>
       <c r="D473" s="13">
-        <v>3</v>
+        <v>1672</v>
       </c>
       <c r="E473" s="1">
         <v>0</v>
@@ -11024,10 +11024,10 @@
         <v>0</v>
       </c>
       <c r="C474" s="10" t="s">
-        <v>509</v>
+        <v>262</v>
       </c>
       <c r="D474" s="13">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E474" s="1">
         <v>0</v>
@@ -11035,16 +11035,16 @@
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>615</v>
+        <v>577</v>
       </c>
       <c r="B475" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C475" s="10" t="s">
-        <v>263</v>
+        <v>509</v>
       </c>
       <c r="D475" s="13">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E475" s="1">
         <v>0</v>
@@ -11058,10 +11058,10 @@
         <v>0</v>
       </c>
       <c r="C476" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D476" s="13">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E476" s="1">
         <v>0</v>
@@ -11072,13 +11072,13 @@
         <v>615</v>
       </c>
       <c r="B477" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C477" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D477" s="13">
-        <v>840</v>
+        <v>6</v>
       </c>
       <c r="E477" s="1">
         <v>0</v>
@@ -11092,10 +11092,10 @@
         <v>39</v>
       </c>
       <c r="C478" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D478" s="13">
-        <v>15</v>
+        <v>840</v>
       </c>
       <c r="E478" s="1">
         <v>0</v>
@@ -11109,10 +11109,10 @@
         <v>39</v>
       </c>
       <c r="C479" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D479" s="13">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E479" s="1">
         <v>0</v>
@@ -11126,10 +11126,10 @@
         <v>39</v>
       </c>
       <c r="C480" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D480" s="13">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="E480" s="1">
         <v>0</v>
@@ -11143,10 +11143,10 @@
         <v>39</v>
       </c>
       <c r="C481" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D481" s="13">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E481" s="1">
         <v>0</v>
@@ -11160,10 +11160,10 @@
         <v>39</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D482" s="13">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E482" s="1">
         <v>0</v>
@@ -11177,10 +11177,10 @@
         <v>39</v>
       </c>
       <c r="C483" s="10" t="s">
-        <v>418</v>
+        <v>270</v>
       </c>
       <c r="D483" s="13">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E483" s="1">
         <v>0</v>
@@ -11188,16 +11188,16 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="10" t="s">
-        <v>558</v>
+        <v>615</v>
       </c>
       <c r="B484" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C484" s="10" t="s">
-        <v>271</v>
+        <v>418</v>
       </c>
       <c r="D484" s="13">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="E484" s="1">
         <v>0</v>
@@ -11205,16 +11205,16 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="10" t="s">
-        <v>661</v>
+        <v>558</v>
       </c>
       <c r="B485" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C485" s="10" t="s">
-        <v>788</v>
+        <v>271</v>
       </c>
       <c r="D485" s="13">
-        <v>575</v>
+        <v>75</v>
       </c>
       <c r="E485" s="1">
         <v>0</v>
@@ -11228,10 +11228,10 @@
         <v>39</v>
       </c>
       <c r="C486" s="10" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D486" s="13">
-        <v>9625</v>
+        <v>575</v>
       </c>
       <c r="E486" s="1">
         <v>0</v>
@@ -11245,10 +11245,10 @@
         <v>39</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D487" s="13">
-        <v>575</v>
+        <v>9500</v>
       </c>
       <c r="E487" s="1">
         <v>0</v>
@@ -11259,13 +11259,13 @@
         <v>661</v>
       </c>
       <c r="B488" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C488" s="10" t="s">
-        <v>272</v>
+        <v>789</v>
       </c>
       <c r="D488" s="13">
-        <v>40</v>
+        <v>575</v>
       </c>
       <c r="E488" s="1">
         <v>0</v>
@@ -11276,13 +11276,13 @@
         <v>661</v>
       </c>
       <c r="B489" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C489" s="10" t="s">
-        <v>791</v>
+        <v>272</v>
       </c>
       <c r="D489" s="13">
-        <v>5000</v>
+        <v>40</v>
       </c>
       <c r="E489" s="1">
         <v>0</v>
@@ -11290,16 +11290,16 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
-        <v>560</v>
+        <v>661</v>
       </c>
       <c r="B490" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C490" s="10" t="s">
-        <v>410</v>
+        <v>790</v>
       </c>
       <c r="D490" s="13">
-        <v>16400</v>
+        <v>5000</v>
       </c>
       <c r="E490" s="1">
         <v>0</v>
@@ -11307,16 +11307,16 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" s="10" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="B491" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C491" s="10" t="s">
-        <v>273</v>
+        <v>410</v>
       </c>
       <c r="D491" s="13">
-        <v>1</v>
+        <v>16400</v>
       </c>
       <c r="E491" s="1">
         <v>0</v>
@@ -11330,10 +11330,10 @@
         <v>0</v>
       </c>
       <c r="C492" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D492" s="13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E492" s="1">
         <v>0</v>
@@ -11347,10 +11347,10 @@
         <v>0</v>
       </c>
       <c r="C493" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D493" s="13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E493" s="1">
         <v>0</v>
@@ -11364,10 +11364,10 @@
         <v>0</v>
       </c>
       <c r="C494" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D494" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E494" s="1">
         <v>0</v>
@@ -11381,7 +11381,7 @@
         <v>0</v>
       </c>
       <c r="C495" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D495" s="13">
         <v>1</v>
@@ -11398,7 +11398,7 @@
         <v>0</v>
       </c>
       <c r="C496" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D496" s="13">
         <v>1</v>
@@ -11415,7 +11415,7 @@
         <v>0</v>
       </c>
       <c r="C497" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D497" s="13">
         <v>1</v>
@@ -11432,10 +11432,10 @@
         <v>0</v>
       </c>
       <c r="C498" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D498" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E498" s="1">
         <v>0</v>
@@ -11449,10 +11449,10 @@
         <v>0</v>
       </c>
       <c r="C499" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D499" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E499" s="1">
         <v>0</v>
@@ -11466,10 +11466,10 @@
         <v>0</v>
       </c>
       <c r="C500" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D500" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E500" s="1">
         <v>0</v>
@@ -11477,16 +11477,16 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B501" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C501" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D501" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E501" s="1">
         <v>0</v>
@@ -11494,16 +11494,16 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B502" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C502" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D502" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E502" s="1">
         <v>0</v>
@@ -11517,10 +11517,10 @@
         <v>0</v>
       </c>
       <c r="C503" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D503" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E503" s="1">
         <v>0</v>
@@ -11528,13 +11528,13 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B504" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C504" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D504" s="13">
         <v>1</v>
@@ -11545,13 +11545,13 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="B505" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C505" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D505" s="13">
         <v>1</v>
@@ -11562,13 +11562,13 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>620</v>
+        <v>558</v>
       </c>
       <c r="B506" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C506" s="10" t="s">
-        <v>484</v>
+        <v>287</v>
       </c>
       <c r="D506" s="13">
         <v>1</v>
@@ -11585,7 +11585,7 @@
         <v>0</v>
       </c>
       <c r="C507" s="10" t="s">
-        <v>288</v>
+        <v>484</v>
       </c>
       <c r="D507" s="13">
         <v>1</v>
@@ -11596,16 +11596,16 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>558</v>
+        <v>620</v>
       </c>
       <c r="B508" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C508" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D508" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E508" s="1">
         <v>0</v>
@@ -11613,16 +11613,16 @@
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="B509" s="10" t="s">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="C509" s="10" t="s">
-        <v>717</v>
+        <v>289</v>
       </c>
       <c r="D509" s="13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E509" s="1">
         <v>0</v>
@@ -11636,10 +11636,10 @@
         <v>523</v>
       </c>
       <c r="C510" s="10" t="s">
-        <v>686</v>
+        <v>716</v>
       </c>
       <c r="D510" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E510" s="1">
         <v>0</v>
@@ -11653,10 +11653,10 @@
         <v>523</v>
       </c>
       <c r="C511" s="10" t="s">
-        <v>766</v>
+        <v>686</v>
       </c>
       <c r="D511" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E511" s="1">
         <v>0</v>
@@ -11670,10 +11670,10 @@
         <v>523</v>
       </c>
       <c r="C512" s="10" t="s">
-        <v>524</v>
+        <v>765</v>
       </c>
       <c r="D512" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E512" s="1">
         <v>0</v>
@@ -11687,10 +11687,10 @@
         <v>523</v>
       </c>
       <c r="C513" s="10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D513" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E513" s="1">
         <v>0</v>
@@ -11698,16 +11698,16 @@
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>665</v>
+        <v>564</v>
       </c>
       <c r="B514" s="10" t="s">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="C514" s="10" t="s">
-        <v>704</v>
+        <v>525</v>
       </c>
       <c r="D514" s="13">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E514" s="1">
         <v>0</v>
@@ -11715,16 +11715,16 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>564</v>
+        <v>665</v>
       </c>
       <c r="B515" s="10" t="s">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="C515" s="10" t="s">
-        <v>526</v>
+        <v>703</v>
       </c>
       <c r="D515" s="13">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E515" s="1">
         <v>0</v>
@@ -11738,10 +11738,10 @@
         <v>523</v>
       </c>
       <c r="C516" s="10" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D516" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E516" s="1">
         <v>0</v>
@@ -11755,10 +11755,10 @@
         <v>523</v>
       </c>
       <c r="C517" s="10" t="s">
-        <v>690</v>
+        <v>527</v>
       </c>
       <c r="D517" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E517" s="1">
         <v>0</v>
@@ -11772,7 +11772,7 @@
         <v>523</v>
       </c>
       <c r="C518" s="10" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D518" s="13">
         <v>2</v>
@@ -11789,7 +11789,7 @@
         <v>523</v>
       </c>
       <c r="C519" s="10" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D519" s="13">
         <v>2</v>
@@ -11823,7 +11823,7 @@
         <v>523</v>
       </c>
       <c r="C521" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D521" s="13">
         <v>1</v>
@@ -12010,7 +12010,7 @@
         <v>523</v>
       </c>
       <c r="C532" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D532" s="13">
         <v>4</v>
@@ -12044,7 +12044,7 @@
         <v>523</v>
       </c>
       <c r="C534" s="10" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D534" s="13">
         <v>5</v>
@@ -12061,7 +12061,7 @@
         <v>523</v>
       </c>
       <c r="C535" s="10" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D535" s="13">
         <v>2</v>
@@ -12078,7 +12078,7 @@
         <v>523</v>
       </c>
       <c r="C536" s="10" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D536" s="13">
         <v>3</v>
@@ -12089,13 +12089,13 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" s="10" t="s">
+        <v>754</v>
+      </c>
+      <c r="B537" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C537" s="10" t="s">
         <v>755</v>
-      </c>
-      <c r="B537" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C537" s="10" t="s">
-        <v>756</v>
       </c>
       <c r="D537" s="13">
         <v>8</v>
@@ -12112,7 +12112,7 @@
         <v>523</v>
       </c>
       <c r="C538" s="10" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D538" s="13">
         <v>1</v>
@@ -12146,7 +12146,7 @@
         <v>523</v>
       </c>
       <c r="C540" s="10" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D540" s="13">
         <v>1</v>
@@ -12163,7 +12163,7 @@
         <v>523</v>
       </c>
       <c r="C541" s="10" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D541" s="13">
         <v>2</v>
@@ -12602,7 +12602,7 @@
         <v>564</v>
       </c>
       <c r="B567" s="10" t="s">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="C567" s="10" t="s">
         <v>300</v>
@@ -12619,7 +12619,7 @@
         <v>564</v>
       </c>
       <c r="B568" s="10" t="s">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="C568" s="10" t="s">
         <v>300</v>
@@ -12724,7 +12724,7 @@
         <v>523</v>
       </c>
       <c r="C574" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D574" s="13">
         <v>2</v>
@@ -12741,7 +12741,7 @@
         <v>523</v>
       </c>
       <c r="C575" s="10" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D575" s="13">
         <v>1</v>
@@ -12758,7 +12758,7 @@
         <v>523</v>
       </c>
       <c r="C576" s="10" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D576" s="13">
         <v>2</v>
@@ -12792,7 +12792,7 @@
         <v>523</v>
       </c>
       <c r="C578" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D578" s="13">
         <v>1</v>
@@ -12809,7 +12809,7 @@
         <v>523</v>
       </c>
       <c r="C579" s="10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D579" s="13">
         <v>5</v>
@@ -12826,7 +12826,7 @@
         <v>523</v>
       </c>
       <c r="C580" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D580" s="13">
         <v>2</v>
@@ -12843,7 +12843,7 @@
         <v>523</v>
       </c>
       <c r="C581" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D581" s="13">
         <v>2</v>
@@ -12860,7 +12860,7 @@
         <v>523</v>
       </c>
       <c r="C582" s="10" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D582" s="13">
         <v>4</v>
@@ -12877,7 +12877,7 @@
         <v>523</v>
       </c>
       <c r="C583" s="10" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D583" s="13">
         <v>4</v>
@@ -12894,7 +12894,7 @@
         <v>523</v>
       </c>
       <c r="C584" s="10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D584" s="13">
         <v>2</v>
@@ -13030,7 +13030,7 @@
         <v>523</v>
       </c>
       <c r="C592" s="10" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D592" s="13">
         <v>3</v>
@@ -13047,7 +13047,7 @@
         <v>523</v>
       </c>
       <c r="C593" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D593" s="13">
         <v>3</v>
@@ -13064,7 +13064,7 @@
         <v>523</v>
       </c>
       <c r="C594" s="10" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D594" s="13">
         <v>2</v>
@@ -13081,7 +13081,7 @@
         <v>523</v>
       </c>
       <c r="C595" s="10" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D595" s="13">
         <v>3</v>
@@ -13115,7 +13115,7 @@
         <v>39</v>
       </c>
       <c r="C597" s="10" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D597" s="13">
         <v>2000</v>
@@ -13132,7 +13132,7 @@
         <v>39</v>
       </c>
       <c r="C598" s="10" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D598" s="13">
         <v>2500</v>
@@ -13149,7 +13149,7 @@
         <v>39</v>
       </c>
       <c r="C599" s="10" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="D599" s="13">
         <v>2400</v>
@@ -13285,7 +13285,7 @@
         <v>39</v>
       </c>
       <c r="C607" s="10" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D607" s="13">
         <v>1900</v>
@@ -13319,7 +13319,7 @@
         <v>39</v>
       </c>
       <c r="C609" s="10" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D609" s="13">
         <v>2500</v>
@@ -13336,7 +13336,7 @@
         <v>39</v>
       </c>
       <c r="C610" s="10" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D610" s="13">
         <v>2400</v>
@@ -13353,7 +13353,7 @@
         <v>39</v>
       </c>
       <c r="C611" s="10" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D611" s="13">
         <v>800</v>
@@ -13370,7 +13370,7 @@
         <v>39</v>
       </c>
       <c r="C612" s="10" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D612" s="13">
         <v>1600</v>
@@ -13387,7 +13387,7 @@
         <v>39</v>
       </c>
       <c r="C613" s="10" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D613" s="13">
         <v>1000</v>
@@ -13404,7 +13404,7 @@
         <v>39</v>
       </c>
       <c r="C614" s="10" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D614" s="13">
         <v>1600</v>
@@ -13421,7 +13421,7 @@
         <v>39</v>
       </c>
       <c r="C615" s="10" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D615" s="13">
         <v>800</v>
@@ -13438,10 +13438,10 @@
         <v>39</v>
       </c>
       <c r="C616" s="10" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D616" s="13">
-        <v>1400</v>
+        <v>1250</v>
       </c>
       <c r="E616" s="1">
         <v>0</v>
@@ -13455,10 +13455,10 @@
         <v>39</v>
       </c>
       <c r="C617" s="10" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="D617" s="13">
-        <v>1850</v>
+        <v>1550</v>
       </c>
       <c r="E617" s="1">
         <v>0</v>
@@ -13489,7 +13489,7 @@
         <v>39</v>
       </c>
       <c r="C619" s="10" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D619" s="13">
         <v>1700</v>
@@ -13506,7 +13506,7 @@
         <v>39</v>
       </c>
       <c r="C620" s="10" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="D620" s="13">
         <v>1000</v>
@@ -13639,7 +13639,7 @@
         <v>670</v>
       </c>
       <c r="B628" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C628" s="10" t="s">
         <v>317</v>
@@ -13656,7 +13656,7 @@
         <v>670</v>
       </c>
       <c r="B629" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C629" s="10" t="s">
         <v>317</v>
@@ -13741,13 +13741,13 @@
         <v>671</v>
       </c>
       <c r="B634" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C634" s="10" t="s">
         <v>321</v>
       </c>
       <c r="D634" s="13">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="E634" s="1">
         <v>0</v>
@@ -13758,13 +13758,13 @@
         <v>671</v>
       </c>
       <c r="B635" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C635" s="10" t="s">
         <v>321</v>
       </c>
       <c r="D635" s="13">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="E635" s="1">
         <v>0</v>
@@ -13840,13 +13840,13 @@
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C640" s="1" t="s">
         <v>730</v>
-      </c>
-      <c r="B640" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C640" s="1" t="s">
-        <v>731</v>
       </c>
       <c r="D640" s="14">
         <v>100</v>
@@ -13874,13 +13874,13 @@
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B642" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D642" s="14">
         <v>35</v>
@@ -13925,13 +13925,13 @@
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B645" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C645" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D645" s="14">
         <v>30</v>
@@ -14220,7 +14220,7 @@
         <v>0</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D662" s="14">
         <v>465</v>
@@ -14642,13 +14642,13 @@
         <v>684</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C687" s="1" t="s">
         <v>353</v>
       </c>
       <c r="D687" s="14">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="E687" s="1">
         <v>0</v>
@@ -14659,13 +14659,13 @@
         <v>684</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C688" s="1" t="s">
         <v>353</v>
       </c>
       <c r="D688" s="14">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="E688" s="1">
         <v>0</v>
@@ -14696,7 +14696,7 @@
         <v>0</v>
       </c>
       <c r="C690" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D690" s="14">
         <v>235</v>
@@ -14713,7 +14713,7 @@
         <v>0</v>
       </c>
       <c r="C691" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D691" s="14">
         <v>150</v>
@@ -14727,13 +14727,13 @@
         <v>684</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C692" s="1" t="s">
         <v>355</v>
       </c>
       <c r="D692" s="14">
-        <v>200</v>
+        <v>950</v>
       </c>
       <c r="E692" s="1">
         <v>0</v>
@@ -14744,13 +14744,13 @@
         <v>684</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C693" s="1" t="s">
         <v>355</v>
       </c>
       <c r="D693" s="14">
-        <v>950</v>
+        <v>200</v>
       </c>
       <c r="E693" s="1">
         <v>0</v>
@@ -14812,13 +14812,13 @@
         <v>684</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C697" s="1" t="s">
         <v>358</v>
       </c>
       <c r="D697" s="14">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="E697" s="1">
         <v>0</v>
@@ -14829,13 +14829,13 @@
         <v>684</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C698" s="1" t="s">
         <v>358</v>
       </c>
       <c r="D698" s="14">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="E698" s="1">
         <v>0</v>
@@ -14863,13 +14863,13 @@
         <v>684</v>
       </c>
       <c r="B700" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C700" s="1" t="s">
         <v>360</v>
       </c>
       <c r="D700" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E700" s="1">
         <v>0</v>
@@ -14880,13 +14880,13 @@
         <v>684</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C701" s="1" t="s">
         <v>360</v>
       </c>
       <c r="D701" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E701" s="1">
         <v>0</v>

--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3E0A1D-206B-41C0-A56C-FEC1FF8F166B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E867F3C2-90E7-4644-B9BC-5CE920143DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -2296,9 +2296,6 @@
     <t>قازان غاز فضي مصري</t>
   </si>
   <si>
-    <t>خزانة 60 سم ابيض مع مراية وطني</t>
-  </si>
-  <si>
     <t>خزانة 60 سم بني مع مراية وطني</t>
   </si>
   <si>
@@ -2450,6 +2447,9 @@
   </si>
   <si>
     <t>موتير 2 حصان دوبل توربين ليو LEO 2ACM150</t>
+  </si>
+  <si>
+    <t>جرن مجلى صناعي 60*45</t>
   </si>
 </sst>
 </file>
@@ -3070,7 +3070,7 @@
         <v>39</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D7" s="13">
         <v>600</v>
@@ -3124,7 +3124,7 @@
         <v>417</v>
       </c>
       <c r="D10" s="13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -3175,7 +3175,7 @@
         <v>7</v>
       </c>
       <c r="D13" s="13">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>741</v>
       </c>
       <c r="D16" s="13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D27" s="13">
         <v>5</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D28" s="13">
         <v>3</v>
@@ -3478,7 +3478,7 @@
         <v>0</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D31" s="13">
         <v>5</v>
@@ -4053,13 +4053,13 @@
         <v>575</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>45</v>
       </c>
       <c r="D65" s="13">
-        <v>31</v>
+        <v>200</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
@@ -4070,13 +4070,13 @@
         <v>575</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>45</v>
       </c>
       <c r="D66" s="13">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E66" s="1">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         <v>577</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D75" s="13">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
@@ -4240,13 +4240,13 @@
         <v>577</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D76" s="13">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
@@ -4359,13 +4359,13 @@
         <v>581</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D83" s="13">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="E83" s="1">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>581</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D84" s="13">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="E84" s="1">
         <v>0</v>
@@ -4427,13 +4427,13 @@
         <v>581</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C87" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D87" s="13">
-        <v>1350</v>
+        <v>2725</v>
       </c>
       <c r="E87" s="1">
         <v>0</v>
@@ -4444,13 +4444,13 @@
         <v>581</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D88" s="13">
-        <v>2725</v>
+        <v>1350</v>
       </c>
       <c r="E88" s="1">
         <v>0</v>
@@ -4668,10 +4668,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>503</v>
+        <v>796</v>
       </c>
       <c r="D101" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E101" s="1">
         <v>0</v>
@@ -4679,13 +4679,13 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>568</v>
+        <v>586</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>682</v>
+        <v>503</v>
       </c>
       <c r="D102" s="13">
         <v>3</v>
@@ -4702,10 +4702,10 @@
         <v>0</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>506</v>
+        <v>682</v>
       </c>
       <c r="D103" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E103" s="1">
         <v>0</v>
@@ -4713,16 +4713,16 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>425</v>
+        <v>506</v>
       </c>
       <c r="D104" s="13">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E104" s="1">
         <v>0</v>
@@ -4730,16 +4730,16 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
-        <v>587</v>
+        <v>552</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D105" s="13">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E105" s="1">
         <v>0</v>
@@ -4753,10 +4753,10 @@
         <v>0</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>62</v>
+        <v>421</v>
       </c>
       <c r="D106" s="13">
-        <v>800</v>
+        <v>35</v>
       </c>
       <c r="E106" s="1">
         <v>0</v>
@@ -4767,13 +4767,13 @@
         <v>587</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>774</v>
+        <v>62</v>
       </c>
       <c r="D107" s="13">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E107" s="1">
         <v>0</v>
@@ -4784,13 +4784,13 @@
         <v>587</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>63</v>
+        <v>773</v>
       </c>
       <c r="D108" s="13">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="E108" s="1">
         <v>0</v>
@@ -4804,10 +4804,10 @@
         <v>0</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D109" s="13">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="E109" s="1">
         <v>0</v>
@@ -4821,10 +4821,10 @@
         <v>0</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D110" s="13">
-        <v>50</v>
+        <v>195</v>
       </c>
       <c r="E110" s="1">
         <v>0</v>
@@ -4838,10 +4838,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D111" s="13">
-        <v>320</v>
+        <v>50</v>
       </c>
       <c r="E111" s="1">
         <v>0</v>
@@ -4849,16 +4849,16 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B112" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D112" s="13">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E112" s="1">
         <v>0</v>
@@ -4872,10 +4872,10 @@
         <v>0</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D113" s="13">
-        <v>54</v>
+        <v>312</v>
       </c>
       <c r="E113" s="1">
         <v>0</v>
@@ -4883,16 +4883,16 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D114" s="13">
-        <v>2100</v>
+        <v>54</v>
       </c>
       <c r="E114" s="1">
         <v>0</v>
@@ -4900,16 +4900,16 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D115" s="13">
-        <v>90</v>
+        <v>2100</v>
       </c>
       <c r="E115" s="1">
         <v>0</v>
@@ -4917,16 +4917,16 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D116" s="13">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E116" s="1">
         <v>0</v>
@@ -4934,16 +4934,16 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B117" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>427</v>
+        <v>71</v>
       </c>
       <c r="D117" s="13">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="E117" s="1">
         <v>0</v>
@@ -4957,10 +4957,10 @@
         <v>0</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D118" s="13">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E118" s="1">
         <v>0</v>
@@ -4968,16 +4968,16 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B119" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>496</v>
+        <v>428</v>
       </c>
       <c r="D119" s="13">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E119" s="1">
         <v>0</v>
@@ -4991,10 +4991,10 @@
         <v>0</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D120" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" s="1">
         <v>0</v>
@@ -5002,16 +5002,16 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B121" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>745</v>
+        <v>497</v>
       </c>
       <c r="D121" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" s="1">
         <v>0</v>
@@ -5025,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D122" s="13">
         <v>2</v>
@@ -5158,13 +5158,13 @@
         <v>593</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D130" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
@@ -5175,13 +5175,13 @@
         <v>593</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D131" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -5192,13 +5192,13 @@
         <v>593</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>79</v>
       </c>
       <c r="D132" s="13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -5209,13 +5209,13 @@
         <v>593</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>79</v>
       </c>
       <c r="D133" s="13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -5226,13 +5226,13 @@
         <v>593</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D134" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -5243,13 +5243,13 @@
         <v>593</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D135" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
@@ -5260,13 +5260,13 @@
         <v>593</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>81</v>
       </c>
       <c r="D136" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
@@ -5277,13 +5277,13 @@
         <v>593</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>81</v>
       </c>
       <c r="D137" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
@@ -5294,13 +5294,13 @@
         <v>593</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D138" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
@@ -5311,13 +5311,13 @@
         <v>593</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D139" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
@@ -5957,13 +5957,13 @@
         <v>600</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>111</v>
       </c>
       <c r="D177" s="13">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E177" s="1">
         <v>0</v>
@@ -5974,13 +5974,13 @@
         <v>600</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>111</v>
       </c>
       <c r="D178" s="13">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E178" s="1">
         <v>0</v>
@@ -6144,13 +6144,13 @@
         <v>587</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C188" s="10" t="s">
         <v>499</v>
       </c>
       <c r="D188" s="13">
-        <v>1600</v>
+        <v>240</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
@@ -6161,13 +6161,13 @@
         <v>587</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C189" s="10" t="s">
         <v>499</v>
       </c>
       <c r="D189" s="13">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
@@ -6212,13 +6212,13 @@
         <v>587</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C192" s="10" t="s">
         <v>500</v>
       </c>
       <c r="D192" s="13">
-        <v>4400</v>
+        <v>600</v>
       </c>
       <c r="E192" s="1">
         <v>0</v>
@@ -6229,13 +6229,13 @@
         <v>587</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C193" s="10" t="s">
         <v>500</v>
       </c>
       <c r="D193" s="13">
-        <v>600</v>
+        <v>4400</v>
       </c>
       <c r="E193" s="1">
         <v>0</v>
@@ -6283,7 +6283,7 @@
         <v>39</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D196" s="13">
         <v>2040</v>
@@ -6742,7 +6742,7 @@
         <v>39</v>
       </c>
       <c r="C223" s="10" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D223" s="13">
         <v>100</v>
@@ -6759,7 +6759,7 @@
         <v>9</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D224" s="13">
         <v>4</v>
@@ -7014,7 +7014,7 @@
         <v>0</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D239" s="13">
         <v>10</v>
@@ -7031,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D240" s="13">
         <v>10</v>
@@ -7048,7 +7048,7 @@
         <v>0</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D241" s="13">
         <v>15</v>
@@ -7099,7 +7099,7 @@
         <v>39</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D244" s="13">
         <v>800</v>
@@ -7164,13 +7164,13 @@
         <v>616</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C248" s="10" t="s">
         <v>146</v>
       </c>
       <c r="D248" s="13">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="E248" s="1">
         <v>0</v>
@@ -7181,13 +7181,13 @@
         <v>616</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C249" s="10" t="s">
         <v>146</v>
       </c>
       <c r="D249" s="13">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="E249" s="1">
         <v>0</v>
@@ -7218,7 +7218,7 @@
         <v>0</v>
       </c>
       <c r="C251" s="10" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D251" s="13">
         <v>40</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="C259" s="10" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D259" s="13">
         <v>49</v>
@@ -7864,7 +7864,7 @@
         <v>0</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D289" s="13">
         <v>30</v>
@@ -8255,7 +8255,7 @@
         <v>0</v>
       </c>
       <c r="C312" s="10" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D312" s="13">
         <v>75</v>
@@ -8286,13 +8286,13 @@
         <v>623</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C314" s="10" t="s">
         <v>181</v>
       </c>
       <c r="D314" s="13">
-        <v>125</v>
+        <v>800</v>
       </c>
       <c r="E314" s="1">
         <v>0</v>
@@ -8303,13 +8303,13 @@
         <v>623</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C315" s="10" t="s">
         <v>181</v>
       </c>
       <c r="D315" s="13">
-        <v>800</v>
+        <v>102</v>
       </c>
       <c r="E315" s="1">
         <v>0</v>
@@ -8320,13 +8320,13 @@
         <v>623</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C316" s="10" t="s">
         <v>181</v>
       </c>
       <c r="D316" s="13">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="E316" s="1">
         <v>0</v>
@@ -8340,7 +8340,7 @@
         <v>0</v>
       </c>
       <c r="C317" s="10" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D317" s="13">
         <v>20</v>
@@ -8374,7 +8374,7 @@
         <v>9</v>
       </c>
       <c r="C319" s="10" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D319" s="13">
         <v>450</v>
@@ -8473,13 +8473,13 @@
         <v>626</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C325" s="10" t="s">
         <v>183</v>
       </c>
       <c r="D325" s="13">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="E325" s="1">
         <v>0</v>
@@ -8490,13 +8490,13 @@
         <v>626</v>
       </c>
       <c r="B326" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C326" s="10" t="s">
         <v>183</v>
       </c>
       <c r="D326" s="13">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="E326" s="1">
         <v>0</v>
@@ -9102,7 +9102,7 @@
         <v>596</v>
       </c>
       <c r="B362" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C362" s="10" t="s">
         <v>200</v>
@@ -9119,7 +9119,7 @@
         <v>596</v>
       </c>
       <c r="B363" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C363" s="10" t="s">
         <v>200</v>
@@ -9173,7 +9173,7 @@
         <v>9</v>
       </c>
       <c r="C366" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D366" s="13">
         <v>4</v>
@@ -9258,7 +9258,7 @@
         <v>0</v>
       </c>
       <c r="C371" s="10" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D371" s="13">
         <v>24</v>
@@ -9629,13 +9629,13 @@
         <v>639</v>
       </c>
       <c r="B393" s="10" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C393" s="10" t="s">
         <v>217</v>
       </c>
       <c r="D393" s="13">
-        <v>2550</v>
+        <v>360</v>
       </c>
       <c r="E393" s="1">
         <v>0</v>
@@ -9646,13 +9646,13 @@
         <v>639</v>
       </c>
       <c r="B394" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C394" s="10" t="s">
         <v>217</v>
       </c>
       <c r="D394" s="13">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="E394" s="1">
         <v>0</v>
@@ -9663,13 +9663,13 @@
         <v>639</v>
       </c>
       <c r="B395" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C395" s="10" t="s">
         <v>217</v>
       </c>
       <c r="D395" s="13">
-        <v>200</v>
+        <v>2550</v>
       </c>
       <c r="E395" s="1">
         <v>0</v>
@@ -9901,13 +9901,13 @@
         <v>644</v>
       </c>
       <c r="B409" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C409" s="10" t="s">
         <v>229</v>
       </c>
       <c r="D409" s="13">
-        <v>14</v>
+        <v>316</v>
       </c>
       <c r="E409" s="1">
         <v>0</v>
@@ -9918,13 +9918,13 @@
         <v>644</v>
       </c>
       <c r="B410" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C410" s="10" t="s">
         <v>229</v>
       </c>
       <c r="D410" s="13">
-        <v>316</v>
+        <v>14</v>
       </c>
       <c r="E410" s="1">
         <v>0</v>
@@ -10122,13 +10122,13 @@
         <v>647</v>
       </c>
       <c r="B422" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C422" s="10" t="s">
         <v>233</v>
       </c>
       <c r="D422" s="13">
-        <v>300</v>
+        <v>1775</v>
       </c>
       <c r="E422" s="1">
         <v>0</v>
@@ -10139,13 +10139,13 @@
         <v>647</v>
       </c>
       <c r="B423" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C423" s="10" t="s">
         <v>233</v>
       </c>
       <c r="D423" s="13">
-        <v>1775</v>
+        <v>300</v>
       </c>
       <c r="E423" s="1">
         <v>0</v>
@@ -10445,13 +10445,13 @@
         <v>653</v>
       </c>
       <c r="B441" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C441" s="10" t="s">
         <v>242</v>
       </c>
       <c r="D441" s="13">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E441" s="1">
         <v>0</v>
@@ -10462,13 +10462,13 @@
         <v>653</v>
       </c>
       <c r="B442" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C442" s="10" t="s">
         <v>242</v>
       </c>
       <c r="D442" s="13">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E442" s="1">
         <v>0</v>
@@ -10737,7 +10737,7 @@
         <v>0</v>
       </c>
       <c r="C458" s="10" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D458" s="13">
         <v>16</v>
@@ -10754,7 +10754,7 @@
         <v>0</v>
       </c>
       <c r="C459" s="10" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D459" s="13">
         <v>16</v>
@@ -10771,7 +10771,7 @@
         <v>0</v>
       </c>
       <c r="C460" s="10" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D460" s="13">
         <v>16</v>
@@ -10924,7 +10924,7 @@
         <v>39</v>
       </c>
       <c r="C469" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D469" s="13">
         <v>3760</v>
@@ -10938,13 +10938,13 @@
         <v>655</v>
       </c>
       <c r="B470" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C470" s="10" t="s">
         <v>260</v>
       </c>
       <c r="D470" s="13">
-        <v>779</v>
+        <v>280</v>
       </c>
       <c r="E470" s="1">
         <v>0</v>
@@ -10955,13 +10955,13 @@
         <v>655</v>
       </c>
       <c r="B471" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C471" s="10" t="s">
         <v>260</v>
       </c>
       <c r="D471" s="13">
-        <v>280</v>
+        <v>779</v>
       </c>
       <c r="E471" s="1">
         <v>0</v>
@@ -10992,7 +10992,7 @@
         <v>39</v>
       </c>
       <c r="C473" s="10" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D473" s="13">
         <v>1672</v>
@@ -11213,7 +11213,7 @@
         <v>39</v>
       </c>
       <c r="C486" s="10" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D486" s="13">
         <v>575</v>
@@ -11230,7 +11230,7 @@
         <v>39</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D487" s="13">
         <v>9500</v>
@@ -11247,7 +11247,7 @@
         <v>39</v>
       </c>
       <c r="C488" s="10" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D488" s="13">
         <v>575</v>
@@ -11281,7 +11281,7 @@
         <v>39</v>
       </c>
       <c r="C490" s="10" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D490" s="13">
         <v>5000</v>
@@ -11655,7 +11655,7 @@
         <v>517</v>
       </c>
       <c r="C512" s="10" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D512" s="13">
         <v>3</v>
@@ -11757,7 +11757,7 @@
         <v>517</v>
       </c>
       <c r="C518" s="10" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D518" s="13">
         <v>3</v>
@@ -11825,7 +11825,7 @@
         <v>517</v>
       </c>
       <c r="C522" s="10" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D522" s="13">
         <v>1</v>
@@ -12063,7 +12063,7 @@
         <v>517</v>
       </c>
       <c r="C536" s="10" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D536" s="13">
         <v>3</v>
@@ -12074,13 +12074,13 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="B537" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C537" s="10" t="s">
         <v>747</v>
-      </c>
-      <c r="B537" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C537" s="10" t="s">
-        <v>748</v>
       </c>
       <c r="D537" s="13">
         <v>8</v>
@@ -12587,7 +12587,7 @@
         <v>558</v>
       </c>
       <c r="B567" s="10" t="s">
-        <v>517</v>
+        <v>0</v>
       </c>
       <c r="C567" s="10" t="s">
         <v>300</v>
@@ -12604,7 +12604,7 @@
         <v>558</v>
       </c>
       <c r="B568" s="10" t="s">
-        <v>0</v>
+        <v>517</v>
       </c>
       <c r="C568" s="10" t="s">
         <v>300</v>
@@ -13015,7 +13015,7 @@
         <v>517</v>
       </c>
       <c r="C592" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D592" s="13">
         <v>3</v>
@@ -13032,7 +13032,7 @@
         <v>517</v>
       </c>
       <c r="C593" s="10" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D593" s="13">
         <v>3</v>
@@ -13049,7 +13049,7 @@
         <v>517</v>
       </c>
       <c r="C594" s="10" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D594" s="13">
         <v>2</v>
@@ -13066,7 +13066,7 @@
         <v>517</v>
       </c>
       <c r="C595" s="10" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D595" s="13">
         <v>3</v>
@@ -13100,7 +13100,7 @@
         <v>39</v>
       </c>
       <c r="C597" s="10" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D597" s="13">
         <v>2000</v>
@@ -13117,7 +13117,7 @@
         <v>39</v>
       </c>
       <c r="C598" s="10" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D598" s="13">
         <v>2500</v>
@@ -13134,7 +13134,7 @@
         <v>39</v>
       </c>
       <c r="C599" s="10" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D599" s="13">
         <v>2400</v>
@@ -13185,7 +13185,7 @@
         <v>39</v>
       </c>
       <c r="C602" s="10" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D602" s="13">
         <v>1900</v>
@@ -13219,7 +13219,7 @@
         <v>39</v>
       </c>
       <c r="C604" s="10" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D604" s="13">
         <v>2500</v>
@@ -13236,7 +13236,7 @@
         <v>39</v>
       </c>
       <c r="C605" s="10" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D605" s="13">
         <v>2400</v>
@@ -13338,7 +13338,7 @@
         <v>39</v>
       </c>
       <c r="C611" s="10" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="D611" s="13">
         <v>1250</v>
@@ -13355,7 +13355,7 @@
         <v>39</v>
       </c>
       <c r="C612" s="10" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D612" s="13">
         <v>1550</v>
@@ -13389,7 +13389,7 @@
         <v>39</v>
       </c>
       <c r="C614" s="10" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D614" s="13">
         <v>1700</v>
@@ -13406,7 +13406,7 @@
         <v>39</v>
       </c>
       <c r="C615" s="10" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D615" s="13">
         <v>1000</v>
@@ -13641,13 +13641,13 @@
         <v>664</v>
       </c>
       <c r="B629" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C629" s="10" t="s">
         <v>321</v>
       </c>
       <c r="D629" s="13">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="E629" s="1">
         <v>0</v>
@@ -13658,13 +13658,13 @@
         <v>664</v>
       </c>
       <c r="B630" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C630" s="10" t="s">
         <v>321</v>
       </c>
       <c r="D630" s="13">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="E630" s="1">
         <v>0</v>
@@ -14542,13 +14542,13 @@
         <v>677</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C682" s="1" t="s">
         <v>353</v>
       </c>
       <c r="D682" s="14">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="E682" s="1">
         <v>0</v>
@@ -14559,13 +14559,13 @@
         <v>677</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C683" s="1" t="s">
         <v>353</v>
       </c>
       <c r="D683" s="14">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="E683" s="1">
         <v>0</v>
@@ -14596,7 +14596,7 @@
         <v>0</v>
       </c>
       <c r="C685" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D685" s="14">
         <v>235</v>
@@ -14627,13 +14627,13 @@
         <v>677</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C687" s="1" t="s">
         <v>355</v>
       </c>
       <c r="D687" s="14">
-        <v>200</v>
+        <v>950</v>
       </c>
       <c r="E687" s="1">
         <v>0</v>
@@ -14644,13 +14644,13 @@
         <v>677</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C688" s="1" t="s">
         <v>355</v>
       </c>
       <c r="D688" s="14">
-        <v>950</v>
+        <v>200</v>
       </c>
       <c r="E688" s="1">
         <v>0</v>
@@ -14763,13 +14763,13 @@
         <v>677</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C695" s="1" t="s">
         <v>360</v>
       </c>
       <c r="D695" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E695" s="1">
         <v>0</v>
@@ -14780,13 +14780,13 @@
         <v>677</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C696" s="1" t="s">
         <v>360</v>
       </c>
       <c r="D696" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E696" s="1">
         <v>0</v>
@@ -14797,13 +14797,13 @@
         <v>677</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C697" s="1" t="s">
         <v>361</v>
       </c>
       <c r="D697" s="14">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="E697" s="1">
         <v>0</v>
@@ -14814,13 +14814,13 @@
         <v>677</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C698" s="1" t="s">
         <v>361</v>
       </c>
       <c r="D698" s="14">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E698" s="1">
         <v>0</v>
@@ -14902,7 +14902,7 @@
         <v>بار دوش دوبل غروهي صيني</v>
       </c>
       <c r="C6" s="4">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4"/>
     </row>
@@ -14938,7 +14938,7 @@
         <v>بار دوش شاور بانل دوبل كروم اسود تركي بريفا PRIVA</v>
       </c>
       <c r="C9" s="4">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D9" s="4"/>
     </row>

--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC96F3CA-CCC8-474D-95B7-D8C9E8E00E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69FD367-2A14-464A-95CE-40B1D64EF256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="797">
   <si>
     <t>3-ديوان</t>
   </si>
@@ -1702,9 +1702,6 @@
     <t>موتير غاطس فرامة ليو LEO LSWM30A</t>
   </si>
   <si>
-    <t>موتير غاطس ليو LEO 5DWM4/6.1.1P</t>
-  </si>
-  <si>
     <t>موتير غاطس ليو LEO 5DWM4/8.1.5P</t>
   </si>
   <si>
@@ -2447,6 +2444,12 @@
   </si>
   <si>
     <t>ايزي فليكس مع صباب 1 1/4 تركي</t>
+  </si>
+  <si>
+    <t>نربيج زراعي 1 1/2" 50 ملم 25 متر اسود</t>
+  </si>
+  <si>
+    <t>نربيج زراعي 1 1/2" 50 ملم 50 متر اسود</t>
   </si>
 </sst>
 </file>
@@ -2973,7 +2976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E5C9A6-5EC3-4592-9122-0E1001CE6231}">
-  <dimension ref="A1:E697"/>
+  <dimension ref="A1:E698"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.8984375" style="2" bestFit="1" customWidth="1"/>
@@ -3010,7 +3013,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>0</v>
@@ -3027,7 +3030,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>0</v>
@@ -3044,7 +3047,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>0</v>
@@ -3061,13 +3064,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D7" s="13">
         <v>600</v>
@@ -3078,7 +3081,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>0</v>
@@ -3095,7 +3098,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>0</v>
@@ -3112,13 +3115,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D10" s="13">
         <v>500</v>
@@ -3129,7 +3132,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>0</v>
@@ -3146,7 +3149,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>0</v>
@@ -3163,7 +3166,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>0</v>
@@ -3180,7 +3183,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>0</v>
@@ -3189,7 +3192,7 @@
         <v>7</v>
       </c>
       <c r="D14" s="13">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -3197,7 +3200,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>0</v>
@@ -3214,7 +3217,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>9</v>
@@ -3231,13 +3234,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D17" s="13">
         <v>6</v>
@@ -3248,7 +3251,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>0</v>
@@ -3265,13 +3268,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D19" s="13">
         <v>1</v>
@@ -3282,7 +3285,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>0</v>
@@ -3299,7 +3302,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>0</v>
@@ -3316,7 +3319,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>0</v>
@@ -3333,7 +3336,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>0</v>
@@ -3350,7 +3353,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>0</v>
@@ -3367,7 +3370,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>0</v>
@@ -3384,7 +3387,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>0</v>
@@ -3401,13 +3404,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D27" s="13">
         <v>8</v>
@@ -3418,13 +3421,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D28" s="13">
         <v>5</v>
@@ -3435,13 +3438,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D29" s="13">
         <v>3</v>
@@ -3452,7 +3455,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>0</v>
@@ -3469,7 +3472,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>0</v>
@@ -3486,13 +3489,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D32" s="13">
         <v>5</v>
@@ -3503,7 +3506,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>0</v>
@@ -3520,7 +3523,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>0</v>
@@ -3537,7 +3540,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>0</v>
@@ -3554,7 +3557,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>0</v>
@@ -3571,7 +3574,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>0</v>
@@ -3588,7 +3591,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>0</v>
@@ -3605,7 +3608,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>0</v>
@@ -3622,7 +3625,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>0</v>
@@ -3639,7 +3642,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>0</v>
@@ -3656,7 +3659,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>0</v>
@@ -3673,7 +3676,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>0</v>
@@ -3690,7 +3693,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>0</v>
@@ -3707,7 +3710,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>0</v>
@@ -3724,7 +3727,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>0</v>
@@ -3741,7 +3744,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>0</v>
@@ -3758,7 +3761,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>0</v>
@@ -3775,7 +3778,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>0</v>
@@ -3792,7 +3795,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>0</v>
@@ -3809,7 +3812,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>0</v>
@@ -3826,7 +3829,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>0</v>
@@ -3843,7 +3846,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>0</v>
@@ -3860,7 +3863,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>0</v>
@@ -3877,7 +3880,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>39</v>
@@ -3894,7 +3897,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>39</v>
@@ -3911,7 +3914,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>39</v>
@@ -3928,7 +3931,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>0</v>
@@ -3945,7 +3948,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>0</v>
@@ -3962,7 +3965,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>0</v>
@@ -3979,7 +3982,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B61" s="10" t="s">
         <v>0</v>
@@ -3996,7 +3999,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>0</v>
@@ -4013,16 +4016,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D63" s="13">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -4030,16 +4033,16 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D64" s="13">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
@@ -4047,7 +4050,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>9</v>
@@ -4064,7 +4067,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>9</v>
@@ -4081,7 +4084,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>0</v>
@@ -4098,7 +4101,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>9</v>
@@ -4115,7 +4118,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>0</v>
@@ -4132,7 +4135,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>0</v>
@@ -4149,7 +4152,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B71" s="10" t="s">
         <v>0</v>
@@ -4166,16 +4169,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D72" s="13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
@@ -4183,16 +4186,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D73" s="13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
@@ -4200,7 +4203,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>9</v>
@@ -4217,7 +4220,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>0</v>
@@ -4234,16 +4237,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D76" s="13">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
@@ -4251,16 +4254,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D77" s="13">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E77" s="1">
         <v>0</v>
@@ -4268,7 +4271,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>0</v>
@@ -4285,7 +4288,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>0</v>
@@ -4302,7 +4305,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B80" s="10" t="s">
         <v>39</v>
@@ -4319,13 +4322,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
+        <v>708</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C81" s="10" t="s">
         <v>709</v>
-      </c>
-      <c r="B81" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>710</v>
       </c>
       <c r="D81" s="13">
         <v>70</v>
@@ -4336,7 +4339,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>0</v>
@@ -4353,7 +4356,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B83" s="10" t="s">
         <v>39</v>
@@ -4370,7 +4373,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>39</v>
@@ -4387,7 +4390,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>0</v>
@@ -4404,7 +4407,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>39</v>
@@ -4421,13 +4424,13 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D87" s="13">
         <v>170</v>
@@ -4438,7 +4441,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>9</v>
@@ -4455,7 +4458,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B89" s="10" t="s">
         <v>0</v>
@@ -4472,7 +4475,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B90" s="10" t="s">
         <v>0</v>
@@ -4489,7 +4492,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>9</v>
@@ -4506,7 +4509,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>0</v>
@@ -4523,7 +4526,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B93" s="10" t="s">
         <v>0</v>
@@ -4540,7 +4543,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B94" s="10" t="s">
         <v>0</v>
@@ -4557,7 +4560,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B95" s="10" t="s">
         <v>39</v>
@@ -4574,7 +4577,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B96" s="10" t="s">
         <v>39</v>
@@ -4591,7 +4594,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B97" s="10" t="s">
         <v>0</v>
@@ -4608,7 +4611,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>9</v>
@@ -4625,7 +4628,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B99" s="10" t="s">
         <v>9</v>
@@ -4642,7 +4645,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B100" s="10" t="s">
         <v>0</v>
@@ -4659,13 +4662,13 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D101" s="13">
         <v>4</v>
@@ -4676,13 +4679,13 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D102" s="13">
         <v>1</v>
@@ -4693,7 +4696,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B103" s="10" t="s">
         <v>0</v>
@@ -4710,13 +4713,13 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B104" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D104" s="13">
         <v>1</v>
@@ -4727,7 +4730,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B105" s="10" t="s">
         <v>0</v>
@@ -4744,7 +4747,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>0</v>
@@ -4761,7 +4764,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>0</v>
@@ -4778,13 +4781,13 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D108" s="13">
         <v>600</v>
@@ -4795,7 +4798,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B109" s="10" t="s">
         <v>0</v>
@@ -4812,7 +4815,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>0</v>
@@ -4829,7 +4832,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B111" s="10" t="s">
         <v>0</v>
@@ -4846,7 +4849,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B112" s="10" t="s">
         <v>0</v>
@@ -4863,7 +4866,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B113" s="10" t="s">
         <v>0</v>
@@ -4880,7 +4883,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B114" s="10" t="s">
         <v>0</v>
@@ -4897,7 +4900,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B115" s="10" t="s">
         <v>39</v>
@@ -4914,7 +4917,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>0</v>
@@ -4931,7 +4934,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B117" s="10" t="s">
         <v>0</v>
@@ -4948,7 +4951,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B118" s="10" t="s">
         <v>0</v>
@@ -4965,7 +4968,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B119" s="10" t="s">
         <v>0</v>
@@ -4982,7 +4985,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B120" s="10" t="s">
         <v>0</v>
@@ -4999,7 +5002,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B121" s="10" t="s">
         <v>0</v>
@@ -5016,13 +5019,13 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D122" s="13">
         <v>2</v>
@@ -5033,7 +5036,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B123" s="10" t="s">
         <v>39</v>
@@ -5050,7 +5053,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B124" s="10" t="s">
         <v>39</v>
@@ -5067,7 +5070,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B125" s="10" t="s">
         <v>39</v>
@@ -5084,7 +5087,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B126" s="10" t="s">
         <v>39</v>
@@ -5101,7 +5104,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B127" s="10" t="s">
         <v>39</v>
@@ -5118,7 +5121,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B128" s="10" t="s">
         <v>0</v>
@@ -5135,7 +5138,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B129" s="10" t="s">
         <v>39</v>
@@ -5152,16 +5155,16 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D130" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
@@ -5169,16 +5172,16 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D131" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -5186,16 +5189,16 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>79</v>
       </c>
       <c r="D132" s="13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -5203,16 +5206,16 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>79</v>
       </c>
       <c r="D133" s="13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -5220,16 +5223,16 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D134" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -5237,16 +5240,16 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D135" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
@@ -5254,7 +5257,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B136" s="10" t="s">
         <v>39</v>
@@ -5271,7 +5274,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B137" s="10" t="s">
         <v>0</v>
@@ -5288,16 +5291,16 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D138" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
@@ -5305,16 +5308,16 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D139" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
@@ -5322,7 +5325,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B140" s="10" t="s">
         <v>39</v>
@@ -5339,7 +5342,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B141" s="10" t="s">
         <v>0</v>
@@ -5356,7 +5359,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B142" s="10" t="s">
         <v>39</v>
@@ -5373,7 +5376,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B143" s="10" t="s">
         <v>39</v>
@@ -5390,7 +5393,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B144" s="10" t="s">
         <v>39</v>
@@ -5407,7 +5410,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B145" s="10" t="s">
         <v>39</v>
@@ -5424,7 +5427,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B146" s="10" t="s">
         <v>39</v>
@@ -5441,7 +5444,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B147" s="10" t="s">
         <v>39</v>
@@ -5458,7 +5461,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B148" s="10" t="s">
         <v>39</v>
@@ -5475,7 +5478,7 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B149" s="10" t="s">
         <v>39</v>
@@ -5492,7 +5495,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B150" s="10" t="s">
         <v>0</v>
@@ -5509,7 +5512,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B151" s="10" t="s">
         <v>39</v>
@@ -5526,7 +5529,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B152" s="10" t="s">
         <v>39</v>
@@ -5543,7 +5546,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B153" s="10" t="s">
         <v>39</v>
@@ -5560,7 +5563,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B154" s="10" t="s">
         <v>0</v>
@@ -5577,7 +5580,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B155" s="10" t="s">
         <v>0</v>
@@ -5594,7 +5597,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B156" s="10" t="s">
         <v>0</v>
@@ -5611,7 +5614,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B157" s="10" t="s">
         <v>39</v>
@@ -5628,7 +5631,7 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B158" s="10" t="s">
         <v>0</v>
@@ -5645,7 +5648,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B159" s="10" t="s">
         <v>0</v>
@@ -5662,7 +5665,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B160" s="10" t="s">
         <v>0</v>
@@ -5679,7 +5682,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B161" s="10" t="s">
         <v>0</v>
@@ -5696,7 +5699,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B162" s="10" t="s">
         <v>39</v>
@@ -5713,7 +5716,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B163" s="10" t="s">
         <v>0</v>
@@ -5730,7 +5733,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B164" s="10" t="s">
         <v>0</v>
@@ -5747,7 +5750,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B165" s="10" t="s">
         <v>0</v>
@@ -5764,7 +5767,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B166" s="10" t="s">
         <v>0</v>
@@ -5781,7 +5784,7 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B167" s="10" t="s">
         <v>39</v>
@@ -5798,7 +5801,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B168" s="10" t="s">
         <v>0</v>
@@ -5815,7 +5818,7 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B169" s="10" t="s">
         <v>0</v>
@@ -5832,7 +5835,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B170" s="10" t="s">
         <v>0</v>
@@ -5849,7 +5852,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B171" s="10" t="s">
         <v>0</v>
@@ -5866,7 +5869,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B172" s="10" t="s">
         <v>0</v>
@@ -5883,7 +5886,7 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B173" s="10" t="s">
         <v>0</v>
@@ -5900,7 +5903,7 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B174" s="10" t="s">
         <v>0</v>
@@ -5917,16 +5920,16 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C175" s="10" t="s">
         <v>110</v>
       </c>
       <c r="D175" s="13">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E175" s="1">
         <v>0</v>
@@ -5934,16 +5937,16 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C176" s="10" t="s">
         <v>110</v>
       </c>
       <c r="D176" s="13">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E176" s="1">
         <v>0</v>
@@ -5951,7 +5954,7 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B177" s="10" t="s">
         <v>0</v>
@@ -5968,7 +5971,7 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B178" s="10" t="s">
         <v>39</v>
@@ -5985,7 +5988,7 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B179" s="10" t="s">
         <v>39</v>
@@ -6002,7 +6005,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B180" s="10" t="s">
         <v>39</v>
@@ -6019,7 +6022,7 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B181" s="10" t="s">
         <v>0</v>
@@ -6036,7 +6039,7 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B182" s="10" t="s">
         <v>39</v>
@@ -6053,7 +6056,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B183" s="10" t="s">
         <v>0</v>
@@ -6070,13 +6073,13 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B184" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C184" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D184" s="13">
         <v>14</v>
@@ -6087,7 +6090,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B185" s="10" t="s">
         <v>9</v>
@@ -6104,16 +6107,16 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D186" s="13">
-        <v>400</v>
+        <v>1920</v>
       </c>
       <c r="E186" s="1">
         <v>0</v>
@@ -6121,16 +6124,16 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C187" s="10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D187" s="13">
-        <v>1920</v>
+        <v>400</v>
       </c>
       <c r="E187" s="1">
         <v>0</v>
@@ -6138,16 +6141,16 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C188" s="10" t="s">
         <v>497</v>
       </c>
       <c r="D188" s="13">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
@@ -6155,16 +6158,16 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C189" s="10" t="s">
         <v>497</v>
       </c>
       <c r="D189" s="13">
-        <v>1600</v>
+        <v>240</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
@@ -6172,13 +6175,13 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B190" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D190" s="13">
         <v>800</v>
@@ -6189,7 +6192,7 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B191" s="10" t="s">
         <v>0</v>
@@ -6206,16 +6209,16 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C192" s="10" t="s">
         <v>498</v>
       </c>
       <c r="D192" s="13">
-        <v>4400</v>
+        <v>600</v>
       </c>
       <c r="E192" s="1">
         <v>0</v>
@@ -6223,16 +6226,16 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C193" s="10" t="s">
         <v>498</v>
       </c>
       <c r="D193" s="13">
-        <v>600</v>
+        <v>4400</v>
       </c>
       <c r="E193" s="1">
         <v>0</v>
@@ -6240,13 +6243,13 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B194" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D194" s="13">
         <v>2880</v>
@@ -6257,7 +6260,7 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B195" s="10" t="s">
         <v>0</v>
@@ -6274,13 +6277,13 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B196" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D196" s="13">
         <v>2040</v>
@@ -6291,13 +6294,13 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B197" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D197" s="13">
         <v>1080</v>
@@ -6308,7 +6311,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B198" s="10" t="s">
         <v>39</v>
@@ -6325,7 +6328,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="10" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B199" s="10" t="s">
         <v>0</v>
@@ -6342,7 +6345,7 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B200" s="10" t="s">
         <v>39</v>
@@ -6359,7 +6362,7 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B201" s="10" t="s">
         <v>39</v>
@@ -6376,7 +6379,7 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B202" s="10" t="s">
         <v>39</v>
@@ -6393,7 +6396,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B203" s="10" t="s">
         <v>39</v>
@@ -6410,7 +6413,7 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B204" s="10" t="s">
         <v>0</v>
@@ -6427,7 +6430,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B205" s="10" t="s">
         <v>0</v>
@@ -6444,7 +6447,7 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B206" s="10" t="s">
         <v>0</v>
@@ -6461,7 +6464,7 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B207" s="10" t="s">
         <v>0</v>
@@ -6478,7 +6481,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B208" s="10" t="s">
         <v>0</v>
@@ -6495,7 +6498,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B209" s="10" t="s">
         <v>0</v>
@@ -6512,7 +6515,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B210" s="10" t="s">
         <v>0</v>
@@ -6529,7 +6532,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B211" s="10" t="s">
         <v>0</v>
@@ -6546,7 +6549,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B212" s="10" t="s">
         <v>0</v>
@@ -6563,7 +6566,7 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B213" s="10" t="s">
         <v>0</v>
@@ -6580,13 +6583,13 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B214" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C214" s="10" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D214" s="13">
         <v>22</v>
@@ -6597,7 +6600,7 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B215" s="10" t="s">
         <v>0</v>
@@ -6614,7 +6617,7 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B216" s="10" t="s">
         <v>0</v>
@@ -6631,7 +6634,7 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B217" s="10" t="s">
         <v>0</v>
@@ -6648,7 +6651,7 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B218" s="10" t="s">
         <v>0</v>
@@ -6665,7 +6668,7 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B219" s="10" t="s">
         <v>0</v>
@@ -6682,7 +6685,7 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B220" s="10" t="s">
         <v>0</v>
@@ -6699,7 +6702,7 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B221" s="10" t="s">
         <v>0</v>
@@ -6716,7 +6719,7 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B222" s="10" t="s">
         <v>0</v>
@@ -6733,13 +6736,13 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B223" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C223" s="10" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D223" s="13">
         <v>100</v>
@@ -6750,16 +6753,16 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B224" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D224" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E224" s="1">
         <v>0</v>
@@ -6767,16 +6770,16 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B225" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C225" s="10" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D225" s="13">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E225" s="1">
         <v>0</v>
@@ -6784,7 +6787,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B226" s="10" t="s">
         <v>0</v>
@@ -6801,7 +6804,7 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B227" s="10" t="s">
         <v>0</v>
@@ -6818,13 +6821,13 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B228" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C228" s="10" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D228" s="13">
         <v>10</v>
@@ -6835,7 +6838,7 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B229" s="10" t="s">
         <v>0</v>
@@ -6852,7 +6855,7 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B230" s="10" t="s">
         <v>0</v>
@@ -6869,7 +6872,7 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B231" s="10" t="s">
         <v>0</v>
@@ -6886,7 +6889,7 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B232" s="10" t="s">
         <v>0</v>
@@ -6903,7 +6906,7 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B233" s="10" t="s">
         <v>0</v>
@@ -6920,7 +6923,7 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B234" s="10" t="s">
         <v>39</v>
@@ -6929,7 +6932,7 @@
         <v>139</v>
       </c>
       <c r="D234" s="13">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="E234" s="1">
         <v>0</v>
@@ -6937,7 +6940,7 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B235" s="10" t="s">
         <v>39</v>
@@ -6946,7 +6949,7 @@
         <v>140</v>
       </c>
       <c r="D235" s="13">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="E235" s="1">
         <v>0</v>
@@ -6954,7 +6957,7 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B236" s="10" t="s">
         <v>0</v>
@@ -6971,7 +6974,7 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B237" s="10" t="s">
         <v>0</v>
@@ -6988,7 +6991,7 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B238" s="10" t="s">
         <v>0</v>
@@ -7005,13 +7008,13 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B239" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D239" s="13">
         <v>10</v>
@@ -7022,13 +7025,13 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B240" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D240" s="13">
         <v>10</v>
@@ -7039,13 +7042,13 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B241" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D241" s="13">
         <v>15</v>
@@ -7056,7 +7059,7 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B242" s="10" t="s">
         <v>0</v>
@@ -7073,7 +7076,7 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B243" s="10" t="s">
         <v>9</v>
@@ -7090,13 +7093,13 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B244" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D244" s="13">
         <v>800</v>
@@ -7107,13 +7110,13 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B245" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C245" s="10" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D245" s="13">
         <v>2000</v>
@@ -7124,13 +7127,13 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B246" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C246" s="10" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D246" s="13">
         <v>1800</v>
@@ -7141,7 +7144,7 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B247" s="10" t="s">
         <v>39</v>
@@ -7158,16 +7161,16 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C248" s="10" t="s">
         <v>146</v>
       </c>
       <c r="D248" s="13">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="E248" s="1">
         <v>0</v>
@@ -7175,16 +7178,16 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C249" s="10" t="s">
         <v>146</v>
       </c>
       <c r="D249" s="13">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="E249" s="1">
         <v>0</v>
@@ -7192,7 +7195,7 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B250" s="10" t="s">
         <v>39</v>
@@ -7209,13 +7212,13 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B251" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C251" s="10" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D251" s="13">
         <v>40</v>
@@ -7226,7 +7229,7 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B252" s="10" t="s">
         <v>0</v>
@@ -7243,7 +7246,7 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B253" s="10" t="s">
         <v>39</v>
@@ -7260,7 +7263,7 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B254" s="10" t="s">
         <v>0</v>
@@ -7277,7 +7280,7 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B255" s="10" t="s">
         <v>39</v>
@@ -7294,7 +7297,7 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B256" s="10" t="s">
         <v>0</v>
@@ -7311,7 +7314,7 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B257" s="10" t="s">
         <v>39</v>
@@ -7328,7 +7331,7 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B258" s="10" t="s">
         <v>0</v>
@@ -7345,13 +7348,13 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B259" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C259" s="10" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D259" s="13">
         <v>49</v>
@@ -7362,7 +7365,7 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B260" s="10" t="s">
         <v>0</v>
@@ -7379,7 +7382,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B261" s="10" t="s">
         <v>0</v>
@@ -7396,7 +7399,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B262" s="10" t="s">
         <v>0</v>
@@ -7413,7 +7416,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B263" s="10" t="s">
         <v>0</v>
@@ -7430,7 +7433,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B264" s="10" t="s">
         <v>0</v>
@@ -7447,7 +7450,7 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B265" s="10" t="s">
         <v>0</v>
@@ -7464,7 +7467,7 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B266" s="10" t="s">
         <v>0</v>
@@ -7481,7 +7484,7 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B267" s="10" t="s">
         <v>0</v>
@@ -7498,7 +7501,7 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B268" s="10" t="s">
         <v>0</v>
@@ -7515,7 +7518,7 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B269" s="10" t="s">
         <v>0</v>
@@ -7532,7 +7535,7 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B270" s="10" t="s">
         <v>0</v>
@@ -7549,7 +7552,7 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B271" s="10" t="s">
         <v>0</v>
@@ -7566,7 +7569,7 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B272" s="10" t="s">
         <v>9</v>
@@ -7583,7 +7586,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B273" s="10" t="s">
         <v>9</v>
@@ -7600,7 +7603,7 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B274" s="10" t="s">
         <v>9</v>
@@ -7617,13 +7620,13 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B275" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C275" s="10" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D275" s="13">
         <v>100</v>
@@ -7634,7 +7637,7 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B276" s="10" t="s">
         <v>0</v>
@@ -7651,7 +7654,7 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B277" s="10" t="s">
         <v>0</v>
@@ -7668,7 +7671,7 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B278" s="10" t="s">
         <v>0</v>
@@ -7685,7 +7688,7 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B279" s="10" t="s">
         <v>0</v>
@@ -7702,7 +7705,7 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B280" s="10" t="s">
         <v>0</v>
@@ -7719,7 +7722,7 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B281" s="10" t="s">
         <v>0</v>
@@ -7736,7 +7739,7 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B282" s="10" t="s">
         <v>0</v>
@@ -7753,7 +7756,7 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B283" s="10" t="s">
         <v>0</v>
@@ -7770,7 +7773,7 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B284" s="10" t="s">
         <v>0</v>
@@ -7787,7 +7790,7 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="10" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B285" s="10" t="s">
         <v>0</v>
@@ -7804,7 +7807,7 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B286" s="10" t="s">
         <v>0</v>
@@ -7821,7 +7824,7 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B287" s="10" t="s">
         <v>0</v>
@@ -7838,7 +7841,7 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B288" s="10" t="s">
         <v>0</v>
@@ -7855,13 +7858,13 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B289" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D289" s="13">
         <v>30</v>
@@ -7872,13 +7875,13 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B290" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C290" s="10" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D290" s="13">
         <v>4</v>
@@ -7889,7 +7892,7 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B291" s="10" t="s">
         <v>0</v>
@@ -7906,13 +7909,13 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B292" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C292" s="10" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D292" s="13">
         <v>5</v>
@@ -7923,7 +7926,7 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B293" s="10" t="s">
         <v>0</v>
@@ -7940,7 +7943,7 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B294" s="10" t="s">
         <v>0</v>
@@ -7957,7 +7960,7 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B295" s="10" t="s">
         <v>0</v>
@@ -7974,7 +7977,7 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B296" s="10" t="s">
         <v>0</v>
@@ -7991,7 +7994,7 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B297" s="10" t="s">
         <v>0</v>
@@ -8008,7 +8011,7 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B298" s="10" t="s">
         <v>39</v>
@@ -8025,7 +8028,7 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B299" s="10" t="s">
         <v>0</v>
@@ -8042,7 +8045,7 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B300" s="10" t="s">
         <v>0</v>
@@ -8059,7 +8062,7 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B301" s="10" t="s">
         <v>39</v>
@@ -8076,7 +8079,7 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B302" s="10" t="s">
         <v>39</v>
@@ -8093,7 +8096,7 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B303" s="10" t="s">
         <v>9</v>
@@ -8110,7 +8113,7 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B304" s="10" t="s">
         <v>9</v>
@@ -8127,7 +8130,7 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B305" s="10" t="s">
         <v>39</v>
@@ -8144,7 +8147,7 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B306" s="10" t="s">
         <v>9</v>
@@ -8161,13 +8164,13 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B307" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C307" s="10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D307" s="13">
         <v>250</v>
@@ -8178,7 +8181,7 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B308" s="10" t="s">
         <v>0</v>
@@ -8195,7 +8198,7 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B309" s="10" t="s">
         <v>9</v>
@@ -8212,7 +8215,7 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B310" s="10" t="s">
         <v>39</v>
@@ -8229,7 +8232,7 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B311" s="10" t="s">
         <v>39</v>
@@ -8246,13 +8249,13 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B312" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C312" s="10" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D312" s="13">
         <v>75</v>
@@ -8263,7 +8266,7 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B313" s="10" t="s">
         <v>39</v>
@@ -8272,7 +8275,7 @@
         <v>371</v>
       </c>
       <c r="D313" s="13">
-        <v>1560</v>
+        <v>1500</v>
       </c>
       <c r="E313" s="1">
         <v>0</v>
@@ -8280,7 +8283,7 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B314" s="10" t="s">
         <v>39</v>
@@ -8297,7 +8300,7 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B315" s="10" t="s">
         <v>0</v>
@@ -8314,7 +8317,7 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B316" s="10" t="s">
         <v>9</v>
@@ -8331,13 +8334,13 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B317" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C317" s="10" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D317" s="13">
         <v>20</v>
@@ -8348,7 +8351,7 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B318" s="10" t="s">
         <v>9</v>
@@ -8365,13 +8368,13 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B319" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C319" s="10" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D319" s="13">
         <v>450</v>
@@ -8382,7 +8385,7 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B320" s="10" t="s">
         <v>39</v>
@@ -8399,7 +8402,7 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B321" s="10" t="s">
         <v>0</v>
@@ -8416,7 +8419,7 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B322" s="10" t="s">
         <v>9</v>
@@ -8433,7 +8436,7 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B323" s="10" t="s">
         <v>39</v>
@@ -8450,7 +8453,7 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B324" s="10" t="s">
         <v>0</v>
@@ -8467,16 +8470,16 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C325" s="10" t="s">
         <v>183</v>
       </c>
       <c r="D325" s="13">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="E325" s="1">
         <v>0</v>
@@ -8484,16 +8487,16 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B326" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C326" s="10" t="s">
         <v>183</v>
       </c>
       <c r="D326" s="13">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="E326" s="1">
         <v>0</v>
@@ -8501,7 +8504,7 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B327" s="10" t="s">
         <v>39</v>
@@ -8518,7 +8521,7 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B328" s="10" t="s">
         <v>39</v>
@@ -8527,7 +8530,7 @@
         <v>185</v>
       </c>
       <c r="D328" s="13">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="E328" s="1">
         <v>0</v>
@@ -8535,7 +8538,7 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B329" s="10" t="s">
         <v>9</v>
@@ -8552,7 +8555,7 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B330" s="10" t="s">
         <v>9</v>
@@ -8569,13 +8572,13 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="10" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B331" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C331" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D331" s="13">
         <v>1</v>
@@ -8586,7 +8589,7 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B332" s="10" t="s">
         <v>9</v>
@@ -8603,7 +8606,7 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B333" s="10" t="s">
         <v>9</v>
@@ -8620,7 +8623,7 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B334" s="10" t="s">
         <v>9</v>
@@ -8637,7 +8640,7 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B335" s="10" t="s">
         <v>39</v>
@@ -8654,7 +8657,7 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B336" s="10" t="s">
         <v>39</v>
@@ -8671,7 +8674,7 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B337" s="10" t="s">
         <v>39</v>
@@ -8688,7 +8691,7 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B338" s="10" t="s">
         <v>0</v>
@@ -8705,7 +8708,7 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B339" s="10" t="s">
         <v>39</v>
@@ -8722,7 +8725,7 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B340" s="10" t="s">
         <v>39</v>
@@ -8739,7 +8742,7 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B341" s="10" t="s">
         <v>39</v>
@@ -8756,7 +8759,7 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B342" s="10" t="s">
         <v>39</v>
@@ -8773,7 +8776,7 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B343" s="10" t="s">
         <v>0</v>
@@ -8790,7 +8793,7 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B344" s="10" t="s">
         <v>39</v>
@@ -8807,10 +8810,10 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B345" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C345" s="10" t="s">
         <v>191</v>
@@ -8824,10 +8827,10 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C346" s="10" t="s">
         <v>191</v>
@@ -8841,16 +8844,16 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B347" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C347" s="10" t="s">
         <v>192</v>
       </c>
       <c r="D347" s="13">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E347" s="1">
         <v>0</v>
@@ -8858,16 +8861,16 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B348" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C348" s="10" t="s">
         <v>192</v>
       </c>
       <c r="D348" s="13">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E348" s="1">
         <v>0</v>
@@ -8875,7 +8878,7 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B349" s="10" t="s">
         <v>0</v>
@@ -8892,7 +8895,7 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B350" s="10" t="s">
         <v>39</v>
@@ -8909,7 +8912,7 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B351" s="10" t="s">
         <v>39</v>
@@ -8926,13 +8929,13 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B352" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C352" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D352" s="13">
         <v>90</v>
@@ -8943,13 +8946,13 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="10" t="s">
+        <v>713</v>
+      </c>
+      <c r="B353" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C353" s="10" t="s">
         <v>714</v>
-      </c>
-      <c r="B353" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C353" s="10" t="s">
-        <v>715</v>
       </c>
       <c r="D353" s="13">
         <v>50</v>
@@ -8960,7 +8963,7 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B354" s="10" t="s">
         <v>39</v>
@@ -8977,7 +8980,7 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B355" s="10" t="s">
         <v>39</v>
@@ -8994,7 +8997,7 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B356" s="10" t="s">
         <v>39</v>
@@ -9011,7 +9014,7 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B357" s="10" t="s">
         <v>0</v>
@@ -9028,7 +9031,7 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B358" s="10" t="s">
         <v>0</v>
@@ -9045,7 +9048,7 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B359" s="10" t="s">
         <v>0</v>
@@ -9062,7 +9065,7 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B360" s="10" t="s">
         <v>0</v>
@@ -9079,7 +9082,7 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B361" s="10" t="s">
         <v>0</v>
@@ -9096,10 +9099,10 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B362" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C362" s="10" t="s">
         <v>200</v>
@@ -9113,10 +9116,10 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B363" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C363" s="10" t="s">
         <v>200</v>
@@ -9130,7 +9133,7 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B364" s="10" t="s">
         <v>0</v>
@@ -9147,7 +9150,7 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B365" s="10" t="s">
         <v>0</v>
@@ -9164,16 +9167,16 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B366" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C366" s="10" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D366" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E366" s="1">
         <v>0</v>
@@ -9181,7 +9184,7 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B367" s="10" t="s">
         <v>0</v>
@@ -9198,16 +9201,16 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B368" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C368" s="10" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D368" s="13">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E368" s="1">
         <v>0</v>
@@ -9215,7 +9218,7 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B369" s="10" t="s">
         <v>0</v>
@@ -9232,13 +9235,13 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B370" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C370" s="10" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D370" s="13">
         <v>14</v>
@@ -9249,13 +9252,13 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B371" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C371" s="10" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D371" s="13">
         <v>24</v>
@@ -9266,7 +9269,7 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B372" s="10" t="s">
         <v>0</v>
@@ -9283,7 +9286,7 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B373" s="10" t="s">
         <v>0</v>
@@ -9300,7 +9303,7 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B374" s="10" t="s">
         <v>9</v>
@@ -9317,7 +9320,7 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B375" s="10" t="s">
         <v>0</v>
@@ -9334,7 +9337,7 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B376" s="10" t="s">
         <v>0</v>
@@ -9351,7 +9354,7 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B377" s="10" t="s">
         <v>0</v>
@@ -9368,7 +9371,7 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B378" s="10" t="s">
         <v>0</v>
@@ -9385,7 +9388,7 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B379" s="10" t="s">
         <v>0</v>
@@ -9402,7 +9405,7 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B380" s="10" t="s">
         <v>39</v>
@@ -9419,7 +9422,7 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B381" s="10" t="s">
         <v>39</v>
@@ -9436,7 +9439,7 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B382" s="10" t="s">
         <v>39</v>
@@ -9453,7 +9456,7 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B383" s="10" t="s">
         <v>39</v>
@@ -9470,7 +9473,7 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B384" s="10" t="s">
         <v>39</v>
@@ -9487,7 +9490,7 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B385" s="10" t="s">
         <v>0</v>
@@ -9504,7 +9507,7 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B386" s="10" t="s">
         <v>0</v>
@@ -9521,7 +9524,7 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B387" s="10" t="s">
         <v>0</v>
@@ -9538,7 +9541,7 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B388" s="10" t="s">
         <v>0</v>
@@ -9555,7 +9558,7 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B389" s="10" t="s">
         <v>39</v>
@@ -9572,7 +9575,7 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B390" s="10" t="s">
         <v>0</v>
@@ -9589,7 +9592,7 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B391" s="10" t="s">
         <v>0</v>
@@ -9606,7 +9609,7 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B392" s="10" t="s">
         <v>39</v>
@@ -9623,16 +9626,16 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B393" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C393" s="10" t="s">
         <v>217</v>
       </c>
       <c r="D393" s="13">
-        <v>2550</v>
+        <v>200</v>
       </c>
       <c r="E393" s="1">
         <v>0</v>
@@ -9640,16 +9643,16 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B394" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C394" s="10" t="s">
         <v>217</v>
       </c>
       <c r="D394" s="13">
-        <v>200</v>
+        <v>2550</v>
       </c>
       <c r="E394" s="1">
         <v>0</v>
@@ -9657,7 +9660,7 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B395" s="10" t="s">
         <v>39</v>
@@ -9674,7 +9677,7 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B396" s="10" t="s">
         <v>0</v>
@@ -9691,7 +9694,7 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B397" s="10" t="s">
         <v>39</v>
@@ -9708,7 +9711,7 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B398" s="10" t="s">
         <v>0</v>
@@ -9725,7 +9728,7 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B399" s="10" t="s">
         <v>0</v>
@@ -9742,7 +9745,7 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B400" s="10" t="s">
         <v>0</v>
@@ -9759,7 +9762,7 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B401" s="10" t="s">
         <v>0</v>
@@ -9776,7 +9779,7 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B402" s="10" t="s">
         <v>0</v>
@@ -9793,7 +9796,7 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B403" s="10" t="s">
         <v>0</v>
@@ -9810,7 +9813,7 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B404" s="10" t="s">
         <v>0</v>
@@ -9827,7 +9830,7 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B405" s="10" t="s">
         <v>0</v>
@@ -9844,7 +9847,7 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B406" s="10" t="s">
         <v>0</v>
@@ -9861,7 +9864,7 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B407" s="10" t="s">
         <v>9</v>
@@ -9878,16 +9881,16 @@
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B408" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C408" s="10" t="s">
         <v>229</v>
       </c>
       <c r="D408" s="13">
-        <v>14</v>
+        <v>316</v>
       </c>
       <c r="E408" s="1">
         <v>0</v>
@@ -9895,16 +9898,16 @@
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B409" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C409" s="10" t="s">
         <v>229</v>
       </c>
       <c r="D409" s="13">
-        <v>316</v>
+        <v>14</v>
       </c>
       <c r="E409" s="1">
         <v>0</v>
@@ -9912,7 +9915,7 @@
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B410" s="10" t="s">
         <v>9</v>
@@ -9929,7 +9932,7 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B411" s="10" t="s">
         <v>9</v>
@@ -9946,16 +9949,16 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B412" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C412" s="10" t="s">
         <v>232</v>
       </c>
       <c r="D412" s="13">
-        <v>129</v>
+        <v>1200</v>
       </c>
       <c r="E412" s="1">
         <v>0</v>
@@ -9963,16 +9966,16 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B413" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C413" s="10" t="s">
         <v>232</v>
       </c>
       <c r="D413" s="13">
-        <v>1200</v>
+        <v>129</v>
       </c>
       <c r="E413" s="1">
         <v>0</v>
@@ -9980,7 +9983,7 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B414" s="10" t="s">
         <v>39</v>
@@ -9997,7 +10000,7 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B415" s="10" t="s">
         <v>0</v>
@@ -10014,7 +10017,7 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B416" s="10" t="s">
         <v>39</v>
@@ -10031,7 +10034,7 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B417" s="10" t="s">
         <v>39</v>
@@ -10048,13 +10051,13 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B418" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C418" s="10" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D418" s="13">
         <v>290</v>
@@ -10065,7 +10068,7 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B419" s="10" t="s">
         <v>39</v>
@@ -10082,7 +10085,7 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B420" s="10" t="s">
         <v>0</v>
@@ -10099,16 +10102,16 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B421" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C421" s="10" t="s">
         <v>233</v>
       </c>
       <c r="D421" s="13">
-        <v>300</v>
+        <v>1775</v>
       </c>
       <c r="E421" s="1">
         <v>0</v>
@@ -10116,16 +10119,16 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B422" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C422" s="10" t="s">
         <v>233</v>
       </c>
       <c r="D422" s="13">
-        <v>1775</v>
+        <v>300</v>
       </c>
       <c r="E422" s="1">
         <v>0</v>
@@ -10133,7 +10136,7 @@
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B423" s="10" t="s">
         <v>0</v>
@@ -10150,16 +10153,16 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B424" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C424" s="10" t="s">
         <v>234</v>
       </c>
       <c r="D424" s="13">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="E424" s="1">
         <v>0</v>
@@ -10167,16 +10170,16 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B425" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C425" s="10" t="s">
         <v>234</v>
       </c>
       <c r="D425" s="13">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="E425" s="1">
         <v>0</v>
@@ -10184,7 +10187,7 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B426" s="10" t="s">
         <v>39</v>
@@ -10201,7 +10204,7 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B427" s="10" t="s">
         <v>0</v>
@@ -10218,7 +10221,7 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B428" s="10" t="s">
         <v>0</v>
@@ -10235,7 +10238,7 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B429" s="10" t="s">
         <v>0</v>
@@ -10252,7 +10255,7 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B430" s="10" t="s">
         <v>0</v>
@@ -10269,7 +10272,7 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B431" s="10" t="s">
         <v>0</v>
@@ -10286,7 +10289,7 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B432" s="10" t="s">
         <v>0</v>
@@ -10303,7 +10306,7 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B433" s="10" t="s">
         <v>9</v>
@@ -10320,7 +10323,7 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B434" s="10" t="s">
         <v>9</v>
@@ -10337,7 +10340,7 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B435" s="10" t="s">
         <v>0</v>
@@ -10354,7 +10357,7 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B436" s="10" t="s">
         <v>0</v>
@@ -10371,7 +10374,7 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B437" s="10" t="s">
         <v>39</v>
@@ -10388,13 +10391,13 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B438" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C438" s="10" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D438" s="13">
         <v>140</v>
@@ -10405,7 +10408,7 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B439" s="10" t="s">
         <v>0</v>
@@ -10422,7 +10425,7 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B440" s="10" t="s">
         <v>39</v>
@@ -10439,7 +10442,7 @@
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B441" s="10" t="s">
         <v>0</v>
@@ -10456,13 +10459,13 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B442" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C442" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D442" s="13">
         <v>60</v>
@@ -10473,7 +10476,7 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B443" s="10" t="s">
         <v>39</v>
@@ -10490,7 +10493,7 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B444" s="10" t="s">
         <v>39</v>
@@ -10507,7 +10510,7 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B445" s="10" t="s">
         <v>39</v>
@@ -10524,7 +10527,7 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B446" s="10" t="s">
         <v>9</v>
@@ -10541,7 +10544,7 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B447" s="10" t="s">
         <v>0</v>
@@ -10558,7 +10561,7 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B448" s="10" t="s">
         <v>0</v>
@@ -10575,7 +10578,7 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B449" s="10" t="s">
         <v>0</v>
@@ -10592,7 +10595,7 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B450" s="10" t="s">
         <v>0</v>
@@ -10609,7 +10612,7 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B451" s="10" t="s">
         <v>0</v>
@@ -10626,7 +10629,7 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B452" s="10" t="s">
         <v>0</v>
@@ -10643,7 +10646,7 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B453" s="10" t="s">
         <v>0</v>
@@ -10660,7 +10663,7 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B454" s="10" t="s">
         <v>0</v>
@@ -10677,7 +10680,7 @@
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B455" s="10" t="s">
         <v>0</v>
@@ -10694,7 +10697,7 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B456" s="10" t="s">
         <v>0</v>
@@ -10711,13 +10714,13 @@
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B457" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C457" s="10" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D457" s="13">
         <v>16</v>
@@ -10728,13 +10731,13 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B458" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C458" s="10" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D458" s="13">
         <v>16</v>
@@ -10745,13 +10748,13 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B459" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C459" s="10" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D459" s="13">
         <v>16</v>
@@ -10762,13 +10765,13 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B460" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C460" s="10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D460" s="13">
         <v>4</v>
@@ -10779,7 +10782,7 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B461" s="10" t="s">
         <v>0</v>
@@ -10796,7 +10799,7 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B462" s="10" t="s">
         <v>0</v>
@@ -10813,7 +10816,7 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B463" s="10" t="s">
         <v>0</v>
@@ -10830,7 +10833,7 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B464" s="10" t="s">
         <v>39</v>
@@ -10847,7 +10850,7 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B465" s="10" t="s">
         <v>39</v>
@@ -10864,7 +10867,7 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B466" s="10" t="s">
         <v>39</v>
@@ -10881,7 +10884,7 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B467" s="10" t="s">
         <v>39</v>
@@ -10898,13 +10901,13 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B468" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C468" s="10" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D468" s="13">
         <v>3760</v>
@@ -10915,7 +10918,7 @@
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B469" s="10" t="s">
         <v>39</v>
@@ -10932,7 +10935,7 @@
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B470" s="10" t="s">
         <v>0</v>
@@ -10949,7 +10952,7 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B471" s="10" t="s">
         <v>0</v>
@@ -10966,16 +10969,16 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B472" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C472" s="10" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D472" s="13">
-        <v>1672</v>
+        <v>1632</v>
       </c>
       <c r="E472" s="1">
         <v>0</v>
@@ -10983,7 +10986,7 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B473" s="10" t="s">
         <v>0</v>
@@ -11000,7 +11003,7 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B474" s="10" t="s">
         <v>0</v>
@@ -11017,7 +11020,7 @@
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B475" s="10" t="s">
         <v>0</v>
@@ -11034,7 +11037,7 @@
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B476" s="10" t="s">
         <v>0</v>
@@ -11051,7 +11054,7 @@
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B477" s="10" t="s">
         <v>39</v>
@@ -11068,7 +11071,7 @@
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B478" s="10" t="s">
         <v>39</v>
@@ -11077,7 +11080,7 @@
         <v>266</v>
       </c>
       <c r="D478" s="13">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E478" s="1">
         <v>0</v>
@@ -11085,7 +11088,7 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B479" s="10" t="s">
         <v>39</v>
@@ -11094,7 +11097,7 @@
         <v>267</v>
       </c>
       <c r="D479" s="13">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E479" s="1">
         <v>0</v>
@@ -11102,7 +11105,7 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B480" s="10" t="s">
         <v>39</v>
@@ -11119,7 +11122,7 @@
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B481" s="10" t="s">
         <v>39</v>
@@ -11136,7 +11139,7 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B482" s="10" t="s">
         <v>39</v>
@@ -11145,7 +11148,7 @@
         <v>270</v>
       </c>
       <c r="D482" s="13">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E482" s="1">
         <v>0</v>
@@ -11153,7 +11156,7 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B483" s="10" t="s">
         <v>39</v>
@@ -11170,7 +11173,7 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B484" s="10" t="s">
         <v>0</v>
@@ -11187,13 +11190,13 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B485" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C485" s="10" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D485" s="13">
         <v>575</v>
@@ -11204,13 +11207,13 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B486" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C486" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D486" s="13">
         <v>9500</v>
@@ -11221,13 +11224,13 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B487" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D487" s="13">
         <v>575</v>
@@ -11238,7 +11241,7 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B488" s="10" t="s">
         <v>0</v>
@@ -11255,13 +11258,13 @@
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B489" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C489" s="10" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D489" s="13">
         <v>5000</v>
@@ -11272,7 +11275,7 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B490" s="10" t="s">
         <v>39</v>
@@ -11289,7 +11292,7 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B491" s="10" t="s">
         <v>0</v>
@@ -11306,7 +11309,7 @@
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B492" s="10" t="s">
         <v>0</v>
@@ -11323,7 +11326,7 @@
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B493" s="10" t="s">
         <v>0</v>
@@ -11340,7 +11343,7 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B494" s="10" t="s">
         <v>0</v>
@@ -11357,7 +11360,7 @@
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B495" s="10" t="s">
         <v>0</v>
@@ -11374,7 +11377,7 @@
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B496" s="10" t="s">
         <v>0</v>
@@ -11391,7 +11394,7 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B497" s="10" t="s">
         <v>0</v>
@@ -11408,7 +11411,7 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B498" s="10" t="s">
         <v>0</v>
@@ -11425,7 +11428,7 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B499" s="10" t="s">
         <v>0</v>
@@ -11442,7 +11445,7 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B500" s="10" t="s">
         <v>0</v>
@@ -11459,7 +11462,7 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B501" s="10" t="s">
         <v>0</v>
@@ -11476,7 +11479,7 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B502" s="10" t="s">
         <v>0</v>
@@ -11493,7 +11496,7 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B503" s="10" t="s">
         <v>0</v>
@@ -11510,7 +11513,7 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B504" s="10" t="s">
         <v>0</v>
@@ -11527,7 +11530,7 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B505" s="10" t="s">
         <v>0</v>
@@ -11544,7 +11547,7 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B506" s="10" t="s">
         <v>0</v>
@@ -11561,7 +11564,7 @@
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B507" s="10" t="s">
         <v>0</v>
@@ -11578,7 +11581,7 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B508" s="10" t="s">
         <v>0</v>
@@ -11595,13 +11598,13 @@
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B509" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C509" s="10" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D509" s="13">
         <v>7</v>
@@ -11612,13 +11615,13 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B510" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C510" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D510" s="13">
         <v>1</v>
@@ -11629,13 +11632,13 @@
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B511" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C511" s="10" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D511" s="13">
         <v>3</v>
@@ -11646,7 +11649,7 @@
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B512" s="10" t="s">
         <v>515</v>
@@ -11663,7 +11666,7 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B513" s="10" t="s">
         <v>515</v>
@@ -11680,13 +11683,13 @@
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B514" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C514" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D514" s="13">
         <v>23</v>
@@ -11697,7 +11700,7 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B515" s="10" t="s">
         <v>515</v>
@@ -11714,7 +11717,7 @@
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B516" s="10" t="s">
         <v>515</v>
@@ -11731,13 +11734,13 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B517" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C517" s="10" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D517" s="13">
         <v>3</v>
@@ -11748,13 +11751,13 @@
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B518" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C518" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D518" s="13">
         <v>2</v>
@@ -11765,13 +11768,13 @@
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B519" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C519" s="10" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D519" s="13">
         <v>2</v>
@@ -11782,7 +11785,7 @@
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B520" s="10" t="s">
         <v>515</v>
@@ -11799,13 +11802,13 @@
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B521" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C521" s="10" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D521" s="13">
         <v>1</v>
@@ -11816,7 +11819,7 @@
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B522" s="10" t="s">
         <v>0</v>
@@ -11833,7 +11836,7 @@
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B523" s="10" t="s">
         <v>0</v>
@@ -11850,7 +11853,7 @@
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B524" s="10" t="s">
         <v>0</v>
@@ -11867,7 +11870,7 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B525" s="10" t="s">
         <v>0</v>
@@ -11884,7 +11887,7 @@
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B526" s="10" t="s">
         <v>0</v>
@@ -11901,7 +11904,7 @@
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B527" s="10" t="s">
         <v>0</v>
@@ -11918,7 +11921,7 @@
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B528" s="10" t="s">
         <v>0</v>
@@ -11935,7 +11938,7 @@
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B529" s="10" t="s">
         <v>0</v>
@@ -11952,7 +11955,7 @@
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B530" s="10" t="s">
         <v>515</v>
@@ -11969,13 +11972,13 @@
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B531" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C531" s="10" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D531" s="13">
         <v>4</v>
@@ -11986,7 +11989,7 @@
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B532" s="10" t="s">
         <v>515</v>
@@ -12003,13 +12006,13 @@
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B533" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C533" s="10" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D533" s="13">
         <v>5</v>
@@ -12020,13 +12023,13 @@
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B534" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C534" s="10" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D534" s="13">
         <v>2</v>
@@ -12037,13 +12040,13 @@
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B535" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C535" s="10" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D535" s="13">
         <v>3</v>
@@ -12054,13 +12057,13 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="B536" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C536" s="10" t="s">
         <v>744</v>
-      </c>
-      <c r="B536" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C536" s="10" t="s">
-        <v>745</v>
       </c>
       <c r="D536" s="13">
         <v>8</v>
@@ -12071,13 +12074,13 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B537" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C537" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D537" s="13">
         <v>1</v>
@@ -12088,7 +12091,7 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B538" s="10" t="s">
         <v>515</v>
@@ -12105,13 +12108,13 @@
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B539" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C539" s="10" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D539" s="13">
         <v>1</v>
@@ -12122,13 +12125,13 @@
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B540" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C540" s="10" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D540" s="13">
         <v>2</v>
@@ -12139,7 +12142,7 @@
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B541" s="10" t="s">
         <v>515</v>
@@ -12156,7 +12159,7 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B542" s="10" t="s">
         <v>515</v>
@@ -12173,7 +12176,7 @@
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B543" s="10" t="s">
         <v>515</v>
@@ -12190,7 +12193,7 @@
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B544" s="10" t="s">
         <v>515</v>
@@ -12207,7 +12210,7 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B545" s="10" t="s">
         <v>515</v>
@@ -12224,7 +12227,7 @@
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B546" s="10" t="s">
         <v>515</v>
@@ -12241,7 +12244,7 @@
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B547" s="10" t="s">
         <v>515</v>
@@ -12258,7 +12261,7 @@
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B548" s="10" t="s">
         <v>515</v>
@@ -12275,7 +12278,7 @@
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B549" s="10" t="s">
         <v>515</v>
@@ -12292,7 +12295,7 @@
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B550" s="10" t="s">
         <v>515</v>
@@ -12309,7 +12312,7 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B551" s="10" t="s">
         <v>515</v>
@@ -12326,7 +12329,7 @@
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B552" s="10" t="s">
         <v>515</v>
@@ -12343,7 +12346,7 @@
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B553" s="10" t="s">
         <v>515</v>
@@ -12360,7 +12363,7 @@
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B554" s="10" t="s">
         <v>515</v>
@@ -12377,13 +12380,13 @@
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B555" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C555" s="10" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="D555" s="13">
         <v>1</v>
@@ -12394,16 +12397,16 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B556" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C556" s="10" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D556" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E556" s="1">
         <v>0</v>
@@ -12411,16 +12414,16 @@
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B557" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C557" s="10" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D557" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E557" s="1">
         <v>0</v>
@@ -12428,16 +12431,16 @@
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B558" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C558" s="10" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D558" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E558" s="1">
         <v>0</v>
@@ -12445,16 +12448,16 @@
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B559" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C559" s="10" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D559" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E559" s="1">
         <v>0</v>
@@ -12462,16 +12465,16 @@
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B560" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C560" s="10" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D560" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E560" s="1">
         <v>0</v>
@@ -12479,16 +12482,16 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" s="10" t="s">
-        <v>556</v>
+        <v>611</v>
       </c>
       <c r="B561" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C561" s="10" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D561" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E561" s="1">
         <v>0</v>
@@ -12496,16 +12499,16 @@
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" s="10" t="s">
-        <v>612</v>
+        <v>655</v>
       </c>
       <c r="B562" s="10" t="s">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="C562" s="10" t="s">
-        <v>541</v>
+        <v>298</v>
       </c>
       <c r="D562" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E562" s="1">
         <v>0</v>
@@ -12513,13 +12516,13 @@
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" s="10" t="s">
-        <v>656</v>
+        <v>555</v>
       </c>
       <c r="B563" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C563" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D563" s="13">
         <v>1</v>
@@ -12530,13 +12533,13 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B564" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C564" s="10" t="s">
-        <v>299</v>
+        <v>486</v>
       </c>
       <c r="D564" s="13">
         <v>1</v>
@@ -12547,16 +12550,16 @@
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B565" s="10" t="s">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="C565" s="10" t="s">
-        <v>486</v>
+        <v>300</v>
       </c>
       <c r="D565" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E565" s="1">
         <v>0</v>
@@ -12564,7 +12567,7 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B566" s="10" t="s">
         <v>0</v>
@@ -12581,13 +12584,13 @@
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" s="10" t="s">
-        <v>556</v>
+        <v>611</v>
       </c>
       <c r="B567" s="10" t="s">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="C567" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D567" s="13">
         <v>2</v>
@@ -12598,16 +12601,16 @@
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B568" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C568" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D568" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E568" s="1">
         <v>0</v>
@@ -12615,13 +12618,13 @@
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B569" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C569" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D569" s="13">
         <v>1</v>
@@ -12632,13 +12635,13 @@
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" s="10" t="s">
-        <v>612</v>
+        <v>557</v>
       </c>
       <c r="B570" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C570" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D570" s="13">
         <v>1</v>
@@ -12649,13 +12652,13 @@
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B571" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C571" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D571" s="13">
         <v>1</v>
@@ -12666,16 +12669,16 @@
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" s="10" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B572" s="10" t="s">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="C572" s="10" t="s">
-        <v>305</v>
+        <v>680</v>
       </c>
       <c r="D572" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E572" s="1">
         <v>0</v>
@@ -12683,7 +12686,7 @@
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B573" s="10" t="s">
         <v>515</v>
@@ -12692,7 +12695,7 @@
         <v>681</v>
       </c>
       <c r="D573" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E573" s="1">
         <v>0</v>
@@ -12700,7 +12703,7 @@
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B574" s="10" t="s">
         <v>515</v>
@@ -12709,7 +12712,7 @@
         <v>682</v>
       </c>
       <c r="D574" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E574" s="1">
         <v>0</v>
@@ -12717,16 +12720,16 @@
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B575" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C575" s="10" t="s">
-        <v>683</v>
+        <v>542</v>
       </c>
       <c r="D575" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E575" s="1">
         <v>0</v>
@@ -12734,13 +12737,13 @@
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B576" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C576" s="10" t="s">
-        <v>542</v>
+        <v>683</v>
       </c>
       <c r="D576" s="13">
         <v>1</v>
@@ -12751,7 +12754,7 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B577" s="10" t="s">
         <v>515</v>
@@ -12760,7 +12763,7 @@
         <v>684</v>
       </c>
       <c r="D577" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E577" s="1">
         <v>0</v>
@@ -12768,7 +12771,7 @@
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B578" s="10" t="s">
         <v>515</v>
@@ -12777,7 +12780,7 @@
         <v>685</v>
       </c>
       <c r="D578" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E578" s="1">
         <v>0</v>
@@ -12785,7 +12788,7 @@
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B579" s="10" t="s">
         <v>515</v>
@@ -12802,7 +12805,7 @@
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B580" s="10" t="s">
         <v>515</v>
@@ -12811,7 +12814,7 @@
         <v>687</v>
       </c>
       <c r="D580" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E580" s="1">
         <v>0</v>
@@ -12819,7 +12822,7 @@
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B581" s="10" t="s">
         <v>515</v>
@@ -12836,7 +12839,7 @@
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B582" s="10" t="s">
         <v>515</v>
@@ -12845,7 +12848,7 @@
         <v>689</v>
       </c>
       <c r="D582" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E582" s="1">
         <v>0</v>
@@ -12853,13 +12856,13 @@
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A583" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B583" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C583" s="10" t="s">
-        <v>690</v>
+        <v>543</v>
       </c>
       <c r="D583" s="13">
         <v>2</v>
@@ -12870,16 +12873,16 @@
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B584" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C584" s="10" t="s">
-        <v>543</v>
+        <v>677</v>
       </c>
       <c r="D584" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E584" s="1">
         <v>0</v>
@@ -12887,13 +12890,13 @@
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585" s="10" t="s">
-        <v>556</v>
+        <v>611</v>
       </c>
       <c r="B585" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C585" s="10" t="s">
-        <v>678</v>
+        <v>544</v>
       </c>
       <c r="D585" s="13">
         <v>1</v>
@@ -12904,16 +12907,16 @@
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A586" s="10" t="s">
-        <v>612</v>
+        <v>557</v>
       </c>
       <c r="B586" s="10" t="s">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="C586" s="10" t="s">
-        <v>544</v>
+        <v>306</v>
       </c>
       <c r="D586" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E586" s="1">
         <v>0</v>
@@ -12921,16 +12924,16 @@
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587" s="10" t="s">
-        <v>558</v>
+        <v>611</v>
       </c>
       <c r="B587" s="10" t="s">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="C587" s="10" t="s">
-        <v>306</v>
+        <v>548</v>
       </c>
       <c r="D587" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E587" s="1">
         <v>0</v>
@@ -12938,16 +12941,16 @@
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588" s="10" t="s">
-        <v>612</v>
+        <v>633</v>
       </c>
       <c r="B588" s="10" t="s">
-        <v>515</v>
+        <v>39</v>
       </c>
       <c r="C588" s="10" t="s">
-        <v>549</v>
+        <v>398</v>
       </c>
       <c r="D588" s="13">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E588" s="1">
         <v>0</v>
@@ -12955,16 +12958,16 @@
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B589" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C589" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D589" s="13">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E589" s="1">
         <v>0</v>
@@ -12972,16 +12975,16 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" s="10" t="s">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="B590" s="10" t="s">
-        <v>39</v>
+        <v>515</v>
       </c>
       <c r="C590" s="10" t="s">
-        <v>399</v>
+        <v>765</v>
       </c>
       <c r="D590" s="13">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E590" s="1">
         <v>0</v>
@@ -12989,7 +12992,7 @@
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B591" s="10" t="s">
         <v>515</v>
@@ -13006,7 +13009,7 @@
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A592" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B592" s="10" t="s">
         <v>515</v>
@@ -13015,7 +13018,7 @@
         <v>767</v>
       </c>
       <c r="D592" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E592" s="1">
         <v>0</v>
@@ -13023,7 +13026,7 @@
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A593" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B593" s="10" t="s">
         <v>515</v>
@@ -13032,7 +13035,7 @@
         <v>768</v>
       </c>
       <c r="D593" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E593" s="1">
         <v>0</v>
@@ -13040,16 +13043,16 @@
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A594" s="10" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="B594" s="10" t="s">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="C594" s="10" t="s">
-        <v>769</v>
+        <v>307</v>
       </c>
       <c r="D594" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E594" s="1">
         <v>0</v>
@@ -13057,16 +13060,16 @@
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A595" s="10" t="s">
-        <v>550</v>
+        <v>657</v>
       </c>
       <c r="B595" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C595" s="10" t="s">
-        <v>307</v>
+        <v>780</v>
       </c>
       <c r="D595" s="13">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="E595" s="1">
         <v>0</v>
@@ -13074,7 +13077,7 @@
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A596" s="10" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="B596" s="10" t="s">
         <v>39</v>
@@ -13083,7 +13086,7 @@
         <v>781</v>
       </c>
       <c r="D596" s="13">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E596" s="1">
         <v>0</v>
@@ -13091,16 +13094,16 @@
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A597" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B597" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C597" s="10" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="D597" s="13">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="E597" s="1">
         <v>0</v>
@@ -13108,16 +13111,16 @@
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A598" s="10" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B598" s="10" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C598" s="10" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="D598" s="13">
-        <v>2400</v>
+        <v>1</v>
       </c>
       <c r="E598" s="1">
         <v>0</v>
@@ -13125,16 +13128,16 @@
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A599" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B599" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C599" s="10" t="s">
-        <v>423</v>
+        <v>796</v>
       </c>
       <c r="D599" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E599" s="1">
         <v>0</v>
@@ -13142,16 +13145,16 @@
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A600" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B600" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C600" s="10" t="s">
-        <v>512</v>
+        <v>423</v>
       </c>
       <c r="D600" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E600" s="1">
         <v>0</v>
@@ -13159,16 +13162,16 @@
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A601" s="10" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B601" s="10" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C601" s="10" t="s">
-        <v>783</v>
+        <v>512</v>
       </c>
       <c r="D601" s="13">
-        <v>1900</v>
+        <v>1</v>
       </c>
       <c r="E601" s="1">
         <v>0</v>
@@ -13176,16 +13179,16 @@
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A602" s="10" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="B602" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C602" s="10" t="s">
-        <v>308</v>
+        <v>782</v>
       </c>
       <c r="D602" s="13">
-        <v>37</v>
+        <v>1850</v>
       </c>
       <c r="E602" s="1">
         <v>0</v>
@@ -13193,16 +13196,16 @@
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A603" s="10" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B603" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C603" s="10" t="s">
-        <v>784</v>
+        <v>308</v>
       </c>
       <c r="D603" s="13">
-        <v>2500</v>
+        <v>37</v>
       </c>
       <c r="E603" s="1">
         <v>0</v>
@@ -13210,16 +13213,16 @@
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A604" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B604" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C604" s="10" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="D604" s="13">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="E604" s="1">
         <v>0</v>
@@ -13227,16 +13230,16 @@
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A605" s="10" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="B605" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C605" s="10" t="s">
-        <v>729</v>
+        <v>790</v>
       </c>
       <c r="D605" s="13">
-        <v>800</v>
+        <v>2400</v>
       </c>
       <c r="E605" s="1">
         <v>0</v>
@@ -13244,16 +13247,16 @@
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A606" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B606" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C606" s="10" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D606" s="13">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="E606" s="1">
         <v>0</v>
@@ -13261,16 +13264,16 @@
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A607" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B607" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C607" s="10" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D607" s="13">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="E607" s="1">
         <v>0</v>
@@ -13278,16 +13281,16 @@
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A608" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B608" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C608" s="10" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D608" s="13">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="E608" s="1">
         <v>0</v>
@@ -13295,16 +13298,16 @@
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A609" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B609" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C609" s="10" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D609" s="13">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="E609" s="1">
         <v>0</v>
@@ -13312,16 +13315,16 @@
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A610" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B610" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C610" s="10" t="s">
-        <v>785</v>
+        <v>732</v>
       </c>
       <c r="D610" s="13">
-        <v>1250</v>
+        <v>800</v>
       </c>
       <c r="E610" s="1">
         <v>0</v>
@@ -13329,16 +13332,16 @@
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A611" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B611" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C611" s="10" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D611" s="13">
-        <v>1550</v>
+        <v>1250</v>
       </c>
       <c r="E611" s="1">
         <v>0</v>
@@ -13346,16 +13349,16 @@
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A612" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B612" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C612" s="10" t="s">
-        <v>309</v>
+        <v>785</v>
       </c>
       <c r="D612" s="13">
-        <v>1070</v>
+        <v>1550</v>
       </c>
       <c r="E612" s="1">
         <v>0</v>
@@ -13363,16 +13366,16 @@
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A613" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B613" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C613" s="10" t="s">
-        <v>787</v>
+        <v>309</v>
       </c>
       <c r="D613" s="13">
-        <v>1700</v>
+        <v>1070</v>
       </c>
       <c r="E613" s="1">
         <v>0</v>
@@ -13380,16 +13383,16 @@
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A614" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B614" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C614" s="10" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D614" s="13">
-        <v>1000</v>
+        <v>1700</v>
       </c>
       <c r="E614" s="1">
         <v>0</v>
@@ -13397,16 +13400,16 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" s="10" t="s">
-        <v>566</v>
+        <v>657</v>
       </c>
       <c r="B615" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C615" s="10" t="s">
-        <v>310</v>
+        <v>787</v>
       </c>
       <c r="D615" s="13">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="E615" s="1">
         <v>0</v>
@@ -13414,16 +13417,16 @@
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A616" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B616" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C616" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D616" s="13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E616" s="1">
         <v>0</v>
@@ -13431,16 +13434,16 @@
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" s="10" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B617" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C617" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D617" s="13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E617" s="1">
         <v>0</v>
@@ -13448,13 +13451,13 @@
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A618" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B618" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C618" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D618" s="13">
         <v>1</v>
@@ -13465,16 +13468,16 @@
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A619" s="10" t="s">
-        <v>659</v>
+        <v>566</v>
       </c>
       <c r="B619" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C619" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D619" s="13">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E619" s="1">
         <v>0</v>
@@ -13482,16 +13485,16 @@
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A620" s="10" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B620" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C620" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D620" s="13">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E620" s="1">
         <v>0</v>
@@ -13499,16 +13502,16 @@
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A621" s="10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B621" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C621" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D621" s="13">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="E621" s="1">
         <v>0</v>
@@ -13516,16 +13519,16 @@
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A622" s="10" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B622" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C622" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D622" s="13">
-        <v>300</v>
+        <v>121</v>
       </c>
       <c r="E622" s="1">
         <v>0</v>
@@ -13533,10 +13536,10 @@
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A623" s="10" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B623" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C623" s="10" t="s">
         <v>317</v>
@@ -13550,13 +13553,13 @@
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A624" s="10" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B624" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C624" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D624" s="13">
         <v>300</v>
@@ -13573,10 +13576,10 @@
         <v>39</v>
       </c>
       <c r="C625" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D625" s="13">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E625" s="1">
         <v>0</v>
@@ -13584,16 +13587,16 @@
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A626" s="10" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B626" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C626" s="10" t="s">
-        <v>447</v>
+        <v>319</v>
       </c>
       <c r="D626" s="13">
-        <v>43</v>
+        <v>310</v>
       </c>
       <c r="E626" s="1">
         <v>0</v>
@@ -13607,10 +13610,10 @@
         <v>0</v>
       </c>
       <c r="C627" s="10" t="s">
-        <v>320</v>
+        <v>447</v>
       </c>
       <c r="D627" s="13">
-        <v>250</v>
+        <v>43</v>
       </c>
       <c r="E627" s="1">
         <v>0</v>
@@ -13618,16 +13621,16 @@
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A628" s="10" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B628" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C628" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D628" s="13">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="E628" s="1">
         <v>0</v>
@@ -13635,7 +13638,7 @@
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A629" s="10" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B629" s="10" t="s">
         <v>39</v>
@@ -13652,16 +13655,16 @@
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A630" s="10" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B630" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C630" s="10" t="s">
-        <v>393</v>
+        <v>321</v>
       </c>
       <c r="D630" s="13">
-        <v>42</v>
+        <v>280</v>
       </c>
       <c r="E630" s="1">
         <v>0</v>
@@ -13669,16 +13672,16 @@
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A631" s="10" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B631" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C631" s="10" t="s">
-        <v>322</v>
+        <v>393</v>
       </c>
       <c r="D631" s="13">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E631" s="1">
         <v>0</v>
@@ -13686,16 +13689,16 @@
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632" s="10" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B632" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C632" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D632" s="13">
-        <v>250</v>
+        <v>24</v>
       </c>
       <c r="E632" s="1">
         <v>0</v>
@@ -13703,16 +13706,16 @@
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A633" s="10" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B633" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C633" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D633" s="13">
-        <v>1250</v>
+        <v>250</v>
       </c>
       <c r="E633" s="1">
         <v>0</v>
@@ -13720,16 +13723,16 @@
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A634" s="10" t="s">
-        <v>720</v>
+        <v>664</v>
       </c>
       <c r="B634" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C634" s="10" t="s">
-        <v>721</v>
+        <v>324</v>
       </c>
       <c r="D634" s="13">
-        <v>100</v>
+        <v>1250</v>
       </c>
       <c r="E634" s="1">
         <v>0</v>
@@ -13737,16 +13740,16 @@
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A635" s="10" t="s">
-        <v>665</v>
+        <v>719</v>
       </c>
       <c r="B635" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C635" s="10" t="s">
-        <v>325</v>
+        <v>720</v>
       </c>
       <c r="D635" s="13">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="E635" s="1">
         <v>0</v>
@@ -13754,16 +13757,16 @@
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636" s="10" t="s">
-        <v>720</v>
+        <v>664</v>
       </c>
       <c r="B636" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C636" s="10" t="s">
-        <v>722</v>
+        <v>325</v>
       </c>
       <c r="D636" s="13">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="E636" s="1">
         <v>0</v>
@@ -13771,16 +13774,16 @@
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A637" s="10" t="s">
-        <v>665</v>
+        <v>719</v>
       </c>
       <c r="B637" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C637" s="10" t="s">
-        <v>326</v>
+        <v>721</v>
       </c>
       <c r="D637" s="13">
-        <v>600</v>
+        <v>35</v>
       </c>
       <c r="E637" s="1">
         <v>0</v>
@@ -13788,16 +13791,16 @@
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A638" s="10" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B638" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C638" s="10" t="s">
         <v>326</v>
       </c>
       <c r="D638" s="13">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="E638" s="1">
         <v>0</v>
@@ -13805,16 +13808,16 @@
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>720</v>
+        <v>664</v>
       </c>
       <c r="B639" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C639" s="1" t="s">
-        <v>723</v>
+        <v>326</v>
       </c>
       <c r="D639" s="14">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E639" s="1">
         <v>0</v>
@@ -13822,16 +13825,16 @@
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>665</v>
+        <v>719</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>391</v>
+        <v>722</v>
       </c>
       <c r="D640" s="14">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E640" s="1">
         <v>0</v>
@@ -13839,16 +13842,16 @@
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B641" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C641" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D641" s="14">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E641" s="1">
         <v>0</v>
@@ -13856,16 +13859,16 @@
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B642" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>327</v>
+        <v>392</v>
       </c>
       <c r="D642" s="14">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E642" s="1">
         <v>0</v>
@@ -13873,16 +13876,16 @@
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>405</v>
+        <v>39</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>416</v>
+        <v>327</v>
       </c>
       <c r="D643" s="14">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="E643" s="1">
         <v>0</v>
@@ -13890,16 +13893,16 @@
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="C644" s="1" t="s">
-        <v>328</v>
+        <v>416</v>
       </c>
       <c r="D644" s="14">
-        <v>1300</v>
+        <v>2</v>
       </c>
       <c r="E644" s="1">
         <v>0</v>
@@ -13907,16 +13910,16 @@
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B645" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C645" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D645" s="14">
-        <v>29</v>
+        <v>1300</v>
       </c>
       <c r="E645" s="1">
         <v>0</v>
@@ -13924,16 +13927,16 @@
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B646" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C646" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D646" s="14">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E646" s="1">
         <v>0</v>
@@ -13941,16 +13944,16 @@
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B647" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C647" s="1" t="s">
-        <v>464</v>
+        <v>330</v>
       </c>
       <c r="D647" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E647" s="1">
         <v>0</v>
@@ -13958,16 +13961,16 @@
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B648" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D648" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E648" s="1">
         <v>0</v>
@@ -13975,16 +13978,16 @@
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B649" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C649" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D649" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E649" s="1">
         <v>0</v>
@@ -13992,16 +13995,16 @@
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C650" s="1" t="s">
-        <v>331</v>
+        <v>466</v>
       </c>
       <c r="D650" s="14">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="E650" s="1">
         <v>0</v>
@@ -14009,16 +14012,16 @@
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B651" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D651" s="14">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E651" s="1">
         <v>0</v>
@@ -14026,16 +14029,16 @@
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B652" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D652" s="14">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="E652" s="1">
         <v>0</v>
@@ -14043,16 +14046,16 @@
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B653" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C653" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D653" s="14">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="E653" s="1">
         <v>0</v>
@@ -14060,16 +14063,16 @@
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C654" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D654" s="14">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="E654" s="1">
         <v>0</v>
@@ -14077,16 +14080,16 @@
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B655" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C655" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D655" s="14">
-        <v>825</v>
+        <v>600</v>
       </c>
       <c r="E655" s="1">
         <v>0</v>
@@ -14094,16 +14097,16 @@
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C656" s="1" t="s">
-        <v>724</v>
+        <v>336</v>
       </c>
       <c r="D656" s="14">
-        <v>465</v>
+        <v>825</v>
       </c>
       <c r="E656" s="1">
         <v>0</v>
@@ -14114,13 +14117,13 @@
         <v>670</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C657" s="1" t="s">
-        <v>337</v>
+        <v>723</v>
       </c>
       <c r="D657" s="14">
-        <v>600</v>
+        <v>465</v>
       </c>
       <c r="E657" s="1">
         <v>0</v>
@@ -14128,16 +14131,16 @@
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C658" s="1" t="s">
         <v>337</v>
       </c>
       <c r="D658" s="14">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E658" s="1">
         <v>0</v>
@@ -14145,16 +14148,16 @@
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B659" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C659" s="1" t="s">
-        <v>448</v>
+        <v>337</v>
       </c>
       <c r="D659" s="14">
-        <v>65</v>
+        <v>400</v>
       </c>
       <c r="E659" s="1">
         <v>0</v>
@@ -14165,13 +14168,13 @@
         <v>670</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C660" s="1" t="s">
-        <v>377</v>
+        <v>448</v>
       </c>
       <c r="D660" s="14">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E660" s="1">
         <v>0</v>
@@ -14179,16 +14182,16 @@
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B661" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C661" s="1" t="s">
-        <v>338</v>
+        <v>377</v>
       </c>
       <c r="D661" s="14">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E661" s="1">
         <v>0</v>
@@ -14196,16 +14199,16 @@
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D662" s="14">
-        <v>1001</v>
+        <v>72</v>
       </c>
       <c r="E662" s="1">
         <v>0</v>
@@ -14213,16 +14216,16 @@
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B663" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C663" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D663" s="14">
-        <v>1508</v>
+        <v>1001</v>
       </c>
       <c r="E663" s="1">
         <v>0</v>
@@ -14230,16 +14233,16 @@
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B664" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D664" s="14">
-        <v>600</v>
+        <v>1508</v>
       </c>
       <c r="E664" s="1">
         <v>0</v>
@@ -14247,16 +14250,16 @@
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B665" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C665" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D665" s="14">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E665" s="1">
         <v>0</v>
@@ -14264,16 +14267,16 @@
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B666" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C666" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D666" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E666" s="1">
         <v>0</v>
@@ -14281,16 +14284,16 @@
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B667" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C667" s="1" t="s">
-        <v>500</v>
+        <v>343</v>
       </c>
       <c r="D667" s="14">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="E667" s="1">
         <v>0</v>
@@ -14298,16 +14301,16 @@
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B668" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C668" s="1" t="s">
-        <v>344</v>
+        <v>500</v>
       </c>
       <c r="D668" s="14">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E668" s="1">
         <v>0</v>
@@ -14315,13 +14318,13 @@
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B669" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C669" s="1" t="s">
-        <v>404</v>
+        <v>344</v>
       </c>
       <c r="D669" s="14">
         <v>100</v>
@@ -14332,16 +14335,16 @@
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B670" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C670" s="1" t="s">
-        <v>345</v>
+        <v>404</v>
       </c>
       <c r="D670" s="14">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E670" s="1">
         <v>0</v>
@@ -14349,16 +14352,16 @@
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="B671" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C671" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D671" s="14">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="E671" s="1">
         <v>0</v>
@@ -14366,16 +14369,16 @@
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B672" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C672" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D672" s="14">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="E672" s="1">
         <v>0</v>
@@ -14383,16 +14386,16 @@
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="B673" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C673" s="1" t="s">
-        <v>467</v>
+        <v>347</v>
       </c>
       <c r="D673" s="14">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="E673" s="1">
         <v>0</v>
@@ -14400,16 +14403,16 @@
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B674" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C674" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D674" s="14">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E674" s="1">
         <v>0</v>
@@ -14417,16 +14420,16 @@
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B675" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C675" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D675" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E675" s="1">
         <v>0</v>
@@ -14434,16 +14437,16 @@
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>660</v>
+        <v>673</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C676" s="1" t="s">
-        <v>348</v>
+        <v>469</v>
       </c>
       <c r="D676" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E676" s="1">
         <v>0</v>
@@ -14451,16 +14454,16 @@
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B677" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C677" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D677" s="14">
-        <v>225</v>
+        <v>15</v>
       </c>
       <c r="E677" s="1">
         <v>0</v>
@@ -14468,16 +14471,16 @@
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B678" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C678" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D678" s="14">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="E678" s="1">
         <v>0</v>
@@ -14485,16 +14488,16 @@
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C679" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D679" s="14">
-        <v>1200</v>
+        <v>150</v>
       </c>
       <c r="E679" s="1">
         <v>0</v>
@@ -14502,13 +14505,13 @@
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C680" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D680" s="14">
         <v>1200</v>
@@ -14519,16 +14522,16 @@
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C681" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D681" s="14">
-        <v>225</v>
+        <v>1200</v>
       </c>
       <c r="E681" s="1">
         <v>0</v>
@@ -14536,16 +14539,16 @@
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C682" s="1" t="s">
         <v>353</v>
       </c>
       <c r="D682" s="14">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="E682" s="1">
         <v>0</v>
@@ -14553,16 +14556,16 @@
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B683" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D683" s="14">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E683" s="1">
         <v>0</v>
@@ -14570,16 +14573,16 @@
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C684" s="1" t="s">
-        <v>749</v>
+        <v>354</v>
       </c>
       <c r="D684" s="14">
-        <v>235</v>
+        <v>500</v>
       </c>
       <c r="E684" s="1">
         <v>0</v>
@@ -14587,16 +14590,16 @@
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B685" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C685" s="1" t="s">
-        <v>725</v>
+        <v>748</v>
       </c>
       <c r="D685" s="14">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="E685" s="1">
         <v>0</v>
@@ -14610,10 +14613,10 @@
         <v>0</v>
       </c>
       <c r="C686" s="1" t="s">
-        <v>355</v>
+        <v>724</v>
       </c>
       <c r="D686" s="14">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="E686" s="1">
         <v>0</v>
@@ -14621,16 +14624,16 @@
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C687" s="1" t="s">
         <v>355</v>
       </c>
       <c r="D687" s="14">
-        <v>200</v>
+        <v>950</v>
       </c>
       <c r="E687" s="1">
         <v>0</v>
@@ -14638,16 +14641,16 @@
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C688" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D688" s="14">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="E688" s="1">
         <v>0</v>
@@ -14655,16 +14658,16 @@
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B689" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C689" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D689" s="14">
-        <v>225</v>
+        <v>175</v>
       </c>
       <c r="E689" s="1">
         <v>0</v>
@@ -14672,16 +14675,16 @@
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B690" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C690" s="1" t="s">
-        <v>449</v>
+        <v>357</v>
       </c>
       <c r="D690" s="14">
-        <v>10</v>
+        <v>225</v>
       </c>
       <c r="E690" s="1">
         <v>0</v>
@@ -14692,13 +14695,13 @@
         <v>675</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C691" s="1" t="s">
-        <v>358</v>
+        <v>449</v>
       </c>
       <c r="D691" s="14">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="E691" s="1">
         <v>0</v>
@@ -14706,7 +14709,7 @@
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B692" s="1" t="s">
         <v>0</v>
@@ -14723,16 +14726,16 @@
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C693" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D693" s="14">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="E693" s="1">
         <v>0</v>
@@ -14740,16 +14743,16 @@
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C694" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D694" s="14">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E694" s="1">
         <v>0</v>
@@ -14757,16 +14760,16 @@
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C695" s="1" t="s">
         <v>360</v>
       </c>
       <c r="D695" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E695" s="1">
         <v>0</v>
@@ -14774,16 +14777,16 @@
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C696" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D696" s="14">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E696" s="1">
         <v>0</v>
@@ -14791,7 +14794,7 @@
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B697" s="1" t="s">
         <v>0</v>
@@ -14803,6 +14806,23 @@
         <v>30</v>
       </c>
       <c r="E697" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A698" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C698" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D698" s="14">
+        <v>64</v>
+      </c>
+      <c r="E698" s="1">
         <v>0</v>
       </c>
     </row>
@@ -14918,7 +14938,7 @@
         <v>بار دوش شاور بانل دوبل كروم اسود تركي بريفا PRIVA</v>
       </c>
       <c r="C9" s="4">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D9" s="4"/>
     </row>

--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69FD367-2A14-464A-95CE-40B1D64EF256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FF9D37-64BD-4D0C-A42A-240746678CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="796">
   <si>
     <t>3-ديوان</t>
   </si>
@@ -2351,9 +2351,6 @@
   </si>
   <si>
     <t>مجراية بكادوش 50 سم بلاطة جروميكس GROMIX</t>
-  </si>
-  <si>
-    <t>مجراية بكادوش 60 سم بلاطة جروميكس GROMIX</t>
   </si>
   <si>
     <t>مويتر طرمبة غاطسة ليو LEO QDX1.5-17-0.37LA</t>
@@ -2976,7 +2973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E5C9A6-5EC3-4592-9122-0E1001CE6231}">
-  <dimension ref="A1:E698"/>
+  <dimension ref="A1:E697"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.8984375" style="2" bestFit="1" customWidth="1"/>
@@ -3070,7 +3067,7 @@
         <v>39</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D7" s="13">
         <v>600</v>
@@ -3121,7 +3118,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D10" s="13">
         <v>500</v>
@@ -4019,13 +4016,13 @@
         <v>572</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D63" s="13">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -4036,13 +4033,13 @@
         <v>572</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D64" s="13">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
@@ -4172,13 +4169,13 @@
         <v>574</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D72" s="13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
@@ -4189,13 +4186,13 @@
         <v>574</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D73" s="13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
@@ -4444,13 +4441,13 @@
         <v>578</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D88" s="13">
-        <v>1350</v>
+        <v>2725</v>
       </c>
       <c r="E88" s="1">
         <v>0</v>
@@ -4461,13 +4458,13 @@
         <v>578</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D89" s="13">
-        <v>2725</v>
+        <v>1350</v>
       </c>
       <c r="E89" s="1">
         <v>0</v>
@@ -4495,13 +4492,13 @@
         <v>578</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D91" s="13">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
@@ -4512,13 +4509,13 @@
         <v>578</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D92" s="13">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
@@ -4685,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D102" s="13">
         <v>1</v>
@@ -4787,7 +4784,7 @@
         <v>39</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D108" s="13">
         <v>600</v>
@@ -5158,13 +5155,13 @@
         <v>590</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D130" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
@@ -5175,13 +5172,13 @@
         <v>590</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D131" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -5192,13 +5189,13 @@
         <v>590</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>79</v>
       </c>
       <c r="D132" s="13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -5209,13 +5206,13 @@
         <v>590</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>79</v>
       </c>
       <c r="D133" s="13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -5226,13 +5223,13 @@
         <v>590</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D134" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -5243,13 +5240,13 @@
         <v>590</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D135" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
@@ -5345,7 +5342,7 @@
         <v>590</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C141" s="10" t="s">
         <v>84</v>
@@ -5362,7 +5359,7 @@
         <v>590</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C142" s="10" t="s">
         <v>84</v>
@@ -5498,13 +5495,13 @@
         <v>590</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>92</v>
       </c>
       <c r="D150" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E150" s="1">
         <v>0</v>
@@ -5515,13 +5512,13 @@
         <v>590</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C151" s="10" t="s">
         <v>92</v>
       </c>
       <c r="D151" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E151" s="1">
         <v>0</v>
@@ -6110,13 +6107,13 @@
         <v>584</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C186" s="10" t="s">
         <v>699</v>
       </c>
       <c r="D186" s="13">
-        <v>1920</v>
+        <v>400</v>
       </c>
       <c r="E186" s="1">
         <v>0</v>
@@ -6127,13 +6124,13 @@
         <v>584</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C187" s="10" t="s">
         <v>699</v>
       </c>
       <c r="D187" s="13">
-        <v>400</v>
+        <v>1920</v>
       </c>
       <c r="E187" s="1">
         <v>0</v>
@@ -6144,13 +6141,13 @@
         <v>584</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C188" s="10" t="s">
         <v>497</v>
       </c>
       <c r="D188" s="13">
-        <v>1600</v>
+        <v>240</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
@@ -6161,13 +6158,13 @@
         <v>584</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C189" s="10" t="s">
         <v>497</v>
       </c>
       <c r="D189" s="13">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
@@ -6252,7 +6249,7 @@
         <v>701</v>
       </c>
       <c r="D194" s="13">
-        <v>2880</v>
+        <v>2720</v>
       </c>
       <c r="E194" s="1">
         <v>0</v>
@@ -6283,7 +6280,7 @@
         <v>39</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D196" s="13">
         <v>2040</v>
@@ -6742,7 +6739,7 @@
         <v>39</v>
       </c>
       <c r="C223" s="10" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D223" s="13">
         <v>100</v>
@@ -7099,7 +7096,7 @@
         <v>39</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D244" s="13">
         <v>800</v>
@@ -7164,13 +7161,13 @@
         <v>613</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C248" s="10" t="s">
         <v>146</v>
       </c>
       <c r="D248" s="13">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="E248" s="1">
         <v>0</v>
@@ -7181,13 +7178,13 @@
         <v>613</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C249" s="10" t="s">
         <v>146</v>
       </c>
       <c r="D249" s="13">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="E249" s="1">
         <v>0</v>
@@ -7266,13 +7263,13 @@
         <v>613</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C254" s="10" t="s">
         <v>148</v>
       </c>
       <c r="D254" s="13">
-        <v>520</v>
+        <v>600</v>
       </c>
       <c r="E254" s="1">
         <v>0</v>
@@ -7283,13 +7280,13 @@
         <v>613</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C255" s="10" t="s">
         <v>148</v>
       </c>
       <c r="D255" s="13">
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="E255" s="1">
         <v>0</v>
@@ -7493,7 +7490,7 @@
         <v>158</v>
       </c>
       <c r="D267" s="13">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="E267" s="1">
         <v>0</v>
@@ -7864,7 +7861,7 @@
         <v>0</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D289" s="13">
         <v>30</v>
@@ -7884,7 +7881,7 @@
         <v>740</v>
       </c>
       <c r="D290" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E290" s="1">
         <v>0</v>
@@ -8286,13 +8283,13 @@
         <v>620</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C314" s="10" t="s">
         <v>181</v>
       </c>
       <c r="D314" s="13">
-        <v>800</v>
+        <v>125</v>
       </c>
       <c r="E314" s="1">
         <v>0</v>
@@ -8320,13 +8317,13 @@
         <v>620</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C316" s="10" t="s">
         <v>181</v>
       </c>
       <c r="D316" s="13">
-        <v>125</v>
+        <v>800</v>
       </c>
       <c r="E316" s="1">
         <v>0</v>
@@ -8694,13 +8691,13 @@
         <v>628</v>
       </c>
       <c r="B338" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C338" s="10" t="s">
         <v>188</v>
       </c>
       <c r="D338" s="13">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="E338" s="1">
         <v>0</v>
@@ -8711,13 +8708,13 @@
         <v>628</v>
       </c>
       <c r="B339" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C339" s="10" t="s">
         <v>188</v>
       </c>
       <c r="D339" s="13">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="E339" s="1">
         <v>0</v>
@@ -9258,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="C371" s="10" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="D371" s="13">
         <v>24</v>
@@ -9612,13 +9609,13 @@
         <v>636</v>
       </c>
       <c r="B392" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C392" s="10" t="s">
         <v>217</v>
       </c>
       <c r="D392" s="13">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="E392" s="1">
         <v>0</v>
@@ -9629,13 +9626,13 @@
         <v>636</v>
       </c>
       <c r="B393" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C393" s="10" t="s">
         <v>217</v>
       </c>
       <c r="D393" s="13">
-        <v>200</v>
+        <v>2550</v>
       </c>
       <c r="E393" s="1">
         <v>0</v>
@@ -9646,13 +9643,13 @@
         <v>636</v>
       </c>
       <c r="B394" s="10" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C394" s="10" t="s">
         <v>217</v>
       </c>
       <c r="D394" s="13">
-        <v>2550</v>
+        <v>360</v>
       </c>
       <c r="E394" s="1">
         <v>0</v>
@@ -10105,13 +10102,13 @@
         <v>644</v>
       </c>
       <c r="B421" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C421" s="10" t="s">
         <v>233</v>
       </c>
       <c r="D421" s="13">
-        <v>1775</v>
+        <v>300</v>
       </c>
       <c r="E421" s="1">
         <v>0</v>
@@ -10122,13 +10119,13 @@
         <v>644</v>
       </c>
       <c r="B422" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C422" s="10" t="s">
         <v>233</v>
       </c>
       <c r="D422" s="13">
-        <v>300</v>
+        <v>1775</v>
       </c>
       <c r="E422" s="1">
         <v>0</v>
@@ -10723,7 +10720,7 @@
         <v>762</v>
       </c>
       <c r="D457" s="13">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E457" s="1">
         <v>0</v>
@@ -10740,7 +10737,7 @@
         <v>763</v>
       </c>
       <c r="D458" s="13">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E458" s="1">
         <v>0</v>
@@ -10748,16 +10745,16 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="10" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="B459" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C459" s="10" t="s">
-        <v>764</v>
+        <v>694</v>
       </c>
       <c r="D459" s="13">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E459" s="1">
         <v>0</v>
@@ -10771,10 +10768,10 @@
         <v>0</v>
       </c>
       <c r="C460" s="10" t="s">
-        <v>694</v>
+        <v>474</v>
       </c>
       <c r="D460" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E460" s="1">
         <v>0</v>
@@ -10782,16 +10779,16 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="10" t="s">
-        <v>583</v>
+        <v>652</v>
       </c>
       <c r="B461" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C461" s="10" t="s">
-        <v>474</v>
+        <v>254</v>
       </c>
       <c r="D461" s="13">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E461" s="1">
         <v>0</v>
@@ -10799,16 +10796,16 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="10" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B462" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C462" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D462" s="13">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E462" s="1">
         <v>0</v>
@@ -10819,13 +10816,13 @@
         <v>653</v>
       </c>
       <c r="B463" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C463" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D463" s="13">
-        <v>47</v>
+        <v>830</v>
       </c>
       <c r="E463" s="1">
         <v>0</v>
@@ -10839,10 +10836,10 @@
         <v>39</v>
       </c>
       <c r="C464" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D464" s="13">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="E464" s="1">
         <v>0</v>
@@ -10856,10 +10853,10 @@
         <v>39</v>
       </c>
       <c r="C465" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D465" s="13">
-        <v>850</v>
+        <v>1250</v>
       </c>
       <c r="E465" s="1">
         <v>0</v>
@@ -10873,10 +10870,10 @@
         <v>39</v>
       </c>
       <c r="C466" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D466" s="13">
-        <v>1250</v>
+        <v>400</v>
       </c>
       <c r="E466" s="1">
         <v>0</v>
@@ -10884,16 +10881,16 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B467" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C467" s="10" t="s">
-        <v>259</v>
+        <v>773</v>
       </c>
       <c r="D467" s="13">
-        <v>400</v>
+        <v>3760</v>
       </c>
       <c r="E467" s="1">
         <v>0</v>
@@ -10904,13 +10901,13 @@
         <v>652</v>
       </c>
       <c r="B468" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C468" s="10" t="s">
-        <v>774</v>
+        <v>260</v>
       </c>
       <c r="D468" s="13">
-        <v>3760</v>
+        <v>779</v>
       </c>
       <c r="E468" s="1">
         <v>0</v>
@@ -10935,16 +10932,16 @@
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="10" t="s">
-        <v>652</v>
+        <v>552</v>
       </c>
       <c r="B470" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C470" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D470" s="13">
-        <v>779</v>
+        <v>273</v>
       </c>
       <c r="E470" s="1">
         <v>0</v>
@@ -10952,16 +10949,16 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="10" t="s">
-        <v>552</v>
+        <v>652</v>
       </c>
       <c r="B471" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C471" s="10" t="s">
-        <v>261</v>
+        <v>774</v>
       </c>
       <c r="D471" s="13">
-        <v>273</v>
+        <v>1632</v>
       </c>
       <c r="E471" s="1">
         <v>0</v>
@@ -10969,16 +10966,16 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="10" t="s">
-        <v>652</v>
+        <v>568</v>
       </c>
       <c r="B472" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C472" s="10" t="s">
-        <v>775</v>
+        <v>262</v>
       </c>
       <c r="D472" s="13">
-        <v>1632</v>
+        <v>3</v>
       </c>
       <c r="E472" s="1">
         <v>0</v>
@@ -10992,10 +10989,10 @@
         <v>0</v>
       </c>
       <c r="C473" s="10" t="s">
-        <v>262</v>
+        <v>502</v>
       </c>
       <c r="D473" s="13">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E473" s="1">
         <v>0</v>
@@ -11003,16 +11000,16 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>568</v>
+        <v>606</v>
       </c>
       <c r="B474" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C474" s="10" t="s">
-        <v>502</v>
+        <v>263</v>
       </c>
       <c r="D474" s="13">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E474" s="1">
         <v>0</v>
@@ -11026,10 +11023,10 @@
         <v>0</v>
       </c>
       <c r="C475" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D475" s="13">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E475" s="1">
         <v>0</v>
@@ -11040,13 +11037,13 @@
         <v>606</v>
       </c>
       <c r="B476" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C476" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D476" s="13">
-        <v>6</v>
+        <v>840</v>
       </c>
       <c r="E476" s="1">
         <v>0</v>
@@ -11060,10 +11057,10 @@
         <v>39</v>
       </c>
       <c r="C477" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D477" s="13">
-        <v>840</v>
+        <v>10</v>
       </c>
       <c r="E477" s="1">
         <v>0</v>
@@ -11077,7 +11074,7 @@
         <v>39</v>
       </c>
       <c r="C478" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D478" s="13">
         <v>10</v>
@@ -11094,10 +11091,10 @@
         <v>39</v>
       </c>
       <c r="C479" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D479" s="13">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="E479" s="1">
         <v>0</v>
@@ -11111,10 +11108,10 @@
         <v>39</v>
       </c>
       <c r="C480" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D480" s="13">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E480" s="1">
         <v>0</v>
@@ -11128,10 +11125,10 @@
         <v>39</v>
       </c>
       <c r="C481" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D481" s="13">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E481" s="1">
         <v>0</v>
@@ -11145,10 +11142,10 @@
         <v>39</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>270</v>
+        <v>418</v>
       </c>
       <c r="D482" s="13">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E482" s="1">
         <v>0</v>
@@ -11156,16 +11153,16 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="10" t="s">
-        <v>606</v>
+        <v>549</v>
       </c>
       <c r="B483" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C483" s="10" t="s">
-        <v>418</v>
+        <v>271</v>
       </c>
       <c r="D483" s="13">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="E483" s="1">
         <v>0</v>
@@ -11173,16 +11170,16 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="10" t="s">
-        <v>549</v>
+        <v>652</v>
       </c>
       <c r="B484" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C484" s="10" t="s">
-        <v>271</v>
+        <v>775</v>
       </c>
       <c r="D484" s="13">
-        <v>75</v>
+        <v>575</v>
       </c>
       <c r="E484" s="1">
         <v>0</v>
@@ -11199,7 +11196,7 @@
         <v>776</v>
       </c>
       <c r="D485" s="13">
-        <v>575</v>
+        <v>9500</v>
       </c>
       <c r="E485" s="1">
         <v>0</v>
@@ -11216,7 +11213,7 @@
         <v>777</v>
       </c>
       <c r="D486" s="13">
-        <v>9500</v>
+        <v>575</v>
       </c>
       <c r="E486" s="1">
         <v>0</v>
@@ -11227,13 +11224,13 @@
         <v>652</v>
       </c>
       <c r="B487" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>778</v>
+        <v>272</v>
       </c>
       <c r="D487" s="13">
-        <v>575</v>
+        <v>40</v>
       </c>
       <c r="E487" s="1">
         <v>0</v>
@@ -11244,13 +11241,13 @@
         <v>652</v>
       </c>
       <c r="B488" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C488" s="10" t="s">
-        <v>272</v>
+        <v>778</v>
       </c>
       <c r="D488" s="13">
-        <v>40</v>
+        <v>5000</v>
       </c>
       <c r="E488" s="1">
         <v>0</v>
@@ -11258,16 +11255,16 @@
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
-        <v>652</v>
+        <v>551</v>
       </c>
       <c r="B489" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C489" s="10" t="s">
-        <v>779</v>
+        <v>410</v>
       </c>
       <c r="D489" s="13">
-        <v>5000</v>
+        <v>16400</v>
       </c>
       <c r="E489" s="1">
         <v>0</v>
@@ -11275,16 +11272,16 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="B490" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C490" s="10" t="s">
-        <v>410</v>
+        <v>273</v>
       </c>
       <c r="D490" s="13">
-        <v>16400</v>
+        <v>1</v>
       </c>
       <c r="E490" s="1">
         <v>0</v>
@@ -11298,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="C491" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D491" s="13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E491" s="1">
         <v>0</v>
@@ -11315,10 +11312,10 @@
         <v>0</v>
       </c>
       <c r="C492" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D492" s="13">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E492" s="1">
         <v>0</v>
@@ -11332,10 +11329,10 @@
         <v>0</v>
       </c>
       <c r="C493" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D493" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E493" s="1">
         <v>0</v>
@@ -11349,7 +11346,7 @@
         <v>0</v>
       </c>
       <c r="C494" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D494" s="13">
         <v>1</v>
@@ -11366,7 +11363,7 @@
         <v>0</v>
       </c>
       <c r="C495" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D495" s="13">
         <v>1</v>
@@ -11383,7 +11380,7 @@
         <v>0</v>
       </c>
       <c r="C496" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D496" s="13">
         <v>1</v>
@@ -11400,10 +11397,10 @@
         <v>0</v>
       </c>
       <c r="C497" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D497" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E497" s="1">
         <v>0</v>
@@ -11417,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="C498" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D498" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E498" s="1">
         <v>0</v>
@@ -11434,10 +11431,10 @@
         <v>0</v>
       </c>
       <c r="C499" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D499" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E499" s="1">
         <v>0</v>
@@ -11445,16 +11442,16 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B500" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C500" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D500" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E500" s="1">
         <v>0</v>
@@ -11462,16 +11459,16 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B501" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C501" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D501" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E501" s="1">
         <v>0</v>
@@ -11485,10 +11482,10 @@
         <v>0</v>
       </c>
       <c r="C502" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D502" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E502" s="1">
         <v>0</v>
@@ -11496,13 +11493,13 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B503" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C503" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D503" s="13">
         <v>1</v>
@@ -11513,13 +11510,13 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="B504" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C504" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D504" s="13">
         <v>1</v>
@@ -11530,13 +11527,13 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>549</v>
+        <v>611</v>
       </c>
       <c r="B505" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C505" s="10" t="s">
-        <v>287</v>
+        <v>478</v>
       </c>
       <c r="D505" s="13">
         <v>1</v>
@@ -11553,7 +11550,7 @@
         <v>0</v>
       </c>
       <c r="C506" s="10" t="s">
-        <v>478</v>
+        <v>288</v>
       </c>
       <c r="D506" s="13">
         <v>1</v>
@@ -11564,16 +11561,16 @@
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>611</v>
+        <v>549</v>
       </c>
       <c r="B507" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C507" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D507" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E507" s="1">
         <v>0</v>
@@ -11581,13 +11578,13 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B508" s="10" t="s">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="C508" s="10" t="s">
-        <v>289</v>
+        <v>706</v>
       </c>
       <c r="D508" s="13">
         <v>7</v>
@@ -11604,10 +11601,10 @@
         <v>515</v>
       </c>
       <c r="C509" s="10" t="s">
-        <v>706</v>
+        <v>676</v>
       </c>
       <c r="D509" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E509" s="1">
         <v>0</v>
@@ -11621,10 +11618,10 @@
         <v>515</v>
       </c>
       <c r="C510" s="10" t="s">
-        <v>676</v>
+        <v>754</v>
       </c>
       <c r="D510" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E510" s="1">
         <v>0</v>
@@ -11638,10 +11635,10 @@
         <v>515</v>
       </c>
       <c r="C511" s="10" t="s">
-        <v>754</v>
+        <v>516</v>
       </c>
       <c r="D511" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E511" s="1">
         <v>0</v>
@@ -11655,10 +11652,10 @@
         <v>515</v>
       </c>
       <c r="C512" s="10" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D512" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E512" s="1">
         <v>0</v>
@@ -11666,16 +11663,16 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>555</v>
+        <v>655</v>
       </c>
       <c r="B513" s="10" t="s">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="C513" s="10" t="s">
-        <v>517</v>
+        <v>693</v>
       </c>
       <c r="D513" s="13">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E513" s="1">
         <v>0</v>
@@ -11683,16 +11680,16 @@
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>655</v>
+        <v>555</v>
       </c>
       <c r="B514" s="10" t="s">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="C514" s="10" t="s">
-        <v>693</v>
+        <v>518</v>
       </c>
       <c r="D514" s="13">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E514" s="1">
         <v>0</v>
@@ -11706,10 +11703,10 @@
         <v>515</v>
       </c>
       <c r="C515" s="10" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D515" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E515" s="1">
         <v>0</v>
@@ -11723,10 +11720,10 @@
         <v>515</v>
       </c>
       <c r="C516" s="10" t="s">
-        <v>519</v>
+        <v>791</v>
       </c>
       <c r="D516" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E516" s="1">
         <v>0</v>
@@ -11740,10 +11737,10 @@
         <v>515</v>
       </c>
       <c r="C517" s="10" t="s">
-        <v>792</v>
+        <v>695</v>
       </c>
       <c r="D517" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E517" s="1">
         <v>0</v>
@@ -11757,7 +11754,7 @@
         <v>515</v>
       </c>
       <c r="C518" s="10" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="D518" s="13">
         <v>2</v>
@@ -11774,10 +11771,10 @@
         <v>515</v>
       </c>
       <c r="C519" s="10" t="s">
-        <v>707</v>
+        <v>520</v>
       </c>
       <c r="D519" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E519" s="1">
         <v>0</v>
@@ -11791,7 +11788,7 @@
         <v>515</v>
       </c>
       <c r="C520" s="10" t="s">
-        <v>520</v>
+        <v>757</v>
       </c>
       <c r="D520" s="13">
         <v>1</v>
@@ -11805,10 +11802,10 @@
         <v>555</v>
       </c>
       <c r="B521" s="10" t="s">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="C521" s="10" t="s">
-        <v>757</v>
+        <v>290</v>
       </c>
       <c r="D521" s="13">
         <v>1</v>
@@ -11819,13 +11816,13 @@
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
-        <v>555</v>
+        <v>655</v>
       </c>
       <c r="B522" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C522" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D522" s="13">
         <v>1</v>
@@ -11842,10 +11839,10 @@
         <v>0</v>
       </c>
       <c r="C523" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D523" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E523" s="1">
         <v>0</v>
@@ -11859,10 +11856,10 @@
         <v>0</v>
       </c>
       <c r="C524" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D524" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E524" s="1">
         <v>0</v>
@@ -11876,7 +11873,7 @@
         <v>0</v>
       </c>
       <c r="C525" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D525" s="13">
         <v>1</v>
@@ -11893,7 +11890,7 @@
         <v>0</v>
       </c>
       <c r="C526" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D526" s="13">
         <v>1</v>
@@ -11910,7 +11907,7 @@
         <v>0</v>
       </c>
       <c r="C527" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D527" s="13">
         <v>1</v>
@@ -11927,10 +11924,10 @@
         <v>0</v>
       </c>
       <c r="C528" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D528" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E528" s="1">
         <v>0</v>
@@ -11938,13 +11935,13 @@
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" s="10" t="s">
-        <v>655</v>
+        <v>555</v>
       </c>
       <c r="B529" s="10" t="s">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="C529" s="10" t="s">
-        <v>297</v>
+        <v>521</v>
       </c>
       <c r="D529" s="13">
         <v>2</v>
@@ -11961,10 +11958,10 @@
         <v>515</v>
       </c>
       <c r="C530" s="10" t="s">
-        <v>521</v>
+        <v>698</v>
       </c>
       <c r="D530" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E530" s="1">
         <v>0</v>
@@ -11978,10 +11975,10 @@
         <v>515</v>
       </c>
       <c r="C531" s="10" t="s">
-        <v>698</v>
+        <v>522</v>
       </c>
       <c r="D531" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E531" s="1">
         <v>0</v>
@@ -11995,10 +11992,10 @@
         <v>515</v>
       </c>
       <c r="C532" s="10" t="s">
-        <v>522</v>
+        <v>692</v>
       </c>
       <c r="D532" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E532" s="1">
         <v>0</v>
@@ -12012,10 +12009,10 @@
         <v>515</v>
       </c>
       <c r="C533" s="10" t="s">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="D533" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E533" s="1">
         <v>0</v>
@@ -12029,10 +12026,10 @@
         <v>515</v>
       </c>
       <c r="C534" s="10" t="s">
-        <v>705</v>
+        <v>750</v>
       </c>
       <c r="D534" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E534" s="1">
         <v>0</v>
@@ -12040,16 +12037,16 @@
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" s="10" t="s">
-        <v>555</v>
+        <v>743</v>
       </c>
       <c r="B535" s="10" t="s">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="C535" s="10" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="D535" s="13">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E535" s="1">
         <v>0</v>
@@ -12057,16 +12054,16 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="10" t="s">
-        <v>743</v>
+        <v>557</v>
       </c>
       <c r="B536" s="10" t="s">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="C536" s="10" t="s">
-        <v>744</v>
+        <v>696</v>
       </c>
       <c r="D536" s="13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E536" s="1">
         <v>0</v>
@@ -12080,7 +12077,7 @@
         <v>515</v>
       </c>
       <c r="C537" s="10" t="s">
-        <v>696</v>
+        <v>523</v>
       </c>
       <c r="D537" s="13">
         <v>1</v>
@@ -12091,13 +12088,13 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="10" t="s">
-        <v>557</v>
+        <v>611</v>
       </c>
       <c r="B538" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C538" s="10" t="s">
-        <v>523</v>
+        <v>736</v>
       </c>
       <c r="D538" s="13">
         <v>1</v>
@@ -12114,10 +12111,10 @@
         <v>515</v>
       </c>
       <c r="C539" s="10" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D539" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E539" s="1">
         <v>0</v>
@@ -12125,16 +12122,16 @@
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" s="10" t="s">
-        <v>611</v>
+        <v>654</v>
       </c>
       <c r="B540" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C540" s="10" t="s">
-        <v>737</v>
+        <v>524</v>
       </c>
       <c r="D540" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E540" s="1">
         <v>0</v>
@@ -12148,7 +12145,7 @@
         <v>515</v>
       </c>
       <c r="C541" s="10" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D541" s="13">
         <v>1</v>
@@ -12159,13 +12156,13 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" s="10" t="s">
-        <v>654</v>
+        <v>557</v>
       </c>
       <c r="B542" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C542" s="10" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D542" s="13">
         <v>1</v>
@@ -12182,7 +12179,7 @@
         <v>515</v>
       </c>
       <c r="C543" s="10" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D543" s="13">
         <v>1</v>
@@ -12199,7 +12196,7 @@
         <v>515</v>
       </c>
       <c r="C544" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D544" s="13">
         <v>1</v>
@@ -12216,10 +12213,10 @@
         <v>515</v>
       </c>
       <c r="C545" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D545" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E545" s="1">
         <v>0</v>
@@ -12233,10 +12230,10 @@
         <v>515</v>
       </c>
       <c r="C546" s="10" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D546" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E546" s="1">
         <v>0</v>
@@ -12244,16 +12241,16 @@
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" s="10" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B547" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C547" s="10" t="s">
-        <v>530</v>
+        <v>545</v>
       </c>
       <c r="D547" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E547" s="1">
         <v>0</v>
@@ -12267,10 +12264,10 @@
         <v>515</v>
       </c>
       <c r="C548" s="10" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="D548" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E548" s="1">
         <v>0</v>
@@ -12284,7 +12281,7 @@
         <v>515</v>
       </c>
       <c r="C549" s="10" t="s">
-        <v>531</v>
+        <v>546</v>
       </c>
       <c r="D549" s="13">
         <v>1</v>
@@ -12301,7 +12298,7 @@
         <v>515</v>
       </c>
       <c r="C550" s="10" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="D550" s="13">
         <v>1</v>
@@ -12312,13 +12309,13 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" s="10" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B551" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C551" s="10" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D551" s="13">
         <v>1</v>
@@ -12335,7 +12332,7 @@
         <v>515</v>
       </c>
       <c r="C552" s="10" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D552" s="13">
         <v>1</v>
@@ -12346,13 +12343,13 @@
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" s="10" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B553" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C553" s="10" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="D553" s="13">
         <v>1</v>
@@ -12369,7 +12366,7 @@
         <v>515</v>
       </c>
       <c r="C554" s="10" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="D554" s="13">
         <v>1</v>
@@ -12386,10 +12383,10 @@
         <v>515</v>
       </c>
       <c r="C555" s="10" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D555" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E555" s="1">
         <v>0</v>
@@ -12403,10 +12400,10 @@
         <v>515</v>
       </c>
       <c r="C556" s="10" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D556" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E556" s="1">
         <v>0</v>
@@ -12420,10 +12417,10 @@
         <v>515</v>
       </c>
       <c r="C557" s="10" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D557" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E557" s="1">
         <v>0</v>
@@ -12437,10 +12434,10 @@
         <v>515</v>
       </c>
       <c r="C558" s="10" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D558" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E558" s="1">
         <v>0</v>
@@ -12454,10 +12451,10 @@
         <v>515</v>
       </c>
       <c r="C559" s="10" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D559" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E559" s="1">
         <v>0</v>
@@ -12465,16 +12462,16 @@
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" s="10" t="s">
-        <v>555</v>
+        <v>611</v>
       </c>
       <c r="B560" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C560" s="10" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D560" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E560" s="1">
         <v>0</v>
@@ -12482,16 +12479,16 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" s="10" t="s">
-        <v>611</v>
+        <v>655</v>
       </c>
       <c r="B561" s="10" t="s">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="C561" s="10" t="s">
-        <v>541</v>
+        <v>298</v>
       </c>
       <c r="D561" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E561" s="1">
         <v>0</v>
@@ -12499,13 +12496,13 @@
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" s="10" t="s">
-        <v>655</v>
+        <v>555</v>
       </c>
       <c r="B562" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C562" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D562" s="13">
         <v>1</v>
@@ -12522,7 +12519,7 @@
         <v>0</v>
       </c>
       <c r="C563" s="10" t="s">
-        <v>299</v>
+        <v>486</v>
       </c>
       <c r="D563" s="13">
         <v>1</v>
@@ -12539,10 +12536,10 @@
         <v>0</v>
       </c>
       <c r="C564" s="10" t="s">
-        <v>486</v>
+        <v>300</v>
       </c>
       <c r="D564" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E564" s="1">
         <v>0</v>
@@ -12567,13 +12564,13 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" s="10" t="s">
-        <v>555</v>
+        <v>611</v>
       </c>
       <c r="B566" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C566" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D566" s="13">
         <v>2</v>
@@ -12590,10 +12587,10 @@
         <v>0</v>
       </c>
       <c r="C567" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D567" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E567" s="1">
         <v>0</v>
@@ -12607,7 +12604,7 @@
         <v>0</v>
       </c>
       <c r="C568" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D568" s="13">
         <v>1</v>
@@ -12618,13 +12615,13 @@
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" s="10" t="s">
-        <v>611</v>
+        <v>557</v>
       </c>
       <c r="B569" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C569" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D569" s="13">
         <v>1</v>
@@ -12641,7 +12638,7 @@
         <v>0</v>
       </c>
       <c r="C570" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D570" s="13">
         <v>1</v>
@@ -12652,16 +12649,16 @@
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" s="10" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B571" s="10" t="s">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="C571" s="10" t="s">
-        <v>305</v>
+        <v>680</v>
       </c>
       <c r="D571" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E571" s="1">
         <v>0</v>
@@ -12675,10 +12672,10 @@
         <v>515</v>
       </c>
       <c r="C572" s="10" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D572" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E572" s="1">
         <v>0</v>
@@ -12692,10 +12689,10 @@
         <v>515</v>
       </c>
       <c r="C573" s="10" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D573" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E573" s="1">
         <v>0</v>
@@ -12709,10 +12706,10 @@
         <v>515</v>
       </c>
       <c r="C574" s="10" t="s">
-        <v>682</v>
+        <v>542</v>
       </c>
       <c r="D574" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E574" s="1">
         <v>0</v>
@@ -12726,7 +12723,7 @@
         <v>515</v>
       </c>
       <c r="C575" s="10" t="s">
-        <v>542</v>
+        <v>683</v>
       </c>
       <c r="D575" s="13">
         <v>1</v>
@@ -12743,10 +12740,10 @@
         <v>515</v>
       </c>
       <c r="C576" s="10" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D576" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E576" s="1">
         <v>0</v>
@@ -12760,10 +12757,10 @@
         <v>515</v>
       </c>
       <c r="C577" s="10" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D577" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E577" s="1">
         <v>0</v>
@@ -12777,7 +12774,7 @@
         <v>515</v>
       </c>
       <c r="C578" s="10" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D578" s="13">
         <v>2</v>
@@ -12794,10 +12791,10 @@
         <v>515</v>
       </c>
       <c r="C579" s="10" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D579" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E579" s="1">
         <v>0</v>
@@ -12811,7 +12808,7 @@
         <v>515</v>
       </c>
       <c r="C580" s="10" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D580" s="13">
         <v>4</v>
@@ -12828,10 +12825,10 @@
         <v>515</v>
       </c>
       <c r="C581" s="10" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D581" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E581" s="1">
         <v>0</v>
@@ -12845,7 +12842,7 @@
         <v>515</v>
       </c>
       <c r="C582" s="10" t="s">
-        <v>689</v>
+        <v>543</v>
       </c>
       <c r="D582" s="13">
         <v>2</v>
@@ -12862,10 +12859,10 @@
         <v>515</v>
       </c>
       <c r="C583" s="10" t="s">
-        <v>543</v>
+        <v>677</v>
       </c>
       <c r="D583" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E583" s="1">
         <v>0</v>
@@ -12873,13 +12870,13 @@
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" s="10" t="s">
-        <v>555</v>
+        <v>611</v>
       </c>
       <c r="B584" s="10" t="s">
         <v>515</v>
       </c>
       <c r="C584" s="10" t="s">
-        <v>677</v>
+        <v>544</v>
       </c>
       <c r="D584" s="13">
         <v>1</v>
@@ -12890,16 +12887,16 @@
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585" s="10" t="s">
-        <v>611</v>
+        <v>557</v>
       </c>
       <c r="B585" s="10" t="s">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="C585" s="10" t="s">
-        <v>544</v>
+        <v>306</v>
       </c>
       <c r="D585" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E585" s="1">
         <v>0</v>
@@ -12907,16 +12904,16 @@
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A586" s="10" t="s">
-        <v>557</v>
+        <v>611</v>
       </c>
       <c r="B586" s="10" t="s">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="C586" s="10" t="s">
-        <v>306</v>
+        <v>548</v>
       </c>
       <c r="D586" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E586" s="1">
         <v>0</v>
@@ -12924,16 +12921,16 @@
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587" s="10" t="s">
-        <v>611</v>
+        <v>633</v>
       </c>
       <c r="B587" s="10" t="s">
-        <v>515</v>
+        <v>39</v>
       </c>
       <c r="C587" s="10" t="s">
-        <v>548</v>
+        <v>398</v>
       </c>
       <c r="D587" s="13">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E587" s="1">
         <v>0</v>
@@ -12947,10 +12944,10 @@
         <v>39</v>
       </c>
       <c r="C588" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D588" s="13">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E588" s="1">
         <v>0</v>
@@ -12958,16 +12955,16 @@
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" s="10" t="s">
-        <v>633</v>
+        <v>555</v>
       </c>
       <c r="B589" s="10" t="s">
-        <v>39</v>
+        <v>515</v>
       </c>
       <c r="C589" s="10" t="s">
-        <v>399</v>
+        <v>764</v>
       </c>
       <c r="D589" s="13">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E589" s="1">
         <v>0</v>
@@ -13001,7 +12998,7 @@
         <v>766</v>
       </c>
       <c r="D591" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E591" s="1">
         <v>0</v>
@@ -13018,7 +13015,7 @@
         <v>767</v>
       </c>
       <c r="D592" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E592" s="1">
         <v>0</v>
@@ -13026,16 +13023,16 @@
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A593" s="10" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B593" s="10" t="s">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="C593" s="10" t="s">
-        <v>768</v>
+        <v>307</v>
       </c>
       <c r="D593" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E593" s="1">
         <v>0</v>
@@ -13043,16 +13040,16 @@
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A594" s="10" t="s">
-        <v>549</v>
+        <v>657</v>
       </c>
       <c r="B594" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C594" s="10" t="s">
-        <v>307</v>
+        <v>779</v>
       </c>
       <c r="D594" s="13">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="E594" s="1">
         <v>0</v>
@@ -13060,7 +13057,7 @@
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A595" s="10" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="B595" s="10" t="s">
         <v>39</v>
@@ -13069,7 +13066,7 @@
         <v>780</v>
       </c>
       <c r="D595" s="13">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E595" s="1">
         <v>0</v>
@@ -13083,10 +13080,10 @@
         <v>39</v>
       </c>
       <c r="C596" s="10" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="D596" s="13">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="E596" s="1">
         <v>0</v>
@@ -13094,16 +13091,16 @@
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A597" s="10" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B597" s="10" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C597" s="10" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="D597" s="13">
-        <v>2400</v>
+        <v>1</v>
       </c>
       <c r="E597" s="1">
         <v>0</v>
@@ -13120,7 +13117,7 @@
         <v>795</v>
       </c>
       <c r="D598" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E598" s="1">
         <v>0</v>
@@ -13134,10 +13131,10 @@
         <v>9</v>
       </c>
       <c r="C599" s="10" t="s">
-        <v>796</v>
+        <v>423</v>
       </c>
       <c r="D599" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E599" s="1">
         <v>0</v>
@@ -13151,10 +13148,10 @@
         <v>9</v>
       </c>
       <c r="C600" s="10" t="s">
-        <v>423</v>
+        <v>512</v>
       </c>
       <c r="D600" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E600" s="1">
         <v>0</v>
@@ -13162,16 +13159,16 @@
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A601" s="10" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B601" s="10" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C601" s="10" t="s">
-        <v>512</v>
+        <v>781</v>
       </c>
       <c r="D601" s="13">
-        <v>1</v>
+        <v>1850</v>
       </c>
       <c r="E601" s="1">
         <v>0</v>
@@ -13179,16 +13176,16 @@
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A602" s="10" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B602" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C602" s="10" t="s">
-        <v>782</v>
+        <v>308</v>
       </c>
       <c r="D602" s="13">
-        <v>1850</v>
+        <v>37</v>
       </c>
       <c r="E602" s="1">
         <v>0</v>
@@ -13196,16 +13193,16 @@
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A603" s="10" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="B603" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C603" s="10" t="s">
-        <v>308</v>
+        <v>782</v>
       </c>
       <c r="D603" s="13">
-        <v>37</v>
+        <v>2500</v>
       </c>
       <c r="E603" s="1">
         <v>0</v>
@@ -13219,10 +13216,10 @@
         <v>39</v>
       </c>
       <c r="C604" s="10" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="D604" s="13">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="E604" s="1">
         <v>0</v>
@@ -13230,16 +13227,16 @@
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A605" s="10" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B605" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C605" s="10" t="s">
-        <v>790</v>
+        <v>728</v>
       </c>
       <c r="D605" s="13">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="E605" s="1">
         <v>0</v>
@@ -13253,10 +13250,10 @@
         <v>39</v>
       </c>
       <c r="C606" s="10" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D606" s="13">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="E606" s="1">
         <v>0</v>
@@ -13270,10 +13267,10 @@
         <v>39</v>
       </c>
       <c r="C607" s="10" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D607" s="13">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="E607" s="1">
         <v>0</v>
@@ -13287,10 +13284,10 @@
         <v>39</v>
       </c>
       <c r="C608" s="10" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D608" s="13">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="E608" s="1">
         <v>0</v>
@@ -13304,10 +13301,10 @@
         <v>39</v>
       </c>
       <c r="C609" s="10" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D609" s="13">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="E609" s="1">
         <v>0</v>
@@ -13321,10 +13318,10 @@
         <v>39</v>
       </c>
       <c r="C610" s="10" t="s">
-        <v>732</v>
+        <v>783</v>
       </c>
       <c r="D610" s="13">
-        <v>800</v>
+        <v>1250</v>
       </c>
       <c r="E610" s="1">
         <v>0</v>
@@ -13341,7 +13338,7 @@
         <v>784</v>
       </c>
       <c r="D611" s="13">
-        <v>1250</v>
+        <v>1550</v>
       </c>
       <c r="E611" s="1">
         <v>0</v>
@@ -13352,13 +13349,13 @@
         <v>657</v>
       </c>
       <c r="B612" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C612" s="10" t="s">
-        <v>785</v>
+        <v>309</v>
       </c>
       <c r="D612" s="13">
-        <v>1550</v>
+        <v>1070</v>
       </c>
       <c r="E612" s="1">
         <v>0</v>
@@ -13369,13 +13366,13 @@
         <v>657</v>
       </c>
       <c r="B613" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C613" s="10" t="s">
-        <v>309</v>
+        <v>785</v>
       </c>
       <c r="D613" s="13">
-        <v>1070</v>
+        <v>1700</v>
       </c>
       <c r="E613" s="1">
         <v>0</v>
@@ -13392,7 +13389,7 @@
         <v>786</v>
       </c>
       <c r="D614" s="13">
-        <v>1700</v>
+        <v>1000</v>
       </c>
       <c r="E614" s="1">
         <v>0</v>
@@ -13400,16 +13397,16 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" s="10" t="s">
-        <v>657</v>
+        <v>565</v>
       </c>
       <c r="B615" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C615" s="10" t="s">
-        <v>787</v>
+        <v>310</v>
       </c>
       <c r="D615" s="13">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="E615" s="1">
         <v>0</v>
@@ -13423,10 +13420,10 @@
         <v>0</v>
       </c>
       <c r="C616" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D616" s="13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E616" s="1">
         <v>0</v>
@@ -13434,16 +13431,16 @@
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" s="10" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B617" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C617" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D617" s="13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E617" s="1">
         <v>0</v>
@@ -13457,7 +13454,7 @@
         <v>0</v>
       </c>
       <c r="C618" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D618" s="13">
         <v>1</v>
@@ -13468,16 +13465,16 @@
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A619" s="10" t="s">
-        <v>566</v>
+        <v>658</v>
       </c>
       <c r="B619" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C619" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D619" s="13">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E619" s="1">
         <v>0</v>
@@ -13485,16 +13482,16 @@
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A620" s="10" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B620" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C620" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D620" s="13">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E620" s="1">
         <v>0</v>
@@ -13508,10 +13505,10 @@
         <v>0</v>
       </c>
       <c r="C621" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D621" s="13">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="E621" s="1">
         <v>0</v>
@@ -13519,16 +13516,16 @@
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A622" s="10" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B622" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C622" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D622" s="13">
-        <v>121</v>
+        <v>300</v>
       </c>
       <c r="E622" s="1">
         <v>0</v>
@@ -13539,7 +13536,7 @@
         <v>660</v>
       </c>
       <c r="B623" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C623" s="10" t="s">
         <v>317</v>
@@ -13553,13 +13550,13 @@
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A624" s="10" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B624" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C624" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D624" s="13">
         <v>300</v>
@@ -13570,16 +13567,16 @@
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A625" s="10" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B625" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C625" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D625" s="13">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E625" s="1">
         <v>0</v>
@@ -13587,16 +13584,16 @@
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A626" s="10" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B626" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C626" s="10" t="s">
-        <v>319</v>
+        <v>447</v>
       </c>
       <c r="D626" s="13">
-        <v>310</v>
+        <v>43</v>
       </c>
       <c r="E626" s="1">
         <v>0</v>
@@ -13604,16 +13601,16 @@
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A627" s="10" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B627" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C627" s="10" t="s">
-        <v>447</v>
+        <v>320</v>
       </c>
       <c r="D627" s="13">
-        <v>43</v>
+        <v>250</v>
       </c>
       <c r="E627" s="1">
         <v>0</v>
@@ -13624,13 +13621,13 @@
         <v>661</v>
       </c>
       <c r="B628" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C628" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D628" s="13">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E628" s="1">
         <v>0</v>
@@ -13641,13 +13638,13 @@
         <v>661</v>
       </c>
       <c r="B629" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C629" s="10" t="s">
         <v>321</v>
       </c>
       <c r="D629" s="13">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="E629" s="1">
         <v>0</v>
@@ -13658,13 +13655,13 @@
         <v>661</v>
       </c>
       <c r="B630" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C630" s="10" t="s">
-        <v>321</v>
+        <v>393</v>
       </c>
       <c r="D630" s="13">
-        <v>280</v>
+        <v>42</v>
       </c>
       <c r="E630" s="1">
         <v>0</v>
@@ -13678,10 +13675,10 @@
         <v>39</v>
       </c>
       <c r="C631" s="10" t="s">
-        <v>393</v>
+        <v>322</v>
       </c>
       <c r="D631" s="13">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E631" s="1">
         <v>0</v>
@@ -13689,16 +13686,16 @@
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632" s="10" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B632" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C632" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D632" s="13">
-        <v>24</v>
+        <v>250</v>
       </c>
       <c r="E632" s="1">
         <v>0</v>
@@ -13706,16 +13703,16 @@
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A633" s="10" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B633" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C633" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D633" s="13">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="E633" s="1">
         <v>0</v>
@@ -13723,16 +13720,16 @@
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A634" s="10" t="s">
-        <v>664</v>
+        <v>719</v>
       </c>
       <c r="B634" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C634" s="10" t="s">
-        <v>324</v>
+        <v>720</v>
       </c>
       <c r="D634" s="13">
-        <v>1250</v>
+        <v>100</v>
       </c>
       <c r="E634" s="1">
         <v>0</v>
@@ -13740,16 +13737,16 @@
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A635" s="10" t="s">
-        <v>719</v>
+        <v>664</v>
       </c>
       <c r="B635" s="10" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C635" s="10" t="s">
-        <v>720</v>
+        <v>325</v>
       </c>
       <c r="D635" s="13">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E635" s="1">
         <v>0</v>
@@ -13757,16 +13754,16 @@
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636" s="10" t="s">
-        <v>664</v>
+        <v>719</v>
       </c>
       <c r="B636" s="10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C636" s="10" t="s">
-        <v>325</v>
+        <v>721</v>
       </c>
       <c r="D636" s="13">
-        <v>160</v>
+        <v>35</v>
       </c>
       <c r="E636" s="1">
         <v>0</v>
@@ -13774,16 +13771,16 @@
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A637" s="10" t="s">
-        <v>719</v>
+        <v>664</v>
       </c>
       <c r="B637" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C637" s="10" t="s">
-        <v>721</v>
+        <v>326</v>
       </c>
       <c r="D637" s="13">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E637" s="1">
         <v>0</v>
@@ -13808,16 +13805,16 @@
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>664</v>
+        <v>719</v>
       </c>
       <c r="B639" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C639" s="1" t="s">
-        <v>326</v>
+        <v>722</v>
       </c>
       <c r="D639" s="14">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E639" s="1">
         <v>0</v>
@@ -13825,16 +13822,16 @@
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>719</v>
+        <v>664</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>722</v>
+        <v>391</v>
       </c>
       <c r="D640" s="14">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E640" s="1">
         <v>0</v>
@@ -13848,10 +13845,10 @@
         <v>39</v>
       </c>
       <c r="C641" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D641" s="14">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E641" s="1">
         <v>0</v>
@@ -13865,10 +13862,10 @@
         <v>39</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>392</v>
+        <v>327</v>
       </c>
       <c r="D642" s="14">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E642" s="1">
         <v>0</v>
@@ -13876,16 +13873,16 @@
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>39</v>
+        <v>405</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>327</v>
+        <v>416</v>
       </c>
       <c r="D643" s="14">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="E643" s="1">
         <v>0</v>
@@ -13896,13 +13893,13 @@
         <v>665</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="C644" s="1" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
       <c r="D644" s="14">
-        <v>2</v>
+        <v>1300</v>
       </c>
       <c r="E644" s="1">
         <v>0</v>
@@ -13916,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="C645" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D645" s="14">
-        <v>1300</v>
+        <v>29</v>
       </c>
       <c r="E645" s="1">
         <v>0</v>
@@ -13933,10 +13930,10 @@
         <v>0</v>
       </c>
       <c r="C646" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D646" s="14">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E646" s="1">
         <v>0</v>
@@ -13944,16 +13941,16 @@
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B647" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C647" s="1" t="s">
-        <v>330</v>
+        <v>464</v>
       </c>
       <c r="D647" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E647" s="1">
         <v>0</v>
@@ -13967,10 +13964,10 @@
         <v>0</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D648" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E648" s="1">
         <v>0</v>
@@ -13984,10 +13981,10 @@
         <v>0</v>
       </c>
       <c r="C649" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D649" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E649" s="1">
         <v>0</v>
@@ -13995,16 +13992,16 @@
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C650" s="1" t="s">
-        <v>466</v>
+        <v>331</v>
       </c>
       <c r="D650" s="14">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="E650" s="1">
         <v>0</v>
@@ -14018,10 +14015,10 @@
         <v>9</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D651" s="14">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E651" s="1">
         <v>0</v>
@@ -14035,10 +14032,10 @@
         <v>9</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D652" s="14">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="E652" s="1">
         <v>0</v>
@@ -14052,10 +14049,10 @@
         <v>9</v>
       </c>
       <c r="C653" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D653" s="14">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="E653" s="1">
         <v>0</v>
@@ -14063,16 +14060,16 @@
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C654" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D654" s="14">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E654" s="1">
         <v>0</v>
@@ -14086,10 +14083,10 @@
         <v>39</v>
       </c>
       <c r="C655" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D655" s="14">
-        <v>600</v>
+        <v>825</v>
       </c>
       <c r="E655" s="1">
         <v>0</v>
@@ -14097,16 +14094,16 @@
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C656" s="1" t="s">
-        <v>336</v>
+        <v>723</v>
       </c>
       <c r="D656" s="14">
-        <v>825</v>
+        <v>465</v>
       </c>
       <c r="E656" s="1">
         <v>0</v>
@@ -14114,16 +14111,16 @@
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B657" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C657" s="1" t="s">
-        <v>723</v>
+        <v>337</v>
       </c>
       <c r="D657" s="14">
-        <v>465</v>
+        <v>400</v>
       </c>
       <c r="E657" s="1">
         <v>0</v>
@@ -14148,16 +14145,16 @@
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B659" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C659" s="1" t="s">
-        <v>337</v>
+        <v>448</v>
       </c>
       <c r="D659" s="14">
-        <v>400</v>
+        <v>65</v>
       </c>
       <c r="E659" s="1">
         <v>0</v>
@@ -14165,16 +14162,16 @@
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C660" s="1" t="s">
-        <v>448</v>
+        <v>377</v>
       </c>
       <c r="D660" s="14">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E660" s="1">
         <v>0</v>
@@ -14188,10 +14185,10 @@
         <v>39</v>
       </c>
       <c r="C661" s="1" t="s">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="D661" s="14">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E661" s="1">
         <v>0</v>
@@ -14199,16 +14196,16 @@
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D662" s="14">
-        <v>72</v>
+        <v>1001</v>
       </c>
       <c r="E662" s="1">
         <v>0</v>
@@ -14222,10 +14219,10 @@
         <v>0</v>
       </c>
       <c r="C663" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D663" s="14">
-        <v>1001</v>
+        <v>1508</v>
       </c>
       <c r="E663" s="1">
         <v>0</v>
@@ -14233,16 +14230,16 @@
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B664" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D664" s="14">
-        <v>1508</v>
+        <v>600</v>
       </c>
       <c r="E664" s="1">
         <v>0</v>
@@ -14256,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="C665" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D665" s="14">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E665" s="1">
         <v>0</v>
@@ -14273,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="C666" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D666" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E666" s="1">
         <v>0</v>
@@ -14290,10 +14287,10 @@
         <v>0</v>
       </c>
       <c r="C667" s="1" t="s">
-        <v>343</v>
+        <v>500</v>
       </c>
       <c r="D667" s="14">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="E667" s="1">
         <v>0</v>
@@ -14307,10 +14304,10 @@
         <v>0</v>
       </c>
       <c r="C668" s="1" t="s">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="D668" s="14">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E668" s="1">
         <v>0</v>
@@ -14324,7 +14321,7 @@
         <v>0</v>
       </c>
       <c r="C669" s="1" t="s">
-        <v>344</v>
+        <v>404</v>
       </c>
       <c r="D669" s="14">
         <v>100</v>
@@ -14341,10 +14338,10 @@
         <v>0</v>
       </c>
       <c r="C670" s="1" t="s">
-        <v>404</v>
+        <v>345</v>
       </c>
       <c r="D670" s="14">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E670" s="1">
         <v>0</v>
@@ -14352,16 +14349,16 @@
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="B671" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C671" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D671" s="14">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="E671" s="1">
         <v>0</v>
@@ -14375,10 +14372,10 @@
         <v>0</v>
       </c>
       <c r="C672" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D672" s="14">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="E672" s="1">
         <v>0</v>
@@ -14386,16 +14383,16 @@
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>658</v>
+        <v>673</v>
       </c>
       <c r="B673" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C673" s="1" t="s">
-        <v>347</v>
+        <v>467</v>
       </c>
       <c r="D673" s="14">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="E673" s="1">
         <v>0</v>
@@ -14409,10 +14406,10 @@
         <v>0</v>
       </c>
       <c r="C674" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D674" s="14">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E674" s="1">
         <v>0</v>
@@ -14426,10 +14423,10 @@
         <v>0</v>
       </c>
       <c r="C675" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D675" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E675" s="1">
         <v>0</v>
@@ -14437,16 +14434,16 @@
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C676" s="1" t="s">
-        <v>469</v>
+        <v>348</v>
       </c>
       <c r="D676" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E676" s="1">
         <v>0</v>
@@ -14460,10 +14457,10 @@
         <v>9</v>
       </c>
       <c r="C677" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D677" s="14">
-        <v>15</v>
+        <v>225</v>
       </c>
       <c r="E677" s="1">
         <v>0</v>
@@ -14477,10 +14474,10 @@
         <v>9</v>
       </c>
       <c r="C678" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D678" s="14">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="E678" s="1">
         <v>0</v>
@@ -14488,16 +14485,16 @@
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>659</v>
+        <v>674</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C679" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D679" s="14">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="E679" s="1">
         <v>0</v>
@@ -14508,10 +14505,10 @@
         <v>674</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C680" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D680" s="14">
         <v>1200</v>
@@ -14528,10 +14525,10 @@
         <v>39</v>
       </c>
       <c r="C681" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D681" s="14">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="E681" s="1">
         <v>0</v>
@@ -14562,10 +14559,10 @@
         <v>39</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D683" s="14">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E683" s="1">
         <v>0</v>
@@ -14573,16 +14570,16 @@
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C684" s="1" t="s">
-        <v>354</v>
+        <v>748</v>
       </c>
       <c r="D684" s="14">
-        <v>500</v>
+        <v>235</v>
       </c>
       <c r="E684" s="1">
         <v>0</v>
@@ -14596,10 +14593,10 @@
         <v>0</v>
       </c>
       <c r="C685" s="1" t="s">
-        <v>748</v>
+        <v>724</v>
       </c>
       <c r="D685" s="14">
-        <v>235</v>
+        <v>150</v>
       </c>
       <c r="E685" s="1">
         <v>0</v>
@@ -14607,16 +14604,16 @@
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C686" s="1" t="s">
-        <v>724</v>
+        <v>355</v>
       </c>
       <c r="D686" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E686" s="1">
         <v>0</v>
@@ -14644,13 +14641,13 @@
         <v>674</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C688" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D688" s="14">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E688" s="1">
         <v>0</v>
@@ -14664,10 +14661,10 @@
         <v>0</v>
       </c>
       <c r="C689" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D689" s="14">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="E689" s="1">
         <v>0</v>
@@ -14675,16 +14672,16 @@
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B690" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C690" s="1" t="s">
-        <v>357</v>
+        <v>449</v>
       </c>
       <c r="D690" s="14">
-        <v>225</v>
+        <v>10</v>
       </c>
       <c r="E690" s="1">
         <v>0</v>
@@ -14692,16 +14689,16 @@
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C691" s="1" t="s">
-        <v>449</v>
+        <v>358</v>
       </c>
       <c r="D691" s="14">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="E691" s="1">
         <v>0</v>
@@ -14729,13 +14726,13 @@
         <v>674</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C693" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D693" s="14">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="E693" s="1">
         <v>0</v>
@@ -14746,13 +14743,13 @@
         <v>674</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C694" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D694" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E694" s="1">
         <v>0</v>
@@ -14763,13 +14760,13 @@
         <v>674</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C695" s="1" t="s">
         <v>360</v>
       </c>
       <c r="D695" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E695" s="1">
         <v>0</v>
@@ -14780,13 +14777,13 @@
         <v>674</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C696" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D696" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E696" s="1">
         <v>0</v>
@@ -14806,23 +14803,6 @@
         <v>30</v>
       </c>
       <c r="E697" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A698" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="B698" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C698" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="D698" s="14">
-        <v>64</v>
-      </c>
-      <c r="E698" s="1">
         <v>0</v>
       </c>
     </row>
@@ -14889,11 +14869,11 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str" cm="1">
-        <f t="array" ref="A6:C9">_xlfn._xlws.SORT(_xlfn._xlws.FILTER('جرد المواد'!B5:D9560,
-ISNUMBER(SEARCH(IF(B1="","*",B1),'جرد المواد'!C5:C9560))*
-ISNUMBER(SEARCH(IF(B2="","*",B2),'جرد المواد'!C5:C9560))*
-ISNUMBER(SEARCH(IF(B3="","*",B3),'جرد المواد'!C5:C9560))*
-ISNUMBER(SEARCH(IF(B4="","*",B4),'جرد المواد'!B5:B9560)),
+        <f t="array" ref="A6:C9">_xlfn._xlws.SORT(_xlfn._xlws.FILTER('جرد المواد'!B5:D9559,
+ISNUMBER(SEARCH(IF(B1="","*",B1),'جرد المواد'!C5:C9559))*
+ISNUMBER(SEARCH(IF(B2="","*",B2),'جرد المواد'!C5:C9559))*
+ISNUMBER(SEARCH(IF(B3="","*",B3),'جرد المواد'!C5:C9559))*
+ISNUMBER(SEARCH(IF(B4="","*",B4),'جرد المواد'!B5:B9559)),
 "لا توجد نتائج"),
 2,1)</f>
         <v>3-ديوان</v>

--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970AEC00-D5BC-4B14-8DD7-7DC3A96CD9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0443691A-434D-40ED-A7FF-7339ECF00B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2080" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="792">
   <si>
     <t>3-ديوان</t>
   </si>
@@ -1480,9 +1480,6 @@
     <t>قسطل تلحيم 32 ملم اخضر تركي</t>
   </si>
   <si>
-    <t>مجلى ستانلس 100*50</t>
-  </si>
-  <si>
     <t>غطاء زغرتا ابيض بلاستيك</t>
   </si>
   <si>
@@ -2305,9 +2302,6 @@
     <t>برميل طرش نص كاوتشوك غاردينا 102 بريمو PRIMO</t>
   </si>
   <si>
-    <t>موتير 0.75 حصان صامت ليو LEO ACM60</t>
-  </si>
-  <si>
     <t>صندوق 040 ابيض</t>
   </si>
   <si>
@@ -2429,6 +2423,18 @@
   </si>
   <si>
     <t>نربيج زراعي 1 1/2" 50 ملم 50 متر اسود</t>
+  </si>
+  <si>
+    <t>موتير 0.75 حصان سارق LEO AJM 60H JET</t>
+  </si>
+  <si>
+    <t>موتير 0.75 حصان صامت ليو LEO 3ACM60</t>
+  </si>
+  <si>
+    <t>موتير غاطس ليو LEO 5DWM4/6.1.1P</t>
+  </si>
+  <si>
+    <t>موتير غاطس ليو LEO AKS-251PH (0.3HP)</t>
   </si>
 </sst>
 </file>
@@ -2955,7 +2961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E5C9A6-5EC3-4592-9122-0E1001CE6231}">
-  <dimension ref="A1:E691"/>
+  <dimension ref="A1:E693"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.8984375" style="2" bestFit="1" customWidth="1"/>
@@ -2992,7 +2998,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>0</v>
@@ -3009,7 +3015,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>0</v>
@@ -3026,7 +3032,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>0</v>
@@ -3043,13 +3049,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D7" s="13">
         <v>600</v>
@@ -3060,7 +3066,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>0</v>
@@ -3077,7 +3083,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>0</v>
@@ -3094,13 +3100,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D10" s="13">
         <v>500</v>
@@ -3111,7 +3117,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>0</v>
@@ -3128,7 +3134,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>0</v>
@@ -3145,7 +3151,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>0</v>
@@ -3162,7 +3168,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>0</v>
@@ -3179,7 +3185,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>0</v>
@@ -3196,7 +3202,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>9</v>
@@ -3213,13 +3219,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D17" s="13">
         <v>6</v>
@@ -3230,13 +3236,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D18" s="13">
         <v>3</v>
@@ -3247,13 +3253,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D19" s="13">
         <v>1</v>
@@ -3264,7 +3270,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>0</v>
@@ -3281,7 +3287,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>0</v>
@@ -3298,7 +3304,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>0</v>
@@ -3315,7 +3321,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>0</v>
@@ -3332,13 +3338,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D24" s="13">
         <v>360</v>
@@ -3349,7 +3355,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>0</v>
@@ -3366,7 +3372,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>0</v>
@@ -3383,13 +3389,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D27" s="13">
         <v>8</v>
@@ -3400,13 +3406,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D28" s="13">
         <v>5</v>
@@ -3417,13 +3423,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D29" s="13">
         <v>3</v>
@@ -3434,7 +3440,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>0</v>
@@ -3451,13 +3457,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D31" s="13">
         <v>5</v>
@@ -3468,7 +3474,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>0</v>
@@ -3485,13 +3491,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D33" s="13">
         <v>1</v>
@@ -3502,7 +3508,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>0</v>
@@ -3519,7 +3525,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>0</v>
@@ -3536,7 +3542,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>0</v>
@@ -3553,7 +3559,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>0</v>
@@ -3570,7 +3576,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>0</v>
@@ -3587,7 +3593,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>0</v>
@@ -3604,7 +3610,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>0</v>
@@ -3621,7 +3627,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>0</v>
@@ -3638,7 +3644,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>0</v>
@@ -3655,7 +3661,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>0</v>
@@ -3672,7 +3678,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>0</v>
@@ -3689,7 +3695,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>0</v>
@@ -3706,7 +3712,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>0</v>
@@ -3723,7 +3729,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>0</v>
@@ -3740,7 +3746,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>0</v>
@@ -3757,7 +3763,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>0</v>
@@ -3774,13 +3780,13 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D50" s="13">
         <v>790</v>
@@ -3791,7 +3797,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>0</v>
@@ -3808,7 +3814,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>0</v>
@@ -3825,7 +3831,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>0</v>
@@ -3842,7 +3848,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>38</v>
@@ -3859,7 +3865,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>38</v>
@@ -3876,7 +3882,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>38</v>
@@ -3893,13 +3899,13 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D57" s="13">
         <v>132</v>
@@ -3910,7 +3916,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>0</v>
@@ -3927,7 +3933,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>0</v>
@@ -3944,7 +3950,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>0</v>
@@ -3961,7 +3967,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B61" s="10" t="s">
         <v>0</v>
@@ -3978,16 +3984,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D62" s="13">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3995,16 +4001,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D63" s="13">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -4012,7 +4018,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>9</v>
@@ -4029,7 +4035,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>0</v>
@@ -4046,7 +4052,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>9</v>
@@ -4063,7 +4069,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>9</v>
@@ -4080,7 +4086,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>0</v>
@@ -4097,7 +4103,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>0</v>
@@ -4114,7 +4120,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>0</v>
@@ -4131,7 +4137,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B71" s="10" t="s">
         <v>0</v>
@@ -4148,7 +4154,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>9</v>
@@ -4165,7 +4171,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B73" s="10" t="s">
         <v>9</v>
@@ -4182,7 +4188,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>0</v>
@@ -4199,7 +4205,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>9</v>
@@ -4216,7 +4222,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>0</v>
@@ -4233,7 +4239,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B77" s="10" t="s">
         <v>0</v>
@@ -4250,7 +4256,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>0</v>
@@ -4267,7 +4273,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>38</v>
@@ -4284,13 +4290,13 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C80" s="10" t="s">
         <v>702</v>
-      </c>
-      <c r="B80" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>703</v>
       </c>
       <c r="D80" s="13">
         <v>70</v>
@@ -4301,7 +4307,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B81" s="10" t="s">
         <v>0</v>
@@ -4318,7 +4324,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>38</v>
@@ -4335,16 +4341,16 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D83" s="13">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="E83" s="1">
         <v>0</v>
@@ -4352,16 +4358,16 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D84" s="13">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="E84" s="1">
         <v>0</v>
@@ -4369,7 +4375,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>38</v>
@@ -4386,13 +4392,13 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D86" s="13">
         <v>170</v>
@@ -4403,7 +4409,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>9</v>
@@ -4420,7 +4426,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>0</v>
@@ -4437,7 +4443,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B89" s="10" t="s">
         <v>0</v>
@@ -4454,7 +4460,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B90" s="10" t="s">
         <v>9</v>
@@ -4471,7 +4477,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>0</v>
@@ -4488,7 +4494,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>0</v>
@@ -4505,7 +4511,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B93" s="10" t="s">
         <v>0</v>
@@ -4522,7 +4528,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B94" s="10" t="s">
         <v>38</v>
@@ -4539,7 +4545,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B95" s="10" t="s">
         <v>38</v>
@@ -4556,7 +4562,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B96" s="10" t="s">
         <v>0</v>
@@ -4573,7 +4579,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B97" s="10" t="s">
         <v>9</v>
@@ -4590,7 +4596,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>9</v>
@@ -4607,7 +4613,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B99" s="10" t="s">
         <v>0</v>
@@ -4624,13 +4630,13 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B100" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D100" s="13">
         <v>4</v>
@@ -4641,13 +4647,13 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D101" s="13">
         <v>1</v>
@@ -4658,13 +4664,13 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D102" s="13">
         <v>3</v>
@@ -4675,13 +4681,13 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B103" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D103" s="13">
         <v>1</v>
@@ -4692,13 +4698,13 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B104" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D104" s="13">
         <v>4</v>
@@ -4709,7 +4715,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B105" s="10" t="s">
         <v>0</v>
@@ -4726,7 +4732,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>0</v>
@@ -4743,13 +4749,13 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D107" s="13">
         <v>600</v>
@@ -4760,7 +4766,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>0</v>
@@ -4777,7 +4783,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B109" s="10" t="s">
         <v>0</v>
@@ -4794,7 +4800,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>0</v>
@@ -4811,7 +4817,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B111" s="10" t="s">
         <v>0</v>
@@ -4828,7 +4834,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B112" s="10" t="s">
         <v>0</v>
@@ -4845,7 +4851,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B113" s="10" t="s">
         <v>0</v>
@@ -4862,7 +4868,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B114" s="10" t="s">
         <v>38</v>
@@ -4879,7 +4885,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B115" s="10" t="s">
         <v>0</v>
@@ -4896,7 +4902,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>0</v>
@@ -4913,7 +4919,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B117" s="10" t="s">
         <v>0</v>
@@ -4930,7 +4936,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B118" s="10" t="s">
         <v>0</v>
@@ -4947,13 +4953,13 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B119" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D119" s="13">
         <v>1</v>
@@ -4964,13 +4970,13 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B120" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D120" s="13">
         <v>2</v>
@@ -4981,13 +4987,13 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B121" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D121" s="13">
         <v>2</v>
@@ -4998,7 +5004,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>38</v>
@@ -5015,7 +5021,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B123" s="10" t="s">
         <v>38</v>
@@ -5032,7 +5038,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B124" s="10" t="s">
         <v>38</v>
@@ -5049,7 +5055,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B125" s="10" t="s">
         <v>38</v>
@@ -5066,7 +5072,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B126" s="10" t="s">
         <v>38</v>
@@ -5083,7 +5089,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B127" s="10" t="s">
         <v>0</v>
@@ -5100,7 +5106,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B128" s="10" t="s">
         <v>38</v>
@@ -5117,16 +5123,16 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>77</v>
       </c>
       <c r="D129" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E129" s="1">
         <v>0</v>
@@ -5134,16 +5140,16 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>77</v>
       </c>
       <c r="D130" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
@@ -5151,16 +5157,16 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D131" s="13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -5168,16 +5174,16 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D132" s="13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -5185,7 +5191,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B133" s="10" t="s">
         <v>38</v>
@@ -5202,7 +5208,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B134" s="10" t="s">
         <v>0</v>
@@ -5219,7 +5225,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B135" s="10" t="s">
         <v>38</v>
@@ -5236,7 +5242,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B136" s="10" t="s">
         <v>0</v>
@@ -5253,16 +5259,16 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>81</v>
       </c>
       <c r="D137" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
@@ -5270,16 +5276,16 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>81</v>
       </c>
       <c r="D138" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
@@ -5287,7 +5293,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B139" s="10" t="s">
         <v>38</v>
@@ -5304,10 +5310,10 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C140" s="10" t="s">
         <v>83</v>
@@ -5321,16 +5327,16 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C141" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D141" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E141" s="1">
         <v>0</v>
@@ -5338,7 +5344,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B142" s="10" t="s">
         <v>38</v>
@@ -5355,7 +5361,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B143" s="10" t="s">
         <v>38</v>
@@ -5372,7 +5378,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B144" s="10" t="s">
         <v>38</v>
@@ -5389,7 +5395,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B145" s="10" t="s">
         <v>38</v>
@@ -5406,7 +5412,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B146" s="10" t="s">
         <v>38</v>
@@ -5423,7 +5429,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B147" s="10" t="s">
         <v>38</v>
@@ -5440,7 +5446,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B148" s="10" t="s">
         <v>38</v>
@@ -5457,7 +5463,7 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B149" s="10" t="s">
         <v>0</v>
@@ -5474,7 +5480,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B150" s="10" t="s">
         <v>38</v>
@@ -5491,7 +5497,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B151" s="10" t="s">
         <v>38</v>
@@ -5508,7 +5514,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B152" s="10" t="s">
         <v>38</v>
@@ -5525,7 +5531,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B153" s="10" t="s">
         <v>0</v>
@@ -5542,7 +5548,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B154" s="10" t="s">
         <v>0</v>
@@ -5559,7 +5565,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B155" s="10" t="s">
         <v>0</v>
@@ -5576,7 +5582,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B156" s="10" t="s">
         <v>38</v>
@@ -5593,7 +5599,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B157" s="10" t="s">
         <v>0</v>
@@ -5610,7 +5616,7 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B158" s="10" t="s">
         <v>0</v>
@@ -5627,7 +5633,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B159" s="10" t="s">
         <v>0</v>
@@ -5644,7 +5650,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B160" s="10" t="s">
         <v>0</v>
@@ -5661,7 +5667,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B161" s="10" t="s">
         <v>38</v>
@@ -5678,7 +5684,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B162" s="10" t="s">
         <v>0</v>
@@ -5695,7 +5701,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B163" s="10" t="s">
         <v>0</v>
@@ -5712,7 +5718,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B164" s="10" t="s">
         <v>0</v>
@@ -5729,7 +5735,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B165" s="10" t="s">
         <v>0</v>
@@ -5746,7 +5752,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B166" s="10" t="s">
         <v>38</v>
@@ -5763,7 +5769,7 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B167" s="10" t="s">
         <v>0</v>
@@ -5780,7 +5786,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B168" s="10" t="s">
         <v>0</v>
@@ -5797,7 +5803,7 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B169" s="10" t="s">
         <v>0</v>
@@ -5814,7 +5820,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B170" s="10" t="s">
         <v>0</v>
@@ -5831,7 +5837,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="10" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B171" s="10" t="s">
         <v>0</v>
@@ -5848,7 +5854,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="10" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B172" s="10" t="s">
         <v>0</v>
@@ -5865,13 +5871,13 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B173" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D173" s="13">
         <v>1</v>
@@ -5882,16 +5888,16 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C174" s="10" t="s">
         <v>109</v>
       </c>
       <c r="D174" s="13">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E174" s="1">
         <v>0</v>
@@ -5899,16 +5905,16 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C175" s="10" t="s">
         <v>109</v>
       </c>
       <c r="D175" s="13">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E175" s="1">
         <v>0</v>
@@ -5916,16 +5922,16 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C176" s="10" t="s">
         <v>110</v>
       </c>
       <c r="D176" s="13">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E176" s="1">
         <v>0</v>
@@ -5933,16 +5939,16 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>110</v>
       </c>
       <c r="D177" s="13">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E177" s="1">
         <v>0</v>
@@ -5950,7 +5956,7 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B178" s="10" t="s">
         <v>38</v>
@@ -5967,7 +5973,7 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B179" s="10" t="s">
         <v>38</v>
@@ -5984,7 +5990,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B180" s="10" t="s">
         <v>38</v>
@@ -6001,7 +6007,7 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B181" s="10" t="s">
         <v>0</v>
@@ -6018,7 +6024,7 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B182" s="10" t="s">
         <v>0</v>
@@ -6035,13 +6041,13 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B183" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C183" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D183" s="13">
         <v>14</v>
@@ -6052,7 +6058,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B184" s="10" t="s">
         <v>9</v>
@@ -6069,16 +6075,16 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C185" s="10" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D185" s="13">
-        <v>1920</v>
+        <v>400</v>
       </c>
       <c r="E185" s="1">
         <v>0</v>
@@ -6086,16 +6092,16 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D186" s="13">
-        <v>400</v>
+        <v>1920</v>
       </c>
       <c r="E186" s="1">
         <v>0</v>
@@ -6103,13 +6109,13 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B187" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C187" s="10" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D187" s="13">
         <v>240</v>
@@ -6120,13 +6126,13 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B188" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D188" s="13">
         <v>1600</v>
@@ -6137,13 +6143,13 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B189" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D189" s="13">
         <v>800</v>
@@ -6154,7 +6160,7 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B190" s="10" t="s">
         <v>0</v>
@@ -6171,16 +6177,16 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D191" s="13">
-        <v>600</v>
+        <v>4400</v>
       </c>
       <c r="E191" s="1">
         <v>0</v>
@@ -6188,16 +6194,16 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D192" s="13">
-        <v>4400</v>
+        <v>600</v>
       </c>
       <c r="E192" s="1">
         <v>0</v>
@@ -6205,13 +6211,13 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B193" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D193" s="13">
         <v>2720</v>
@@ -6222,7 +6228,7 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B194" s="10" t="s">
         <v>0</v>
@@ -6239,13 +6245,13 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B195" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D195" s="13">
         <v>2040</v>
@@ -6256,13 +6262,13 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B196" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D196" s="13">
         <v>1080</v>
@@ -6273,7 +6279,7 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B197" s="10" t="s">
         <v>38</v>
@@ -6290,7 +6296,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B198" s="10" t="s">
         <v>0</v>
@@ -6307,7 +6313,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B199" s="10" t="s">
         <v>38</v>
@@ -6324,7 +6330,7 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B200" s="10" t="s">
         <v>38</v>
@@ -6341,7 +6347,7 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B201" s="10" t="s">
         <v>38</v>
@@ -6358,7 +6364,7 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B202" s="10" t="s">
         <v>38</v>
@@ -6375,7 +6381,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B203" s="10" t="s">
         <v>0</v>
@@ -6392,7 +6398,7 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B204" s="10" t="s">
         <v>0</v>
@@ -6409,7 +6415,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B205" s="10" t="s">
         <v>0</v>
@@ -6426,7 +6432,7 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B206" s="10" t="s">
         <v>0</v>
@@ -6443,7 +6449,7 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B207" s="10" t="s">
         <v>0</v>
@@ -6460,7 +6466,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B208" s="10" t="s">
         <v>0</v>
@@ -6477,7 +6483,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B209" s="10" t="s">
         <v>0</v>
@@ -6494,7 +6500,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B210" s="10" t="s">
         <v>0</v>
@@ -6511,7 +6517,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B211" s="10" t="s">
         <v>0</v>
@@ -6528,7 +6534,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B212" s="10" t="s">
         <v>0</v>
@@ -6545,13 +6551,13 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B213" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C213" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D213" s="13">
         <v>22</v>
@@ -6562,7 +6568,7 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B214" s="10" t="s">
         <v>0</v>
@@ -6579,7 +6585,7 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B215" s="10" t="s">
         <v>0</v>
@@ -6596,7 +6602,7 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B216" s="10" t="s">
         <v>0</v>
@@ -6613,7 +6619,7 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B217" s="10" t="s">
         <v>0</v>
@@ -6630,7 +6636,7 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B218" s="10" t="s">
         <v>0</v>
@@ -6647,7 +6653,7 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B219" s="10" t="s">
         <v>0</v>
@@ -6664,7 +6670,7 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B220" s="10" t="s">
         <v>0</v>
@@ -6681,7 +6687,7 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B221" s="10" t="s">
         <v>0</v>
@@ -6698,13 +6704,13 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B222" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D222" s="13">
         <v>100</v>
@@ -6715,16 +6721,16 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B223" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C223" s="10" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D223" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E223" s="1">
         <v>0</v>
@@ -6732,13 +6738,13 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B224" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D224" s="13">
         <v>19</v>
@@ -6749,7 +6755,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B225" s="10" t="s">
         <v>0</v>
@@ -6766,7 +6772,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B226" s="10" t="s">
         <v>0</v>
@@ -6783,13 +6789,13 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B227" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C227" s="10" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D227" s="13">
         <v>10</v>
@@ -6800,13 +6806,13 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B228" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C228" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D228" s="13">
         <v>1</v>
@@ -6817,7 +6823,7 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B229" s="10" t="s">
         <v>0</v>
@@ -6834,7 +6840,7 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B230" s="10" t="s">
         <v>0</v>
@@ -6851,7 +6857,7 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B231" s="10" t="s">
         <v>0</v>
@@ -6868,7 +6874,7 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B232" s="10" t="s">
         <v>0</v>
@@ -6885,7 +6891,7 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="10" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B233" s="10" t="s">
         <v>38</v>
@@ -6902,7 +6908,7 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="10" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B234" s="10" t="s">
         <v>38</v>
@@ -6919,7 +6925,7 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B235" s="10" t="s">
         <v>0</v>
@@ -6936,7 +6942,7 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B236" s="10" t="s">
         <v>0</v>
@@ -6953,7 +6959,7 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B237" s="10" t="s">
         <v>0</v>
@@ -6970,13 +6976,13 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B238" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C238" s="10" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D238" s="13">
         <v>10</v>
@@ -6987,13 +6993,13 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B239" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D239" s="13">
         <v>10</v>
@@ -7004,13 +7010,13 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B240" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D240" s="13">
         <v>15</v>
@@ -7021,7 +7027,7 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B241" s="10" t="s">
         <v>0</v>
@@ -7038,7 +7044,7 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B242" s="10" t="s">
         <v>9</v>
@@ -7055,13 +7061,13 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B243" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D243" s="13">
         <v>800</v>
@@ -7072,13 +7078,13 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B244" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D244" s="13">
         <v>2000</v>
@@ -7089,13 +7095,13 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B245" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C245" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D245" s="13">
         <v>1800</v>
@@ -7106,7 +7112,7 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B246" s="10" t="s">
         <v>38</v>
@@ -7123,7 +7129,7 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B247" s="10" t="s">
         <v>38</v>
@@ -7140,7 +7146,7 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B248" s="10" t="s">
         <v>0</v>
@@ -7157,13 +7163,13 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B249" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C249" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D249" s="13">
         <v>60</v>
@@ -7174,13 +7180,13 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B250" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C250" s="10" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D250" s="13">
         <v>40</v>
@@ -7191,7 +7197,7 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B251" s="10" t="s">
         <v>0</v>
@@ -7208,7 +7214,7 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B252" s="10" t="s">
         <v>38</v>
@@ -7225,7 +7231,7 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B253" s="10" t="s">
         <v>38</v>
@@ -7242,7 +7248,7 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B254" s="10" t="s">
         <v>0</v>
@@ -7259,7 +7265,7 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B255" s="10" t="s">
         <v>0</v>
@@ -7276,7 +7282,7 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B256" s="10" t="s">
         <v>38</v>
@@ -7293,7 +7299,7 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B257" s="10" t="s">
         <v>0</v>
@@ -7310,13 +7316,13 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B258" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C258" s="10" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D258" s="13">
         <v>49</v>
@@ -7327,7 +7333,7 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B259" s="10" t="s">
         <v>0</v>
@@ -7344,7 +7350,7 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B260" s="10" t="s">
         <v>0</v>
@@ -7361,7 +7367,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B261" s="10" t="s">
         <v>0</v>
@@ -7378,7 +7384,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B262" s="10" t="s">
         <v>0</v>
@@ -7395,7 +7401,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B263" s="10" t="s">
         <v>0</v>
@@ -7412,7 +7418,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B264" s="10" t="s">
         <v>0</v>
@@ -7429,7 +7435,7 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B265" s="10" t="s">
         <v>0</v>
@@ -7446,7 +7452,7 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B266" s="10" t="s">
         <v>0</v>
@@ -7463,7 +7469,7 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B267" s="10" t="s">
         <v>0</v>
@@ -7480,13 +7486,13 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B268" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C268" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D268" s="13">
         <v>28</v>
@@ -7497,7 +7503,7 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B269" s="10" t="s">
         <v>0</v>
@@ -7514,7 +7520,7 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B270" s="10" t="s">
         <v>0</v>
@@ -7531,13 +7537,13 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B271" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C271" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D271" s="13">
         <v>12</v>
@@ -7548,7 +7554,7 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B272" s="10" t="s">
         <v>9</v>
@@ -7565,7 +7571,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B273" s="10" t="s">
         <v>9</v>
@@ -7582,13 +7588,13 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B274" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C274" s="10" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D274" s="13">
         <v>100</v>
@@ -7599,7 +7605,7 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B275" s="10" t="s">
         <v>0</v>
@@ -7616,13 +7622,13 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B276" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C276" s="10" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D276" s="13">
         <v>30</v>
@@ -7633,13 +7639,13 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B277" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C277" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D277" s="13">
         <v>40</v>
@@ -7650,7 +7656,7 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B278" s="10" t="s">
         <v>0</v>
@@ -7667,7 +7673,7 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B279" s="10" t="s">
         <v>0</v>
@@ -7684,7 +7690,7 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B280" s="10" t="s">
         <v>0</v>
@@ -7701,7 +7707,7 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B281" s="10" t="s">
         <v>0</v>
@@ -7718,7 +7724,7 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B282" s="10" t="s">
         <v>0</v>
@@ -7735,13 +7741,13 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B283" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C283" s="10" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D283" s="13">
         <v>3</v>
@@ -7752,7 +7758,7 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B284" s="10" t="s">
         <v>0</v>
@@ -7769,13 +7775,13 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B285" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C285" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D285" s="13">
         <v>1</v>
@@ -7786,7 +7792,7 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B286" s="10" t="s">
         <v>0</v>
@@ -7803,7 +7809,7 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B287" s="10" t="s">
         <v>0</v>
@@ -7820,13 +7826,13 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B288" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C288" s="10" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D288" s="13">
         <v>30</v>
@@ -7837,13 +7843,13 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B289" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D289" s="13">
         <v>1</v>
@@ -7854,13 +7860,13 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B290" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C290" s="10" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D290" s="13">
         <v>1</v>
@@ -7871,13 +7877,13 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B291" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C291" s="10" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D291" s="13">
         <v>5</v>
@@ -7888,13 +7894,13 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B292" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C292" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D292" s="13">
         <v>1</v>
@@ -7905,7 +7911,7 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B293" s="10" t="s">
         <v>0</v>
@@ -7922,7 +7928,7 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B294" s="10" t="s">
         <v>0</v>
@@ -7939,7 +7945,7 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B295" s="10" t="s">
         <v>0</v>
@@ -7956,13 +7962,13 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B296" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D296" s="13">
         <v>1</v>
@@ -7973,7 +7979,7 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B297" s="10" t="s">
         <v>38</v>
@@ -7990,13 +7996,13 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B298" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C298" s="10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D298" s="13">
         <v>165</v>
@@ -8007,13 +8013,13 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B299" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C299" s="10" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D299" s="13">
         <v>65</v>
@@ -8024,7 +8030,7 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B300" s="10" t="s">
         <v>38</v>
@@ -8041,7 +8047,7 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B301" s="10" t="s">
         <v>38</v>
@@ -8058,13 +8064,13 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B302" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D302" s="13">
         <v>14</v>
@@ -8075,13 +8081,13 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B303" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C303" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D303" s="13">
         <v>13</v>
@@ -8092,7 +8098,7 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B304" s="10" t="s">
         <v>38</v>
@@ -8109,13 +8115,13 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B305" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C305" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D305" s="13">
         <v>28</v>
@@ -8126,13 +8132,13 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B306" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C306" s="10" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D306" s="13">
         <v>250</v>
@@ -8143,7 +8149,7 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B307" s="10" t="s">
         <v>0</v>
@@ -8160,7 +8166,7 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B308" s="10" t="s">
         <v>38</v>
@@ -8177,7 +8183,7 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B309" s="10" t="s">
         <v>9</v>
@@ -8194,7 +8200,7 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B310" s="10" t="s">
         <v>38</v>
@@ -8211,13 +8217,13 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B311" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C311" s="10" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D311" s="13">
         <v>75</v>
@@ -8228,7 +8234,7 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B312" s="10" t="s">
         <v>38</v>
@@ -8245,16 +8251,16 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B313" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C313" s="10" t="s">
         <v>180</v>
       </c>
       <c r="D313" s="13">
-        <v>102</v>
+        <v>800</v>
       </c>
       <c r="E313" s="1">
         <v>0</v>
@@ -8262,16 +8268,16 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C314" s="10" t="s">
         <v>180</v>
       </c>
       <c r="D314" s="13">
-        <v>800</v>
+        <v>125</v>
       </c>
       <c r="E314" s="1">
         <v>0</v>
@@ -8279,16 +8285,16 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C315" s="10" t="s">
         <v>180</v>
       </c>
       <c r="D315" s="13">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="E315" s="1">
         <v>0</v>
@@ -8296,13 +8302,13 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B316" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C316" s="10" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D316" s="13">
         <v>20</v>
@@ -8313,7 +8319,7 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B317" s="10" t="s">
         <v>9</v>
@@ -8330,13 +8336,13 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B318" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C318" s="10" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D318" s="13">
         <v>450</v>
@@ -8347,7 +8353,7 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B319" s="10" t="s">
         <v>38</v>
@@ -8364,7 +8370,7 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B320" s="10" t="s">
         <v>0</v>
@@ -8381,7 +8387,7 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B321" s="10" t="s">
         <v>9</v>
@@ -8398,7 +8404,7 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B322" s="10" t="s">
         <v>38</v>
@@ -8415,7 +8421,7 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B323" s="10" t="s">
         <v>0</v>
@@ -8432,16 +8438,16 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B324" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C324" s="10" t="s">
         <v>182</v>
       </c>
       <c r="D324" s="13">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="E324" s="1">
         <v>0</v>
@@ -8449,16 +8455,16 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C325" s="10" t="s">
         <v>182</v>
       </c>
       <c r="D325" s="13">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="E325" s="1">
         <v>0</v>
@@ -8466,7 +8472,7 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B326" s="10" t="s">
         <v>38</v>
@@ -8483,7 +8489,7 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B327" s="10" t="s">
         <v>38</v>
@@ -8500,7 +8506,7 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B328" s="10" t="s">
         <v>9</v>
@@ -8517,7 +8523,7 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B329" s="10" t="s">
         <v>9</v>
@@ -8534,13 +8540,13 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B330" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C330" s="10" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D330" s="13">
         <v>1</v>
@@ -8551,13 +8557,13 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B331" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C331" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D331" s="13">
         <v>25</v>
@@ -8568,13 +8574,13 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B332" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C332" s="10" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D332" s="13">
         <v>10</v>
@@ -8585,7 +8591,7 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B333" s="10" t="s">
         <v>38</v>
@@ -8602,7 +8608,7 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B334" s="10" t="s">
         <v>38</v>
@@ -8619,7 +8625,7 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B335" s="10" t="s">
         <v>38</v>
@@ -8636,16 +8642,16 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B336" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C336" s="10" t="s">
         <v>187</v>
       </c>
       <c r="D336" s="13">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="E336" s="1">
         <v>0</v>
@@ -8653,16 +8659,16 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B337" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C337" s="10" t="s">
         <v>187</v>
       </c>
       <c r="D337" s="13">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="E337" s="1">
         <v>0</v>
@@ -8670,7 +8676,7 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B338" s="10" t="s">
         <v>38</v>
@@ -8687,7 +8693,7 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B339" s="10" t="s">
         <v>38</v>
@@ -8704,7 +8710,7 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B340" s="10" t="s">
         <v>38</v>
@@ -8721,7 +8727,7 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B341" s="10" t="s">
         <v>0</v>
@@ -8738,7 +8744,7 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B342" s="10" t="s">
         <v>38</v>
@@ -8755,10 +8761,10 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C343" s="10" t="s">
         <v>190</v>
@@ -8772,10 +8778,10 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C344" s="10" t="s">
         <v>190</v>
@@ -8789,16 +8795,16 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B345" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C345" s="10" t="s">
         <v>191</v>
       </c>
       <c r="D345" s="13">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E345" s="1">
         <v>0</v>
@@ -8806,16 +8812,16 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C346" s="10" t="s">
         <v>191</v>
       </c>
       <c r="D346" s="13">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E346" s="1">
         <v>0</v>
@@ -8823,7 +8829,7 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B347" s="10" t="s">
         <v>0</v>
@@ -8840,7 +8846,7 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B348" s="10" t="s">
         <v>38</v>
@@ -8857,7 +8863,7 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B349" s="10" t="s">
         <v>38</v>
@@ -8874,13 +8880,13 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="10" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B350" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C350" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D350" s="13">
         <v>90</v>
@@ -8891,13 +8897,13 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="10" t="s">
+        <v>706</v>
+      </c>
+      <c r="B351" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C351" s="10" t="s">
         <v>707</v>
-      </c>
-      <c r="B351" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C351" s="10" t="s">
-        <v>708</v>
       </c>
       <c r="D351" s="13">
         <v>50</v>
@@ -8908,7 +8914,7 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B352" s="10" t="s">
         <v>38</v>
@@ -8925,7 +8931,7 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B353" s="10" t="s">
         <v>38</v>
@@ -8942,7 +8948,7 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B354" s="10" t="s">
         <v>38</v>
@@ -8959,7 +8965,7 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B355" s="10" t="s">
         <v>0</v>
@@ -8976,7 +8982,7 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B356" s="10" t="s">
         <v>0</v>
@@ -8993,7 +8999,7 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B357" s="10" t="s">
         <v>0</v>
@@ -9010,7 +9016,7 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B358" s="10" t="s">
         <v>0</v>
@@ -9027,13 +9033,13 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B359" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C359" s="10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D359" s="13">
         <v>1</v>
@@ -9044,7 +9050,7 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" s="10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B360" s="10" t="s">
         <v>0</v>
@@ -9061,7 +9067,7 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B361" s="10" t="s">
         <v>9</v>
@@ -9078,7 +9084,7 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B362" s="10" t="s">
         <v>0</v>
@@ -9095,7 +9101,7 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B363" s="10" t="s">
         <v>0</v>
@@ -9112,16 +9118,16 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B364" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C364" s="10" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D364" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E364" s="1">
         <v>0</v>
@@ -9129,7 +9135,7 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B365" s="10" t="s">
         <v>0</v>
@@ -9146,13 +9152,13 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B366" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C366" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D366" s="13">
         <v>19</v>
@@ -9163,7 +9169,7 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B367" s="10" t="s">
         <v>0</v>
@@ -9180,13 +9186,13 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B368" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C368" s="10" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D368" s="13">
         <v>14</v>
@@ -9197,16 +9203,16 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B369" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C369" s="10" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D369" s="13">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E369" s="1">
         <v>0</v>
@@ -9214,7 +9220,7 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B370" s="10" t="s">
         <v>0</v>
@@ -9231,7 +9237,7 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B371" s="10" t="s">
         <v>0</v>
@@ -9248,16 +9254,16 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B372" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C372" s="10" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D372" s="13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E372" s="1">
         <v>0</v>
@@ -9265,7 +9271,7 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B373" s="10" t="s">
         <v>0</v>
@@ -9282,7 +9288,7 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B374" s="10" t="s">
         <v>0</v>
@@ -9299,13 +9305,13 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B375" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C375" s="10" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D375" s="13">
         <v>1</v>
@@ -9316,7 +9322,7 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B376" s="10" t="s">
         <v>0</v>
@@ -9333,7 +9339,7 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B377" s="10" t="s">
         <v>0</v>
@@ -9350,7 +9356,7 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B378" s="10" t="s">
         <v>38</v>
@@ -9367,7 +9373,7 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B379" s="10" t="s">
         <v>38</v>
@@ -9384,7 +9390,7 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B380" s="10" t="s">
         <v>38</v>
@@ -9401,7 +9407,7 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B381" s="10" t="s">
         <v>38</v>
@@ -9418,7 +9424,7 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B382" s="10" t="s">
         <v>38</v>
@@ -9435,7 +9441,7 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B383" s="10" t="s">
         <v>0</v>
@@ -9452,7 +9458,7 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B384" s="10" t="s">
         <v>0</v>
@@ -9469,7 +9475,7 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B385" s="10" t="s">
         <v>0</v>
@@ -9486,7 +9492,7 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B386" s="10" t="s">
         <v>0</v>
@@ -9503,7 +9509,7 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B387" s="10" t="s">
         <v>38</v>
@@ -9520,7 +9526,7 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B388" s="10" t="s">
         <v>0</v>
@@ -9537,7 +9543,7 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B389" s="10" t="s">
         <v>0</v>
@@ -9554,7 +9560,7 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B390" s="10" t="s">
         <v>9</v>
@@ -9571,7 +9577,7 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B391" s="10" t="s">
         <v>0</v>
@@ -9588,7 +9594,7 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B392" s="10" t="s">
         <v>38</v>
@@ -9605,7 +9611,7 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B393" s="10" t="s">
         <v>38</v>
@@ -9622,7 +9628,7 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B394" s="10" t="s">
         <v>0</v>
@@ -9639,7 +9645,7 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B395" s="10" t="s">
         <v>38</v>
@@ -9656,7 +9662,7 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B396" s="10" t="s">
         <v>0</v>
@@ -9673,7 +9679,7 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B397" s="10" t="s">
         <v>0</v>
@@ -9690,7 +9696,7 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B398" s="10" t="s">
         <v>0</v>
@@ -9707,7 +9713,7 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B399" s="10" t="s">
         <v>0</v>
@@ -9724,7 +9730,7 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B400" s="10" t="s">
         <v>0</v>
@@ -9741,7 +9747,7 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B401" s="10" t="s">
         <v>0</v>
@@ -9758,7 +9764,7 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B402" s="10" t="s">
         <v>0</v>
@@ -9775,7 +9781,7 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B403" s="10" t="s">
         <v>0</v>
@@ -9792,7 +9798,7 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B404" s="10" t="s">
         <v>0</v>
@@ -9809,7 +9815,7 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B405" s="10" t="s">
         <v>9</v>
@@ -9826,7 +9832,7 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B406" s="10" t="s">
         <v>9</v>
@@ -9843,7 +9849,7 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B407" s="10" t="s">
         <v>0</v>
@@ -9860,7 +9866,7 @@
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B408" s="10" t="s">
         <v>9</v>
@@ -9877,7 +9883,7 @@
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B409" s="10" t="s">
         <v>9</v>
@@ -9894,7 +9900,7 @@
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B410" s="10" t="s">
         <v>9</v>
@@ -9911,7 +9917,7 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B411" s="10" t="s">
         <v>0</v>
@@ -9928,7 +9934,7 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B412" s="10" t="s">
         <v>38</v>
@@ -9945,7 +9951,7 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B413" s="10" t="s">
         <v>0</v>
@@ -9962,7 +9968,7 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B414" s="10" t="s">
         <v>38</v>
@@ -9979,7 +9985,7 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B415" s="10" t="s">
         <v>38</v>
@@ -9996,13 +10002,13 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B416" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C416" s="10" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D416" s="13">
         <v>290</v>
@@ -10013,7 +10019,7 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B417" s="10" t="s">
         <v>38</v>
@@ -10030,7 +10036,7 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B418" s="10" t="s">
         <v>0</v>
@@ -10047,7 +10053,7 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B419" s="10" t="s">
         <v>0</v>
@@ -10064,7 +10070,7 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B420" s="10" t="s">
         <v>9</v>
@@ -10081,7 +10087,7 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B421" s="10" t="s">
         <v>0</v>
@@ -10098,7 +10104,7 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B422" s="10" t="s">
         <v>0</v>
@@ -10115,7 +10121,7 @@
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B423" s="10" t="s">
         <v>38</v>
@@ -10132,7 +10138,7 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B424" s="10" t="s">
         <v>38</v>
@@ -10149,7 +10155,7 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B425" s="10" t="s">
         <v>0</v>
@@ -10166,7 +10172,7 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B426" s="10" t="s">
         <v>0</v>
@@ -10183,7 +10189,7 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B427" s="10" t="s">
         <v>0</v>
@@ -10200,7 +10206,7 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B428" s="10" t="s">
         <v>0</v>
@@ -10217,13 +10223,13 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B429" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C429" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D429" s="13">
         <v>1</v>
@@ -10234,7 +10240,7 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B430" s="10" t="s">
         <v>0</v>
@@ -10251,7 +10257,7 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B431" s="10" t="s">
         <v>9</v>
@@ -10268,7 +10274,7 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B432" s="10" t="s">
         <v>9</v>
@@ -10285,7 +10291,7 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B433" s="10" t="s">
         <v>0</v>
@@ -10302,7 +10308,7 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B434" s="10" t="s">
         <v>0</v>
@@ -10319,7 +10325,7 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B435" s="10" t="s">
         <v>38</v>
@@ -10336,13 +10342,13 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B436" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C436" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D436" s="13">
         <v>140</v>
@@ -10353,7 +10359,7 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B437" s="10" t="s">
         <v>0</v>
@@ -10370,7 +10376,7 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B438" s="10" t="s">
         <v>38</v>
@@ -10387,7 +10393,7 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B439" s="10" t="s">
         <v>0</v>
@@ -10404,13 +10410,13 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B440" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C440" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D440" s="13">
         <v>60</v>
@@ -10421,7 +10427,7 @@
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B441" s="10" t="s">
         <v>38</v>
@@ -10438,7 +10444,7 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B442" s="10" t="s">
         <v>38</v>
@@ -10455,7 +10461,7 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B443" s="10" t="s">
         <v>38</v>
@@ -10472,7 +10478,7 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B444" s="10" t="s">
         <v>9</v>
@@ -10489,7 +10495,7 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B445" s="10" t="s">
         <v>0</v>
@@ -10506,7 +10512,7 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B446" s="10" t="s">
         <v>0</v>
@@ -10523,7 +10529,7 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B447" s="10" t="s">
         <v>0</v>
@@ -10540,7 +10546,7 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B448" s="10" t="s">
         <v>0</v>
@@ -10557,7 +10563,7 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B449" s="10" t="s">
         <v>0</v>
@@ -10574,7 +10580,7 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B450" s="10" t="s">
         <v>0</v>
@@ -10591,7 +10597,7 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B451" s="10" t="s">
         <v>0</v>
@@ -10608,7 +10614,7 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B452" s="10" t="s">
         <v>0</v>
@@ -10625,7 +10631,7 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B453" s="10" t="s">
         <v>0</v>
@@ -10642,7 +10648,7 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B454" s="10" t="s">
         <v>0</v>
@@ -10659,13 +10665,13 @@
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B455" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C455" s="10" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D455" s="13">
         <v>6</v>
@@ -10676,13 +10682,13 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B456" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C456" s="10" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D456" s="13">
         <v>6</v>
@@ -10693,13 +10699,13 @@
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B457" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C457" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D457" s="13">
         <v>4</v>
@@ -10710,16 +10716,16 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="10" t="s">
-        <v>578</v>
+        <v>646</v>
       </c>
       <c r="B458" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C458" s="10" t="s">
-        <v>473</v>
+        <v>253</v>
       </c>
       <c r="D458" s="13">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E458" s="1">
         <v>0</v>
@@ -10733,10 +10739,10 @@
         <v>0</v>
       </c>
       <c r="C459" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D459" s="13">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E459" s="1">
         <v>0</v>
@@ -10744,16 +10750,16 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B460" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C460" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D460" s="13">
-        <v>47</v>
+        <v>830</v>
       </c>
       <c r="E460" s="1">
         <v>0</v>
@@ -10761,16 +10767,16 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B461" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C461" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D461" s="13">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="E461" s="1">
         <v>0</v>
@@ -10778,16 +10784,16 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B462" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C462" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D462" s="13">
-        <v>850</v>
+        <v>1250</v>
       </c>
       <c r="E462" s="1">
         <v>0</v>
@@ -10795,16 +10801,16 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B463" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C463" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D463" s="13">
-        <v>1250</v>
+        <v>400</v>
       </c>
       <c r="E463" s="1">
         <v>0</v>
@@ -10812,16 +10818,16 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="10" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B464" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C464" s="10" t="s">
-        <v>258</v>
+        <v>765</v>
       </c>
       <c r="D464" s="13">
-        <v>400</v>
+        <v>3760</v>
       </c>
       <c r="E464" s="1">
         <v>0</v>
@@ -10829,16 +10835,16 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B465" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C465" s="10" t="s">
-        <v>767</v>
+        <v>259</v>
       </c>
       <c r="D465" s="13">
-        <v>3760</v>
+        <v>280</v>
       </c>
       <c r="E465" s="1">
         <v>0</v>
@@ -10846,16 +10852,16 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B466" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C466" s="10" t="s">
         <v>259</v>
       </c>
       <c r="D466" s="13">
-        <v>280</v>
+        <v>779</v>
       </c>
       <c r="E466" s="1">
         <v>0</v>
@@ -10863,16 +10869,16 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="10" t="s">
-        <v>647</v>
+        <v>546</v>
       </c>
       <c r="B467" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C467" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D467" s="13">
-        <v>779</v>
+        <v>273</v>
       </c>
       <c r="E467" s="1">
         <v>0</v>
@@ -10880,16 +10886,16 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="10" t="s">
-        <v>547</v>
+        <v>646</v>
       </c>
       <c r="B468" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C468" s="10" t="s">
-        <v>260</v>
+        <v>766</v>
       </c>
       <c r="D468" s="13">
-        <v>273</v>
+        <v>1632</v>
       </c>
       <c r="E468" s="1">
         <v>0</v>
@@ -10897,16 +10903,16 @@
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="10" t="s">
-        <v>647</v>
+        <v>562</v>
       </c>
       <c r="B469" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C469" s="10" t="s">
-        <v>768</v>
+        <v>261</v>
       </c>
       <c r="D469" s="13">
-        <v>1632</v>
+        <v>3</v>
       </c>
       <c r="E469" s="1">
         <v>0</v>
@@ -10914,16 +10920,16 @@
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B470" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C470" s="10" t="s">
-        <v>261</v>
+        <v>500</v>
       </c>
       <c r="D470" s="13">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E470" s="1">
         <v>0</v>
@@ -10931,16 +10937,16 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="10" t="s">
-        <v>563</v>
+        <v>600</v>
       </c>
       <c r="B471" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C471" s="10" t="s">
-        <v>501</v>
+        <v>262</v>
       </c>
       <c r="D471" s="13">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E471" s="1">
         <v>0</v>
@@ -10948,16 +10954,16 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B472" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C472" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D472" s="13">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E472" s="1">
         <v>0</v>
@@ -10965,16 +10971,16 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B473" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C473" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D473" s="13">
-        <v>6</v>
+        <v>840</v>
       </c>
       <c r="E473" s="1">
         <v>0</v>
@@ -10982,16 +10988,16 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B474" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C474" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D474" s="13">
-        <v>840</v>
+        <v>10</v>
       </c>
       <c r="E474" s="1">
         <v>0</v>
@@ -10999,13 +11005,13 @@
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B475" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C475" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D475" s="13">
         <v>10</v>
@@ -11016,16 +11022,16 @@
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B476" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C476" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D476" s="13">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="E476" s="1">
         <v>0</v>
@@ -11033,16 +11039,16 @@
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B477" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C477" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D477" s="13">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E477" s="1">
         <v>0</v>
@@ -11050,16 +11056,16 @@
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B478" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C478" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D478" s="13">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E478" s="1">
         <v>0</v>
@@ -11067,16 +11073,16 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B479" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C479" s="10" t="s">
-        <v>269</v>
+        <v>417</v>
       </c>
       <c r="D479" s="13">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E479" s="1">
         <v>0</v>
@@ -11084,16 +11090,16 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="10" t="s">
-        <v>601</v>
+        <v>543</v>
       </c>
       <c r="B480" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C480" s="10" t="s">
-        <v>417</v>
+        <v>270</v>
       </c>
       <c r="D480" s="13">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="E480" s="1">
         <v>0</v>
@@ -11101,16 +11107,16 @@
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="10" t="s">
-        <v>544</v>
+        <v>646</v>
       </c>
       <c r="B481" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C481" s="10" t="s">
-        <v>270</v>
+        <v>767</v>
       </c>
       <c r="D481" s="13">
-        <v>75</v>
+        <v>575</v>
       </c>
       <c r="E481" s="1">
         <v>0</v>
@@ -11118,16 +11124,16 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B482" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D482" s="13">
-        <v>575</v>
+        <v>9500</v>
       </c>
       <c r="E482" s="1">
         <v>0</v>
@@ -11135,16 +11141,16 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B483" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C483" s="10" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D483" s="13">
-        <v>9500</v>
+        <v>575</v>
       </c>
       <c r="E483" s="1">
         <v>0</v>
@@ -11152,16 +11158,16 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B484" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C484" s="10" t="s">
-        <v>771</v>
+        <v>271</v>
       </c>
       <c r="D484" s="13">
-        <v>575</v>
+        <v>40</v>
       </c>
       <c r="E484" s="1">
         <v>0</v>
@@ -11169,16 +11175,16 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B485" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C485" s="10" t="s">
-        <v>271</v>
+        <v>770</v>
       </c>
       <c r="D485" s="13">
-        <v>40</v>
+        <v>5000</v>
       </c>
       <c r="E485" s="1">
         <v>0</v>
@@ -11186,16 +11192,16 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="10" t="s">
-        <v>647</v>
+        <v>545</v>
       </c>
       <c r="B486" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C486" s="10" t="s">
-        <v>772</v>
+        <v>409</v>
       </c>
       <c r="D486" s="13">
-        <v>5000</v>
+        <v>16400</v>
       </c>
       <c r="E486" s="1">
         <v>0</v>
@@ -11203,16 +11209,16 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" s="10" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="B487" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>409</v>
+        <v>272</v>
       </c>
       <c r="D487" s="13">
-        <v>16400</v>
+        <v>1</v>
       </c>
       <c r="E487" s="1">
         <v>0</v>
@@ -11220,16 +11226,16 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B488" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C488" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D488" s="13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E488" s="1">
         <v>0</v>
@@ -11237,16 +11243,16 @@
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B489" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C489" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D489" s="13">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E489" s="1">
         <v>0</v>
@@ -11254,16 +11260,16 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B490" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C490" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D490" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E490" s="1">
         <v>0</v>
@@ -11271,13 +11277,13 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B491" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C491" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D491" s="13">
         <v>1</v>
@@ -11288,13 +11294,13 @@
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B492" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C492" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D492" s="13">
         <v>1</v>
@@ -11305,13 +11311,13 @@
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B493" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C493" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D493" s="13">
         <v>1</v>
@@ -11322,16 +11328,16 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B494" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C494" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D494" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E494" s="1">
         <v>0</v>
@@ -11339,16 +11345,16 @@
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B495" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C495" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D495" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E495" s="1">
         <v>0</v>
@@ -11356,16 +11362,16 @@
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B496" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C496" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D496" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E496" s="1">
         <v>0</v>
@@ -11379,10 +11385,10 @@
         <v>0</v>
       </c>
       <c r="C497" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D497" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E497" s="1">
         <v>0</v>
@@ -11390,16 +11396,16 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B498" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C498" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D498" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E498" s="1">
         <v>0</v>
@@ -11407,16 +11413,16 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B499" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C499" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D499" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E499" s="1">
         <v>0</v>
@@ -11430,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="C500" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D500" s="13">
         <v>1</v>
@@ -11441,13 +11447,13 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="B501" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C501" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D501" s="13">
         <v>1</v>
@@ -11458,13 +11464,13 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>544</v>
+        <v>605</v>
       </c>
       <c r="B502" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C502" s="10" t="s">
-        <v>286</v>
+        <v>476</v>
       </c>
       <c r="D502" s="13">
         <v>1</v>
@@ -11475,13 +11481,13 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B503" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C503" s="10" t="s">
-        <v>477</v>
+        <v>287</v>
       </c>
       <c r="D503" s="13">
         <v>1</v>
@@ -11492,16 +11498,16 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>606</v>
+        <v>543</v>
       </c>
       <c r="B504" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C504" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D504" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E504" s="1">
         <v>0</v>
@@ -11509,16 +11515,16 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B505" s="10" t="s">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="C505" s="10" t="s">
-        <v>288</v>
+        <v>699</v>
       </c>
       <c r="D505" s="13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E505" s="1">
         <v>0</v>
@@ -11526,16 +11532,16 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B506" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C506" s="10" t="s">
-        <v>700</v>
+        <v>788</v>
       </c>
       <c r="D506" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E506" s="1">
         <v>0</v>
@@ -11543,13 +11549,13 @@
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B507" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C507" s="10" t="s">
-        <v>748</v>
+        <v>789</v>
       </c>
       <c r="D507" s="13">
         <v>3</v>
@@ -11560,13 +11566,13 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B508" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="C508" s="10" t="s">
         <v>513</v>
-      </c>
-      <c r="C508" s="10" t="s">
-        <v>514</v>
       </c>
       <c r="D508" s="13">
         <v>3</v>
@@ -11577,13 +11583,13 @@
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B509" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C509" s="10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D509" s="13">
         <v>2</v>
@@ -11594,13 +11600,13 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B510" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C510" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D510" s="13">
         <v>23</v>
@@ -11611,13 +11617,13 @@
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B511" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C511" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D511" s="13">
         <v>1</v>
@@ -11628,13 +11634,13 @@
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B512" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C512" s="10" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D512" s="13">
         <v>1</v>
@@ -11645,13 +11651,13 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B513" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C513" s="10" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D513" s="13">
         <v>3</v>
@@ -11662,13 +11668,13 @@
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B514" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C514" s="10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D514" s="13">
         <v>2</v>
@@ -11679,13 +11685,13 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B515" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C515" s="10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D515" s="13">
         <v>2</v>
@@ -11696,13 +11702,13 @@
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B516" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C516" s="10" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D516" s="13">
         <v>1</v>
@@ -11713,13 +11719,13 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B517" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C517" s="10" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D517" s="13">
         <v>1</v>
@@ -11730,7 +11736,7 @@
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B518" s="10" t="s">
         <v>0</v>
@@ -11747,7 +11753,7 @@
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B519" s="10" t="s">
         <v>0</v>
@@ -11764,7 +11770,7 @@
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B520" s="10" t="s">
         <v>0</v>
@@ -11781,7 +11787,7 @@
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B521" s="10" t="s">
         <v>0</v>
@@ -11798,7 +11804,7 @@
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B522" s="10" t="s">
         <v>0</v>
@@ -11815,7 +11821,7 @@
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B523" s="10" t="s">
         <v>0</v>
@@ -11832,7 +11838,7 @@
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B524" s="10" t="s">
         <v>0</v>
@@ -11849,7 +11855,7 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B525" s="10" t="s">
         <v>0</v>
@@ -11866,13 +11872,13 @@
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B526" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C526" s="10" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D526" s="13">
         <v>2</v>
@@ -11883,13 +11889,13 @@
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B527" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C527" s="10" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D527" s="13">
         <v>4</v>
@@ -11900,13 +11906,13 @@
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B528" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C528" s="10" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D528" s="13">
         <v>2</v>
@@ -11917,13 +11923,13 @@
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B529" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C529" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D529" s="13">
         <v>3</v>
@@ -11934,13 +11940,13 @@
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B530" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C530" s="10" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D530" s="13">
         <v>2</v>
@@ -11951,13 +11957,13 @@
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B531" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C531" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D531" s="13">
         <v>3</v>
@@ -11968,13 +11974,13 @@
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="B532" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C532" s="10" t="s">
         <v>737</v>
-      </c>
-      <c r="B532" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C532" s="10" t="s">
-        <v>738</v>
       </c>
       <c r="D532" s="13">
         <v>8</v>
@@ -11985,13 +11991,13 @@
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B533" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C533" s="10" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D533" s="13">
         <v>1</v>
@@ -12002,13 +12008,13 @@
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B534" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C534" s="10" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D534" s="13">
         <v>1</v>
@@ -12019,13 +12025,13 @@
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B535" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C535" s="10" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D535" s="13">
         <v>1</v>
@@ -12036,13 +12042,13 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B536" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C536" s="10" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D536" s="13">
         <v>2</v>
@@ -12053,13 +12059,13 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B537" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C537" s="10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D537" s="13">
         <v>1</v>
@@ -12070,13 +12076,13 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B538" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C538" s="10" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D538" s="13">
         <v>1</v>
@@ -12087,13 +12093,13 @@
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B539" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C539" s="10" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D539" s="13">
         <v>1</v>
@@ -12104,13 +12110,13 @@
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B540" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C540" s="10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D540" s="13">
         <v>2</v>
@@ -12121,13 +12127,13 @@
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B541" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C541" s="10" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D541" s="13">
         <v>1</v>
@@ -12138,13 +12144,13 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B542" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C542" s="10" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D542" s="13">
         <v>2</v>
@@ -12155,13 +12161,13 @@
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B543" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C543" s="10" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D543" s="13">
         <v>1</v>
@@ -12172,13 +12178,13 @@
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B544" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C544" s="10" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D544" s="13">
         <v>1</v>
@@ -12189,13 +12195,13 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B545" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C545" s="10" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D545" s="13">
         <v>1</v>
@@ -12206,13 +12212,13 @@
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B546" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C546" s="10" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D546" s="13">
         <v>1</v>
@@ -12223,13 +12229,13 @@
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B547" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C547" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D547" s="13">
         <v>1</v>
@@ -12240,16 +12246,16 @@
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B548" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C548" s="10" t="s">
-        <v>542</v>
+        <v>790</v>
       </c>
       <c r="D548" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E548" s="1">
         <v>0</v>
@@ -12257,16 +12263,16 @@
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B549" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C549" s="10" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="D549" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E549" s="1">
         <v>0</v>
@@ -12274,16 +12280,16 @@
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B550" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C550" s="10" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D550" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E550" s="1">
         <v>0</v>
@@ -12291,13 +12297,13 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B551" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C551" s="10" t="s">
-        <v>533</v>
+        <v>791</v>
       </c>
       <c r="D551" s="13">
         <v>4</v>
@@ -12308,16 +12314,16 @@
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B552" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C552" s="10" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D552" s="13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E552" s="1">
         <v>0</v>
@@ -12325,16 +12331,16 @@
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B553" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C553" s="10" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D553" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E553" s="1">
         <v>0</v>
@@ -12342,16 +12348,16 @@
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" s="10" t="s">
-        <v>606</v>
+        <v>549</v>
       </c>
       <c r="B554" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C554" s="10" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D554" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E554" s="1">
         <v>0</v>
@@ -12359,16 +12365,16 @@
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" s="10" t="s">
-        <v>650</v>
+        <v>549</v>
       </c>
       <c r="B555" s="10" t="s">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="C555" s="10" t="s">
-        <v>297</v>
+        <v>534</v>
       </c>
       <c r="D555" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E555" s="1">
         <v>0</v>
@@ -12376,16 +12382,16 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" s="10" t="s">
-        <v>550</v>
+        <v>605</v>
       </c>
       <c r="B556" s="10" t="s">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="C556" s="10" t="s">
-        <v>298</v>
+        <v>535</v>
       </c>
       <c r="D556" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E556" s="1">
         <v>0</v>
@@ -12393,13 +12399,13 @@
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" s="10" t="s">
-        <v>550</v>
+        <v>649</v>
       </c>
       <c r="B557" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C557" s="10" t="s">
-        <v>485</v>
+        <v>297</v>
       </c>
       <c r="D557" s="13">
         <v>1</v>
@@ -12410,16 +12416,16 @@
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B558" s="10" t="s">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="C558" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D558" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E558" s="1">
         <v>0</v>
@@ -12427,16 +12433,16 @@
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B559" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C559" s="10" t="s">
-        <v>299</v>
+        <v>484</v>
       </c>
       <c r="D559" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E559" s="1">
         <v>0</v>
@@ -12444,13 +12450,13 @@
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" s="10" t="s">
-        <v>606</v>
+        <v>549</v>
       </c>
       <c r="B560" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C560" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D560" s="13">
         <v>2</v>
@@ -12461,16 +12467,16 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" s="10" t="s">
-        <v>606</v>
+        <v>549</v>
       </c>
       <c r="B561" s="10" t="s">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="C561" s="10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D561" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E561" s="1">
         <v>0</v>
@@ -12478,16 +12484,16 @@
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B562" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C562" s="10" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D562" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E562" s="1">
         <v>0</v>
@@ -12495,13 +12501,13 @@
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" s="10" t="s">
-        <v>552</v>
+        <v>605</v>
       </c>
       <c r="B563" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C563" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D563" s="13">
         <v>1</v>
@@ -12512,13 +12518,13 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" s="10" t="s">
-        <v>552</v>
+        <v>605</v>
       </c>
       <c r="B564" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C564" s="10" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D564" s="13">
         <v>1</v>
@@ -12529,16 +12535,16 @@
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" s="10" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B565" s="10" t="s">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="C565" s="10" t="s">
-        <v>674</v>
+        <v>303</v>
       </c>
       <c r="D565" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E565" s="1">
         <v>0</v>
@@ -12546,13 +12552,13 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" s="10" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B566" s="10" t="s">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="C566" s="10" t="s">
-        <v>675</v>
+        <v>304</v>
       </c>
       <c r="D566" s="13">
         <v>1</v>
@@ -12563,13 +12569,13 @@
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B567" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C567" s="10" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D567" s="13">
         <v>2</v>
@@ -12580,13 +12586,13 @@
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B568" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C568" s="10" t="s">
-        <v>537</v>
+        <v>674</v>
       </c>
       <c r="D568" s="13">
         <v>1</v>
@@ -12597,16 +12603,16 @@
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B569" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C569" s="10" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D569" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E569" s="1">
         <v>0</v>
@@ -12614,16 +12620,16 @@
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B570" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C570" s="10" t="s">
-        <v>678</v>
+        <v>536</v>
       </c>
       <c r="D570" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E570" s="1">
         <v>0</v>
@@ -12631,13 +12637,13 @@
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B571" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C571" s="10" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D571" s="13">
         <v>1</v>
@@ -12648,13 +12654,13 @@
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B572" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C572" s="10" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D572" s="13">
         <v>2</v>
@@ -12665,13 +12671,13 @@
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B573" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C573" s="10" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D573" s="13">
         <v>3</v>
@@ -12682,16 +12688,16 @@
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B574" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C574" s="10" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D574" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E574" s="1">
         <v>0</v>
@@ -12699,16 +12705,16 @@
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B575" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C575" s="10" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D575" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E575" s="1">
         <v>0</v>
@@ -12716,16 +12722,16 @@
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B576" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C576" s="10" t="s">
-        <v>538</v>
+        <v>681</v>
       </c>
       <c r="D576" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E576" s="1">
         <v>0</v>
@@ -12733,16 +12739,16 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B577" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C577" s="10" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="D577" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E577" s="1">
         <v>0</v>
@@ -12750,16 +12756,16 @@
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578" s="10" t="s">
-        <v>606</v>
+        <v>549</v>
       </c>
       <c r="B578" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C578" s="10" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D578" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E578" s="1">
         <v>0</v>
@@ -12767,16 +12773,16 @@
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" s="10" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B579" s="10" t="s">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="C579" s="10" t="s">
-        <v>305</v>
+        <v>670</v>
       </c>
       <c r="D579" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E579" s="1">
         <v>0</v>
@@ -12784,13 +12790,13 @@
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B580" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C580" s="10" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D580" s="13">
         <v>1</v>
@@ -12801,16 +12807,16 @@
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581" s="10" t="s">
-        <v>628</v>
+        <v>551</v>
       </c>
       <c r="B581" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C581" s="10" t="s">
-        <v>397</v>
+        <v>305</v>
       </c>
       <c r="D581" s="13">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E581" s="1">
         <v>0</v>
@@ -12818,16 +12824,16 @@
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" s="10" t="s">
-        <v>628</v>
+        <v>605</v>
       </c>
       <c r="B582" s="10" t="s">
-        <v>38</v>
+        <v>512</v>
       </c>
       <c r="C582" s="10" t="s">
-        <v>398</v>
+        <v>542</v>
       </c>
       <c r="D582" s="13">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E582" s="1">
         <v>0</v>
@@ -12835,16 +12841,16 @@
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A583" s="10" t="s">
-        <v>550</v>
+        <v>627</v>
       </c>
       <c r="B583" s="10" t="s">
-        <v>513</v>
+        <v>38</v>
       </c>
       <c r="C583" s="10" t="s">
-        <v>758</v>
+        <v>397</v>
       </c>
       <c r="D583" s="13">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E583" s="1">
         <v>0</v>
@@ -12852,16 +12858,16 @@
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" s="10" t="s">
-        <v>550</v>
+        <v>627</v>
       </c>
       <c r="B584" s="10" t="s">
-        <v>513</v>
+        <v>38</v>
       </c>
       <c r="C584" s="10" t="s">
-        <v>759</v>
+        <v>398</v>
       </c>
       <c r="D584" s="13">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E584" s="1">
         <v>0</v>
@@ -12869,16 +12875,16 @@
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B585" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C585" s="10" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="D585" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E585" s="1">
         <v>0</v>
@@ -12886,13 +12892,13 @@
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A586" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B586" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C586" s="10" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D586" s="13">
         <v>3</v>
@@ -12903,16 +12909,16 @@
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587" s="10" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B587" s="10" t="s">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="C587" s="10" t="s">
-        <v>306</v>
+        <v>758</v>
       </c>
       <c r="D587" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E587" s="1">
         <v>0</v>
@@ -12920,16 +12926,16 @@
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588" s="10" t="s">
-        <v>652</v>
+        <v>549</v>
       </c>
       <c r="B588" s="10" t="s">
-        <v>38</v>
+        <v>512</v>
       </c>
       <c r="C588" s="10" t="s">
-        <v>773</v>
+        <v>759</v>
       </c>
       <c r="D588" s="13">
-        <v>2000</v>
+        <v>3</v>
       </c>
       <c r="E588" s="1">
         <v>0</v>
@@ -12937,16 +12943,16 @@
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" s="10" t="s">
-        <v>647</v>
+        <v>543</v>
       </c>
       <c r="B589" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C589" s="10" t="s">
-        <v>774</v>
+        <v>306</v>
       </c>
       <c r="D589" s="13">
-        <v>2500</v>
+        <v>1</v>
       </c>
       <c r="E589" s="1">
         <v>0</v>
@@ -12954,16 +12960,16 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" s="10" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B590" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C590" s="10" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="D590" s="13">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="E590" s="1">
         <v>0</v>
@@ -12971,16 +12977,16 @@
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B591" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C591" s="10" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="D591" s="13">
-        <v>1</v>
+        <v>2500</v>
       </c>
       <c r="E591" s="1">
         <v>0</v>
@@ -12988,16 +12994,16 @@
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A592" s="10" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B592" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C592" s="10" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="D592" s="13">
-        <v>2</v>
+        <v>2400</v>
       </c>
       <c r="E592" s="1">
         <v>0</v>
@@ -13005,16 +13011,16 @@
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A593" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B593" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C593" s="10" t="s">
-        <v>422</v>
+        <v>786</v>
       </c>
       <c r="D593" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E593" s="1">
         <v>0</v>
@@ -13022,16 +13028,16 @@
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A594" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B594" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C594" s="10" t="s">
-        <v>510</v>
+        <v>787</v>
       </c>
       <c r="D594" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E594" s="1">
         <v>0</v>
@@ -13039,16 +13045,16 @@
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A595" s="10" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B595" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C595" s="10" t="s">
-        <v>775</v>
+        <v>422</v>
       </c>
       <c r="D595" s="13">
-        <v>1850</v>
+        <v>5</v>
       </c>
       <c r="E595" s="1">
         <v>0</v>
@@ -13056,16 +13062,16 @@
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A596" s="10" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B596" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C596" s="10" t="s">
-        <v>307</v>
+        <v>509</v>
       </c>
       <c r="D596" s="13">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E596" s="1">
         <v>0</v>
@@ -13073,16 +13079,16 @@
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A597" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B597" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C597" s="10" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="D597" s="13">
-        <v>2500</v>
+        <v>1850</v>
       </c>
       <c r="E597" s="1">
         <v>0</v>
@@ -13090,16 +13096,16 @@
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A598" s="10" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B598" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C598" s="10" t="s">
-        <v>783</v>
+        <v>307</v>
       </c>
       <c r="D598" s="13">
-        <v>2400</v>
+        <v>37</v>
       </c>
       <c r="E598" s="1">
         <v>0</v>
@@ -13107,16 +13113,16 @@
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A599" s="10" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B599" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C599" s="10" t="s">
-        <v>722</v>
+        <v>774</v>
       </c>
       <c r="D599" s="13">
-        <v>800</v>
+        <v>2500</v>
       </c>
       <c r="E599" s="1">
         <v>0</v>
@@ -13124,16 +13130,16 @@
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A600" s="10" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B600" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C600" s="10" t="s">
-        <v>723</v>
+        <v>781</v>
       </c>
       <c r="D600" s="13">
-        <v>1600</v>
+        <v>2400</v>
       </c>
       <c r="E600" s="1">
         <v>0</v>
@@ -13141,16 +13147,16 @@
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A601" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B601" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C601" s="10" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D601" s="13">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E601" s="1">
         <v>0</v>
@@ -13158,13 +13164,13 @@
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A602" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B602" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C602" s="10" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D602" s="13">
         <v>1600</v>
@@ -13175,16 +13181,16 @@
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A603" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B603" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C603" s="10" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D603" s="13">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E603" s="1">
         <v>0</v>
@@ -13192,16 +13198,16 @@
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A604" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B604" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C604" s="10" t="s">
-        <v>777</v>
+        <v>724</v>
       </c>
       <c r="D604" s="13">
-        <v>1250</v>
+        <v>1600</v>
       </c>
       <c r="E604" s="1">
         <v>0</v>
@@ -13209,16 +13215,16 @@
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A605" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B605" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C605" s="10" t="s">
-        <v>778</v>
+        <v>725</v>
       </c>
       <c r="D605" s="13">
-        <v>1550</v>
+        <v>800</v>
       </c>
       <c r="E605" s="1">
         <v>0</v>
@@ -13226,16 +13232,16 @@
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A606" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B606" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C606" s="10" t="s">
-        <v>308</v>
+        <v>775</v>
       </c>
       <c r="D606" s="13">
-        <v>1070</v>
+        <v>1250</v>
       </c>
       <c r="E606" s="1">
         <v>0</v>
@@ -13243,16 +13249,16 @@
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A607" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B607" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C607" s="10" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D607" s="13">
-        <v>1700</v>
+        <v>1550</v>
       </c>
       <c r="E607" s="1">
         <v>0</v>
@@ -13260,16 +13266,16 @@
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A608" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B608" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C608" s="10" t="s">
-        <v>780</v>
+        <v>308</v>
       </c>
       <c r="D608" s="13">
-        <v>1000</v>
+        <v>1070</v>
       </c>
       <c r="E608" s="1">
         <v>0</v>
@@ -13277,16 +13283,16 @@
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A609" s="10" t="s">
-        <v>560</v>
+        <v>651</v>
       </c>
       <c r="B609" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C609" s="10" t="s">
-        <v>309</v>
+        <v>777</v>
       </c>
       <c r="D609" s="13">
-        <v>1</v>
+        <v>1700</v>
       </c>
       <c r="E609" s="1">
         <v>0</v>
@@ -13294,16 +13300,16 @@
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A610" s="10" t="s">
-        <v>560</v>
+        <v>651</v>
       </c>
       <c r="B610" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C610" s="10" t="s">
-        <v>310</v>
+        <v>778</v>
       </c>
       <c r="D610" s="13">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="E610" s="1">
         <v>0</v>
@@ -13311,13 +13317,13 @@
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A611" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B611" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C611" s="10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D611" s="13">
         <v>1</v>
@@ -13328,16 +13334,16 @@
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A612" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B612" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C612" s="10" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D612" s="13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E612" s="1">
         <v>0</v>
@@ -13345,16 +13351,16 @@
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A613" s="10" t="s">
-        <v>653</v>
+        <v>560</v>
       </c>
       <c r="B613" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C613" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D613" s="13">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E613" s="1">
         <v>0</v>
@@ -13362,16 +13368,16 @@
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A614" s="10" t="s">
-        <v>654</v>
+        <v>560</v>
       </c>
       <c r="B614" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C614" s="10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D614" s="13">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E614" s="1">
         <v>0</v>
@@ -13379,16 +13385,16 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" s="10" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B615" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C615" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D615" s="13">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="E615" s="1">
         <v>0</v>
@@ -13396,16 +13402,16 @@
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A616" s="10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B616" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C616" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D616" s="13">
-        <v>300</v>
+        <v>46</v>
       </c>
       <c r="E616" s="1">
         <v>0</v>
@@ -13413,16 +13419,16 @@
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" s="10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B617" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C617" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D617" s="13">
-        <v>300</v>
+        <v>121</v>
       </c>
       <c r="E617" s="1">
         <v>0</v>
@@ -13430,13 +13436,13 @@
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A618" s="10" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B618" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C618" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D618" s="13">
         <v>300</v>
@@ -13447,16 +13453,16 @@
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A619" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B619" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C619" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D619" s="13">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E619" s="1">
         <v>0</v>
@@ -13464,16 +13470,16 @@
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A620" s="10" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B620" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C620" s="10" t="s">
-        <v>446</v>
+        <v>317</v>
       </c>
       <c r="D620" s="13">
-        <v>43</v>
+        <v>300</v>
       </c>
       <c r="E620" s="1">
         <v>0</v>
@@ -13481,16 +13487,16 @@
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A621" s="10" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B621" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C621" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D621" s="13">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="E621" s="1">
         <v>0</v>
@@ -13504,10 +13510,10 @@
         <v>0</v>
       </c>
       <c r="C622" s="10" t="s">
-        <v>320</v>
+        <v>446</v>
       </c>
       <c r="D622" s="13">
-        <v>280</v>
+        <v>43</v>
       </c>
       <c r="E622" s="1">
         <v>0</v>
@@ -13515,16 +13521,16 @@
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A623" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B623" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C623" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D623" s="13">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E623" s="1">
         <v>0</v>
@@ -13532,16 +13538,16 @@
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A624" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B624" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C624" s="10" t="s">
-        <v>392</v>
+        <v>320</v>
       </c>
       <c r="D624" s="13">
-        <v>42</v>
+        <v>280</v>
       </c>
       <c r="E624" s="1">
         <v>0</v>
@@ -13549,16 +13555,16 @@
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A625" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B625" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C625" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D625" s="13">
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="E625" s="1">
         <v>0</v>
@@ -13566,16 +13572,16 @@
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A626" s="10" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B626" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C626" s="10" t="s">
-        <v>322</v>
+        <v>392</v>
       </c>
       <c r="D626" s="13">
-        <v>250</v>
+        <v>42</v>
       </c>
       <c r="E626" s="1">
         <v>0</v>
@@ -13583,16 +13589,16 @@
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A627" s="10" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B627" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C627" s="10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D627" s="13">
-        <v>1250</v>
+        <v>24</v>
       </c>
       <c r="E627" s="1">
         <v>0</v>
@@ -13600,16 +13606,16 @@
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A628" s="10" t="s">
-        <v>713</v>
+        <v>657</v>
       </c>
       <c r="B628" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C628" s="10" t="s">
-        <v>714</v>
+        <v>322</v>
       </c>
       <c r="D628" s="13">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E628" s="1">
         <v>0</v>
@@ -13617,16 +13623,16 @@
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A629" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B629" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C629" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D629" s="13">
-        <v>160</v>
+        <v>1250</v>
       </c>
       <c r="E629" s="1">
         <v>0</v>
@@ -13634,16 +13640,16 @@
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A630" s="10" t="s">
+        <v>712</v>
+      </c>
+      <c r="B630" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C630" s="10" t="s">
         <v>713</v>
       </c>
-      <c r="B630" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C630" s="10" t="s">
-        <v>715</v>
-      </c>
       <c r="D630" s="13">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E630" s="1">
         <v>0</v>
@@ -13651,16 +13657,16 @@
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A631" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B631" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C631" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D631" s="13">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="E631" s="1">
         <v>0</v>
@@ -13668,16 +13674,16 @@
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632" s="10" t="s">
-        <v>659</v>
+        <v>712</v>
       </c>
       <c r="B632" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C632" s="10" t="s">
-        <v>325</v>
+        <v>714</v>
       </c>
       <c r="D632" s="13">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E632" s="1">
         <v>0</v>
@@ -13685,16 +13691,16 @@
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A633" s="10" t="s">
-        <v>713</v>
+        <v>658</v>
       </c>
       <c r="B633" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C633" s="10" t="s">
-        <v>716</v>
+        <v>325</v>
       </c>
       <c r="D633" s="13">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E633" s="1">
         <v>0</v>
@@ -13702,16 +13708,16 @@
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A634" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B634" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C634" s="10" t="s">
-        <v>390</v>
+        <v>325</v>
       </c>
       <c r="D634" s="13">
-        <v>48</v>
+        <v>600</v>
       </c>
       <c r="E634" s="1">
         <v>0</v>
@@ -13719,16 +13725,16 @@
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A635" s="10" t="s">
-        <v>659</v>
+        <v>712</v>
       </c>
       <c r="B635" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C635" s="10" t="s">
-        <v>391</v>
+        <v>715</v>
       </c>
       <c r="D635" s="13">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="E635" s="1">
         <v>0</v>
@@ -13736,16 +13742,16 @@
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B636" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C636" s="10" t="s">
-        <v>326</v>
+        <v>390</v>
       </c>
       <c r="D636" s="13">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="E636" s="1">
         <v>0</v>
@@ -13753,16 +13759,16 @@
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A637" s="10" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B637" s="10" t="s">
-        <v>404</v>
+        <v>38</v>
       </c>
       <c r="C637" s="10" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="D637" s="13">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="E637" s="1">
         <v>0</v>
@@ -13770,16 +13776,16 @@
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A638" s="10" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B638" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C638" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D638" s="13">
-        <v>1300</v>
+        <v>72</v>
       </c>
       <c r="E638" s="1">
         <v>0</v>
@@ -13787,16 +13793,16 @@
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B639" s="1" t="s">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="C639" s="1" t="s">
-        <v>328</v>
+        <v>415</v>
       </c>
       <c r="D639" s="14">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="E639" s="1">
         <v>0</v>
@@ -13804,16 +13810,16 @@
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B640" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D640" s="14">
-        <v>15</v>
+        <v>1300</v>
       </c>
       <c r="E640" s="1">
         <v>0</v>
@@ -13821,16 +13827,16 @@
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B641" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C641" s="1" t="s">
-        <v>463</v>
+        <v>328</v>
       </c>
       <c r="D641" s="14">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E641" s="1">
         <v>0</v>
@@ -13838,16 +13844,16 @@
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B642" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>464</v>
+        <v>329</v>
       </c>
       <c r="D642" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E642" s="1">
         <v>0</v>
@@ -13855,16 +13861,16 @@
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B643" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D643" s="14">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E643" s="1">
         <v>0</v>
@@ -13872,16 +13878,16 @@
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B644" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C644" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D644" s="14">
         <v>9</v>
-      </c>
-      <c r="C644" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="D644" s="14">
-        <v>72</v>
       </c>
       <c r="E644" s="1">
         <v>0</v>
@@ -13889,16 +13895,16 @@
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C645" s="1" t="s">
-        <v>331</v>
+        <v>465</v>
       </c>
       <c r="D645" s="14">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="E645" s="1">
         <v>0</v>
@@ -13906,16 +13912,16 @@
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B646" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C646" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D646" s="14">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="E646" s="1">
         <v>0</v>
@@ -13923,16 +13929,16 @@
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B647" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C647" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D647" s="14">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="E647" s="1">
         <v>0</v>
@@ -13940,16 +13946,16 @@
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B648" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D648" s="14">
-        <v>600</v>
+        <v>8</v>
       </c>
       <c r="E648" s="1">
         <v>0</v>
@@ -13957,16 +13963,16 @@
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C649" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D649" s="14">
-        <v>825</v>
+        <v>200</v>
       </c>
       <c r="E649" s="1">
         <v>0</v>
@@ -13974,16 +13980,16 @@
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C650" s="1" t="s">
-        <v>717</v>
+        <v>334</v>
       </c>
       <c r="D650" s="14">
-        <v>465</v>
+        <v>600</v>
       </c>
       <c r="E650" s="1">
         <v>0</v>
@@ -13991,16 +13997,16 @@
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D651" s="14">
-        <v>400</v>
+        <v>825</v>
       </c>
       <c r="E651" s="1">
         <v>0</v>
@@ -14011,13 +14017,13 @@
         <v>664</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>336</v>
+        <v>716</v>
       </c>
       <c r="D652" s="14">
-        <v>600</v>
+        <v>465</v>
       </c>
       <c r="E652" s="1">
         <v>0</v>
@@ -14025,16 +14031,16 @@
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B653" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C653" s="1" t="s">
-        <v>447</v>
+        <v>336</v>
       </c>
       <c r="D653" s="14">
-        <v>65</v>
+        <v>400</v>
       </c>
       <c r="E653" s="1">
         <v>0</v>
@@ -14042,16 +14048,16 @@
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C654" s="1" t="s">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="D654" s="14">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="E654" s="1">
         <v>0</v>
@@ -14062,13 +14068,13 @@
         <v>664</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C655" s="1" t="s">
-        <v>337</v>
+        <v>447</v>
       </c>
       <c r="D655" s="14">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E655" s="1">
         <v>0</v>
@@ -14076,16 +14082,16 @@
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C656" s="1" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="D656" s="14">
-        <v>1001</v>
+        <v>80</v>
       </c>
       <c r="E656" s="1">
         <v>0</v>
@@ -14093,16 +14099,16 @@
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C657" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D657" s="14">
-        <v>1508</v>
+        <v>72</v>
       </c>
       <c r="E657" s="1">
         <v>0</v>
@@ -14110,16 +14116,16 @@
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B658" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C658" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D658" s="14">
-        <v>600</v>
+        <v>1001</v>
       </c>
       <c r="E658" s="1">
         <v>0</v>
@@ -14127,16 +14133,16 @@
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B659" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C659" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D659" s="14">
-        <v>400</v>
+        <v>1508</v>
       </c>
       <c r="E659" s="1">
         <v>0</v>
@@ -14144,16 +14150,16 @@
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B660" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C660" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D660" s="14">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E660" s="1">
         <v>0</v>
@@ -14161,16 +14167,16 @@
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B661" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C661" s="1" t="s">
-        <v>499</v>
+        <v>341</v>
       </c>
       <c r="D661" s="14">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="E661" s="1">
         <v>0</v>
@@ -14178,16 +14184,16 @@
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B662" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D662" s="14">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E662" s="1">
         <v>0</v>
@@ -14195,16 +14201,16 @@
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B663" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C663" s="1" t="s">
-        <v>403</v>
+        <v>498</v>
       </c>
       <c r="D663" s="14">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E663" s="1">
         <v>0</v>
@@ -14212,16 +14218,16 @@
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B664" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D664" s="14">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E664" s="1">
         <v>0</v>
@@ -14229,16 +14235,16 @@
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>653</v>
+        <v>666</v>
       </c>
       <c r="B665" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C665" s="1" t="s">
-        <v>345</v>
+        <v>403</v>
       </c>
       <c r="D665" s="14">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="E665" s="1">
         <v>0</v>
@@ -14246,16 +14252,16 @@
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
-        <v>653</v>
+        <v>666</v>
       </c>
       <c r="B666" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C666" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D666" s="14">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="E666" s="1">
         <v>0</v>
@@ -14263,16 +14269,16 @@
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
       <c r="B667" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C667" s="1" t="s">
-        <v>466</v>
+        <v>345</v>
       </c>
       <c r="D667" s="14">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="E667" s="1">
         <v>0</v>
@@ -14280,16 +14286,16 @@
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
       <c r="B668" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C668" s="1" t="s">
-        <v>467</v>
+        <v>346</v>
       </c>
       <c r="D668" s="14">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="E668" s="1">
         <v>0</v>
@@ -14297,16 +14303,16 @@
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B669" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C669" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D669" s="14">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E669" s="1">
         <v>0</v>
@@ -14314,16 +14320,16 @@
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>654</v>
+        <v>667</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C670" s="1" t="s">
-        <v>347</v>
+        <v>467</v>
       </c>
       <c r="D670" s="14">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E670" s="1">
         <v>0</v>
@@ -14331,16 +14337,16 @@
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>654</v>
+        <v>667</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C671" s="1" t="s">
-        <v>348</v>
+        <v>468</v>
       </c>
       <c r="D671" s="14">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="E671" s="1">
         <v>0</v>
@@ -14348,16 +14354,16 @@
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B672" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C672" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D672" s="14">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="E672" s="1">
         <v>0</v>
@@ -14365,16 +14371,16 @@
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C673" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D673" s="14">
-        <v>1200</v>
+        <v>225</v>
       </c>
       <c r="E673" s="1">
         <v>0</v>
@@ -14382,16 +14388,16 @@
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C674" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D674" s="14">
-        <v>1200</v>
+        <v>150</v>
       </c>
       <c r="E674" s="1">
         <v>0</v>
@@ -14399,16 +14405,16 @@
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B675" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C675" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D675" s="14">
-        <v>225</v>
+        <v>1200</v>
       </c>
       <c r="E675" s="1">
         <v>0</v>
@@ -14416,16 +14422,16 @@
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B676" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C676" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D676" s="14">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="E676" s="1">
         <v>0</v>
@@ -14433,16 +14439,16 @@
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C677" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D677" s="14">
-        <v>500</v>
+        <v>225</v>
       </c>
       <c r="E677" s="1">
         <v>0</v>
@@ -14450,16 +14456,16 @@
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C678" s="1" t="s">
-        <v>742</v>
+        <v>352</v>
       </c>
       <c r="D678" s="14">
-        <v>235</v>
+        <v>300</v>
       </c>
       <c r="E678" s="1">
         <v>0</v>
@@ -14467,16 +14473,16 @@
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C679" s="1" t="s">
-        <v>718</v>
+        <v>353</v>
       </c>
       <c r="D679" s="14">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="E679" s="1">
         <v>0</v>
@@ -14487,13 +14493,13 @@
         <v>669</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C680" s="1" t="s">
-        <v>354</v>
+        <v>741</v>
       </c>
       <c r="D680" s="14">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="E680" s="1">
         <v>0</v>
@@ -14507,10 +14513,10 @@
         <v>0</v>
       </c>
       <c r="C681" s="1" t="s">
-        <v>354</v>
+        <v>717</v>
       </c>
       <c r="D681" s="14">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="E681" s="1">
         <v>0</v>
@@ -14518,16 +14524,16 @@
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B682" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C682" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D682" s="14">
-        <v>175</v>
+        <v>950</v>
       </c>
       <c r="E682" s="1">
         <v>0</v>
@@ -14535,16 +14541,16 @@
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D683" s="14">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="E683" s="1">
         <v>0</v>
@@ -14552,16 +14558,16 @@
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B684" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C684" s="1" t="s">
-        <v>448</v>
+        <v>355</v>
       </c>
       <c r="D684" s="14">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="E684" s="1">
         <v>0</v>
@@ -14569,16 +14575,16 @@
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B685" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C685" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D685" s="14">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c r="E685" s="1">
         <v>0</v>
@@ -14589,13 +14595,13 @@
         <v>669</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C686" s="1" t="s">
-        <v>357</v>
+        <v>448</v>
       </c>
       <c r="D686" s="14">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="E686" s="1">
         <v>0</v>
@@ -14603,16 +14609,16 @@
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C687" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D687" s="14">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="E687" s="1">
         <v>0</v>
@@ -14620,16 +14626,16 @@
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C688" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D688" s="14">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E688" s="1">
         <v>0</v>
@@ -14637,16 +14643,16 @@
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B689" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C689" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D689" s="14">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="E689" s="1">
         <v>0</v>
@@ -14654,16 +14660,16 @@
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C690" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D690" s="14">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E690" s="1">
         <v>0</v>
@@ -14671,18 +14677,52 @@
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C691" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D691" s="14">
+        <v>100</v>
+      </c>
+      <c r="E691" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A692" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C692" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D691" s="14">
+      <c r="D692" s="14">
         <v>30</v>
       </c>
-      <c r="E691" s="1">
+      <c r="E692" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A693" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C693" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D693" s="14">
+        <v>64</v>
+      </c>
+      <c r="E693" s="1">
         <v>0</v>
       </c>
     </row>

--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0443691A-434D-40ED-A7FF-7339ECF00B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBF7087-BAA1-4C6A-A9DA-5FB859E7A03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="792">
   <si>
     <t>3-ديوان</t>
   </si>
@@ -1477,9 +1477,6 @@
     <t>قسطل حديد 3/4</t>
   </si>
   <si>
-    <t>قسطل تلحيم 32 ملم اخضر تركي</t>
-  </si>
-  <si>
     <t>غطاء زغرتا ابيض بلاستيك</t>
   </si>
   <si>
@@ -2435,6 +2432,9 @@
   </si>
   <si>
     <t>موتير غاطس ليو LEO AKS-251PH (0.3HP)</t>
+  </si>
+  <si>
+    <t>قسطل تلحيم 32 ملم اخضر تركي B باب ثاني</t>
   </si>
 </sst>
 </file>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>0</v>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>0</v>
@@ -3032,7 +3032,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>0</v>
@@ -3049,13 +3049,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D7" s="13">
         <v>600</v>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>0</v>
@@ -3083,7 +3083,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>0</v>
@@ -3100,13 +3100,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D10" s="13">
         <v>500</v>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>0</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>0</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>0</v>
@@ -3168,7 +3168,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>0</v>
@@ -3185,7 +3185,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>0</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>9</v>
@@ -3219,13 +3219,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D17" s="13">
         <v>6</v>
@@ -3236,13 +3236,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D18" s="13">
         <v>3</v>
@@ -3253,13 +3253,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D19" s="13">
         <v>1</v>
@@ -3270,7 +3270,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>0</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>0</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>0</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>0</v>
@@ -3338,13 +3338,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D24" s="13">
         <v>360</v>
@@ -3355,7 +3355,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>0</v>
@@ -3372,7 +3372,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>0</v>
@@ -3389,13 +3389,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D27" s="13">
         <v>8</v>
@@ -3406,13 +3406,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D28" s="13">
         <v>5</v>
@@ -3423,13 +3423,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D29" s="13">
         <v>3</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>0</v>
@@ -3457,13 +3457,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D31" s="13">
         <v>5</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>0</v>
@@ -3491,13 +3491,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D33" s="13">
         <v>1</v>
@@ -3508,7 +3508,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>0</v>
@@ -3525,7 +3525,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>0</v>
@@ -3576,7 +3576,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>0</v>
@@ -3593,7 +3593,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>0</v>
@@ -3610,7 +3610,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>0</v>
@@ -3627,7 +3627,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>0</v>
@@ -3644,7 +3644,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>0</v>
@@ -3661,7 +3661,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>0</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>0</v>
@@ -3695,7 +3695,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>0</v>
@@ -3712,7 +3712,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>0</v>
@@ -3729,7 +3729,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>0</v>
@@ -3746,7 +3746,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>0</v>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>0</v>
@@ -3780,13 +3780,13 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D50" s="13">
         <v>790</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>0</v>
@@ -3831,7 +3831,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>0</v>
@@ -3848,7 +3848,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>38</v>
@@ -3865,7 +3865,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>38</v>
@@ -3882,7 +3882,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>38</v>
@@ -3899,13 +3899,13 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D57" s="13">
         <v>132</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>0</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B61" s="10" t="s">
         <v>0</v>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>9</v>
@@ -4001,7 +4001,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>9</v>
@@ -4035,7 +4035,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>0</v>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>9</v>
@@ -4069,7 +4069,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>9</v>
@@ -4086,7 +4086,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>0</v>
@@ -4103,7 +4103,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>0</v>
@@ -4120,7 +4120,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>0</v>
@@ -4137,7 +4137,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B71" s="10" t="s">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>9</v>
@@ -4171,7 +4171,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B73" s="10" t="s">
         <v>9</v>
@@ -4188,7 +4188,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>0</v>
@@ -4205,16 +4205,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D75" s="13">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
@@ -4222,16 +4222,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D76" s="13">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B77" s="10" t="s">
         <v>0</v>
@@ -4256,7 +4256,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>0</v>
@@ -4273,7 +4273,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>38</v>
@@ -4290,13 +4290,13 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C80" s="10" t="s">
         <v>701</v>
-      </c>
-      <c r="B80" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>702</v>
       </c>
       <c r="D80" s="13">
         <v>70</v>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B81" s="10" t="s">
         <v>0</v>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>38</v>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B83" s="10" t="s">
         <v>38</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>0</v>
@@ -4375,7 +4375,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>38</v>
@@ -4392,13 +4392,13 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D86" s="13">
         <v>170</v>
@@ -4409,7 +4409,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>9</v>
@@ -4426,7 +4426,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B89" s="10" t="s">
         <v>0</v>
@@ -4460,16 +4460,16 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D90" s="13">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="E90" s="1">
         <v>0</v>
@@ -4477,16 +4477,16 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D91" s="13">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>0</v>
@@ -4511,7 +4511,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B93" s="10" t="s">
         <v>0</v>
@@ -4528,7 +4528,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B94" s="10" t="s">
         <v>38</v>
@@ -4545,7 +4545,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B95" s="10" t="s">
         <v>38</v>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B96" s="10" t="s">
         <v>0</v>
@@ -4579,7 +4579,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B97" s="10" t="s">
         <v>9</v>
@@ -4596,7 +4596,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>9</v>
@@ -4613,7 +4613,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B99" s="10" t="s">
         <v>0</v>
@@ -4630,13 +4630,13 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B100" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D100" s="13">
         <v>4</v>
@@ -4647,13 +4647,13 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D101" s="13">
         <v>1</v>
@@ -4664,13 +4664,13 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D102" s="13">
         <v>3</v>
@@ -4681,13 +4681,13 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B103" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D103" s="13">
         <v>1</v>
@@ -4698,13 +4698,13 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B104" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D104" s="13">
         <v>4</v>
@@ -4715,7 +4715,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B105" s="10" t="s">
         <v>0</v>
@@ -4732,7 +4732,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>0</v>
@@ -4749,13 +4749,13 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D107" s="13">
         <v>600</v>
@@ -4766,7 +4766,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>0</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B109" s="10" t="s">
         <v>0</v>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>0</v>
@@ -4817,7 +4817,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B111" s="10" t="s">
         <v>0</v>
@@ -4834,7 +4834,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B112" s="10" t="s">
         <v>0</v>
@@ -4851,7 +4851,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B113" s="10" t="s">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B114" s="10" t="s">
         <v>38</v>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B115" s="10" t="s">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>0</v>
@@ -4919,7 +4919,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B117" s="10" t="s">
         <v>0</v>
@@ -4936,7 +4936,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B118" s="10" t="s">
         <v>0</v>
@@ -4953,13 +4953,13 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B119" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D119" s="13">
         <v>1</v>
@@ -4970,13 +4970,13 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B120" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D120" s="13">
         <v>2</v>
@@ -4987,13 +4987,13 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B121" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D121" s="13">
         <v>2</v>
@@ -5004,7 +5004,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>38</v>
@@ -5021,7 +5021,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B123" s="10" t="s">
         <v>38</v>
@@ -5038,7 +5038,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B124" s="10" t="s">
         <v>38</v>
@@ -5055,7 +5055,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B125" s="10" t="s">
         <v>38</v>
@@ -5072,7 +5072,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B126" s="10" t="s">
         <v>38</v>
@@ -5089,7 +5089,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B127" s="10" t="s">
         <v>0</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B128" s="10" t="s">
         <v>38</v>
@@ -5123,7 +5123,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B129" s="10" t="s">
         <v>38</v>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B130" s="10" t="s">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B131" s="10" t="s">
         <v>0</v>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B132" s="10" t="s">
         <v>38</v>
@@ -5191,7 +5191,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B133" s="10" t="s">
         <v>38</v>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B134" s="10" t="s">
         <v>0</v>
@@ -5225,16 +5225,16 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D135" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
@@ -5242,16 +5242,16 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D136" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B137" s="10" t="s">
         <v>38</v>
@@ -5276,7 +5276,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B138" s="10" t="s">
         <v>0</v>
@@ -5293,7 +5293,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B139" s="10" t="s">
         <v>38</v>
@@ -5310,16 +5310,16 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C140" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D140" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
@@ -5327,16 +5327,16 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C141" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D141" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E141" s="1">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B142" s="10" t="s">
         <v>38</v>
@@ -5361,7 +5361,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B143" s="10" t="s">
         <v>38</v>
@@ -5378,7 +5378,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B144" s="10" t="s">
         <v>38</v>
@@ -5395,7 +5395,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B145" s="10" t="s">
         <v>38</v>
@@ -5412,7 +5412,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B146" s="10" t="s">
         <v>38</v>
@@ -5429,7 +5429,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B147" s="10" t="s">
         <v>38</v>
@@ -5446,7 +5446,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B148" s="10" t="s">
         <v>38</v>
@@ -5463,16 +5463,16 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>91</v>
       </c>
       <c r="D149" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E149" s="1">
         <v>0</v>
@@ -5480,16 +5480,16 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>91</v>
       </c>
       <c r="D150" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E150" s="1">
         <v>0</v>
@@ -5497,7 +5497,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B151" s="10" t="s">
         <v>38</v>
@@ -5514,7 +5514,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B152" s="10" t="s">
         <v>38</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B153" s="10" t="s">
         <v>0</v>
@@ -5548,7 +5548,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B154" s="10" t="s">
         <v>0</v>
@@ -5565,7 +5565,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B155" s="10" t="s">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B156" s="10" t="s">
         <v>38</v>
@@ -5599,7 +5599,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B157" s="10" t="s">
         <v>0</v>
@@ -5616,7 +5616,7 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B158" s="10" t="s">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B159" s="10" t="s">
         <v>0</v>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B160" s="10" t="s">
         <v>0</v>
@@ -5667,7 +5667,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B161" s="10" t="s">
         <v>38</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B162" s="10" t="s">
         <v>0</v>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B163" s="10" t="s">
         <v>0</v>
@@ -5718,7 +5718,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B164" s="10" t="s">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B165" s="10" t="s">
         <v>0</v>
@@ -5752,7 +5752,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B166" s="10" t="s">
         <v>38</v>
@@ -5769,7 +5769,7 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B167" s="10" t="s">
         <v>0</v>
@@ -5786,7 +5786,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B168" s="10" t="s">
         <v>0</v>
@@ -5803,7 +5803,7 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B169" s="10" t="s">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B170" s="10" t="s">
         <v>0</v>
@@ -5837,7 +5837,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B171" s="10" t="s">
         <v>0</v>
@@ -5854,7 +5854,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="10" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B172" s="10" t="s">
         <v>0</v>
@@ -5871,13 +5871,13 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="10" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B173" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D173" s="13">
         <v>1</v>
@@ -5888,16 +5888,16 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C174" s="10" t="s">
         <v>109</v>
       </c>
       <c r="D174" s="13">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E174" s="1">
         <v>0</v>
@@ -5905,16 +5905,16 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C175" s="10" t="s">
         <v>109</v>
       </c>
       <c r="D175" s="13">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E175" s="1">
         <v>0</v>
@@ -5922,16 +5922,16 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C176" s="10" t="s">
         <v>110</v>
       </c>
       <c r="D176" s="13">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E176" s="1">
         <v>0</v>
@@ -5939,16 +5939,16 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>110</v>
       </c>
       <c r="D177" s="13">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E177" s="1">
         <v>0</v>
@@ -5956,7 +5956,7 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B178" s="10" t="s">
         <v>38</v>
@@ -5973,7 +5973,7 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B179" s="10" t="s">
         <v>38</v>
@@ -5990,7 +5990,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B180" s="10" t="s">
         <v>38</v>
@@ -6007,7 +6007,7 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B181" s="10" t="s">
         <v>0</v>
@@ -6024,7 +6024,7 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B182" s="10" t="s">
         <v>0</v>
@@ -6041,13 +6041,13 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B183" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C183" s="10" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D183" s="13">
         <v>14</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B184" s="10" t="s">
         <v>9</v>
@@ -6075,16 +6075,16 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C185" s="10" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D185" s="13">
-        <v>400</v>
+        <v>1920</v>
       </c>
       <c r="E185" s="1">
         <v>0</v>
@@ -6092,16 +6092,16 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D186" s="13">
-        <v>1920</v>
+        <v>400</v>
       </c>
       <c r="E186" s="1">
         <v>0</v>
@@ -6109,13 +6109,13 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B187" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C187" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D187" s="13">
         <v>240</v>
@@ -6126,13 +6126,13 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B188" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D188" s="13">
         <v>1600</v>
@@ -6143,13 +6143,13 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B189" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D189" s="13">
         <v>800</v>
@@ -6160,7 +6160,7 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B190" s="10" t="s">
         <v>0</v>
@@ -6177,16 +6177,16 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D191" s="13">
-        <v>4400</v>
+        <v>600</v>
       </c>
       <c r="E191" s="1">
         <v>0</v>
@@ -6194,16 +6194,16 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D192" s="13">
-        <v>600</v>
+        <v>4400</v>
       </c>
       <c r="E192" s="1">
         <v>0</v>
@@ -6211,13 +6211,13 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B193" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D193" s="13">
         <v>2720</v>
@@ -6228,7 +6228,7 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B194" s="10" t="s">
         <v>0</v>
@@ -6245,13 +6245,13 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B195" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D195" s="13">
         <v>2040</v>
@@ -6262,13 +6262,13 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B196" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D196" s="13">
         <v>1080</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B197" s="10" t="s">
         <v>38</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B198" s="10" t="s">
         <v>0</v>
@@ -6313,7 +6313,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B199" s="10" t="s">
         <v>38</v>
@@ -6330,7 +6330,7 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B200" s="10" t="s">
         <v>38</v>
@@ -6347,7 +6347,7 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B201" s="10" t="s">
         <v>38</v>
@@ -6364,7 +6364,7 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B202" s="10" t="s">
         <v>38</v>
@@ -6381,7 +6381,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B203" s="10" t="s">
         <v>0</v>
@@ -6398,7 +6398,7 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B204" s="10" t="s">
         <v>0</v>
@@ -6415,7 +6415,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B205" s="10" t="s">
         <v>0</v>
@@ -6432,7 +6432,7 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B206" s="10" t="s">
         <v>0</v>
@@ -6449,7 +6449,7 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B207" s="10" t="s">
         <v>0</v>
@@ -6466,7 +6466,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B208" s="10" t="s">
         <v>0</v>
@@ -6483,7 +6483,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B209" s="10" t="s">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B210" s="10" t="s">
         <v>0</v>
@@ -6517,7 +6517,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B211" s="10" t="s">
         <v>0</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B212" s="10" t="s">
         <v>0</v>
@@ -6551,13 +6551,13 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B213" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C213" s="10" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D213" s="13">
         <v>22</v>
@@ -6568,7 +6568,7 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B214" s="10" t="s">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B215" s="10" t="s">
         <v>0</v>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B216" s="10" t="s">
         <v>0</v>
@@ -6619,7 +6619,7 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B217" s="10" t="s">
         <v>0</v>
@@ -6636,7 +6636,7 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B218" s="10" t="s">
         <v>0</v>
@@ -6653,7 +6653,7 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B219" s="10" t="s">
         <v>0</v>
@@ -6670,7 +6670,7 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B220" s="10" t="s">
         <v>0</v>
@@ -6687,7 +6687,7 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B221" s="10" t="s">
         <v>0</v>
@@ -6704,13 +6704,13 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B222" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D222" s="13">
         <v>100</v>
@@ -6721,13 +6721,13 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B223" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C223" s="10" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D223" s="13">
         <v>1</v>
@@ -6738,13 +6738,13 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B224" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D224" s="13">
         <v>19</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B225" s="10" t="s">
         <v>0</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B226" s="10" t="s">
         <v>0</v>
@@ -6789,13 +6789,13 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B227" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C227" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D227" s="13">
         <v>10</v>
@@ -6806,13 +6806,13 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B228" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C228" s="10" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D228" s="13">
         <v>1</v>
@@ -6823,7 +6823,7 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B229" s="10" t="s">
         <v>0</v>
@@ -6840,7 +6840,7 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B230" s="10" t="s">
         <v>0</v>
@@ -6857,7 +6857,7 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B231" s="10" t="s">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B232" s="10" t="s">
         <v>0</v>
@@ -6891,7 +6891,7 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B233" s="10" t="s">
         <v>38</v>
@@ -6908,7 +6908,7 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B234" s="10" t="s">
         <v>38</v>
@@ -6925,7 +6925,7 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="10" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B235" s="10" t="s">
         <v>0</v>
@@ -6942,7 +6942,7 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B236" s="10" t="s">
         <v>0</v>
@@ -6959,7 +6959,7 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B237" s="10" t="s">
         <v>0</v>
@@ -6976,13 +6976,13 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B238" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C238" s="10" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D238" s="13">
         <v>10</v>
@@ -6993,13 +6993,13 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B239" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D239" s="13">
         <v>10</v>
@@ -7010,13 +7010,13 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B240" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D240" s="13">
         <v>15</v>
@@ -7027,7 +7027,7 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B241" s="10" t="s">
         <v>0</v>
@@ -7044,7 +7044,7 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B242" s="10" t="s">
         <v>9</v>
@@ -7061,13 +7061,13 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B243" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D243" s="13">
         <v>800</v>
@@ -7078,13 +7078,13 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B244" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D244" s="13">
         <v>2000</v>
@@ -7095,13 +7095,13 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B245" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C245" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D245" s="13">
         <v>1800</v>
@@ -7112,7 +7112,7 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B246" s="10" t="s">
         <v>38</v>
@@ -7129,7 +7129,7 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B247" s="10" t="s">
         <v>38</v>
@@ -7146,7 +7146,7 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B248" s="10" t="s">
         <v>0</v>
@@ -7163,13 +7163,13 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B249" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C249" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D249" s="13">
         <v>60</v>
@@ -7180,13 +7180,13 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B250" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C250" s="10" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D250" s="13">
         <v>40</v>
@@ -7197,7 +7197,7 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B251" s="10" t="s">
         <v>0</v>
@@ -7214,7 +7214,7 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B252" s="10" t="s">
         <v>38</v>
@@ -7231,7 +7231,7 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B253" s="10" t="s">
         <v>38</v>
@@ -7248,7 +7248,7 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B254" s="10" t="s">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B255" s="10" t="s">
         <v>0</v>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B256" s="10" t="s">
         <v>38</v>
@@ -7299,7 +7299,7 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B257" s="10" t="s">
         <v>0</v>
@@ -7316,13 +7316,13 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B258" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C258" s="10" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D258" s="13">
         <v>49</v>
@@ -7333,7 +7333,7 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B259" s="10" t="s">
         <v>0</v>
@@ -7350,7 +7350,7 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B260" s="10" t="s">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B261" s="10" t="s">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B262" s="10" t="s">
         <v>0</v>
@@ -7401,7 +7401,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B263" s="10" t="s">
         <v>0</v>
@@ -7418,7 +7418,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B264" s="10" t="s">
         <v>0</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B265" s="10" t="s">
         <v>0</v>
@@ -7452,7 +7452,7 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B266" s="10" t="s">
         <v>0</v>
@@ -7469,7 +7469,7 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B267" s="10" t="s">
         <v>0</v>
@@ -7486,13 +7486,13 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B268" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C268" s="10" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D268" s="13">
         <v>28</v>
@@ -7503,7 +7503,7 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B269" s="10" t="s">
         <v>0</v>
@@ -7520,7 +7520,7 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B270" s="10" t="s">
         <v>0</v>
@@ -7537,13 +7537,13 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B271" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C271" s="10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D271" s="13">
         <v>12</v>
@@ -7554,7 +7554,7 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B272" s="10" t="s">
         <v>9</v>
@@ -7571,7 +7571,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B273" s="10" t="s">
         <v>9</v>
@@ -7588,13 +7588,13 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B274" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C274" s="10" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D274" s="13">
         <v>100</v>
@@ -7605,7 +7605,7 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B275" s="10" t="s">
         <v>0</v>
@@ -7622,13 +7622,13 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B276" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C276" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D276" s="13">
         <v>30</v>
@@ -7639,13 +7639,13 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B277" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C277" s="10" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D277" s="13">
         <v>40</v>
@@ -7656,7 +7656,7 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B278" s="10" t="s">
         <v>0</v>
@@ -7673,7 +7673,7 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B279" s="10" t="s">
         <v>0</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B280" s="10" t="s">
         <v>0</v>
@@ -7707,7 +7707,7 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B281" s="10" t="s">
         <v>0</v>
@@ -7724,7 +7724,7 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B282" s="10" t="s">
         <v>0</v>
@@ -7741,13 +7741,13 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B283" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C283" s="10" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D283" s="13">
         <v>3</v>
@@ -7758,7 +7758,7 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B284" s="10" t="s">
         <v>0</v>
@@ -7775,13 +7775,13 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B285" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C285" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D285" s="13">
         <v>1</v>
@@ -7792,7 +7792,7 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B286" s="10" t="s">
         <v>0</v>
@@ -7809,7 +7809,7 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B287" s="10" t="s">
         <v>0</v>
@@ -7826,13 +7826,13 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B288" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C288" s="10" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D288" s="13">
         <v>30</v>
@@ -7843,13 +7843,13 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B289" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D289" s="13">
         <v>1</v>
@@ -7860,13 +7860,13 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B290" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C290" s="10" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D290" s="13">
         <v>1</v>
@@ -7877,13 +7877,13 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B291" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C291" s="10" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D291" s="13">
         <v>5</v>
@@ -7894,13 +7894,13 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B292" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C292" s="10" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D292" s="13">
         <v>1</v>
@@ -7911,7 +7911,7 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B293" s="10" t="s">
         <v>0</v>
@@ -7928,7 +7928,7 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B294" s="10" t="s">
         <v>0</v>
@@ -7945,7 +7945,7 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B295" s="10" t="s">
         <v>0</v>
@@ -7962,13 +7962,13 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B296" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D296" s="13">
         <v>1</v>
@@ -7979,7 +7979,7 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B297" s="10" t="s">
         <v>38</v>
@@ -7996,13 +7996,13 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B298" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C298" s="10" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D298" s="13">
         <v>165</v>
@@ -8013,13 +8013,13 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B299" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C299" s="10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D299" s="13">
         <v>65</v>
@@ -8030,7 +8030,7 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B300" s="10" t="s">
         <v>38</v>
@@ -8047,7 +8047,7 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B301" s="10" t="s">
         <v>38</v>
@@ -8064,13 +8064,13 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B302" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D302" s="13">
         <v>14</v>
@@ -8081,13 +8081,13 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B303" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C303" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D303" s="13">
         <v>13</v>
@@ -8098,7 +8098,7 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B304" s="10" t="s">
         <v>38</v>
@@ -8115,13 +8115,13 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B305" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C305" s="10" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D305" s="13">
         <v>28</v>
@@ -8132,13 +8132,13 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B306" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C306" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D306" s="13">
         <v>250</v>
@@ -8149,7 +8149,7 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B307" s="10" t="s">
         <v>0</v>
@@ -8166,7 +8166,7 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B308" s="10" t="s">
         <v>38</v>
@@ -8183,7 +8183,7 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B309" s="10" t="s">
         <v>9</v>
@@ -8200,7 +8200,7 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B310" s="10" t="s">
         <v>38</v>
@@ -8217,13 +8217,13 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B311" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C311" s="10" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D311" s="13">
         <v>75</v>
@@ -8234,7 +8234,7 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B312" s="10" t="s">
         <v>38</v>
@@ -8251,7 +8251,7 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B313" s="10" t="s">
         <v>38</v>
@@ -8268,16 +8268,16 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C314" s="10" t="s">
         <v>180</v>
       </c>
       <c r="D314" s="13">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="E314" s="1">
         <v>0</v>
@@ -8285,16 +8285,16 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C315" s="10" t="s">
         <v>180</v>
       </c>
       <c r="D315" s="13">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="E315" s="1">
         <v>0</v>
@@ -8302,13 +8302,13 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B316" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C316" s="10" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D316" s="13">
         <v>20</v>
@@ -8319,13 +8319,13 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B317" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C317" s="10" t="s">
-        <v>472</v>
+        <v>791</v>
       </c>
       <c r="D317" s="13">
         <v>990</v>
@@ -8336,13 +8336,13 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B318" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C318" s="10" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D318" s="13">
         <v>450</v>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B319" s="10" t="s">
         <v>38</v>
@@ -8370,7 +8370,7 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B320" s="10" t="s">
         <v>0</v>
@@ -8387,7 +8387,7 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B321" s="10" t="s">
         <v>9</v>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B322" s="10" t="s">
         <v>38</v>
@@ -8421,7 +8421,7 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="10" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B323" s="10" t="s">
         <v>0</v>
@@ -8438,16 +8438,16 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B324" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C324" s="10" t="s">
         <v>182</v>
       </c>
       <c r="D324" s="13">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="E324" s="1">
         <v>0</v>
@@ -8455,16 +8455,16 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="10" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C325" s="10" t="s">
         <v>182</v>
       </c>
       <c r="D325" s="13">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="E325" s="1">
         <v>0</v>
@@ -8472,7 +8472,7 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B326" s="10" t="s">
         <v>38</v>
@@ -8489,7 +8489,7 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B327" s="10" t="s">
         <v>38</v>
@@ -8506,7 +8506,7 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B328" s="10" t="s">
         <v>9</v>
@@ -8523,7 +8523,7 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B329" s="10" t="s">
         <v>9</v>
@@ -8540,13 +8540,13 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B330" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C330" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D330" s="13">
         <v>1</v>
@@ -8557,13 +8557,13 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B331" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C331" s="10" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D331" s="13">
         <v>25</v>
@@ -8574,13 +8574,13 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B332" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C332" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D332" s="13">
         <v>10</v>
@@ -8591,7 +8591,7 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B333" s="10" t="s">
         <v>38</v>
@@ -8608,7 +8608,7 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B334" s="10" t="s">
         <v>38</v>
@@ -8625,7 +8625,7 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B335" s="10" t="s">
         <v>38</v>
@@ -8642,7 +8642,7 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B336" s="10" t="s">
         <v>38</v>
@@ -8659,7 +8659,7 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B337" s="10" t="s">
         <v>0</v>
@@ -8676,7 +8676,7 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B338" s="10" t="s">
         <v>38</v>
@@ -8693,7 +8693,7 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B339" s="10" t="s">
         <v>38</v>
@@ -8710,7 +8710,7 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B340" s="10" t="s">
         <v>38</v>
@@ -8727,16 +8727,16 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B341" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C341" s="10" t="s">
         <v>189</v>
       </c>
       <c r="D341" s="13">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E341" s="1">
         <v>0</v>
@@ -8744,16 +8744,16 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B342" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C342" s="10" t="s">
         <v>189</v>
       </c>
       <c r="D342" s="13">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="E342" s="1">
         <v>0</v>
@@ -8761,10 +8761,10 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C343" s="10" t="s">
         <v>190</v>
@@ -8778,10 +8778,10 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C344" s="10" t="s">
         <v>190</v>
@@ -8795,7 +8795,7 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B345" s="10" t="s">
         <v>0</v>
@@ -8812,7 +8812,7 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B346" s="10" t="s">
         <v>38</v>
@@ -8829,7 +8829,7 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B347" s="10" t="s">
         <v>0</v>
@@ -8846,7 +8846,7 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B348" s="10" t="s">
         <v>38</v>
@@ -8863,7 +8863,7 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B349" s="10" t="s">
         <v>38</v>
@@ -8880,13 +8880,13 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="10" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B350" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C350" s="10" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D350" s="13">
         <v>90</v>
@@ -8897,13 +8897,13 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="B351" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C351" s="10" t="s">
         <v>706</v>
-      </c>
-      <c r="B351" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C351" s="10" t="s">
-        <v>707</v>
       </c>
       <c r="D351" s="13">
         <v>50</v>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B352" s="10" t="s">
         <v>38</v>
@@ -8931,7 +8931,7 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B353" s="10" t="s">
         <v>38</v>
@@ -8948,7 +8948,7 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B354" s="10" t="s">
         <v>38</v>
@@ -8965,7 +8965,7 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B355" s="10" t="s">
         <v>0</v>
@@ -8982,7 +8982,7 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B356" s="10" t="s">
         <v>0</v>
@@ -8999,7 +8999,7 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B357" s="10" t="s">
         <v>0</v>
@@ -9016,7 +9016,7 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B358" s="10" t="s">
         <v>0</v>
@@ -9033,13 +9033,13 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B359" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C359" s="10" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D359" s="13">
         <v>1</v>
@@ -9050,7 +9050,7 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B360" s="10" t="s">
         <v>0</v>
@@ -9067,7 +9067,7 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B361" s="10" t="s">
         <v>9</v>
@@ -9084,7 +9084,7 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B362" s="10" t="s">
         <v>0</v>
@@ -9101,7 +9101,7 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B363" s="10" t="s">
         <v>0</v>
@@ -9118,13 +9118,13 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B364" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C364" s="10" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D364" s="13">
         <v>1</v>
@@ -9135,7 +9135,7 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B365" s="10" t="s">
         <v>0</v>
@@ -9152,13 +9152,13 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B366" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C366" s="10" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D366" s="13">
         <v>19</v>
@@ -9169,7 +9169,7 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B367" s="10" t="s">
         <v>0</v>
@@ -9186,13 +9186,13 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B368" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C368" s="10" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D368" s="13">
         <v>14</v>
@@ -9203,13 +9203,13 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B369" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C369" s="10" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D369" s="13">
         <v>18</v>
@@ -9220,7 +9220,7 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B370" s="10" t="s">
         <v>0</v>
@@ -9237,7 +9237,7 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B371" s="10" t="s">
         <v>0</v>
@@ -9254,13 +9254,13 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B372" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C372" s="10" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D372" s="13">
         <v>30</v>
@@ -9271,7 +9271,7 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B373" s="10" t="s">
         <v>0</v>
@@ -9288,7 +9288,7 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B374" s="10" t="s">
         <v>0</v>
@@ -9305,13 +9305,13 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B375" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C375" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D375" s="13">
         <v>1</v>
@@ -9322,7 +9322,7 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B376" s="10" t="s">
         <v>0</v>
@@ -9339,7 +9339,7 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B377" s="10" t="s">
         <v>0</v>
@@ -9356,7 +9356,7 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B378" s="10" t="s">
         <v>38</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B379" s="10" t="s">
         <v>38</v>
@@ -9390,7 +9390,7 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B380" s="10" t="s">
         <v>38</v>
@@ -9407,7 +9407,7 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B381" s="10" t="s">
         <v>38</v>
@@ -9424,7 +9424,7 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B382" s="10" t="s">
         <v>38</v>
@@ -9441,7 +9441,7 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B383" s="10" t="s">
         <v>0</v>
@@ -9458,7 +9458,7 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B384" s="10" t="s">
         <v>0</v>
@@ -9475,7 +9475,7 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B385" s="10" t="s">
         <v>0</v>
@@ -9492,7 +9492,7 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B386" s="10" t="s">
         <v>0</v>
@@ -9509,7 +9509,7 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B387" s="10" t="s">
         <v>38</v>
@@ -9526,7 +9526,7 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B388" s="10" t="s">
         <v>0</v>
@@ -9543,7 +9543,7 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B389" s="10" t="s">
         <v>0</v>
@@ -9560,16 +9560,16 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B390" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C390" s="10" t="s">
         <v>216</v>
       </c>
       <c r="D390" s="13">
-        <v>2550</v>
+        <v>360</v>
       </c>
       <c r="E390" s="1">
         <v>0</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B391" s="10" t="s">
         <v>0</v>
@@ -9594,16 +9594,16 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B392" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C392" s="10" t="s">
         <v>216</v>
       </c>
       <c r="D392" s="13">
-        <v>360</v>
+        <v>2550</v>
       </c>
       <c r="E392" s="1">
         <v>0</v>
@@ -9611,7 +9611,7 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B393" s="10" t="s">
         <v>38</v>
@@ -9628,7 +9628,7 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B394" s="10" t="s">
         <v>0</v>
@@ -9645,7 +9645,7 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B395" s="10" t="s">
         <v>38</v>
@@ -9662,7 +9662,7 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B396" s="10" t="s">
         <v>0</v>
@@ -9679,7 +9679,7 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B397" s="10" t="s">
         <v>0</v>
@@ -9696,7 +9696,7 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B398" s="10" t="s">
         <v>0</v>
@@ -9713,7 +9713,7 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B399" s="10" t="s">
         <v>0</v>
@@ -9730,7 +9730,7 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B400" s="10" t="s">
         <v>0</v>
@@ -9747,7 +9747,7 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B401" s="10" t="s">
         <v>0</v>
@@ -9764,7 +9764,7 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B402" s="10" t="s">
         <v>0</v>
@@ -9781,7 +9781,7 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B403" s="10" t="s">
         <v>0</v>
@@ -9798,7 +9798,7 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B404" s="10" t="s">
         <v>0</v>
@@ -9815,7 +9815,7 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B405" s="10" t="s">
         <v>9</v>
@@ -9832,16 +9832,16 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B406" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C406" s="10" t="s">
         <v>228</v>
       </c>
       <c r="D406" s="13">
-        <v>316</v>
+        <v>14</v>
       </c>
       <c r="E406" s="1">
         <v>0</v>
@@ -9849,16 +9849,16 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B407" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C407" s="10" t="s">
         <v>228</v>
       </c>
       <c r="D407" s="13">
-        <v>14</v>
+        <v>316</v>
       </c>
       <c r="E407" s="1">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B408" s="10" t="s">
         <v>9</v>
@@ -9883,7 +9883,7 @@
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B409" s="10" t="s">
         <v>9</v>
@@ -9900,16 +9900,16 @@
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B410" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C410" s="10" t="s">
         <v>231</v>
       </c>
       <c r="D410" s="13">
-        <v>1200</v>
+        <v>129</v>
       </c>
       <c r="E410" s="1">
         <v>0</v>
@@ -9917,16 +9917,16 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B411" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C411" s="10" t="s">
         <v>231</v>
       </c>
       <c r="D411" s="13">
-        <v>129</v>
+        <v>1200</v>
       </c>
       <c r="E411" s="1">
         <v>0</v>
@@ -9934,7 +9934,7 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B412" s="10" t="s">
         <v>38</v>
@@ -9951,7 +9951,7 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B413" s="10" t="s">
         <v>0</v>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B414" s="10" t="s">
         <v>38</v>
@@ -9985,7 +9985,7 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B415" s="10" t="s">
         <v>38</v>
@@ -10002,13 +10002,13 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B416" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C416" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D416" s="13">
         <v>290</v>
@@ -10019,7 +10019,7 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B417" s="10" t="s">
         <v>38</v>
@@ -10036,7 +10036,7 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B418" s="10" t="s">
         <v>0</v>
@@ -10053,16 +10053,16 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B419" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C419" s="10" t="s">
         <v>232</v>
       </c>
       <c r="D419" s="13">
-        <v>1525</v>
+        <v>300</v>
       </c>
       <c r="E419" s="1">
         <v>0</v>
@@ -10070,16 +10070,16 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B420" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C420" s="10" t="s">
         <v>232</v>
       </c>
       <c r="D420" s="13">
-        <v>300</v>
+        <v>1525</v>
       </c>
       <c r="E420" s="1">
         <v>0</v>
@@ -10087,7 +10087,7 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B421" s="10" t="s">
         <v>0</v>
@@ -10104,16 +10104,16 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B422" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C422" s="10" t="s">
         <v>233</v>
       </c>
       <c r="D422" s="13">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="E422" s="1">
         <v>0</v>
@@ -10121,16 +10121,16 @@
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B423" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C423" s="10" t="s">
         <v>233</v>
       </c>
       <c r="D423" s="13">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="E423" s="1">
         <v>0</v>
@@ -10138,7 +10138,7 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B424" s="10" t="s">
         <v>38</v>
@@ -10155,7 +10155,7 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B425" s="10" t="s">
         <v>0</v>
@@ -10172,7 +10172,7 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B426" s="10" t="s">
         <v>0</v>
@@ -10189,7 +10189,7 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B427" s="10" t="s">
         <v>0</v>
@@ -10206,7 +10206,7 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B428" s="10" t="s">
         <v>0</v>
@@ -10223,13 +10223,13 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B429" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C429" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D429" s="13">
         <v>1</v>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B430" s="10" t="s">
         <v>0</v>
@@ -10257,7 +10257,7 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B431" s="10" t="s">
         <v>9</v>
@@ -10274,7 +10274,7 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B432" s="10" t="s">
         <v>9</v>
@@ -10291,7 +10291,7 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B433" s="10" t="s">
         <v>0</v>
@@ -10308,7 +10308,7 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B434" s="10" t="s">
         <v>0</v>
@@ -10325,7 +10325,7 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B435" s="10" t="s">
         <v>38</v>
@@ -10342,13 +10342,13 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B436" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C436" s="10" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D436" s="13">
         <v>140</v>
@@ -10359,7 +10359,7 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B437" s="10" t="s">
         <v>0</v>
@@ -10376,7 +10376,7 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B438" s="10" t="s">
         <v>38</v>
@@ -10393,7 +10393,7 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B439" s="10" t="s">
         <v>0</v>
@@ -10410,13 +10410,13 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B440" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C440" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D440" s="13">
         <v>60</v>
@@ -10427,7 +10427,7 @@
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B441" s="10" t="s">
         <v>38</v>
@@ -10444,7 +10444,7 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B442" s="10" t="s">
         <v>38</v>
@@ -10461,7 +10461,7 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B443" s="10" t="s">
         <v>38</v>
@@ -10478,7 +10478,7 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B444" s="10" t="s">
         <v>9</v>
@@ -10495,7 +10495,7 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B445" s="10" t="s">
         <v>0</v>
@@ -10512,7 +10512,7 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B446" s="10" t="s">
         <v>0</v>
@@ -10529,7 +10529,7 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B447" s="10" t="s">
         <v>0</v>
@@ -10546,7 +10546,7 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B448" s="10" t="s">
         <v>0</v>
@@ -10563,7 +10563,7 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B449" s="10" t="s">
         <v>0</v>
@@ -10580,7 +10580,7 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B450" s="10" t="s">
         <v>0</v>
@@ -10597,7 +10597,7 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B451" s="10" t="s">
         <v>0</v>
@@ -10614,7 +10614,7 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B452" s="10" t="s">
         <v>0</v>
@@ -10631,7 +10631,7 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B453" s="10" t="s">
         <v>0</v>
@@ -10648,7 +10648,7 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B454" s="10" t="s">
         <v>0</v>
@@ -10665,13 +10665,13 @@
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B455" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C455" s="10" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D455" s="13">
         <v>6</v>
@@ -10682,13 +10682,13 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B456" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C456" s="10" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D456" s="13">
         <v>6</v>
@@ -10699,13 +10699,13 @@
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="10" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B457" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C457" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D457" s="13">
         <v>4</v>
@@ -10716,7 +10716,7 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B458" s="10" t="s">
         <v>0</v>
@@ -10733,7 +10733,7 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B459" s="10" t="s">
         <v>0</v>
@@ -10750,7 +10750,7 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B460" s="10" t="s">
         <v>38</v>
@@ -10767,7 +10767,7 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B461" s="10" t="s">
         <v>38</v>
@@ -10784,7 +10784,7 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B462" s="10" t="s">
         <v>38</v>
@@ -10801,7 +10801,7 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B463" s="10" t="s">
         <v>38</v>
@@ -10818,13 +10818,13 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B464" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C464" s="10" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D464" s="13">
         <v>3760</v>
@@ -10835,7 +10835,7 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B465" s="10" t="s">
         <v>38</v>
@@ -10852,7 +10852,7 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B466" s="10" t="s">
         <v>0</v>
@@ -10869,7 +10869,7 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B467" s="10" t="s">
         <v>0</v>
@@ -10886,13 +10886,13 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B468" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C468" s="10" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D468" s="13">
         <v>1632</v>
@@ -10903,7 +10903,7 @@
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B469" s="10" t="s">
         <v>0</v>
@@ -10920,13 +10920,13 @@
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B470" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C470" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D470" s="13">
         <v>40</v>
@@ -10937,7 +10937,7 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B471" s="10" t="s">
         <v>0</v>
@@ -10954,7 +10954,7 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B472" s="10" t="s">
         <v>0</v>
@@ -10971,7 +10971,7 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B473" s="10" t="s">
         <v>38</v>
@@ -10988,7 +10988,7 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B474" s="10" t="s">
         <v>38</v>
@@ -11005,7 +11005,7 @@
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B475" s="10" t="s">
         <v>38</v>
@@ -11022,7 +11022,7 @@
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B476" s="10" t="s">
         <v>38</v>
@@ -11039,7 +11039,7 @@
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B477" s="10" t="s">
         <v>38</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B478" s="10" t="s">
         <v>38</v>
@@ -11073,7 +11073,7 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B479" s="10" t="s">
         <v>38</v>
@@ -11090,7 +11090,7 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B480" s="10" t="s">
         <v>0</v>
@@ -11107,13 +11107,13 @@
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B481" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C481" s="10" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D481" s="13">
         <v>575</v>
@@ -11124,13 +11124,13 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B482" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D482" s="13">
         <v>9500</v>
@@ -11141,13 +11141,13 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B483" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C483" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D483" s="13">
         <v>575</v>
@@ -11158,7 +11158,7 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B484" s="10" t="s">
         <v>0</v>
@@ -11175,13 +11175,13 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B485" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C485" s="10" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D485" s="13">
         <v>5000</v>
@@ -11192,7 +11192,7 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B486" s="10" t="s">
         <v>38</v>
@@ -11209,7 +11209,7 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B487" s="10" t="s">
         <v>0</v>
@@ -11226,7 +11226,7 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B488" s="10" t="s">
         <v>0</v>
@@ -11243,7 +11243,7 @@
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B489" s="10" t="s">
         <v>0</v>
@@ -11260,7 +11260,7 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B490" s="10" t="s">
         <v>0</v>
@@ -11277,7 +11277,7 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B491" s="10" t="s">
         <v>0</v>
@@ -11294,7 +11294,7 @@
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B492" s="10" t="s">
         <v>0</v>
@@ -11311,7 +11311,7 @@
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B493" s="10" t="s">
         <v>0</v>
@@ -11328,7 +11328,7 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B494" s="10" t="s">
         <v>0</v>
@@ -11345,7 +11345,7 @@
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B495" s="10" t="s">
         <v>0</v>
@@ -11362,7 +11362,7 @@
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B496" s="10" t="s">
         <v>0</v>
@@ -11379,7 +11379,7 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B497" s="10" t="s">
         <v>0</v>
@@ -11396,7 +11396,7 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B498" s="10" t="s">
         <v>0</v>
@@ -11413,7 +11413,7 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B499" s="10" t="s">
         <v>0</v>
@@ -11430,7 +11430,7 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B500" s="10" t="s">
         <v>0</v>
@@ -11447,7 +11447,7 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B501" s="10" t="s">
         <v>0</v>
@@ -11464,13 +11464,13 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B502" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C502" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D502" s="13">
         <v>1</v>
@@ -11481,7 +11481,7 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B503" s="10" t="s">
         <v>0</v>
@@ -11498,7 +11498,7 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B504" s="10" t="s">
         <v>0</v>
@@ -11515,13 +11515,13 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B505" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C505" s="10" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D505" s="13">
         <v>5</v>
@@ -11532,13 +11532,13 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B506" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C506" s="10" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="D506" s="13">
         <v>2</v>
@@ -11549,13 +11549,13 @@
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B507" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C507" s="10" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D507" s="13">
         <v>3</v>
@@ -11566,13 +11566,13 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B508" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="C508" s="10" t="s">
         <v>512</v>
-      </c>
-      <c r="C508" s="10" t="s">
-        <v>513</v>
       </c>
       <c r="D508" s="13">
         <v>3</v>
@@ -11583,13 +11583,13 @@
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B509" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C509" s="10" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D509" s="13">
         <v>2</v>
@@ -11600,13 +11600,13 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B510" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C510" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D510" s="13">
         <v>23</v>
@@ -11617,13 +11617,13 @@
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B511" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C511" s="10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D511" s="13">
         <v>1</v>
@@ -11634,13 +11634,13 @@
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B512" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C512" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D512" s="13">
         <v>1</v>
@@ -11651,13 +11651,13 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B513" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C513" s="10" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D513" s="13">
         <v>3</v>
@@ -11668,13 +11668,13 @@
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B514" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C514" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D514" s="13">
         <v>2</v>
@@ -11685,13 +11685,13 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B515" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C515" s="10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D515" s="13">
         <v>2</v>
@@ -11702,13 +11702,13 @@
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B516" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C516" s="10" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D516" s="13">
         <v>1</v>
@@ -11719,13 +11719,13 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B517" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C517" s="10" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D517" s="13">
         <v>1</v>
@@ -11736,7 +11736,7 @@
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B518" s="10" t="s">
         <v>0</v>
@@ -11753,7 +11753,7 @@
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B519" s="10" t="s">
         <v>0</v>
@@ -11770,7 +11770,7 @@
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B520" s="10" t="s">
         <v>0</v>
@@ -11787,7 +11787,7 @@
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B521" s="10" t="s">
         <v>0</v>
@@ -11804,7 +11804,7 @@
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B522" s="10" t="s">
         <v>0</v>
@@ -11821,7 +11821,7 @@
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B523" s="10" t="s">
         <v>0</v>
@@ -11838,7 +11838,7 @@
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B524" s="10" t="s">
         <v>0</v>
@@ -11855,7 +11855,7 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B525" s="10" t="s">
         <v>0</v>
@@ -11872,13 +11872,13 @@
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B526" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C526" s="10" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D526" s="13">
         <v>2</v>
@@ -11889,13 +11889,13 @@
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B527" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C527" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D527" s="13">
         <v>4</v>
@@ -11906,13 +11906,13 @@
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B528" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C528" s="10" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D528" s="13">
         <v>2</v>
@@ -11923,13 +11923,13 @@
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B529" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C529" s="10" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D529" s="13">
         <v>3</v>
@@ -11940,13 +11940,13 @@
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B530" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C530" s="10" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D530" s="13">
         <v>2</v>
@@ -11957,13 +11957,13 @@
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B531" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C531" s="10" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D531" s="13">
         <v>3</v>
@@ -11974,13 +11974,13 @@
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="B532" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C532" s="10" t="s">
         <v>736</v>
-      </c>
-      <c r="B532" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C532" s="10" t="s">
-        <v>737</v>
       </c>
       <c r="D532" s="13">
         <v>8</v>
@@ -11991,13 +11991,13 @@
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B533" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C533" s="10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D533" s="13">
         <v>1</v>
@@ -12008,13 +12008,13 @@
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B534" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C534" s="10" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D534" s="13">
         <v>1</v>
@@ -12025,13 +12025,13 @@
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B535" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C535" s="10" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D535" s="13">
         <v>1</v>
@@ -12042,13 +12042,13 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B536" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C536" s="10" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D536" s="13">
         <v>2</v>
@@ -12059,13 +12059,13 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B537" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C537" s="10" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D537" s="13">
         <v>1</v>
@@ -12076,13 +12076,13 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B538" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C538" s="10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D538" s="13">
         <v>1</v>
@@ -12093,13 +12093,13 @@
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B539" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C539" s="10" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D539" s="13">
         <v>1</v>
@@ -12110,13 +12110,13 @@
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B540" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C540" s="10" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D540" s="13">
         <v>2</v>
@@ -12127,13 +12127,13 @@
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B541" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C541" s="10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D541" s="13">
         <v>1</v>
@@ -12144,13 +12144,13 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B542" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C542" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D542" s="13">
         <v>2</v>
@@ -12161,13 +12161,13 @@
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B543" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C543" s="10" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D543" s="13">
         <v>1</v>
@@ -12178,13 +12178,13 @@
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B544" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C544" s="10" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D544" s="13">
         <v>1</v>
@@ -12195,13 +12195,13 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B545" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C545" s="10" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D545" s="13">
         <v>1</v>
@@ -12212,13 +12212,13 @@
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B546" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C546" s="10" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D546" s="13">
         <v>1</v>
@@ -12229,13 +12229,13 @@
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B547" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C547" s="10" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D547" s="13">
         <v>1</v>
@@ -12246,13 +12246,13 @@
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B548" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C548" s="10" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D548" s="13">
         <v>2</v>
@@ -12263,13 +12263,13 @@
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B549" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C549" s="10" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D549" s="13">
         <v>3</v>
@@ -12280,13 +12280,13 @@
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B550" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C550" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D550" s="13">
         <v>1</v>
@@ -12297,13 +12297,13 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B551" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C551" s="10" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D551" s="13">
         <v>4</v>
@@ -12314,13 +12314,13 @@
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B552" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C552" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D552" s="13">
         <v>3</v>
@@ -12331,13 +12331,13 @@
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B553" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C553" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D553" s="13">
         <v>4</v>
@@ -12348,13 +12348,13 @@
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B554" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C554" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D554" s="13">
         <v>5</v>
@@ -12365,13 +12365,13 @@
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B555" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C555" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D555" s="13">
         <v>2</v>
@@ -12382,13 +12382,13 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B556" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C556" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D556" s="13">
         <v>3</v>
@@ -12399,7 +12399,7 @@
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B557" s="10" t="s">
         <v>0</v>
@@ -12416,7 +12416,7 @@
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B558" s="10" t="s">
         <v>0</v>
@@ -12433,13 +12433,13 @@
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B559" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C559" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D559" s="13">
         <v>1</v>
@@ -12450,10 +12450,10 @@
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B560" s="10" t="s">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="C560" s="10" t="s">
         <v>299</v>
@@ -12467,10 +12467,10 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B561" s="10" t="s">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="C561" s="10" t="s">
         <v>299</v>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B562" s="10" t="s">
         <v>0</v>
@@ -12501,7 +12501,7 @@
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B563" s="10" t="s">
         <v>0</v>
@@ -12518,7 +12518,7 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B564" s="10" t="s">
         <v>0</v>
@@ -12535,7 +12535,7 @@
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B565" s="10" t="s">
         <v>0</v>
@@ -12552,7 +12552,7 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B566" s="10" t="s">
         <v>0</v>
@@ -12569,13 +12569,13 @@
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B567" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C567" s="10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D567" s="13">
         <v>2</v>
@@ -12586,13 +12586,13 @@
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B568" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C568" s="10" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D568" s="13">
         <v>1</v>
@@ -12603,13 +12603,13 @@
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B569" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C569" s="10" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D569" s="13">
         <v>2</v>
@@ -12620,13 +12620,13 @@
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B570" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C570" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D570" s="13">
         <v>1</v>
@@ -12637,13 +12637,13 @@
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B571" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C571" s="10" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D571" s="13">
         <v>1</v>
@@ -12654,13 +12654,13 @@
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B572" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C572" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D572" s="13">
         <v>2</v>
@@ -12671,13 +12671,13 @@
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B573" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C573" s="10" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D573" s="13">
         <v>3</v>
@@ -12688,13 +12688,13 @@
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B574" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C574" s="10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D574" s="13">
         <v>2</v>
@@ -12705,13 +12705,13 @@
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B575" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C575" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D575" s="13">
         <v>3</v>
@@ -12722,13 +12722,13 @@
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B576" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C576" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D576" s="13">
         <v>4</v>
@@ -12739,13 +12739,13 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B577" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C577" s="10" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D577" s="13">
         <v>2</v>
@@ -12756,13 +12756,13 @@
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B578" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C578" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D578" s="13">
         <v>2</v>
@@ -12773,13 +12773,13 @@
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B579" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C579" s="10" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D579" s="13">
         <v>1</v>
@@ -12790,13 +12790,13 @@
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B580" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C580" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D580" s="13">
         <v>1</v>
@@ -12807,7 +12807,7 @@
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B581" s="10" t="s">
         <v>0</v>
@@ -12824,13 +12824,13 @@
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B582" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C582" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D582" s="13">
         <v>1</v>
@@ -12841,7 +12841,7 @@
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A583" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B583" s="10" t="s">
         <v>38</v>
@@ -12858,7 +12858,7 @@
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B584" s="10" t="s">
         <v>38</v>
@@ -12875,13 +12875,13 @@
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B585" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C585" s="10" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D585" s="13">
         <v>3</v>
@@ -12892,13 +12892,13 @@
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A586" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B586" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C586" s="10" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D586" s="13">
         <v>3</v>
@@ -12909,13 +12909,13 @@
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B587" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C587" s="10" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D587" s="13">
         <v>2</v>
@@ -12926,13 +12926,13 @@
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B588" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C588" s="10" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D588" s="13">
         <v>3</v>
@@ -12943,7 +12943,7 @@
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" s="10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B589" s="10" t="s">
         <v>0</v>
@@ -12960,13 +12960,13 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B590" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C590" s="10" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D590" s="13">
         <v>2000</v>
@@ -12977,13 +12977,13 @@
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B591" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C591" s="10" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D591" s="13">
         <v>2500</v>
@@ -12994,13 +12994,13 @@
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A592" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B592" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C592" s="10" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D592" s="13">
         <v>2400</v>
@@ -13011,13 +13011,13 @@
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A593" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B593" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C593" s="10" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D593" s="13">
         <v>1</v>
@@ -13028,13 +13028,13 @@
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A594" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B594" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C594" s="10" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D594" s="13">
         <v>2</v>
@@ -13045,7 +13045,7 @@
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A595" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B595" s="10" t="s">
         <v>9</v>
@@ -13062,13 +13062,13 @@
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A596" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B596" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C596" s="10" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D596" s="13">
         <v>1</v>
@@ -13079,13 +13079,13 @@
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A597" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B597" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C597" s="10" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D597" s="13">
         <v>1850</v>
@@ -13096,7 +13096,7 @@
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A598" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B598" s="10" t="s">
         <v>0</v>
@@ -13113,13 +13113,13 @@
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A599" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B599" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C599" s="10" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D599" s="13">
         <v>2500</v>
@@ -13130,13 +13130,13 @@
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A600" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B600" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C600" s="10" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D600" s="13">
         <v>2400</v>
@@ -13147,13 +13147,13 @@
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A601" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B601" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C601" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D601" s="13">
         <v>800</v>
@@ -13164,13 +13164,13 @@
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A602" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B602" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C602" s="10" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D602" s="13">
         <v>1600</v>
@@ -13181,13 +13181,13 @@
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A603" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B603" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C603" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D603" s="13">
         <v>1000</v>
@@ -13198,13 +13198,13 @@
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A604" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B604" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C604" s="10" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D604" s="13">
         <v>1600</v>
@@ -13215,13 +13215,13 @@
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A605" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B605" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C605" s="10" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D605" s="13">
         <v>800</v>
@@ -13232,13 +13232,13 @@
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A606" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B606" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C606" s="10" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D606" s="13">
         <v>1250</v>
@@ -13249,13 +13249,13 @@
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A607" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B607" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C607" s="10" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D607" s="13">
         <v>1550</v>
@@ -13266,7 +13266,7 @@
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A608" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B608" s="10" t="s">
         <v>0</v>
@@ -13283,13 +13283,13 @@
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A609" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B609" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C609" s="10" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D609" s="13">
         <v>1700</v>
@@ -13300,13 +13300,13 @@
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A610" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B610" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C610" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D610" s="13">
         <v>1000</v>
@@ -13317,7 +13317,7 @@
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A611" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B611" s="10" t="s">
         <v>0</v>
@@ -13334,7 +13334,7 @@
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A612" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B612" s="10" t="s">
         <v>0</v>
@@ -13351,7 +13351,7 @@
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A613" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B613" s="10" t="s">
         <v>0</v>
@@ -13368,7 +13368,7 @@
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A614" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B614" s="10" t="s">
         <v>0</v>
@@ -13385,7 +13385,7 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B615" s="10" t="s">
         <v>0</v>
@@ -13402,7 +13402,7 @@
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A616" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B616" s="10" t="s">
         <v>0</v>
@@ -13419,7 +13419,7 @@
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B617" s="10" t="s">
         <v>0</v>
@@ -13436,7 +13436,7 @@
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A618" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B618" s="10" t="s">
         <v>0</v>
@@ -13453,7 +13453,7 @@
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A619" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B619" s="10" t="s">
         <v>38</v>
@@ -13470,7 +13470,7 @@
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A620" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B620" s="10" t="s">
         <v>38</v>
@@ -13487,7 +13487,7 @@
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A621" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B621" s="10" t="s">
         <v>38</v>
@@ -13504,7 +13504,7 @@
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A622" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B622" s="10" t="s">
         <v>0</v>
@@ -13521,7 +13521,7 @@
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A623" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B623" s="10" t="s">
         <v>0</v>
@@ -13538,7 +13538,7 @@
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A624" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B624" s="10" t="s">
         <v>0</v>
@@ -13555,7 +13555,7 @@
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A625" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B625" s="10" t="s">
         <v>38</v>
@@ -13572,7 +13572,7 @@
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A626" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B626" s="10" t="s">
         <v>38</v>
@@ -13589,7 +13589,7 @@
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A627" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B627" s="10" t="s">
         <v>38</v>
@@ -13606,7 +13606,7 @@
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A628" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B628" s="10" t="s">
         <v>0</v>
@@ -13623,7 +13623,7 @@
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A629" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B629" s="10" t="s">
         <v>38</v>
@@ -13640,13 +13640,13 @@
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A630" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="B630" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C630" s="10" t="s">
         <v>712</v>
-      </c>
-      <c r="B630" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C630" s="10" t="s">
-        <v>713</v>
       </c>
       <c r="D630" s="13">
         <v>100</v>
@@ -13657,7 +13657,7 @@
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A631" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B631" s="10" t="s">
         <v>38</v>
@@ -13674,13 +13674,13 @@
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B632" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C632" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D632" s="13">
         <v>35</v>
@@ -13691,7 +13691,7 @@
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A633" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B633" s="10" t="s">
         <v>0</v>
@@ -13708,7 +13708,7 @@
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A634" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B634" s="10" t="s">
         <v>38</v>
@@ -13725,13 +13725,13 @@
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A635" s="10" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B635" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C635" s="10" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D635" s="13">
         <v>30</v>
@@ -13742,7 +13742,7 @@
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B636" s="10" t="s">
         <v>38</v>
@@ -13759,7 +13759,7 @@
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A637" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B637" s="10" t="s">
         <v>38</v>
@@ -13776,7 +13776,7 @@
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A638" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B638" s="10" t="s">
         <v>38</v>
@@ -13793,7 +13793,7 @@
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B639" s="1" t="s">
         <v>404</v>
@@ -13810,7 +13810,7 @@
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B640" s="1" t="s">
         <v>0</v>
@@ -13827,7 +13827,7 @@
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B641" s="1" t="s">
         <v>0</v>
@@ -13844,7 +13844,7 @@
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B642" s="1" t="s">
         <v>0</v>
@@ -13861,7 +13861,7 @@
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B643" s="1" t="s">
         <v>0</v>
@@ -13878,7 +13878,7 @@
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B644" s="1" t="s">
         <v>0</v>
@@ -13895,7 +13895,7 @@
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B645" s="1" t="s">
         <v>0</v>
@@ -13912,7 +13912,7 @@
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B646" s="1" t="s">
         <v>9</v>
@@ -13929,7 +13929,7 @@
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B647" s="1" t="s">
         <v>9</v>
@@ -13946,7 +13946,7 @@
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B648" s="1" t="s">
         <v>9</v>
@@ -13963,7 +13963,7 @@
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B649" s="1" t="s">
         <v>9</v>
@@ -13980,7 +13980,7 @@
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B650" s="1" t="s">
         <v>38</v>
@@ -13997,7 +13997,7 @@
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B651" s="1" t="s">
         <v>38</v>
@@ -14014,13 +14014,13 @@
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B652" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D652" s="14">
         <v>465</v>
@@ -14031,16 +14031,16 @@
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C653" s="1" t="s">
         <v>336</v>
       </c>
       <c r="D653" s="14">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E653" s="1">
         <v>0</v>
@@ -14048,16 +14048,16 @@
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C654" s="1" t="s">
         <v>336</v>
       </c>
       <c r="D654" s="14">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E654" s="1">
         <v>0</v>
@@ -14065,7 +14065,7 @@
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B655" s="1" t="s">
         <v>0</v>
@@ -14082,7 +14082,7 @@
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B656" s="1" t="s">
         <v>38</v>
@@ -14099,7 +14099,7 @@
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B657" s="1" t="s">
         <v>38</v>
@@ -14116,7 +14116,7 @@
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B658" s="1" t="s">
         <v>0</v>
@@ -14133,7 +14133,7 @@
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B659" s="1" t="s">
         <v>0</v>
@@ -14150,7 +14150,7 @@
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B660" s="1" t="s">
         <v>0</v>
@@ -14167,7 +14167,7 @@
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B661" s="1" t="s">
         <v>0</v>
@@ -14184,7 +14184,7 @@
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B662" s="1" t="s">
         <v>0</v>
@@ -14201,13 +14201,13 @@
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B663" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C663" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D663" s="14">
         <v>1000</v>
@@ -14218,7 +14218,7 @@
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B664" s="1" t="s">
         <v>0</v>
@@ -14235,7 +14235,7 @@
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B665" s="1" t="s">
         <v>0</v>
@@ -14252,7 +14252,7 @@
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B666" s="1" t="s">
         <v>0</v>
@@ -14269,7 +14269,7 @@
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B667" s="1" t="s">
         <v>0</v>
@@ -14286,7 +14286,7 @@
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B668" s="1" t="s">
         <v>0</v>
@@ -14303,7 +14303,7 @@
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B669" s="1" t="s">
         <v>0</v>
@@ -14320,7 +14320,7 @@
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B670" s="1" t="s">
         <v>0</v>
@@ -14337,7 +14337,7 @@
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B671" s="1" t="s">
         <v>0</v>
@@ -14354,7 +14354,7 @@
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B672" s="1" t="s">
         <v>9</v>
@@ -14371,7 +14371,7 @@
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B673" s="1" t="s">
         <v>9</v>
@@ -14388,7 +14388,7 @@
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B674" s="1" t="s">
         <v>9</v>
@@ -14405,7 +14405,7 @@
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B675" s="1" t="s">
         <v>0</v>
@@ -14422,7 +14422,7 @@
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B676" s="1" t="s">
         <v>38</v>
@@ -14439,7 +14439,7 @@
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B677" s="1" t="s">
         <v>0</v>
@@ -14456,7 +14456,7 @@
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B678" s="1" t="s">
         <v>38</v>
@@ -14473,7 +14473,7 @@
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B679" s="1" t="s">
         <v>38</v>
@@ -14490,13 +14490,13 @@
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B680" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C680" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D680" s="14">
         <v>235</v>
@@ -14507,13 +14507,13 @@
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B681" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C681" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D681" s="14">
         <v>150</v>
@@ -14524,16 +14524,16 @@
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C682" s="1" t="s">
         <v>354</v>
       </c>
       <c r="D682" s="14">
-        <v>950</v>
+        <v>200</v>
       </c>
       <c r="E682" s="1">
         <v>0</v>
@@ -14541,16 +14541,16 @@
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C683" s="1" t="s">
         <v>354</v>
       </c>
       <c r="D683" s="14">
-        <v>200</v>
+        <v>950</v>
       </c>
       <c r="E683" s="1">
         <v>0</v>
@@ -14558,7 +14558,7 @@
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B684" s="1" t="s">
         <v>0</v>
@@ -14575,7 +14575,7 @@
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B685" s="1" t="s">
         <v>0</v>
@@ -14592,7 +14592,7 @@
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B686" s="1" t="s">
         <v>0</v>
@@ -14609,16 +14609,16 @@
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C687" s="1" t="s">
         <v>357</v>
       </c>
       <c r="D687" s="14">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="E687" s="1">
         <v>0</v>
@@ -14626,16 +14626,16 @@
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C688" s="1" t="s">
         <v>357</v>
       </c>
       <c r="D688" s="14">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="E688" s="1">
         <v>0</v>
@@ -14643,7 +14643,7 @@
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B689" s="1" t="s">
         <v>0</v>
@@ -14660,16 +14660,16 @@
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C690" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D690" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E690" s="1">
         <v>0</v>
@@ -14677,16 +14677,16 @@
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C691" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D691" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E691" s="1">
         <v>0</v>
@@ -14694,16 +14694,16 @@
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C692" s="1" t="s">
         <v>360</v>
       </c>
       <c r="D692" s="14">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="E692" s="1">
         <v>0</v>
@@ -14711,16 +14711,16 @@
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C693" s="1" t="s">
         <v>360</v>
       </c>
       <c r="D693" s="14">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E693" s="1">
         <v>0</v>

--- a/جرد المواد.xlsx
+++ b/جرد المواد.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\InventorySearch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBF7087-BAA1-4C6A-A9DA-5FB859E7A03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24B0354-39FB-4939-95F1-F753F1CDF3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9897150A-1D18-4DC5-83DE-EA3717EE1A52}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="792">
   <si>
     <t>3-ديوان</t>
   </si>
@@ -2299,12 +2299,6 @@
     <t>برميل طرش نص كاوتشوك غاردينا 102 بريمو PRIMO</t>
   </si>
   <si>
-    <t>صندوق 040 ابيض</t>
-  </si>
-  <si>
-    <t>كرسي 040 ابيض</t>
-  </si>
-  <si>
     <t>موتير 4 حصان ليو LEO 2AC300</t>
   </si>
   <si>
@@ -2435,6 +2429,12 @@
   </si>
   <si>
     <t>قسطل تلحيم 32 ملم اخضر تركي B باب ثاني</t>
+  </si>
+  <si>
+    <t>شاسيه صندوق تعليق 8 سم غروهي GROHE 38729000</t>
+  </si>
+  <si>
+    <t>قسطل حديد دلمين 1</t>
   </si>
 </sst>
 </file>
@@ -3055,7 +3055,7 @@
         <v>38</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D7" s="13">
         <v>600</v>
@@ -3106,7 +3106,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D10" s="13">
         <v>500</v>
@@ -3211,7 +3211,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
@@ -3987,13 +3987,13 @@
         <v>565</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D62" s="13">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -4004,13 +4004,13 @@
         <v>565</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D63" s="13">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -4038,13 +4038,13 @@
         <v>565</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>44</v>
       </c>
       <c r="D65" s="13">
-        <v>31</v>
+        <v>200</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
@@ -4055,13 +4055,13 @@
         <v>565</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>44</v>
       </c>
       <c r="D66" s="13">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E66" s="1">
         <v>0</v>
@@ -4208,13 +4208,13 @@
         <v>567</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D75" s="13">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
@@ -4225,13 +4225,13 @@
         <v>567</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D76" s="13">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>399</v>
       </c>
       <c r="D82" s="13">
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="E82" s="1">
         <v>0</v>
@@ -4344,13 +4344,13 @@
         <v>571</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D83" s="13">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="E83" s="1">
         <v>0</v>
@@ -4361,13 +4361,13 @@
         <v>571</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D84" s="13">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="E84" s="1">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         <v>53</v>
       </c>
       <c r="D85" s="13">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="E85" s="1">
         <v>0</v>
@@ -4653,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D101" s="13">
         <v>1</v>
@@ -4755,7 +4755,7 @@
         <v>38</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D107" s="13">
         <v>600</v>
@@ -5160,13 +5160,13 @@
         <v>583</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D131" s="13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -5177,13 +5177,13 @@
         <v>583</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D132" s="13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -5194,13 +5194,13 @@
         <v>583</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>79</v>
       </c>
       <c r="D133" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -5211,13 +5211,13 @@
         <v>583</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>79</v>
       </c>
       <c r="D134" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -5313,13 +5313,13 @@
         <v>583</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C140" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D140" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
@@ -5330,13 +5330,13 @@
         <v>583</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C141" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D141" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E141" s="1">
         <v>0</v>
@@ -5523,7 +5523,7 @@
         <v>93</v>
       </c>
       <c r="D152" s="13">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="E152" s="1">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>96</v>
       </c>
       <c r="D156" s="13">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="E156" s="1">
         <v>0</v>
@@ -5891,13 +5891,13 @@
         <v>590</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C174" s="10" t="s">
         <v>109</v>
       </c>
       <c r="D174" s="13">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E174" s="1">
         <v>0</v>
@@ -5908,13 +5908,13 @@
         <v>590</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C175" s="10" t="s">
         <v>109</v>
       </c>
       <c r="D175" s="13">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E175" s="1">
         <v>0</v>
@@ -5931,7 +5931,7 @@
         <v>110</v>
       </c>
       <c r="D176" s="13">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="E176" s="1">
         <v>0</v>
@@ -5993,13 +5993,13 @@
         <v>590</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C180" s="10" t="s">
         <v>113</v>
       </c>
       <c r="D180" s="13">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="E180" s="1">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>590</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C181" s="10" t="s">
         <v>113</v>
       </c>
       <c r="D181" s="13">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="E181" s="1">
         <v>0</v>
@@ -6078,13 +6078,13 @@
         <v>577</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C185" s="10" t="s">
         <v>691</v>
       </c>
       <c r="D185" s="13">
-        <v>1920</v>
+        <v>400</v>
       </c>
       <c r="E185" s="1">
         <v>0</v>
@@ -6095,13 +6095,13 @@
         <v>577</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>691</v>
+        <v>494</v>
       </c>
       <c r="D186" s="13">
-        <v>400</v>
+        <v>240</v>
       </c>
       <c r="E186" s="1">
         <v>0</v>
@@ -6112,13 +6112,13 @@
         <v>577</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C187" s="10" t="s">
         <v>494</v>
       </c>
       <c r="D187" s="13">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="E187" s="1">
         <v>0</v>
@@ -6129,13 +6129,13 @@
         <v>577</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>494</v>
+        <v>692</v>
       </c>
       <c r="D188" s="13">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
@@ -6146,13 +6146,13 @@
         <v>577</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>692</v>
+        <v>115</v>
       </c>
       <c r="D189" s="13">
-        <v>800</v>
+        <v>960</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
@@ -6166,10 +6166,10 @@
         <v>0</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>115</v>
+        <v>495</v>
       </c>
       <c r="D190" s="13">
-        <v>960</v>
+        <v>600</v>
       </c>
       <c r="E190" s="1">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>577</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C191" s="10" t="s">
         <v>495</v>
       </c>
       <c r="D191" s="13">
-        <v>600</v>
+        <v>4400</v>
       </c>
       <c r="E191" s="1">
         <v>0</v>
@@ -6197,13 +6197,13 @@
         <v>577</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>495</v>
+        <v>693</v>
       </c>
       <c r="D192" s="13">
-        <v>4400</v>
+        <v>2720</v>
       </c>
       <c r="E192" s="1">
         <v>0</v>
@@ -6214,13 +6214,13 @@
         <v>577</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>693</v>
+        <v>116</v>
       </c>
       <c r="D193" s="13">
-        <v>2720</v>
+        <v>84</v>
       </c>
       <c r="E193" s="1">
         <v>0</v>
@@ -6231,13 +6231,13 @@
         <v>577</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>116</v>
+        <v>759</v>
       </c>
       <c r="D194" s="13">
-        <v>84</v>
+        <v>2040</v>
       </c>
       <c r="E194" s="1">
         <v>0</v>
@@ -6248,13 +6248,13 @@
         <v>577</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>761</v>
+        <v>694</v>
       </c>
       <c r="D195" s="13">
-        <v>2040</v>
+        <v>1080</v>
       </c>
       <c r="E195" s="1">
         <v>0</v>
@@ -6262,16 +6262,16 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="10" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>694</v>
+        <v>117</v>
       </c>
       <c r="D196" s="13">
-        <v>1080</v>
+        <v>880</v>
       </c>
       <c r="E196" s="1">
         <v>0</v>
@@ -6279,16 +6279,16 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="10" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D197" s="13">
-        <v>880</v>
+        <v>61</v>
       </c>
       <c r="E197" s="1">
         <v>0</v>
@@ -6296,16 +6296,16 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>118</v>
+        <v>384</v>
       </c>
       <c r="D198" s="13">
-        <v>61</v>
+        <v>490</v>
       </c>
       <c r="E198" s="1">
         <v>0</v>
@@ -6319,10 +6319,10 @@
         <v>38</v>
       </c>
       <c r="C199" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D199" s="13">
-        <v>490</v>
+        <v>60</v>
       </c>
       <c r="E199" s="1">
         <v>0</v>
@@ -6336,10 +6336,10 @@
         <v>38</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D200" s="13">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E200" s="1">
         <v>0</v>
@@ -6353,7 +6353,7 @@
         <v>38</v>
       </c>
       <c r="C201" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D201" s="13">
         <v>20</v>
@@ -6364,16 +6364,16 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="10" t="s">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C202" s="10" t="s">
-        <v>387</v>
+        <v>119</v>
       </c>
       <c r="D202" s="13">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E202" s="1">
         <v>0</v>
@@ -6387,10 +6387,10 @@
         <v>0</v>
       </c>
       <c r="C203" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D203" s="13">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E203" s="1">
         <v>0</v>
@@ -6404,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="C204" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D204" s="13">
         <v>25</v>
@@ -6421,10 +6421,10 @@
         <v>0</v>
       </c>
       <c r="C205" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D205" s="13">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E205" s="1">
         <v>0</v>
@@ -6438,10 +6438,10 @@
         <v>0</v>
       </c>
       <c r="C206" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D206" s="13">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E206" s="1">
         <v>0</v>
@@ -6455,10 +6455,10 @@
         <v>0</v>
       </c>
       <c r="C207" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D207" s="13">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="E207" s="1">
         <v>0</v>
@@ -6466,16 +6466,16 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="10" t="s">
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="B208" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D208" s="13">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="E208" s="1">
         <v>0</v>
@@ -6483,16 +6483,16 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="10" t="s">
-        <v>555</v>
+        <v>596</v>
       </c>
       <c r="B209" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C209" s="10" t="s">
-        <v>125</v>
+        <v>456</v>
       </c>
       <c r="D209" s="13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E209" s="1">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>0</v>
       </c>
       <c r="C210" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D210" s="13">
         <v>10</v>
@@ -6523,10 +6523,10 @@
         <v>0</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D211" s="13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E211" s="1">
         <v>0</v>
@@ -6534,16 +6534,16 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="10" t="s">
-        <v>596</v>
+        <v>545</v>
       </c>
       <c r="B212" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C212" s="10" t="s">
-        <v>458</v>
+        <v>790</v>
       </c>
       <c r="D212" s="13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E212" s="1">
         <v>0</v>
@@ -6710,7 +6710,7 @@
         <v>38</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D222" s="13">
         <v>100</v>
@@ -6727,10 +6727,10 @@
         <v>9</v>
       </c>
       <c r="C223" s="10" t="s">
-        <v>746</v>
+        <v>704</v>
       </c>
       <c r="D223" s="13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E223" s="1">
         <v>0</v>
@@ -6741,13 +6741,13 @@
         <v>558</v>
       </c>
       <c r="B224" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>704</v>
+        <v>132</v>
       </c>
       <c r="D224" s="13">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E224" s="1">
         <v>0</v>
@@ -6761,7 +6761,7 @@
         <v>0</v>
       </c>
       <c r="C225" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D225" s="13">
         <v>1</v>
@@ -6772,16 +6772,16 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B226" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C226" s="10" t="s">
-        <v>133</v>
+        <v>725</v>
       </c>
       <c r="D226" s="13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E226" s="1">
         <v>0</v>
@@ -6792,13 +6792,13 @@
         <v>559</v>
       </c>
       <c r="B227" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C227" s="10" t="s">
-        <v>725</v>
+        <v>480</v>
       </c>
       <c r="D227" s="13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E227" s="1">
         <v>0</v>
@@ -6806,13 +6806,13 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B228" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C228" s="10" t="s">
-        <v>480</v>
+        <v>134</v>
       </c>
       <c r="D228" s="13">
         <v>1</v>
@@ -6823,13 +6823,13 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B229" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C229" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D229" s="13">
         <v>1</v>
@@ -6840,16 +6840,16 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="10" t="s">
-        <v>559</v>
+        <v>599</v>
       </c>
       <c r="B230" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C230" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D230" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E230" s="1">
         <v>0</v>
@@ -6857,16 +6857,16 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="10" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B231" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C231" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D231" s="13">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E231" s="1">
         <v>0</v>
@@ -6874,16 +6874,16 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="10" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B232" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C232" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D232" s="13">
-        <v>40</v>
+        <v>1500</v>
       </c>
       <c r="E232" s="1">
         <v>0</v>
@@ -6897,10 +6897,10 @@
         <v>38</v>
       </c>
       <c r="C233" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D233" s="13">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="E233" s="1">
         <v>0</v>
@@ -6908,16 +6908,16 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="10" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B234" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C234" s="10" t="s">
-        <v>139</v>
+        <v>406</v>
       </c>
       <c r="D234" s="13">
-        <v>1350</v>
+        <v>15</v>
       </c>
       <c r="E234" s="1">
         <v>0</v>
@@ -6925,16 +6925,16 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="10" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B235" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C235" s="10" t="s">
-        <v>406</v>
+        <v>140</v>
       </c>
       <c r="D235" s="13">
-        <v>15</v>
+        <v>410</v>
       </c>
       <c r="E235" s="1">
         <v>0</v>
@@ -6948,10 +6948,10 @@
         <v>0</v>
       </c>
       <c r="C236" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D236" s="13">
-        <v>410</v>
+        <v>64</v>
       </c>
       <c r="E236" s="1">
         <v>0</v>
@@ -6959,16 +6959,16 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>603</v>
+        <v>560</v>
       </c>
       <c r="B237" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C237" s="10" t="s">
-        <v>141</v>
+        <v>747</v>
       </c>
       <c r="D237" s="13">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="E237" s="1">
         <v>0</v>
@@ -6982,7 +6982,7 @@
         <v>0</v>
       </c>
       <c r="C238" s="10" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D238" s="13">
         <v>10</v>
@@ -6999,10 +6999,10 @@
         <v>0</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D239" s="13">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E239" s="1">
         <v>0</v>
@@ -7016,10 +7016,10 @@
         <v>0</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>751</v>
+        <v>142</v>
       </c>
       <c r="D240" s="13">
-        <v>15</v>
+        <v>385</v>
       </c>
       <c r="E240" s="1">
         <v>0</v>
@@ -7027,16 +7027,16 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="10" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="B241" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D241" s="13">
-        <v>385</v>
+        <v>15</v>
       </c>
       <c r="E241" s="1">
         <v>0</v>
@@ -7044,16 +7044,16 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="10" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B242" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C242" s="10" t="s">
-        <v>143</v>
+        <v>761</v>
       </c>
       <c r="D242" s="13">
-        <v>15</v>
+        <v>800</v>
       </c>
       <c r="E242" s="1">
         <v>0</v>
@@ -7061,16 +7061,16 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="10" t="s">
-        <v>542</v>
+        <v>650</v>
       </c>
       <c r="B243" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>763</v>
+        <v>718</v>
       </c>
       <c r="D243" s="13">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="E243" s="1">
         <v>0</v>
@@ -7084,10 +7084,10 @@
         <v>38</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D244" s="13">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="E244" s="1">
         <v>0</v>
@@ -7095,16 +7095,16 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="10" t="s">
-        <v>650</v>
+        <v>605</v>
       </c>
       <c r="B245" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C245" s="10" t="s">
-        <v>719</v>
+        <v>144</v>
       </c>
       <c r="D245" s="13">
-        <v>1800</v>
+        <v>75</v>
       </c>
       <c r="E245" s="1">
         <v>0</v>
@@ -7112,16 +7112,16 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="10" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C246" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D246" s="13">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="E246" s="1">
         <v>0</v>
@@ -7149,13 +7149,13 @@
         <v>606</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C248" s="10" t="s">
-        <v>145</v>
+        <v>489</v>
       </c>
       <c r="D248" s="13">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="E248" s="1">
         <v>0</v>
@@ -7163,16 +7163,16 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="10" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C249" s="10" t="s">
-        <v>489</v>
+        <v>737</v>
       </c>
       <c r="D249" s="13">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E249" s="1">
         <v>0</v>
@@ -7186,10 +7186,10 @@
         <v>0</v>
       </c>
       <c r="C250" s="10" t="s">
-        <v>737</v>
+        <v>436</v>
       </c>
       <c r="D250" s="13">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E250" s="1">
         <v>0</v>
@@ -7197,16 +7197,16 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="10" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C251" s="10" t="s">
-        <v>436</v>
+        <v>146</v>
       </c>
       <c r="D251" s="13">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="E251" s="1">
         <v>0</v>
@@ -7214,16 +7214,16 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="10" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C252" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D252" s="13">
-        <v>240</v>
+        <v>520</v>
       </c>
       <c r="E252" s="1">
         <v>0</v>
@@ -7248,16 +7248,16 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B254" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C254" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D254" s="13">
-        <v>520</v>
+        <v>80</v>
       </c>
       <c r="E254" s="1">
         <v>0</v>
@@ -7265,16 +7265,16 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="10" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C255" s="10" t="s">
-        <v>148</v>
+        <v>377</v>
       </c>
       <c r="D255" s="13">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="E255" s="1">
         <v>0</v>
@@ -7282,16 +7282,16 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="10" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C256" s="10" t="s">
-        <v>377</v>
+        <v>149</v>
       </c>
       <c r="D256" s="13">
-        <v>470</v>
+        <v>30</v>
       </c>
       <c r="E256" s="1">
         <v>0</v>
@@ -7299,16 +7299,16 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="10" t="s">
-        <v>608</v>
+        <v>542</v>
       </c>
       <c r="B257" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C257" s="10" t="s">
-        <v>149</v>
+        <v>750</v>
       </c>
       <c r="D257" s="13">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E257" s="1">
         <v>0</v>
@@ -7316,16 +7316,16 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="10" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="B258" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C258" s="10" t="s">
-        <v>752</v>
+        <v>150</v>
       </c>
       <c r="D258" s="13">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="E258" s="1">
         <v>0</v>
@@ -7339,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="C259" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D259" s="13">
         <v>1</v>
@@ -7356,10 +7356,10 @@
         <v>0</v>
       </c>
       <c r="C260" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D260" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E260" s="1">
         <v>0</v>
@@ -7373,10 +7373,10 @@
         <v>0</v>
       </c>
       <c r="C261" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D261" s="13">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E261" s="1">
         <v>0</v>
@@ -7390,10 +7390,10 @@
         <v>0</v>
       </c>
       <c r="C262" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D262" s="13">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E262" s="1">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="C263" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D263" s="13">
         <v>7</v>
@@ -7418,16 +7418,16 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B264" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C264" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D264" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E264" s="1">
         <v>0</v>
@@ -7435,16 +7435,16 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="10" t="s">
-        <v>559</v>
+        <v>609</v>
       </c>
       <c r="B265" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C265" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D265" s="13">
-        <v>1</v>
+        <v>249</v>
       </c>
       <c r="E265" s="1">
         <v>0</v>
@@ -7458,10 +7458,10 @@
         <v>0</v>
       </c>
       <c r="C266" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D266" s="13">
-        <v>249</v>
+        <v>111</v>
       </c>
       <c r="E266" s="1">
         <v>0</v>
@@ -7475,10 +7475,10 @@
         <v>0</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>158</v>
+        <v>482</v>
       </c>
       <c r="D267" s="13">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="E267" s="1">
         <v>0</v>
@@ -7486,16 +7486,16 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="10" t="s">
-        <v>609</v>
+        <v>560</v>
       </c>
       <c r="B268" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C268" s="10" t="s">
-        <v>482</v>
+        <v>159</v>
       </c>
       <c r="D268" s="13">
-        <v>28</v>
+        <v>307</v>
       </c>
       <c r="E268" s="1">
         <v>0</v>
@@ -7509,10 +7509,10 @@
         <v>0</v>
       </c>
       <c r="C269" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D269" s="13">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="E269" s="1">
         <v>0</v>
@@ -7520,16 +7520,16 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="10" t="s">
-        <v>560</v>
+        <v>610</v>
       </c>
       <c r="B270" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C270" s="10" t="s">
-        <v>160</v>
+        <v>472</v>
       </c>
       <c r="D270" s="13">
-        <v>300</v>
+        <v>12</v>
       </c>
       <c r="E270" s="1">
         <v>0</v>
@@ -7543,10 +7543,10 @@
         <v>9</v>
       </c>
       <c r="C271" s="10" t="s">
-        <v>472</v>
+        <v>161</v>
       </c>
       <c r="D271" s="13">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E271" s="1">
         <v>0</v>
@@ -7560,10 +7560,10 @@
         <v>9</v>
       </c>
       <c r="C272" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D272" s="13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E272" s="1">
         <v>0</v>
@@ -7577,10 +7577,10 @@
         <v>9</v>
       </c>
       <c r="C273" s="10" t="s">
-        <v>162</v>
+        <v>727</v>
       </c>
       <c r="D273" s="13">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E273" s="1">
         <v>0</v>
@@ -7591,13 +7591,13 @@
         <v>610</v>
       </c>
       <c r="B274" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C274" s="10" t="s">
-        <v>727</v>
+        <v>163</v>
       </c>
       <c r="D274" s="13">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="E274" s="1">
         <v>0</v>
@@ -7611,10 +7611,10 @@
         <v>0</v>
       </c>
       <c r="C275" s="10" t="s">
-        <v>163</v>
+        <v>473</v>
       </c>
       <c r="D275" s="13">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E275" s="1">
         <v>0</v>
@@ -7628,10 +7628,10 @@
         <v>0</v>
       </c>
       <c r="C276" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D276" s="13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E276" s="1">
         <v>0</v>
@@ -7645,10 +7645,10 @@
         <v>0</v>
       </c>
       <c r="C277" s="10" t="s">
-        <v>474</v>
+        <v>164</v>
       </c>
       <c r="D277" s="13">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E277" s="1">
         <v>0</v>
@@ -7662,10 +7662,10 @@
         <v>0</v>
       </c>
       <c r="C278" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D278" s="13">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E278" s="1">
         <v>0</v>
@@ -7673,16 +7673,16 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="10" t="s">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="B279" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C279" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D279" s="13">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="E279" s="1">
         <v>0</v>
@@ -7696,10 +7696,10 @@
         <v>0</v>
       </c>
       <c r="C280" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D280" s="13">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="E280" s="1">
         <v>0</v>
@@ -7713,10 +7713,10 @@
         <v>0</v>
       </c>
       <c r="C281" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D281" s="13">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E281" s="1">
         <v>0</v>
@@ -7724,16 +7724,16 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="10" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B282" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C282" s="10" t="s">
-        <v>168</v>
+        <v>477</v>
       </c>
       <c r="D282" s="13">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="E282" s="1">
         <v>0</v>
@@ -7747,10 +7747,10 @@
         <v>0</v>
       </c>
       <c r="C283" s="10" t="s">
-        <v>477</v>
+        <v>169</v>
       </c>
       <c r="D283" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E283" s="1">
         <v>0</v>
@@ -7758,13 +7758,13 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>581</v>
+        <v>611</v>
       </c>
       <c r="B284" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C284" s="10" t="s">
-        <v>169</v>
+        <v>493</v>
       </c>
       <c r="D284" s="13">
         <v>1</v>
@@ -7781,10 +7781,10 @@
         <v>0</v>
       </c>
       <c r="C285" s="10" t="s">
-        <v>493</v>
+        <v>170</v>
       </c>
       <c r="D285" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E285" s="1">
         <v>0</v>
@@ -7798,7 +7798,7 @@
         <v>0</v>
       </c>
       <c r="C286" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D286" s="13">
         <v>2</v>
@@ -7809,16 +7809,16 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="10" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B287" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C287" s="10" t="s">
-        <v>171</v>
+        <v>779</v>
       </c>
       <c r="D287" s="13">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E287" s="1">
         <v>0</v>
@@ -7832,10 +7832,10 @@
         <v>0</v>
       </c>
       <c r="C288" s="10" t="s">
-        <v>781</v>
+        <v>732</v>
       </c>
       <c r="D288" s="13">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E288" s="1">
         <v>0</v>
@@ -7849,7 +7849,7 @@
         <v>0</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>732</v>
+        <v>507</v>
       </c>
       <c r="D289" s="13">
         <v>1</v>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="C290" s="10" t="s">
-        <v>507</v>
+        <v>733</v>
       </c>
       <c r="D290" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E290" s="1">
         <v>0</v>
@@ -7877,16 +7877,16 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="10" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B291" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C291" s="10" t="s">
-        <v>733</v>
+        <v>486</v>
       </c>
       <c r="D291" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E291" s="1">
         <v>0</v>
@@ -7900,7 +7900,7 @@
         <v>0</v>
       </c>
       <c r="C292" s="10" t="s">
-        <v>486</v>
+        <v>172</v>
       </c>
       <c r="D292" s="13">
         <v>1</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="C293" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D293" s="13">
         <v>1</v>
@@ -7934,7 +7934,7 @@
         <v>0</v>
       </c>
       <c r="C294" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D294" s="13">
         <v>1</v>
@@ -7951,7 +7951,7 @@
         <v>0</v>
       </c>
       <c r="C295" s="10" t="s">
-        <v>174</v>
+        <v>490</v>
       </c>
       <c r="D295" s="13">
         <v>1</v>
@@ -7962,16 +7962,16 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B296" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>490</v>
+        <v>175</v>
       </c>
       <c r="D296" s="13">
-        <v>1</v>
+        <v>1025</v>
       </c>
       <c r="E296" s="1">
         <v>0</v>
@@ -7982,13 +7982,13 @@
         <v>613</v>
       </c>
       <c r="B297" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C297" s="10" t="s">
-        <v>175</v>
+        <v>502</v>
       </c>
       <c r="D297" s="13">
-        <v>1025</v>
+        <v>165</v>
       </c>
       <c r="E297" s="1">
         <v>0</v>
@@ -8002,10 +8002,10 @@
         <v>0</v>
       </c>
       <c r="C298" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D298" s="13">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="E298" s="1">
         <v>0</v>
@@ -8016,13 +8016,13 @@
         <v>613</v>
       </c>
       <c r="B299" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C299" s="10" t="s">
-        <v>503</v>
+        <v>176</v>
       </c>
       <c r="D299" s="13">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="E299" s="1">
         <v>0</v>
@@ -8036,10 +8036,10 @@
         <v>38</v>
       </c>
       <c r="C300" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D300" s="13">
-        <v>270</v>
+        <v>115</v>
       </c>
       <c r="E300" s="1">
         <v>0</v>
@@ -8047,16 +8047,16 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="10" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B301" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C301" s="10" t="s">
-        <v>177</v>
+        <v>509</v>
       </c>
       <c r="D301" s="13">
-        <v>115</v>
+        <v>14</v>
       </c>
       <c r="E301" s="1">
         <v>0</v>
@@ -8070,10 +8070,10 @@
         <v>9</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D302" s="13">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E302" s="1">
         <v>0</v>
@@ -8084,13 +8084,13 @@
         <v>614</v>
       </c>
       <c r="B303" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C303" s="10" t="s">
-        <v>505</v>
+        <v>178</v>
       </c>
       <c r="D303" s="13">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E303" s="1">
         <v>0</v>
@@ -8101,13 +8101,13 @@
         <v>614</v>
       </c>
       <c r="B304" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C304" s="10" t="s">
-        <v>178</v>
+        <v>510</v>
       </c>
       <c r="D304" s="13">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E304" s="1">
         <v>0</v>
@@ -8115,16 +8115,16 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="10" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B305" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C305" s="10" t="s">
-        <v>510</v>
+        <v>670</v>
       </c>
       <c r="D305" s="13">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="E305" s="1">
         <v>0</v>
@@ -8132,16 +8132,16 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="10" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B306" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C306" s="10" t="s">
-        <v>670</v>
+        <v>437</v>
       </c>
       <c r="D306" s="13">
-        <v>250</v>
+        <v>39</v>
       </c>
       <c r="E306" s="1">
         <v>0</v>
@@ -8149,16 +8149,16 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B307" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C307" s="10" t="s">
-        <v>437</v>
+        <v>179</v>
       </c>
       <c r="D307" s="13">
-        <v>39</v>
+        <v>400</v>
       </c>
       <c r="E307" s="1">
         <v>0</v>
@@ -8169,13 +8169,13 @@
         <v>616</v>
       </c>
       <c r="B308" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C308" s="10" t="s">
         <v>179</v>
       </c>
       <c r="D308" s="13">
-        <v>400</v>
+        <v>650</v>
       </c>
       <c r="E308" s="1">
         <v>0</v>
@@ -8183,16 +8183,16 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="10" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B309" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C309" s="10" t="s">
-        <v>179</v>
+        <v>366</v>
       </c>
       <c r="D309" s="13">
-        <v>650</v>
+        <v>235</v>
       </c>
       <c r="E309" s="1">
         <v>0</v>
@@ -8200,16 +8200,16 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="10" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C310" s="10" t="s">
-        <v>366</v>
+        <v>738</v>
       </c>
       <c r="D310" s="13">
-        <v>235</v>
+        <v>75</v>
       </c>
       <c r="E310" s="1">
         <v>0</v>
@@ -8217,16 +8217,16 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B311" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C311" s="10" t="s">
-        <v>738</v>
+        <v>370</v>
       </c>
       <c r="D311" s="13">
-        <v>75</v>
+        <v>1440</v>
       </c>
       <c r="E311" s="1">
         <v>0</v>
@@ -8234,16 +8234,16 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="10" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B312" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C312" s="10" t="s">
-        <v>370</v>
+        <v>180</v>
       </c>
       <c r="D312" s="13">
-        <v>1500</v>
+        <v>102</v>
       </c>
       <c r="E312" s="1">
         <v>0</v>
@@ -8271,13 +8271,13 @@
         <v>613</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C314" s="10" t="s">
         <v>180</v>
       </c>
       <c r="D314" s="13">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="E314" s="1">
         <v>0</v>
@@ -8285,16 +8285,16 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="10" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C315" s="10" t="s">
-        <v>180</v>
+        <v>739</v>
       </c>
       <c r="D315" s="13">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="E315" s="1">
         <v>0</v>
@@ -8302,16 +8302,16 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C316" s="10" t="s">
-        <v>739</v>
+        <v>789</v>
       </c>
       <c r="D316" s="13">
-        <v>20</v>
+        <v>990</v>
       </c>
       <c r="E316" s="1">
         <v>0</v>
@@ -8325,10 +8325,10 @@
         <v>9</v>
       </c>
       <c r="C317" s="10" t="s">
-        <v>791</v>
+        <v>741</v>
       </c>
       <c r="D317" s="13">
-        <v>990</v>
+        <v>450</v>
       </c>
       <c r="E317" s="1">
         <v>0</v>
@@ -8336,16 +8336,16 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="10" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B318" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C318" s="10" t="s">
-        <v>741</v>
+        <v>388</v>
       </c>
       <c r="D318" s="13">
-        <v>450</v>
+        <v>110</v>
       </c>
       <c r="E318" s="1">
         <v>0</v>
@@ -8353,16 +8353,16 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="10" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B319" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C319" s="10" t="s">
-        <v>388</v>
+        <v>438</v>
       </c>
       <c r="D319" s="13">
-        <v>260</v>
+        <v>98</v>
       </c>
       <c r="E319" s="1">
         <v>0</v>
@@ -8370,16 +8370,16 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B320" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C320" s="10" t="s">
-        <v>438</v>
+        <v>181</v>
       </c>
       <c r="D320" s="13">
-        <v>98</v>
+        <v>310</v>
       </c>
       <c r="E320" s="1">
         <v>0</v>
@@ -8387,16 +8387,16 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="10" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B321" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C321" s="10" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="D321" s="13">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="E321" s="1">
         <v>0</v>
@@ -8404,16 +8404,16 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="10" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B322" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C322" s="10" t="s">
-        <v>389</v>
+        <v>439</v>
       </c>
       <c r="D322" s="13">
-        <v>350</v>
+        <v>8</v>
       </c>
       <c r="E322" s="1">
         <v>0</v>
@@ -8421,16 +8421,16 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B323" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C323" s="10" t="s">
-        <v>439</v>
+        <v>182</v>
       </c>
       <c r="D323" s="13">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E323" s="1">
         <v>0</v>
@@ -8447,7 +8447,7 @@
         <v>182</v>
       </c>
       <c r="D324" s="13">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E324" s="1">
         <v>0</v>
@@ -8455,16 +8455,16 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="10" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C325" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D325" s="13">
-        <v>4</v>
+        <v>1150</v>
       </c>
       <c r="E325" s="1">
         <v>0</v>
@@ -8478,10 +8478,10 @@
         <v>38</v>
       </c>
       <c r="C326" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D326" s="13">
-        <v>1150</v>
+        <v>210</v>
       </c>
       <c r="E326" s="1">
         <v>0</v>
@@ -8489,16 +8489,16 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="10" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B327" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C327" s="10" t="s">
-        <v>184</v>
+        <v>470</v>
       </c>
       <c r="D327" s="13">
-        <v>210</v>
+        <v>17</v>
       </c>
       <c r="E327" s="1">
         <v>0</v>
@@ -8512,10 +8512,10 @@
         <v>9</v>
       </c>
       <c r="C328" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D328" s="13">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E328" s="1">
         <v>0</v>
@@ -8523,16 +8523,16 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="10" t="s">
-        <v>619</v>
+        <v>695</v>
       </c>
       <c r="B329" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C329" s="10" t="s">
-        <v>471</v>
+        <v>791</v>
       </c>
       <c r="D329" s="13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E329" s="1">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>381</v>
       </c>
       <c r="D335" s="13">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="E335" s="1">
         <v>0</v>
@@ -9121,13 +9121,13 @@
         <v>558</v>
       </c>
       <c r="B364" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C364" s="10" t="s">
-        <v>747</v>
+        <v>201</v>
       </c>
       <c r="D364" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E364" s="1">
         <v>0</v>
@@ -9138,13 +9138,13 @@
         <v>558</v>
       </c>
       <c r="B365" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C365" s="10" t="s">
-        <v>201</v>
+        <v>707</v>
       </c>
       <c r="D365" s="13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E365" s="1">
         <v>0</v>
@@ -9155,13 +9155,13 @@
         <v>558</v>
       </c>
       <c r="B366" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C366" s="10" t="s">
-        <v>707</v>
+        <v>202</v>
       </c>
       <c r="D366" s="13">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E366" s="1">
         <v>0</v>
@@ -9169,16 +9169,16 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B367" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C367" s="10" t="s">
-        <v>202</v>
+        <v>726</v>
       </c>
       <c r="D367" s="13">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E367" s="1">
         <v>0</v>
@@ -9186,16 +9186,16 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B368" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C368" s="10" t="s">
-        <v>726</v>
+        <v>776</v>
       </c>
       <c r="D368" s="13">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E368" s="1">
         <v>0</v>
@@ -9209,10 +9209,10 @@
         <v>0</v>
       </c>
       <c r="C369" s="10" t="s">
-        <v>778</v>
+        <v>203</v>
       </c>
       <c r="D369" s="13">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E369" s="1">
         <v>0</v>
@@ -9226,7 +9226,7 @@
         <v>0</v>
       </c>
       <c r="C370" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D370" s="13">
         <v>10</v>
@@ -9240,13 +9240,13 @@
         <v>558</v>
       </c>
       <c r="B371" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C371" s="10" t="s">
-        <v>204</v>
+        <v>496</v>
       </c>
       <c r="D371" s="13">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E371" s="1">
         <v>0</v>
@@ -9257,13 +9257,13 @@
         <v>558</v>
       </c>
       <c r="B372" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C372" s="10" t="s">
-        <v>496</v>
+        <v>205</v>
       </c>
       <c r="D372" s="13">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E372" s="1">
         <v>0</v>
@@ -9277,7 +9277,7 @@
         <v>0</v>
       </c>
       <c r="C373" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D373" s="13">
         <v>1</v>
@@ -9288,13 +9288,13 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B374" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C374" s="10" t="s">
-        <v>206</v>
+        <v>481</v>
       </c>
       <c r="D374" s="13">
         <v>1</v>
@@ -9305,13 +9305,13 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B375" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C375" s="10" t="s">
-        <v>481</v>
+        <v>207</v>
       </c>
       <c r="D375" s="13">
         <v>1</v>
@@ -9328,7 +9328,7 @@
         <v>0</v>
       </c>
       <c r="C376" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D376" s="13">
         <v>1</v>
@@ -9339,16 +9339,16 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="10" t="s">
-        <v>558</v>
+        <v>626</v>
       </c>
       <c r="B377" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C377" s="10" t="s">
-        <v>208</v>
+        <v>393</v>
       </c>
       <c r="D377" s="13">
-        <v>1</v>
+        <v>1800</v>
       </c>
       <c r="E377" s="1">
         <v>0</v>
@@ -9362,10 +9362,10 @@
         <v>38</v>
       </c>
       <c r="C378" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D378" s="13">
-        <v>1800</v>
+        <v>2700</v>
       </c>
       <c r="E378" s="1">
         <v>0</v>
@@ -9379,10 +9379,10 @@
         <v>38</v>
       </c>
       <c r="C379" s="10" t="s">
-        <v>394</v>
+        <v>209</v>
       </c>
       <c r="D379" s="13">
-        <v>2700</v>
+        <v>900</v>
       </c>
       <c r="E379" s="1">
         <v>0</v>
@@ -9396,7 +9396,7 @@
         <v>38</v>
       </c>
       <c r="C380" s="10" t="s">
-        <v>209</v>
+        <v>395</v>
       </c>
       <c r="D380" s="13">
         <v>900</v>
@@ -9413,10 +9413,10 @@
         <v>38</v>
       </c>
       <c r="C381" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D381" s="13">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="E381" s="1">
         <v>0</v>
@@ -9424,16 +9424,16 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="10" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B382" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C382" s="10" t="s">
-        <v>396</v>
+        <v>210</v>
       </c>
       <c r="D382" s="13">
-        <v>1200</v>
+        <v>40</v>
       </c>
       <c r="E382" s="1">
         <v>0</v>
@@ -9441,16 +9441,16 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="10" t="s">
-        <v>627</v>
+        <v>544</v>
       </c>
       <c r="B383" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C383" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D383" s="13">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E383" s="1">
         <v>0</v>
@@ -9458,16 +9458,16 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B384" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C384" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D384" s="13">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="E384" s="1">
         <v>0</v>
@@ -9475,16 +9475,16 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="10" t="s">
-        <v>543</v>
+        <v>628</v>
       </c>
       <c r="B385" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C385" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D385" s="13">
-        <v>36</v>
+        <v>240</v>
       </c>
       <c r="E385" s="1">
         <v>0</v>
@@ -9492,16 +9492,16 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="10" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B386" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C386" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D386" s="13">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="E386" s="1">
         <v>0</v>
@@ -9509,16 +9509,16 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B387" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C387" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D387" s="13">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="E387" s="1">
         <v>0</v>
@@ -9526,16 +9526,16 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="10" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B388" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C388" s="10" t="s">
-        <v>215</v>
+        <v>440</v>
       </c>
       <c r="D388" s="13">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="E388" s="1">
         <v>0</v>
@@ -9543,16 +9543,16 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B389" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C389" s="10" t="s">
-        <v>440</v>
+        <v>216</v>
       </c>
       <c r="D389" s="13">
-        <v>159</v>
+        <v>360</v>
       </c>
       <c r="E389" s="1">
         <v>0</v>
@@ -9563,13 +9563,13 @@
         <v>629</v>
       </c>
       <c r="B390" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C390" s="10" t="s">
         <v>216</v>
       </c>
       <c r="D390" s="13">
-        <v>360</v>
+        <v>2550</v>
       </c>
       <c r="E390" s="1">
         <v>0</v>
@@ -9597,13 +9597,13 @@
         <v>629</v>
       </c>
       <c r="B392" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C392" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D392" s="13">
-        <v>2550</v>
+        <v>120</v>
       </c>
       <c r="E392" s="1">
         <v>0</v>
@@ -9614,13 +9614,13 @@
         <v>629</v>
       </c>
       <c r="B393" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C393" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D393" s="13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E393" s="1">
         <v>0</v>
@@ -9631,13 +9631,13 @@
         <v>629</v>
       </c>
       <c r="B394" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C394" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D394" s="13">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E394" s="1">
         <v>0</v>
@@ -9645,16 +9645,16 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" s="10" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B395" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C395" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D395" s="13">
-        <v>300</v>
+        <v>56</v>
       </c>
       <c r="E395" s="1">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="C396" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D396" s="13">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="E396" s="1">
         <v>0</v>
@@ -9685,10 +9685,10 @@
         <v>0</v>
       </c>
       <c r="C397" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D397" s="13">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E397" s="1">
         <v>0</v>
@@ -9696,16 +9696,16 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="10" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B398" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C398" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D398" s="13">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="E398" s="1">
         <v>0</v>
@@ -9719,10 +9719,10 @@
         <v>0</v>
       </c>
       <c r="C399" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D399" s="13">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="E399" s="1">
         <v>0</v>
@@ -9736,10 +9736,10 @@
         <v>0</v>
       </c>
       <c r="C400" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D400" s="13">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E400" s="1">
         <v>0</v>
@@ -9747,16 +9747,16 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="10" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B401" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C401" s="10" t="s">
-        <v>225</v>
+        <v>459</v>
       </c>
       <c r="D401" s="13">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E401" s="1">
         <v>0</v>
@@ -9770,10 +9770,10 @@
         <v>0</v>
       </c>
       <c r="C402" s="10" t="s">
-        <v>459</v>
+        <v>226</v>
       </c>
       <c r="D402" s="13">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E402" s="1">
         <v>0</v>
@@ -9787,10 +9787,10 @@
         <v>0</v>
       </c>
       <c r="C403" s="10" t="s">
-        <v>226</v>
+        <v>460</v>
       </c>
       <c r="D403" s="13">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="E403" s="1">
         <v>0</v>
@@ -9798,16 +9798,16 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="10" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B404" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C404" s="10" t="s">
-        <v>460</v>
+        <v>227</v>
       </c>
       <c r="D404" s="13">
-        <v>29</v>
+        <v>210</v>
       </c>
       <c r="E404" s="1">
         <v>0</v>
@@ -9821,10 +9821,10 @@
         <v>9</v>
       </c>
       <c r="C405" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D405" s="13">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="E405" s="1">
         <v>0</v>
@@ -9855,10 +9855,10 @@
         <v>9</v>
       </c>
       <c r="C407" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D407" s="13">
-        <v>316</v>
+        <v>110</v>
       </c>
       <c r="E407" s="1">
         <v>0</v>
@@ -9872,10 +9872,10 @@
         <v>9</v>
       </c>
       <c r="C408" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D408" s="13">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="E408" s="1">
         <v>0</v>
@@ -9886,13 +9886,13 @@
         <v>634</v>
       </c>
       <c r="B409" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C409" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D409" s="13">
-        <v>6</v>
+        <v>129</v>
       </c>
       <c r="E409" s="1">
         <v>0</v>
@@ -9903,13 +9903,13 @@
         <v>634</v>
       </c>
       <c r="B410" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C410" s="10" t="s">
         <v>231</v>
       </c>
       <c r="D410" s="13">
-        <v>129</v>
+        <v>1200</v>
       </c>
       <c r="E410" s="1">
         <v>0</v>
@@ -9917,16 +9917,16 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="10" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B411" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C411" s="10" t="s">
-        <v>231</v>
+        <v>401</v>
       </c>
       <c r="D411" s="13">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="E411" s="1">
         <v>0</v>
@@ -9934,16 +9934,16 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="10" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B412" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C412" s="10" t="s">
-        <v>401</v>
+        <v>441</v>
       </c>
       <c r="D412" s="13">
-        <v>400</v>
+        <v>75</v>
       </c>
       <c r="E412" s="1">
         <v>0</v>
@@ -9951,16 +9951,16 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="10" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B413" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C413" s="10" t="s">
-        <v>441</v>
+        <v>371</v>
       </c>
       <c r="D413" s="13">
-        <v>75</v>
+        <v>1200</v>
       </c>
       <c r="E413" s="1">
         <v>0</v>
@@ -9968,13 +9968,13 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B414" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C414" s="10" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D414" s="13">
         <v>1200</v>
@@ -9985,16 +9985,16 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="10" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B415" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>402</v>
+        <v>708</v>
       </c>
       <c r="D415" s="13">
-        <v>1200</v>
+        <v>290</v>
       </c>
       <c r="E415" s="1">
         <v>0</v>
@@ -10002,16 +10002,16 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="10" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B416" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C416" s="10" t="s">
-        <v>708</v>
+        <v>372</v>
       </c>
       <c r="D416" s="13">
-        <v>290</v>
+        <v>26100</v>
       </c>
       <c r="E416" s="1">
         <v>0</v>
@@ -10019,16 +10019,16 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B417" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C417" s="10" t="s">
-        <v>372</v>
+        <v>442</v>
       </c>
       <c r="D417" s="13">
-        <v>26500</v>
+        <v>80</v>
       </c>
       <c r="E417" s="1">
         <v>0</v>
@@ -10036,16 +10036,16 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="10" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B418" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C418" s="10" t="s">
-        <v>442</v>
+        <v>232</v>
       </c>
       <c r="D418" s="13">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="E418" s="1">
         <v>0</v>
@@ -10056,13 +10056,13 @@
         <v>637</v>
       </c>
       <c r="B419" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C419" s="10" t="s">
         <v>232</v>
       </c>
       <c r="D419" s="13">
-        <v>300</v>
+        <v>1525</v>
       </c>
       <c r="E419" s="1">
         <v>0</v>
@@ -10070,16 +10070,16 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B420" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C420" s="10" t="s">
-        <v>232</v>
+        <v>443</v>
       </c>
       <c r="D420" s="13">
-        <v>1525</v>
+        <v>70</v>
       </c>
       <c r="E420" s="1">
         <v>0</v>
@@ -10087,16 +10087,16 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="10" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B421" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C421" s="10" t="s">
-        <v>443</v>
+        <v>233</v>
       </c>
       <c r="D421" s="13">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="E421" s="1">
         <v>0</v>
@@ -10107,13 +10107,13 @@
         <v>637</v>
       </c>
       <c r="B422" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C422" s="10" t="s">
         <v>233</v>
       </c>
       <c r="D422" s="13">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="E422" s="1">
         <v>0</v>
@@ -10124,13 +10124,13 @@
         <v>637</v>
       </c>
       <c r="B423" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C423" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D423" s="13">
-        <v>360</v>
+        <v>72</v>
       </c>
       <c r="E423" s="1">
         <v>0</v>
@@ -10138,16 +10138,16 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="10" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B424" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C424" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D424" s="13">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="E424" s="1">
         <v>0</v>
@@ -10155,16 +10155,16 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="10" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B425" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C425" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D425" s="13">
-        <v>600</v>
+        <v>97</v>
       </c>
       <c r="E425" s="1">
         <v>0</v>
@@ -10172,16 +10172,16 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="10" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B426" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C426" s="10" t="s">
-        <v>236</v>
+        <v>461</v>
       </c>
       <c r="D426" s="13">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="E426" s="1">
         <v>0</v>
@@ -10195,10 +10195,10 @@
         <v>0</v>
       </c>
       <c r="C427" s="10" t="s">
-        <v>461</v>
+        <v>367</v>
       </c>
       <c r="D427" s="13">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E427" s="1">
         <v>0</v>
@@ -10212,10 +10212,10 @@
         <v>0</v>
       </c>
       <c r="C428" s="10" t="s">
-        <v>367</v>
+        <v>488</v>
       </c>
       <c r="D428" s="13">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E428" s="1">
         <v>0</v>
@@ -10229,10 +10229,10 @@
         <v>0</v>
       </c>
       <c r="C429" s="10" t="s">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="D429" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E429" s="1">
         <v>0</v>
@@ -10240,16 +10240,16 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" s="10" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B430" s="10" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C430" s="10" t="s">
-        <v>462</v>
+        <v>237</v>
       </c>
       <c r="D430" s="13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E430" s="1">
         <v>0</v>
@@ -10263,10 +10263,10 @@
         <v>9</v>
       </c>
       <c r="C431" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D431" s="13">
-        <v>8</v>
+        <v>530</v>
       </c>
       <c r="E431" s="1">
         <v>0</v>
@@ -10274,16 +10274,16 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" s="10" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B432" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C432" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D432" s="13">
-        <v>530</v>
+        <v>400</v>
       </c>
       <c r="E432" s="1">
         <v>0</v>
@@ -10291,16 +10291,16 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="10" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B433" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C433" s="10" t="s">
-        <v>239</v>
+        <v>444</v>
       </c>
       <c r="D433" s="13">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="E433" s="1">
         <v>0</v>
@@ -10308,16 +10308,16 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="10" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B434" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C434" s="10" t="s">
-        <v>444</v>
+        <v>240</v>
       </c>
       <c r="D434" s="13">
-        <v>50</v>
+        <v>1200</v>
       </c>
       <c r="E434" s="1">
         <v>0</v>
@@ -10325,16 +10325,16 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B435" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C435" s="10" t="s">
-        <v>240</v>
+        <v>709</v>
       </c>
       <c r="D435" s="13">
-        <v>1200</v>
+        <v>140</v>
       </c>
       <c r="E435" s="1">
         <v>0</v>
@@ -10348,10 +10348,10 @@
         <v>0</v>
       </c>
       <c r="C436" s="10" t="s">
-        <v>709</v>
+        <v>445</v>
       </c>
       <c r="D436" s="13">
-        <v>140</v>
+        <v>31</v>
       </c>
       <c r="E436" s="1">
         <v>0</v>
@@ -10359,16 +10359,16 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="10" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B437" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C437" s="10" t="s">
-        <v>445</v>
+        <v>241</v>
       </c>
       <c r="D437" s="13">
-        <v>31</v>
+        <v>200</v>
       </c>
       <c r="E437" s="1">
         <v>0</v>
@@ -10393,16 +10393,16 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B439" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C439" s="10" t="s">
-        <v>241</v>
+        <v>710</v>
       </c>
       <c r="D439" s="13">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="E439" s="1">
         <v>0</v>
@@ -10410,16 +10410,16 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="10" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B440" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C440" s="10" t="s">
-        <v>710</v>
+        <v>373</v>
       </c>
       <c r="D440" s="13">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E440" s="1">
         <v>0</v>
@@ -10433,10 +10433,10 @@
         <v>38</v>
       </c>
       <c r="C441" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D441" s="13">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="E441" s="1">
         <v>0</v>
@@ -10450,10 +10450,10 @@
         <v>38</v>
       </c>
       <c r="C442" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D442" s="13">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="E442" s="1">
         <v>0</v>
@@ -10461,16 +10461,16 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="10" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="B443" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C443" s="10" t="s">
-        <v>375</v>
+        <v>242</v>
       </c>
       <c r="D443" s="13">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E443" s="1">
         <v>0</v>
@@ -10478,16 +10478,16 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="10" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="B444" s="10" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C444" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D444" s="13">
-        <v>173</v>
+        <v>24</v>
       </c>
       <c r="E444" s="1">
         <v>0</v>
@@ -10501,10 +10501,10 @@
         <v>0</v>
       </c>
       <c r="C445" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D445" s="13">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E445" s="1">
         <v>0</v>
@@ -10518,10 +10518,10 @@
         <v>0</v>
       </c>
       <c r="C446" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D446" s="13">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E446" s="1">
         <v>0</v>
@@ -10535,10 +10535,10 @@
         <v>0</v>
       </c>
       <c r="C447" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D447" s="13">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E447" s="1">
         <v>0</v>
@@ -10552,10 +10552,10 @@
         <v>0</v>
       </c>
       <c r="C448" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D448" s="13">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E448" s="1">
         <v>0</v>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="C449" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D449" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E449" s="1">
         <v>0</v>
@@ -10586,10 +10586,10 @@
         <v>0</v>
       </c>
       <c r="C450" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D450" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E450" s="1">
         <v>0</v>
@@ -10597,16 +10597,16 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="10" t="s">
-        <v>644</v>
+        <v>585</v>
       </c>
       <c r="B451" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C451" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D451" s="13">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E451" s="1">
         <v>0</v>
@@ -10620,10 +10620,10 @@
         <v>0</v>
       </c>
       <c r="C452" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D452" s="13">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E452" s="1">
         <v>0</v>
@@ -10637,10 +10637,10 @@
         <v>0</v>
       </c>
       <c r="C453" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D453" s="13">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E453" s="1">
         <v>0</v>
@@ -10654,10 +10654,10 @@
         <v>0</v>
       </c>
       <c r="C454" s="10" t="s">
-        <v>252</v>
+        <v>751</v>
       </c>
       <c r="D454" s="13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E454" s="1">
         <v>0</v>
@@ -10671,7 +10671,7 @@
         <v>0</v>
       </c>
       <c r="C455" s="10" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D455" s="13">
         <v>6</v>
@@ -10682,16 +10682,16 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="10" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="B456" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C456" s="10" t="s">
-        <v>754</v>
+        <v>686</v>
       </c>
       <c r="D456" s="13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E456" s="1">
         <v>0</v>
@@ -10699,16 +10699,16 @@
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="10" t="s">
-        <v>576</v>
+        <v>645</v>
       </c>
       <c r="B457" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C457" s="10" t="s">
-        <v>686</v>
+        <v>253</v>
       </c>
       <c r="D457" s="13">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E457" s="1">
         <v>0</v>
@@ -10716,16 +10716,16 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="10" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B458" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C458" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D458" s="13">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E458" s="1">
         <v>0</v>
@@ -10736,13 +10736,13 @@
         <v>646</v>
       </c>
       <c r="B459" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C459" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D459" s="13">
-        <v>47</v>
+        <v>830</v>
       </c>
       <c r="E459" s="1">
         <v>0</v>
@@ -10756,10 +10756,10 @@
         <v>38</v>
       </c>
       <c r="C460" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D460" s="13">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="E460" s="1">
         <v>0</v>
@@ -10773,10 +10773,10 @@
         <v>38</v>
       </c>
       <c r="C461" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D461" s="13">
-        <v>850</v>
+        <v>1250</v>
       </c>
       <c r="E461" s="1">
         <v>0</v>
@@ -10790,10 +10790,10 @@
         <v>38</v>
       </c>
       <c r="C462" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D462" s="13">
-        <v>1250</v>
+        <v>400</v>
       </c>
       <c r="E462" s="1">
         <v>0</v>
@@ -10801,16 +10801,16 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B463" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C463" s="10" t="s">
-        <v>258</v>
+        <v>762</v>
       </c>
       <c r="D463" s="13">
-        <v>400</v>
+        <v>3720</v>
       </c>
       <c r="E463" s="1">
         <v>0</v>
@@ -10824,10 +10824,10 @@
         <v>38</v>
       </c>
       <c r="C464" s="10" t="s">
-        <v>764</v>
+        <v>259</v>
       </c>
       <c r="D464" s="13">
-        <v>3760</v>
+        <v>280</v>
       </c>
       <c r="E464" s="1">
         <v>0</v>
@@ -10838,13 +10838,13 @@
         <v>645</v>
       </c>
       <c r="B465" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C465" s="10" t="s">
         <v>259</v>
       </c>
       <c r="D465" s="13">
-        <v>280</v>
+        <v>779</v>
       </c>
       <c r="E465" s="1">
         <v>0</v>
@@ -10852,16 +10852,16 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="10" t="s">
-        <v>645</v>
+        <v>545</v>
       </c>
       <c r="B466" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C466" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D466" s="13">
-        <v>779</v>
+        <v>273</v>
       </c>
       <c r="E466" s="1">
         <v>0</v>
@@ -10869,16 +10869,16 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="10" t="s">
-        <v>545</v>
+        <v>645</v>
       </c>
       <c r="B467" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C467" s="10" t="s">
-        <v>260</v>
+        <v>763</v>
       </c>
       <c r="D467" s="13">
-        <v>273</v>
+        <v>1592</v>
       </c>
       <c r="E467" s="1">
         <v>0</v>
@@ -10886,16 +10886,16 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="10" t="s">
-        <v>645</v>
+        <v>561</v>
       </c>
       <c r="B468" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C468" s="10" t="s">
-        <v>765</v>
+        <v>261</v>
       </c>
       <c r="D468" s="13">
-        <v>1632</v>
+        <v>3</v>
       </c>
       <c r="E468" s="1">
         <v>0</v>
@@ -10909,10 +10909,10 @@
         <v>0</v>
       </c>
       <c r="C469" s="10" t="s">
-        <v>261</v>
+        <v>499</v>
       </c>
       <c r="D469" s="13">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E469" s="1">
         <v>0</v>
@@ -10920,16 +10920,16 @@
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="10" t="s">
-        <v>561</v>
+        <v>599</v>
       </c>
       <c r="B470" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C470" s="10" t="s">
-        <v>499</v>
+        <v>262</v>
       </c>
       <c r="D470" s="13">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E470" s="1">
         <v>0</v>
@@ -10943,10 +10943,10 @@
         <v>0</v>
       </c>
       <c r="C471" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D471" s="13">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E471" s="1">
         <v>0</v>
@@ -10957,13 +10957,13 @@
         <v>599</v>
       </c>
       <c r="B472" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C472" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D472" s="13">
-        <v>6</v>
+        <v>840</v>
       </c>
       <c r="E472" s="1">
         <v>0</v>
@@ -10977,10 +10977,10 @@
         <v>38</v>
       </c>
       <c r="C473" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D473" s="13">
-        <v>840</v>
+        <v>10</v>
       </c>
       <c r="E473" s="1">
         <v>0</v>
@@ -10994,7 +10994,7 @@
         <v>38</v>
       </c>
       <c r="C474" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D474" s="13">
         <v>10</v>
@@ -11011,10 +11011,10 @@
         <v>38</v>
       </c>
       <c r="C475" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D475" s="13">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="E475" s="1">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>38</v>
       </c>
       <c r="C476" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D476" s="13">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E476" s="1">
         <v>0</v>
@@ -11045,10 +11045,10 @@
         <v>38</v>
       </c>
       <c r="C477" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D477" s="13">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E477" s="1">
         <v>0</v>
@@ -11062,10 +11062,10 @@
         <v>38</v>
       </c>
       <c r="C478" s="10" t="s">
-        <v>269</v>
+        <v>417</v>
       </c>
       <c r="D478" s="13">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E478" s="1">
         <v>0</v>
@@ -11073,16 +11073,16 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" s="10" t="s">
-        <v>599</v>
+        <v>542</v>
       </c>
       <c r="B479" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C479" s="10" t="s">
-        <v>417</v>
+        <v>270</v>
       </c>
       <c r="D479" s="13">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="E479" s="1">
         <v>0</v>
@@ -11090,16 +11090,16 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="10" t="s">
-        <v>542</v>
+        <v>645</v>
       </c>
       <c r="B480" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C480" s="10" t="s">
-        <v>270</v>
+        <v>764</v>
       </c>
       <c r="D480" s="13">
-        <v>75</v>
+        <v>575</v>
       </c>
       <c r="E480" s="1">
         <v>0</v>
@@ -11113,10 +11113,10 @@
         <v>38</v>
       </c>
       <c r="C481" s="10" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D481" s="13">
-        <v>575</v>
+        <v>9375</v>
       </c>
       <c r="E481" s="1">
         <v>0</v>
@@ -11130,10 +11130,10 @@
         <v>38</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D482" s="13">
-        <v>9500</v>
+        <v>575</v>
       </c>
       <c r="E482" s="1">
         <v>0</v>
@@ -11144,13 +11144,13 @@
         <v>645</v>
       </c>
       <c r="B483" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C483" s="10" t="s">
-        <v>768</v>
+        <v>271</v>
       </c>
       <c r="D483" s="13">
-        <v>575</v>
+        <v>40</v>
       </c>
       <c r="E483" s="1">
         <v>0</v>
@@ -11161,13 +11161,13 @@
         <v>645</v>
       </c>
       <c r="B484" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C484" s="10" t="s">
-        <v>271</v>
+        <v>767</v>
       </c>
       <c r="D484" s="13">
-        <v>40</v>
+        <v>5000</v>
       </c>
       <c r="E484" s="1">
         <v>0</v>
@@ -11175,16 +11175,16 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="10" t="s">
-        <v>645</v>
+        <v>544</v>
       </c>
       <c r="B485" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C485" s="10" t="s">
-        <v>769</v>
+        <v>409</v>
       </c>
       <c r="D485" s="13">
-        <v>5000</v>
+        <v>16400</v>
       </c>
       <c r="E485" s="1">
         <v>0</v>
@@ -11192,16 +11192,16 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="10" t="s">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="B486" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C486" s="10" t="s">
-        <v>409</v>
+        <v>272</v>
       </c>
       <c r="D486" s="13">
-        <v>16400</v>
+        <v>1</v>
       </c>
       <c r="E486" s="1">
         <v>0</v>
@@ -11215,10 +11215,10 @@
         <v>0</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D487" s="13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E487" s="1">
         <v>0</v>
@@ -11232,10 +11232,10 @@
         <v>0</v>
       </c>
       <c r="C488" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D488" s="13">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E488" s="1">
         <v>0</v>
@@ -11249,10 +11249,10 @@
         <v>0</v>
       </c>
       <c r="C489" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D489" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E489" s="1">
         <v>0</v>
@@ -11266,7 +11266,7 @@
         <v>0</v>
       </c>
       <c r="C490" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D490" s="13">
         <v>1</v>
@@ -11283,7 +11283,7 @@
         <v>0</v>
       </c>
       <c r="C491" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D491" s="13">
         <v>1</v>
@@ -11300,7 +11300,7 @@
         <v>0</v>
       </c>
       <c r="C492" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D492" s="13">
         <v>1</v>
@@ -11317,10 +11317,10 @@
         <v>0</v>
       </c>
       <c r="C493" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D493" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E493" s="1">
         <v>0</v>
@@ -11334,10 +11334,10 @@
         <v>0</v>
       </c>
       <c r="C494" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D494" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E494" s="1">
         <v>0</v>
@@ -11351,10 +11351,10 @@
         <v>0</v>
       </c>
       <c r="C495" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D495" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E495" s="1">
         <v>0</v>
@@ -11362,16 +11362,16 @@
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B496" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C496" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D496" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E496" s="1">
         <v>0</v>
@@ -11379,16 +11379,16 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B497" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C497" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D497" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E497" s="1">
         <v>0</v>
@@ -11402,10 +11402,10 @@
         <v>0</v>
       </c>
       <c r="C498" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D498" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E498" s="1">
         <v>0</v>
@@ -11413,13 +11413,13 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B499" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C499" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D499" s="13">
         <v>1</v>
@@ -11430,13 +11430,13 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="B500" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C500" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D500" s="13">
         <v>1</v>
@@ -11447,13 +11447,13 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>542</v>
+        <v>604</v>
       </c>
       <c r="B501" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C501" s="10" t="s">
-        <v>286</v>
+        <v>475</v>
       </c>
       <c r="D501" s="13">
         <v>1</v>
@@ -11470,7 +11470,7 @@
         <v>0</v>
       </c>
       <c r="C502" s="10" t="s">
-        <v>475</v>
+        <v>287</v>
       </c>
       <c r="D502" s="13">
         <v>1</v>
@@ -11481,16 +11481,16 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>604</v>
+        <v>542</v>
       </c>
       <c r="B503" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C503" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D503" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E503" s="1">
         <v>0</v>
@@ -11498,16 +11498,16 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B504" s="10" t="s">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="C504" s="10" t="s">
-        <v>288</v>
+        <v>698</v>
       </c>
       <c r="D504" s="13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E504" s="1">
         <v>0</v>
@@ -11521,10 +11521,10 @@
         <v>511</v>
       </c>
       <c r="C505" s="10" t="s">
-        <v>698</v>
+        <v>785</v>
       </c>
       <c r="D505" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E505" s="1">
         <v>0</v>
@@ -11538,10 +11538,10 @@
         <v>511</v>
       </c>
       <c r="C506" s="10" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D506" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E506" s="1">
         <v>0</v>
@@ -11555,7 +11555,7 @@
         <v>511</v>
       </c>
       <c r="C507" s="10" t="s">
-        <v>788</v>
+        <v>512</v>
       </c>
       <c r="D507" s="13">
         <v>3</v>
@@ -11572,10 +11572,10 @@
         <v>511</v>
       </c>
       <c r="C508" s="10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D508" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E508" s="1">
         <v>0</v>
@@ -11583,16 +11583,16 @@
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>548</v>
+        <v>648</v>
       </c>
       <c r="B509" s="10" t="s">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="C509" s="10" t="s">
-        <v>513</v>
+        <v>685</v>
       </c>
       <c r="D509" s="13">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E509" s="1">
         <v>0</v>
@@ -11600,16 +11600,16 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>648</v>
+        <v>548</v>
       </c>
       <c r="B510" s="10" t="s">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="C510" s="10" t="s">
-        <v>685</v>
+        <v>514</v>
       </c>
       <c r="D510" s="13">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E510" s="1">
         <v>0</v>
@@ -11623,7 +11623,7 @@
         <v>511</v>
       </c>
       <c r="C511" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D511" s="13">
         <v>1</v>
@@ -11640,10 +11640,10 @@
         <v>511</v>
       </c>
       <c r="C512" s="10" t="s">
-        <v>515</v>
+        <v>780</v>
       </c>
       <c r="D512" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E512" s="1">
         <v>0</v>
@@ -11657,10 +11657,10 @@
         <v>511</v>
       </c>
       <c r="C513" s="10" t="s">
-        <v>782</v>
+        <v>687</v>
       </c>
       <c r="D513" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E513" s="1">
         <v>0</v>
@@ -11674,7 +11674,7 @@
         <v>511</v>
       </c>
       <c r="C514" s="10" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="D514" s="13">
         <v>2</v>
@@ -11691,10 +11691,10 @@
         <v>511</v>
       </c>
       <c r="C515" s="10" t="s">
-        <v>699</v>
+        <v>516</v>
       </c>
       <c r="D515" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E515" s="1">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>511</v>
       </c>
       <c r="C516" s="10" t="s">
-        <v>516</v>
+        <v>746</v>
       </c>
       <c r="D516" s="13">
         <v>1</v>
@@ -11722,10 +11722,10 @@
         <v>548</v>
       </c>
       <c r="B517" s="10" t="s">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="C517" s="10" t="s">
-        <v>748</v>
+        <v>289</v>
       </c>
       <c r="D517" s="13">
         <v>1</v>
@@ -11736,13 +11736,13 @@
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
-        <v>548</v>
+        <v>648</v>
       </c>
       <c r="B518" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C518" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D518" s="13">
         <v>1</v>
@@ -11759,10 +11759,10 @@
         <v>0</v>
       </c>
       <c r="C519" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D519" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E519" s="1">
         <v>0</v>
@@ -11776,10 +11776,10 @@
         <v>0</v>
       </c>
       <c r="C520" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D520" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E520" s="1">
         <v>0</v>
@@ -11793,7 +11793,7 @@
         <v>0</v>
       </c>
       <c r="C521" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D521" s="13">
         <v>1</v>
@@ -11810,7 +11810,7 @@
         <v>0</v>
       </c>
       <c r="C522" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D522" s="13">
         <v>1</v>
@@ -11827,7 +11827,7 @@
         <v>0</v>
       </c>
       <c r="C523" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D523" s="13">
         <v>1</v>
@@ -11844,10 +11844,10 @@
         <v>0</v>
       </c>
       <c r="C524" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D524" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E524" s="1">
         <v>0</v>
@@ -11855,13 +11855,13 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" s="10" t="s">
-        <v>648</v>
+        <v>548</v>
       </c>
       <c r="B525" s="10" t="s">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="C525" s="10" t="s">
-        <v>296</v>
+        <v>517</v>
       </c>
       <c r="D525" s="13">
         <v>2</v>
@@ -11878,10 +11878,10 @@
         <v>511</v>
       </c>
       <c r="C526" s="10" t="s">
-        <v>517</v>
+        <v>690</v>
       </c>
       <c r="D526" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E526" s="1">
         <v>0</v>
@@ -11895,10 +11895,10 @@
         <v>511</v>
       </c>
       <c r="C527" s="10" t="s">
-        <v>690</v>
+        <v>518</v>
       </c>
       <c r="D527" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E527" s="1">
         <v>0</v>
@@ -11912,10 +11912,10 @@
         <v>511</v>
       </c>
       <c r="C528" s="10" t="s">
-        <v>518</v>
+        <v>684</v>
       </c>
       <c r="D528" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E528" s="1">
         <v>0</v>
@@ -11929,10 +11929,10 @@
         <v>511</v>
       </c>
       <c r="C529" s="10" t="s">
-        <v>684</v>
+        <v>697</v>
       </c>
       <c r="D529" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E529" s="1">
         <v>0</v>
@@ -11946,10 +11946,10 @@
         <v>511</v>
       </c>
       <c r="C530" s="10" t="s">
-        <v>697</v>
+        <v>742</v>
       </c>
       <c r="D530" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E530" s="1">
         <v>0</v>
@@ -11957,16 +11957,16 @@
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" s="10" t="s">
-        <v>548</v>
+        <v>735</v>
       </c>
       <c r="B531" s="10" t="s">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="C531" s="10" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="D531" s="13">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E531" s="1">
         <v>0</v>
@@ -11974,16 +11974,16 @@
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
-        <v>735</v>
+        <v>550</v>
       </c>
       <c r="B532" s="10" t="s">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="C532" s="10" t="s">
-        <v>736</v>
+        <v>688</v>
       </c>
       <c r="D532" s="13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E532" s="1">
         <v>0</v>
@@ -11997,7 +11997,7 @@
         <v>511</v>
       </c>
       <c r="C533" s="10" t="s">
-        <v>688</v>
+        <v>519</v>
       </c>
       <c r="D533" s="13">
         <v>1</v>
@@ -12008,13 +12008,13 @@
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" s="10" t="s">
-        <v>550</v>
+        <v>604</v>
       </c>
       <c r="B534" s="10" t="s">
         <v>511</v>
       </c>
       <c r="C534" s="10" t="s">
-        <v>519</v>
+        <v>728</v>
       </c>
       <c r="D534" s="13">
         <v>1</v>
@@ -12031,10 +12031,10 @@
         <v>511</v>
       </c>
       <c r="C535" s="10" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D535" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E535" s="1">
         <v>0</v>
@@ -12042,16 +12042,16 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="10" t="s">
-        <v>604</v>
+        <v>647</v>
       </c>
       <c r="B536" s="10" t="s">
         <v>511</v>
       </c>
       <c r="C536" s="10" t="s">
-        <v>729</v>
+        <v>520</v>
       </c>
       <c r="D536" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E536" s="1">
         <v>0</v>
@@ -12065,7 +12065,7 @@
         <v>511</v>
       </c>
       <c r="C537" s="10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D537" s="13">
         <v>1</v>
@@ -12076,13 +12076,13 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="10" t="s">
-        <v>647</v>
+        <v>550</v>
       </c>
       <c r="B538" s="10" t="s">
         <v>511</v>
       </c>
       <c r="C538" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D538" s="13">
         <v>1</v>
@@ -12099,10 +12099,10 @@
         <v>511</v>
       </c>
       <c r="C539" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D539" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E539" s="1">
         <v>0</v>
@@ -12116,10 +12116,10 @@
         <v>511</v>
       </c>
       <c r="C540" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D540" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E540" s="1">
         <v>0</v>
@@ -12127,16 +12127,16 @@
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" s="10" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B541" s="10" t="s">
         <v>511</v>
       </c>
       <c r="C541" s="10" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="D541" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E541" s="1">
         <v>0</v>
@@ -12150,10 +12150,10 @@
         <v>511</v>
       </c>
       <c r="C542" s="10" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="D542" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E542" s="1">
         <v>0</v>
@@ -12167,7 +12167,7 @@
         <v>511</v>
       </c>
       <c r="C543" s="10" t="s">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="D543" s="13">
         <v>1</v>
@@ -12184,7 +12184,7 @@
         <v>511</v>
       </c>
       <c r="C544" s="10" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="D544" s="13">
         <v>1</v>
@@ -12195,13 +12195,13 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="10" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B545" s="10" t="s">
         <v>511</v>
       </c>
       <c r="C545" s="10" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D545" s="13">
         <v>1</v>
@@ -12218,7 +12218,7 @@
         <v>511</v>
       </c>
       <c r="C546" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D546" s="13">
         <v>1</v>
@@ -12229,16 +12229,16 @@
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" s="10" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B547" s="10" t="s">
         <v>511</v>
       </c>
       <c r="C547" s="10" t="s">
-        <v>528</v>
+        <v>787</v>
       </c>
       <c r="D547" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E547" s="1">
         <v>0</v>
@@ -12252,10 +12252,10 @@
         <v>511</v>
       </c>
       <c r="C548" s="10" t="s">
-        <v>789</v>
+        <v>540</v>
       </c>
       <c r="D548" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E548" s="1">
         <v>0</v>
@@ -12269,10 +12269,10 @@
         <v>511</v>
       </c>
       <c r="C549" s="10" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="D549" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E549" s="1">
         <v>0</v>
@@ -12286,10 +12286,10 @@
         <v>511</v>
       </c>
       <c r="C550" s="10" t="s">
-        <v>529</v>
+        <v>788</v>
       </c>
       <c r="D550" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E550" s="1">
         <v>0</v>
@@ -12303,10 +12303,10 @@
         <v>511</v>
       </c>
       <c r="C551" s="10" t="s">
-        <v>790</v>
+        <v>530</v>
       </c>
       <c r="D551" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E551" s="1">
         <v>0</v>
@@ -12320,10 +12320,10 @@
         <v>511</v>
       </c>
       <c r="C552" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D552" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E552" s="1">
         <v>0</v>
@@ -12337,10 +12337,10 @@
         <v>511</v>
       </c>
       <c r="C553" s="10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D553" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E553" s="1">
         <v>0</v>
@@ -12354,10 +12354,10 @@
         <v>511</v>
       </c>
       <c r="C554" s="10" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D554" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E554" s="1">
         <v>0</v>
@@ -12365,16 +12365,16 @@
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" s="10" t="s">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="B555" s="10" t="s">
         <v>511</v>
       </c>
       <c r="C555" s="10" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D555" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E555" s="1">
         <v>0</v>
@@ -12382,16 +12382,16 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" s="10" t="s">
-        <v>604</v>
+        <v>648</v>
       </c>
       <c r="B556" s="10" t="s">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="C556" s="10" t="s">
-        <v>534</v>
+        <v>297</v>
       </c>
       <c r="D556" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E556" s="1">
         <v>0</v>
@@ -12399,13 +12399,13 @@
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" s="10" t="s">
-        <v>648</v>
+        <v>548</v>
       </c>
       <c r="B557" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C557" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D557" s="13">
         <v>1</v>
@@ -12422,7 +12422,7 @@
         <v>0</v>
       </c>
       <c r="C558" s="10" t="s">
-        <v>298</v>
+        <v>483</v>
       </c>
       <c r="D558" s="13">
         <v>1</v>
@@ -12436,13 +12436,13 @@
         <v>548</v>
       </c>
       <c r="B559" s="10" t="s">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="C559" s="10" t="s">
-        <v>483</v>
+        <v>299</v>
       </c>
       <c r="D559" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E559" s="1">
         <v>0</v>
@@ -12453,7 +12453,7 @@
         <v>548</v>
       </c>
       <c r="B560" s="10" t="s">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="C560" s="10" t="s">
         <v>299</v>
@@ -12467,13 +12467,13 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" s="10" t="s">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="B561" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C561" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D561" s="13">
         <v>2</v>
@@ -12490,10 +12490,10 @@
         <v>0</v>
       </c>
       <c r="C562" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D562" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E562" s="1">
         <v>0</v>
@@ -12507,7 +12507,7 @@
         <v>0</v>
       </c>
       <c r="C563" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D563" s="13">
         <v>1</v>
@@ -12518,13 +12518,13 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" s="10" t="s">
-        <v>604</v>
+        <v>550</v>
       </c>
       <c r="B564" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C564" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D564" s="13">
         <v>1</v>
@@ -12541,7 +12541,7 @@
         <v>0</v>
       </c>
       <c r="C565" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D565" s="13">
         <v>1</v>
@@ -12552,16 +12552,16 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" s="10" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B566" s="10" t="s">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="C566" s="10" t="s">
-        <v>304</v>
+        <v>672</v>
       </c>
       <c r="D566" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E566" s="1">
         <v>0</v>
@@ -12575,10 +12575,10 @@
         <v>511</v>
       </c>
       <c r="C567" s="10" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D567" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E567" s="1">
         <v>0</v>
@@ -12592,10 +12592,10 @@
         <v>511</v>
       </c>
       <c r="C568" s="10" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D568" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E568" s="1">
         <v>0</v>
@@ -12609,10 +12609,10 @@
         <v>511</v>
       </c>
       <c r="C569" s="10" t="s">
-        <v>674</v>
+        <v>535</v>
       </c>
       <c r="D569" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E569" s="1">
         <v>0</v>
@@ -12626,7 +12626,7 @@
         <v>511</v>
       </c>
       <c r="C570" s="10" t="s">
-        <v>535</v>
+        <v>675</v>
       </c>
       <c r="D570" s="13">
         <v>1</v>
@@ -12643,10 +12643,10 @@
         <v>511</v>
       </c>
       <c r="C571" s="10" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D571" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E571" s="1">
         <v>0</v>
@@ -12660,10 +12660,10 @@
         <v>511</v>
       </c>
       <c r="C572" s="10" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D572" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E572" s="1">
         <v>0</v>
@@ -12677,10 +12677,10 @@
         <v>511</v>
       </c>
       <c r="C573" s="10" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D573" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E573" s="1">
         <v>0</v>
@@ -12694,10 +12694,10 @@
         <v>511</v>
       </c>
       <c r="C574" s="10" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D574" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E574" s="1">
         <v>0</v>
@@ -12711,10 +12711,10 @@
         <v>511</v>
       </c>
       <c r="C575" s="10" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D575" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E575" s="1">
         <v>0</v>
@@ -12728,10 +12728,10 @@
         <v>511</v>
       </c>
       <c r="C576" s="10" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D576" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E576" s="1">
         <v>0</v>
@@ -12745,7 +12745,7 @@
         <v>511</v>
       </c>
       <c r="C577" s="10" t="s">
-        <v>681</v>
+        <v>536</v>
       </c>
       <c r="D577" s="13">
         <v>2</v>
@@ -12762,10 +12762,10 @@
         <v>511</v>
       </c>
       <c r="C578" s="10" t="s">
-        <v>536</v>
+        <v>669</v>
       </c>
       <c r="D578" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E578" s="1">
         <v>0</v>
@@ -12773,13 +12773,13 @@
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" s="10" t="s">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="B579" s="10" t="s">
         <v>511</v>
       </c>
       <c r="C579" s="10" t="s">
-        <v>669</v>
+        <v>537</v>
       </c>
       <c r="D579" s="13">
         <v>1</v>
@@ -12790,16 +12790,16 @@
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" s="10" t="s">
-        <v>604</v>
+        <v>550</v>
       </c>
       <c r="B580" s="10" t="s">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="C580" s="10" t="s">
-        <v>537</v>
+        <v>305</v>
       </c>
       <c r="D580" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E580" s="1">
         <v>0</v>
@@ -12807,16 +12807,16 @@
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581" s="10" t="s">
-        <v>550</v>
+        <v>604</v>
       </c>
       <c r="B581" s="10" t="s">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="C581" s="10" t="s">
-        <v>305</v>
+        <v>541</v>
       </c>
       <c r="D581" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E581" s="1">
         <v>0</v>
@@ -12824,16 +12824,16 @@
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" s="10" t="s">
-        <v>604</v>
+        <v>626</v>
       </c>
       <c r="B582" s="10" t="s">
-        <v>511</v>
+        <v>38</v>
       </c>
       <c r="C582" s="10" t="s">
-        <v>541</v>
+        <v>397</v>
       </c>
       <c r="D582" s="13">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E582" s="1">
         <v>0</v>
@@ -12847,10 +12847,10 @@
         <v>38</v>
       </c>
       <c r="C583" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D583" s="13">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E583" s="1">
         <v>0</v>
@@ -12858,16 +12858,16 @@
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" s="10" t="s">
-        <v>626</v>
+        <v>548</v>
       </c>
       <c r="B584" s="10" t="s">
-        <v>38</v>
+        <v>511</v>
       </c>
       <c r="C584" s="10" t="s">
-        <v>398</v>
+        <v>753</v>
       </c>
       <c r="D584" s="13">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E584" s="1">
         <v>0</v>
@@ -12881,7 +12881,7 @@
         <v>511</v>
       </c>
       <c r="C585" s="10" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D585" s="13">
         <v>3</v>
@@ -12898,10 +12898,10 @@
         <v>511</v>
       </c>
       <c r="C586" s="10" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D586" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E586" s="1">
         <v>0</v>
@@ -12915,10 +12915,10 @@
         <v>511</v>
       </c>
       <c r="C587" s="10" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D587" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E587" s="1">
         <v>0</v>
@@ -12926,16 +12926,16 @@
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588" s="10" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="B588" s="10" t="s">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="C588" s="10" t="s">
-        <v>758</v>
+        <v>306</v>
       </c>
       <c r="D588" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E588" s="1">
         <v>0</v>
@@ -12943,16 +12943,16 @@
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" s="10" t="s">
-        <v>542</v>
+        <v>650</v>
       </c>
       <c r="B589" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C589" s="10" t="s">
-        <v>306</v>
+        <v>768</v>
       </c>
       <c r="D589" s="13">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="E589" s="1">
         <v>0</v>
@@ -12960,16 +12960,16 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" s="10" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="B590" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C590" s="10" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D590" s="13">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E590" s="1">
         <v>0</v>
@@ -12983,10 +12983,10 @@
         <v>38</v>
       </c>
       <c r="C591" s="10" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="D591" s="13">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="E591" s="1">
         <v>0</v>
@@ -12994,16 +12994,16 @@
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A592" s="10" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B592" s="10" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C592" s="10" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="D592" s="13">
-        <v>2400</v>
+        <v>1</v>
       </c>
       <c r="E592" s="1">
         <v>0</v>
@@ -13017,10 +13017,10 @@
         <v>9</v>
       </c>
       <c r="C593" s="10" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D593" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E593" s="1">
         <v>0</v>
@@ -13034,10 +13034,10 @@
         <v>9</v>
       </c>
       <c r="C594" s="10" t="s">
-        <v>786</v>
+        <v>422</v>
       </c>
       <c r="D594" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E594" s="1">
         <v>0</v>
@@ -13051,10 +13051,10 @@
         <v>9</v>
       </c>
       <c r="C595" s="10" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="D595" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E595" s="1">
         <v>0</v>
@@ -13062,16 +13062,16 @@
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A596" s="10" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B596" s="10" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C596" s="10" t="s">
-        <v>508</v>
+        <v>770</v>
       </c>
       <c r="D596" s="13">
-        <v>1</v>
+        <v>1850</v>
       </c>
       <c r="E596" s="1">
         <v>0</v>
@@ -13079,16 +13079,16 @@
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A597" s="10" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="B597" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C597" s="10" t="s">
-        <v>772</v>
+        <v>307</v>
       </c>
       <c r="D597" s="13">
-        <v>1850</v>
+        <v>37</v>
       </c>
       <c r="E597" s="1">
         <v>0</v>
@@ -13096,16 +13096,16 @@
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A598" s="10" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="B598" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C598" s="10" t="s">
-        <v>307</v>
+        <v>771</v>
       </c>
       <c r="D598" s="13">
-        <v>37</v>
+        <v>2500</v>
       </c>
       <c r="E598" s="1">
         <v>0</v>
@@ -13119,10 +13119,10 @@
         <v>38</v>
       </c>
       <c r="C599" s="10" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="D599" s="13">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="E599" s="1">
         <v>0</v>
@@ -13130,16 +13130,16 @@
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A600" s="10" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="B600" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C600" s="10" t="s">
-        <v>780</v>
+        <v>720</v>
       </c>
       <c r="D600" s="13">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="E600" s="1">
         <v>0</v>
@@ -13153,10 +13153,10 @@
         <v>38</v>
       </c>
       <c r="C601" s="10" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D601" s="13">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="E601" s="1">
         <v>0</v>
@@ -13170,10 +13170,10 @@
         <v>38</v>
       </c>
       <c r="C602" s="10" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D602" s="13">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="E602" s="1">
         <v>0</v>
@@ -13187,10 +13187,10 @@
         <v>38</v>
       </c>
       <c r="C603" s="10" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D603" s="13">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="E603" s="1">
         <v>0</v>
@@ -13204,10 +13204,10 @@
         <v>38</v>
       </c>
       <c r="C604" s="10" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D604" s="13">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="E604" s="1">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>38</v>
       </c>
       <c r="C605" s="10" t="s">
-        <v>724</v>
+        <v>772</v>
       </c>
       <c r="D605" s="13">
-        <v>800</v>
+        <v>1250</v>
       </c>
       <c r="E605" s="1">
         <v>0</v>
@@ -13238,10 +13238,10 @@
         <v>38</v>
       </c>
       <c r="C606" s="10" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D606" s="13">
-        <v>1250</v>
+        <v>1550</v>
       </c>
       <c r="E606" s="1">
         <v>0</v>
@@ -13252,13 +13252,13 @@
         <v>650</v>
       </c>
       <c r="B607" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C607" s="10" t="s">
-        <v>775</v>
+        <v>308</v>
       </c>
       <c r="D607" s="13">
-        <v>1550</v>
+        <v>1070</v>
       </c>
       <c r="E607" s="1">
         <v>0</v>
@@ -13269,13 +13269,13 @@
         <v>650</v>
       </c>
       <c r="B608" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C608" s="10" t="s">
-        <v>308</v>
+        <v>774</v>
       </c>
       <c r="D608" s="13">
-        <v>1070</v>
+        <v>1700</v>
       </c>
       <c r="E608" s="1">
         <v>0</v>
@@ -13289,10 +13289,10 @@
         <v>38</v>
       </c>
       <c r="C609" s="10" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D609" s="13">
-        <v>1700</v>
+        <v>1000</v>
       </c>
       <c r="E609" s="1">
         <v>0</v>
@@ -13300,16 +13300,16 @@
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A610" s="10" t="s">
-        <v>650</v>
+        <v>558</v>
       </c>
       <c r="B610" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C610" s="10" t="s">
-        <v>777</v>
+        <v>309</v>
       </c>
       <c r="D610" s="13">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="E610" s="1">
         <v>0</v>
@@ -13323,10 +13323,10 @@
         <v>0</v>
       </c>
       <c r="C611" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D611" s="13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E611" s="1">
         <v>0</v>
@@ -13334,16 +13334,16 @@
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A612" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B612" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C612" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D612" s="13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E612" s="1">
         <v>0</v>
@@ -13357,7 +13357,7 @@
         <v>0</v>
       </c>
       <c r="C613" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D613" s="13">
         <v>1</v>
@@ -13368,16 +13368,16 @@
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A614" s="10" t="s">
-        <v>559</v>
+        <v>651</v>
       </c>
       <c r="B614" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C614" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D614" s="13">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E614" s="1">
         <v>0</v>
@@ -13385,16 +13385,16 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" s="10" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B615" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C615" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D615" s="13">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E615" s="1">
         <v>0</v>
@@ -13408,10 +13408,10 @@
         <v>0</v>
       </c>
       <c r="C616" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D616" s="13">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="E616" s="1">
         <v>0</v>
@@ -13419,16 +13419,16 @@
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" s="10" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B617" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C617" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D617" s="13">
-        <v>121</v>
+        <v>300</v>
       </c>
       <c r="E617" s="1">
         <v>0</v>
@@ -13439,7 +13439,7 @@
         <v>653</v>
       </c>
       <c r="B618" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C618" s="10" t="s">
         <v>316</v>
@@ -13453,13 +13453,13 @@
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A619" s="10" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B619" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C619" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D619" s="13">
         <v>300</v>
@@ -13470,16 +13470,16 @@
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A620" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B620" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C620" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D620" s="13">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E620" s="1">
         <v>0</v>
@@ -13487,16 +13487,16 @@
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A621" s="10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B621" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C621" s="10" t="s">
-        <v>318</v>
+        <v>446</v>
       </c>
       <c r="D621" s="13">
-        <v>310</v>
+        <v>43</v>
       </c>
       <c r="E621" s="1">
         <v>0</v>
@@ -13504,16 +13504,16 @@
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A622" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B622" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C622" s="10" t="s">
-        <v>446</v>
+        <v>319</v>
       </c>
       <c r="D622" s="13">
-        <v>43</v>
+        <v>250</v>
       </c>
       <c r="E622" s="1">
         <v>0</v>
@@ -13524,13 +13524,13 @@
         <v>654</v>
       </c>
       <c r="B623" s="10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C623" s="10" t="s">
         <v>319</v>
       </c>
       <c r="D623" s="13">
-        <v>250</v>
+        <v>-160</v>
       </c>
       <c r="E623" s="1">
         <v>0</v>
@@ -14034,13 +14034,13 @@
         <v>662</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C653" s="1" t="s">
         <v>336</v>
       </c>
       <c r="D653" s="14">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E653" s="1">
         <v>0</v>
@@ -14051,13 +14051,13 @@
         <v>662</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C654" s="1" t="s">
         <v>336</v>
       </c>
       <c r="D654" s="14">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E654" s="1">
         <v>0</v>
@@ -14442,13 +14442,13 @@
         <v>667</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C677" s="1" t="s">
         <v>352</v>
       </c>
       <c r="D677" s="14">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="E677" s="1">
         <v>0</v>
@@ -14459,13 +14459,13 @@
         <v>667</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C678" s="1" t="s">
         <v>352</v>
       </c>
       <c r="D678" s="14">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="E678" s="1">
         <v>0</v>
@@ -14612,13 +14612,13 @@
         <v>667</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C687" s="1" t="s">
         <v>357</v>
       </c>
       <c r="D687" s="14">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="E687" s="1">
         <v>0</v>
@@ -14629,13 +14629,13 @@
         <v>667</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C688" s="1" t="s">
         <v>357</v>
       </c>
       <c r="D688" s="14">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="E688" s="1">
         <v>0</v>
@@ -14663,13 +14663,13 @@
         <v>667</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C690" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D690" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E690" s="1">
         <v>0</v>
@@ -14680,13 +14680,13 @@
         <v>667</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C691" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D691" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E691" s="1">
         <v>0</v>
@@ -14697,13 +14697,13 @@
         <v>667</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C692" s="1" t="s">
         <v>360</v>
       </c>
       <c r="D692" s="14">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E692" s="1">
         <v>0</v>
@@ -14714,13 +14714,13 @@
         <v>667</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C693" s="1" t="s">
         <v>360</v>
       </c>
       <c r="D693" s="14">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="E693" s="1">
         <v>0</v>
